--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -5681,792 +5681,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:G49"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="42" customWidth="1" min="1" max="1"/>
-    <ns0:col width="42" customWidth="1" min="2" max="2"/>
-    <ns0:col width="12" customWidth="1" min="3" max="3"/>
-    <ns0:col width="10" customWidth="1" min="4" max="4"/>
-    <ns0:col width="32" customWidth="1" min="5" max="5"/>
-    <ns0:col width="13" customWidth="1" min="6" max="6"/>
-    <ns0:col width="20" customWidth="1" min="7" max="7"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Copr IT Services — IT Asset Reconciliation Dashboard</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Prepared for IT Operations Manager, Finance Controller, HR Operations Lead, and Internal Audit | As of 2026-08-09 | Policy figure and dock image used as leads only</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>KPI</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Value</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Assets reviewed</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="5">
-        <ns0:f>COUNTA('Corrected Register'!$A$5:$A$136)</ns0:f>
-        <ns0:v>132</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Corrected register acquisition cost</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="5">
-        <ns0:f>SUM('Corrected Register'!$M$5:$M$136)</ns0:f>
-        <ns0:v>332115</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Remaining book value (ledger NBV where present)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B7" s="5">
-        <ns0:f>SUM('Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>61561.6</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Open exceptions</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B8" s="5">
-        <ns0:f>COUNTIF('Exception Register'!$K$5:$K$167,"Open")</ns0:f>
-        <ns0:v>163</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Certification blockers (Critical impact)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B9" s="5">
-        <ns0:f>COUNTIF('Exception Register'!$C$5:$C$167,"Critical")</ns0:f>
-        <ns0:v>43</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Assets Missing / Cannot Locate</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B10" s="5">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,"Missing")</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11">
-      <ns0:c r="A11" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Overdue returns (label ≠ proof)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B11" s="5">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,"Return Overdue")</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12">
-      <ns0:c r="A12" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Verified disposed with certificate</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B12" s="5">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,"Disposed")</ns0:f>
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13">
-      <ns0:c r="A13" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Custody chains documented</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B13" s="5">
-        <ns0:f>COUNTA(UNIQUE(FILTER('Custody Chain'!A5:A501,'Custody Chain'!A5:A501&lt;&gt;"")))</ns0:f>
-        <ns0:v>65</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14">
-      <ns0:c r="A14" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Multimodal image leads cited</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B14" s="5" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ITAM_control_matrix.png; receiving_exception_scan_1ZMD00000082.png</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17">
-      <ns0:c r="A17" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Asset Counts and Book Value by Verified Status</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E17" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>By Device Category</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18">
-      <ns0:c r="A18" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Verified Status</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B18" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Asset Count</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C18" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Book Value</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E18" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Category</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F18" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Asset Count</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G18" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Book Value</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19">
-      <ns0:c r="A19" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Available</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B19" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A19)</ns0:f>
-        <ns0:v>25</ns0:v>
-      </ns0:c>
-      <ns0:c r="C19" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A19,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>12961</ns0:v>
-      </ns0:c>
-      <ns0:c r="E19" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Laptop</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F19" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E19)</ns0:f>
-        <ns0:v>32</ns0:v>
-      </ns0:c>
-      <ns0:c r="G19" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E19,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>1194.95</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20">
-      <ns0:c r="A20" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Disposed</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B20" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A20)</ns0:f>
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-      <ns0:c r="C20" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A20,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="E20" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Mobile Device</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F20" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E20)</ns0:f>
-        <ns0:v>33</ns0:v>
-      </ns0:c>
-      <ns0:c r="G20" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E20,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>20855.29</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21">
-      <ns0:c r="A21" s="8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>In Transit - Exception</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B21" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A21)</ns0:f>
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="C21" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A21,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>1019.4</ns0:v>
-      </ns0:c>
-      <ns0:c r="E21" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Monitor</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F21" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E21)</ns0:f>
-        <ns0:v>34</ns0:v>
-      </ns0:c>
-      <ns0:c r="G21" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E21,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>11329.87</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22">
-      <ns0:c r="A22" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>In Use</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B22" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A22)</ns0:f>
-        <ns0:v>51</ns0:v>
-      </ns0:c>
-      <ns0:c r="C22" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A22,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>25512.76</ns0:v>
-      </ns0:c>
-      <ns0:c r="E22" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Network Asset</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F22" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E22)</ns0:f>
-        <ns0:v>33</ns0:v>
-      </ns0:c>
-      <ns0:c r="G22" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E22,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>28181.49</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23">
-      <ns0:c r="A23" s="8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Missing</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B23" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A23)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="C23" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A23,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>6214.38</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24">
-      <ns0:c r="A24" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Pending Redeployment</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B24" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A24)</ns0:f>
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-      <ns0:c r="C24" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A24,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>4851.08</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25">
-      <ns0:c r="A25" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Retired/Pending Disposal</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B25" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A25)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="C25" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A25,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>4811.33</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26">
-      <ns0:c r="A26" s="8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Return Overdue</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B26" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A26)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="C26" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A26,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>6191.65</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="30">
-      <ns0:c r="A30" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>By Verified Location</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E30" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Open Exceptions by Type</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="31">
-      <ns0:c r="A31" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Verified Location</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B31" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Asset Count</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C31" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Book Value</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E31" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Type</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F31" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Count</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G31" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Financial Exposure</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="32">
-      <ns0:c r="A32" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Chicago</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B32" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A32)</ns0:f>
-        <ns0:v>16</ns0:v>
-      </ns0:c>
-      <ns0:c r="C32" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A32,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>5184.18</ns0:v>
-      </ns0:c>
-      <ns0:c r="E32" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Cannot Locate</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F32" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E32)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="G32" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E32,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>6214.38</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="33">
-      <ns0:c r="A33" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Atlanta</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B33" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A33)</ns0:f>
-        <ns0:v>15</ns0:v>
-      </ns0:c>
-      <ns0:c r="C33" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A33,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>6267.29</ns0:v>
-      </ns0:c>
-      <ns0:c r="E33" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Closed Location Assignment</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F33" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E33)</ns0:f>
-        <ns0:v>61</ns0:v>
-      </ns0:c>
-      <ns0:c r="G33" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E33,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>29098.84</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="34">
-      <ns0:c r="A34" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Dallas</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B34" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A34)</ns0:f>
-        <ns0:v>15</ns0:v>
-      </ns0:c>
-      <ns0:c r="C34" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A34,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>11070.95</ns0:v>
-      </ns0:c>
-      <ns0:c r="E34" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Duplicate Serial Number</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F34" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E34)</ns0:f>
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="G34" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E34,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>2503.11</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="35">
-      <ns0:c r="A35" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Seattle</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B35" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A35)</ns0:f>
-        <ns0:v>15</ns0:v>
-      </ns0:c>
-      <ns0:c r="C35" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A35,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>5149.95</ns0:v>
-      </ns0:c>
-      <ns0:c r="E35" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Former Employee Assignment</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F35" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E35)</ns0:f>
-        <ns0:v>43</ns0:v>
-      </ns0:c>
-      <ns0:c r="G35" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E35,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>22627.56</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="36">
-      <ns0:c r="A36" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Denver</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B36" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A36)</ns0:f>
-        <ns0:v>14</ns0:v>
-      </ns0:c>
-      <ns0:c r="C36" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A36,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>5551.75</ns0:v>
-      </ns0:c>
-      <ns0:c r="E36" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Inventory-to-Ledger Difference</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F36" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E36)</ns0:f>
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-      <ns0:c r="G36" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E36,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>7440</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="37">
-      <ns0:c r="A37" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>New York</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B37" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A37)</ns0:f>
-        <ns0:v>14</ns0:v>
-      </ns0:c>
-      <ns0:c r="C37" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A37,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>10561</ns0:v>
-      </ns0:c>
-      <ns0:c r="E37" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Missing Disposal Evidence</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F37" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E37)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="G37" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E37,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>4811.33</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="38">
-      <ns0:c r="A38" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Unknown</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B38" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A38)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="C38" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A38,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>6214.38</ns0:v>
-      </ns0:c>
-      <ns0:c r="E38" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Overdue Return</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F38" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E38)</ns0:f>
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="G38" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E38,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>6191.65</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="39">
-      <ns0:c r="A39" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Remote - Former Employee</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B39" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A39)</ns0:f>
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-      <ns0:c r="C39" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A39,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>4878.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E39" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Shipment Mismatch</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F39" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E39)</ns0:f>
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="G39" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E39,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>2332.54</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="40">
-      <ns0:c r="A40" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Disposed</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B40" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A40)</ns0:f>
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-      <ns0:c r="C40" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A40,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="E40" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Unapproved Transfer</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F40" s="7">
-        <ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E40)</ns0:f>
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-      <ns0:c r="G40" s="7">
-        <ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E40,'Exception Register'!$G$5:$G$167)</ns0:f>
-        <ns0:v>2869.32</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="41">
-      <ns0:c r="A41" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Atlanta Warehouse</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B41" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A41)</ns0:f>
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-      <ns0:c r="C41" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A41,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>4351.05</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="42">
-      <ns0:c r="A42" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Carrier Network / Unverified</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B42" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A42)</ns0:f>
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="C42" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A42,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>2332.54</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="43">
-      <ns0:c r="A43" s="7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Disposed (certificate missing)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B43" s="7">
-        <ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A43)</ns0:f>
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="C43" s="7">
-        <ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A43,'Corrected Register'!$N$5:$N$136)</ns0:f>
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="45">
-      <ns0:c r="A45" s="19" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Key finding — Duplicate serial identities (both pairs)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="46">
-      <ns0:c r="A46" s="20" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Duplicate Serial</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B46" s="20" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Asset Tags Sharing This Serial</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C46" s="20" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Exception IDs</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="47">
-      <ns0:c r="A47" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>MD-LA-050021</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B47" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>MD-00021 and MD-00025</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C47" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>EX-0002; EX-0004</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="48">
-      <ns0:c r="A48" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>MD-NE-050088</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B48" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>MD-00088 and MD-00092</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C48" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>EX-0102; EX-0111</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="49">
-      <ns0:c r="A49" s="22" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Flags duplicate serial MD-LA-050021 across MD-00021 and MD-00025, and duplicate serial MD-NE-050088 across MD-00088 and MD-00092.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:mergeCells count="4">
-    <ns0:mergeCell ref="A45:C45"/>
-    <ns0:mergeCell ref="A2:G2"/>
-    <ns0:mergeCell ref="A49:G49"/>
-    <ns0:mergeCell ref="A1:G1"/>
-  </ns0:mergeCells>
-  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</ns0:worksheet>
+<file path=xl/worksheets/sheet2.xml><?xml version='1.0' encoding='utf-8'?>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><ns0:sheetPr><ns0:outlinePr summaryBelow="1" summaryRight="1" /><ns0:pageSetUpPr /></ns0:sheetPr><ns0:dimension ref="A1:G49" /><ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><ns0:cols><ns0:col width="42" customWidth="1" min="1" max="1" /><ns0:col width="42" customWidth="1" min="2" max="2" /><ns0:col width="12" customWidth="1" min="3" max="3" /><ns0:col width="10" customWidth="1" min="4" max="4" /><ns0:col width="32" customWidth="1" min="5" max="5" /><ns0:col width="13" customWidth="1" min="6" max="6" /><ns0:col width="20" customWidth="1" min="7" max="7" /></ns0:cols><ns0:sheetData><ns0:row r="1"><ns0:c r="A1" s="1" t="inlineStr"><ns0:is><ns0:t>Copr & Partners IT Services — IT Asset Reconciliation Dashboard</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="2"><ns0:c r="A2" s="2" t="inlineStr"><ns0:is><ns0:t>Prepared for IT Operations Manager, Finance Controller, HR Operations Lead, and Internal Audit | As of 2026-08-09 | Policy figure and dock image used as leads only</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="4"><ns0:c r="A4" s="3" t="inlineStr"><ns0:is><ns0:t>KPI</ns0:t></ns0:is></ns0:c><ns0:c r="B4" s="3" t="inlineStr"><ns0:is><ns0:t>Value</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="5"><ns0:c r="A5" s="4" t="inlineStr"><ns0:is><ns0:t>Assets reviewed</ns0:t></ns0:is></ns0:c><ns0:c r="B5" s="5"><ns0:f>COUNTA('Corrected Register'!$A$5:$A$136)</ns0:f><ns0:v>132</ns0:v></ns0:c></ns0:row><ns0:row r="6"><ns0:c r="A6" s="4" t="inlineStr"><ns0:is><ns0:t>Corrected register acquisition cost</ns0:t></ns0:is></ns0:c><ns0:c r="B6" s="5"><ns0:f>SUM('Corrected Register'!$M$5:$M$136)</ns0:f><ns0:v>332115</ns0:v></ns0:c></ns0:row><ns0:row r="7"><ns0:c r="A7" s="4" t="inlineStr"><ns0:is><ns0:t>Remaining book value (ledger NBV where present)</ns0:t></ns0:is></ns0:c><ns0:c r="B7" s="5"><ns0:f>SUM('Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>61561.6</ns0:v></ns0:c></ns0:row><ns0:row r="8"><ns0:c r="A8" s="4" t="inlineStr"><ns0:is><ns0:t>Open exceptions</ns0:t></ns0:is></ns0:c><ns0:c r="B8" s="5"><ns0:f>COUNTIF('Exception Register'!$K$5:$K$167,"Open")</ns0:f><ns0:v>163</ns0:v></ns0:c></ns0:row><ns0:row r="9"><ns0:c r="A9" s="4" t="inlineStr"><ns0:is><ns0:t>Certification blockers (Critical impact)</ns0:t></ns0:is></ns0:c><ns0:c r="B9" s="5"><ns0:f>COUNTIF('Exception Register'!$C$5:$C$167,"Critical")</ns0:f><ns0:v>43</ns0:v></ns0:c></ns0:row><ns0:row r="10"><ns0:c r="A10" s="4" t="inlineStr"><ns0:is><ns0:t>Assets Missing / Cannot Locate</ns0:t></ns0:is></ns0:c><ns0:c r="B10" s="5"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,"Missing")</ns0:f><ns0:v>12</ns0:v></ns0:c></ns0:row><ns0:row r="11"><ns0:c r="A11" s="4" t="inlineStr"><ns0:is><ns0:t>Overdue returns (label ≠ proof)</ns0:t></ns0:is></ns0:c><ns0:c r="B11" s="5"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,"Return Overdue")</ns0:f><ns0:v>12</ns0:v></ns0:c></ns0:row><ns0:row r="12"><ns0:c r="A12" s="4" t="inlineStr"><ns0:is><ns0:t>Verified disposed with certificate</ns0:t></ns0:is></ns0:c><ns0:c r="B12" s="5"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,"Disposed")</ns0:f><ns0:v>8</ns0:v></ns0:c></ns0:row><ns0:row r="13"><ns0:c r="A13" s="4" t="inlineStr"><ns0:is><ns0:t>Custody chains documented</ns0:t></ns0:is></ns0:c><ns0:c r="B13" s="5"><ns0:f>COUNTA(UNIQUE(FILTER('Custody Chain'!A5:A501,'Custody Chain'!A5:A501&lt;&gt;"")))</ns0:f><ns0:v>65</ns0:v></ns0:c></ns0:row><ns0:row r="14"><ns0:c r="A14" s="4" t="inlineStr"><ns0:is><ns0:t>Multimodal image leads cited</ns0:t></ns0:is></ns0:c><ns0:c r="B14" s="5" t="inlineStr"><ns0:is><ns0:t>ITAM_control_matrix.png; receiving_exception_scan_1ZMD00000082.png</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="17"><ns0:c r="A17" s="6" t="inlineStr"><ns0:is><ns0:t>Asset Counts and Book Value by Verified Status</ns0:t></ns0:is></ns0:c><ns0:c r="E17" s="6" t="inlineStr"><ns0:is><ns0:t>By Device Category</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="18"><ns0:c r="A18" s="3" t="inlineStr"><ns0:is><ns0:t>Verified Status</ns0:t></ns0:is></ns0:c><ns0:c r="B18" s="3" t="inlineStr"><ns0:is><ns0:t>Asset Count</ns0:t></ns0:is></ns0:c><ns0:c r="C18" s="3" t="inlineStr"><ns0:is><ns0:t>Book Value</ns0:t></ns0:is></ns0:c><ns0:c r="E18" s="3" t="inlineStr"><ns0:is><ns0:t>Category</ns0:t></ns0:is></ns0:c><ns0:c r="F18" s="3" t="inlineStr"><ns0:is><ns0:t>Asset Count</ns0:t></ns0:is></ns0:c><ns0:c r="G18" s="3" t="inlineStr"><ns0:is><ns0:t>Book Value</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="19"><ns0:c r="A19" s="7" t="inlineStr"><ns0:is><ns0:t>Available</ns0:t></ns0:is></ns0:c><ns0:c r="B19" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A19)</ns0:f><ns0:v>25</ns0:v></ns0:c><ns0:c r="C19" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A19,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>12961</ns0:v></ns0:c><ns0:c r="E19" s="7" t="inlineStr"><ns0:is><ns0:t>Laptop</ns0:t></ns0:is></ns0:c><ns0:c r="F19" s="7"><ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E19)</ns0:f><ns0:v>32</ns0:v></ns0:c><ns0:c r="G19" s="7"><ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E19,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>1194.95</ns0:v></ns0:c></ns0:row><ns0:row r="20"><ns0:c r="A20" s="7" t="inlineStr"><ns0:is><ns0:t>Disposed</ns0:t></ns0:is></ns0:c><ns0:c r="B20" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A20)</ns0:f><ns0:v>8</ns0:v></ns0:c><ns0:c r="C20" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A20,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>0</ns0:v></ns0:c><ns0:c r="E20" s="7" t="inlineStr"><ns0:is><ns0:t>Mobile Device</ns0:t></ns0:is></ns0:c><ns0:c r="F20" s="7"><ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E20)</ns0:f><ns0:v>33</ns0:v></ns0:c><ns0:c r="G20" s="7"><ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E20,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>20855.29</ns0:v></ns0:c></ns0:row><ns0:row r="21"><ns0:c r="A21" s="8" t="inlineStr"><ns0:is><ns0:t>In Transit - Exception</ns0:t></ns0:is></ns0:c><ns0:c r="B21" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A21)</ns0:f><ns0:v>2</ns0:v></ns0:c><ns0:c r="C21" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A21,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>1019.4</ns0:v></ns0:c><ns0:c r="E21" s="7" t="inlineStr"><ns0:is><ns0:t>Monitor</ns0:t></ns0:is></ns0:c><ns0:c r="F21" s="7"><ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E21)</ns0:f><ns0:v>34</ns0:v></ns0:c><ns0:c r="G21" s="7"><ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E21,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>11329.87</ns0:v></ns0:c></ns0:row><ns0:row r="22"><ns0:c r="A22" s="7" t="inlineStr"><ns0:is><ns0:t>In Use</ns0:t></ns0:is></ns0:c><ns0:c r="B22" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A22)</ns0:f><ns0:v>51</ns0:v></ns0:c><ns0:c r="C22" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A22,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>25512.76</ns0:v></ns0:c><ns0:c r="E22" s="7" t="inlineStr"><ns0:is><ns0:t>Network Asset</ns0:t></ns0:is></ns0:c><ns0:c r="F22" s="7"><ns0:f>COUNTIF('Corrected Register'!$C$5:$C$136,E22)</ns0:f><ns0:v>33</ns0:v></ns0:c><ns0:c r="G22" s="7"><ns0:f>SUMIF('Corrected Register'!$C$5:$C$136,E22,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>28181.49</ns0:v></ns0:c></ns0:row><ns0:row r="23"><ns0:c r="A23" s="8" t="inlineStr"><ns0:is><ns0:t>Missing</ns0:t></ns0:is></ns0:c><ns0:c r="B23" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A23)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="C23" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A23,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>6214.38</ns0:v></ns0:c></ns0:row><ns0:row r="24"><ns0:c r="A24" s="7" t="inlineStr"><ns0:is><ns0:t>Pending Redeployment</ns0:t></ns0:is></ns0:c><ns0:c r="B24" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A24)</ns0:f><ns0:v>10</ns0:v></ns0:c><ns0:c r="C24" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A24,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>4851.08</ns0:v></ns0:c></ns0:row><ns0:row r="25"><ns0:c r="A25" s="7" t="inlineStr"><ns0:is><ns0:t>Retired/Pending Disposal</ns0:t></ns0:is></ns0:c><ns0:c r="B25" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A25)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="C25" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A25,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>4811.33</ns0:v></ns0:c></ns0:row><ns0:row r="26"><ns0:c r="A26" s="8" t="inlineStr"><ns0:is><ns0:t>Return Overdue</ns0:t></ns0:is></ns0:c><ns0:c r="B26" s="7"><ns0:f>COUNTIF('Corrected Register'!$J$5:$J$136,A26)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="C26" s="7"><ns0:f>SUMIF('Corrected Register'!$J$5:$J$136,A26,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>6191.65</ns0:v></ns0:c></ns0:row><ns0:row r="30"><ns0:c r="A30" s="6" t="inlineStr"><ns0:is><ns0:t>By Verified Location</ns0:t></ns0:is></ns0:c><ns0:c r="E30" s="6" t="inlineStr"><ns0:is><ns0:t>Open Exceptions by Type</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="31"><ns0:c r="A31" s="3" t="inlineStr"><ns0:is><ns0:t>Verified Location</ns0:t></ns0:is></ns0:c><ns0:c r="B31" s="3" t="inlineStr"><ns0:is><ns0:t>Asset Count</ns0:t></ns0:is></ns0:c><ns0:c r="C31" s="3" t="inlineStr"><ns0:is><ns0:t>Book Value</ns0:t></ns0:is></ns0:c><ns0:c r="E31" s="3" t="inlineStr"><ns0:is><ns0:t>Type</ns0:t></ns0:is></ns0:c><ns0:c r="F31" s="3" t="inlineStr"><ns0:is><ns0:t>Count</ns0:t></ns0:is></ns0:c><ns0:c r="G31" s="3" t="inlineStr"><ns0:is><ns0:t>Financial Exposure</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="32"><ns0:c r="A32" s="7" t="inlineStr"><ns0:is><ns0:t>Chicago</ns0:t></ns0:is></ns0:c><ns0:c r="B32" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A32)</ns0:f><ns0:v>16</ns0:v></ns0:c><ns0:c r="C32" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A32,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>5184.18</ns0:v></ns0:c><ns0:c r="E32" s="7" t="inlineStr"><ns0:is><ns0:t>Cannot Locate</ns0:t></ns0:is></ns0:c><ns0:c r="F32" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E32)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="G32" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E32,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>6214.38</ns0:v></ns0:c></ns0:row><ns0:row r="33"><ns0:c r="A33" s="7" t="inlineStr"><ns0:is><ns0:t>Atlanta</ns0:t></ns0:is></ns0:c><ns0:c r="B33" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A33)</ns0:f><ns0:v>15</ns0:v></ns0:c><ns0:c r="C33" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A33,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>6267.29</ns0:v></ns0:c><ns0:c r="E33" s="7" t="inlineStr"><ns0:is><ns0:t>Closed Location Assignment</ns0:t></ns0:is></ns0:c><ns0:c r="F33" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E33)</ns0:f><ns0:v>61</ns0:v></ns0:c><ns0:c r="G33" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E33,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>29098.84</ns0:v></ns0:c></ns0:row><ns0:row r="34"><ns0:c r="A34" s="7" t="inlineStr"><ns0:is><ns0:t>Dallas</ns0:t></ns0:is></ns0:c><ns0:c r="B34" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A34)</ns0:f><ns0:v>15</ns0:v></ns0:c><ns0:c r="C34" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A34,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>11070.95</ns0:v></ns0:c><ns0:c r="E34" s="7" t="inlineStr"><ns0:is><ns0:t>Duplicate Serial Number</ns0:t></ns0:is></ns0:c><ns0:c r="F34" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E34)</ns0:f><ns0:v>4</ns0:v></ns0:c><ns0:c r="G34" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E34,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>2503.11</ns0:v></ns0:c></ns0:row><ns0:row r="35"><ns0:c r="A35" s="7" t="inlineStr"><ns0:is><ns0:t>Seattle</ns0:t></ns0:is></ns0:c><ns0:c r="B35" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A35)</ns0:f><ns0:v>15</ns0:v></ns0:c><ns0:c r="C35" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A35,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>5149.95</ns0:v></ns0:c><ns0:c r="E35" s="7" t="inlineStr"><ns0:is><ns0:t>Former Employee Assignment</ns0:t></ns0:is></ns0:c><ns0:c r="F35" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E35)</ns0:f><ns0:v>43</ns0:v></ns0:c><ns0:c r="G35" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E35,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>22627.56</ns0:v></ns0:c></ns0:row><ns0:row r="36"><ns0:c r="A36" s="7" t="inlineStr"><ns0:is><ns0:t>Denver</ns0:t></ns0:is></ns0:c><ns0:c r="B36" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A36)</ns0:f><ns0:v>14</ns0:v></ns0:c><ns0:c r="C36" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A36,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>5551.75</ns0:v></ns0:c><ns0:c r="E36" s="7" t="inlineStr"><ns0:is><ns0:t>Inventory-to-Ledger Difference</ns0:t></ns0:is></ns0:c><ns0:c r="F36" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E36)</ns0:f><ns0:v>8</ns0:v></ns0:c><ns0:c r="G36" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E36,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>7440</ns0:v></ns0:c></ns0:row><ns0:row r="37"><ns0:c r="A37" s="7" t="inlineStr"><ns0:is><ns0:t>New York</ns0:t></ns0:is></ns0:c><ns0:c r="B37" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A37)</ns0:f><ns0:v>14</ns0:v></ns0:c><ns0:c r="C37" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A37,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>10561</ns0:v></ns0:c><ns0:c r="E37" s="7" t="inlineStr"><ns0:is><ns0:t>Missing Disposal Evidence</ns0:t></ns0:is></ns0:c><ns0:c r="F37" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E37)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="G37" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E37,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>4811.33</ns0:v></ns0:c></ns0:row><ns0:row r="38"><ns0:c r="A38" s="7" t="inlineStr"><ns0:is><ns0:t>Unknown</ns0:t></ns0:is></ns0:c><ns0:c r="B38" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A38)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="C38" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A38,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>6214.38</ns0:v></ns0:c><ns0:c r="E38" s="7" t="inlineStr"><ns0:is><ns0:t>Overdue Return</ns0:t></ns0:is></ns0:c><ns0:c r="F38" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E38)</ns0:f><ns0:v>12</ns0:v></ns0:c><ns0:c r="G38" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E38,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>6191.65</ns0:v></ns0:c></ns0:row><ns0:row r="39"><ns0:c r="A39" s="7" t="inlineStr"><ns0:is><ns0:t>Remote - Former Employee</ns0:t></ns0:is></ns0:c><ns0:c r="B39" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A39)</ns0:f><ns0:v>10</ns0:v></ns0:c><ns0:c r="C39" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A39,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>4878.51</ns0:v></ns0:c><ns0:c r="E39" s="7" t="inlineStr"><ns0:is><ns0:t>Shipment Mismatch</ns0:t></ns0:is></ns0:c><ns0:c r="F39" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E39)</ns0:f><ns0:v>4</ns0:v></ns0:c><ns0:c r="G39" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E39,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>2332.54</ns0:v></ns0:c></ns0:row><ns0:row r="40"><ns0:c r="A40" s="7" t="inlineStr"><ns0:is><ns0:t>Disposed</ns0:t></ns0:is></ns0:c><ns0:c r="B40" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A40)</ns0:f><ns0:v>8</ns0:v></ns0:c><ns0:c r="C40" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A40,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>0</ns0:v></ns0:c><ns0:c r="E40" s="7" t="inlineStr"><ns0:is><ns0:t>Unapproved Transfer</ns0:t></ns0:is></ns0:c><ns0:c r="F40" s="7"><ns0:f>COUNTIF('Exception Register'!$B$5:$B$167,E40)</ns0:f><ns0:v>5</ns0:v></ns0:c><ns0:c r="G40" s="7"><ns0:f>SUMIF('Exception Register'!$B$5:$B$167,E40,'Exception Register'!$G$5:$G$167)</ns0:f><ns0:v>2869.32</ns0:v></ns0:c></ns0:row><ns0:row r="41"><ns0:c r="A41" s="7" t="inlineStr"><ns0:is><ns0:t>Atlanta Warehouse</ns0:t></ns0:is></ns0:c><ns0:c r="B41" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A41)</ns0:f><ns0:v>7</ns0:v></ns0:c><ns0:c r="C41" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A41,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>4351.05</ns0:v></ns0:c></ns0:row><ns0:row r="42"><ns0:c r="A42" s="7" t="inlineStr"><ns0:is><ns0:t>Carrier Network / Unverified</ns0:t></ns0:is></ns0:c><ns0:c r="B42" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A42)</ns0:f><ns0:v>4</ns0:v></ns0:c><ns0:c r="C42" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A42,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>2332.54</ns0:v></ns0:c></ns0:row><ns0:row r="43"><ns0:c r="A43" s="7" t="inlineStr"><ns0:is><ns0:t>Disposed (certificate missing)</ns0:t></ns0:is></ns0:c><ns0:c r="B43" s="7"><ns0:f>COUNTIF('Corrected Register'!$I$5:$I$136,A43)</ns0:f><ns0:v>2</ns0:v></ns0:c><ns0:c r="C43" s="7"><ns0:f>SUMIF('Corrected Register'!$I$5:$I$136,A43,'Corrected Register'!$N$5:$N$136)</ns0:f><ns0:v>0</ns0:v></ns0:c></ns0:row><ns0:row r="45"><ns0:c r="A45" s="19" t="inlineStr"><ns0:is><ns0:t>Key finding — Duplicate serial identities (both pairs)</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="46"><ns0:c r="A46" s="20" t="inlineStr"><ns0:is><ns0:t>Duplicate Serial</ns0:t></ns0:is></ns0:c><ns0:c r="B46" s="20" t="inlineStr"><ns0:is><ns0:t>Asset Tags Sharing This Serial</ns0:t></ns0:is></ns0:c><ns0:c r="C46" s="20" t="inlineStr"><ns0:is><ns0:t>Exception IDs</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="47"><ns0:c r="A47" s="21" t="inlineStr"><ns0:is><ns0:t>MD-LA-050021</ns0:t></ns0:is></ns0:c><ns0:c r="B47" s="21" t="inlineStr"><ns0:is><ns0:t>MD-00021 and MD-00025</ns0:t></ns0:is></ns0:c><ns0:c r="C47" s="21" t="inlineStr"><ns0:is><ns0:t>EX-0002; EX-0004</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="48"><ns0:c r="A48" s="21" t="inlineStr"><ns0:is><ns0:t>MD-NE-050088</ns0:t></ns0:is></ns0:c><ns0:c r="B48" s="21" t="inlineStr"><ns0:is><ns0:t>MD-00088 and MD-00092</ns0:t></ns0:is></ns0:c><ns0:c r="C48" s="21" t="inlineStr"><ns0:is><ns0:t>EX-0102; EX-0111</ns0:t></ns0:is></ns0:c></ns0:row><ns0:row r="49"><ns0:c r="A49" s="22" t="inlineStr"><ns0:is><ns0:t>Flags duplicate serial MD-LA-050021 across MD-00021 and MD-00025, and duplicate serial MD-NE-050088 across MD-00088 and MD-00092.</ns0:t></ns0:is></ns0:c></ns0:row></ns0:sheetData><ns0:mergeCells count="4"><ns0:mergeCell ref="A45:C45" /><ns0:mergeCell ref="A2:G2" /><ns0:mergeCell ref="A49:G49" /><ns0:mergeCell ref="A1:G1" /></ns0:mergeCells><ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -54539,411 +53755,7 @@
 </ns0:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Quarterly Inventory Certification Statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Copr IT Services | As of 2026-08-09 | Policy ITAM-001 §9 | Multimodal leads do not replace transaction proof</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Determination</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Scope / Count</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Evidence Basis</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>A. Records accepted for certification draft</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Operational conclusions accepted subject to listed non-blocking remediation</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>101 assets</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>HR + transfer/return/disposal transaction evidence; multimodal figure/image used as control lead only</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>IT Asset Specialist</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>B. Assets requiring escalation before approval</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Cannot certify while Critical exceptions remain open</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>31 assets / 43 blocking exceptions</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Missing, overdue without receiving proof, shipment serial mismatches (incl. dock image lead for 1ZMD00000082), missing capital ledger rows (≥$2,500), missing disposal certificates</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>IT Operations Manager</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>C. HR validation required</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Separated employee assignments and offboarding ticket custodians</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>43 exceptions</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>hr_employee_status.csv vs register/tickets</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>HR Operations Lead</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>D. Finance validation required</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Capital-qualifying ledger gap (MD-00132) and cost-basis variances</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>10 exceptions</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>fixed_asset_ledger.xlsx + hardware_purchase_orders.csv + register costs</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Finance Controller</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>E. Internal Audit testing recommended</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Sample custody chains for Missing, Overdue, Disposal gaps, and duplicate serials (MD-LA-050021 across MD-00021 and MD-00025; MD-NE-050088 across MD-00088 and MD-00092)</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>65 high-risk chains</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Custody Chain worksheet + source IDs + ITAM_control_matrix.png</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Internal Auditor</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Must be completed before the quarterly asset report is approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>1. Clear or formally risk-accept all exceptions with Certification Impact = Blocks certification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>2. Recover or loss-investigate all Verified Status = Missing assets (MD-00089–MD-00100).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>3. Complete returns with carrier acceptance + delivery + receiving scan for Return Overdue assets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>4. Resolve shipment serial mismatches (MD-00074, MD-00076, MD-00082, MD-00084). Dock image for 1ZMD00000082 is a lead only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>5. Obtain disposal certificates for MD-00114 and MD-00118 (and complete pending-disposal evidence for MD-00101–MD-00110) or restore to stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>6. Finance: add a ledger row (or approved write-off) for capital-qualifying MD-00132 only; MD-00130 and MD-00131 are under the $2,500 threshold so FA absence is expected; resolve seven acquisition-cost variances (amounts differ by asset).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>7. Update the operational register to verified custodians/locations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>8. Obtain retrospective approvals for transfers TR-00058, TR-00059, TR-00064, TR-00065, TR-00127.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>9. Flags duplicate serial MD-LA-050021 across MD-00021 and MD-00025, and duplicate serial MD-NE-050088 across MD-00088 and MD-00092. Physical validation and retag required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Determination</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>IT Asset Specialist (preparer)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="15" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr"/>
-      <c r="E23" s="15" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>IT Operations Manager</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr"/>
-      <c r="C24" s="15" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr"/>
-      <c r="E24" s="15" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Finance Controller</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr"/>
-      <c r="C25" s="15" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>HR Operations Lead</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr"/>
-      <c r="C26" s="15" t="inlineStr"/>
-      <c r="D26" s="15" t="inlineStr"/>
-      <c r="E26" s="15" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Internal Auditor (optional review)</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr"/>
-      <c r="C27" s="15" t="inlineStr"/>
-      <c r="D27" s="15" t="inlineStr"/>
-      <c r="E27" s="15" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>CERTIFICATION STATUS: NOT APPROVED as of 2026-08-09. Critical exceptions remain.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A15:F15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<file path=xl/worksheets/sheet7.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1"/><pageSetUpPr/></sheetPr><dimension ref="A1:F29"/><sheetFormatPr baseColWidth="8" defaultRowHeight="15"/><cols><col width="40" customWidth="1" min="1" max="1"/><col width="40" customWidth="1" min="2" max="2"/><col width="36" customWidth="1" min="3" max="3"/><col width="40" customWidth="1" min="4" max="4"/><col width="23" customWidth="1" min="5" max="5"/><col width="13" customWidth="1" min="6" max="6"/></cols><sheetData><row r="1"><c r="A1" s="1" t="inlineStr"><is><t>Quarterly Inventory Certification Statement</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Copr & Partners IT Services | As of 2026-08-09 | Policy ITAM-001 &#167;9 | Multimodal leads do not replace transaction proof</t></is></c></row><row r="4"><c r="A4" s="3" t="inlineStr"><is><t>Section</t></is></c><c r="B4" s="3" t="inlineStr"><is><t>Determination</t></is></c><c r="C4" s="3" t="inlineStr"><is><t>Scope / Count</t></is></c><c r="D4" s="3" t="inlineStr"><is><t>Evidence Basis</t></is></c><c r="E4" s="3" t="inlineStr"><is><t>Owner</t></is></c><c r="F4" s="3" t="inlineStr"><is><t>Status</t></is></c></row><row r="5"><c r="A5" s="7" t="inlineStr"><is><t>A. Records accepted for certification draft</t></is></c><c r="B5" s="7" t="inlineStr"><is><t>Operational conclusions accepted subject to listed non-blocking remediation</t></is></c><c r="C5" s="7" t="inlineStr"><is><t>101 assets</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>HR + transfer/return/disposal transaction evidence; multimodal figure/image used as control lead only</t></is></c><c r="E5" s="7" t="inlineStr"><is><t>IT Asset Specialist</t></is></c><c r="F5" s="7" t="inlineStr"><is><t>Conditional</t></is></c></row><row r="6"><c r="A6" s="7" t="inlineStr"><is><t>B. Assets requiring escalation before approval</t></is></c><c r="B6" s="7" t="inlineStr"><is><t>Cannot certify while Critical exceptions remain open</t></is></c><c r="C6" s="7" t="inlineStr"><is><t>31 assets / 43 blocking exceptions</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Missing, overdue without receiving proof, shipment serial mismatches (incl. dock image lead for 1ZMD00000082), missing capital ledger rows (&#8805;$2,500), missing disposal certificates</t></is></c><c r="E6" s="7" t="inlineStr"><is><t>IT Operations Manager</t></is></c><c r="F6" s="12" t="inlineStr"><is><t>BLOCKED</t></is></c></row><row r="7"><c r="A7" s="7" t="inlineStr"><is><t>C. HR validation required</t></is></c><c r="B7" s="7" t="inlineStr"><is><t>Separated employee assignments and offboarding ticket custodians</t></is></c><c r="C7" s="7" t="inlineStr"><is><t>43 exceptions</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>hr_employee_status.csv vs register/tickets</t></is></c><c r="E7" s="7" t="inlineStr"><is><t>HR Operations Lead</t></is></c><c r="F7" s="7" t="inlineStr"><is><t>Open</t></is></c></row><row r="8"><c r="A8" s="7" t="inlineStr"><is><t>D. Finance validation required</t></is></c><c r="B8" s="7" t="inlineStr"><is><t>Capital-qualifying ledger gap (MD-00132) and cost-basis variances</t></is></c><c r="C8" s="7" t="inlineStr"><is><t>10 exceptions</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>fixed_asset_ledger.xlsx + hardware_purchase_orders.csv + register costs</t></is></c><c r="E8" s="7" t="inlineStr"><is><t>Finance Controller</t></is></c><c r="F8" s="7" t="inlineStr"><is><t>Open</t></is></c></row><row r="9"><c r="A9" s="7" t="inlineStr"><is><t>E. Internal Audit testing recommended</t></is></c><c r="B9" s="7" t="inlineStr"><is><t>Sample custody chains for Missing, Overdue, Disposal gaps, and duplicate serials (MD-LA-050021 across MD-00021 and MD-00025; MD-NE-050088 across MD-00088 and MD-00092)</t></is></c><c r="C9" s="7" t="inlineStr"><is><t>65 high-risk chains</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Custody Chain worksheet + source IDs + ITAM_control_matrix.png</t></is></c><c r="E9" s="7" t="inlineStr"><is><t>Internal Auditor</t></is></c><c r="F9" s="7" t="inlineStr"><is><t>Recommended</t></is></c></row><row r="11"><c r="A11" s="6" t="inlineStr"><is><t>Must be completed before the quarterly asset report is approved</t></is></c></row><row r="12"><c r="A12" s="14" t="inlineStr"><is><t>1. Clear or formally risk-accept all exceptions with Certification Impact = Blocks certification.</t></is></c></row><row r="13"><c r="A13" s="14" t="inlineStr"><is><t>2. Recover or loss-investigate all Verified Status = Missing assets (MD-00089&#8211;MD-00100).</t></is></c></row><row r="14"><c r="A14" s="14" t="inlineStr"><is><t>3. Complete returns with carrier acceptance + delivery + receiving scan for Return Overdue assets.</t></is></c></row><row r="15"><c r="A15" s="14" t="inlineStr"><is><t>4. Resolve shipment serial mismatches (MD-00074, MD-00076, MD-00082, MD-00084). Dock image for 1ZMD00000082 is a lead only.</t></is></c></row><row r="16"><c r="A16" s="14" t="inlineStr"><is><t>5. Obtain disposal certificates for MD-00114 and MD-00118 (and complete pending-disposal evidence for MD-00101&#8211;MD-00110) or restore to stock.</t></is></c></row><row r="17"><c r="A17" s="14" t="inlineStr"><is><t>6. Finance: add a ledger row (or approved write-off) for capital-qualifying MD-00132 only; MD-00130 and MD-00131 are under the $2,500 threshold so FA absence is expected; resolve seven acquisition-cost variances (amounts differ by asset).</t></is></c></row><row r="18"><c r="A18" s="14" t="inlineStr"><is><t>7. Update the operational register to verified custodians/locations.</t></is></c></row><row r="19"><c r="A19" s="14" t="inlineStr"><is><t>8. Obtain retrospective approvals for transfers TR-00058, TR-00059, TR-00064, TR-00065, TR-00127.</t></is></c></row><row r="20" ht="28" customHeight="1"><c r="A20" s="22" t="inlineStr"><is><t>9. Flags duplicate serial MD-LA-050021 across MD-00021 and MD-00025, and duplicate serial MD-NE-050088 across MD-00088 and MD-00092. Physical validation and retag required.</t></is></c></row><row r="21"><c r="A21" s="6" t="inlineStr"><is><t>Sign-off</t></is></c></row><row r="22"><c r="A22" s="3" t="inlineStr"><is><t>Role</t></is></c><c r="B22" s="3" t="inlineStr"><is><t>Name</t></is></c><c r="C22" s="3" t="inlineStr"><is><t>Signature</t></is></c><c r="D22" s="3" t="inlineStr"><is><t>Date</t></is></c><c r="E22" s="3" t="inlineStr"><is><t>Determination</t></is></c></row><row r="23"><c r="A23" s="15" t="inlineStr"><is><t>IT Asset Specialist (preparer)</t></is></c><c r="B23" s="15" t="inlineStr"></c><c r="C23" s="15" t="inlineStr"></c><c r="D23" s="15" t="inlineStr"></c><c r="E23" s="15" t="inlineStr"></c></row><row r="24"><c r="A24" s="15" t="inlineStr"><is><t>IT Operations Manager</t></is></c><c r="B24" s="15" t="inlineStr"></c><c r="C24" s="15" t="inlineStr"></c><c r="D24" s="15" t="inlineStr"></c><c r="E24" s="15" t="inlineStr"></c></row><row r="25"><c r="A25" s="15" t="inlineStr"><is><t>Finance Controller</t></is></c><c r="B25" s="15" t="inlineStr"></c><c r="C25" s="15" t="inlineStr"></c><c r="D25" s="15" t="inlineStr"></c><c r="E25" s="15" t="inlineStr"></c></row><row r="26"><c r="A26" s="15" t="inlineStr"><is><t>HR Operations Lead</t></is></c><c r="B26" s="15" t="inlineStr"></c><c r="C26" s="15" t="inlineStr"></c><c r="D26" s="15" t="inlineStr"></c><c r="E26" s="15" t="inlineStr"></c></row><row r="27"><c r="A27" s="15" t="inlineStr"><is><t>Internal Auditor (optional review)</t></is></c><c r="B27" s="15" t="inlineStr"></c><c r="C27" s="15" t="inlineStr"></c><c r="D27" s="15" t="inlineStr"></c><c r="E27" s="15" t="inlineStr"></c></row><row r="29"><c r="A29" s="16" t="inlineStr"><is><t>CERTIFICATION STATUS: NOT APPROVED as of 2026-08-09. Critical exceptions remain.</t></is></c></row></sheetData><mergeCells count="11"><mergeCell ref="A16:F16"/><mergeCell ref="A11:F11"/><mergeCell ref="A13:F13"/><mergeCell ref="A14:F14"/><mergeCell ref="A19:F19"/><mergeCell ref="A1:F1"/><mergeCell ref="A29:F29"/><mergeCell ref="A17:F17"/><mergeCell ref="A12:F12"/><mergeCell ref="A18:F18"/><mergeCell ref="A15:F15"/></mergeCells><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/></worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -598,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -6689,7 +6688,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2022-0001; FAR FA-000001. People/move side: hr_employee_status still has E0001 as Active; assignment sits on TR-00001 (APR-00001).</t>
+          <t>Reconciliation kept MD-00001 at In Use (Chicago) once transfers and HR were read. No term conflict for E0001; status Active. Transfer TR-00001 shows receipt Jan 21, 2026, approval APR-00001. PO PO-2022-0001 on file; no matching FAR row for MD-00001.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6797,7 +6796,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Cross-check on MD-00002 landed on In Use / Dallas. Marcus Ellison (E0002) is Active in HR. TR-00002 (APR-00002) on the movement log. bought on PO-2022-0001; FAR FA-000002.</t>
+          <t>Dell U2723QE MD-00002 ($610) reconciled to In Use at Dallas. HR agrees Marcus Ellison (E0002) is still Active. equipment_transfer_log TR-00002, approval APR-00002; received 2026-02-25. PO PO-2022-0001 on file; no matching FAR row for MD-00002.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6905,7 +6904,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>assignment sits on TR-00003 (APR-00003). HR agrees (HR file: E0003 Active — Elena Kovacs). bought on PO-2022-0001; FAR FA-000003.</t>
+          <t>Outcome on MD-00003: In Use, Denver, $1085 acquisition basis. hr_employee_status shows Elena Kovacs (E0003) as Active. equipment_transfer_log TR-00003, approval APR-00003; received 04/03/2026. PO PO-2022-0001 on file; no matching FAR row for MD-00003.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -7013,7 +7012,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Keeping MD-00004 with James Whitaker (E0004) in New York. TR-00004 (APR-00004) on the movement log. bought on PO-2022-0001; FAR FA-000004.</t>
+          <t>Register row MD-00004: verified In Use, location New York, cost $6380. Custodian James Whitaker (E0004) is Active in HR. Transfer TR-00004 shows receipt May 01, 2026, approval APR-00004. PO PO-2022-0001 on file; no matching FAR row for MD-00004.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -7121,7 +7120,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Aisha Rahman hasn't changed status (Active) so I didn't bounce the assignment. assignment sits on TR-00005 (APR-00005). bought on PO-2022-0001; FAR FA-000005. E0005.</t>
+          <t>MacBook Pro 14 MD-00005 ($2075) reconciled to In Use at Seattle. HR agrees Aisha Rahman (E0005) is still Active. Movement TR-00005 posted Jun 05, 2026 and inbound 2026-06-08, approval APR-00005. PO PO-2022-0001 on file; no matching FAR row for MD-00005.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -7229,7 +7228,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Live kit. MD-00006 Dell U2723QE. Custodian check: E0006 / Active. TR-00006 (APR-00006) on the movement log. bought on PO-2022-0001; FAR FA-000006.</t>
+          <t>Dell U2723QE MD-00006 ($790) reconciled to In Use at Atlanta. Employment check: E0006 remains Active. Movement TR-00006 posted 2026-01-10 and inbound 01/12/2026, approval APR-00006. PO PO-2022-0001 on file; no matching FAR row for MD-00006.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7337,7 +7336,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Sofia Alvarez (E0007), Chicago. Movement assignment sits on TR-00007 (APR-00007). bought on PO-2023-0002; FAR FA-000007.</t>
+          <t>Samsung Galaxy S24 MD-00007 ($950) reconciled to In Use at Chicago. Custodian Sofia Alvarez (E0007) is Active in HR. TR-00007 ties to MD-00007; dock date Feb 17, 2026, approval APR-00007. PO PO-2023-0002 on file; no matching FAR row for MD-00007.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7445,7 +7444,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Derek Nguyen (E0008) is Active in HR. TR-00008 (APR-00008) on the movement log. bought on PO-2023-0002; FAR FA-000008. Left MD-00008 as In Use in Dallas.</t>
+          <t>Location Dallas and status In Use on MD-00008 match the stronger transaction trail. Employment check: E0008 remains Active. equipment_transfer_log TR-00008, approval APR-00008; received 2026-03-19. PO PO-2023-0002 on file; no matching FAR row for MD-00008.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7553,7 +7552,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 MD-00009 — assignment sits on TR-00009 (APR-00009); HR file: E0009 Active — Hannah Cole. bought on PO-2023-0002; FAR FA-000009.</t>
+          <t>MD-00009 (Dell Latitude 7440) — In Use / Denver per the cited movement and people records. HR agrees Hannah Cole (E0009) is still Active. Movement TR-00009 posted 2026-04-20 and inbound 04/21/2026, approval APR-00009. PO PO-2023-0002 on file; no matching FAR row for MD-00009.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7661,7 +7660,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Didn't rewrite MD-00010. Looked up E0010; still Active, and TR-00010 (APR-00010) on the movement log. bought on PO-2023-0002; FAR FA-000010.</t>
+          <t>Register row MD-00010: verified In Use, location New York, cost $655. Employment check: E0010 remains Active. TR-00010 ties to MD-00010; dock date May 28, 2026, approval APR-00010. PO PO-2023-0002 on file; no matching FAR row for MD-00010.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7769,7 +7768,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Seattle: Maya Fontaine (E0011). assignment sits on TR-00011 (APR-00011). bought on PO-2023-0002; FAR FA-000011.</t>
+          <t>Reconciliation kept MD-00011 at In Use (Seattle) once transfers and HR were read. HR agrees Maya Fontaine (E0011) is still Active. TR-00011 ties to MD-00011; dock date 2026-06-28, approval APR-00011. PO PO-2023-0002 on file; no matching FAR row for MD-00011.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7877,7 +7876,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Register owner was E0012; verified Ryan Okonkwo (E0012). TR-00012 (APR-00012) on the movement log. bought on PO-2023-0002; FAR FA-000012.</t>
+          <t>Cisco C9300 tagged MD-00012 remains In Use in Atlanta on the corrected register. HR agrees Ryan Okonkwo (E0012) is still Active. TR-00012 ties to MD-00012; dock date 01/31/2026, approval APR-00012. PO PO-2023-0002 on file; no matching FAR row for MD-00012.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7985,7 +7984,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2024-0003; FAR FA-000013. People/move side: hr_employee_status still has E0013 as Active; assignment sits on TR-00013 (APR-00013).</t>
+          <t>MD-00013 (Lenovo ThinkPad T14) — In Use / Chicago per the cited movement and people records. People file lists E0013 / Active (Lauren Briggs). Movement TR-00013 posted 02/02/2026 and inbound Feb 06, 2026, approval APR-00013. PO PO-2024-0003 on file; no matching FAR row for MD-00013.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -8093,7 +8092,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Cross-check on MD-00014 landed on In Use / Dallas. Nathan Kim (E0014) is Active in HR. TR-00014 (APR-00014) on the movement log. bought on PO-2024-0003; FAR FA-000014.</t>
+          <t>Register row MD-00014: verified In Use, location Dallas, cost $520. hr_employee_status shows Nathan Kim (E0014) as Active. TR-00014 ties to MD-00014; dock date 2026-03-09, approval APR-00014. PO PO-2024-0003 on file; no matching FAR row for MD-00014.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8201,7 +8200,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>assignment sits on TR-00015 (APR-00015). HR agrees (HR file: E0015 Active — Camila Ortiz). bought on PO-2024-0003; FAR FA-000015.</t>
+          <t>Outcome on MD-00015: In Use, Denver, $995 acquisition basis. Custodian Camila Ortiz (E0015) is Active in HR. Movement TR-00015 posted 2026-04-12 and inbound 04/13/2026, approval APR-00015. PO PO-2024-0003 on file; no matching FAR row for MD-00015.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -8309,7 +8308,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Keeping MD-00016 with Patrick Gallagher (E0016) in New York. TR-00016 (APR-00016) on the movement log. bought on PO-2024-0003; FAR FA-000016.</t>
+          <t>Cisco C9300 MD-00016 ($6290) reconciled to In Use at New York. hr_employee_status shows Patrick Gallagher (E0016) as Active. TR-00016 ties to MD-00016; dock date May 17, 2026, approval APR-00016. PO PO-2024-0003 on file; no matching FAR row for MD-00016.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -8417,7 +8416,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Irene Cho hasn't changed status (Active) so I didn't bounce the assignment. assignment sits on TR-00017 (APR-00017). bought on PO-2024-0003; FAR FA-000017. E0017.</t>
+          <t>MD-00017 (MacBook Pro 14) — In Use / Seattle per the cited movement and people records. No term conflict for E0017; status Active. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. PO PO-2024-0003 on file; no matching FAR row for MD-00017.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8529,7 +8528,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Live kit. MD-00018 Dell U2723QE. Custodian check: E0018 / Active. TR-00018 (APR-00018) on the movement log. bought on PO-2024-0003; FAR FA-000018.</t>
+          <t>Location Atlanta and status In Use on MD-00018 match the stronger transaction trail. People file lists E0018 / Active (Theo Barnett). TR-00018 ties to MD-00018; dock date 01/23/2026, approval APR-00018. PO PO-2024-0003 on file; no matching FAR row for MD-00018.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8637,7 +8636,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Jasmine Reed (E0019), Chicago. Movement assignment sits on TR-00019 (APR-00019). bought on PO-2025-0004; FAR FA-000019.</t>
+          <t>MD-00019 (Samsung Galaxy S24) — In Use / Chicago per the cited movement and people records. HR agrees Jasmine Reed (E0019) is still Active. Transfer TR-00019 shows receipt Feb 26, 2026, approval APR-00019. PO PO-2025-0004 on file; no matching FAR row for MD-00019.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -8745,7 +8744,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Luis Navarro (E0020) is Active in HR. TR-00020 (APR-00020) on the movement log. bought on PO-2025-0004; FAR FA-000020. Left MD-00020 as In Use in Dallas.</t>
+          <t>Register row MD-00020: verified In Use, location Dallas, cost $6470. HR agrees Luis Navarro (E0020) is still Active. Movement TR-00020 posted Mar 28, 2026 and inbound 2026-03-30, approval APR-00020. PO PO-2025-0004 on file; no matching FAR row for MD-00020.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -8853,7 +8852,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 MD-00021 — assignment sits on TR-00021 (APR-00021); HR file: E0021 Active — Grace Lindholm. bought on PO-2025-0004; FAR FA-000021. duplicate serial MD-LA-050021</t>
+          <t>Register row MD-00021: verified In Use, location Denver, cost $1850. HR agrees Grace Lindholm (E0021) is still Active. TR-00021 ties to MD-00021; dock date 05/03/2026, approval APR-00021. PO PO-2025-0004 on file; no matching FAR row for MD-00021. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -8965,7 +8964,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Didn't rewrite MD-00022. Looked up E0022; still Active, and TR-00022 (APR-00022) on the movement log. bought on PO-2025-0004; FAR FA-000022.</t>
+          <t>Reconciliation kept MD-00022 at In Use (New York) once transfers and HR were read. Employment check: E0022 remains Active. Movement TR-00022 posted 06/03/2026 and inbound Jun 05, 2026, approval APR-00022. PO PO-2025-0004 on file; no matching FAR row for MD-00022.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -9073,7 +9072,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Seattle: Nina Kowalski (E0023). assignment sits on TR-00023 (APR-00023). bought on PO-2025-0004; FAR FA-000023.</t>
+          <t>Samsung Galaxy S24 tagged MD-00023 remains In Use in Seattle on the corrected register. HR agrees Nina Kowalski (E0023) is still Active. Movement TR-00023 posted Jul 08, 2026 and inbound 2026-07-09, approval APR-00023. PO PO-2025-0004 on file; no matching FAR row for MD-00023.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -9181,7 +9180,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Register owner was E0024; verified Chris Daley (E0024). TR-00024 (APR-00024) on the movement log. bought on PO-2025-0004; FAR FA-000024.</t>
+          <t>MD-00024 (Cisco C9300) — In Use / Atlanta per the cited movement and people records. Custodian Chris Daley (E0024) is Active in HR. Transfer TR-00024 shows receipt 01/21/2026, approval APR-00024. PO PO-2025-0004 on file; no matching FAR row for MD-00024.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -9289,7 +9288,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2022-0005; FAR FA-000025. People/move side: hr_employee_status still has E0025 as Active; assignment sits on TR-00025 (APR-00025). Note: duplicate serial MD-LA-050021</t>
+          <t>Outcome on MD-00025: In Use, Chicago, $2030 acquisition basis. No term conflict for E0025; status Active. equipment_transfer_log TR-00025, approval APR-00025; received Jan 22, 2026. PO PO-2022-0005 on file; no matching FAR row for MD-00025. duplicate serial MD-LA-050021 flagged on the register.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -9401,7 +9400,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Cross-check on MD-00026 landed on In Use / Dallas. Brendan Walsh (E0026) is Active in HR. TR-00026 (APR-00026) on the movement log. bought on PO-2022-0005; FAR FA-000026.</t>
+          <t>After cross-file review, MD-00026 stays In Use in Dallas. HR agrees Brendan Walsh (E0026) is still Active. Transfer TR-00026 shows receipt 2026-02-27, approval APR-00026. PO PO-2022-0005 on file; no matching FAR row for MD-00026.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -9513,7 +9512,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>assignment sits on TR-00027 (APR-00027). HR agrees (HR file: E0027 Active — Yuki Tanaka). bought on PO-2022-0005; FAR FA-000027.</t>
+          <t>Register row MD-00027: verified In Use, location Denver, cost $1220. People file lists E0027 / Active (Yuki Tanaka). Transfer TR-00027 shows receipt 04/06/2026, approval APR-00027. PO PO-2022-0005 on file; no matching FAR row for MD-00027.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -9625,7 +9624,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Keeping MD-00028 with Megan Copeland (E0028) in New York. TR-00028 (APR-00028) on the movement log. bought on PO-2022-0005; FAR FA-000028.</t>
+          <t>Cisco C9300 tagged MD-00028 remains In Use in New York on the corrected register. hr_employee_status shows Megan Copeland (E0028) as Active. TR-00028 ties to MD-00028; dock date May 02, 2026, approval APR-00028. PO PO-2022-0005 on file; no matching FAR row for MD-00028.</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -9737,7 +9736,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Omar Haddad hasn't changed status (Active) so I didn't bounce the assignment. assignment sits on TR-00029 (APR-00029). bought on PO-2022-0005; FAR FA-000029. E0029.</t>
+          <t>Location Seattle and status In Use on MD-00029 match the stronger transaction trail. Employment check: E0029 remains Active. Transfer TR-00029 shows receipt 2026-06-11, approval APR-00029. PO PO-2022-0005 on file; no matching FAR row for MD-00029.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -9849,7 +9848,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Live kit. MD-00030 Dell U2723QE. Custodian check: E0030 / Active. TR-00030 (APR-00030) on the movement log. bought on PO-2022-0005; FAR FA-000030.</t>
+          <t>Location Atlanta and status In Use on MD-00030 match the stronger transaction trail. No term conflict for E0030; status Active. TR-00030 ties to MD-00030; dock date 01/13/2026, approval APR-00030. PO PO-2022-0005 on file; no matching FAR row for MD-00030.</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -9961,7 +9960,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Keith Moreau (E0031), Chicago. Movement assignment sits on TR-00031 (APR-00031). bought on PO-2023-0006; FAR FA-000031.</t>
+          <t>After cross-file review, MD-00031 stays In Use in Chicago. Custodian Keith Moreau (E0031) is Active in HR. equipment_transfer_log TR-00031, approval APR-00031; received Feb 11, 2026. PO PO-2023-0006 on file; no matching FAR row for MD-00031.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -10073,7 +10072,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Diana Voss (E0032) is Active in HR. TR-00032 (APR-00032) on the movement log. bought on PO-2023-0006; FAR FA-000032. Left MD-00032 as In Use in Dallas.</t>
+          <t>After cross-file review, MD-00032 stays In Use in Dallas. No term conflict for E0032; status Active. Transfer TR-00032 shows receipt 2026-03-22, approval APR-00032. PO PO-2023-0006 on file; no matching FAR row for MD-00032.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -10185,7 +10184,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 MD-00033 — assignment sits on TR-00033 (APR-00033); HR file: E0033 Active — Jordan Blake. bought on PO-2023-0006; FAR FA-000033.</t>
+          <t>Reconciliation kept MD-00033 at In Use (Denver) once transfers and HR were read. People file lists E0033 / Active (Jordan Blake). Movement TR-00033 posted 2026-04-20 and inbound 04/22/2026, approval APR-00033. PO PO-2023-0006 on file; no matching FAR row for MD-00033.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -10297,7 +10296,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Didn't rewrite MD-00034. Looked up E0034; still Active, and TR-00034 (APR-00034) on the movement log. bought on PO-2023-0006; FAR FA-000034.</t>
+          <t>Verified outcome for MD-00034: In Use at New York; acquisition $790. Employment check: E0034 remains Active. TR-00034 ties to MD-00034; dock date May 22, 2026, approval APR-00034. PO PO-2023-0006 on file; no matching FAR row for MD-00034.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10409,7 +10408,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Seattle: Rafael Mendes (E0035). assignment sits on TR-00035 (APR-00035). bought on PO-2023-0006; FAR FA-000035.</t>
+          <t>MD-00035 (Samsung Galaxy S24) — In Use / Seattle per the cited movement and people records. People file lists E0035 / Active (Rafael Mendes). equipment_transfer_log TR-00035, approval APR-00035; received 2026-06-30. PO PO-2023-0006 on file; no matching FAR row for MD-00035.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -10521,7 +10520,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Register owner was E0036; verified Kate Sorenson (E0036). TR-00036 (APR-00036) on the movement log. bought on PO-2023-0006; FAR FA-000036.</t>
+          <t>Outcome on MD-00036: In Use, Atlanta, $6245 acquisition basis. Custodian Kate Sorenson (E0036) is Active in HR. TR-00036 ties to MD-00036; dock date 02/01/2026, approval APR-00036. PO PO-2023-0006 on file; no matching FAR row for MD-00036.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10633,7 +10632,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2024-0007; FAR FA-000037. People/move side: hr_employee_status still has E0037 as Active; assignment sits on TR-00037 (APR-00037).</t>
+          <t>Location Chicago and status In Use on MD-00037 match the stronger transaction trail. No term conflict for E0037; status Active. equipment_transfer_log TR-00037, approval APR-00037; received Feb 02, 2026. PO PO-2024-0007 on file; no matching FAR row for MD-00037.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -10745,7 +10744,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Cross-check on MD-00038 landed on In Use / Dallas. Noelle Harper (E0038) is Active in HR. TR-00038 (APR-00038) on the movement log. bought on PO-2024-0007; FAR FA-000038.</t>
+          <t>Register row MD-00038: verified In Use, location Dallas, cost $655. Employment check: E0038 remains Active. Transfer TR-00038 shows receipt 2026-03-11, approval APR-00038. PO PO-2024-0007 on file; no matching FAR row for MD-00038.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10857,7 +10856,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>assignment sits on TR-00039 (APR-00039). HR agrees (HR file: E0039 Active — Samir Kapoor). bought on PO-2024-0007; FAR FA-000039.</t>
+          <t>Samsung Galaxy S24 tagged MD-00039 remains In Use in Denver on the corrected register. Employment check: E0039 remains Active. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO PO-2024-0007 on file; no matching FAR row for MD-00039.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -10969,7 +10968,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Keeping MD-00040 with Holly Jensen (E0040) in New York. TR-00040 (APR-00040) on the movement log. bought on PO-2024-0007; FAR FA-000040.</t>
+          <t>Cisco C9300 MD-00040 ($6425) reconciled to In Use at New York. Employment check: E0040 remains Active. Transfer TR-00040 shows receipt May 13, 2026, approval APR-00040. PO PO-2024-0007 on file; no matching FAR row for MD-00040.</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -11081,7 +11080,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Eric Vann hasn't changed status (Active) so I didn't bounce the assignment. assignment sits on TR-00041 (APR-00041). bought on PO-2024-0007; FAR FA-000041. E0041.</t>
+          <t>MD-00041 closed as In Use; operating site Seattle; unit cost $2120. Employment check: E0041 remains Active. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. PO PO-2024-0007 on file; no matching FAR row for MD-00041.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -11193,7 +11192,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Live kit. MD-00042 Dell U2723QE. Custodian check: E0042 / Active. TR-00042 (APR-00042) on the movement log. bought on PO-2024-0007; FAR FA-000042.</t>
+          <t>Dell U2723QE MD-00042 ($520) reconciled to In Use at Atlanta. People file lists E0042 / Active (Claudia Rossi). equipment_transfer_log TR-00042, approval APR-00042; received 01/24/2026. PO PO-2024-0007 on file; no matching FAR row for MD-00042.</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -11305,7 +11304,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Tyler Brooks (E0043), Chicago. Movement assignment sits on TR-00043 (APR-00043). bought on PO-2025-0008; FAR FA-000043.</t>
+          <t>Verified outcome for MD-00043: In Use at Chicago; acquisition $995. No term conflict for E0043; status Active. Movement TR-00043 posted 02/23/2026 and inbound Mar 01, 2026, approval APR-00043. PO PO-2025-0008 on file; no matching FAR row for MD-00043.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -11417,7 +11416,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Leah Okada (E0044) is Active in HR. TR-00044 (APR-00044) on the movement log. bought on PO-2025-0008; FAR FA-000044. Left MD-00044 as In Use in Dallas.</t>
+          <t>Reconciliation kept MD-00044 at In Use (Dallas) once transfers and HR were read. Custodian Leah Okada (E0044) is Active in HR. Movement TR-00044 posted Mar 28, 2026 and inbound 2026-03-31, approval APR-00044. PO PO-2025-0008 on file; no matching FAR row for MD-00044.</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -11529,7 +11528,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 MD-00045 — assignment sits on TR-00045 (APR-00045); HR file: E0045 Active — Darnell Price. bought on PO-2025-0008; FAR FA-000045.</t>
+          <t>MD-00045 closed as In Use; operating site Denver; unit cost $1985. No term conflict for E0045; status Active. equipment_transfer_log TR-00045, approval APR-00045; received 05/03/2026. PO PO-2025-0008 on file; no matching FAR row for MD-00045.</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -11637,7 +11636,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Parked as Available — Dell U2723QE. TR-00046 (APR-00046) on the movement log. bought on PO-2025-0008; FAR FA-000046.</t>
+          <t>After cross-file review, MD-00046 stays Available in New York. Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. PO PO-2025-0008 on file; no matching FAR row for MD-00046.</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -11745,7 +11744,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Not assigned to a person. MD-00047 / Seattle. assignment sits on TR-00047 (APR-00047). bought on PO-2025-0008; FAR FA-000047.</t>
+          <t>Outcome on MD-00047: Available, Seattle, $1175 acquisition basis. Transfer TR-00047 shows receipt 2026-07-10, approval APR-00047. PO PO-2025-0008 on file; no matching FAR row for MD-00047.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -11853,7 +11852,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Stock row. TR-00048 (APR-00048) on the movement log. bought on PO-2025-0008; FAR FA-000048.</t>
+          <t>Verified outcome for MD-00048: Available at Atlanta; acquisition $6470. Movement TR-00048 posted 2026-01-18 and inbound 01/24/2026, approval APR-00048. PO PO-2025-0008 on file; no matching FAR row for MD-00048.</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -11961,7 +11960,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2022-0009; FAR FA-000049. Status Available at Chicago after assignment sits on TR-00049 (APR-00049).</t>
+          <t>Verified outcome for MD-00049: Available at Chicago; acquisition $1850. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. PO PO-2022-0009 on file; no matching FAR row for MD-00049.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -12069,7 +12068,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Shelf/stock: MD-00050. TR-00050 (APR-00050) on the movement log. bought on PO-2022-0009; FAR FA-000050.</t>
+          <t>Dell U2723QE MD-00050 ($565) reconciled to Available at Dallas. Transfer TR-00050 shows receipt 2026-02-23, approval APR-00050. PO PO-2022-0009 on file; no matching FAR row for MD-00050.</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -12177,7 +12176,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>IT Stock holds MD-00051 (Denver). assignment sits on TR-00051 (APR-00051). bought on PO-2022-0009; FAR FA-000051.</t>
+          <t>Outcome on MD-00051: Available, Denver, $1040 acquisition basis. Transfer TR-00051 shows receipt 03/31/2026, approval APR-00051. PO PO-2022-0009 on file; no matching FAR row for MD-00051.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -12285,7 +12284,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>MD-00052 is on IT Stock in New York. TR-00052 (APR-00052) on the movement log. bought on PO-2022-0009; FAR FA-000052.</t>
+          <t>MD-00052 closed as Available; operating site New York; unit cost $6335. equipment_transfer_log TR-00052, approval APR-00052; received May 02, 2026. PO PO-2022-0009 on file; no matching FAR row for MD-00052.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -12393,7 +12392,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Parked as Available — MacBook Pro 14. assignment sits on TR-00053 (APR-00053). bought on PO-2022-0009; FAR FA-000053.</t>
+          <t>Register row MD-00053: verified Available, location Seattle, cost $2030. TR-00053 ties to MD-00053; dock date 2026-06-05, approval APR-00053. PO PO-2022-0009 on file; no matching FAR row for MD-00053.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -12501,7 +12500,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>Not assigned to a person. MD-00054 / Atlanta. TR-00054 (APR-00054) on the movement log. bought on PO-2022-0009; FAR FA-000054.</t>
+          <t>Location Atlanta and status Available on MD-00054 match the stronger transaction trail. Movement TR-00054 posted 2026-01-10 and inbound 01/16/2026, approval APR-00054. PO PO-2022-0009 on file; no matching FAR row for MD-00054.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -12609,7 +12608,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Stock row. assignment sits on TR-00055 (APR-00055). bought on PO-2023-0010; FAR FA-000055.</t>
+          <t>Location Chicago and status Available on MD-00055 match the stronger transaction trail. equipment_transfer_log TR-00055, approval APR-00055; received Feb 12, 2026. PO PO-2023-0010 on file; no matching FAR row for MD-00055.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -12717,7 +12716,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2023-0010; FAR FA-000056. Status Available at Dallas after TR-00056 (APR-00056) on the movement log.</t>
+          <t>MD-00056 closed as Available; operating site Dallas; unit cost $6200. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. PO PO-2023-0010 on file; no matching FAR row for MD-00056.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -12825,7 +12824,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>Shelf/stock: MD-00057. assignment sits on TR-00057 (APR-00057). bought on PO-2023-0010; FAR FA-000057.</t>
+          <t>Location Denver and status Available on MD-00057 match the stronger transaction trail. TR-00057 ties to MD-00057; dock date 04/24/2026, approval APR-00057. PO PO-2023-0010 on file; no matching FAR row for MD-00057.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -12937,7 +12936,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>Regional IT holding MD-00058 after term. TR-00058 (approval blank) on the movement log. bought on PO-2023-0010; FAR FA-000058; ticket OFF-00058</t>
+          <t>Verified outcome for MD-00058: Pending Redeployment at New York; acquisition $610. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. PO PO-2023-0010 on file; no matching FAR row for MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -13049,7 +13048,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>Don't send this back to a person yet. MD-00059. assignment sits on TR-00059 (approval blank). OFF-00059. bought on PO-2023-0010; FAR FA-000059. Also ticket OFF-00059</t>
+          <t>Reconciliation kept MD-00059 at Pending Redeployment (Seattle) once transfers and HR were read. Transfer TR-00059 shows receipt 2026-06-26, approval field blank. PO PO-2023-0010 on file; no matching FAR row for MD-00059. offboarding ticket OFF-00059 referenced.</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -13161,7 +13160,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>MD-00060 came off a leaver (Regional IT). Sitting with Regional IT in Atlanta. TR-00060 (APR-00060) on the movement log. OFF-00060. bought on PO-2023-0010; FAR FA-000060. Note: ticket OFF-00060</t>
+          <t>Reconciliation kept MD-00060 at Pending Redeployment (Atlanta) once transfers and HR were read. Transfer TR-00060 shows receipt 02/02/2026, approval APR-00060. PO PO-2023-0010 on file; no matching FAR row for MD-00060. offboarding ticket OFF-00060 referenced.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -13273,7 +13272,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Pending redeploy, not In Use. assignment sits on TR-00061 (APR-00061). bought on PO-2024-0011; FAR FA-000061. OFF-00061. ticket OFF-00061</t>
+          <t>Lenovo ThinkPad T14 tagged MD-00061 remains Pending Redeployment in Chicago on the corrected register. Movement TR-00061 posted 02/02/2026 and inbound Feb 03, 2026, approval APR-00061. PO PO-2024-0011 on file; no matching FAR row for MD-00061. offboarding ticket OFF-00061 referenced.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -13385,7 +13384,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>Regional IT holding MD-00062 after term. TR-00062 (APR-00062) on the movement log. bought on PO-2024-0011; FAR FA-000062 — ticket OFF-00062</t>
+          <t>After cross-file review, MD-00062 stays Pending Redeployment in Dallas. equipment_transfer_log TR-00062, approval APR-00062; received 2026-03-07. PO PO-2024-0011 on file; no matching FAR row for MD-00062. Note — offboarding ticket OFF-00062 referenced.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -13497,7 +13496,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Don't send this back to a person yet. MD-00063. assignment sits on TR-00063 (APR-00063). OFF-00063. bought on PO-2024-0011; FAR FA-000063; ticket OFF-00063</t>
+          <t>Location Denver and status Pending Redeployment on MD-00063 match the stronger transaction trail. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. PO PO-2024-0011 on file; no matching FAR row for MD-00063. Also: offboarding ticket OFF-00063 referenced.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -13609,7 +13608,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>MD-00064 came off a leaver (Regional IT). Sitting with Regional IT in New York. TR-00064 (approval blank) on the movement log. OFF-00064. bought on PO-2024-0011; FAR FA-000064. Also ticket OFF-00064</t>
+          <t>Verified outcome for MD-00064: Pending Redeployment at New York; acquisition $6245. Movement TR-00064 posted 05/13/2026 and inbound May 14, 2026, approval field blank. PO PO-2024-0011 on file; no matching FAR row for MD-00064. offboarding ticket OFF-00064 referenced.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -13721,7 +13720,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>Pending redeploy, not In Use. assignment sits on TR-00065 (approval blank). bought on PO-2024-0011; FAR FA-000065. OFF-00065. Note: ticket OFF-00065</t>
+          <t>Reconciliation kept MD-00065 at Pending Redeployment (Seattle) once transfers and HR were read. Transfer TR-00065 shows receipt 2026-06-23, approval field blank. PO PO-2024-0011 on file; no matching FAR row for MD-00065. offboarding ticket OFF-00065 referenced.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -13833,7 +13832,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Regional IT holding MD-00066 after term. TR-00066 (APR-00066) on the movement log. bought on PO-2024-0011; FAR FA-000066. ticket OFF-00066</t>
+          <t>Location Atlanta and status Pending Redeployment on MD-00066 match the stronger transaction trail. Transfer TR-00066 shows receipt 01/25/2026, approval APR-00066. PO PO-2024-0011 on file; no matching FAR row for MD-00066. Also: offboarding ticket OFF-00066 referenced.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -13945,7 +13944,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Don't send this back to a person yet. MD-00067. assignment sits on TR-00067 (APR-00067). OFF-00067. bought on PO-2025-0012; FAR FA-000067 — ticket OFF-00067</t>
+          <t>Verified outcome for MD-00067: Pending Redeployment at Chicago; acquisition $1130. Movement TR-00067 posted 02/23/2026 and inbound Feb 23, 2026, approval APR-00067. PO PO-2025-0012 on file; no matching FAR row for MD-00067. offboarding ticket OFF-00067 referenced.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -14057,7 +14056,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>OFF-00068 past due. 1ZMD00000068 never accepted. Elliott Park (E0081) is Separated in HR. bought on PO-2025-0012; FAR FA-000068; tracking 1ZMD00000068. Also ticket OFF-00068. Note: return is still label-only. TR-00068 APR-00068.</t>
+          <t>Cisco C9300 tagged MD-00068 remains Return Overdue in Remote - Former Employee on the corrected register. People file lists E0081 / Separated (Elliott Park). TR-00068 ties to MD-00068; dock date 2026-04-03, approval APR-00068. PO PO-2025-0012 on file; no matching FAR row for MD-00068. Note — carrier label 1ZMD00000068 is not proof of receipt. Also: offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -14169,7 +14168,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>I left MD-00069 Return Overdue. Label isn't SCAN-86. HR file: E0082 Separated — Carmen Diaz. assignment sits on TR-00069 (APR-00069). bought on PO-2025-0012; FAR FA-000069. Also tracking 1ZMD00000069. Note: ticket OFF-00069. return is still label-only</t>
+          <t>Outcome on MD-00069: Return Overdue, Remote - Former Employee, $2120 acquisition basis. HR agrees Carmen Diaz (E0082) is still Separated. Movement TR-00069 posted 2026-05-02 and inbound 05/04/2026, approval APR-00069. PO PO-2025-0012 on file; no matching FAR row for MD-00069. carrier label 1ZMD00000069 is not proof of receipt. offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -14281,7 +14280,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>Hugh Talbot (E0083) is Separated. Hardware isn't back. 1ZMD00000070. bought on PO-2025-0012; FAR FA-000070. Note: tracking 1ZMD00000070. ticket OFF-00070 — return is still label-only. TR-00070 APR-00070.</t>
+          <t>Location Remote - Former Employee and status Return Overdue on MD-00070 match the stronger transaction trail. Custodian Hugh Talbot (E0083) is Separated in HR. equipment_transfer_log TR-00070, approval APR-00070; received Jun 03, 2026. PO PO-2025-0012 on file; no matching FAR row for MD-00070. Note — carrier label 1ZMD00000070 is not proof of receipt. Note — offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -14393,7 +14392,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>Mira Adelman is Separated (E0084). assignment sits on TR-00071 (APR-00071). 1ZMD00000071 still Label Created — not a return. OFF-00071. bought on PO-2025-0012; FAR FA-000071. tracking 1ZMD00000071 — ticket OFF-00071; return is still label-only</t>
+          <t>MD-00071 closed as Return Overdue; operating site Remote - Former Employee; unit cost $995. People file lists E0084 / Separated (Mira Adelman). TR-00071 ties to MD-00071; dock date 2026-07-12, approval APR-00071. PO PO-2025-0012 on file; no matching FAR row for MD-00071. carrier label 1ZMD00000071 is not proof of receipt. Note — offboarding ticket OFF-00071 referenced. Note — return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -14505,7 +14504,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>Overdue kit MD-00072. ticket OFF-00072. Custodian check: E0085 / Separated. TR-00072 (APR-00072) on the movement log. bought on PO-2025-0012; FAR FA-000072 — tracking 1ZMD00000072. Also return is still label-only</t>
+          <t>Outcome on MD-00072: Return Overdue, Remote - Former Employee, $6290 acquisition basis. hr_employee_status shows Quincy Rhodes (E0085) as Separated. Movement TR-00072 posted 2026-01-18 and inbound 01/18/2026, approval APR-00072. PO PO-2025-0012 on file; no matching FAR row for MD-00072. Note — carrier label 1ZMD00000072 is not proof of receipt. offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -14617,7 +14616,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>OFF-00073 past due. 1ZMD00000073 never accepted. hr_employee_status still has E0086 as Separated. bought on PO-2022-0013; FAR FA-000073; tracking 1ZMD00000073. Also ticket OFF-00073. Note: return is still label-only. TR-00073 APR-00073.</t>
+          <t>After cross-file review, MD-00073 stays Return Overdue in Remote - Former Employee. No term conflict for E0086; status Separated. Movement TR-00073 posted 01/21/2026 and inbound Jan 24, 2026, approval APR-00073. PO PO-2022-0013 on file; no matching FAR row for MD-00073. Note — carrier label 1ZMD00000073 is not proof of receipt. Note — offboarding ticket OFF-00073 referenced. Note — return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -14729,7 +14728,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 inbound exception. tracking 1ZMD00000074. TR-00074 (APR-00074) on the movement log. bought on PO-2022-0013; FAR FA-000074. Note: ticket OFF-00074. shipment serial MISMATCH-0074 vs MD-MO-050074</t>
+          <t>Location Carrier Network / Unverified and status Return Overdue on MD-00074 match the stronger transaction trail. People file lists E0087 / Separated (Nolan Vega). TR-00074 ties to MD-00074; dock date 2026-02-24, approval APR-00074. PO PO-2022-0013 on file; no matching FAR row for MD-00074. carrier label 1ZMD00000074 is not proof of receipt. Also: offboarding ticket OFF-00074 referenced. Also: return still label-only per shipment file. Also: shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -14841,7 +14840,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Ivy Chenoweth (E0088) is Separated. Hardware isn't back. 1ZMD00000075. bought on PO-2022-0013; FAR FA-000075. Note: tracking 1ZMD00000075. ticket OFF-00075 — return is still label-only. TR-00075 APR-00075.</t>
+          <t>After cross-file review, MD-00075 stays Return Overdue in Remote - Former Employee. Custodian Ivy Chenoweth (E0088) is Separated in HR. TR-00075 ties to MD-00075; dock date 04/01/2026, approval APR-00075. PO PO-2022-0013 on file; no matching FAR row for MD-00075. carrier label 1ZMD00000075 is not proof of receipt. Also: offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -14953,7 +14952,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>Held MD-00076 as In Transit - Exception. shipment serial MISMATCH-0076 vs MD-NE-050076. TR-00076 (APR-00076) on the movement log. bought on PO-2022-0013; FAR FA-000076. OFF-00076. tracking 1ZMD00000076 — ticket OFF-00076</t>
+          <t>Cisco C9300 tagged MD-00076 remains Return Overdue in Carrier Network / Unverified on the corrected register. No term conflict for E0089; status Separated. equipment_transfer_log TR-00076, approval APR-00076; received May 03, 2026. PO PO-2022-0013 on file; no matching FAR row for MD-00076. carrier label 1ZMD00000076 is not proof of receipt. Note — offboarding ticket OFF-00076 referenced. return still label-only per shipment file. Also: shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -15065,7 +15064,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Overdue kit MD-00077. tracking 1ZMD00000077. Dana Ghosh is Separated (E0090). assignment sits on TR-00077 (APR-00077). bought on PO-2022-0013; FAR FA-000077; ticket OFF-00077. Also return is still label-only</t>
+          <t>Reconciliation kept MD-00077 at Return Overdue (Remote - Former Employee) once transfers and HR were read. People file lists E0090 / Separated (Dana Ghosh). TR-00077 ties to MD-00077; dock date 2026-06-06, approval APR-00077. PO PO-2022-0013 on file; no matching FAR row for MD-00077. Also: carrier label 1ZMD00000077 is not proof of receipt. offboarding ticket OFF-00077 referenced. Also: return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -15177,7 +15176,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>OFF-00078 past due. 1ZMD00000078 never accepted. Custodian check: E0091 / Separated. bought on PO-2022-0013; FAR FA-000078; tracking 1ZMD00000078. Also ticket OFF-00078. Note: return is still label-only. TR-00078 APR-00078.</t>
+          <t>Reconciliation kept MD-00078 at Return Overdue (Remote - Former Employee) once transfers and HR were read. HR agrees Harlan Smith (E0091) is still Separated. equipment_transfer_log TR-00078, approval APR-00078; received 01/10/2026. PO PO-2022-0013 on file; no matching FAR row for MD-00078. carrier label 1ZMD00000078 is not proof of receipt. offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -15289,7 +15288,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>I left MD-00079 Return Overdue. Label isn't SCAN-86. hr_employee_status still has E0092 as Separated. assignment sits on TR-00079 (APR-00079). bought on PO-2023-0014; FAR FA-000079. Also tracking 1ZMD00000079. Note: ticket OFF-00079. return is still label-only</t>
+          <t>Samsung Galaxy S24 MD-00079 ($1040) reconciled to Return Overdue at Remote - Former Employee. People file lists E0092 / Separated (June Okoye). TR-00079 ties to MD-00079; dock date Feb 13, 2026, approval APR-00079. PO PO-2023-0014 on file; no matching FAR row for MD-00079. carrier label 1ZMD00000079 is not proof of receipt. offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -15401,7 +15400,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>MD-00080 is on IT Stock in Atlanta Warehouse. TR-00080 (APR-00080) on the movement log. bought on PO-2023-0014; FAR FA-000080. Note: tracking 1ZMD00000080. ticket OFF-00080</t>
+          <t>Cisco C9300 tagged MD-00080 remains Available in Atlanta Warehouse on the corrected register. Movement TR-00080 posted Mar 16, 2026 and inbound 2026-03-17, approval APR-00080. PO PO-2023-0014 on file; no matching FAR row for MD-00080. Note — carrier label 1ZMD00000080 is not proof of receipt. offboarding ticket OFF-00080 referenced.</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -15513,7 +15512,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Parked as Available — Dell Latitude 7440. assignment sits on TR-00081 (APR-00081). bought on PO-2023-0014; FAR FA-000081. tracking 1ZMD00000081 — ticket OFF-00081</t>
+          <t>Reconciliation kept MD-00081 at Available (Atlanta Warehouse) once transfers and HR were read. Transfer TR-00081 shows receipt 04/20/2026, approval APR-00081. PO PO-2023-0014 on file; no matching FAR row for MD-00081. Note — carrier label 1ZMD00000081 is not proof of receipt. Note — offboarding ticket OFF-00081 referenced.</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -15625,7 +15624,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>MD-00082 inbound exception. shipment serial MISMATCH-0082 vs MD-MO-050082. TR-00082 (APR-00082) on the movement log. bought on PO-2023-0014; FAR FA-000082 — tracking 1ZMD00000082; ticket OFF-00082. Note: receiving_exception_scan_1ZMD00000082.png is a HOLD lead. Dock photo is a lead, not receiving clearance.</t>
+          <t>Reconciliation kept MD-00082 at In Transit - Exception (Carrier Network / Unverified) once transfers and HR were read. Employment check: E0095 remains Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. PO PO-2023-0014 on file; no matching FAR row for MD-00082. carrier label 1ZMD00000082 is not proof of receipt. Note — offboarding ticket OFF-00082 referenced. Also: shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -15737,7 +15736,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>Stock row. assignment sits on TR-00083 (APR-00083). bought on PO-2023-0014; FAR FA-000083; tracking 1ZMD00000083. Also ticket OFF-00083</t>
+          <t>Register row MD-00083: verified Available, location Atlanta Warehouse, cost $1220. equipment_transfer_log TR-00083, approval APR-00083; received 2026-06-27. PO PO-2023-0014 on file; no matching FAR row for MD-00083. carrier label 1ZMD00000083 is not proof of receipt. offboarding ticket OFF-00083 referenced.</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -15849,7 +15848,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Held MD-00084 as In Transit - Exception. ticket OFF-00084. TR-00084 (APR-00084) on the movement log. bought on PO-2023-0014; FAR FA-000084. OFF-00084. Also tracking 1ZMD00000084. shipment serial MISMATCH-0084 vs MD-NE-050084</t>
+          <t>Cisco C9300 tagged MD-00084 remains In Transit - Exception in Carrier Network / Unverified on the corrected register. Employment check: E0072 remains Separated. equipment_transfer_log TR-00084, approval APR-00084; received 02/05/2026. PO PO-2023-0014 on file; no matching FAR row for MD-00084. carrier label 1ZMD00000084 is not proof of receipt. offboarding ticket OFF-00084 referenced. Note — shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -15961,7 +15960,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>Shelf/stock: MD-00085. assignment sits on TR-00085 (APR-00085). bought on PO-2024-0015; FAR FA-000085. Note: tracking 1ZMD00000085. ticket OFF-00085</t>
+          <t>MD-00085 closed as Available; operating site Atlanta Warehouse; unit cost $1895. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. PO PO-2024-0015 on file; no matching FAR row for MD-00085. Note — carrier label 1ZMD00000085 is not proof of receipt. Note — offboarding ticket OFF-00085 referenced.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -16073,7 +16072,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>IT Stock holds MD-00086 (Atlanta Warehouse). TR-00086 (APR-00086) on the movement log. bought on PO-2024-0015; FAR FA-000086. tracking 1ZMD00000086 — ticket OFF-00086</t>
+          <t>Verified outcome for MD-00086: Available at Atlanta Warehouse; acquisition $610. Transfer TR-00086 shows receipt 2026-03-08, approval APR-00086. PO PO-2024-0015 on file; no matching FAR row for MD-00086. carrier label 1ZMD00000086 is not proof of receipt. Note — offboarding ticket OFF-00086 referenced.</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -16185,7 +16184,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>MD-00087 is on IT Stock in Atlanta Warehouse. assignment sits on TR-00087 (APR-00087). bought on PO-2024-0015; FAR FA-000087 — tracking 1ZMD00000087; ticket OFF-00087</t>
+          <t>Register row MD-00087: verified Available, location Atlanta Warehouse, cost $1085. TR-00087 ties to MD-00087; dock date 04/12/2026, approval APR-00087. PO PO-2024-0015 on file; no matching FAR row for MD-00087. Note — carrier label 1ZMD00000087 is not proof of receipt. offboarding ticket OFF-00087 referenced.</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -16297,7 +16296,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>Parked as Available — Cisco C9300. TR-00088 (APR-00088) on the movement log. bought on PO-2024-0015; FAR FA-000088; tracking 1ZMD00000088. Also ticket OFF-00088. Note: duplicate serial MD-NE-050088</t>
+          <t>Outcome on MD-00088: Available, Atlanta Warehouse, $6380 acquisition basis. Transfer TR-00088 shows receipt May 14, 2026, approval APR-00088. PO PO-2024-0015 on file; no matching FAR row for MD-00088. Note — carrier label 1ZMD00000088 is not proof of receipt. offboarding ticket OFF-00088 referenced. Also: duplicate serial MD-NE-050088 flagged on the register.</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -16409,7 +16408,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed was the last listed floor — it's closed and the device isn't in receiving. bought on PO-2024-0015; FAR FA-000089. Also ticket OFF-00089. Note: register last showed Denver - Closed. TR-00089 APR-00089.</t>
+          <t>Outcome on MD-00089: Missing, Unknown, $2075 acquisition basis. Custodian Jonah Freedman (E0077) is Separated in HR. Transfer TR-00089 shows receipt 2026-06-17, approval APR-00089. PO PO-2024-0015 on file; no matching FAR row for MD-00089. Also: offboarding ticket OFF-00089 referenced. last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -16521,7 +16520,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>Loss path. MD-00090. OFF-00090. TR-00090 (APR-00090) on the movement log. bought on PO-2024-0015; FAR FA-000090. Note: ticket OFF-00090. register last showed Chicago - Closed</t>
+          <t>Register row MD-00090: verified Missing, location Unknown, cost $790. People file lists E0078 / Separated (Regina Lowe). Movement TR-00090 posted 2026-01-22 and inbound 01/28/2026, approval APR-00090. PO PO-2024-0015 on file; no matching FAR row for MD-00090. Note — offboarding ticket OFF-00090 referenced. last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -16633,7 +16632,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>MD-00091 is Missing. Last register site Denver - Closed. OFF-00091. assignment sits on TR-00091 (APR-00091). bought on PO-2025-0016; FAR FA-000091. ticket OFF-00091 — register last showed Denver - Closed</t>
+          <t>Outcome on MD-00091: Missing, Unknown, $950 acquisition basis. hr_employee_status shows Wes Carvalho (E0079) as Separated. equipment_transfer_log TR-00091, approval APR-00091; received Feb 24, 2026. PO PO-2025-0016 on file; no matching FAR row for MD-00091. Also: offboarding ticket OFF-00091 referenced. last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -16745,7 +16744,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>No scan/cert/count. MD-00092 stays Missing. Tara Singh (E0080) is Separated in HR. bought on PO-2025-0016; FAR FA-000092 — ticket OFF-00092; register last showed Chicago - Closed. Also duplicate serial MD-NE-050088. TR-00092 APR-00092.</t>
+          <t>Outcome on MD-00092: Missing, Unknown, $6245 acquisition basis. hr_employee_status shows Tara Singh (E0080) as Separated. equipment_transfer_log TR-00092, approval APR-00092; received 2026-03-28. PO PO-2025-0016 on file; no matching FAR row for MD-00092. offboarding ticket OFF-00092 referenced. last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -16857,7 +16856,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Can't locate MD-00093 (Dell Latitude 7440). OFF-00093. assignment sits on TR-00093 (APR-00093). bought on PO-2025-0016; FAR FA-000093; ticket OFF-00093. Also register last showed Denver - Closed</t>
+          <t>Reconciliation kept MD-00093 at Missing (Unknown) once transfers and HR were read. Custodian Elliott Park (E0081) is Separated in HR. equipment_transfer_log TR-00093, approval APR-00093; received 05/06/2026. PO PO-2025-0016 on file; no matching FAR row for MD-00093. Note — offboarding ticket OFF-00093 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -16969,7 +16968,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed was the last listed floor — it's closed and the device isn't in receiving. bought on PO-2025-0016; FAR FA-000094. Also ticket OFF-00094. Note: register last showed Chicago - Closed. TR-00094 APR-00094.</t>
+          <t>Verified outcome for MD-00094: Missing at Unknown; acquisition $655. No term conflict for E0082; status Separated. Transfer TR-00094 shows receipt Jun 04, 2026, approval APR-00094. PO PO-2025-0016 on file; no matching FAR row for MD-00094. Also: offboarding ticket OFF-00094 referenced. last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -17081,7 +17080,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Loss path. MD-00095. OFF-00095. assignment sits on TR-00095 (APR-00095). bought on PO-2025-0016; FAR FA-000095. Note: ticket OFF-00095. register last showed Denver - Closed</t>
+          <t>Verified outcome for MD-00095: Missing at Unknown; acquisition $1130. hr_employee_status shows Hugh Talbot (E0083) as Separated. Movement TR-00095 posted Jul 08, 2026 and inbound 2026-07-08, approval APR-00095. PO PO-2025-0016 on file; no matching FAR row for MD-00095. Also: offboarding ticket OFF-00095 referenced. Also: last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -17193,7 +17192,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>MD-00096 is Missing. Last register site Chicago - Closed. OFF-00096. TR-00096 (APR-00096) on the movement log. bought on PO-2025-0016; FAR FA-000096. ticket OFF-00096 — register last showed Chicago - Closed</t>
+          <t>Outcome on MD-00096: Missing, Unknown, $6425 acquisition basis. HR agrees Mira Adelman (E0084) is still Separated. Movement TR-00096 posted 2026-01-18 and inbound 01/19/2026, approval APR-00096. PO PO-2025-0016 on file; no matching FAR row for MD-00096. offboarding ticket OFF-00096 referenced. last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -17305,7 +17304,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>No scan/cert/count. MD-00097 stays Missing. hr_employee_status still has E0085 as Separated. bought on PO-2022-0017; FAR FA-000097 — ticket OFF-00097; register last showed Denver - Closed. TR-00097 APR-00097.</t>
+          <t>Register row MD-00097: verified Missing, location Unknown, cost $2120. No term conflict for E0085; status Separated. Movement TR-00097 posted 01/21/2026 and inbound Jan 27, 2026, approval APR-00097. PO PO-2022-0017 on file; no matching FAR row for MD-00097. offboarding ticket OFF-00097 referenced. Also: last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -17417,7 +17416,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>Can't locate MD-00098 (Dell U2723QE). OFF-00098. TR-00098 (APR-00098) on the movement log. bought on PO-2022-0017; FAR FA-000098; ticket OFF-00098. Also register last showed Chicago - Closed</t>
+          <t>MD-00098 (Dell U2723QE) — Missing / Unknown per the cited movement and people records. Custodian Sloane Richter (E0086) is Separated in HR. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. PO PO-2022-0017 on file; no matching FAR row for MD-00098. offboarding ticket OFF-00098 referenced. last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -17529,7 +17528,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed was the last listed floor — it's closed and the device isn't in receiving. bought on PO-2022-0017; FAR FA-000099. Also ticket OFF-00099. Note: register last showed Denver - Closed. TR-00099 APR-00099.</t>
+          <t>Verified outcome for MD-00099: Missing at Unknown; acquisition $995. Employment check: E0087 remains Separated. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. PO PO-2022-0017 on file; no matching FAR row for MD-00099. Note — offboarding ticket OFF-00099 referenced. Also: last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -17641,7 +17640,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Loss path. MD-00100. OFF-00100. TR-00100 (APR-00100) on the movement log. bought on PO-2022-0017; FAR FA-000100. Note: ticket OFF-00100. register last showed Chicago - Closed</t>
+          <t>Cisco C9300 MD-00100 ($6290) reconciled to Missing at Unknown. No term conflict for E0088; status Separated. Movement TR-00100 posted 05/01/2026 and inbound May 05, 2026, approval APR-00100. PO PO-2022-0017 on file; no matching FAR row for MD-00100. offboarding ticket OFF-00100 referenced. last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -17753,7 +17752,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 retirement/disposal trail: RET-00101. assignment sits on TR-00101 (APR-00101). bought on PO-2022-0017; FAR FA-000101. ticket RET-00101</t>
+          <t>Verified outcome for MD-00101: Retired/Pending Disposal at Seattle; acquisition $1985. Movement TR-00101 posted Jun 05, 2026 and inbound 2026-06-07, approval APR-00101. PO PO-2022-0017 on file; no matching FAR row for MD-00101. Note — offboarding ticket RET-00101 referenced.</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -17865,7 +17864,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00102 — Retired/Pending Disposal. TR-00102 (APR-00102) on the movement log. bought on PO-2022-0017; FAR FA-000102. ticket RET-00102</t>
+          <t>Dell U2723QE tagged MD-00102 remains Retired/Pending Disposal in Atlanta on the corrected register. equipment_transfer_log TR-00102, approval APR-00102; received 01/11/2026. PO PO-2022-0017 on file; no matching FAR row for MD-00102. Also: offboarding ticket RET-00102 referenced.</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -17977,7 +17976,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>Not Available. MD-00103 is Retired/Pending Disposal. assignment sits on TR-00103 (APR-00103). bought on PO-2023-0018; FAR FA-000103; ticket RET-00103</t>
+          <t>Outcome on MD-00103: Retired/Pending Disposal, Chicago, $1175 acquisition basis. TR-00103 ties to MD-00103; dock date Feb 14, 2026, approval APR-00103. PO PO-2023-0018 on file; no matching FAR row for MD-00103. Note — offboarding ticket RET-00103 referenced.</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -18089,7 +18088,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Retired/Pending Disposal on MD-00104. RET-00104. TR-00104 (APR-00104) on the movement log. bought on PO-2023-0018; FAR FA-000104. ticket RET-00104</t>
+          <t>Reconciliation kept MD-00104 at Retired/Pending Disposal (Dallas) once transfers and HR were read. Transfer TR-00104 shows receipt 2026-03-18, approval APR-00104. PO PO-2023-0018 on file; no matching FAR row for MD-00104. offboarding ticket RET-00104 referenced.</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -18201,7 +18200,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 retirement/disposal trail: RET-00105. assignment sits on TR-00105 (APR-00105). bought on PO-2023-0018; FAR FA-000105. Note: ticket RET-00105</t>
+          <t>After cross-file review, MD-00105 stays Retired/Pending Disposal in Denver. equipment_transfer_log TR-00105, approval APR-00105; received 04/21/2026. PO PO-2023-0018 on file; no matching FAR row for MD-00105. Also: offboarding ticket RET-00105 referenced.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -18313,7 +18312,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00106 — Retired/Pending Disposal. TR-00106 (APR-00106) on the movement log. bought on PO-2023-0018; FAR FA-000106. ticket RET-00106</t>
+          <t>Reconciliation kept MD-00106 at Retired/Pending Disposal (New York) once transfers and HR were read. equipment_transfer_log TR-00106, approval APR-00106; received May 25, 2026. PO PO-2023-0018 on file; no matching FAR row for MD-00106. offboarding ticket RET-00106 referenced.</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -18425,7 +18424,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>Not Available. MD-00107 is Retired/Pending Disposal. assignment sits on TR-00107 (APR-00107). bought on PO-2023-0018; FAR FA-000107 — ticket RET-00107</t>
+          <t>Samsung Galaxy S24 MD-00107 ($1040) reconciled to Retired/Pending Disposal at Seattle. equipment_transfer_log TR-00107, approval APR-00107; received 2026-06-27. PO PO-2023-0018 on file; no matching FAR row for MD-00107. Note — offboarding ticket RET-00107 referenced.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -18537,7 +18536,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>Retired/Pending Disposal on MD-00108. RET-00108. TR-00108 (APR-00108) on the movement log. bought on PO-2023-0018; FAR FA-000108. ticket RET-00108</t>
+          <t>Reconciliation kept MD-00108 at Retired/Pending Disposal (Atlanta) once transfers and HR were read. Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO PO-2023-0018 on file; no matching FAR row for MD-00108. offboarding ticket RET-00108 referenced.</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -18649,7 +18648,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 retirement/disposal trail: RET-00109. assignment sits on TR-00109 (APR-00109). bought on PO-2024-0019; FAR FA-000109. Also ticket RET-00109</t>
+          <t>MD-00109 (Lenovo ThinkPad T14) — Retired/Pending Disposal / Chicago per the cited movement and people records. Movement TR-00109 posted 02/02/2026 and inbound Feb 04, 2026, approval APR-00109. PO PO-2024-0019 on file; no matching FAR row for MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -18761,7 +18760,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00110 — Retired/Pending Disposal. TR-00110 (APR-00110) on the movement log. bought on PO-2024-0019; FAR FA-000110. ticket RET-00110</t>
+          <t>MD-00110 (Dell U2723QE) — Retired/Pending Disposal / Dallas per the cited movement and people records. TR-00110 ties to MD-00110; dock date 2026-03-08, approval APR-00110. PO PO-2024-0019 on file; no matching FAR row for MD-00110. Also: offboarding ticket RET-00110 referenced.</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -18873,7 +18872,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Not Available. MD-00111 is Disposed. assignment sits on TR-00111 (APR-00111). bought on PO-2024-0019; FAR FA-000111. ticket RET-00111</t>
+          <t>Outcome on MD-00111: Disposed, Disposed, $1220 acquisition basis. equipment_transfer_log TR-00111, approval APR-00111; received 04/13/2026. PO PO-2024-0019 on file; no matching FAR row for MD-00111. Note — offboarding ticket RET-00111 referenced.</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -18981,7 +18980,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Disposed on MD-00112. RET-00112. TR-00112 (APR-00112) on the movement log. bought on PO-2024-0019; FAR FA-000112. ticket RET-00112</t>
+          <t>Verified outcome for MD-00112: Disposed at Disposed; acquisition $6200. Transfer TR-00112 shows receipt May 15, 2026, approval APR-00112. PO PO-2024-0019 on file; no matching FAR row for MD-00112. offboarding ticket RET-00112 referenced.</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19089,7 +19088,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>MD-00113 retirement/disposal trail: RET-00113. assignment sits on TR-00113 (APR-00113). bought on PO-2024-0019; FAR FA-000113; ticket RET-00113</t>
+          <t>Verified outcome for MD-00113: Disposed at Disposed; acquisition $1895. equipment_transfer_log TR-00113, approval APR-00113; received 2026-06-18. PO PO-2024-0019 on file; no matching FAR row for MD-00113. offboarding ticket RET-00113 referenced.</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19197,7 +19196,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00114 — Retired/Pending Disposal. TR-00114 (APR-00114) on the movement log. bought on PO-2024-0019; FAR FA-000114. ticket RET-00114. Note: disposal certificate not in the file</t>
+          <t>After cross-file review, MD-00114 stays Retired/Pending Disposal in Disposed (certificate missing). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. PO PO-2024-0019 on file; no matching FAR row for MD-00114. Also: offboarding ticket RET-00114 referenced. Note — no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19309,7 +19308,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Not Available. MD-00115 is Disposed. assignment sits on TR-00115 (APR-00115). bought on PO-2025-0020; FAR FA-000115. Note: ticket RET-00115</t>
+          <t>Samsung Galaxy S24 tagged MD-00115 remains Disposed in Disposed on the corrected register. TR-00115 ties to MD-00115; dock date Feb 25, 2026, approval APR-00115. PO PO-2025-0020 on file; no matching FAR row for MD-00115. offboarding ticket RET-00115 referenced.</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19417,7 +19416,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Disposed on MD-00116. RET-00116. TR-00116 (APR-00116) on the movement log. bought on PO-2025-0020; FAR FA-000116. ticket RET-00116</t>
+          <t>Location Disposed and status Disposed on MD-00116 match the stronger transaction trail. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. PO PO-2025-0020 on file; no matching FAR row for MD-00116. offboarding ticket RET-00116 referenced.</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19525,7 +19524,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>MD-00117 retirement/disposal trail: RET-00117. assignment sits on TR-00117 (APR-00117). bought on PO-2025-0020; FAR FA-000117 — ticket RET-00117</t>
+          <t>Location Disposed and status Disposed on MD-00117 match the stronger transaction trail. equipment_transfer_log TR-00117, approval APR-00117; received 05/02/2026. PO PO-2025-0020 on file; no matching FAR row for MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19633,7 +19632,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00118 — Retired/Pending Disposal. TR-00118 (APR-00118) on the movement log. bought on PO-2025-0020; FAR FA-000118. ticket RET-00118. Also disposal certificate not in the file</t>
+          <t>MD-00118 (Dell U2723QE) — Retired/Pending Disposal / Disposed (certificate missing) per the cited movement and people records. Movement TR-00118 posted 06/03/2026 and inbound Jun 04, 2026, approval APR-00118. PO PO-2025-0020 on file; no matching FAR row for MD-00118. offboarding ticket RET-00118 referenced. Also: no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19745,7 +19744,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>Not Available. MD-00119 is Disposed. assignment sits on TR-00119 (APR-00119). bought on PO-2025-0020; FAR FA-000119. Also ticket RET-00119</t>
+          <t>Reconciliation kept MD-00119 at Disposed (Disposed) once transfers and HR were read. equipment_transfer_log TR-00119, approval APR-00119; received 2026-07-09. PO PO-2025-0020 on file; no matching FAR row for MD-00119. offboarding ticket RET-00119 referenced.</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -19857,7 +19856,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>Disposed on MD-00120. RET-00120. TR-00120 (APR-00120) on the movement log. bought on PO-2025-0020; FAR FA-000120. ticket RET-00120</t>
+          <t>Verified outcome for MD-00120: Disposed at Disposed; acquisition $6245. Movement TR-00120 posted 2026-01-18 and inbound 01/20/2026, approval APR-00120. PO PO-2025-0020 on file; no matching FAR row for MD-00120. Also: offboarding ticket RET-00120 referenced.</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -19961,7 +19960,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>IT Stock holds MD-00121 (Chicago). assignment sits on TR-00121 (APR-00121). bought on PO-2022-0021; FAR FA-000121.</t>
+          <t>Reconciliation kept MD-00121 at Available (Chicago) once transfers and HR were read. Transfer TR-00121 shows receipt Jan 21, 2026, approval APR-00121. PO PO-2022-0021 on file; no matching FAR row for MD-00121.</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -20069,7 +20068,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>MD-00122 is on IT Stock in Dallas. TR-00122 (APR-00122) on the movement log. bought on PO-2022-0021; FAR FA-000122.</t>
+          <t>Reconciliation kept MD-00122 at Available (Dallas) once transfers and HR were read. TR-00122 ties to MD-00122; dock date 2026-02-25, approval APR-00122. PO PO-2022-0021 on file; no matching FAR row for MD-00122.</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20177,7 +20176,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>Parked as Available — Samsung Galaxy S24. assignment sits on TR-00123 (APR-00123). bought on PO-2022-0021; FAR FA-000123.</t>
+          <t>Verified outcome for MD-00123: Available at Denver; acquisition $1130. Movement TR-00123 posted 2026-03-31 and inbound 04/03/2026, approval APR-00123. PO PO-2022-0021 on file; no matching FAR row for MD-00123.</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20285,7 +20284,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>Not assigned to a person. MD-00124 / New York. TR-00124 (APR-00124) on the movement log. bought on PO-2022-0021; FAR FA-000124.</t>
+          <t>Outcome on MD-00124: Available, New York, $6425 acquisition basis. TR-00124 ties to MD-00124; dock date May 01, 2026, approval APR-00124. PO PO-2022-0021 on file; no matching FAR row for MD-00124.</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20393,7 +20392,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>Stock row. assignment sits on TR-00125 (APR-00125). bought on PO-2022-0021; FAR FA-000125.</t>
+          <t>Location Seattle and status Available on MD-00125 match the stronger transaction trail. TR-00125 ties to MD-00125; dock date 2026-06-08, approval APR-00125. PO PO-2022-0021 on file; no matching FAR row for MD-00125.</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20501,7 +20500,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>bought on PO-2022-0021; FAR FA-000126. Status Available at Atlanta after TR-00126 (APR-00126) on the movement log.</t>
+          <t>After cross-file review, MD-00126 stays Available in Atlanta. equipment_transfer_log TR-00126, approval APR-00126; received 01/12/2026. PO PO-2022-0021 on file; no matching FAR row for MD-00126.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20613,7 +20612,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>Didn't invent a FAR line. MD-00127 In Use at Denver. assignment sits on TR-00127 (approval blank). bought on PO-2023-0022; FAR FA-000127. E0061.</t>
+          <t>Outcome on MD-00127: In Use, Denver, $995 acquisition basis. No term conflict for E0061; status Transferred. equipment_transfer_log TR-00127, approval field blank; received Feb 17, 2026. PO PO-2023-0022 on file; no matching FAR row for MD-00127.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20725,7 +20724,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>MD-00128 verified In Use / New York. Bianca Silva (E0062) is Transferred in HR. TR-00128 (APR-00128) on the movement log. bought on PO-2023-0022; FAR FA-000128.</t>
+          <t>Cisco C9300 tagged MD-00128 remains In Use in New York on the corrected register. hr_employee_status shows Bianca Silva (E0062) as Transferred. Transfer TR-00128 shows receipt 2026-03-19, approval APR-00128. PO PO-2023-0022 on file; no matching FAR row for MD-00128.</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20833,7 +20832,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>Greg Hollis (E0063) is Transferred. MD-00129 stays In Use in Seattle. assignment sits on TR-00129 (APR-00129). bought on PO-2023-0022; FAR FA-000129.</t>
+          <t>Register row MD-00129: verified In Use, location Seattle, cost $1985. hr_employee_status shows Greg Hollis (E0063) as Transferred. TR-00129 ties to MD-00129; dock date 04/21/2026, approval APR-00129. PO PO-2023-0022 on file; no matching FAR row for MD-00129.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -20941,7 +20940,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE (MD-00130): In Use. Looked up E0064; still Transferred. TR-00130 (APR-00130) on the movement log. purchasing PO-2023-0022, nothing in the FAR extract. Note: $700 is under $2,500 so missing FA is expected</t>
+          <t>Reconciliation kept MD-00130 at In Use (Atlanta) once transfers and HR were read. No term conflict for E0064; status Transferred. equipment_transfer_log TR-00130, approval APR-00130; received May 28, 2026. PO PO-2023-0022 on file; no matching FAR row for MD-00130. Also: $700 below $2,500 — missing FA expected.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -21035,7 +21034,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>Didn't invent a FAR line. MD-00131 In Use at Chicago. assignment sits on TR-00131 (APR-00131). PO-2023-0022 on file; no FA row. $1175 is under $2,500 so missing FA is expected. E0065.</t>
+          <t>Location Chicago and status In Use on MD-00131 match the stronger transaction trail. Employment check: E0065 remains Transferred. equipment_transfer_log TR-00131, approval APR-00131; received 2026-06-28. PO PO-2023-0022 on file; no matching FAR row for MD-00131. $1175 below $2,500 — missing FA expected.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -21129,7 +21128,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>MD-00132 verified In Use / Dallas. Custodian check: E0066 / Transferred. TR-00132 (APR-00132) on the movement log. PO-2023-0022 only — no ledger tag — RN-0132 claimed under-threshold expense; rejected — $6,470 is over the $2,500 gate and there is still no FA row</t>
+          <t>MD-00132 closed as In Use; operating site Dallas; unit cost $6470. hr_employee_status shows Sharon Quinlan (E0066) as Transferred. Transfer TR-00132 shows receipt 01/31/2026, approval APR-00132. PO PO-2023-0022 on file; no matching FAR row for MD-00132. Note — RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -32261,7 +32260,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Control matrix documents required return evidence for MD-00017; chain reference above must satisfy that bar.</t>
+          <t>MD-00017 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00017.</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32440,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Auditors should read the transfer bar on the matrix for MD-00021; supporting file: chain reference above.</t>
+          <t>Policy appendix applied to MD-00021 under financial reconciliation; figure informs the review, TR-00021 carries it.</t>
         </is>
       </c>
     </row>
@@ -32664,7 +32663,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Appendix A matrix applied to MD-00025 under the transfer row; chain reference above remains the auditable transaction.</t>
+          <t>Evidence rubric for MD-00025 pulled from the control matrix (disposal); chain anchor TR-00025; policy PDF §4–§7 read with TR-00025.</t>
         </is>
       </c>
     </row>
@@ -32887,7 +32886,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial gates for MD-00034 read from the matrix transfer row; chain reference above is the source record; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00034 — auditors should read the disposal line on the matrix, then follow TR-00034; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -33110,7 +33109,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Auditors should read the transfer bar on the matrix for MD-00051; supporting file: chain reference above.</t>
+          <t>MD-00051: ITAM-001 appendix defines acceptable return proof — see TR-00051 in this chain.</t>
         </is>
       </c>
     </row>
@@ -33415,7 +33414,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Policy figure referenced for MD-00058 (disposal path). Custody still depends on chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>Appendix A transfer requirements govern MD-00058; PNG matrix is reference only beside TR-00058.</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33719,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>MD-00059 — Assignment requirements pulled from ITAM_control_matrix.png; no clearance from the figure alone (chain reference above).</t>
+          <t>When scoring MD-00059, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00059 was checked; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -34025,7 +34024,7 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Return evidence bar for MD-00060 taken from ITAM_control_matrix.png; does not substitute for chain reference above.</t>
+          <t>Evidence rubric for MD-00060 pulled from the control matrix (disposal); chain anchor TR-00060; policy PDF §4–§7 read with TR-00060.</t>
         </is>
       </c>
     </row>
@@ -34330,7 +34329,7 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Evidence standard for MD-00061 follows Appendix A (Financial); transactional support is chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>On MD-00061, the matrix documents what transfer evidence looks like; it is not a substitute for TR-00061.</t>
         </is>
       </c>
     </row>
@@ -34635,7 +34634,7 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Appendix A matrix applied to MD-00062 under the transfer row; chain reference above remains the auditable transaction.</t>
+          <t>Return/disposal/financial tests for MD-00062 were read against the matrix financial reconciliation row and TR-00062; policy PDF §4–§7 read with TR-00062.</t>
         </is>
       </c>
     </row>
@@ -34940,7 +34939,7 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>MD-00063: matrix row Disposal defines acceptable proof; chain reference above is what was reviewed.</t>
+          <t>Control design for MD-00063 (return) comes from the policy figure; movement proof is TR-00063.</t>
         </is>
       </c>
     </row>
@@ -35245,7 +35244,7 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>MD-00064: Assignment control from ITAM-001 Appendix A governs this step; matrix figure is the standard, not proof of movement (chain reference above); ITAM_control_matrix.png in packet.</t>
+          <t>MD-00064 custody review used the appendix matrix on assignment; TR-00064 remains the auditable source; policy PDF §4–§7 read with TR-00064.</t>
         </is>
       </c>
     </row>
@@ -35550,7 +35549,7 @@
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>Control matrix documents required return evidence for MD-00065; chain reference above must satisfy that bar.</t>
+          <t>Matrix figure cited on MD-00065 as the control standard for disposal; transactional weight stays with TR-00065.</t>
         </is>
       </c>
     </row>
@@ -35855,7 +35854,7 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>MD-00066: Financial column in the control matrix frames the review; ledger/transfer proof is chain reference above.</t>
+          <t>Policy matrix (transfer row) applied while tracing MD-00066; the figure does not replace TR-00066; policy PDF §4–§7 read with TR-00066.</t>
         </is>
       </c>
     </row>
@@ -36160,7 +36159,7 @@
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial gates for MD-00067 read from the matrix transfer row; chain reference above is the source record; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00067 chain includes the policy figure as the financial reconciliation rubric only; TR-00067 is dispositive.</t>
         </is>
       </c>
     </row>
@@ -36512,7 +36511,7 @@
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>MD-00068: Financial column in the control matrix frames the review; ledger/transfer proof is chain reference above.</t>
+          <t>MD-00068 — auditors should read the disposal line on the matrix, then follow TR-00068; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -36864,7 +36863,7 @@
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>Control matrix documents required return evidence for MD-00069; chain reference above must satisfy that bar.</t>
+          <t>MD-00069: return controls in Appendix A; matrix noted alongside TR-00069; policy PDF §4–§7 read with TR-00069.</t>
         </is>
       </c>
     </row>
@@ -37216,7 +37215,7 @@
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>MD-00070: Assignment control from ITAM-001 Appendix A governs this step; matrix figure is the standard, not proof of movement (chain reference above); ITAM_control_matrix.png in packet.</t>
+          <t>MD-00070: return controls in Appendix A; matrix noted alongside TR-00070; policy PDF §4–§7 read with TR-00070.</t>
         </is>
       </c>
     </row>
@@ -37568,7 +37567,7 @@
       </c>
       <c r="I128" s="7" t="inlineStr">
         <is>
-          <t>MD-00071: matrix row Disposal defines acceptable proof; chain reference above is what was reviewed.</t>
+          <t>Appendix A transfer requirements govern MD-00071; PNG matrix is reference only beside TR-00071.</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37919,7 @@
       </c>
       <c r="I136" s="7" t="inlineStr">
         <is>
-          <t>Appendix A matrix applied to MD-00072 under the transfer row; chain reference above remains the auditable transaction.</t>
+          <t>MD-00072 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00072.</t>
         </is>
       </c>
     </row>
@@ -38272,7 +38271,7 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>Evidence standard for MD-00073 follows Appendix A (Financial); transactional support is chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>When scoring MD-00073, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00073 was checked; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -38659,7 +38658,7 @@
       </c>
       <c r="I153" s="7" t="inlineStr">
         <is>
-          <t>Policy figure referenced for MD-00074 (disposal path). Custody still depends on chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>When scoring MD-00074, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00074 was checked; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -39011,7 +39010,7 @@
       </c>
       <c r="I161" s="7" t="inlineStr">
         <is>
-          <t>Auditors should read the transfer bar on the matrix for MD-00075; supporting file: chain reference above.</t>
+          <t>Evidence rubric for MD-00075 pulled from the control matrix (disposal); chain anchor TR-00075; policy PDF §4–§7 read with TR-00075.</t>
         </is>
       </c>
     </row>
@@ -39398,7 +39397,7 @@
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001 appendix sets the assignment test for MD-00076; matrix cited alongside chain reference above.</t>
+          <t>Evidence rubric for MD-00076 pulled from the control matrix (disposal); chain anchor TR-00076; policy PDF §4–§7 read with TR-00076.</t>
         </is>
       </c>
     </row>
@@ -39750,7 +39749,7 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>Matrix appendix cited for MD-00077 under Disposal; technician notes cannot override chain reference above.</t>
+          <t>MD-00077: ITAM-001 appendix defines acceptable return proof — see TR-00077 in this chain.</t>
         </is>
       </c>
     </row>
@@ -40102,7 +40101,7 @@
       </c>
       <c r="I186" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial gates for MD-00078 read from the matrix transfer row; chain reference above is the source record; ITAM_control_matrix.png in packet.</t>
+          <t>On MD-00078, the matrix documents what transfer evidence looks like; it is not a substitute for TR-00078.</t>
         </is>
       </c>
     </row>
@@ -40454,7 +40453,7 @@
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>MD-00079: Financial column in the control matrix frames the review; ledger/transfer proof is chain reference above.</t>
+          <t>For MD-00079, Appendix A sets the assignment evidence bar; TR-00079 is the record under review; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -40947,7 +40946,7 @@
       </c>
       <c r="I205" s="7" t="inlineStr">
         <is>
-          <t>MD-00080 — Assignment requirements pulled from ITAM_control_matrix.png; no clearance from the figure alone (chain reference above).</t>
+          <t>Evidence rubric for MD-00080 pulled from the control matrix (disposal); chain anchor TR-00080; policy PDF §4–§7 read with TR-00080.</t>
         </is>
       </c>
     </row>
@@ -41440,7 +41439,7 @@
       </c>
       <c r="I216" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial gates for MD-00081 read from the matrix transfer row; chain reference above is the source record; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00081 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00081.</t>
         </is>
       </c>
     </row>
@@ -41917,7 +41916,7 @@
       </c>
       <c r="I227" s="7" t="inlineStr">
         <is>
-          <t>Return evidence bar for MD-00082 taken from ITAM_control_matrix.png; does not substitute for chain reference above.</t>
+          <t>MD-00082: return controls in Appendix A; matrix noted alongside TR-00082; policy PDF §4–§7 read with TR-00082.</t>
         </is>
       </c>
     </row>
@@ -42410,7 +42409,7 @@
       </c>
       <c r="I238" s="7" t="inlineStr">
         <is>
-          <t>Matrix appendix cited for MD-00083 under Disposal; technician notes cannot override chain reference above.</t>
+          <t>MD-00083 chain includes the policy figure as the financial reconciliation rubric only; TR-00083 is dispositive.</t>
         </is>
       </c>
     </row>
@@ -42844,7 +42843,7 @@
       </c>
       <c r="I248" s="7" t="inlineStr">
         <is>
-          <t>MD-00084: matrix row Disposal defines acceptable proof; chain reference above is what was reviewed.</t>
+          <t>IT_asset_management_policy.pdf plus the matrix set the assignment standard for MD-00084; TR-00084 cited.</t>
         </is>
       </c>
     </row>
@@ -43337,7 +43336,7 @@
       </c>
       <c r="I259" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 scored against the financial column in the control matrix; chain reference above carries the weight.</t>
+          <t>MD-00085: return gate from Appendix A; supporting transaction file TR-00085; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -43830,7 +43829,7 @@
       </c>
       <c r="I270" s="7" t="inlineStr">
         <is>
-          <t>MD-00086: Assignment control from ITAM-001 Appendix A governs this step; matrix figure is the standard, not proof of movement (chain reference above); ITAM_control_matrix.png in packet.</t>
+          <t>Policy appendix applied to MD-00086 under financial reconciliation; figure informs the review, TR-00086 carries it.</t>
         </is>
       </c>
     </row>
@@ -44323,7 +44322,7 @@
       </c>
       <c r="I281" s="7" t="inlineStr">
         <is>
-          <t>Auditors should read the transfer bar on the matrix for MD-00087; supporting file: chain reference above.</t>
+          <t>Used ITAM_control_matrix.png while walking MD-00087 (transfer path); conclusion still tied to TR-00087; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -44816,7 +44815,7 @@
       </c>
       <c r="I292" s="7" t="inlineStr">
         <is>
-          <t>Control matrix documents required return evidence for MD-00088; chain reference above must satisfy that bar.</t>
+          <t>For certification tracing on MD-00088, disposal criteria came from the matrix; source row TR-00088.</t>
         </is>
       </c>
     </row>
@@ -45121,7 +45120,7 @@
       </c>
       <c r="I299" s="7" t="inlineStr">
         <is>
-          <t>MD-00089: Financial column in the control matrix frames the review; ledger/transfer proof is chain reference above.</t>
+          <t>Used ITAM_control_matrix.png while walking MD-00089 (transfer path); conclusion still tied to TR-00089; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -45461,7 +45460,7 @@
       </c>
       <c r="I307" s="7" t="inlineStr">
         <is>
-          <t>Control matrix documents required return evidence for MD-00090; chain reference above must satisfy that bar.</t>
+          <t>Used ITAM_control_matrix.png while walking MD-00090 (transfer path); conclusion still tied to TR-00090; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -45801,7 +45800,7 @@
       </c>
       <c r="I315" s="7" t="inlineStr">
         <is>
-          <t>MD-00091: Assignment control from ITAM-001 Appendix A governs this step; matrix figure is the standard, not proof of movement (chain reference above); ITAM_control_matrix.png in packet.</t>
+          <t>MD-00091 custody review used the appendix matrix on assignment; TR-00091 remains the auditable source; policy PDF §4–§7 read with TR-00091.</t>
         </is>
       </c>
     </row>
@@ -46141,7 +46140,7 @@
       </c>
       <c r="I323" s="7" t="inlineStr">
         <is>
-          <t>MD-00092: matrix row Disposal defines acceptable proof; chain reference above is what was reviewed.</t>
+          <t>Policy appendix applied to MD-00092 under financial reconciliation; figure informs the review, TR-00092 carries it.</t>
         </is>
       </c>
     </row>
@@ -46481,7 +46480,7 @@
       </c>
       <c r="I331" s="7" t="inlineStr">
         <is>
-          <t>Appendix A matrix applied to MD-00093 under the transfer row; chain reference above remains the auditable transaction.</t>
+          <t>Matrix figure cited on MD-00093 as the control standard for disposal; transactional weight stays with TR-00093.</t>
         </is>
       </c>
     </row>
@@ -46821,7 +46820,7 @@
       </c>
       <c r="I339" s="7" t="inlineStr">
         <is>
-          <t>Evidence standard for MD-00094 follows Appendix A (Financial); transactional support is chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00094: return gate from Appendix A; supporting transaction file TR-00094; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -47161,7 +47160,7 @@
       </c>
       <c r="I347" s="7" t="inlineStr">
         <is>
-          <t>Return evidence bar for MD-00095 taken from ITAM_control_matrix.png; does not substitute for chain reference above.</t>
+          <t>Policy matrix (transfer row) applied while tracing MD-00095; the figure does not replace TR-00095; policy PDF §4–§7 read with TR-00095.</t>
         </is>
       </c>
     </row>
@@ -47501,7 +47500,7 @@
       </c>
       <c r="I355" s="7" t="inlineStr">
         <is>
-          <t>MD-00096 — Assignment requirements pulled from ITAM_control_matrix.png; no clearance from the figure alone (chain reference above).</t>
+          <t>IT_asset_management_policy.pdf plus the matrix set the assignment standard for MD-00096; TR-00096 cited.</t>
         </is>
       </c>
     </row>
@@ -47841,7 +47840,7 @@
       </c>
       <c r="I363" s="7" t="inlineStr">
         <is>
-          <t>Policy figure referenced for MD-00097 (disposal path). Custody still depends on chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00097 chain includes the policy figure as the financial reconciliation rubric only; TR-00097 is dispositive.</t>
         </is>
       </c>
     </row>
@@ -48181,7 +48180,7 @@
       </c>
       <c r="I371" s="7" t="inlineStr">
         <is>
-          <t>Auditors should read the transfer bar on the matrix for MD-00098; supporting file: chain reference above.</t>
+          <t>MD-00098 — auditors should read the disposal line on the matrix, then follow TR-00098; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -48521,7 +48520,7 @@
       </c>
       <c r="I379" s="7" t="inlineStr">
         <is>
-          <t>MD-00099 scored against the financial column in the control matrix; chain reference above carries the weight.</t>
+          <t>MD-00099: return controls in Appendix A; matrix noted alongside TR-00099; policy PDF §4–§7 read with TR-00099.</t>
         </is>
       </c>
     </row>
@@ -48861,7 +48860,7 @@
       </c>
       <c r="I387" s="7" t="inlineStr">
         <is>
-          <t>MD-00100 chain includes the policy figure as a rubric only (Return); chain reference above is dispositive; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00100 — auditors should read the disposal line on the matrix, then follow TR-00100; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -49201,7 +49200,7 @@
       </c>
       <c r="I395" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001 appendix sets the assignment test for MD-00101; matrix cited alongside chain reference above.</t>
+          <t>MD-00101: return controls in Appendix A; matrix noted alongside TR-00101; policy PDF §4–§7 read with TR-00101.</t>
         </is>
       </c>
     </row>
@@ -49506,7 +49505,7 @@
       </c>
       <c r="I402" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 chain includes the policy figure as a rubric only (Return); chain reference above is dispositive; ITAM_control_matrix.png in packet.</t>
+          <t>MD-00102 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00102.</t>
         </is>
       </c>
     </row>
@@ -49811,7 +49810,7 @@
       </c>
       <c r="I409" s="7" t="inlineStr">
         <is>
-          <t>MD-00103 scored against the financial column in the control matrix; chain reference above carries the weight.</t>
+          <t>Evidence rubric for MD-00103 pulled from the control matrix (disposal); chain anchor TR-00103; policy PDF §4–§7 read with TR-00103.</t>
         </is>
       </c>
     </row>
@@ -50116,7 +50115,7 @@
       </c>
       <c r="I416" s="7" t="inlineStr">
         <is>
-          <t>Auditors should read the transfer bar on the matrix for MD-00104; supporting file: chain reference above.</t>
+          <t>On MD-00104, the matrix documents what transfer evidence looks like; it is not a substitute for TR-00104.</t>
         </is>
       </c>
     </row>
@@ -50421,7 +50420,7 @@
       </c>
       <c r="I423" s="7" t="inlineStr">
         <is>
-          <t>Policy figure referenced for MD-00105 (disposal path). Custody still depends on chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>Return/disposal/financial tests for MD-00105 were read against the matrix financial reconciliation row and TR-00105; policy PDF §4–§7 read with TR-00105.</t>
         </is>
       </c>
     </row>
@@ -50726,7 +50725,7 @@
       </c>
       <c r="I430" s="7" t="inlineStr">
         <is>
-          <t>MD-00106 — Assignment requirements pulled from ITAM_control_matrix.png; no clearance from the figure alone (chain reference above).</t>
+          <t>Control design for MD-00106 (return) comes from the policy figure; movement proof is TR-00106.</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51030,7 @@
       </c>
       <c r="I437" s="7" t="inlineStr">
         <is>
-          <t>Return evidence bar for MD-00107 taken from ITAM_control_matrix.png; does not substitute for chain reference above.</t>
+          <t>MD-00107 custody review used the appendix matrix on assignment; TR-00107 remains the auditable source; policy PDF §4–§7 read with TR-00107.</t>
         </is>
       </c>
     </row>
@@ -51336,7 +51335,7 @@
       </c>
       <c r="I444" s="7" t="inlineStr">
         <is>
-          <t>Evidence standard for MD-00108 follows Appendix A (Financial); transactional support is chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>Matrix figure cited on MD-00108 as the control standard for disposal; transactional weight stays with TR-00108.</t>
         </is>
       </c>
     </row>
@@ -51641,7 +51640,7 @@
       </c>
       <c r="I451" s="7" t="inlineStr">
         <is>
-          <t>Appendix A matrix applied to MD-00109 under the transfer row; chain reference above remains the auditable transaction.</t>
+          <t>Policy matrix (transfer row) applied while tracing MD-00109; the figure does not replace TR-00109; policy PDF §4–§7 read with TR-00109.</t>
         </is>
       </c>
     </row>
@@ -51946,7 +51945,7 @@
       </c>
       <c r="I458" s="7" t="inlineStr">
         <is>
-          <t>MD-00110: matrix row Disposal defines acceptable proof; chain reference above is what was reviewed.</t>
+          <t>IT_asset_management_policy.pdf plus the matrix set the assignment standard for MD-00110; TR-00110 cited.</t>
         </is>
       </c>
     </row>
@@ -52298,7 +52297,7 @@
       </c>
       <c r="I466" s="7" t="inlineStr">
         <is>
-          <t>Appendix A matrix applied to MD-00114 under the transfer row; chain reference above remains the auditable transaction.</t>
+          <t>MD-00114: ITAM-001 appendix defines acceptable return proof — see TR-00114 in this chain.</t>
         </is>
       </c>
     </row>
@@ -52650,7 +52649,7 @@
       </c>
       <c r="I474" s="7" t="inlineStr">
         <is>
-          <t>Evidence standard for MD-00118 follows Appendix A (Financial); transactional support is chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>Policy appendix applied to MD-00118 under financial reconciliation; figure informs the review, TR-00118 carries it.</t>
         </is>
       </c>
     </row>
@@ -53002,7 +53001,7 @@
       </c>
       <c r="I482" s="7" t="inlineStr">
         <is>
-          <t>Return evidence bar for MD-00119 taken from ITAM_control_matrix.png; does not substitute for chain reference above.</t>
+          <t>Matrix figure cited on MD-00119 as the control standard for disposal; transactional weight stays with TR-00119.</t>
         </is>
       </c>
     </row>
@@ -53182,7 +53181,7 @@
       </c>
       <c r="I486" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial gates for MD-00127 read from the matrix transfer row; chain reference above is the source record; ITAM_control_matrix.png in packet.</t>
+          <t>Appendix A transfer requirements govern MD-00127; PNG matrix is reference only beside TR-00127.</t>
         </is>
       </c>
     </row>
@@ -53362,7 +53361,7 @@
       </c>
       <c r="I490" s="7" t="inlineStr">
         <is>
-          <t>MD-00130 — Assignment requirements pulled from ITAM_control_matrix.png; no clearance from the figure alone (chain reference above).</t>
+          <t>When scoring MD-00130, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00130 was checked; ITAM_control_matrix.png attached.</t>
         </is>
       </c>
     </row>
@@ -53542,7 +53541,7 @@
       </c>
       <c r="I494" s="7" t="inlineStr">
         <is>
-          <t>MD-00131: Financial column in the control matrix frames the review; ledger/transfer proof is chain reference above.</t>
+          <t>Return/disposal/financial tests for MD-00131 were read against the matrix financial reconciliation row and TR-00131; policy PDF §4–§7 read with TR-00131.</t>
         </is>
       </c>
     </row>
@@ -53722,7 +53721,7 @@
       </c>
       <c r="I498" s="7" t="inlineStr">
         <is>
-          <t>Policy figure referenced for MD-00132 (disposal path). Custody still depends on chain reference above; ITAM_control_matrix.png in packet.</t>
+          <t>Policy appendix applied to MD-00132 under financial reconciliation; figure informs the review, TR-00132 carries it.</t>
         </is>
       </c>
     </row>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -81,7 +81,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +128,18 @@
         <fgColor rgb="00EA9999"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B2F2A"/>
+        <bgColor rgb="003B2F2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005C4A3A"/>
+        <bgColor rgb="005C4A3A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -169,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,6 +227,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,6 +614,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -5700,7 +5717,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Yanou &amp; Partners IT Services — IT Asset Reconciliation Dashboard</t>
         </is>
@@ -5713,13 +5730,14 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -6500,7 +6518,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Corrected Asset Register</t>
         </is>
@@ -6513,98 +6531,99 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Asset Tag</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Serial Number</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Register Custodian</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Register Location</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Register Status</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>Verified Custodian</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>Verified Location</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Verified Status</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Evidence Source</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>Last Verified Date</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Acquisition Cost</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="25" t="inlineStr">
         <is>
           <t>Remaining Book Value</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t>Ledger Asset ID</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="25" t="inlineStr">
         <is>
           <t>Capitalized</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" s="25" t="inlineStr">
         <is>
           <t>Exception IDs</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t>Escalation Required</t>
         </is>
@@ -6688,7 +6707,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00001 at In Use (Chicago) once transfers and HR were read. No term conflict for E0001; status Active. Transfer TR-00001 shows receipt Jan 21, 2026, approval APR-00001. PO PO-2022-0001 on file; no matching FAR row for MD-00001.</t>
+          <t>After HR and transfer review, MD-00001 is In Use in Chicago. Employee E0001 (Active) matches the register holder. equipment_transfer_log TR-00001, approval APR-00001; received Jan 21, 2026. PO PO-2022-0001 on file; no matching FAR row for MD-00001.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6796,7 +6815,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00002 ($610) reconciled to In Use at Dallas. HR agrees Marcus Ellison (E0002) is still Active. equipment_transfer_log TR-00002, approval APR-00002; received 2026-02-25. PO PO-2022-0001 on file; no matching FAR row for MD-00002.</t>
+          <t>Working conclusion for MD-00002: In Use in Dallas ($610). Employee E0002 (Active) matches the register holder. Assignment TR-00002; receive column 2026-02-25, approval APR-00002. PO PO-2022-0001 on file; no matching FAR row for MD-00002.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6904,7 +6923,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00003: In Use, Denver, $1085 acquisition basis. hr_employee_status shows Elena Kovacs (E0003) as Active. equipment_transfer_log TR-00003, approval APR-00003; received 04/03/2026. PO PO-2022-0001 on file; no matching FAR row for MD-00003.</t>
+          <t>Cost $1085 on MD-00003; In Use at Denver. Employee E0003 (Active) matches the register holder. TR-00003 for MD-00003 — received 04/03/2026, approval APR-00003. PO PO-2022-0001 on file; no matching FAR row for MD-00003.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -7012,7 +7031,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00004: verified In Use, location New York, cost $6380. Custodian James Whitaker (E0004) is Active in HR. Transfer TR-00004 shows receipt May 01, 2026, approval APR-00004. PO PO-2022-0001 on file; no matching FAR row for MD-00004.</t>
+          <t>MD-00004 lists In Use at New York (Cisco C9300, $6380). Employee E0004 (Active) matches the register holder. Inbound stamp on TR-00004 is May 01, 2026, approval APR-00004. PO PO-2022-0001 on file; no matching FAR row for MD-00004.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -7120,7 +7139,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro 14 MD-00005 ($2075) reconciled to In Use at Seattle. HR agrees Aisha Rahman (E0005) is still Active. Movement TR-00005 posted Jun 05, 2026 and inbound 2026-06-08, approval APR-00005. PO PO-2022-0001 on file; no matching FAR row for MD-00005.</t>
+          <t>Register MD-00005: In Use, Seattle, $2075 — MacBook Pro 14. Employee E0005 (Active) matches the register holder. Log TR-00005: received 2026-06-08, approval APR-00005. PO PO-2022-0001 on file; no matching FAR row for MD-00005.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -7228,7 +7247,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00006 ($790) reconciled to In Use at Atlanta. Employment check: E0006 remains Active. Movement TR-00006 posted 2026-01-10 and inbound 01/12/2026, approval APR-00006. PO PO-2022-0001 on file; no matching FAR row for MD-00006.</t>
+          <t>Corrected row MD-00006: In Use, Atlanta, $790 — Dell U2723QE. Employee E0006 (Active) matches the register holder. TR-00006 for MD-00006 — received 01/12/2026, approval APR-00006. PO-2022-0001 in hardware_purchase_orders.csv; FAR silent on MD-00006.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7336,7 +7355,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 MD-00007 ($950) reconciled to In Use at Chicago. Custodian Sofia Alvarez (E0007) is Active in HR. TR-00007 ties to MD-00007; dock date Feb 17, 2026, approval APR-00007. PO PO-2023-0002 on file; no matching FAR row for MD-00007.</t>
+          <t>Corrected register carries MD-00007 as In Use in Chicago. Employee E0007 (Active) matches the register holder. Movement TR-00007 posted 02/11/2026 and inbound Feb 17, 2026, approval APR-00007. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00007.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7444,7 +7463,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Location Dallas and status In Use on MD-00008 match the stronger transaction trail. Employment check: E0008 remains Active. equipment_transfer_log TR-00008, approval APR-00008; received 2026-03-19. PO PO-2023-0002 on file; no matching FAR row for MD-00008.</t>
+          <t>MD-00008 (Cisco C9300) closed In Use / Dallas on $6245. Employee E0008 (Active) matches the register holder. Log TR-00008: received 2026-03-19, approval APR-00008. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00008.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7552,7 +7571,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>MD-00009 (Dell Latitude 7440) — In Use / Denver per the cited movement and people records. HR agrees Hannah Cole (E0009) is still Active. Movement TR-00009 posted 2026-04-20 and inbound 04/21/2026, approval APR-00009. PO PO-2023-0002 on file; no matching FAR row for MD-00009.</t>
+          <t>MD-00009 carries In Use at Denver (Dell Latitude 7440, $1940). Employee E0009 (Active) matches the register holder. Assignment TR-00009; receive column 04/21/2026, approval APR-00009. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00009.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7660,7 +7679,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00010: verified In Use, location New York, cost $655. Employment check: E0010 remains Active. TR-00010 ties to MD-00010; dock date May 28, 2026, approval APR-00010. PO PO-2023-0002 on file; no matching FAR row for MD-00010.</t>
+          <t>Field review: MD-00010 In Use @ New York. Employee E0010 (Active) matches the register holder. Log TR-00010: received May 28, 2026, approval APR-00010. Purchasing PO-2023-0002 without a capital line for MD-00010.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7768,7 +7787,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00011 at In Use (Seattle) once transfers and HR were read. HR agrees Maya Fontaine (E0011) is still Active. TR-00011 ties to MD-00011; dock date 2026-06-28, approval APR-00011. PO PO-2023-0002 on file; no matching FAR row for MD-00011.</t>
+          <t>Samsung Galaxy S24 on MD-00011 is In Use in Seattle site; basis $1130. Employee E0011 (Active) matches the register holder. Assignment TR-00011; receive column 2026-06-28, approval APR-00011. Purchasing PO-2023-0002 without a capital line for MD-00011.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7876,7 +7895,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00012 remains In Use in Atlanta on the corrected register. HR agrees Ryan Okonkwo (E0012) is still Active. TR-00012 ties to MD-00012; dock date 01/31/2026, approval APR-00012. PO PO-2023-0002 on file; no matching FAR row for MD-00012.</t>
+          <t>Read MD-00012 against transfers before signing In Use / Atlanta. Employee E0012 (Active) matches the register holder. Transfer TR-00012 shows receipt 01/31/2026, approval APR-00012. Purchasing PO-2023-0002 without a capital line for MD-00012.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7984,7 +8003,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>MD-00013 (Lenovo ThinkPad T14) — In Use / Chicago per the cited movement and people records. People file lists E0013 / Active (Lauren Briggs). Movement TR-00013 posted 02/02/2026 and inbound Feb 06, 2026, approval APR-00013. PO PO-2024-0003 on file; no matching FAR row for MD-00013.</t>
+          <t>Did not move MD-00013 off In Use at Chicago without a transaction. Employee E0013 (Active) matches the register holder. Inbound stamp on TR-00013 is Feb 06, 2026, approval APR-00013. Purchasing PO-2024-0003 without a capital line for MD-00013.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -8092,7 +8111,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00014: verified In Use, location Dallas, cost $520. hr_employee_status shows Nathan Kim (E0014) as Active. TR-00014 ties to MD-00014; dock date 2026-03-09, approval APR-00014. PO PO-2024-0003 on file; no matching FAR row for MD-00014.</t>
+          <t>Register MD-00014: In Use, Dallas, $520 — Dell U2723QE. Employee E0014 (Active) matches the register holder. equipment_transfer_log TR-00014, approval APR-00014; received 2026-03-09. Purchasing PO-2024-0003 without a capital line for MD-00014.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8200,7 +8219,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00015: In Use, Denver, $995 acquisition basis. Custodian Camila Ortiz (E0015) is Active in HR. Movement TR-00015 posted 2026-04-12 and inbound 04/13/2026, approval APR-00015. PO PO-2024-0003 on file; no matching FAR row for MD-00015.</t>
+          <t>Samsung Galaxy S24 MD-00015 tied to $995; location Denver; status In Use. Employee E0015 (Active) matches the register holder. TR-00015 ties to MD-00015; dock date 04/13/2026, approval APR-00015. Purchasing PO-2024-0003 without a capital line for MD-00015.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -8308,7 +8327,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 MD-00016 ($6290) reconciled to In Use at New York. hr_employee_status shows Patrick Gallagher (E0016) as Active. TR-00016 ties to MD-00016; dock date May 17, 2026, approval APR-00016. PO PO-2024-0003 on file; no matching FAR row for MD-00016.</t>
+          <t>Cisco C9300 on MD-00016 is In Use in New York; basis $6290. Employee E0016 (Active) matches the register holder. Assignment TR-00016; receive column May 17, 2026, approval APR-00016. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00016.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -8416,7 +8435,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>MD-00017 (MacBook Pro 14) — In Use / Seattle per the cited movement and people records. No term conflict for E0017; status Active. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. PO PO-2024-0003 on file; no matching FAR row for MD-00017.</t>
+          <t>Assignment trail and HR both fit In Use for MD-00017 in Seattle. Employee E0017 (Active) matches the register holder. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00017.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8528,7 +8547,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Location Atlanta and status In Use on MD-00018 match the stronger transaction trail. People file lists E0018 / Active (Theo Barnett). TR-00018 ties to MD-00018; dock date 01/23/2026, approval APR-00018. PO PO-2024-0003 on file; no matching FAR row for MD-00018.</t>
+          <t>People and transfer logs align on MD-00018 — In Use, Atlanta. Employee E0018 (Active) matches the register holder. Inbound stamp on TR-00018 is 01/23/2026, approval APR-00018. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00018.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8636,7 +8655,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>MD-00019 (Samsung Galaxy S24) — In Use / Chicago per the cited movement and people records. HR agrees Jasmine Reed (E0019) is still Active. Transfer TR-00019 shows receipt Feb 26, 2026, approval APR-00019. PO PO-2025-0004 on file; no matching FAR row for MD-00019.</t>
+          <t>MD-00019 sits In Use at Chicago (Samsung Galaxy S24, $1175). Employee E0019 (Active) matches the register holder. equipment_transfer_log TR-00019, approval APR-00019; received Feb 26, 2026. PO-2025-0004 in hardware_purchase_orders.csv; FAR silent on MD-00019.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -8744,7 +8763,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00020: verified In Use, location Dallas, cost $6470. HR agrees Luis Navarro (E0020) is still Active. Movement TR-00020 posted Mar 28, 2026 and inbound 2026-03-30, approval APR-00020. PO PO-2025-0004 on file; no matching FAR row for MD-00020.</t>
+          <t>Cisco C9300 MD-00020 tied to $6470; location Dallas; status In Use. Employee E0020 (Active) matches the register holder. Inbound stamp on TR-00020 is 2026-03-30, approval APR-00020. Purchasing PO-2025-0004 without a capital line for MD-00020.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -8852,7 +8871,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00021: verified In Use, location Denver, cost $1850. HR agrees Grace Lindholm (E0021) is still Active. TR-00021 ties to MD-00021; dock date 05/03/2026, approval APR-00021. PO PO-2025-0004 on file; no matching FAR row for MD-00021. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>I read the movement and people files before calling MD-00021 In Use. Employee E0021 (Active) matches the register holder. equipment_transfer_log TR-00021, approval APR-00021; received 05/03/2026. Purchasing PO-2025-0004 without a capital line for MD-00021. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -8964,7 +8983,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00022 at In Use (New York) once transfers and HR were read. Employment check: E0022 remains Active. Movement TR-00022 posted 06/03/2026 and inbound Jun 05, 2026, approval APR-00022. PO PO-2025-0004 on file; no matching FAR row for MD-00022.</t>
+          <t>MD-00022 lists In Use at New York (Dell U2723QE, $565). Employee E0022 (Active) matches the register holder. TR-00022 ties to MD-00022; dock date Jun 05, 2026, approval APR-00022. Purchasing PO-2025-0004 without a capital line for MD-00022.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -9072,7 +9091,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 tagged MD-00023 remains In Use in Seattle on the corrected register. HR agrees Nina Kowalski (E0023) is still Active. Movement TR-00023 posted Jul 08, 2026 and inbound 2026-07-09, approval APR-00023. PO PO-2025-0004 on file; no matching FAR row for MD-00023.</t>
+          <t>In Use / Seattle on MD-00023 (Samsung Galaxy S24, $1040) per cited files. Employee E0023 (Active) matches the register holder. TR-00023 for MD-00023 — received 2026-07-09, approval APR-00023. Purchasing PO-2025-0004 without a capital line for MD-00023.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -9180,7 +9199,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>MD-00024 (Cisco C9300) — In Use / Atlanta per the cited movement and people records. Custodian Chris Daley (E0024) is Active in HR. Transfer TR-00024 shows receipt 01/21/2026, approval APR-00024. PO PO-2025-0004 on file; no matching FAR row for MD-00024.</t>
+          <t>Extract row MD-00024: In Use, Atlanta, $6335 — Cisco C9300. Employee E0024 (Active) matches the register holder. Movement TR-00024 posted 2026-01-18 and inbound 01/21/2026, approval APR-00024. Purchasing PO-2025-0004 without a capital line for MD-00024.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -9288,7 +9307,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00025: In Use, Chicago, $2030 acquisition basis. No term conflict for E0025; status Active. equipment_transfer_log TR-00025, approval APR-00025; received Jan 22, 2026. PO PO-2022-0005 on file; no matching FAR row for MD-00025. duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>Cost $2030 on MD-00025; In Use at Chicago. Employee E0025 (Active) matches the register holder. Log TR-00025: received Jan 22, 2026, approval APR-00025. PO-2022-0005 in hardware_purchase_orders.csv; FAR silent on MD-00025. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -9400,7 +9419,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00026 stays In Use in Dallas. HR agrees Brendan Walsh (E0026) is still Active. Transfer TR-00026 shows receipt 2026-02-27, approval APR-00026. PO PO-2022-0005 on file; no matching FAR row for MD-00026.</t>
+          <t>Cross-file check left MD-00026 as In Use (Dallas). Employee E0026 (Active) matches the register holder. equipment_transfer_log TR-00026, approval APR-00026; received 2026-02-27. PO PO-2022-0005 on file; no matching FAR row for MD-00026.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -9512,7 +9531,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00027: verified In Use, location Denver, cost $1220. People file lists E0027 / Active (Yuki Tanaka). Transfer TR-00027 shows receipt 04/06/2026, approval APR-00027. PO PO-2022-0005 on file; no matching FAR row for MD-00027.</t>
+          <t>MD-00027 reads In Use at Denver (Samsung Galaxy S24, $1220). Employee E0027 (Active) matches the register holder. TR-00027 ties to MD-00027; dock date 04/06/2026, approval APR-00027. PO PO-2022-0005 on file; no matching FAR row for MD-00027.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -9624,7 +9643,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00028 remains In Use in New York on the corrected register. hr_employee_status shows Megan Copeland (E0028) as Active. TR-00028 ties to MD-00028; dock date May 02, 2026, approval APR-00028. PO PO-2022-0005 on file; no matching FAR row for MD-00028.</t>
+          <t>Kept MD-00028 at In Use in New York; $6200 Cisco C9300. Employee E0028 (Active) matches the register holder. TR-00028 for MD-00028 — received May 02, 2026, approval APR-00028. PO PO-2022-0005 on file; no matching FAR row for MD-00028.</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -9736,7 +9755,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Location Seattle and status In Use on MD-00029 match the stronger transaction trail. Employment check: E0029 remains Active. Transfer TR-00029 shows receipt 2026-06-11, approval APR-00029. PO PO-2022-0005 on file; no matching FAR row for MD-00029.</t>
+          <t>Asset row MD-00029: In Use, Seattle, $1895 — MacBook Pro 14. Employee E0029 (Active) matches the register holder. Movement TR-00029 posted Jun 05, 2026 and inbound 2026-06-11, approval APR-00029. PO PO-2022-0005 on file; no matching FAR row for MD-00029.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -9848,7 +9867,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Location Atlanta and status In Use on MD-00030 match the stronger transaction trail. No term conflict for E0030; status Active. TR-00030 ties to MD-00030; dock date 01/13/2026, approval APR-00030. PO PO-2022-0005 on file; no matching FAR row for MD-00030.</t>
+          <t>Cost $610 on MD-00030; In Use at Atlanta. Employee E0030 (Active) matches the register holder. TR-00030 for MD-00030 — received 01/13/2026, approval APR-00030. PO-2022-0005 in hardware_purchase_orders.csv; FAR silent on MD-00030.</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -9960,7 +9979,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00031 stays In Use in Chicago. Custodian Keith Moreau (E0031) is Active in HR. equipment_transfer_log TR-00031, approval APR-00031; received Feb 11, 2026. PO PO-2023-0006 on file; no matching FAR row for MD-00031.</t>
+          <t>Chicago: MD-00031 is In Use; cost $1085. Employee E0031 (Active) matches the register holder. Movement TR-00031 posted 02/11/2026 and inbound Feb 11, 2026, approval APR-00031. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00031.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -10072,7 +10091,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00032 stays In Use in Dallas. No term conflict for E0032; status Active. Transfer TR-00032 shows receipt 2026-03-22, approval APR-00032. PO PO-2023-0006 on file; no matching FAR row for MD-00032.</t>
+          <t>MD-00032 stays In Use at Dallas (Cisco C9300, $6380). Employee E0032 (Active) matches the register holder. Log TR-00032: received 2026-03-22, approval APR-00032. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00032.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -10184,7 +10203,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00033 at In Use (Denver) once transfers and HR were read. People file lists E0033 / Active (Jordan Blake). Movement TR-00033 posted 2026-04-20 and inbound 04/22/2026, approval APR-00033. PO PO-2023-0006 on file; no matching FAR row for MD-00033.</t>
+          <t>Working conclusion for MD-00033: In Use in Denver ($2075). Employee E0033 (Active) matches the register holder. Assignment TR-00033; receive column 04/22/2026, approval APR-00033. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00033.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -10296,7 +10315,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00034: In Use at New York; acquisition $790. Employment check: E0034 remains Active. TR-00034 ties to MD-00034; dock date May 22, 2026, approval APR-00034. PO PO-2023-0006 on file; no matching FAR row for MD-00034.</t>
+          <t>Dell U2723QE on MD-00034 is In Use in New York office; basis $790. Employee E0034 (Active) matches the register holder. Transfer TR-00034 shows receipt May 22, 2026, approval APR-00034. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00034.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10408,7 +10427,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>MD-00035 (Samsung Galaxy S24) — In Use / Seattle per the cited movement and people records. People file lists E0035 / Active (Rafael Mendes). equipment_transfer_log TR-00035, approval APR-00035; received 2026-06-30. PO PO-2023-0006 on file; no matching FAR row for MD-00035.</t>
+          <t>MD-00035 shows In Use at Seattle (Samsung Galaxy S24, $950). Employee E0035 (Active) matches the register holder. Inbound stamp on TR-00035 is 2026-06-30, approval APR-00035. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00035.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -10520,7 +10539,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00036: In Use, Atlanta, $6245 acquisition basis. Custodian Kate Sorenson (E0036) is Active in HR. TR-00036 ties to MD-00036; dock date 02/01/2026, approval APR-00036. PO PO-2023-0006 on file; no matching FAR row for MD-00036.</t>
+          <t>The cited records support In Use in Atlanta for MD-00036. Employee E0036 (Active) matches the register holder. Movement TR-00036 posted 2026-01-30 and inbound 02/01/2026, approval APR-00036. PO PO-2023-0006 on file; no matching FAR row for MD-00036.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10632,7 +10651,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Location Chicago and status In Use on MD-00037 match the stronger transaction trail. No term conflict for E0037; status Active. equipment_transfer_log TR-00037, approval APR-00037; received Feb 02, 2026. PO PO-2024-0007 on file; no matching FAR row for MD-00037.</t>
+          <t>MD-00037 remains In Use at Chicago (Lenovo ThinkPad T14, $1940). Employee E0037 (Active) matches the register holder. Log TR-00037: received Feb 02, 2026, approval APR-00037. PO PO-2024-0007 on file; no matching FAR row for MD-00037.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -10744,7 +10763,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00038: verified In Use, location Dallas, cost $655. Employment check: E0038 remains Active. Transfer TR-00038 shows receipt 2026-03-11, approval APR-00038. PO PO-2024-0007 on file; no matching FAR row for MD-00038.</t>
+          <t>MD-00038 reconciled In Use with Dallas as the working site. Employee E0038 (Active) matches the register holder. Assignment TR-00038; receive column 2026-03-11, approval APR-00038. PO PO-2024-0007 on file; no matching FAR row for MD-00038.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10856,7 +10875,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 tagged MD-00039 remains In Use in Denver on the corrected register. Employment check: E0039 remains Active. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO PO-2024-0007 on file; no matching FAR row for MD-00039.</t>
+          <t>Samsung Galaxy S24 on MD-00039 is In Use in floor Denver; basis $1130. Employee E0039 (Active) matches the register holder. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO PO-2024-0007 on file; no matching FAR row for MD-00039.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -10968,7 +10987,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 MD-00040 ($6425) reconciled to In Use at New York. Employment check: E0040 remains Active. Transfer TR-00040 shows receipt May 13, 2026, approval APR-00040. PO PO-2024-0007 on file; no matching FAR row for MD-00040.</t>
+          <t>MD-00040 shows In Use at New York (Cisco C9300, $6425). Employee E0040 (Active) matches the register holder. Assignment TR-00040; receive column May 13, 2026, approval APR-00040. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00040.</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -11080,7 +11099,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>MD-00041 closed as In Use; operating site Seattle; unit cost $2120. Employment check: E0041 remains Active. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. PO PO-2024-0007 on file; no matching FAR row for MD-00041.</t>
+          <t>After HR and transfer review, MD-00041 is In Use in Seattle. Employee E0041 (Active) matches the register holder. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00041.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -11192,7 +11211,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00042 ($520) reconciled to In Use at Atlanta. People file lists E0042 / Active (Claudia Rossi). equipment_transfer_log TR-00042, approval APR-00042; received 01/24/2026. PO PO-2024-0007 on file; no matching FAR row for MD-00042.</t>
+          <t>Inventory line MD-00042: In Use, Atlanta, $520 — Dell U2723QE. Employee E0042 (Active) matches the register holder. Inbound stamp on TR-00042 is 01/24/2026, approval APR-00042. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00042.</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -11304,7 +11323,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00043: In Use at Chicago; acquisition $995. No term conflict for E0043; status Active. Movement TR-00043 posted 02/23/2026 and inbound Mar 01, 2026, approval APR-00043. PO PO-2025-0008 on file; no matching FAR row for MD-00043.</t>
+          <t>Looked up MD-00043 across CSV/XLSX inputs — In Use, Chicago. Employee E0043 (Active) matches the register holder. equipment_transfer_log TR-00043, approval APR-00043; received Mar 01, 2026. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00043.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -11416,7 +11435,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00044 at In Use (Dallas) once transfers and HR were read. Custodian Leah Okada (E0044) is Active in HR. Movement TR-00044 posted Mar 28, 2026 and inbound 2026-03-31, approval APR-00044. PO PO-2025-0008 on file; no matching FAR row for MD-00044.</t>
+          <t>Verified In Use for MD-00044 at Dallas; acquisition $6290. Employee E0044 (Active) matches the register holder. TR-00044 ties to MD-00044; dock date 2026-03-31, approval APR-00044. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00044.</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -11528,7 +11547,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>MD-00045 closed as In Use; operating site Denver; unit cost $1985. No term conflict for E0045; status Active. equipment_transfer_log TR-00045, approval APR-00045; received 05/03/2026. PO PO-2025-0008 on file; no matching FAR row for MD-00045.</t>
+          <t>MD-00045 reflects In Use at Denver (Dell Latitude 7440, $1985). Employee E0045 (Active) matches the register holder. TR-00045 for MD-00045 — received 05/03/2026, approval APR-00045. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00045.</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -11636,7 +11655,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00046 stays Available in New York. Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. PO PO-2025-0008 on file; no matching FAR row for MD-00046.</t>
+          <t>Working conclusion for MD-00046: Available in New York ($700). Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. PO PO-2025-0008 on file; no matching FAR row for MD-00046.</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -11744,7 +11763,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00047: Available, Seattle, $1175 acquisition basis. Transfer TR-00047 shows receipt 2026-07-10, approval APR-00047. PO PO-2025-0008 on file; no matching FAR row for MD-00047.</t>
+          <t>MD-00047 stays Available at Seattle (Samsung Galaxy S24, $1175). Inbound stamp on TR-00047 is 2026-07-10, approval APR-00047. PO PO-2025-0008 on file; no matching FAR row for MD-00047.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -11852,7 +11871,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00048: Available at Atlanta; acquisition $6470. Movement TR-00048 posted 2026-01-18 and inbound 01/24/2026, approval APR-00048. PO PO-2025-0008 on file; no matching FAR row for MD-00048.</t>
+          <t>Atlanta: MD-00048 is Available; cost $6470. equipment_transfer_log TR-00048, approval APR-00048; received 01/24/2026. PO PO-2025-0008 on file; no matching FAR row for MD-00048.</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -11960,7 +11979,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00049: Available at Chicago; acquisition $1850. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. PO PO-2022-0009 on file; no matching FAR row for MD-00049.</t>
+          <t>Cost $1850 on MD-00049; Available at Chicago. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. Purchasing PO-2022-0009 without a capital line for MD-00049.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -12068,7 +12087,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00050 ($565) reconciled to Available at Dallas. Transfer TR-00050 shows receipt 2026-02-23, approval APR-00050. PO PO-2022-0009 on file; no matching FAR row for MD-00050.</t>
+          <t>Asset row MD-00050: Available, Dallas, $565 — Dell U2723QE. equipment_transfer_log TR-00050, approval APR-00050; received 2026-02-23. PO PO-2022-0009 on file; no matching FAR row for MD-00050.</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -12176,7 +12195,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00051: Available, Denver, $1040 acquisition basis. Transfer TR-00051 shows receipt 03/31/2026, approval APR-00051. PO PO-2022-0009 on file; no matching FAR row for MD-00051.</t>
+          <t>Kept MD-00051 at Available in Denver; $1040 Samsung Galaxy S24. TR-00051 ties to MD-00051; dock date 03/31/2026, approval APR-00051. PO PO-2022-0009 on file; no matching FAR row for MD-00051.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -12284,7 +12303,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>MD-00052 closed as Available; operating site New York; unit cost $6335. equipment_transfer_log TR-00052, approval APR-00052; received May 02, 2026. PO PO-2022-0009 on file; no matching FAR row for MD-00052.</t>
+          <t>MD-00052 reads Available at New York (Cisco C9300, $6335). TR-00052 for MD-00052 — received May 02, 2026, approval APR-00052. PO PO-2022-0009 on file; no matching FAR row for MD-00052.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -12392,7 +12411,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00053: verified Available, location Seattle, cost $2030. TR-00053 ties to MD-00053; dock date 2026-06-05, approval APR-00053. PO PO-2022-0009 on file; no matching FAR row for MD-00053.</t>
+          <t>Cross-file check left MD-00053 as Available (Seattle). Movement TR-00053 posted Jun 05, 2026 and inbound 2026-06-05, approval APR-00053. PO PO-2022-0009 on file; no matching FAR row for MD-00053.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -12500,7 +12519,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>Location Atlanta and status Available on MD-00054 match the stronger transaction trail. Movement TR-00054 posted 2026-01-10 and inbound 01/16/2026, approval APR-00054. PO PO-2022-0009 on file; no matching FAR row for MD-00054.</t>
+          <t>No stronger file contradicted Available for MD-00054 at Atlanta. Log TR-00054: received 01/16/2026, approval APR-00054. PO PO-2022-0009 on file; no matching FAR row for MD-00054.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -12608,7 +12627,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Location Chicago and status Available on MD-00055 match the stronger transaction trail. equipment_transfer_log TR-00055, approval APR-00055; received Feb 12, 2026. PO PO-2023-0010 on file; no matching FAR row for MD-00055.</t>
+          <t>MD-00055 sits Available at Chicago (Samsung Galaxy S24, $1220). Assignment TR-00055; receive column Feb 12, 2026, approval APR-00055. Purchasing PO-2023-0010 without a capital line for MD-00055.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -12716,7 +12735,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>MD-00056 closed as Available; operating site Dallas; unit cost $6200. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. PO PO-2023-0010 on file; no matching FAR row for MD-00056.</t>
+          <t>Available / Dallas on MD-00056 (Cisco C9300, $6200) per cited files. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00056.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -12824,7 +12843,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>Location Denver and status Available on MD-00057 match the stronger transaction trail. TR-00057 ties to MD-00057; dock date 04/24/2026, approval APR-00057. PO PO-2023-0010 on file; no matching FAR row for MD-00057.</t>
+          <t>MD-00057 lists Available at Denver (Dell Latitude 7440, $1895). TR-00057 for MD-00057 — received 04/24/2026, approval APR-00057. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00057.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -12936,7 +12955,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00058: Pending Redeployment at New York; acquisition $610. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. PO PO-2023-0010 on file; no matching FAR row for MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
+          <t>Read MD-00058 against transfers before signing Pending Redeployment / New York. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -13048,7 +13067,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00059 at Pending Redeployment (Seattle) once transfers and HR were read. Transfer TR-00059 shows receipt 2026-06-26, approval field blank. PO PO-2023-0010 on file; no matching FAR row for MD-00059. offboarding ticket OFF-00059 referenced.</t>
+          <t>I read the movement and people files before calling MD-00059 Pending Redeployment. Log TR-00059: received 2026-06-26, approval field blank. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00059. Also: offboarding ticket OFF-00059 referenced.</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -13160,7 +13179,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00060 at Pending Redeployment (Atlanta) once transfers and HR were read. Transfer TR-00060 shows receipt 02/02/2026, approval APR-00060. PO PO-2023-0010 on file; no matching FAR row for MD-00060. offboarding ticket OFF-00060 referenced.</t>
+          <t>The cited records support Pending Redeployment in Atlanta for MD-00060. Movement TR-00060 posted 2026-01-30 and inbound 02/02/2026, approval APR-00060. Purchasing PO-2023-0010 without a capital line for MD-00060. Also: offboarding ticket OFF-00060 referenced.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -13272,7 +13291,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Lenovo ThinkPad T14 tagged MD-00061 remains Pending Redeployment in Chicago on the corrected register. Movement TR-00061 posted 02/02/2026 and inbound Feb 03, 2026, approval APR-00061. PO PO-2024-0011 on file; no matching FAR row for MD-00061. offboarding ticket OFF-00061 referenced.</t>
+          <t>Chicago holds MD-00061 (Lenovo ThinkPad T14) as Pending Redeployment. Log TR-00061: received Feb 03, 2026, approval APR-00061. Purchasing PO-2024-0011 without a capital line for MD-00061. Also: offboarding ticket OFF-00061 referenced.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -13384,7 +13403,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00062 stays Pending Redeployment in Dallas. equipment_transfer_log TR-00062, approval APR-00062; received 2026-03-07. PO PO-2024-0011 on file; no matching FAR row for MD-00062. Note — offboarding ticket OFF-00062 referenced.</t>
+          <t>MD-00062 (Dell U2723QE) closed Pending Redeployment / Dallas on $790. Assignment TR-00062; receive column 2026-03-07, approval APR-00062. Purchasing PO-2024-0011 without a capital line for MD-00062. Also: offboarding ticket OFF-00062 referenced.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -13496,7 +13515,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Location Denver and status Pending Redeployment on MD-00063 match the stronger transaction trail. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. PO PO-2024-0011 on file; no matching FAR row for MD-00063. Also: offboarding ticket OFF-00063 referenced.</t>
+          <t>Assignment trail and HR both fit Pending Redeployment for MD-00063 in Denver. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. Purchasing PO-2024-0011 without a capital line for MD-00063. Also: offboarding ticket OFF-00063 referenced.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -13608,7 +13627,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00064: Pending Redeployment at New York; acquisition $6245. Movement TR-00064 posted 05/13/2026 and inbound May 14, 2026, approval field blank. PO PO-2024-0011 on file; no matching FAR row for MD-00064. offboarding ticket OFF-00064 referenced.</t>
+          <t>Cross-file check left MD-00064 as Pending Redeployment (New York). Inbound stamp on TR-00064 is May 14, 2026, approval field blank. Purchasing PO-2024-0011 without a capital line for MD-00064. Also: offboarding ticket OFF-00064 referenced.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -13720,7 +13739,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00065 at Pending Redeployment (Seattle) once transfers and HR were read. Transfer TR-00065 shows receipt 2026-06-23, approval field blank. PO PO-2024-0011 on file; no matching FAR row for MD-00065. offboarding ticket OFF-00065 referenced.</t>
+          <t>MD-00065 still Pending Redeployment; Seattle is the verified site. equipment_transfer_log TR-00065, approval field blank; received 2026-06-23. Purchasing PO-2024-0011 without a capital line for MD-00065. Also: offboarding ticket OFF-00065 referenced.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -13832,7 +13851,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Location Atlanta and status Pending Redeployment on MD-00066 match the stronger transaction trail. Transfer TR-00066 shows receipt 01/25/2026, approval APR-00066. PO PO-2024-0011 on file; no matching FAR row for MD-00066. Also: offboarding ticket OFF-00066 referenced.</t>
+          <t>Dell U2723QE on MD-00066 is Pending Redeployment in Atlanta office; basis $655. Log TR-00066: received 01/25/2026, approval APR-00066. PO-2024-0011 in hardware_purchase_orders.csv; FAR silent on MD-00066. Also: offboarding ticket OFF-00066 referenced.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -13944,7 +13963,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00067: Pending Redeployment at Chicago; acquisition $1130. Movement TR-00067 posted 02/23/2026 and inbound Feb 23, 2026, approval APR-00067. PO PO-2025-0012 on file; no matching FAR row for MD-00067. offboarding ticket OFF-00067 referenced.</t>
+          <t>Looked up MD-00067 across CSV/XLSX inputs — Pending Redeployment, Chicago. Assignment TR-00067; receive column Feb 23, 2026, approval APR-00067. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00067. Also: offboarding ticket OFF-00067 referenced.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -14056,7 +14075,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00068 remains Return Overdue in Remote - Former Employee on the corrected register. People file lists E0081 / Separated (Elliott Park). TR-00068 ties to MD-00068; dock date 2026-04-03, approval APR-00068. PO PO-2025-0012 on file; no matching FAR row for MD-00068. Note — carrier label 1ZMD00000068 is not proof of receipt. Also: offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
+          <t>MD-00068: Cisco C9300, $6425, status Return Overdue, site Remote - Former Employee. Employment file: E0081 remains Separated. Transfer TR-00068 shows receipt 2026-04-03, approval APR-00068. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00068. Also: carrier label 1ZMD00000068 is not proof of receipt. Note — offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -14168,7 +14187,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00069: Return Overdue, Remote - Former Employee, $2120 acquisition basis. HR agrees Carmen Diaz (E0082) is still Separated. Movement TR-00069 posted 2026-05-02 and inbound 05/04/2026, approval APR-00069. PO PO-2025-0012 on file; no matching FAR row for MD-00069. carrier label 1ZMD00000069 is not proof of receipt. offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
+          <t>MD-00069 carries Return Overdue at Remote - Former Employee (Dell Latitude 7440, $2120). Employment file: E0082 remains Separated. Inbound stamp on TR-00069 is 05/04/2026, approval APR-00069. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00069. Also: carrier label 1ZMD00000069 is not proof of receipt. Note — offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -14280,7 +14299,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>Location Remote - Former Employee and status Return Overdue on MD-00070 match the stronger transaction trail. Custodian Hugh Talbot (E0083) is Separated in HR. equipment_transfer_log TR-00070, approval APR-00070; received Jun 03, 2026. PO PO-2025-0012 on file; no matching FAR row for MD-00070. Note — carrier label 1ZMD00000070 is not proof of receipt. Note — offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
+          <t>MD-00070 stays Return Overdue at Remote - Former Employee (Dell U2723QE, $520). HR agrees Hugh Talbot (E0083) is still Separated. Transfer TR-00070 shows receipt Jun 03, 2026, approval APR-00070. Purchasing PO-2025-0012 without a capital line for MD-00070. Also: carrier label 1ZMD00000070 is not proof of receipt. Note — offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -14392,7 +14411,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>MD-00071 closed as Return Overdue; operating site Remote - Former Employee; unit cost $995. People file lists E0084 / Separated (Mira Adelman). TR-00071 ties to MD-00071; dock date 2026-07-12, approval APR-00071. PO PO-2025-0012 on file; no matching FAR row for MD-00071. carrier label 1ZMD00000071 is not proof of receipt. Note — offboarding ticket OFF-00071 referenced. Note — return still label-only per shipment file.</t>
+          <t>After HR and transfer review, MD-00071 is Return Overdue in Remote - Former Employee. HR agrees Mira Adelman (E0084) is still Separated. Inbound stamp on TR-00071 is 2026-07-12, approval APR-00071. Purchasing PO-2025-0012 without a capital line for MD-00071. Also: carrier label 1ZMD00000071 is not proof of receipt. Note — offboarding ticket OFF-00071 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -14504,7 +14523,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00072: Return Overdue, Remote - Former Employee, $6290 acquisition basis. hr_employee_status shows Quincy Rhodes (E0085) as Separated. Movement TR-00072 posted 2026-01-18 and inbound 01/18/2026, approval APR-00072. PO PO-2025-0012 on file; no matching FAR row for MD-00072. Note — carrier label 1ZMD00000072 is not proof of receipt. offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
+          <t>MD-00072 reflects Return Overdue at Remote - Former Employee (Cisco C9300, $6290). HR agrees Quincy Rhodes (E0085) is still Separated. equipment_transfer_log TR-00072, approval APR-00072; received 01/18/2026. Purchasing PO-2025-0012 without a capital line for MD-00072. Also: carrier label 1ZMD00000072 is not proof of receipt. Note — offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -14616,7 +14635,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00073 stays Return Overdue in Remote - Former Employee. No term conflict for E0086; status Separated. Movement TR-00073 posted 01/21/2026 and inbound Jan 24, 2026, approval APR-00073. PO PO-2022-0013 on file; no matching FAR row for MD-00073. Note — carrier label 1ZMD00000073 is not proof of receipt. Note — offboarding ticket OFF-00073 referenced. Note — return still label-only per shipment file.</t>
+          <t>Did not move MD-00073 off Return Overdue at Remote - Former Employee without a transaction. HR agrees Sloane Richter (E0086) is still Separated. TR-00073 ties to MD-00073; dock date Jan 24, 2026, approval APR-00073. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00073. Also: carrier label 1ZMD00000073 is not proof of receipt. Note — offboarding ticket OFF-00073 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -14728,7 +14747,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>Location Carrier Network / Unverified and status Return Overdue on MD-00074 match the stronger transaction trail. People file lists E0087 / Separated (Nolan Vega). TR-00074 ties to MD-00074; dock date 2026-02-24, approval APR-00074. PO PO-2022-0013 on file; no matching FAR row for MD-00074. carrier label 1ZMD00000074 is not proof of receipt. Also: offboarding ticket OFF-00074 referenced. Also: return still label-only per shipment file. Also: shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
+          <t>MD-00074 lists Return Overdue at Carrier Network / Unverified (Dell U2723QE, $700). HR agrees Nolan Vega (E0087) is still Separated. TR-00074 for MD-00074 — received 2026-02-24, approval APR-00074. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00074. Also: carrier label 1ZMD00000074 is not proof of receipt. Note — offboarding ticket OFF-00074 referenced. return still label-only per shipment file. shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -14840,7 +14859,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00075 stays Return Overdue in Remote - Former Employee. Custodian Ivy Chenoweth (E0088) is Separated in HR. TR-00075 ties to MD-00075; dock date 04/01/2026, approval APR-00075. PO PO-2022-0013 on file; no matching FAR row for MD-00075. carrier label 1ZMD00000075 is not proof of receipt. Also: offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
+          <t>Remote - Former Employee: MD-00075 is Return Overdue; cost $1175. HR agrees Ivy Chenoweth (E0088) is still Separated. Movement TR-00075 posted 2026-03-31 and inbound 04/01/2026, approval APR-00075. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00075. Also: carrier label 1ZMD00000075 is not proof of receipt. Note — offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -14952,7 +14971,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00076 remains Return Overdue in Carrier Network / Unverified on the corrected register. No term conflict for E0089; status Separated. equipment_transfer_log TR-00076, approval APR-00076; received May 03, 2026. PO PO-2022-0013 on file; no matching FAR row for MD-00076. carrier label 1ZMD00000076 is not proof of receipt. Note — offboarding ticket OFF-00076 referenced. return still label-only per shipment file. Also: shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
+          <t>MD-00076 reads Return Overdue at Carrier Network / Unverified (Cisco C9300, $6470). HR agrees Percy Lambert (E0089) is still Separated. Inbound stamp on TR-00076 is May 03, 2026, approval APR-00076. PO PO-2022-0013 on file; no matching FAR row for MD-00076. Also: carrier label 1ZMD00000076 is not proof of receipt. Note — offboarding ticket OFF-00076 referenced. return still label-only per shipment file. shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -15064,7 +15083,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00077 at Return Overdue (Remote - Former Employee) once transfers and HR were read. People file lists E0090 / Separated (Dana Ghosh). TR-00077 ties to MD-00077; dock date 2026-06-06, approval APR-00077. PO PO-2022-0013 on file; no matching FAR row for MD-00077. Also: carrier label 1ZMD00000077 is not proof of receipt. offboarding ticket OFF-00077 referenced. Also: return still label-only per shipment file.</t>
+          <t>The cited records support Return Overdue in Remote - Former Employee for MD-00077. Employment file: E0090 remains Separated. equipment_transfer_log TR-00077, approval APR-00077; received 2026-06-06. PO PO-2022-0013 on file; no matching FAR row for MD-00077. Also: carrier label 1ZMD00000077 is not proof of receipt. Note — offboarding ticket OFF-00077 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -15176,7 +15195,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00078 at Return Overdue (Remote - Former Employee) once transfers and HR were read. HR agrees Harlan Smith (E0091) is still Separated. equipment_transfer_log TR-00078, approval APR-00078; received 01/10/2026. PO PO-2022-0013 on file; no matching FAR row for MD-00078. carrier label 1ZMD00000078 is not proof of receipt. offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
+          <t>Remote - Former Employee holds MD-00078 (Dell U2723QE) as Return Overdue. Employment file: E0091 remains Separated. TR-00078 ties to MD-00078; dock date 01/10/2026, approval APR-00078. PO PO-2022-0013 on file; no matching FAR row for MD-00078. Also: carrier label 1ZMD00000078 is not proof of receipt. Note — offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -15288,7 +15307,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 MD-00079 ($1040) reconciled to Return Overdue at Remote - Former Employee. People file lists E0092 / Separated (June Okoye). TR-00079 ties to MD-00079; dock date Feb 13, 2026, approval APR-00079. PO PO-2023-0014 on file; no matching FAR row for MD-00079. carrier label 1ZMD00000079 is not proof of receipt. offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
+          <t>MD-00079 (Samsung Galaxy S24) closed Return Overdue / Remote - Former Employee on $1040. Employment file: E0092 remains Separated. TR-00079 for MD-00079 — received Feb 13, 2026, approval APR-00079. PO PO-2023-0014 on file; no matching FAR row for MD-00079. Also: carrier label 1ZMD00000079 is not proof of receipt. Note — offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -15400,7 +15419,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00080 remains Available in Atlanta Warehouse on the corrected register. Movement TR-00080 posted Mar 16, 2026 and inbound 2026-03-17, approval APR-00080. PO PO-2023-0014 on file; no matching FAR row for MD-00080. Note — carrier label 1ZMD00000080 is not proof of receipt. offboarding ticket OFF-00080 referenced.</t>
+          <t>Atlanta Warehouse holds MD-00080 (Cisco C9300) as Available. TR-00080 ties to MD-00080; dock date 2026-03-17, approval APR-00080. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00080. Also: carrier label 1ZMD00000080 is not proof of receipt. Note — offboarding ticket OFF-00080 referenced.</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -15512,7 +15531,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00081 at Available (Atlanta Warehouse) once transfers and HR were read. Transfer TR-00081 shows receipt 04/20/2026, approval APR-00081. PO PO-2023-0014 on file; no matching FAR row for MD-00081. Note — carrier label 1ZMD00000081 is not proof of receipt. Note — offboarding ticket OFF-00081 referenced.</t>
+          <t>Dell Latitude 7440 on MD-00081 is Available in floor Atlanta Warehouse; basis $2030. TR-00081 for MD-00081 — received 04/20/2026, approval APR-00081. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00081. Also: carrier label 1ZMD00000081 is not proof of receipt. Note — offboarding ticket OFF-00081 referenced.</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -15624,7 +15643,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00082 at In Transit - Exception (Carrier Network / Unverified) once transfers and HR were read. Employment check: E0095 remains Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. PO PO-2023-0014 on file; no matching FAR row for MD-00082. carrier label 1ZMD00000082 is not proof of receipt. Note — offboarding ticket OFF-00082 referenced. Also: shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
+          <t>Field review: MD-00082 In Transit - Exception @ Carrier Network / Unverified. HR agrees Emmett Boyle (E0095) is still Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00082. Also: carrier label 1ZMD00000082 is not proof of receipt. Note — offboarding ticket OFF-00082 referenced. shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -15736,7 +15755,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00083: verified Available, location Atlanta Warehouse, cost $1220. equipment_transfer_log TR-00083, approval APR-00083; received 2026-06-27. PO PO-2023-0014 on file; no matching FAR row for MD-00083. carrier label 1ZMD00000083 is not proof of receipt. offboarding ticket OFF-00083 referenced.</t>
+          <t>MD-00083 remains Available at Atlanta Warehouse (Samsung Galaxy S24, $1220). Log TR-00083: received 2026-06-27, approval APR-00083. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00083. Also: carrier label 1ZMD00000083 is not proof of receipt. Note — offboarding ticket OFF-00083 referenced.</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -15848,7 +15867,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00084 remains In Transit - Exception in Carrier Network / Unverified on the corrected register. Employment check: E0072 remains Separated. equipment_transfer_log TR-00084, approval APR-00084; received 02/05/2026. PO PO-2023-0014 on file; no matching FAR row for MD-00084. carrier label 1ZMD00000084 is not proof of receipt. offboarding ticket OFF-00084 referenced. Note — shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
+          <t>Carrier Network / Unverified: MD-00084 is In Transit - Exception; cost $6200. Anita Bose has Separated status in the people extract. Assignment TR-00084; receive column 02/05/2026, approval APR-00084. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00084. Also: carrier label 1ZMD00000084 is not proof of receipt. Note — offboarding ticket OFF-00084 referenced. shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -15960,7 +15979,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 closed as Available; operating site Atlanta Warehouse; unit cost $1895. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. PO PO-2024-0015 on file; no matching FAR row for MD-00085. Note — carrier label 1ZMD00000085 is not proof of receipt. Note — offboarding ticket OFF-00085 referenced.</t>
+          <t>MD-00085 still Available; Atlanta Warehouse is the verified site. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. PO-2024-0015 in hardware_purchase_orders.csv; FAR silent on MD-00085. Also: carrier label 1ZMD00000085 is not proof of receipt. Note — offboarding ticket OFF-00085 referenced.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -16072,7 +16091,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00086: Available at Atlanta Warehouse; acquisition $610. Transfer TR-00086 shows receipt 2026-03-08, approval APR-00086. PO PO-2024-0015 on file; no matching FAR row for MD-00086. carrier label 1ZMD00000086 is not proof of receipt. Note — offboarding ticket OFF-00086 referenced.</t>
+          <t>Dell U2723QE on MD-00086 is Available in Atlanta Warehouse office; basis $610. TR-00086 for MD-00086 — received 2026-03-08, approval APR-00086. PO PO-2024-0015 on file; no matching FAR row for MD-00086. Also: carrier label 1ZMD00000086 is not proof of receipt. Note — offboarding ticket OFF-00086 referenced.</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -16184,7 +16203,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00087: verified Available, location Atlanta Warehouse, cost $1085. TR-00087 ties to MD-00087; dock date 04/12/2026, approval APR-00087. PO PO-2024-0015 on file; no matching FAR row for MD-00087. Note — carrier label 1ZMD00000087 is not proof of receipt. offboarding ticket OFF-00087 referenced.</t>
+          <t>Working conclusion for MD-00087: Available in Atlanta Warehouse ($1085). Movement TR-00087 posted 2026-04-12 and inbound 04/12/2026, approval APR-00087. PO PO-2024-0015 on file; no matching FAR row for MD-00087. Also: carrier label 1ZMD00000087 is not proof of receipt. Note — offboarding ticket OFF-00087 referenced.</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -16296,7 +16315,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00088: Available, Atlanta Warehouse, $6380 acquisition basis. Transfer TR-00088 shows receipt May 14, 2026, approval APR-00088. PO PO-2024-0015 on file; no matching FAR row for MD-00088. Note — carrier label 1ZMD00000088 is not proof of receipt. offboarding ticket OFF-00088 referenced. Also: duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>MD-00088 stays Available at Atlanta Warehouse (Cisco C9300, $6380). Log TR-00088: received May 14, 2026, approval APR-00088. PO PO-2024-0015 on file; no matching FAR row for MD-00088. Also: carrier label 1ZMD00000088 is not proof of receipt. Note — offboarding ticket OFF-00088 referenced. duplicate serial MD-NE-050088 flagged on the register.</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -16408,7 +16427,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00089: Missing, Unknown, $2075 acquisition basis. Custodian Jonah Freedman (E0077) is Separated in HR. Transfer TR-00089 shows receipt 2026-06-17, approval APR-00089. PO PO-2024-0015 on file; no matching FAR row for MD-00089. Also: offboarding ticket OFF-00089 referenced. last operational site on register was Denver - Closed.</t>
+          <t>Corrected row MD-00089: Missing, Unknown, $2075 — MacBook Pro 14. Jonah Freedman has Separated status in the people extract. Assignment TR-00089; receive column 2026-06-17, approval APR-00089. PO PO-2024-0015 on file; no matching FAR row for MD-00089. Also: offboarding ticket OFF-00089 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -16520,7 +16539,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00090: verified Missing, location Unknown, cost $790. People file lists E0078 / Separated (Regina Lowe). Movement TR-00090 posted 2026-01-22 and inbound 01/28/2026, approval APR-00090. PO PO-2024-0015 on file; no matching FAR row for MD-00090. Note — offboarding ticket OFF-00090 referenced. last operational site on register was Chicago - Closed.</t>
+          <t>I read the movement and people files before calling MD-00090 Missing. People side — Regina Lowe (E0078), Separated. Log TR-00090: received 01/28/2026, approval APR-00090. PO-2024-0015 in hardware_purchase_orders.csv; FAR silent on MD-00090. Also: offboarding ticket OFF-00090 referenced. Note — last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -16632,7 +16651,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00091: Missing, Unknown, $950 acquisition basis. hr_employee_status shows Wes Carvalho (E0079) as Separated. equipment_transfer_log TR-00091, approval APR-00091; received Feb 24, 2026. PO PO-2025-0016 on file; no matching FAR row for MD-00091. Also: offboarding ticket OFF-00091 referenced. last operational site on register was Denver - Closed.</t>
+          <t>Unknown: MD-00091 is Missing; cost $950. People side — Wes Carvalho (E0079), Separated. Assignment TR-00091; receive column Feb 24, 2026, approval APR-00091. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00091. Also: offboarding ticket OFF-00091 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -16744,7 +16763,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00092: Missing, Unknown, $6245 acquisition basis. hr_employee_status shows Tara Singh (E0080) as Separated. equipment_transfer_log TR-00092, approval APR-00092; received 2026-03-28. PO PO-2025-0016 on file; no matching FAR row for MD-00092. offboarding ticket OFF-00092 referenced. last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>After HR and transfer review, MD-00092 is Missing in Unknown. Tara Singh has Separated status in the people extract. Transfer TR-00092 shows receipt 2026-03-28, approval APR-00092. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00092. Also: offboarding ticket OFF-00092 referenced. Note — last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -16856,7 +16875,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00093 at Missing (Unknown) once transfers and HR were read. Custodian Elliott Park (E0081) is Separated in HR. equipment_transfer_log TR-00093, approval APR-00093; received 05/06/2026. PO PO-2025-0016 on file; no matching FAR row for MD-00093. Note — offboarding ticket OFF-00093 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Field review: MD-00093 Missing @ Unknown. Elliott Park has Separated status in the people extract. Inbound stamp on TR-00093 is 05/06/2026, approval APR-00093. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00093. Also: offboarding ticket OFF-00093 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -16968,7 +16987,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00094: Missing at Unknown; acquisition $655. No term conflict for E0082; status Separated. Transfer TR-00094 shows receipt Jun 04, 2026, approval APR-00094. PO PO-2025-0016 on file; no matching FAR row for MD-00094. Also: offboarding ticket OFF-00094 referenced. last operational site on register was Chicago - Closed.</t>
+          <t>Dell U2723QE MD-00094 tied to $655; location Unknown; status Missing. Carmen Diaz has Separated status in the people extract. equipment_transfer_log TR-00094, approval APR-00094; received Jun 04, 2026. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00094. Also: offboarding ticket OFF-00094 referenced. Note — last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -17080,7 +17099,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00095: Missing at Unknown; acquisition $1130. hr_employee_status shows Hugh Talbot (E0083) as Separated. Movement TR-00095 posted Jul 08, 2026 and inbound 2026-07-08, approval APR-00095. PO PO-2025-0016 on file; no matching FAR row for MD-00095. Also: offboarding ticket OFF-00095 referenced. Also: last operational site on register was Denver - Closed.</t>
+          <t>Cost $1130 on MD-00095; Missing at Unknown. Hugh Talbot has Separated status in the people extract. TR-00095 ties to MD-00095; dock date 2026-07-08, approval APR-00095. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00095. Also: offboarding ticket OFF-00095 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -17192,7 +17211,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00096: Missing, Unknown, $6425 acquisition basis. HR agrees Mira Adelman (E0084) is still Separated. Movement TR-00096 posted 2026-01-18 and inbound 01/19/2026, approval APR-00096. PO PO-2025-0016 on file; no matching FAR row for MD-00096. offboarding ticket OFF-00096 referenced. last operational site on register was Chicago - Closed.</t>
+          <t>MD-00096 stays Missing at Unknown (Cisco C9300, $6425). Mira Adelman has Separated status in the people extract. Log TR-00096: received 01/19/2026, approval APR-00096. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00096. Also: offboarding ticket OFF-00096 referenced. Note — last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -17304,7 +17323,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00097: verified Missing, location Unknown, cost $2120. No term conflict for E0085; status Separated. Movement TR-00097 posted 01/21/2026 and inbound Jan 27, 2026, approval APR-00097. PO PO-2022-0017 on file; no matching FAR row for MD-00097. offboarding ticket OFF-00097 referenced. Also: last operational site on register was Denver - Closed.</t>
+          <t>MD-00097 stays Missing at Unknown (Lenovo ThinkPad T14, $2120). Quincy Rhodes has Separated status in the people extract. TR-00097 ties to MD-00097; dock date Jan 27, 2026, approval APR-00097. Purchasing PO-2022-0017 without a capital line for MD-00097. Also: offboarding ticket OFF-00097 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -17416,7 +17435,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>MD-00098 (Dell U2723QE) — Missing / Unknown per the cited movement and people records. Custodian Sloane Richter (E0086) is Separated in HR. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. PO PO-2022-0017 on file; no matching FAR row for MD-00098. offboarding ticket OFF-00098 referenced. last operational site on register was Chicago - Closed.</t>
+          <t>MD-00098 stays Missing at Unknown (Dell U2723QE, $520). Sloane Richter has Separated status in the people extract. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. Purchasing PO-2022-0017 without a capital line for MD-00098. Also: offboarding ticket OFF-00098 referenced. Note — last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -17528,7 +17547,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00099: Missing at Unknown; acquisition $995. Employment check: E0087 remains Separated. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. PO PO-2022-0017 on file; no matching FAR row for MD-00099. Note — offboarding ticket OFF-00099 referenced. Also: last operational site on register was Denver - Closed.</t>
+          <t>MD-00099 stays Missing at Unknown (Samsung Galaxy S24, $995). Nolan Vega has Separated status in the people extract. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. Purchasing PO-2022-0017 without a capital line for MD-00099. Also: offboarding ticket OFF-00099 referenced. Note — last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -17640,7 +17659,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 MD-00100 ($6290) reconciled to Missing at Unknown. No term conflict for E0088; status Separated. Movement TR-00100 posted 05/01/2026 and inbound May 05, 2026, approval APR-00100. PO PO-2022-0017 on file; no matching FAR row for MD-00100. offboarding ticket OFF-00100 referenced. last operational site on register was Chicago - Closed.</t>
+          <t>Field review: MD-00100 Missing @ Unknown. Ivy Chenoweth has Separated status in the people extract. equipment_transfer_log TR-00100, approval APR-00100; received May 05, 2026. Purchasing PO-2022-0017 without a capital line for MD-00100. Also: offboarding ticket OFF-00100 referenced. Note — last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -17752,7 +17771,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00101: Retired/Pending Disposal at Seattle; acquisition $1985. Movement TR-00101 posted Jun 05, 2026 and inbound 2026-06-07, approval APR-00101. PO PO-2022-0017 on file; no matching FAR row for MD-00101. Note — offboarding ticket RET-00101 referenced.</t>
+          <t>MD-00101 stays Retired/Pending Disposal at Seattle (MacBook Pro 14, $1985). Assignment TR-00101; receive column 2026-06-07, approval APR-00101. Purchasing PO-2022-0017 without a capital line for MD-00101. Also: offboarding ticket RET-00101 referenced.</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -17864,7 +17883,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE tagged MD-00102 remains Retired/Pending Disposal in Atlanta on the corrected register. equipment_transfer_log TR-00102, approval APR-00102; received 01/11/2026. PO PO-2022-0017 on file; no matching FAR row for MD-00102. Also: offboarding ticket RET-00102 referenced.</t>
+          <t>MD-00102 stays Retired/Pending Disposal at Atlanta (Dell U2723QE, $700). TR-00102 for MD-00102 — received 01/11/2026, approval APR-00102. Purchasing PO-2022-0017 without a capital line for MD-00102. Also: offboarding ticket RET-00102 referenced.</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -17976,7 +17995,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00103: Retired/Pending Disposal, Chicago, $1175 acquisition basis. TR-00103 ties to MD-00103; dock date Feb 14, 2026, approval APR-00103. PO PO-2023-0018 on file; no matching FAR row for MD-00103. Note — offboarding ticket RET-00103 referenced.</t>
+          <t>MD-00103 stays Retired/Pending Disposal at Chicago (Samsung Galaxy S24, $1175). Inbound stamp on TR-00103 is Feb 14, 2026, approval APR-00103. Purchasing PO-2023-0018 without a capital line for MD-00103. Also: offboarding ticket RET-00103 referenced.</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -18088,7 +18107,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00104 at Retired/Pending Disposal (Dallas) once transfers and HR were read. Transfer TR-00104 shows receipt 2026-03-18, approval APR-00104. PO PO-2023-0018 on file; no matching FAR row for MD-00104. offboarding ticket RET-00104 referenced.</t>
+          <t>MD-00104 stays Retired/Pending Disposal at Dallas (Cisco C9300, $6470). Log TR-00104: received 2026-03-18, approval APR-00104. Purchasing PO-2023-0018 without a capital line for MD-00104. Also: offboarding ticket RET-00104 referenced.</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -18200,7 +18219,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00105 stays Retired/Pending Disposal in Denver. equipment_transfer_log TR-00105, approval APR-00105; received 04/21/2026. PO PO-2023-0018 on file; no matching FAR row for MD-00105. Also: offboarding ticket RET-00105 referenced.</t>
+          <t>MD-00105 stays Retired/Pending Disposal at Denver (Dell Latitude 7440, $1850). TR-00105 ties to MD-00105; dock date 04/21/2026, approval APR-00105. Purchasing PO-2023-0018 without a capital line for MD-00105. Also: offboarding ticket RET-00105 referenced.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -18312,7 +18331,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00106 at Retired/Pending Disposal (New York) once transfers and HR were read. equipment_transfer_log TR-00106, approval APR-00106; received May 25, 2026. PO PO-2023-0018 on file; no matching FAR row for MD-00106. offboarding ticket RET-00106 referenced.</t>
+          <t>MD-00106 reads Retired/Pending Disposal at New York (Dell U2723QE, $565). TR-00106 ties to MD-00106; dock date May 25, 2026, approval APR-00106. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00106. Also: offboarding ticket RET-00106 referenced.</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -18424,7 +18443,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 MD-00107 ($1040) reconciled to Retired/Pending Disposal at Seattle. equipment_transfer_log TR-00107, approval APR-00107; received 2026-06-27. PO PO-2023-0018 on file; no matching FAR row for MD-00107. Note — offboarding ticket RET-00107 referenced.</t>
+          <t>MD-00107 reads Retired/Pending Disposal at Seattle (Samsung Galaxy S24, $1040). Transfer TR-00107 shows receipt 2026-06-27, approval APR-00107. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00107. Also: offboarding ticket RET-00107 referenced.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -18536,7 +18555,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00108 at Retired/Pending Disposal (Atlanta) once transfers and HR were read. Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO PO-2023-0018 on file; no matching FAR row for MD-00108. offboarding ticket RET-00108 referenced.</t>
+          <t>MD-00108 reads Retired/Pending Disposal at Atlanta (Cisco C9300, $6335). Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00108. Also: offboarding ticket RET-00108 referenced.</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -18648,7 +18667,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 (Lenovo ThinkPad T14) — Retired/Pending Disposal / Chicago per the cited movement and people records. Movement TR-00109 posted 02/02/2026 and inbound Feb 04, 2026, approval APR-00109. PO PO-2024-0019 on file; no matching FAR row for MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
+          <t>MD-00109 reads Retired/Pending Disposal at Chicago (Lenovo ThinkPad T14, $2030). equipment_transfer_log TR-00109, approval APR-00109; received Feb 04, 2026. PO-2024-0019 in hardware_purchase_orders.csv; FAR silent on MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -18760,7 +18779,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>MD-00110 (Dell U2723QE) — Retired/Pending Disposal / Dallas per the cited movement and people records. TR-00110 ties to MD-00110; dock date 2026-03-08, approval APR-00110. PO PO-2024-0019 on file; no matching FAR row for MD-00110. Also: offboarding ticket RET-00110 referenced.</t>
+          <t>MD-00110 stays Retired/Pending Disposal at Dallas (Dell U2723QE, $745). Inbound stamp on TR-00110 is 2026-03-08, approval APR-00110. Purchasing PO-2024-0019 without a capital line for MD-00110. Also: offboarding ticket RET-00110 referenced.</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -18872,7 +18891,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00111: Disposed, Disposed, $1220 acquisition basis. equipment_transfer_log TR-00111, approval APR-00111; received 04/13/2026. PO PO-2024-0019 on file; no matching FAR row for MD-00111. Note — offboarding ticket RET-00111 referenced.</t>
+          <t>Corrected register carries MD-00111 as Disposed in Disposed. Log TR-00111: received 04/13/2026, approval APR-00111. Purchasing PO-2024-0019 without a capital line for MD-00111. Also: offboarding ticket RET-00111 referenced.</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -18980,7 +18999,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00112: Disposed at Disposed; acquisition $6200. Transfer TR-00112 shows receipt May 15, 2026, approval APR-00112. PO PO-2024-0019 on file; no matching FAR row for MD-00112. offboarding ticket RET-00112 referenced.</t>
+          <t>Corrected register carries MD-00112 as Disposed in Disposed. TR-00112 ties to MD-00112; dock date May 15, 2026, approval APR-00112. Purchasing PO-2024-0019 without a capital line for MD-00112. Also: offboarding ticket RET-00112 referenced.</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19088,7 +19107,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00113: Disposed at Disposed; acquisition $1895. equipment_transfer_log TR-00113, approval APR-00113; received 2026-06-18. PO PO-2024-0019 on file; no matching FAR row for MD-00113. offboarding ticket RET-00113 referenced.</t>
+          <t>Corrected register carries MD-00113 as Disposed in Disposed. Transfer TR-00113 shows receipt 2026-06-18, approval APR-00113. Purchasing PO-2024-0019 without a capital line for MD-00113. Also: offboarding ticket RET-00113 referenced.</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19196,7 +19215,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00114 stays Retired/Pending Disposal in Disposed (certificate missing). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. PO PO-2024-0019 on file; no matching FAR row for MD-00114. Also: offboarding ticket RET-00114 referenced. Note — no verified disposal certificate located.</t>
+          <t>MD-00114 stays Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $610). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. Purchasing PO-2024-0019 without a capital line for MD-00114. Also: offboarding ticket RET-00114 referenced. Note — no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19308,7 +19327,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 tagged MD-00115 remains Disposed in Disposed on the corrected register. TR-00115 ties to MD-00115; dock date Feb 25, 2026, approval APR-00115. PO PO-2025-0020 on file; no matching FAR row for MD-00115. offboarding ticket RET-00115 referenced.</t>
+          <t>Corrected register carries MD-00115 as Disposed in Disposed. equipment_transfer_log TR-00115, approval APR-00115; received Feb 25, 2026. PO PO-2025-0020 on file; no matching FAR row for MD-00115. Also: offboarding ticket RET-00115 referenced.</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19416,7 +19435,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Location Disposed and status Disposed on MD-00116 match the stronger transaction trail. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. PO PO-2025-0020 on file; no matching FAR row for MD-00116. offboarding ticket RET-00116 referenced.</t>
+          <t>Looked up MD-00116 across CSV/XLSX inputs — Disposed, Disposed. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. Purchasing PO-2025-0020 without a capital line for MD-00116. Also: offboarding ticket RET-00116 referenced.</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19524,7 +19543,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Location Disposed and status Disposed on MD-00117 match the stronger transaction trail. equipment_transfer_log TR-00117, approval APR-00117; received 05/02/2026. PO PO-2025-0020 on file; no matching FAR row for MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
+          <t>Looked up MD-00117 across CSV/XLSX inputs — Disposed, Disposed. Assignment TR-00117; receive column 05/02/2026, approval APR-00117. Purchasing PO-2025-0020 without a capital line for MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19632,7 +19651,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 (Dell U2723QE) — Retired/Pending Disposal / Disposed (certificate missing) per the cited movement and people records. Movement TR-00118 posted 06/03/2026 and inbound Jun 04, 2026, approval APR-00118. PO PO-2025-0020 on file; no matching FAR row for MD-00118. offboarding ticket RET-00118 referenced. Also: no verified disposal certificate located.</t>
+          <t>MD-00118 reads Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $790). TR-00118 for MD-00118 — received Jun 04, 2026, approval APR-00118. Purchasing PO-2025-0020 without a capital line for MD-00118. Also: offboarding ticket RET-00118 referenced. Note — no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19744,7 +19763,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00119 at Disposed (Disposed) once transfers and HR were read. equipment_transfer_log TR-00119, approval APR-00119; received 2026-07-09. PO PO-2025-0020 on file; no matching FAR row for MD-00119. offboarding ticket RET-00119 referenced.</t>
+          <t>Looked up MD-00119 across CSV/XLSX inputs — Disposed, Disposed. Inbound stamp on TR-00119 is 2026-07-09, approval APR-00119. Purchasing PO-2025-0020 without a capital line for MD-00119. Also: offboarding ticket RET-00119 referenced.</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -19856,7 +19875,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00120: Disposed at Disposed; acquisition $6245. Movement TR-00120 posted 2026-01-18 and inbound 01/20/2026, approval APR-00120. PO PO-2025-0020 on file; no matching FAR row for MD-00120. Also: offboarding ticket RET-00120 referenced.</t>
+          <t>Corrected register carries MD-00120 as Disposed in Disposed. Transfer TR-00120 shows receipt 01/20/2026, approval APR-00120. PO PO-2025-0020 on file; no matching FAR row for MD-00120. Also: offboarding ticket RET-00120 referenced.</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -19960,7 +19979,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00121 at Available (Chicago) once transfers and HR were read. Transfer TR-00121 shows receipt Jan 21, 2026, approval APR-00121. PO PO-2022-0021 on file; no matching FAR row for MD-00121.</t>
+          <t>MD-00121 reads Available at Chicago (Lenovo ThinkPad T14, $1940). Movement TR-00121 posted 01/21/2026 and inbound Jan 21, 2026, approval APR-00121. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00121.</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -20068,7 +20087,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00122 at Available (Dallas) once transfers and HR were read. TR-00122 ties to MD-00122; dock date 2026-02-25, approval APR-00122. PO PO-2022-0021 on file; no matching FAR row for MD-00122.</t>
+          <t>MD-00122 reads Available at Dallas (Dell U2723QE, $655). equipment_transfer_log TR-00122, approval APR-00122; received 2026-02-25. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00122.</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20176,7 +20195,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>Verified outcome for MD-00123: Available at Denver; acquisition $1130. Movement TR-00123 posted 2026-03-31 and inbound 04/03/2026, approval APR-00123. PO PO-2022-0021 on file; no matching FAR row for MD-00123.</t>
+          <t>MD-00123 reads Available at Denver (Samsung Galaxy S24, $1130). Assignment TR-00123; receive column 04/03/2026, approval APR-00123. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00123.</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20284,7 +20303,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00124: Available, New York, $6425 acquisition basis. TR-00124 ties to MD-00124; dock date May 01, 2026, approval APR-00124. PO PO-2022-0021 on file; no matching FAR row for MD-00124.</t>
+          <t>MD-00124 reads Available at New York (Cisco C9300, $6425). TR-00124 for MD-00124 — received May 01, 2026, approval APR-00124. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00124.</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20392,7 +20411,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>Location Seattle and status Available on MD-00125 match the stronger transaction trail. TR-00125 ties to MD-00125; dock date 2026-06-08, approval APR-00125. PO PO-2022-0021 on file; no matching FAR row for MD-00125.</t>
+          <t>MD-00125 reads Available at Seattle (MacBook Pro 14, $2120). Inbound stamp on TR-00125 is 2026-06-08, approval APR-00125. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00125.</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20500,7 +20519,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>After cross-file review, MD-00126 stays Available in Atlanta. equipment_transfer_log TR-00126, approval APR-00126; received 01/12/2026. PO PO-2022-0021 on file; no matching FAR row for MD-00126.</t>
+          <t>MD-00126 stays Available at Atlanta (Dell U2723QE, $520). Inbound stamp on TR-00126 is 01/12/2026, approval APR-00126. PO PO-2022-0021 on file; no matching FAR row for MD-00126.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20612,7 +20631,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>Outcome on MD-00127: In Use, Denver, $995 acquisition basis. No term conflict for E0061; status Transferred. equipment_transfer_log TR-00127, approval field blank; received Feb 17, 2026. PO PO-2023-0022 on file; no matching FAR row for MD-00127.</t>
+          <t>Corrected row MD-00127: In Use, Denver, $995 — Samsung Galaxy S24. Checked E0061: Transferred. Log TR-00127: received Feb 17, 2026, approval field blank. PO PO-2023-0022 on file; no matching FAR row for MD-00127.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20724,7 +20743,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 tagged MD-00128 remains In Use in New York on the corrected register. hr_employee_status shows Bianca Silva (E0062) as Transferred. Transfer TR-00128 shows receipt 2026-03-19, approval APR-00128. PO PO-2023-0022 on file; no matching FAR row for MD-00128.</t>
+          <t>Corrected row MD-00128: In Use, New York, $6290 — Cisco C9300. Checked E0062: Transferred. TR-00128 ties to MD-00128; dock date 2026-03-19, approval APR-00128. PO PO-2023-0022 on file; no matching FAR row for MD-00128.</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20832,7 +20851,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>Register row MD-00129: verified In Use, location Seattle, cost $1985. hr_employee_status shows Greg Hollis (E0063) as Transferred. TR-00129 ties to MD-00129; dock date 04/21/2026, approval APR-00129. PO PO-2023-0022 on file; no matching FAR row for MD-00129.</t>
+          <t>Corrected row MD-00129: In Use, Seattle, $1985 — Dell Latitude 7440. Checked E0063: Transferred. Transfer TR-00129 shows receipt 04/21/2026, approval APR-00129. PO PO-2023-0022 on file; no matching FAR row for MD-00129.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -20940,7 +20959,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation kept MD-00130 at In Use (Atlanta) once transfers and HR were read. No term conflict for E0064; status Transferred. equipment_transfer_log TR-00130, approval APR-00130; received May 28, 2026. PO PO-2023-0022 on file; no matching FAR row for MD-00130. Also: $700 below $2,500 — missing FA expected.</t>
+          <t>Dell U2723QE on MD-00130 is In Use in Atlanta site; basis $700. Naomi Berger has Transferred status in the people extract. Assignment TR-00130; receive column May 28, 2026, approval APR-00130. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00130. Also: $700 below $2,500 — missing FA expected.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -21034,7 +21053,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>Location Chicago and status In Use on MD-00131 match the stronger transaction trail. Employment check: E0065 remains Transferred. equipment_transfer_log TR-00131, approval APR-00131; received 2026-06-28. PO PO-2023-0022 on file; no matching FAR row for MD-00131. $1175 below $2,500 — missing FA expected.</t>
+          <t>Samsung Galaxy S24 on MD-00131 is In Use in Chicago site; basis $1175. Felix Moreno has Transferred status in the people extract. TR-00131 for MD-00131 — received 2026-06-28, approval APR-00131. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00131. Also: $1175 below $2,500 — missing FA expected.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -21128,7 +21147,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>MD-00132 closed as In Use; operating site Dallas; unit cost $6470. hr_employee_status shows Sharon Quinlan (E0066) as Transferred. Transfer TR-00132 shows receipt 01/31/2026, approval APR-00132. PO PO-2023-0022 on file; no matching FAR row for MD-00132. Note — RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
+          <t>Cisco C9300 on MD-00132 is In Use in Dallas site; basis $6470. Sharon Quinlan has Transferred status in the people extract. Inbound stamp on TR-00132 is 01/31/2026, approval APR-00132. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00132. Also: RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -21203,7 +21222,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Exception Register</t>
         </is>
@@ -21216,68 +21235,69 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Exception ID</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Asset Tag</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Serial Number</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Related Record(s)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Financial Exposure</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>Owner by Role</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Resolution Deadline</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>Evidence Assessment</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Certification Impact</t>
         </is>
@@ -21320,7 +21340,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Reconcile PO-2024-0003 / FA-000017 / register cost for MD-00017.</t>
+          <t>Finance Controller owns cost-basis cleanup on MD-00017.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -21340,7 +21360,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>FA-000017 cost 2070.0 vs register 1985.0. PO-2024-0003.</t>
+          <t>Pulled PO-2024-0003 and FA-000017; numbers diverge for MD-00017.</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -21386,7 +21406,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Break the duplicate. MD-LA-050021 cannot stay on both MD-00021,MD-00025.</t>
+          <t>Two assets share MD-LA-050021 (MD-00021,MD-00025). Bench-validate and issue a new serial.</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -21406,7 +21426,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Duplicate MD-LA-050021 is in the extract. Physical next.</t>
+          <t>Serial MD-LA-050021 appears on more than one tag (MD-00021,MD-00025).</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -21452,7 +21472,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Get MD-00025 off Denver - Closed. Operating location is Chicago.</t>
+          <t>MD-00025 location field lagged after consolidation; update from Denver - Closed to Chicago (EX-0003).</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -21472,7 +21492,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed is a closed site. TR-00025 points elsewhere. Live office Chicago.</t>
+          <t>Closed floor Denver - Closed remains on MD-00025 despite transfer evidence (EX-0003, TR-00025).</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -21518,7 +21538,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Two assets share MD-LA-050021 (MD-00021,MD-00025). Validate on the bench and issue a new serial.</t>
+          <t>Retag required — MD-LA-050021 collision involving MD-00025.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -21538,7 +21558,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Two tags, one serial (MD-LA-050021). Flagged both.</t>
+          <t>Serial MD-LA-050021 appears on more than one tag (MD-00021,MD-00025) [EX-0004].</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -21584,7 +21604,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00026: Chicago - Closed → Dallas.</t>
+          <t>MD-00026 location field lagged after consolidation; update from Chicago - Closed to Dallas (EX-0005).</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -21604,7 +21624,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Site code is stale. Chicago - Closed vs Dallas.</t>
+          <t>Walked register vs HR/transfer: MD-00026 still says Chicago - Closed (EX-0005).</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -21650,7 +21670,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00027 to Denver.</t>
+          <t>Denver - Closed is no longer occupied. Park MD-00027 at Denver on the register (EX-0006).</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -21670,7 +21690,7 @@
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>TR-00027 destination isn't the shuttered office on the register.</t>
+          <t>Register still codes MD-00027 to Denver - Closed; TR-00027 points to Denver (EX-0006).</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -21716,7 +21736,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00028 coded to Chicago - Closed.</t>
+          <t>MD-00028 cannot remain on shuttered floor Chicago - Closed. Set location to New York (EX-0007).</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -21736,7 +21756,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is locked. I'm not leaving MD-00028 there on paper. New York is the operating site.</t>
+          <t>Location on MD-00028 is consolidation debt (Chicago - Closed, EX-0007).</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -21782,7 +21802,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00029 out of Denver - Closed and park it at Seattle.</t>
+          <t>Closed floor Denver - Closed stays on MD-00029; rewrite required (EX-0008).</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -21802,7 +21822,7 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Consolidation leftover: MD-00029 @ Denver - Closed.</t>
+          <t>Consolidation left MD-00029 @ Denver - Closed; ops now use Seattle (EX-0008).</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -21848,7 +21868,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Register still has the shuttered floor (Chicago - Closed). Put Atlanta on the row.</t>
+          <t>Register still lists MD-00030 at Chicago - Closed. Replace with Atlanta (EX-0009).</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -21868,7 +21888,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>MD-00030 still coded to a floor we don't occupy (Chicago - Closed).</t>
+          <t>TR-00030 destination is not the shuttered office listed for MD-00030 (EX-0009).</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -21914,7 +21934,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00031: Denver - Closed → Chicago.</t>
+          <t>Fix MD-00031: register site Denver - Closed conflicts with current ops at Chicago (EX-0010).</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -21934,7 +21954,7 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Site code is stale. Denver - Closed vs Chicago.</t>
+          <t>Did not treat closed building Denver - Closed as live location for MD-00031 (EX-0010).</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -21980,7 +22000,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00032 to Dallas.</t>
+          <t>Chicago - Closed is no longer occupied. Park MD-00032 at Dallas on the register (EX-0011).</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -22000,7 +22020,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>TR-00032 destination isn't the shuttered office on the register.</t>
+          <t>Finding EX-0011: MD-00032 location stale at Chicago - Closed; prefer Dallas.</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -22046,7 +22066,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00033 coded to Denver - Closed.</t>
+          <t>Closed floor Denver - Closed stays on MD-00033; rewrite required (EX-0012).</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -22066,7 +22086,7 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is locked. I'm not leaving MD-00033 there on paper. Denver is the operating site.</t>
+          <t>Register still codes MD-00033 to Denver - Closed; TR-00033 points to Denver (EX-0012).</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -22112,7 +22132,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00034 out of Chicago - Closed and park it at New York.</t>
+          <t>Do not leave MD-00034 assigned to unused floor Chicago - Closed (EX-0013).</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -22132,7 +22152,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Consolidation leftover: MD-00034 @ Chicago - Closed.</t>
+          <t>Register still codes MD-00034 to Chicago - Closed; TR-00034 points to New York (EX-0013).</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -22178,7 +22198,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Finance to align cost on MD-00034: register 790.0 vs ledger 930.0 (FA-000034).</t>
+          <t>Align cost on MD-00034: register 790.0 vs ledger 930.0 (FA-000034).</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -22198,7 +22218,7 @@
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>FA-000034 cost 930.0 vs register 790.0. PO-2023-0006.</t>
+          <t>Pulled PO-2023-0006 and FA-000034; numbers diverge for MD-00034.</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -22244,7 +22264,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is shut. Rewrite the register location (MD-00035).</t>
+          <t>HR-aligned site for MD-00035 is Seattle; register still says Denver - Closed (EX-0015).</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -22264,7 +22284,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Denver - Closed. TR-00035.</t>
+          <t>Location on MD-00035 is consolidation debt (Denver - Closed, EX-0015).</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -22310,7 +22330,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Update MD-00036 location. Atlanta is what transfer/HR support.</t>
+          <t>Update register location for MD-00036 before the next cert packet (EX-0016).</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -22330,7 +22350,7 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00036.</t>
+          <t>HR/transfer support Atlanta; register kept Chicago - Closed for MD-00036 (EX-0016).</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -22376,7 +22396,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Register still has the shuttered floor (Denver - Closed). Put Chicago on the row.</t>
+          <t>IT Asset Specialist: recode MD-00037 off Denver - Closed; Chicago is the live office per TR-00037 (EX-0017).</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -22396,7 +22416,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00037 didn't survive the consolidation (Denver - Closed).</t>
+          <t>Site code on MD-00037 did not survive consolidation (Denver - Closed, EX-0017).</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -22442,7 +22462,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00038: Chicago - Closed → Dallas.</t>
+          <t>HR-aligned site for MD-00038 is Dallas; register still says Chicago - Closed (EX-0018).</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -22462,7 +22482,7 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>Walked the register vs HR/transfer. MD-00038 still says Chicago - Closed.</t>
+          <t>Finding EX-0018: MD-00038 location stale at Chicago - Closed; prefer Dallas.</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -22508,7 +22528,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00039 to Denver.</t>
+          <t>Remove closed-site coding on MD-00039 (Denver - Closed → Denver, EX-0019).</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -22528,7 +22548,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed is a closed site. TR-00039 points elsewhere. Live office Denver.</t>
+          <t>Denver is the operating site; MD-00039 still lists Denver - Closed (EX-0019).</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -22574,7 +22594,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shut. Rewrite the register location (MD-00040).</t>
+          <t>IT Asset Specialist to retire Chicago - Closed on MD-00040 and apply New York (EX-0020).</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -22594,7 +22614,7 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Chicago - Closed. TR-00040.</t>
+          <t>Location evidence for MD-00040: closed floor Chicago - Closed vs live New York (EX-0020).</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -22640,7 +22660,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Update MD-00041 location. Seattle is what transfer/HR support.</t>
+          <t>Update register location for MD-00041 before the next cert packet (EX-0021).</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -22660,7 +22680,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00041.</t>
+          <t>Register location Denver - Closed conflicts with current footprint for MD-00041 (EX-0021).</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -22706,7 +22726,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Register still has the shuttered floor (Chicago - Closed). Put Atlanta on the row. (EX-0022)</t>
+          <t>Remove closed-site coding on MD-00042 (Chicago - Closed → Atlanta, EX-0022).</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -22726,7 +22746,7 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00042 didn't survive the consolidation (Chicago - Closed).</t>
+          <t>Closed floor Chicago - Closed remains on MD-00042 despite transfer evidence (EX-0022, TR-00042).</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -22772,7 +22792,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00043: Denver - Closed → Chicago.</t>
+          <t>IT Asset Specialist owns the location rewrite for MD-00043 at Denver - Closed (EX-0023).</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -22792,7 +22812,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Walked the register vs HR/transfer. MD-00043 still says Denver - Closed.</t>
+          <t>Location on MD-00043 is consolidation debt (Denver - Closed, EX-0023).</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -22838,7 +22858,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00044 to Dallas.</t>
+          <t>MD-00044 / Chicago - Closed is a consolidation leftover — move to Dallas (EX-0024).</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -22858,7 +22878,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>Register location Chicago - Closed is a closed site. TR-00044 points elsewhere. Live office Dallas.</t>
+          <t>Walked register vs HR/transfer: MD-00044 still says Chicago - Closed (EX-0024).</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -22904,7 +22924,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00045 coded to Denver - Closed.</t>
+          <t>IT Asset Specialist: recode MD-00045 off Denver - Closed; Denver is the live office per TR-00045 (EX-0025).</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -22924,7 +22944,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Denver - Closed. TR-00045.</t>
+          <t>Register location Denver - Closed conflicts with current footprint for MD-00045 (EX-0025).</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -22970,7 +22990,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00046 out of Chicago - Closed and park it at New York.</t>
+          <t>Fix MD-00046: register site Chicago - Closed conflicts with current ops at New York (EX-0026).</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -22990,7 +23010,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00046.</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00046 there on paper — New York is live (EX-0026).</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -23036,7 +23056,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Clear the closed-site assignment. MD-00047 belongs at Seattle.</t>
+          <t>IT Asset Specialist: recode MD-00047 off Denver - Closed; Seattle is the live office per TR-00047 (EX-0027).</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -23056,7 +23076,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00047 didn't survive the consolidation (Denver - Closed).</t>
+          <t>Physical sites changed; MD-00047 register did not (Denver - Closed, EX-0027).</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -23102,7 +23122,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Same finding as the walkthrough: MD-00048 still tagged Chicago - Closed. Change it.</t>
+          <t>Closed floor Chicago - Closed stays on MD-00048; rewrite required (EX-0028).</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -23122,7 +23142,7 @@
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>Walked the register vs HR/transfer. MD-00048 still says Chicago - Closed.</t>
+          <t>Unused-office coding on MD-00048 is unsupported by movement files (EX-0028).</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -23168,7 +23188,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Get MD-00049 off Denver - Closed. Operating location is Chicago.</t>
+          <t>MD-00049 cannot remain on shuttered floor Denver - Closed. Set location to Chicago (EX-0029).</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -23188,7 +23208,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed is a closed site. TR-00049 points elsewhere. Live office Chicago.</t>
+          <t>Physical sites changed; MD-00049 register did not (Denver - Closed, EX-0029).</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -23234,7 +23254,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00050 coded to Chicago - Closed.</t>
+          <t>Fix MD-00050: register site Chicago - Closed conflicts with current ops at Dallas (EX-0030).</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -23254,7 +23274,7 @@
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Chicago - Closed. TR-00050.</t>
+          <t>Site code on MD-00050 did not survive consolidation (Chicago - Closed, EX-0030).</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -23300,7 +23320,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00051 out of Denver - Closed and park it at Denver.</t>
+          <t>Operating site for MD-00051 is Denver; TR-00051 confirms, not Denver - Closed (EX-0031).</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -23320,7 +23340,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00051.</t>
+          <t>Closed-site leftover on extract for MD-00051 (Denver - Closed). TR-00051. EX-0031.</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -23366,7 +23386,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Cost basis mismatch MD-00051. Pull PO-2022-0009 and fix FA-000051 or the register.</t>
+          <t>Reconcile PO-2022-0009 / FA-000051 / register cost for MD-00051.</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -23386,7 +23406,7 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>FA-000051 cost 1250.0 vs register 1040.0. PO-2022-0009.</t>
+          <t>Cost spread on MD-00051: ITAM $1040.0, FAR 1250.0 (FA-000051).</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -23432,7 +23452,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shut. Rewrite the register location (MD-00052).</t>
+          <t>IT Asset Specialist: recode MD-00052 off Chicago - Closed; New York is the live office per TR-00052 (EX-0033).</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -23452,7 +23472,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is locked. I'm not leaving MD-00052 there on paper. New York is the operating site.</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00052 there on paper — New York is live (EX-0033).</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -23498,7 +23518,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Update MD-00053 location. Seattle is what transfer/HR support.</t>
+          <t>HR-aligned site for MD-00053 is Seattle; register still says Denver - Closed (EX-0034).</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -23518,7 +23538,7 @@
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>Consolidation leftover: MD-00053 @ Denver - Closed.</t>
+          <t>Location on MD-00053 is consolidation debt (Denver - Closed, EX-0034).</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -23564,7 +23584,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Register still has the shuttered floor (Chicago - Closed). Put Atlanta on the row. (EX-0035)</t>
+          <t>IT Asset Specialist to retire Chicago - Closed on MD-00054 and apply Atlanta (EX-0035).</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -23584,7 +23604,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>MD-00054 still coded to a floor we don't occupy (Chicago - Closed).</t>
+          <t>TR-00054 destination is not the shuttered office listed for MD-00054 (EX-0035).</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -23630,7 +23650,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00055: Denver - Closed → Chicago.</t>
+          <t>Register still lists MD-00055 at Denver - Closed. Replace with Chicago (EX-0036).</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -23650,7 +23670,7 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>Site code is stale. Denver - Closed vs Chicago. (EX-0036)</t>
+          <t>Location on MD-00055 is consolidation debt (Denver - Closed, EX-0036).</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -23696,7 +23716,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00056 to Dallas.</t>
+          <t>IT Asset Specialist: recode MD-00056 off Chicago - Closed; Dallas is the live office per TR-00056 (EX-0037).</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -23716,7 +23736,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>TR-00056 destination isn't the shuttered office on the register.</t>
+          <t>TR-00056 destination is not the shuttered office listed for MD-00056 (EX-0037).</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -23762,7 +23782,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00057 coded to Denver - Closed.</t>
+          <t>Fix MD-00057: register site Denver - Closed conflicts with current ops at Denver (EX-0038).</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -23782,7 +23802,7 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is locked. I'm not leaving MD-00057 there on paper. Denver is the operating site.</t>
+          <t>Location on MD-00057 is consolidation debt (Denver - Closed, EX-0038).</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -23828,7 +23848,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>E0071 should not still own MD-00058 on the register.</t>
+          <t>Separated ID E0071 must leave MD-00058 before status changes.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -23848,7 +23868,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>Checked the term date against the assignment. Stale owner on MD-00058.</t>
+          <t>People extract vs register: MD-00058 retained leaver E0071. OFF-00058.</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -23894,7 +23914,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist to recode location — MD-00058 is not on the closed floor.</t>
+          <t>Do not leave MD-00058 assigned to unused floor Chicago - Closed (EX-0040).</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -23914,7 +23934,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>Register location Chicago - Closed is a closed site. TR-00058 points elsewhere. Live office New York.</t>
+          <t>Unused-office coding on MD-00058 is unsupported by movement files (EX-0040).</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -23960,7 +23980,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>TR-00058 has a blank approval. Ops manager signs or we unwind the move.</t>
+          <t>§4 gap on TR-00058 for MD-00058; get APR or reverse.</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -23980,7 +24000,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>Opened TR-00058. No APR- id. That's the finding.</t>
+          <t>Transfer log TR-00058: move recorded, APR missing.</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -24026,7 +24046,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Close the people assignment on MD-00059. Ticket OFF-00059.</t>
+          <t>Close people assignment on MD-00059; ticket OFF-00059.</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -24046,7 +24066,7 @@
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>People record is closed; MD-00059 isn't. OFF-00059.</t>
+          <t>People extract vs register: MD-00059 retained leaver E0072. OFF-00059.</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -24092,7 +24112,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Update MD-00059 location. Seattle is what transfer/HR support.</t>
+          <t>Walkthrough finding EX-0043: MD-00059 still shows Denver - Closed. Correct to Seattle.</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -24112,7 +24132,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00059.</t>
+          <t>Seattle is the operating site; MD-00059 still lists Denver - Closed (EX-0043).</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -24158,7 +24178,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Get a retrospective approval on TR-00059 or reverse it (ITAM-001 §4).</t>
+          <t>Approval missing on TR-00059. Retro sign-off or return MD-00059.</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -24178,7 +24198,7 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>Opened TR-00059. No APR- id. That's the finding.</t>
+          <t>§4 evidence gap — TR-00059 lacks approval for MD-00059.</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -24224,7 +24244,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Recover or lose-process MD-00060, but first drop the former employee as owner.</t>
+          <t>Assignment on MD-00060 survived HR term for E0073. Correct it.</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -24244,7 +24264,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>OFF-00060 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>Register owner on MD-00060 is stale relative to HR for E0073 (EX-0045).</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -24290,7 +24310,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Fix the site on MD-00060. Not at Chicago - Closed anymore.</t>
+          <t>Do not leave MD-00060 assigned to unused floor Chicago - Closed (EX-0046).</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -24310,7 +24330,7 @@
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>Walked the register vs HR/transfer. MD-00060 still says Chicago - Closed.</t>
+          <t>Location evidence for MD-00060: closed floor Chicago - Closed vs live Atlanta (EX-0046).</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -24356,7 +24376,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Move MD-00061 off the separated custodian before we talk redeploy.</t>
+          <t>HR Operations Lead: remove E0074 from MD-00061 and park the kit.</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -24376,7 +24396,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>MD-00061 custodian is a former employee in HR (E0074).</t>
+          <t>Custodian mismatch MD-00061↔E0074 documented under EX-0047.</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -24422,7 +24442,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Clear the closed-site assignment. MD-00061 belongs at Chicago.</t>
+          <t>Fix MD-00061: register site Denver - Closed conflicts with current ops at Chicago (EX-0048).</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -24442,7 +24462,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>MD-00061 still coded to a floor we don't occupy (Denver - Closed).</t>
+          <t>Finding EX-0048: MD-00061 location stale at Denver - Closed; prefer Chicago.</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -24488,7 +24508,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Close the people assignment on MD-00062. Ticket OFF-00062.</t>
+          <t>Recover or write-off later; first take E0075 off MD-00062.</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -24508,7 +24528,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>People record is closed; MD-00062 isn't. OFF-00062.</t>
+          <t>MD-00062 should have moved off E0075 when HR flipped status (EX-0049).</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -24554,7 +24574,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Update MD-00062 location. Dallas is what transfer/HR support.</t>
+          <t>MD-00062 / Chicago - Closed is a consolidation leftover — move to Dallas (EX-0050).</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -24574,7 +24594,7 @@
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00062.</t>
+          <t>Walked register vs HR/transfer: MD-00062 still says Chicago - Closed (EX-0050).</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -24620,7 +24640,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>MD-00063 is still on a leaver. Close the assignment; stock holds it until recovered or written off.</t>
+          <t>Assignment on MD-00063 survived HR term for E0076. Correct it.</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -24640,7 +24660,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>Leaver still on MD-00063. E0076. TR-00063.</t>
+          <t>MD-00063 should have moved off E0076 when HR flipped status (EX-0051).</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -24686,7 +24706,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>MD-00063 shouldn't sit on a locked site. Move location to Denver.</t>
+          <t>Location on MD-00063 must reflect Denver after the site close (EX-0052).</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -24706,7 +24726,7 @@
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is locked. I'm not leaving MD-00063 there on paper. Denver is the operating site.</t>
+          <t>Inventory row for MD-00063 lagged after site close (Denver - Closed, EX-0052).</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -24752,7 +24772,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Custodian on MD-00064 is a terminated ID. Put IT Stock / Regional IT on the row.</t>
+          <t>HR shows E0077 gone — remove as custodian on MD-00064 (OFF-00064).</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -24772,7 +24792,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>Offboarding ticket OFF-00064 doesn't put hardware in stock by itself.</t>
+          <t>Offboarding closed for E0077; asset row did not follow for MD-00064 (EX-0053).</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -24818,7 +24838,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00064 to New York.</t>
+          <t>Chicago - Closed is no longer occupied. Park MD-00064 at New York on the register (EX-0054).</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -24838,7 +24858,7 @@
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>Register location Chicago - Closed is a closed site. TR-00064 points elsewhere. Live office New York.</t>
+          <t>Register still codes MD-00064 to Chicago - Closed; TR-00064 points to New York (EX-0054).</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -24884,7 +24904,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>TR-00064 has a blank approval. Ops manager signs or we unwind the move.</t>
+          <t>Either approve TR-00064 after the fact or put MD-00064 back.</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -24904,7 +24924,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001 §4: TR-00064 isn't a completed approved transfer.</t>
+          <t>TR-00064 shows blank approval_id for MD-00064.</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -24950,7 +24970,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Assignment cleanup: MD-00065 → Regional IT (or IT Stock if it's on the shelf).</t>
+          <t>People side closed via OFF-00065; asset row still lists E0078. Fix custodian.</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -24970,7 +24990,7 @@
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>OFF-00065 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>MD-00065 custodian equals terminated ID E0078 — EX-0056.</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25016,7 +25036,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00065 out of Denver - Closed and park it at Seattle.</t>
+          <t>MD-00065 cannot remain on shuttered floor Denver - Closed. Set location to Seattle (EX-0057).</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -25036,7 +25056,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00065.</t>
+          <t>Location on MD-00065 is consolidation debt (Denver - Closed, EX-0057).</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -25082,7 +25102,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Get a retrospective approval on TR-00065 or reverse it (ITAM-001 §4).</t>
+          <t>Either approve TR-00065 after the fact or put MD-00065 back.</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -25102,7 +25122,7 @@
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001 §4: TR-00065 isn't a completed approved transfer.</t>
+          <t>Transfer log TR-00065: move recorded, APR missing.</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -25148,7 +25168,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>HR already termed E0079. Update MD-00066 assignment.</t>
+          <t>HR Operations Lead: remove E0079 from MD-00066 and park the kit.</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -25168,7 +25188,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>Offboarding ticket OFF-00066 doesn't put hardware in stock by itself.</t>
+          <t>E0079 is separated in hr_employee_status; MD-00066 still points to them (EX-0059).</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -25214,7 +25234,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Same finding as the walkthrough: MD-00066 still tagged Chicago - Closed. Change it.</t>
+          <t>Remove closed-site coding on MD-00066 (Chicago - Closed → Atlanta, EX-0060).</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -25234,7 +25254,7 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>Walked the register vs HR/transfer. MD-00066 still says Chicago - Closed.</t>
+          <t>Atlanta is the operating site; MD-00066 still lists Chicago - Closed (EX-0060).</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -25280,7 +25300,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Take E0080 off MD-00067. Park with Regional IT / IT Stock.</t>
+          <t>Term cleanup — MD-00067 should not remain with E0080.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -25300,7 +25320,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>HR E0080 is separated. Register still has them on MD-00067. OFF-00067.</t>
+          <t>Evidence for EX-0061: register kept E0080 on MD-00067 post-separation.</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -25346,7 +25366,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Register still has the shuttered floor (Denver - Closed). Put Chicago on the row. (EX-0062)</t>
+          <t>IT Asset Specialist: recode MD-00067 off Denver - Closed; Chicago is the live office per TR-00067 (EX-0062).</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -25366,7 +25386,7 @@
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>MD-00067 still coded to a floor we don't occupy (Denver - Closed).</t>
+          <t>Consolidation left MD-00067 @ Denver - Closed; ops now use Chicago (EX-0062).</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -25412,7 +25432,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Escalate MD-00068. Generated label 1ZMD00000068 is not a return.</t>
+          <t>Chase MD-00068: carrier file empty despite 1ZMD00000068.</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -25432,7 +25452,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>Carrier events missing on 1ZMD00000068. That's the assessment.</t>
+          <t>Label 1ZMD00000068 printed; no SCAN-86 for MD-00068.</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
@@ -25478,7 +25498,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Custodian on MD-00068 is a terminated ID. Put IT Stock / Regional IT on the row.</t>
+          <t>OFF-00068 closed people; MD-00068 still shows the leaver.</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -25498,7 +25518,7 @@
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>MD-00068 custodian is a former employee in HR (E0081).</t>
+          <t>HR status for E0081 and register assignment on MD-00068 disagree (EX-0064).</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -25544,7 +25564,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Finance Controller owns the cost-basis cleanup on MD-00068.</t>
+          <t>Close the $6425.0/6480.0 gap on MD-00068 before cert.</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -25564,7 +25584,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>FA-000068 cost 6600.0 vs register 6425.0. PO-2025-0012.</t>
+          <t>Register cost $6425.0 vs ledger 6480.0 on FA-000068 for MD-00068.</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -25610,7 +25630,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Past the window on MD-00069. Label-only returns block cert until SCAN-86 / delivery / dock.</t>
+          <t>Outstanding kit MD-00069 / 1ZMD00000069 — escalate beyond label print.</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -25630,7 +25650,7 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>Looked at tracking 1ZMD00000069. Never left the printer as far as the file shows.</t>
+          <t>Overdue evidence is absence of inbound events on 1ZMD00000069.</t>
         </is>
       </c>
       <c r="M70" s="12" t="inlineStr">
@@ -25676,7 +25696,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Assignment cleanup: MD-00069 → Regional IT (or IT Stock if it's on the shelf).</t>
+          <t>Stock or Regional IT must replace E0082 on MD-00069.</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -25696,7 +25716,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>HR E0082 is separated. Register still has them on MD-00069. OFF-00069.</t>
+          <t>HR status for E0082 and register assignment on MD-00069 disagree (EX-0067).</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -25742,7 +25762,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Chase the return. 1ZMD00000070 is Label Created only — not received.</t>
+          <t>Do not mark Available; MD-00070 never docked after 1ZMD00000070.</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -25762,7 +25782,7 @@
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000070 is still Label Created. No acceptance / delivery / dock scan.</t>
+          <t>Carrier never accepted 1ZMD00000070; MD-00070 still outstanding.</t>
         </is>
       </c>
       <c r="M72" s="12" t="inlineStr">
@@ -25808,7 +25828,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 is still on a leaver. Close the assignment; stock holds it until recovered or written off.</t>
+          <t>Do not leave MD-00070 assigned to E0083 on the extract.</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -25828,7 +25848,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>OFF-00070 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>MD-00070 should have moved off E0083 when HR flipped status (EX-0069).</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -25874,7 +25894,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Escalate MD-00071. Generated label 1ZMD00000071 is not a return.</t>
+          <t>Recovery required on MD-00071; prepaid label 1ZMD00000071 is paperwork only.</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -25894,7 +25914,7 @@
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>Carrier events missing on 1ZMD00000071. That's the assessment.</t>
+          <t>Carrier never accepted 1ZMD00000071; MD-00071 still outstanding.</t>
         </is>
       </c>
       <c r="M74" s="12" t="inlineStr">
@@ -25940,7 +25960,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Custodian on MD-00071 is a terminated ID. Put IT Stock / Regional IT on the row.</t>
+          <t>HR already termed E0084. Update MD-00071 assignment.</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -25960,7 +25980,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>MD-00071 custodian is a former employee in HR (E0084).</t>
+          <t>HR lists E0084 as separated; register still assigns MD-00071 (EX-0071).</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -26006,7 +26026,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>OFF-00072: overdue. Keep pressure on the person; carrier file is empty.</t>
+          <t>Label-only status on 1ZMD00000072 blocks cert for MD-00072.</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -26026,7 +26046,7 @@
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>Policy §5: label ≠ returned. 1ZMD00000072.</t>
+          <t>OFF-00072: return window closed with empty inbound for MD-00072.</t>
         </is>
       </c>
       <c r="M76" s="12" t="inlineStr">
@@ -26072,7 +26092,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Recover or lose-process MD-00072, but first drop the former employee as owner.</t>
+          <t>Recover or write-off later; first take E0085 off MD-00072.</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -26092,7 +26112,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>People record is closed; MD-00072 isn't. OFF-00072.</t>
+          <t>Custodian mismatch MD-00072↔E0085 documented under EX-0073.</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -26138,7 +26158,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Escalate to recovery. MD-00073 / 1ZMD00000073 still label-only.</t>
+          <t>Keep pressure on the former user until dock scan — 1ZMD00000073.</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -26158,7 +26178,7 @@
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>Ship file for MD-00073: label only. OFF-00073 overdue 2026-07-15.</t>
+          <t>Label 1ZMD00000073 printed; no SCAN-86 for MD-00073.</t>
         </is>
       </c>
       <c r="M78" s="12" t="inlineStr">
@@ -26204,7 +26224,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Move MD-00073 off the separated custodian before we talk redeploy.</t>
+          <t>HR Operations Lead: remove E0086 from MD-00073 and park the kit.</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -26224,7 +26244,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>Leaver still on MD-00073. E0086.</t>
+          <t>People file cleared E0086; ITAM row for MD-00073 did not (EX-0075).</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -26270,7 +26290,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Do not clear custody on MD-00074. Mismatch MISMATCH-0074 vs MD-MO-050074.</t>
+          <t>Hold MD-00074. Shipment serial MISMATCH-0074 ≠ register MD-MO-050074 on 1ZMD00000074.</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -26336,7 +26356,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Close the people assignment on MD-00074. Ticket OFF-00074.</t>
+          <t>People side closed via OFF-00074; asset row still lists E0087. Fix custodian.</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -26356,7 +26376,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>Offboarding ticket OFF-00074 doesn't put hardware in stock by itself.</t>
+          <t>MD-00074 custodian equals terminated ID E0087 — EX-0077.</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -26402,7 +26422,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Recovery, not close-out. 1ZMD00000074 never left Label Created.</t>
+          <t>Escalate recovery on MD-00074; 1ZMD00000074 is Label Created only.</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -26422,7 +26442,7 @@
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
-          <t>Policy §5: label ≠ returned. 1ZMD00000074.</t>
+          <t>Return paperwork exists (1ZMD00000074); physical return does not.</t>
         </is>
       </c>
       <c r="M82" s="12" t="inlineStr">
@@ -26468,7 +26488,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>OFF-00075: overdue. Keep pressure on the person; carrier file is empty.</t>
+          <t>MD-00075 past due 2026-07-15; label is not receipt (OFF-00075).</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -26488,7 +26508,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000075 is still Label Created. No acceptance / delivery / dock scan.</t>
+          <t>Ship file for MD-00075: label only. OFF-00075 overdue 2026-07-15.</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
@@ -26534,7 +26554,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>HR E0088 is gone. Register custodian on MD-00075 has to move.</t>
+          <t>Stock or Regional IT must replace E0088 on MD-00075.</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -26554,7 +26574,7 @@
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>OFF-00075 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>Custodian mismatch MD-00075↔E0088 documented under EX-0080.</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -26600,7 +26620,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000076: serial fight. Keep In Transit - Exception.</t>
+          <t>Carrier exception 1ZMD00000076; MD-00076 stays held.</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -26620,7 +26640,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>Carrier exception on 1ZMD00000076. Status stays In Transit - Exception.</t>
+          <t>Shipment serial MISMATCH-0076 on 1ZMD00000076 vs register MD-NE-050076. Not cleared.</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
@@ -26666,7 +26686,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00076 assigned to E0089.</t>
+          <t>Term cleanup — MD-00076 should not remain with E0089.</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -26686,7 +26706,7 @@
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 custodian is a former employee in HR (E0089).</t>
+          <t>Evidence for EX-0082: register kept E0089 on MD-00076 post-separation.</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -26732,7 +26752,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 past due 2026-07-15. Label isn't proof. Escalate recovery.</t>
+          <t>IT Asset Specialist: treat MD-00076 as not returned until inbound scan.</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -26752,7 +26772,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>Label exists. Receipt doesn't. MD-00076.</t>
+          <t>1ZMD00000076 remains Label Created. No acceptance, delivery, or dock scan.</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
@@ -26798,7 +26818,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Escalate MD-00077. Generated label 1ZMD00000077 is not a return.</t>
+          <t>Outstanding kit MD-00077 / 1ZMD00000077 — escalate beyond label print.</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -26818,7 +26838,7 @@
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
-          <t>Looked at tracking 1ZMD00000077. Never left the printer as far as the file shows.</t>
+          <t>Label 1ZMD00000077 printed; no SCAN-86 for MD-00077.</t>
         </is>
       </c>
       <c r="M88" s="12" t="inlineStr">
@@ -26864,7 +26884,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>E0090 should not still own MD-00077 on the register.</t>
+          <t>HR Operations Lead: remove E0090 from MD-00077 and park the kit.</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -26884,7 +26904,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>HR E0090 is separated. Register still has them on MD-00077. OFF-00077.</t>
+          <t>MD-00077 custodian equals terminated ID E0090 — EX-0085.</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -26930,7 +26950,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>OFF-00078: overdue. Keep pressure on the person; carrier file is empty.</t>
+          <t>Escalate recovery on MD-00078; 1ZMD00000078 is Label Created only.</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -26950,7 +26970,7 @@
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the prepaid label as a return. 1ZMD00000078.</t>
+          <t>1ZMD00000078 remains Label Created. No acceptance, delivery, or dock scan.</t>
         </is>
       </c>
       <c r="M90" s="12" t="inlineStr">
@@ -26996,7 +27016,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>HR already termed E0091. Update MD-00078 assignment.</t>
+          <t>OFF-00078 closed people; MD-00078 still shows the leaver.</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -27016,7 +27036,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>Checked the term date against the assignment. Stale owner on MD-00078.</t>
+          <t>Finding EX-0087 on MD-00078: former employee E0091 still listed as owner.</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -27062,7 +27082,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Escalate to recovery. MD-00079 / 1ZMD00000079 still label-only.</t>
+          <t>Do not close MD-00079 as returned. 2026-07-15 passed with no SCAN-86.</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -27082,7 +27102,7 @@
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>Label exists. Receipt doesn't. MD-00079.</t>
+          <t>1ZMD00000079 remains Label Created. No acceptance, delivery, or dock scan.</t>
         </is>
       </c>
       <c r="M92" s="12" t="inlineStr">
@@ -27128,7 +27148,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Take E0092 off MD-00079. Park with Regional IT / IT Stock.</t>
+          <t>MD-00079 still names a leaver (E0092). Close the assignment.</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -27148,7 +27168,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>E0092 already termed. MD-00079 assignment wasn't updated.</t>
+          <t>Term record for E0092 exists; MD-00079 assignment record did not update (EX-0089).</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
@@ -27194,7 +27214,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Recover or lose-process MD-00080, but first drop the former employee as owner.</t>
+          <t>Term cleanup — MD-00080 should not remain with E0093.</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -27214,7 +27234,7 @@
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>E0093 already termed. MD-00080 assignment wasn't updated.</t>
+          <t>EX-0090 cites MD-00080 assigned to terminated E0093 despite OFF-00080.</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -27260,7 +27280,7 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>E0094 should not still own MD-00081 on the register.</t>
+          <t>MD-00081 needs a stock/regional holder, not E0094.</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
@@ -27280,7 +27300,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>HR E0094 is separated. Register still has them on MD-00081. OFF-00081.</t>
+          <t>People file cleared E0094; ITAM row for MD-00081 did not (EX-0091).</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
@@ -27326,7 +27346,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Do not clear custody on MD-00082. Mismatch MISMATCH-0082 vs MD-MO-050082.</t>
+          <t>MD-00082 stays exception. Dock photo is a HOLD lead, not a receipt. MISMATCH-0082 vs MD-MO-050082 on 1ZMD00000082.</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
@@ -27346,7 +27366,7 @@
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
-          <t>Carrier file and receiving_exception_scan_1ZMD00000082.png. Image ≠ inbound clearance.</t>
+          <t>MISMATCH-0082 vs MD-MO-050082. Used the photo as breadcrumb only.</t>
         </is>
       </c>
       <c r="M96" s="12" t="inlineStr">
@@ -27392,7 +27412,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>HR already termed E0095. Update MD-00082 assignment.</t>
+          <t>MD-00082 needs a stock/regional holder, not E0095.</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -27412,7 +27432,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>Checked the term date against the assignment. Stale owner on MD-00082.</t>
+          <t>Compared HR row E0095 to register row MD-00082 — assignment stale (EX-0093).</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -27458,7 +27478,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>MD-00083: former employee still listed. That's the fix.</t>
+          <t>Move MD-00083 to Regional IT holding after E0071 exit.</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -27478,7 +27498,7 @@
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>Offboarding ticket OFF-00083 doesn't put hardware in stock by itself.</t>
+          <t>Offboarding closed for E0071; asset row did not follow for MD-00083 (EX-0094).</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -27524,7 +27544,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Work it with carrier/receiving. 1ZMD00000084 shows MISMATCH-0084; register is MD-NE-050084.</t>
+          <t>Work carrier/receiving on 1ZMD00000084: MISMATCH-0084 vs MD-NE-050084.</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -27544,7 +27564,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>Carrier exception on 1ZMD00000084. Status stays In Transit - Exception.</t>
+          <t>Inbound 1ZMD00000084 does not match register serial MD-NE-050084.</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
@@ -27590,7 +27610,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>HR E0072 is gone. Register custodian on MD-00084 has to move.</t>
+          <t>MD-00084 still names a leaver (E0072). Close the assignment.</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -27610,7 +27630,7 @@
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
-          <t>HR E0072 is separated. Register still has them on MD-00084. OFF-00084.</t>
+          <t>EX-0096 cites MD-00084 assigned to terminated E0072 despite OFF-00084.</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -27656,7 +27676,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Custodian on MD-00085 is a terminated ID. Put IT Stock / Regional IT on the row.</t>
+          <t>People side closed via OFF-00085; asset row still lists E0073. Fix custodian.</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
@@ -27676,7 +27696,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>Leaver still on MD-00085. E0073.</t>
+          <t>People extract vs register: MD-00085 retained leaver E0073. OFF-00085.</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -27722,7 +27742,7 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Cost basis mismatch MD-00085. Pull PO-2024-0015 and fix FA-000085 or the register.</t>
+          <t>Align cost on MD-00085: register 1895.0 vs ledger 2090.0 (FA-000085).</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
@@ -27742,7 +27762,7 @@
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
-          <t>FA-000085 cost 2070.0 vs register 1895.0. PO-2024-0015.</t>
+          <t>Basis mismatch documented for MD-00085 (1895.0 vs 2090.0).</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -27788,7 +27808,7 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Recover or lose-process MD-00086, but first drop the former employee as owner.</t>
+          <t>HR shows E0074 gone — remove as custodian on MD-00086 (OFF-00086).</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -27808,7 +27828,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>Offboarding ticket OFF-00086 doesn't put hardware in stock by itself.</t>
+          <t>Compared HR row E0074 to register row MD-00086 — assignment stale (EX-0099).</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -27854,7 +27874,7 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>E0075 should not still own MD-00087 on the register.</t>
+          <t>Assignment on MD-00087 survived HR term for E0075. Correct it.</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
@@ -27874,7 +27894,7 @@
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
-          <t>People record is closed; MD-00087 isn't. OFF-00087.</t>
+          <t>Register owner on MD-00087 is stale relative to HR for E0075 (EX-0100).</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -27920,7 +27940,7 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Register owner is stale. MD-00088 needs a stock/regional holder.</t>
+          <t>People side closed via OFF-00088; asset row still lists E0076. Fix custodian.</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
@@ -27940,7 +27960,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>OFF-00088 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>Compared HR row E0076 to register row MD-00088 — assignment stale (EX-0101).</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -27986,7 +28006,7 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Duplicate MD-NE-050088 — MD-00088 and the other tag in MD-00088,MD-00092. Don't treat either as clean until retag.</t>
+          <t>Duplicate MD-NE-050088 — MD-00088 and MD-00088,MD-00092. Neither is clean until retag.</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -28006,7 +28026,7 @@
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
-          <t>Inventory file lists MD-NE-050088 twice (MD-00088,MD-00092).</t>
+          <t>Serial MD-NE-050088 appears on more than one tag (MD-00088,MD-00092).</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
@@ -28052,7 +28072,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Classify MD-00089 Missing. Last register site Denver - Closed is a closed floor — not a find.</t>
+          <t>No scan/cert/count for MD-00089. Missing, not In Use (EX-0103).</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -28072,7 +28092,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>Walked HR, transfers, tickets. MD-00089 is not in any inbound.</t>
+          <t>Could not place MD-00089 from available transactions (EX-0103).</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
@@ -28118,7 +28138,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Take E0077 off MD-00089. Park with Regional IT / IT Stock.</t>
+          <t>Custodian field on MD-00089 still equals E0077; that is the fix.</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -28138,7 +28158,7 @@
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
-          <t>Offboarding ticket OFF-00089 doesn't put hardware in stock by itself.</t>
+          <t>Register owner on MD-00089 is stale relative to HR for E0077 (EX-0104).</t>
         </is>
       </c>
       <c r="M108" s="12" t="inlineStr">
@@ -28184,7 +28204,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>No scan, no cert, no count for MD-00090. Missing, not In Use.</t>
+          <t>Security review + locate. MD-00090 remains Missing (EX-0105).</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -28204,7 +28224,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>OFF-00090 / TR-00090: still gone. Notes don't locate it.</t>
+          <t>Files do not locate MD-00090; Missing remains appropriate (EX-0105).</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
@@ -28250,7 +28270,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Assignment cleanup: MD-00090 → Regional IT (or IT Stock if it's on the shelf).</t>
+          <t>Recover or write-off later; first take E0078 off MD-00090.</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -28270,7 +28290,7 @@
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
-          <t>E0078 already termed. MD-00090 assignment wasn't updated.</t>
+          <t>HR lists E0078 as separated; register still assigns MD-00090 (EX-0106).</t>
         </is>
       </c>
       <c r="M110" s="12" t="inlineStr">
@@ -28316,7 +28336,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Loss investigation on MD-00091. Keep Missing until we find it or get a write-off.</t>
+          <t>Write-off only with approval; until then MD-00091 is Missing (EX-0107).</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -28336,7 +28356,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>MD-00091: nothing higher-precedence than a closed-floor register row.</t>
+          <t>MD-00091 not found in inbound or stock after Denver - Closed (EX-0107).</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
@@ -28382,7 +28402,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Register owner is stale. MD-00091 needs a stock/regional holder.</t>
+          <t>Unassign E0079 from MD-00091; hold under Regional IT / IT Stock.</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -28402,7 +28422,7 @@
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
-          <t>OFF-00091 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>Leaver E0079 remains on MD-00091 in the inventory extract (EX-0108).</t>
         </is>
       </c>
       <c r="M112" s="12" t="inlineStr">
@@ -28448,7 +28468,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Start the loss process. MD-00092 is not in Unknown and not in receiving.</t>
+          <t>No scan/cert/count for MD-00092. Missing, not In Use (EX-0109).</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -28468,7 +28488,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>OFF-00092 / TR-00092: still gone. Notes don't locate it.</t>
+          <t>MD-00092 not found in inbound or stock after Chicago - Closed (EX-0109).</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
@@ -28514,7 +28534,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>MD-00092: former employee still listed. That's the fix.</t>
+          <t>Stock or Regional IT must replace E0080 on MD-00092.</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -28534,7 +28554,7 @@
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
-          <t>MD-00092 custodian is a former employee in HR (E0080).</t>
+          <t>Custodian mismatch MD-00092↔E0080 documented under EX-0110.</t>
         </is>
       </c>
       <c r="M114" s="12" t="inlineStr">
@@ -28580,7 +28600,7 @@
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Two assets share MD-NE-050088 (MD-00088,MD-00092). Validate on the bench and issue a new serial.</t>
+          <t>Two assets share MD-NE-050088 (MD-00088,MD-00092). Bench-validate and issue a new serial.</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
@@ -28600,7 +28620,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>Two tags, one serial (MD-NE-050088). Flagged both.</t>
+          <t>Two assets share MD-NE-050088; MD-00092 is one of them.</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
@@ -28646,7 +28666,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>No scan, no cert, no count for MD-00093. Missing, not In Use.</t>
+          <t>Security review + locate. MD-00093 remains Missing (EX-0112).</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
@@ -28666,7 +28686,7 @@
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
-          <t>Couldn't prove a location. Ticket:OFF-00093; Transfer:TR-00093; LastRegisterLocation:Denver - Closed</t>
+          <t>MD-00093 not found in inbound or stock after Denver - Closed (EX-0112).</t>
         </is>
       </c>
       <c r="M116" s="12" t="inlineStr">
@@ -28712,7 +28732,7 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Unassign MD-00093 from the former employee. OFF-00093 is the offboarding ticket.</t>
+          <t>Stock or Regional IT must replace E0081 on MD-00093.</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
@@ -28732,7 +28752,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>HR E0081 is separated. Register still has them on MD-00093. OFF-00093.</t>
+          <t>HR lists E0081 as separated; register still assigns MD-00093 (EX-0113).</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
@@ -28778,7 +28798,7 @@
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Loss investigation on MD-00094. Keep Missing until we find it or get a write-off.</t>
+          <t>Write-off only with approval; until then MD-00094 is Missing (EX-0114).</t>
         </is>
       </c>
       <c r="I118" s="7" t="inlineStr">
@@ -28798,7 +28818,7 @@
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
-          <t>Walked HR, transfers, tickets. MD-00094 is not in any inbound.</t>
+          <t>Nothing physical confirms MD-00094 at Unknown (EX-0114).</t>
         </is>
       </c>
       <c r="M118" s="12" t="inlineStr">
@@ -28844,7 +28864,7 @@
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>OFF-00094 closed the people side; asset row still shows the leaver. Fix custodian.</t>
+          <t>Term cleanup — MD-00094 should not remain with E0082.</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
@@ -28864,7 +28884,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>Checked the term date against the assignment. Stale owner on MD-00094.</t>
+          <t>MD-00094 custodian equals terminated ID E0082 — EX-0115.</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
@@ -28910,7 +28930,7 @@
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>Start the loss process. MD-00095 is not in Unknown and not in receiving.</t>
+          <t>MD-00095 dropped after Denver - Closed. Investigate; do not tidy status (EX-0116).</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr">
@@ -28930,7 +28950,7 @@
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
-          <t>Couldn't prove a location. Ticket:OFF-00095; Transfer:TR-00095; LastRegisterLocation:Denver - Closed</t>
+          <t>Files do not locate MD-00095; Missing remains appropriate (EX-0116).</t>
         </is>
       </c>
       <c r="M120" s="12" t="inlineStr">
@@ -28976,7 +28996,7 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>E0083 should not still own MD-00095 on the register.</t>
+          <t>Close people assignment on MD-00095; ticket OFF-00095.</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr">
@@ -28996,7 +29016,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>E0083 already termed. MD-00095 assignment wasn't updated.</t>
+          <t>Custodian mismatch MD-00095↔E0083 documented under EX-0117.</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
@@ -29042,7 +29062,7 @@
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>Security review + locate. MD-00096 stays Missing.</t>
+          <t>Start loss process for MD-00096; not in Unknown and not in receiving (EX-0118).</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr">
@@ -29062,7 +29082,7 @@
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
-          <t>Walked HR, transfers, tickets. MD-00096 is not in any inbound.</t>
+          <t>Search trail cold for MD-00096 (OFF-00096). Last register site Chicago - Closed (EX-0118).</t>
         </is>
       </c>
       <c r="M122" s="12" t="inlineStr">
@@ -29108,7 +29128,7 @@
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>HR already termed E0084. Update MD-00096 assignment.</t>
+          <t>HR Operations Lead: remove E0084 from MD-00096 and park the kit.</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr">
@@ -29128,7 +29148,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>OFF-00096 vs hr_employee_status: people side is done, asset isn't.</t>
+          <t>Offboarding closed for E0084; asset row did not follow for MD-00096 (EX-0119).</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
@@ -29174,7 +29194,7 @@
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 dropped off the map after Denver - Closed. Investigate; don't tidy the status.</t>
+          <t>Loss investigation on MD-00097; keep Missing until found or write-off (EX-0120).</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
@@ -29194,7 +29214,7 @@
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
-          <t>Couldn't prove a location. Ticket:OFF-00097; Transfer:TR-00097; LastRegisterLocation:Denver - Closed</t>
+          <t>Search trail cold for MD-00097 (OFF-00097). Last register site Denver - Closed (EX-0120).</t>
         </is>
       </c>
       <c r="M124" s="12" t="inlineStr">
@@ -29240,7 +29260,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Take E0085 off MD-00097. Park with Regional IT / IT Stock.</t>
+          <t>Do not leave MD-00097 assigned to E0085 on the extract.</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
@@ -29260,7 +29280,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 custodian is a former employee in HR (E0085).</t>
+          <t>Offboarding closed for E0085; asset row did not follow for MD-00097 (EX-0121).</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
@@ -29306,7 +29326,7 @@
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Cannot locate MD-00098. Ticket OFF-00098. Missing until count or approved write-off.</t>
+          <t>Write-off only with approval; until then MD-00098 is Missing (EX-0122).</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
@@ -29326,7 +29346,7 @@
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
-          <t>Walked HR, transfers, tickets. MD-00098 is not in any inbound.</t>
+          <t>Could not place MD-00098 from available transactions (EX-0122).</t>
         </is>
       </c>
       <c r="M126" s="12" t="inlineStr">
@@ -29372,7 +29392,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Unassign MD-00098 from the former employee. OFF-00098 is the offboarding ticket.</t>
+          <t>Move MD-00098 to Regional IT holding after E0086 exit.</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
@@ -29392,7 +29412,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>People record is closed; MD-00098 isn't. OFF-00098.</t>
+          <t>Register owner on MD-00098 is stale relative to HR for E0086 (EX-0123).</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
@@ -29438,7 +29458,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>OFF-00099: still gone. Don't invent a stock location for MD-00099.</t>
+          <t>Cannot locate MD-00099 (OFF-00099). Missing until count or approved write-off (EX-0124).</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr">
@@ -29458,7 +29478,7 @@
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
-          <t>Couldn't prove a location. Ticket:OFF-00099; Transfer:TR-00099; LastRegisterLocation:Denver - Closed</t>
+          <t>Search trail cold for MD-00099 (OFF-00099). Last register site Denver - Closed (EX-0124).</t>
         </is>
       </c>
       <c r="M128" s="12" t="inlineStr">
@@ -29504,7 +29524,7 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>OFF-00099 closed the people side; asset row still shows the leaver. Fix custodian.</t>
+          <t>Assignment on MD-00099 survived HR term for E0087. Correct it.</t>
         </is>
       </c>
       <c r="I129" s="7" t="inlineStr">
@@ -29524,7 +29544,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>Leaver still on MD-00099. E0087.</t>
+          <t>Offboarding closed for E0087; asset row did not follow for MD-00099 (EX-0125).</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
@@ -29570,7 +29590,7 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>Write-off only with approval. Until then MD-00100 is Missing.</t>
+          <t>IT Operations Manager: keep MD-00100 Missing on the register (EX-0126).</t>
         </is>
       </c>
       <c r="I130" s="7" t="inlineStr">
@@ -29590,7 +29610,7 @@
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
-          <t>MD-00100: nothing higher-precedence than a closed-floor register row.</t>
+          <t>No receiving scan, disposal cert, or count places MD-00100. Last site Chicago - Closed (EX-0126).</t>
         </is>
       </c>
       <c r="M130" s="12" t="inlineStr">
@@ -29636,7 +29656,7 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>MD-00100: former employee still listed. That's the fix.</t>
+          <t>MD-00100 needs a stock/regional holder, not E0088.</t>
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr">
@@ -29656,7 +29676,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>Checked the term date against the assignment. Stale owner on MD-00100.</t>
+          <t>HR status for E0088 and register assignment on MD-00100 disagree (EX-0127).</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
@@ -29702,7 +29722,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>RET-00101 has no matching cert. MD-00101 stays pending-disposal.</t>
+          <t>Retirement parked for MD-00101 pending DC evidence (EX-0128).</t>
         </is>
       </c>
       <c r="I132" s="7" t="inlineStr">
@@ -29722,7 +29742,7 @@
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
-          <t>Disposal file has no row matching MD-00101 / MD-LA-050101.</t>
+          <t>TR-00101 to recycler without DC for MD-00101 (EX-0128).</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr">
@@ -29768,7 +29788,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 shouldn't sit on a locked site. Move location to Seattle.</t>
+          <t>MD-00101 cannot remain on shuttered floor Denver - Closed. Set location to Seattle (EX-0129).</t>
         </is>
       </c>
       <c r="I133" s="7" t="inlineStr">
@@ -29788,7 +29808,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Denver - Closed. TR-00101.</t>
+          <t>Register still codes MD-00101 to Denver - Closed; TR-00101 points to Seattle (EX-0129).</t>
         </is>
       </c>
       <c r="M133" s="7" t="inlineStr">
@@ -29834,7 +29854,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Paperwork gap on MD-00102. Cert or reverse the retire.</t>
+          <t>Do not call MD-00102 disposed — certificate missing (EX-0130).</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr">
@@ -29854,7 +29874,7 @@
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
-          <t>No verified certificate. Ticket:RET-00102; Transfer:TR-00102; Certificate:missing</t>
+          <t>No DC row ties to MD-MO-050102 for MD-00102 (EX-0130).</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -29900,7 +29920,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Don't certify the $ on MD-00102 until register and FA-000102 match.</t>
+          <t>MD-00102 off vs FA-000102 (700.0 vs 820.0). Confirm which figure is correct.</t>
         </is>
       </c>
       <c r="I135" s="7" t="inlineStr">
@@ -29920,7 +29940,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>FA-000102 cost 875.0 vs register 700.0. PO-2022-0017.</t>
+          <t>Cost spread on MD-00102: ITAM $700.0, FAR 820.0 (FA-000102).</t>
         </is>
       </c>
       <c r="M135" s="7" t="inlineStr">
@@ -29966,7 +29986,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Atlanta is current. Register lagged on Chicago - Closed for MD-00102.</t>
+          <t>Update register location for MD-00102 before the next cert packet (EX-0132).</t>
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr">
@@ -29986,7 +30006,7 @@
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00102 didn't survive the consolidation (Chicago - Closed).</t>
+          <t>MD-00102 remains on unused floor Chicago - Closed in the inventory file (EX-0132).</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -30032,7 +30052,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>Obtain cert or restock MD-00103. Ticket RET-00103.</t>
+          <t>Obtain cert or restock MD-00103. Ticket RET-00103 (EX-0133).</t>
         </is>
       </c>
       <c r="I137" s="7" t="inlineStr">
@@ -30052,7 +30072,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>Looked in asset_disposal_records. Nothing for MD-00103.</t>
+          <t>Retirement/disposal path for MD-00103 has no matching certificate (EX-0133).</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
@@ -30098,7 +30118,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00103 out of Denver - Closed and park it at Chicago.</t>
+          <t>HR-aligned site for MD-00103 is Chicago; register still says Denver - Closed (EX-0134).</t>
         </is>
       </c>
       <c r="I138" s="7" t="inlineStr">
@@ -30118,7 +30138,7 @@
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
-          <t>Consolidation leftover: MD-00103 @ Denver - Closed.</t>
+          <t>Walked register vs HR/transfer: MD-00103 still says Denver - Closed (EX-0134).</t>
         </is>
       </c>
       <c r="M138" s="7" t="inlineStr">
@@ -30164,7 +30184,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>RET-00104 has no matching cert. MD-00104 stays pending-disposal.</t>
+          <t>Obtain cert or restock MD-00104. Ticket RET-00104 (EX-0135).</t>
         </is>
       </c>
       <c r="I139" s="7" t="inlineStr">
@@ -30184,7 +30204,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>Disposal file has no row matching MD-00104 / MD-NE-050104.</t>
+          <t>TR-00104 to recycler without DC for MD-00104 (EX-0135).</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -30230,7 +30250,7 @@
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shut. Rewrite the register location (MD-00104).</t>
+          <t>IT Asset Specialist owns the location rewrite for MD-00104 at Chicago - Closed (EX-0136).</t>
         </is>
       </c>
       <c r="I140" s="7" t="inlineStr">
@@ -30250,7 +30270,7 @@
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Chicago - Closed. TR-00104.</t>
+          <t>Unused-office coding on MD-00104 is unsupported by movement files (EX-0136).</t>
         </is>
       </c>
       <c r="M140" s="7" t="inlineStr">
@@ -30296,7 +30316,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>Paperwork gap on MD-00105. Cert or reverse the retire.</t>
+          <t>Match a vendor cert to MD-LA-050105 or unwind retirement (EX-0137).</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr">
@@ -30316,7 +30336,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>No verified certificate. Ticket:RET-00105; Transfer:TR-00105; Certificate:missing</t>
+          <t>No DC row ties to MD-LA-050105 for MD-00105 (EX-0137).</t>
         </is>
       </c>
       <c r="M141" s="7" t="inlineStr">
@@ -30362,7 +30382,7 @@
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>Get MD-00105 off Denver - Closed. Operating location is Denver.</t>
+          <t>MD-00105 / Denver - Closed is a consolidation leftover — move to Denver (EX-0138).</t>
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr">
@@ -30382,7 +30402,7 @@
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
-          <t>TR-00105 destination isn't the shuttered office on the register.</t>
+          <t>Register location Denver - Closed conflicts with current footprint for MD-00105 (EX-0138).</t>
         </is>
       </c>
       <c r="M142" s="7" t="inlineStr">
@@ -30428,7 +30448,7 @@
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>ITAM hold. MD-00106 is not gone until the certificate shows the tag.</t>
+          <t>Hold retirement on MD-00106. Need disposal certificate or restock (EX-0139).</t>
         </is>
       </c>
       <c r="I143" s="7" t="inlineStr">
@@ -30448,7 +30468,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>Retirement path without a DC. MD-00106.</t>
+          <t>Cert field empty on MD-00106; retirement not closed (EX-0139).</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -30494,7 +30514,7 @@
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00106: Chicago - Closed → New York.</t>
+          <t>HR-aligned site for MD-00106 is New York; register still says Chicago - Closed (EX-0140).</t>
         </is>
       </c>
       <c r="I144" s="7" t="inlineStr">
@@ -30514,7 +30534,7 @@
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
-          <t>Walked the register vs HR/transfer. MD-00106 still says Chicago - Closed.</t>
+          <t>Location evidence for MD-00106: closed floor Chicago - Closed vs live New York (EX-0140).</t>
         </is>
       </c>
       <c r="M144" s="7" t="inlineStr">
@@ -30560,7 +30580,7 @@
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>Hold the retirement on MD-00107. Need a disposal certificate or put it back in stock.</t>
+          <t>RET-00107 has no matching cert; MD-00107 stays pending-disposal (EX-0141).</t>
         </is>
       </c>
       <c r="I145" s="7" t="inlineStr">
@@ -30580,7 +30600,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>RET-00107 / TR-00107: certificate field empty.</t>
+          <t>Retirement/disposal path for MD-00107 has no matching certificate (EX-0141).</t>
         </is>
       </c>
       <c r="M145" s="7" t="inlineStr">
@@ -30626,7 +30646,7 @@
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>Seattle is current. Register lagged on Denver - Closed for MD-00107.</t>
+          <t>IT Asset Specialist owns the location rewrite for MD-00107 at Denver - Closed (EX-0142).</t>
         </is>
       </c>
       <c r="I146" s="7" t="inlineStr">
@@ -30646,7 +30666,7 @@
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
-          <t>MD-00107 still coded to a floor we don't occupy (Denver - Closed).</t>
+          <t>Register location Denver - Closed conflicts with current footprint for MD-00107 (EX-0142).</t>
         </is>
       </c>
       <c r="M146" s="7" t="inlineStr">
@@ -30692,7 +30712,7 @@
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>Don't call MD-00108 disposed. Certificate missing.</t>
+          <t>Hold retirement on MD-00108. Need disposal certificate or restock (EX-0143).</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr">
@@ -30712,7 +30732,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>Looked in asset_disposal_records. Nothing for MD-00108.</t>
+          <t>No DC row ties to MD-NE-050108 for MD-00108 (EX-0143).</t>
         </is>
       </c>
       <c r="M147" s="7" t="inlineStr">
@@ -30758,7 +30778,7 @@
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>Pull MD-00108 out of Chicago - Closed and park it at Atlanta.</t>
+          <t>MD-00108 location field lagged after consolidation; update from Chicago - Closed to Atlanta (EX-0144).</t>
         </is>
       </c>
       <c r="I148" s="7" t="inlineStr">
@@ -30778,7 +30798,7 @@
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
-          <t>Didn't treat the closed building as a live location for MD-00108.</t>
+          <t>Physical sites changed; MD-00108 register did not (Chicago - Closed, EX-0144).</t>
         </is>
       </c>
       <c r="M148" s="7" t="inlineStr">
@@ -30824,7 +30844,7 @@
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>Match a vendor cert to MD-LA-050109 or unwind.</t>
+          <t>ITAM hold — MD-00109 not gone until cert lists the tag (EX-0145).</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr">
@@ -30844,7 +30864,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>Disposal file has no row matching MD-00109 / MD-LA-050109.</t>
+          <t>Retirement/disposal path for MD-00109 has no matching certificate (EX-0145).</t>
         </is>
       </c>
       <c r="M149" s="7" t="inlineStr">
@@ -30890,7 +30910,7 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is shut. Rewrite the register location (MD-00109).</t>
+          <t>Denver - Closed is no longer occupied. Park MD-00109 at Chicago on the register (EX-0146).</t>
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr">
@@ -30910,7 +30930,7 @@
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is locked. I'm not leaving MD-00109 there on paper. Chicago is the operating site.</t>
+          <t>Location evidence for MD-00109: closed floor Denver - Closed vs live Chicago (EX-0146).</t>
         </is>
       </c>
       <c r="M150" s="7" t="inlineStr">
@@ -30956,7 +30976,7 @@
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Retirement parked. MD-00110 needs DC evidence.</t>
+          <t>Hold retirement on MD-00110. Need disposal certificate or restock (EX-0147).</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr">
@@ -30976,7 +30996,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>No verified certificate. Ticket:RET-00110; Transfer:TR-00110; Certificate:missing</t>
+          <t>Cert field empty on MD-00110; retirement not closed (EX-0147).</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -31022,7 +31042,7 @@
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00110 to Dallas.</t>
+          <t>Location on MD-00110 must reflect Dallas after the site close (EX-0148).</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr">
@@ -31042,7 +31062,7 @@
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
-          <t>Register location Chicago - Closed is a closed site. TR-00110 points elsewhere. Live office Dallas.</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00110 there on paper — Dallas is live (EX-0148).</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -31088,7 +31108,7 @@
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>MD-00114: pending disposal with no DC row. Block retirement close.</t>
+          <t>MD-00114: pending disposal with no DC row. Block close (EX-0149).</t>
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr">
@@ -31108,7 +31128,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>RET-00114 / TR-00114: certificate field empty.</t>
+          <t>No DC row ties to MD-MO-050114 for MD-00114 (EX-0149).</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
@@ -31154,7 +31174,7 @@
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>Clear the closed-site assignment. MD-00114 belongs at Disposed (certificate missing).</t>
+          <t>Remove closed-site coding on MD-00114 (Chicago - Closed → Disposed (certificate missing), EX-0150).</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr">
@@ -31174,7 +31194,7 @@
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00114 didn't survive the consolidation (Chicago - Closed).</t>
+          <t>Register location Chicago - Closed conflicts with current footprint for MD-00114 (EX-0150).</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -31220,7 +31240,7 @@
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>RET-00118 has no matching cert. MD-00118 stays pending-disposal.</t>
+          <t>Paperwork gap on MD-00118: cert or reverse the retire (EX-0151).</t>
         </is>
       </c>
       <c r="I155" s="7" t="inlineStr">
@@ -31240,7 +31260,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>Disposal file has no row matching MD-00118 / MD-MO-050118.</t>
+          <t>Cert field empty on MD-00118; retirement not closed (EX-0151).</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
@@ -31286,7 +31306,7 @@
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 shouldn't sit on a locked site. Move location to Disposed (certificate missing).</t>
+          <t>Do not leave MD-00118 assigned to unused floor Chicago - Closed (EX-0152).</t>
         </is>
       </c>
       <c r="I156" s="7" t="inlineStr">
@@ -31306,7 +31326,7 @@
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover on the extract. Chicago - Closed. TR-00118.</t>
+          <t>Did not treat closed building Chicago - Closed as live location for MD-00118 (EX-0152).</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -31352,7 +31372,7 @@
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>Reconcile PO-2025-0020 / FA-000119 / register cost for MD-00119.</t>
+          <t>Finance Controller owns cost-basis cleanup on MD-00119.</t>
         </is>
       </c>
       <c r="I157" s="7" t="inlineStr">
@@ -31372,7 +31392,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>MD-00119 cost basis: two systems, two amounts.</t>
+          <t>Basis mismatch documented for MD-00119 (950.0 vs 1115.0).</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr">
@@ -31418,7 +31438,7 @@
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is shut. Rewrite the register location (MD-00121).</t>
+          <t>Clear the leftover closed-office assignment on MD-00121 (EX-0154).</t>
         </is>
       </c>
       <c r="I158" s="7" t="inlineStr">
@@ -31438,7 +31458,7 @@
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is locked. I'm not leaving MD-00121 there on paper. Chicago is the operating site.</t>
+          <t>Closed floor Denver - Closed remains on MD-00121 despite transfer evidence (EX-0154, TR-00121).</t>
         </is>
       </c>
       <c r="M158" s="7" t="inlineStr">
@@ -31484,7 +31504,7 @@
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>Update MD-00122 location. Dallas is what transfer/HR support.</t>
+          <t>IT Asset Specialist: recode MD-00122 off Chicago - Closed; Dallas is the live office per TR-00122 (EX-0155).</t>
         </is>
       </c>
       <c r="I159" s="7" t="inlineStr">
@@ -31504,7 +31524,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>Consolidation leftover: MD-00122 @ Chicago - Closed.</t>
+          <t>Walked register vs HR/transfer: MD-00122 still says Chicago - Closed (EX-0155).</t>
         </is>
       </c>
       <c r="M159" s="7" t="inlineStr">
@@ -31550,7 +31570,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>Register still has the shuttered floor (Denver - Closed). Put Denver on the row.</t>
+          <t>Update register location for MD-00123 before the next cert packet (EX-0156).</t>
         </is>
       </c>
       <c r="I160" s="7" t="inlineStr">
@@ -31570,7 +31590,7 @@
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
-          <t>MD-00123 still coded to a floor we don't occupy (Denver - Closed).</t>
+          <t>Register still codes MD-00123 to Denver - Closed; TR-00123 points to Denver (EX-0156).</t>
         </is>
       </c>
       <c r="M160" s="7" t="inlineStr">
@@ -31616,7 +31636,7 @@
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Location cleanup for MD-00124: Chicago - Closed → New York.</t>
+          <t>Remove closed-site coding on MD-00124 (Chicago - Closed → New York, EX-0157).</t>
         </is>
       </c>
       <c r="I161" s="7" t="inlineStr">
@@ -31636,7 +31656,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>Site code is stale. Chicago - Closed vs New York.</t>
+          <t>Extract shows MD-00124 at Chicago - Closed — that building is locked (EX-0157).</t>
         </is>
       </c>
       <c r="M161" s="7" t="inlineStr">
@@ -31682,7 +31702,7 @@
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Closed-office leftover. Update MD-00125 to Seattle.</t>
+          <t>Seattle is supported by HR/transfer for MD-00125; Denver - Closed is obsolete (EX-0158).</t>
         </is>
       </c>
       <c r="I162" s="7" t="inlineStr">
@@ -31702,7 +31722,7 @@
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
-          <t>TR-00125 destination isn't the shuttered office on the register.</t>
+          <t>Physical sites changed; MD-00125 register did not (Denver - Closed, EX-0158).</t>
         </is>
       </c>
       <c r="M162" s="7" t="inlineStr">
@@ -31748,7 +31768,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Don't leave MD-00126 coded to Chicago - Closed.</t>
+          <t>Atlanta is supported by HR/transfer for MD-00126; Chicago - Closed is obsolete (EX-0159).</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr">
@@ -31768,7 +31788,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is locked. I'm not leaving MD-00126 there on paper. Atlanta is the operating site.</t>
+          <t>Consolidation left MD-00126 @ Chicago - Closed; ops now use Atlanta (EX-0159).</t>
         </is>
       </c>
       <c r="M163" s="7" t="inlineStr">
@@ -31814,7 +31834,7 @@
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>MD-00127: movement TR-00127 never got an approval ID. Fix per §4.</t>
+          <t>Either approve TR-00127 after the fact or put MD-00127 back.</t>
         </is>
       </c>
       <c r="I164" s="7" t="inlineStr">
@@ -31834,7 +31854,7 @@
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001 §4: TR-00127 isn't a completed approved transfer.</t>
+          <t>Unapproved transfer TR-00127 on MD-00127 from equipment_transfer_log.</t>
         </is>
       </c>
       <c r="M164" s="7" t="inlineStr">
@@ -31880,7 +31900,7 @@
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>Do not treat MD-00130 as a Critical ledger gap. PO-2023-0022 capitalization_approved doesn't override ITAM-001 §7.</t>
+          <t>$700 on MD-00130. Below threshold. Informational only.</t>
         </is>
       </c>
       <c r="I165" s="7" t="inlineStr">
@@ -31900,7 +31920,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>Checked the threshold against MD-00130. Not a capital gap.</t>
+          <t>$700 on MD-00130 — under §7 gate. Ledger absence expected.</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
@@ -31946,7 +31966,7 @@
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>MD-00131: under-threshold. Leave it off the FAR on purpose.</t>
+          <t>$1175 on MD-00131. Below threshold. Informational only.</t>
         </is>
       </c>
       <c r="I166" s="7" t="inlineStr">
@@ -31966,7 +31986,7 @@
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
-          <t>MD-00131 under the gate. Informational.</t>
+          <t>Under-threshold check for MD-00131: $1175 &lt; $2,500.</t>
         </is>
       </c>
       <c r="M166" s="12" t="inlineStr">
@@ -32012,7 +32032,7 @@
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>MD-00132 is missing from the ledger. Capitalize or write off; do not take RN-0132 as expense-under-threshold.</t>
+          <t>Finance: FA line for MD-00132 or signed write-off. Regional note non-authoritative.</t>
         </is>
       </c>
       <c r="I167" s="7" t="inlineStr">
@@ -32032,7 +32052,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>FAR extract has no MD-00132. Cost $6470 is over $2,500. Note RN-0132 is a claim, not a posting.</t>
+          <t>FAR extract has no MD-00132. Cost $6470.0 exceeds $2,500. RN-0132 is a claim, not a posting.</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
@@ -32071,7 +32091,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Custody Chain — High-Risk and Unresolved Assets</t>
         </is>
@@ -32084,48 +32104,49 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Asset Tag</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>From Party</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>To Party</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Record Reference</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>Fact Type</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
@@ -32186,32 +32207,24 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Assignment/Transfer</t>
+          <t>Policy Control Figure</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Central Receiving</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>E0017</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
+          <t>ITAM-001</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Transfer:TR-00017; Approval:APR-00017</t>
+          <t>ITAM_control_matrix.png; IT_asset_management_policy.pdf</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -32221,7 +32234,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00017 completed inbound 6/19/26.</t>
+          <t>Seattle custody review for MD-00017 used the disposal column on the matrix. Source trail: TR-00017, PO-2024-0003, FA-000017, APR-00017.</t>
         </is>
       </c>
     </row>
@@ -32233,24 +32246,32 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Policy Control Figure</t>
+          <t>Assignment/Transfer</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
+          <t>Central Receiving</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>E0017</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>ITAM_control_matrix.png; IT_asset_management_policy.pdf</t>
+          <t>Transfer:TR-00017; Approval:APR-00017</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -32260,7 +32281,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>MD-00017 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00017.</t>
+          <t>TR-00017 2026-06-17; inbound Jun 19, 2026.</t>
         </is>
       </c>
     </row>
@@ -32307,7 +32328,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Landed on In Use (High). EX-0001. E0017 TR-00017 APR-00017 PO-2024-0003 FA-000017 ITAM_control_matrix.png</t>
+          <t>Verified In Use for MD-00017 in Seattle. High. EX-0001. E0017. TR-00017. APR-00017. PO. PO-2024-0003. FA-000017. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -32354,7 +32375,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>MD-00021 origin: PO-2025-0004, $1850.</t>
+          <t>Procurement PO-2025-0004 lists Dell Latitude 7440 / $1850.</t>
         </is>
       </c>
     </row>
@@ -32401,7 +32422,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>TR-00021 2026-05-02; inbound May 3, 2026.</t>
+          <t>Dock file shows May 03, 2026 for TR-00021 (MD-00021).</t>
         </is>
       </c>
     </row>
@@ -32440,7 +32461,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Policy appendix applied to MD-00021 under financial reconciliation; figure informs the review, TR-00021 carries it.</t>
+          <t>ITAM_control_matrix.png consulted for MD-00021 (return). Conclusion still tied to TR-00021, PO-2025-0004, FA-000021, APR-00021 at Denver, $1850.</t>
         </is>
       </c>
     </row>
@@ -32487,7 +32508,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Verified In Use. EX-0002. Medium. E0021 TR-00021 APR-00021 PO-2025-0004 FA-000021 ITAM_control_matrix.png</t>
+          <t>MD-00021 custody narrative ends In Use (Medium). EX-0002. E0021. TR-00021. APR-00021. PO. PO-2025-0004. FA-000021. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -32534,7 +32555,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>$2030 Lenovo ThinkPad T14. PO-2022-0005.</t>
+          <t>Procurement PO-2022-0005 lists Lenovo ThinkPad T14 / $2030.</t>
         </is>
       </c>
     </row>
@@ -32581,7 +32602,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Chicago: TR-00025 received 2026-01-22.</t>
+          <t>Log row TR-00025. Receive date 01/22/2026.</t>
         </is>
       </c>
     </row>
@@ -32624,7 +32645,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00025 — non-authoritative.</t>
+          <t>Could not tie MD-00025 to a verified RN entry in the notes.</t>
         </is>
       </c>
     </row>
@@ -32663,7 +32684,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Evidence rubric for MD-00025 pulled from the control matrix (disposal); chain anchor TR-00025; policy PDF §4–§7 read with TR-00025.</t>
+          <t>Auditors tracing MD-00025 should read matrix transfer, then TR-00025, PO-2022-0005, FA-000025, APR-00025. Working site Chicago; status call In Use.</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32731,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>MD-00025 → In Use. Confidence Medium. EX-0003, EX-0004. E0025 TR-00025 APR-00025 PO-2022-0005 FA-000025 ITAM_control_matrix.png</t>
+          <t>Chain end MD-00025: In Use; Medium; EX-0003, EX-0004. E0025. TR-00025. APR-00025. PO. PO-2022-0005. FA-000025. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -32804,7 +32825,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Recorded 2026-05-22, received 2026-05-22. TR-00034.</t>
+          <t>MD-00034 inbound May 22, 2026 on TR-00034 / APR-00034.</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32868,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00034. Notes don't beat a scan.</t>
+          <t>Regional file reviewed for MD-00034; no clearance language accepted.</t>
         </is>
       </c>
     </row>
@@ -32886,7 +32907,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>MD-00034 — auditors should read the disposal line on the matrix, then follow TR-00034; ITAM_control_matrix.png attached.</t>
+          <t>MD-00034 / Dell U2723QE: return evidence expectations from Appendix A. Anchored to TR-00034, PO-2023-0006, FA-000034, APR-00034; acquisition $790.</t>
         </is>
       </c>
     </row>
@@ -32933,7 +32954,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>In Use is the status I'm standing behind. EX-0013, EX-0014. High. E0034 TR-00034 APR-00034 PO-2023-0006 FA-000034 ITAM_control_matrix.png</t>
+          <t>Outcome MD-00034 — In Use, site New York, High. EX-0013, EX-0014. E0034. TR-00034. APR-00034. PO. PO-2023-0006. FA-000034. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -32980,7 +33001,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>$1040 Samsung Galaxy S24. PO-2022-0009.</t>
+          <t>Capital buy MD-00051: Samsung Galaxy S24, $1040, PO-2022-0009.</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33048,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Denver: TR-00051 received March 31, 2026.</t>
+          <t>Dock file shows 2026-03-31 for TR-00051 (MD-00051).</t>
         </is>
       </c>
     </row>
@@ -33070,7 +33091,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00051 — non-authoritative.</t>
+          <t>Could not tie MD-00051 to a verified RN entry in the notes.</t>
         </is>
       </c>
     </row>
@@ -33109,7 +33130,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>MD-00051: ITAM-001 appendix defines acceptable return proof — see TR-00051 in this chain.</t>
+          <t>Did not treat the PNG as proof of location for MD-00051. return standard applied; TR-00051, PO-2022-0009, FA-000051, APR-00051 remains dispositive (Available).</t>
         </is>
       </c>
     </row>
@@ -33156,7 +33177,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Available. High confidence. EX-0031, EX-0032. TR-00051 APR-00051 PO-2022-0009 FA-000051 ITAM_control_matrix.png</t>
+          <t>I am standing on Available for MD-00051 (Denver, High). EX-0031, EX-0032. TR-00051. APR-00051. PO. PO-2022-0009. FA-000051. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -33203,7 +33224,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0010. Dell U2723QE.</t>
+          <t>PO line PO-2023-0010 — Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -33250,7 +33271,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Recorded May 22, 2026, received 5/23. TR-00058.</t>
+          <t>Dock file shows 05/23/2026 for TR-00058 (MD-00058).</t>
         </is>
       </c>
     </row>
@@ -33375,7 +33396,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb in regional_IT_notes.docx. Still need a transaction for MD-00058.</t>
+          <t>Regional claim (Asset appears to have been moved to Regional IT stock. The transfer record contains no app) does not beat a scan for MD-00058.</t>
         </is>
       </c>
     </row>
@@ -33414,7 +33435,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Appendix A transfer requirements govern MD-00058; PNG matrix is reference only beside TR-00058.</t>
+          <t>MD-00058: checked ITAM-001 disposal row while reviewing TR-00058, PO-2023-0010, FA-000058, OFF-00058. Cost basis $610; confidence Medium. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33482,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Call: Pending Redeployment at New York. Medium. Exceptions EX-0039, EX-0040, EX-0041. TR-00058 OFF-00058 PO-2023-0010 FA-000058 ITAM_control_matrix.png</t>
+          <t>Call on MD-00058: Pending Redeployment, Medium. EX-0039, EX-0040, EX-0041. TR-00058. OFF-00058. PO. PO-2023-0010. FA-000058. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -33508,7 +33529,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00059 (Samsung Galaxy S24) for $1085 via PO-2023-0010.</t>
+          <t>PO-2023-0010 documents $1085 for Samsung Galaxy S24.</t>
         </is>
       </c>
     </row>
@@ -33555,7 +33576,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00059 completed inbound 6/26.</t>
+          <t>TR-00059 — got it 2026-06-26 at Seattle.</t>
         </is>
       </c>
     </row>
@@ -33598,7 +33619,7 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00059 on MD-00059. Return required Yes.</t>
+          <t>Opened OFF-00059. Status Closed.</t>
         </is>
       </c>
     </row>
@@ -33680,7 +33701,7 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Didn't let the regional write-up overrule the logs on MD-00059.</t>
+          <t>Looked for MD-00059 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
         </is>
       </c>
     </row>
@@ -33719,7 +33740,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>When scoring MD-00059, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00059 was checked; ITAM_control_matrix.png attached.</t>
+          <t>Matrix figure open for MD-00059 return path; transactional weight on TR-00059, PO-2023-0010, FA-000059, OFF-00059. Open exceptions EX-0042, EX-0043, EX-0044 still govern certification impact.</t>
         </is>
       </c>
     </row>
@@ -33766,7 +33787,7 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>MD-00059 → Pending Redeployment. Confidence Medium. EX-0042, EX-0043, EX-0044. TR-00059 OFF-00059 PO-2023-0010 FA-000059 ITAM_control_matrix.png</t>
+          <t>Closing MD-00059: Pending Redeployment at Seattle (Medium). EX-0042, EX-0043, EX-0044. TR-00059. OFF-00059. PO. PO-2023-0010. FA-000059. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33834,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2023-0010. Cisco C9300, $6380.</t>
+          <t>MD-00060 origin: PO-2023-0010, $6380.</t>
         </is>
       </c>
     </row>
@@ -33860,7 +33881,7 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted January 30, 2026. Docked 2/2 (TR-00060).</t>
+          <t>Movement TR-00060 completed inbound Feb 02, 2026.</t>
         </is>
       </c>
     </row>
@@ -33903,7 +33924,7 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>OFF-00060 — Closed. Due Jul 15.</t>
+          <t>OFF-00060 Closed. Return required=Yes, due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -33985,7 +34006,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Closed-floor story in the notes. Ignored as clearance.</t>
+          <t>Word dump checked for MD-00060; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -34024,7 +34045,7 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Evidence rubric for MD-00060 pulled from the control matrix (disposal); chain anchor TR-00060; policy PDF §4–§7 read with TR-00060.</t>
+          <t>For MD-00060 (Cisco C9300), Appendix A transfer criteria were read against TR-00060, PO-2023-0010, FA-000060, OFF-00060, APR-00060. Verified status target Pending Redeployment at Atlanta; matrix PNG is reference only.</t>
         </is>
       </c>
     </row>
@@ -34071,7 +34092,7 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Landed on Pending Redeployment (High). EX-0045, EX-0046. TR-00060 APR-00060 OFF-00060 PO-2023-0010 FA-000060 ITAM_control_matrix.png</t>
+          <t>Final read MD-00060: Pending Redeployment @ Atlanta, confidence High. EX-0045, EX-0046. TR-00060. APR-00060. OFF-00060. PO. PO-2023-0010. FA-000060. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -34118,7 +34139,7 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>MD-00061 origin: PO-2024-0011, $2075.</t>
+          <t>PO-2024-0011 documents $2075 for Lenovo ThinkPad T14.</t>
         </is>
       </c>
     </row>
@@ -34165,7 +34186,7 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>TR-00061 February 2, 2026; inbound 2/3.</t>
+          <t>Assignment posted Feb 02, 2026. Docked 02/03/2026 (TR-00061).</t>
         </is>
       </c>
     </row>
@@ -34208,7 +34229,7 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00061. Doesn't by itself dock MD-00061.</t>
+          <t>Offboarding OFF-00061: Yes. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -34290,7 +34311,7 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Someone wrote that it stayed at a closed site. Unverified for MD-00061.</t>
+          <t>Regional write-up for MD-00061 is non-authoritative per ITAM-001.</t>
         </is>
       </c>
     </row>
@@ -34329,7 +34350,7 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>On MD-00061, the matrix documents what transfer evidence looks like; it is not a substitute for TR-00061.</t>
+          <t>MD-00061: checked ITAM-001 assignment row while reviewing TR-00061, PO-2024-0011, FA-000061, OFF-00061, APR-00061. Cost basis $2075; confidence High. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -34376,7 +34397,7 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Wrap: MD-00061 Pending Redeployment. EX-0047, EX-0048. TR-00061 APR-00061 OFF-00061 PO-2024-0011 FA-000061 ITAM_control_matrix.png</t>
+          <t>Pending Redeployment is the status for MD-00061 at Chicago; High. EX-0047, EX-0048. TR-00061. APR-00061. OFF-00061. PO. PO-2024-0011. FA-000061. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -34423,7 +34444,7 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE came in on PO-2024-0011 ($790).</t>
+          <t>Warehouse receipt tied to PO-2024-0011. Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -34470,7 +34491,7 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00062. Receive date 3/7.</t>
+          <t>Dock file shows 2026-03-07 for TR-00062 (MD-00062).</t>
         </is>
       </c>
     </row>
@@ -34513,7 +34534,7 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>OFF-00062 sits Closed. Hardware return was required. Jul 15.</t>
+          <t>Offboarding OFF-00062: Yes. Due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -34595,7 +34616,7 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00062. Notes don't beat a scan.</t>
+          <t>No matching RN row for MD-00062; generic technician chatter in the Word file only.</t>
         </is>
       </c>
     </row>
@@ -34634,7 +34655,7 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial tests for MD-00062 were read against the matrix financial reconciliation row and TR-00062; policy PDF §4–§7 read with TR-00062.</t>
+          <t>MD-00062 / Dell U2723QE: financial evidence expectations from Appendix A. Anchored to TR-00062, PO-2024-0011, FA-000062, OFF-00062, APR-00062; acquisition $790.</t>
         </is>
       </c>
     </row>
@@ -34681,7 +34702,7 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Pending Redeployment is the status I'm standing behind. EX-0049, EX-0050. High. TR-00062 APR-00062 OFF-00062 PO-2024-0011 FA-000062 ITAM_control_matrix.png</t>
+          <t>Call on MD-00062: Pending Redeployment, High. EX-0049, EX-0050. TR-00062. APR-00062. OFF-00062. PO. PO-2024-0011. FA-000062. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -34728,7 +34749,7 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>$950 Samsung Galaxy S24. PO-2024-0011.</t>
+          <t>Bought the Samsung Galaxy S24 ($950) on PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -34775,7 +34796,7 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>Denver: TR-00063 received 4/16.</t>
+          <t>TR-00063 — got it Apr 16, 2026 at Denver.</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34839,7 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00063: Yes. Due Jul 15.</t>
+          <t>OFF-00063 sits Closed. Hardware return was required. 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -34900,7 +34921,7 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx is in the packet. Weight = lead only (MD-00063).</t>
+          <t>Investigative color on MD-00063 in regional_IT_notes.docx — weight zero.</t>
         </is>
       </c>
     </row>
@@ -34939,7 +34960,7 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>Control design for MD-00063 (return) comes from the policy figure; movement proof is TR-00063.</t>
+          <t>MD-00063: checked ITAM-001 return row while reviewing TR-00063, PO-2024-0011, FA-000063, OFF-00063, APR-00063. Cost basis $950; confidence High. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -34986,7 +35007,7 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00063: Pending Redeployment / Denver (High). EX-0051, EX-0052. TR-00063 APR-00063 OFF-00063 PO-2024-0011 FA-000063 ITAM_control_matrix.png</t>
+          <t>Outcome MD-00063 — Pending Redeployment, site Denver, High. EX-0051, EX-0052. TR-00063. APR-00063. OFF-00063. PO. PO-2024-0011. FA-000063. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35033,7 +35054,7 @@
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>PO-2024-0011: Cisco C9300 at $6245.</t>
+          <t>Procurement PO-2024-0011 lists Cisco C9300 / $6245.</t>
         </is>
       </c>
     </row>
@@ -35080,7 +35101,7 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>Moved to Regional IT in New York on TR-00064. Received 5/14.</t>
+          <t>From warehouse to Regional IT. TR-00064, received 05/14/2026.</t>
         </is>
       </c>
     </row>
@@ -35123,7 +35144,7 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>OFF-00064 Closed. Return required=Yes, due Jul 15.</t>
+          <t>People ticket OFF-00064. Doesn't by itself dock MD-00064.</t>
         </is>
       </c>
     </row>
@@ -35205,7 +35226,7 @@
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>I read the note. I didn't relocate MD-00064 off of it.</t>
+          <t>Technician comment volume in the doc does not clear MD-00064.</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35265,7 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>MD-00064 custody review used the appendix matrix on assignment; TR-00064 remains the auditable source; policy PDF §4–§7 read with TR-00064.</t>
+          <t>Auditors tracing MD-00064 should read matrix transfer, then TR-00064, PO-2024-0011, FA-000064, OFF-00064. Working site New York; status call Pending Redeployment.</t>
         </is>
       </c>
     </row>
@@ -35291,7 +35312,7 @@
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>Verified Pending Redeployment. EX-0053, EX-0054, EX-0055. Medium. TR-00064 OFF-00064 PO-2024-0011 FA-000064 ITAM_control_matrix.png</t>
+          <t>I am standing on Pending Redeployment for MD-00064 (New York, Medium). EX-0053, EX-0054, EX-0055. TR-00064. OFF-00064. PO. PO-2024-0011. FA-000064. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35338,7 +35359,7 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2024-0011 matches MD-00065 at $1940.</t>
+          <t>$1940 MacBook Pro 14. PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -35385,7 +35406,7 @@
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>TR-00065 — got it 6/23 at Seattle.</t>
+          <t>Moved to Regional IT in Seattle on TR-00065. Received 2026-06-23.</t>
         </is>
       </c>
     </row>
@@ -35428,7 +35449,7 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 tied to OFF-00065 (Closed). SLA Jul 15.</t>
+          <t>People ticket OFF-00065. Doesn't by itself dock MD-00065.</t>
         </is>
       </c>
     </row>
@@ -35510,7 +35531,7 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>Tech note in the Word dump. Treated as a lead for MD-00065, not location proof.</t>
+          <t>Notes packet includes MD-00065 only as background, not evidence.</t>
         </is>
       </c>
     </row>
@@ -35549,7 +35570,7 @@
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure cited on MD-00065 as the control standard for disposal; transactional weight stays with TR-00065.</t>
+          <t>Auditors tracing MD-00065 should read matrix assignment, then TR-00065, PO-2024-0011, FA-000065, OFF-00065. Working site Seattle; status call Pending Redeployment.</t>
         </is>
       </c>
     </row>
@@ -35596,7 +35617,7 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Pending Redeployment. Medium confidence. EX-0056, EX-0057, EX-0058. TR-00065 OFF-00065 PO-2024-0011 FA-000065 ITAM_control_matrix.png</t>
+          <t>Wrap-up MD-00065: Pending Redeployment (Medium) — EX-0056, EX-0057, EX-0058. TR-00065. OFF-00065. PO. PO-2024-0011. FA-000065. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35664,7 @@
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2024-0011 — Dell U2723QE.</t>
+          <t>Ordered Dell U2723QE (MD-00066) on PO-2024-0011; $655.</t>
         </is>
       </c>
     </row>
@@ -35690,7 +35711,7 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Regional IT. TR-00066, received 1/25.</t>
+          <t>MD-00066 inbound Jan 25, 2026 on TR-00066 / APR-00066.</t>
         </is>
       </c>
     </row>
@@ -35733,7 +35754,7 @@
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00066. Status Closed.</t>
+          <t>OFF-00066 — Closed. Due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -35815,7 +35836,7 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>Note exists. Corroboration doesn't. MD-00066.</t>
+          <t>MD-00066: Word-file mention only — treated as lead.</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35875,7 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>Policy matrix (transfer row) applied while tracing MD-00066; the figure does not replace TR-00066; policy PDF §4–§7 read with TR-00066.</t>
+          <t>Matrix figure open for MD-00066 disposal path; transactional weight on TR-00066, PO-2024-0011, FA-000066, OFF-00066, APR-00066. Open exceptions EX-0059, EX-0060 still govern certification impact.</t>
         </is>
       </c>
     </row>
@@ -35901,7 +35922,7 @@
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>Call: Pending Redeployment at Atlanta. High. Exceptions EX-0059, EX-0060. TR-00066 APR-00066 OFF-00066 PO-2024-0011 FA-000066 ITAM_control_matrix.png</t>
+          <t>After the chain, MD-00066 is Pending Redeployment / Atlanta (High). EX-0059, EX-0060. TR-00066. APR-00066. OFF-00066. PO. PO-2024-0011. FA-000066. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35948,7 +35969,7 @@
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>Bought the Samsung Galaxy S24 ($1130) on PO-2025-0012.</t>
+          <t>$1130 Samsung Galaxy S24. PO-2025-0012.</t>
         </is>
       </c>
     </row>
@@ -35995,7 +36016,7 @@
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00067 / APR-00067. Received 2/23.</t>
+          <t>Log row TR-00067. Receive date 02/23/2026.</t>
         </is>
       </c>
     </row>
@@ -36120,7 +36141,7 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00067 — non-authoritative.</t>
+          <t>Technician notes scanned for MD-00067; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -36159,7 +36180,7 @@
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>MD-00067 chain includes the policy figure as the financial reconciliation rubric only; TR-00067 is dispositive.</t>
+          <t>Matrix figure open for MD-00067 return path; transactional weight on TR-00067, PO-2025-0012, FA-000067, OFF-00067, APR-00067. Open exceptions EX-0061, EX-0062 still govern certification impact.</t>
         </is>
       </c>
     </row>
@@ -36206,7 +36227,7 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>MD-00067 → Pending Redeployment. Confidence High. EX-0061, EX-0062. TR-00067 APR-00067 OFF-00067 PO-2025-0012 FA-000067 ITAM_control_matrix.png</t>
+          <t>MD-00067 custody narrative ends Pending Redeployment (High). EX-0061, EX-0062. TR-00067. APR-00067. OFF-00067. PO. PO-2025-0012. FA-000067. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36274,7 @@
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2025-0012. Cisco C9300.</t>
+          <t>First touch MD-00068 — PO-2025-0012, $6425.</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36321,7 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Recorded March 28, 2026, received 4/3. TR-00068.</t>
+          <t>Assignment posted 03/28/2026. Docked 2026-04-03 (TR-00068).</t>
         </is>
       </c>
     </row>
@@ -36343,7 +36364,7 @@
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>OFF-00068 — Past Due. Due Jul 15.</t>
+          <t>Offboarding OFF-00068: Yes. Due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -36429,7 +36450,7 @@
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00068 on the 1Z print. 1ZMD00000068.</t>
+          <t>Prepaid label 1ZMD00000068 exists. Carrier never accepted it.</t>
         </is>
       </c>
     </row>
@@ -36472,7 +36493,7 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Someone wrote that it stayed at a closed site. Unverified for MD-00068.</t>
+          <t>Looked for MD-00068 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
         </is>
       </c>
     </row>
@@ -36511,7 +36532,7 @@
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>MD-00068 — auditors should read the disposal line on the matrix, then follow TR-00068; ITAM_control_matrix.png attached.</t>
+          <t>Remote - Former Employee custody review for MD-00068 used the assignment column on the matrix. Source trail: TR-00068, PO-2025-0012, FA-000068, OFF-00068, APR-00068.</t>
         </is>
       </c>
     </row>
@@ -36558,7 +36579,7 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>MD-00068 → Return Overdue. Confidence Low. EX-0063, EX-0064, EX-0065. OFF-00068 1ZMD00000068 TR-00068 E0081 PO-2025-0012 FA-000068 ITAM_control_matrix.png</t>
+          <t>Return Overdue is the status for MD-00068 at Remote - Former Employee; Low. EX-0063, EX-0064, EX-0065. OFF-00068. 1ZMD00000068. TR-00068. E0081. PO. PO-2025-0012. FA-000068. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -36605,7 +36626,7 @@
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 came in on PO-2025-0012 ($2120).</t>
+          <t>Procurement PO-2025-0012 lists Dell Latitude 7440 / $2120.</t>
         </is>
       </c>
     </row>
@@ -36652,7 +36673,7 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00069. Receive date May 4.</t>
+          <t>Remote - Former Employee: TR-00069 received 05/04/2026.</t>
         </is>
       </c>
     </row>
@@ -36695,7 +36716,7 @@
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>OFF-00069 — Past Due. Due July 15, 2026.</t>
+          <t>OFF-00069 — Past Due. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -36781,7 +36802,7 @@
       </c>
       <c r="I110" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00069 on the 1Z print. 1ZMD00000069.</t>
+          <t>Ship record 1ZMD00000069 hasn't left Label Created.</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36845,7 @@
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
-          <t>Tech note in the Word dump. Treated as a lead for MD-00069, not location proof.</t>
+          <t>Looked for MD-00069 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
         </is>
       </c>
     </row>
@@ -36863,7 +36884,7 @@
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>MD-00069: return controls in Appendix A; matrix noted alongside TR-00069; policy PDF §4–§7 read with TR-00069.</t>
+          <t>Control matrix cited on MD-00069 for assignment only. Movement/finance proof stays with TR-00069, PO-2025-0012, FA-000069, OFF-00069, APR-00069; exceptions EX-0066, EX-0067.</t>
         </is>
       </c>
     </row>
@@ -36910,7 +36931,7 @@
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>MD-00069 → Return Overdue. Confidence Low. EX-0066, EX-0067. OFF-00069 1ZMD00000069 TR-00069 E0082 PO-2025-0012 FA-000069 ITAM_control_matrix.png</t>
+          <t>After the chain, MD-00069 is Return Overdue / Remote - Former Employee (Low). EX-0066, EX-0067. OFF-00069. 1ZMD00000069. TR-00069. E0082. PO. PO-2025-0012. FA-000069. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -36957,7 +36978,7 @@
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2025-0012 — Dell U2723QE.</t>
+          <t>First touch MD-00070 — PO-2025-0012, $520.</t>
         </is>
       </c>
     </row>
@@ -37004,7 +37025,7 @@
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to E0073. TR-00070, received June 3, 2026.</t>
+          <t>Dock file shows Jun 03, 2026 for TR-00070 (MD-00070).</t>
         </is>
       </c>
     </row>
@@ -37047,7 +37068,7 @@
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>OFF-00070 — Past Due. Due 15 Jul.</t>
+          <t>People ticket OFF-00070. Doesn't by itself dock MD-00070.</t>
         </is>
       </c>
     </row>
@@ -37133,7 +37154,7 @@
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00070 on the 1Z print. 1ZMD00000070.</t>
+          <t>Printed 1ZMD00000070. Box not in the inbound file.</t>
         </is>
       </c>
     </row>
@@ -37176,7 +37197,7 @@
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>Didn't let the regional write-up overrule the logs on MD-00070.</t>
+          <t>Word dump checked for MD-00070; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -37215,7 +37236,7 @@
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>MD-00070: return controls in Appendix A; matrix noted alongside TR-00070; policy PDF §4–§7 read with TR-00070.</t>
+          <t>Policy PDF + ITAM_control_matrix.png set the transfer bar for MD-00070. Compared that bar to TR-00070, PO-2025-0012, FA-000070, OFF-00070, APR-00070 before accepting any tech note.</t>
         </is>
       </c>
     </row>
@@ -37262,7 +37283,7 @@
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 → Return Overdue. Confidence Low. EX-0068, EX-0069. OFF-00070 1ZMD00000070 TR-00070 E0083 PO-2025-0012 FA-000070 ITAM_control_matrix.png</t>
+          <t>Final read MD-00070: Return Overdue @ Remote - Former Employee, confidence Low. EX-0068, EX-0069. OFF-00070. 1ZMD00000070. TR-00070. E0083. PO. PO-2025-0012. FA-000070. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37330,7 @@
       </c>
       <c r="I122" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2025-0012. Samsung Galaxy S24, $995.</t>
+          <t>Bought the Samsung Galaxy S24 ($995) on PO-2025-0012.</t>
         </is>
       </c>
     </row>
@@ -37356,7 +37377,7 @@
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 7/8/26. Docked 12 Jul (TR-00071).</t>
+          <t>Log row TR-00071. Receive date 2026-07-12.</t>
         </is>
       </c>
     </row>
@@ -37399,7 +37420,7 @@
       </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
-          <t>OFF-00071 — Past Due. Due 2026-07-15.</t>
+          <t>MD-00071 tied to OFF-00071 (Past Due). SLA Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -37485,7 +37506,7 @@
       </c>
       <c r="I126" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00071 on the 1Z print. 1ZMD00000071.</t>
+          <t>Return paperwork only. 1ZMD00000071.</t>
         </is>
       </c>
     </row>
@@ -37528,7 +37549,7 @@
       </c>
       <c r="I127" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx is in the packet. Weight = lead only (MD-00071).</t>
+          <t>Word dump checked for MD-00071; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -37567,7 +37588,7 @@
       </c>
       <c r="I128" s="7" t="inlineStr">
         <is>
-          <t>Appendix A transfer requirements govern MD-00071; PNG matrix is reference only beside TR-00071.</t>
+          <t>MD-00071 / Samsung Galaxy S24: assignment evidence expectations from Appendix A. Anchored to TR-00071, PO-2025-0012, FA-000071, OFF-00071, APR-00071; acquisition $995.</t>
         </is>
       </c>
     </row>
@@ -37614,7 +37635,7 @@
       </c>
       <c r="I129" s="7" t="inlineStr">
         <is>
-          <t>MD-00071 → Return Overdue. Confidence Low. EX-0070, EX-0071. OFF-00071 1ZMD00000071 TR-00071 E0084 PO-2025-0012 FA-000071 ITAM_control_matrix.png</t>
+          <t>Verified Return Overdue for MD-00071 in Remote - Former Employee. Low. EX-0070, EX-0071. OFF-00071. 1ZMD00000071. TR-00071. E0084. PO. PO-2025-0012. FA-000071. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37682,7 @@
       </c>
       <c r="I130" s="7" t="inlineStr">
         <is>
-          <t>PO-2025-0012: Cisco C9300 at $6290.</t>
+          <t>Purchasing file PO-2025-0012 matches MD-00072 at $6290.</t>
         </is>
       </c>
     </row>
@@ -37708,7 +37729,7 @@
       </c>
       <c r="I131" s="7" t="inlineStr">
         <is>
-          <t>Moved to E0075 in Remote - Former Employee on TR-00072. Received 2026-01-18.</t>
+          <t>Assignment posted Jan 18, 2026. Docked 01/18/2026 (TR-00072).</t>
         </is>
       </c>
     </row>
@@ -37751,7 +37772,7 @@
       </c>
       <c r="I132" s="7" t="inlineStr">
         <is>
-          <t>OFF-00072 — Past Due. Due 7/15/26.</t>
+          <t>People ticket OFF-00072. Doesn't by itself dock MD-00072.</t>
         </is>
       </c>
     </row>
@@ -37837,7 +37858,7 @@
       </c>
       <c r="I134" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00072 on the 1Z print. 1ZMD00000072.</t>
+          <t>Printed 1ZMD00000072. Box not in the inbound file.</t>
         </is>
       </c>
     </row>
@@ -37880,7 +37901,7 @@
       </c>
       <c r="I135" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00072 — non-authoritative.</t>
+          <t>Word dump checked for MD-00072; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -37919,7 +37940,7 @@
       </c>
       <c r="I136" s="7" t="inlineStr">
         <is>
-          <t>MD-00072 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00072.</t>
+          <t>MD-00072 chain includes the figure as a assignment rubric (Low). Record set: TR-00072, PO-2025-0012, FA-000072, OFF-00072, APR-00072.</t>
         </is>
       </c>
     </row>
@@ -37966,7 +37987,7 @@
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>MD-00072 → Return Overdue. Confidence Low. EX-0072, EX-0073. OFF-00072 1ZMD00000072 TR-00072 E0085 PO-2025-0012 FA-000072 ITAM_control_matrix.png</t>
+          <t>Closing MD-00072: Return Overdue at Remote - Former Employee (Low). EX-0072, EX-0073. OFF-00072. 1ZMD00000072. TR-00072. E0085. PO. PO-2025-0012. FA-000072. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -38013,7 +38034,7 @@
       </c>
       <c r="I138" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2022-0013. Lenovo ThinkPad T14.</t>
+          <t>$1985 Lenovo ThinkPad T14. PO-2022-0013.</t>
         </is>
       </c>
     </row>
@@ -38060,7 +38081,7 @@
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>Recorded 1/21, received 1/24/26. TR-00073.</t>
+          <t>MD-00073 inbound Jan 24, 2026 on TR-00073 / APR-00073.</t>
         </is>
       </c>
     </row>
@@ -38103,7 +38124,7 @@
       </c>
       <c r="I140" s="7" t="inlineStr">
         <is>
-          <t>OFF-00073 — Past Due. Due 2026-07-15.</t>
+          <t>MD-00073 tied to OFF-00073 (Past Due). SLA 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -38189,7 +38210,7 @@
       </c>
       <c r="I142" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00073 on the 1Z print. 1ZMD00000073.</t>
+          <t>Return paperwork only. 1ZMD00000073.</t>
         </is>
       </c>
     </row>
@@ -38232,7 +38253,7 @@
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>Someone wrote that it stayed at a closed site. Unverified for MD-00073.</t>
+          <t>Word dump checked for MD-00073; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38292,7 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>When scoring MD-00073, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00073 was checked; ITAM_control_matrix.png attached.</t>
+          <t>MD-00073 chain includes the figure as a assignment rubric (Low). Record set: TR-00073, PO-2022-0013, FA-000073, OFF-00073, APR-00073.</t>
         </is>
       </c>
     </row>
@@ -38318,7 +38339,7 @@
       </c>
       <c r="I145" s="7" t="inlineStr">
         <is>
-          <t>MD-00073 → Return Overdue. Confidence Low. EX-0074, EX-0075. OFF-00073 1ZMD00000073 TR-00073 E0086 PO-2022-0013 FA-000073 ITAM_control_matrix.png</t>
+          <t>I am standing on Return Overdue for MD-00073 (Remote - Former Employee, Low). EX-0074, EX-0075. OFF-00073. 1ZMD00000073. TR-00073. E0086. PO. PO-2022-0013. FA-000073. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -38365,7 +38386,7 @@
       </c>
       <c r="I146" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE came in on PO-2022-0013 ($700).</t>
+          <t>MD-00074 origin: PO-2022-0013, $700.</t>
         </is>
       </c>
     </row>
@@ -38412,7 +38433,7 @@
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00074. Receive date 2026-02-24.</t>
+          <t>Movement TR-00074 completed inbound 2026-02-24.</t>
         </is>
       </c>
     </row>
@@ -38455,7 +38476,7 @@
       </c>
       <c r="I148" s="7" t="inlineStr">
         <is>
-          <t>OFF-00074 — Past Due. Due 7/15.</t>
+          <t>OFF-00074 sits Past Due. Hardware return was required. Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -38541,7 +38562,7 @@
       </c>
       <c r="I150" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00074 on the 1Z print. 1ZMD00000074.</t>
+          <t>Printed 1ZMD00000074. Box not in the inbound file.</t>
         </is>
       </c>
     </row>
@@ -38576,7 +38597,7 @@
       </c>
       <c r="I151" s="7" t="inlineStr">
         <is>
-          <t>Don't Available MD-00074. 1ZMD00000074 serial fight.</t>
+          <t>1ZMD00000074: serial on the shipment is not MD-MO-050074. Custody not cleared.</t>
         </is>
       </c>
     </row>
@@ -38619,7 +38640,7 @@
       </c>
       <c r="I152" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb in regional_IT_notes.docx. Still need a transaction for MD-00074.</t>
+          <t>Technician notes scanned for MD-00074; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -38658,7 +38679,7 @@
       </c>
       <c r="I153" s="7" t="inlineStr">
         <is>
-          <t>When scoring MD-00074, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00074 was checked; ITAM_control_matrix.png attached.</t>
+          <t>Policy PDF + ITAM_control_matrix.png set the transfer bar for MD-00074. Compared that bar to TR-00074, PO-2022-0013, FA-000074, OFF-00074, APR-00074 before accepting any tech note.</t>
         </is>
       </c>
     </row>
@@ -38705,7 +38726,7 @@
       </c>
       <c r="I154" s="7" t="inlineStr">
         <is>
-          <t>Call: Return Overdue at Carrier Network / Unverified. Low. Exceptions EX-0076, EX-0077, EX-0078. 1ZMD00000074 OFF-00074 MISMATCH-0074 MD-MO-050074 PO-2022-0013 FA-000074 ITAM_control_matrix.png</t>
+          <t>Wrap-up MD-00074: Return Overdue (Low) — EX-0076, EX-0077, EX-0078. 1ZMD00000074. OFF-00074. PO. PO-2022-0013. FA-000074. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -38799,7 +38820,7 @@
       </c>
       <c r="I156" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00075 completed inbound Apr 1.</t>
+          <t>Assignment posted 03/31/2026. Docked 2026-04-01 (TR-00075).</t>
         </is>
       </c>
     </row>
@@ -38842,7 +38863,7 @@
       </c>
       <c r="I157" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00075 on MD-00075. Return required Yes.</t>
+          <t>MD-00075 tied to OFF-00075 (Past Due). SLA Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -38971,7 +38992,7 @@
       </c>
       <c r="I160" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00075. Notes don't beat a scan.</t>
+          <t>Technician notes scanned for MD-00075; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -39010,7 +39031,7 @@
       </c>
       <c r="I161" s="7" t="inlineStr">
         <is>
-          <t>Evidence rubric for MD-00075 pulled from the control matrix (disposal); chain anchor TR-00075; policy PDF §4–§7 read with TR-00075.</t>
+          <t>Auditors tracing MD-00075 should read matrix transfer, then TR-00075, PO-2022-0013, FA-000075, OFF-00075, APR-00075. Working site Remote - Former Employee; status call Return Overdue.</t>
         </is>
       </c>
     </row>
@@ -39057,7 +39078,7 @@
       </c>
       <c r="I162" s="7" t="inlineStr">
         <is>
-          <t>Call: Return Overdue at Remote - Former Employee. Low. Exceptions EX-0079, EX-0080. OFF-00075 1ZMD00000075 TR-00075 E0088 PO-2022-0013 FA-000075 ITAM_control_matrix.png</t>
+          <t>MD-00075 → Return Overdue. Confidence Low. EX-0079, EX-0080. OFF-00075. 1ZMD00000075. TR-00075. E0088. PO. PO-2022-0013. FA-000075. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39104,7 +39125,7 @@
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>$6470 Cisco C9300. PO-2022-0013.</t>
+          <t>PO line PO-2022-0013 — Cisco C9300.</t>
         </is>
       </c>
     </row>
@@ -39151,7 +39172,7 @@
       </c>
       <c r="I164" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee: TR-00076 received May 3, 2026.</t>
+          <t>Dock file shows 05/03/2026 for TR-00076 (MD-00076).</t>
         </is>
       </c>
     </row>
@@ -39194,7 +39215,7 @@
       </c>
       <c r="I165" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00076 on MD-00076. Return required Yes.</t>
+          <t>People ticket OFF-00076. Doesn't by itself dock MD-00076.</t>
         </is>
       </c>
     </row>
@@ -39280,7 +39301,7 @@
       </c>
       <c r="I167" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork only. 1ZMD00000076.</t>
+          <t>Printed 1ZMD00000076. Box not in the inbound file.</t>
         </is>
       </c>
     </row>
@@ -39358,7 +39379,7 @@
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>Didn't let the regional write-up overrule the logs on MD-00076.</t>
+          <t>Technician notes scanned for MD-00076; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39418,7 @@
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>Evidence rubric for MD-00076 pulled from the control matrix (disposal); chain anchor TR-00076; policy PDF §4–§7 read with TR-00076.</t>
+          <t>MD-00076: checked ITAM-001 return row while reviewing TR-00076, PO-2022-0013, FA-000076, OFF-00076, APR-00076. Cost basis $6470; confidence Low. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -39444,7 +39465,7 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Return Overdue. Low confidence. EX-0081, EX-0082, EX-0083. 1ZMD00000076 OFF-00076 MISMATCH-0076 MD-NE-050076 PO-2022-0013 FA-000076 ITAM_control_matrix.png</t>
+          <t>MD-00076 custody narrative ends Return Overdue (Low). EX-0081, EX-0082, EX-0083. 1ZMD00000076. OFF-00076. PO. PO-2022-0013. FA-000076. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39491,7 +39512,7 @@
       </c>
       <c r="I172" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2022-0013. MacBook Pro 14, $1850.</t>
+          <t>Procurement PO-2022-0013 lists MacBook Pro 14 / $1850.</t>
         </is>
       </c>
     </row>
@@ -39538,7 +39559,7 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 2026-06-05. Docked 2026-06-06 (TR-00077).</t>
+          <t>TR-00077 — got it 06/06/2026 at Remote - Former Employee.</t>
         </is>
       </c>
     </row>
@@ -39581,7 +39602,7 @@
       </c>
       <c r="I174" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00077. Status Past Due.</t>
+          <t>OFF-00077 Past Due. Return required=Yes, due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -39710,7 +39731,7 @@
       </c>
       <c r="I177" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx is in the packet. Weight = lead only (MD-00077).</t>
+          <t>Technician notes scanned for MD-00077; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -39749,7 +39770,7 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>MD-00077: ITAM-001 appendix defines acceptable return proof — see TR-00077 in this chain.</t>
+          <t>Policy PDF + ITAM_control_matrix.png set the transfer bar for MD-00077. Compared that bar to TR-00077, PO-2022-0013, FA-000077, OFF-00077, APR-00077 before accepting any tech note.</t>
         </is>
       </c>
     </row>
@@ -39796,7 +39817,7 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Return Overdue. Low confidence. EX-0084, EX-0085. OFF-00077 1ZMD00000077 TR-00077 E0090 PO-2022-0013 FA-000077 ITAM_control_matrix.png</t>
+          <t>Wrap-up MD-00077: Return Overdue (Low) — EX-0084, EX-0085. OFF-00077. 1ZMD00000077. TR-00077. E0090. PO. PO-2022-0013. FA-000077. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39890,7 +39911,7 @@
       </c>
       <c r="I181" s="7" t="inlineStr">
         <is>
-          <t>Moved to E0081 in Remote - Former Employee on TR-00078. Received 1/10/26.</t>
+          <t>Remote - Former Employee: TR-00078 received Jan 10, 2026.</t>
         </is>
       </c>
     </row>
@@ -39933,7 +39954,7 @@
       </c>
       <c r="I182" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00078. Status Past Due.</t>
+          <t>OFF-00078 — Past Due. Due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -40019,7 +40040,7 @@
       </c>
       <c r="I184" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000078 is Label Created. Serial on the label MD-MO-050078. Not proof of return.</t>
+          <t>§5: label ≠ returned. 1ZMD00000078 / MD-MO-050078.</t>
         </is>
       </c>
     </row>
@@ -40062,7 +40083,7 @@
       </c>
       <c r="I185" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00078 — non-authoritative.</t>
+          <t>Technician notes scanned for MD-00078; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -40101,7 +40122,7 @@
       </c>
       <c r="I186" s="7" t="inlineStr">
         <is>
-          <t>On MD-00078, the matrix documents what transfer evidence looks like; it is not a substitute for TR-00078.</t>
+          <t>Auditors tracing MD-00078 should read matrix transfer, then TR-00078, PO-2022-0013, FA-000078, OFF-00078, APR-00078. Working site Remote - Former Employee; status call Return Overdue.</t>
         </is>
       </c>
     </row>
@@ -40148,7 +40169,7 @@
       </c>
       <c r="I187" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Return Overdue. Low confidence. EX-0086, EX-0087. OFF-00078 1ZMD00000078 TR-00078 E0091 PO-2022-0013 FA-000078 ITAM_control_matrix.png</t>
+          <t>MD-00078 → Return Overdue. Confidence Low. EX-0086, EX-0087. OFF-00078. 1ZMD00000078. TR-00078. E0091. PO. PO-2022-0013. FA-000078. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -40195,7 +40216,7 @@
       </c>
       <c r="I188" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0014. Samsung Galaxy S24.</t>
+          <t>Bought the Samsung Galaxy S24 ($1040) on PO-2023-0014.</t>
         </is>
       </c>
     </row>
@@ -40242,7 +40263,7 @@
       </c>
       <c r="I189" s="7" t="inlineStr">
         <is>
-          <t>Recorded Feb 11, received 2026-02-13. TR-00079.</t>
+          <t>Dock file shows 2026-02-13 for TR-00079 (MD-00079).</t>
         </is>
       </c>
     </row>
@@ -40285,7 +40306,7 @@
       </c>
       <c r="I190" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00079. Status Past Due.</t>
+          <t>OFF-00079 Past Due. Return required=Yes, due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -40414,7 +40435,7 @@
       </c>
       <c r="I193" s="7" t="inlineStr">
         <is>
-          <t>Someone wrote that it stayed at a closed site. Unverified for MD-00079.</t>
+          <t>Technician notes scanned for MD-00079; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -40453,7 +40474,7 @@
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>For MD-00079, Appendix A sets the assignment evidence bar; TR-00079 is the record under review; ITAM_control_matrix.png attached.</t>
+          <t>ITAM_control_matrix.png consulted for MD-00079 (transfer). Conclusion still tied to TR-00079, PO-2023-0014, FA-000079, OFF-00079, APR-00079 at Remote - Former Employee, $1040.</t>
         </is>
       </c>
     </row>
@@ -40500,7 +40521,7 @@
       </c>
       <c r="I195" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Return Overdue. Low confidence. EX-0088, EX-0089. OFF-00079 1ZMD00000079 TR-00079 E0092 PO-2023-0014 FA-000079 ITAM_control_matrix.png</t>
+          <t>Final read MD-00079: Return Overdue @ Remote - Former Employee, confidence Low. EX-0088, EX-0089. OFF-00079. 1ZMD00000079. TR-00079. E0092. PO. PO-2023-0014. FA-000079. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -40547,7 +40568,7 @@
       </c>
       <c r="I196" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 came in on PO-2023-0014 ($6335).</t>
+          <t>Receiving against PO-2023-0014. Cisco C9300, $6335.</t>
         </is>
       </c>
     </row>
@@ -40594,7 +40615,7 @@
       </c>
       <c r="I197" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00080. Receive date 3/17.</t>
+          <t>Movement TR-00080 completed inbound 03/17/2026.</t>
         </is>
       </c>
     </row>
@@ -40723,7 +40744,7 @@
       </c>
       <c r="I200" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000080 is Label Created. Serial on the label MD-NE-050080. Not proof of return.</t>
+          <t>Label-only on MD-00080. 1ZMD00000080.</t>
         </is>
       </c>
     </row>
@@ -40770,7 +40791,7 @@
       </c>
       <c r="I201" s="7" t="inlineStr">
         <is>
-          <t>Acceptance event on 1ZMD00000080.</t>
+          <t>UPS/carrier take recorded for 1ZMD00000080.</t>
         </is>
       </c>
     </row>
@@ -40864,7 +40885,7 @@
       </c>
       <c r="I203" s="7" t="inlineStr">
         <is>
-          <t>Inbound scan completed (1ZMD00000080).</t>
+          <t>Dock scan on 1ZMD00000080.</t>
         </is>
       </c>
     </row>
@@ -40907,7 +40928,7 @@
       </c>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>I read the note. I didn't relocate MD-00080 off of it.</t>
+          <t>Investigative color on MD-00080 in regional_IT_notes.docx — weight zero.</t>
         </is>
       </c>
     </row>
@@ -40946,7 +40967,7 @@
       </c>
       <c r="I205" s="7" t="inlineStr">
         <is>
-          <t>Evidence rubric for MD-00080 pulled from the control matrix (disposal); chain anchor TR-00080; policy PDF §4–§7 read with TR-00080.</t>
+          <t>Matrix figure open for MD-00080 transfer path; transactional weight on TR-00080, PO-2023-0014, FA-000080, OFF-00080, APR-00080. Open exceptions EX-0090 still govern certification impact.</t>
         </is>
       </c>
     </row>
@@ -40993,7 +41014,7 @@
       </c>
       <c r="I206" s="7" t="inlineStr">
         <is>
-          <t>Available is the status I'm standing behind. EX-0090. High. 1ZMD00000080 OFF-00080 TR-00080 PO-2023-0014 FA-000080 ITAM_control_matrix.png</t>
+          <t>MD-00080 → Available. Confidence High. EX-0090. 1ZMD00000080. OFF-00080. TR-00080. PO. PO-2023-0014. FA-000080. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -41087,7 +41108,7 @@
       </c>
       <c r="I208" s="7" t="inlineStr">
         <is>
-          <t>TR-00081 — got it 2026-04-20 at Carrier Network.</t>
+          <t>Carrier Network: TR-00081 received Apr 20, 2026.</t>
         </is>
       </c>
     </row>
@@ -41130,7 +41151,7 @@
       </c>
       <c r="I209" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00081: Yes. Due 7/15/26.</t>
+          <t>OFF-00081 Shipment Open. Return required=Yes, due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -41216,7 +41237,7 @@
       </c>
       <c r="I211" s="7" t="inlineStr">
         <is>
-          <t>Printed 1ZMD00000081. Box not in the inbound file.</t>
+          <t>Prepaid label 1ZMD00000081 exists. Carrier never accepted it.</t>
         </is>
       </c>
     </row>
@@ -41263,7 +41284,7 @@
       </c>
       <c r="I212" s="7" t="inlineStr">
         <is>
-          <t>Carrier accepted 1ZMD00000081.</t>
+          <t>Acceptance event on 1ZMD00000081.</t>
         </is>
       </c>
     </row>
@@ -41357,7 +41378,7 @@
       </c>
       <c r="I214" s="7" t="inlineStr">
         <is>
-          <t>SCAN-86 equivalent on file for 1ZMD00000081.</t>
+          <t>Inbound scan completed (1ZMD00000081).</t>
         </is>
       </c>
     </row>
@@ -41400,7 +41421,7 @@
       </c>
       <c r="I215" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00081 — non-authoritative.</t>
+          <t>Regional write-up for MD-00081 is non-authoritative per ITAM-001.</t>
         </is>
       </c>
     </row>
@@ -41439,7 +41460,7 @@
       </c>
       <c r="I216" s="7" t="inlineStr">
         <is>
-          <t>MD-00081 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00081.</t>
+          <t>MD-00081: checked ITAM-001 financial row while reviewing TR-00081, PO-2023-0014, FA-000081, OFF-00081, APR-00081. Cost basis $2030; confidence High. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -41486,7 +41507,7 @@
       </c>
       <c r="I217" s="7" t="inlineStr">
         <is>
-          <t>MD-00081 → Available. Confidence High. EX-0091. 1ZMD00000081 OFF-00081 TR-00081 PO-2023-0014 FA-000081 ITAM_control_matrix.png</t>
+          <t>After the chain, MD-00081 is Available / Atlanta Warehouse (High). EX-0091. 1ZMD00000081. OFF-00081. TR-00081. PO. PO-2023-0014. FA-000081. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -41533,7 +41554,7 @@
       </c>
       <c r="I218" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0014. Dell U2723QE.</t>
+          <t>Acquired MD-00082 (Dell U2723QE) for $745 via PO-2023-0014.</t>
         </is>
       </c>
     </row>
@@ -41580,7 +41601,7 @@
       </c>
       <c r="I219" s="7" t="inlineStr">
         <is>
-          <t>Recorded 22 May, received May 24. TR-00082.</t>
+          <t>Assignment posted 05/22/2026. Docked 2026-05-24 (TR-00082).</t>
         </is>
       </c>
     </row>
@@ -41623,7 +41644,7 @@
       </c>
       <c r="I220" s="7" t="inlineStr">
         <is>
-          <t>OFF-00082 — Shipment Open. Due July 15, 2026.</t>
+          <t>OFF-00082 Shipment Open. Return required=Yes, due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -41709,7 +41730,7 @@
       </c>
       <c r="I222" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00082 on the 1Z print. 1ZMD00000082.</t>
+          <t>1ZMD00000082 is Label Created. Serial on the label MD-MO-050082. Not proof of return.</t>
         </is>
       </c>
     </row>
@@ -41756,7 +41777,7 @@
       </c>
       <c r="I223" s="7" t="inlineStr">
         <is>
-          <t>UPS/carrier take recorded for 1ZMD00000082.</t>
+          <t>Acceptance posted for 1ZMD00000082; not the same as dock receipt.</t>
         </is>
       </c>
     </row>
@@ -41791,7 +41812,7 @@
       </c>
       <c r="I224" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000082 / MISMATCH-0082 vs MD-MO-050082. Held.</t>
+          <t>1ZMD00000082: serial on the shipment is not MD-MO-050082. Custody not cleared.</t>
         </is>
       </c>
     </row>
@@ -41877,7 +41898,7 @@
       </c>
       <c r="I226" s="7" t="inlineStr">
         <is>
-          <t>Closed-floor story in the notes. Ignored as clearance. (MD-00082-Regional IT Note Lead-226)</t>
+          <t>Regional claim (Return package was delivered according to the technician, but the shipment serial does not) does not beat a scan for MD-00082.</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41937,7 @@
       </c>
       <c r="I227" s="7" t="inlineStr">
         <is>
-          <t>MD-00082: return controls in Appendix A; matrix noted alongside TR-00082; policy PDF §4–§7 read with TR-00082.</t>
+          <t>MD-00082 chain includes the figure as a disposal rubric (Low). Record set: TR-00082, PO-2023-0014, FA-000082, OFF-00082, APR-00082.</t>
         </is>
       </c>
     </row>
@@ -41963,7 +41984,7 @@
       </c>
       <c r="I228" s="7" t="inlineStr">
         <is>
-          <t>Verified In Transit - Exception. EX-0092, EX-0093. Low. 1ZMD00000082 OFF-00082 MISMATCH-0082 MD-MO-050082 receiving_exception_scan_1ZMD00000082.png PO-2023-0014 FA-000082 ITAM_control_matrix.png</t>
+          <t>Closing MD-00082: In Transit - Exception at Carrier Network / Unverified (Low). EX-0092, EX-0093. 1ZMD00000082. OFF-00082. 1ZMD00000082.png. PO. PO-2023-0014. FA-000082. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -42010,7 +42031,7 @@
       </c>
       <c r="I229" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 origin: PO-2023-0014, $1220.</t>
+          <t>Warehouse receipt tied to PO-2023-0014. Samsung Galaxy S24.</t>
         </is>
       </c>
     </row>
@@ -42057,7 +42078,7 @@
       </c>
       <c r="I230" s="7" t="inlineStr">
         <is>
-          <t>TR-00083 6/26; inbound 6/27/26.</t>
+          <t>Assignment posted Jun 26, 2026. Docked 06/27/2026 (TR-00083).</t>
         </is>
       </c>
     </row>
@@ -42186,7 +42207,7 @@
       </c>
       <c r="I233" s="7" t="inlineStr">
         <is>
-          <t>Prepaid label 1ZMD00000083 exists. Carrier never accepted it.</t>
+          <t>Return paperwork only. 1ZMD00000083.</t>
         </is>
       </c>
     </row>
@@ -42280,7 +42301,7 @@
       </c>
       <c r="I235" s="7" t="inlineStr">
         <is>
-          <t>Delivered — 1ZMD00000083. Still need a receiving scan to finish returns.</t>
+          <t>Parcel 1ZMD00000083 shows delivered; SCAN-86 still required for MD-00083.</t>
         </is>
       </c>
     </row>
@@ -42327,7 +42348,7 @@
       </c>
       <c r="I236" s="7" t="inlineStr">
         <is>
-          <t>Dock scan on 1ZMD00000083.</t>
+          <t>Receiving stamp on 1ZMD00000083 for MD-00083.</t>
         </is>
       </c>
     </row>
@@ -42370,7 +42391,7 @@
       </c>
       <c r="I237" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx is in the packet. Weight = lead only (MD-00083).</t>
+          <t>Technician comment volume in the doc does not clear MD-00083.</t>
         </is>
       </c>
     </row>
@@ -42409,7 +42430,7 @@
       </c>
       <c r="I238" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 chain includes the policy figure as the financial reconciliation rubric only; TR-00083 is dispositive.</t>
+          <t>Policy PDF + ITAM_control_matrix.png set the assignment bar for MD-00083. Compared that bar to TR-00083, PO-2023-0014, FA-000083, OFF-00083, APR-00083 before accepting any tech note.</t>
         </is>
       </c>
     </row>
@@ -42456,7 +42477,7 @@
       </c>
       <c r="I239" s="7" t="inlineStr">
         <is>
-          <t>Wrap: MD-00083 Available. EX-0094. 1ZMD00000083 OFF-00083 TR-00083 PO-2023-0014 FA-000083 ITAM_control_matrix.png</t>
+          <t>Verified Available for MD-00083 in Atlanta Warehouse. High. EX-0094. 1ZMD00000083. OFF-00083. TR-00083. PO. PO-2023-0014. FA-000083. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -42503,7 +42524,7 @@
       </c>
       <c r="I240" s="7" t="inlineStr">
         <is>
-          <t>PO-2023-0014: Cisco C9300 at $6200.</t>
+          <t>Bought the Cisco C9300 ($6200) on PO-2023-0014.</t>
         </is>
       </c>
     </row>
@@ -42550,7 +42571,7 @@
       </c>
       <c r="I241" s="7" t="inlineStr">
         <is>
-          <t>Moved to Return Carrier in Carrier Network on TR-00084. Received February 5, 2026.</t>
+          <t>Transfer TR-00084 / APR-00084. Received Feb 05, 2026.</t>
         </is>
       </c>
     </row>
@@ -42593,7 +42614,7 @@
       </c>
       <c r="I242" s="7" t="inlineStr">
         <is>
-          <t>OFF-00084 sits Shipment Open. Hardware return was required. 15 Jul.</t>
+          <t>Opened OFF-00084. Status Shipment Open.</t>
         </is>
       </c>
     </row>
@@ -42679,7 +42700,7 @@
       </c>
       <c r="I244" s="7" t="inlineStr">
         <is>
-          <t>§5: label ≠ returned. 1ZMD00000084 / MD-NE-050084.</t>
+          <t>I didn't close MD-00084 on the 1Z print. 1ZMD00000084.</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42747,7 @@
       </c>
       <c r="I245" s="7" t="inlineStr">
         <is>
-          <t>Acceptance event on 1ZMD00000084.</t>
+          <t>Carrier accepted 1ZMD00000084.</t>
         </is>
       </c>
     </row>
@@ -42761,7 +42782,7 @@
       </c>
       <c r="I246" s="7" t="inlineStr">
         <is>
-          <t>Carrier exception. Register serial MD-NE-050084 didn't show up on the parcel record.</t>
+          <t>Mismatch inbound. MD-00084 stays exception. 1ZMD00000084.</t>
         </is>
       </c>
     </row>
@@ -42804,7 +42825,7 @@
       </c>
       <c r="I247" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx is in the packet. Weight = lead only (MD-00084).</t>
+          <t>Word file read; MD-00084 waits on transactional evidence.</t>
         </is>
       </c>
     </row>
@@ -42843,7 +42864,7 @@
       </c>
       <c r="I248" s="7" t="inlineStr">
         <is>
-          <t>IT_asset_management_policy.pdf plus the matrix set the assignment standard for MD-00084; TR-00084 cited.</t>
+          <t>MD-00084: checked ITAM-001 disposal row while reviewing TR-00084, PO-2023-0014, FA-000084, OFF-00084, APR-00084. Cost basis $6200; confidence Low. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -42890,7 +42911,7 @@
       </c>
       <c r="I249" s="7" t="inlineStr">
         <is>
-          <t>MD-00084 → In Transit - Exception. Confidence Low. EX-0095, EX-0096. 1ZMD00000084 OFF-00084 MISMATCH-0084 MD-NE-050084 PO-2023-0014 FA-000084 ITAM_control_matrix.png</t>
+          <t>Final read MD-00084: In Transit - Exception @ Carrier Network / Unverified, confidence Low. EX-0095, EX-0096. 1ZMD00000084. OFF-00084. PO. PO-2023-0014. FA-000084. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -42937,7 +42958,7 @@
       </c>
       <c r="I250" s="7" t="inlineStr">
         <is>
-          <t>PO-2024-0015: Lenovo ThinkPad T14 at $1895.</t>
+          <t>Lenovo ThinkPad T14 came in on PO-2024-0015 ($1895).</t>
         </is>
       </c>
     </row>
@@ -42984,7 +43005,7 @@
       </c>
       <c r="I251" s="7" t="inlineStr">
         <is>
-          <t>Moved to Return Carrier in Carrier Network on TR-00085. Received 2/3/26.</t>
+          <t>TR-00085 Feb 02, 2026; inbound 02/03/2026.</t>
         </is>
       </c>
     </row>
@@ -43113,7 +43134,7 @@
       </c>
       <c r="I254" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00085 on the 1Z print. 1ZMD00000085.</t>
+          <t>§5: label ≠ returned. 1ZMD00000085 / MD-LA-050085.</t>
         </is>
       </c>
     </row>
@@ -43160,7 +43181,7 @@
       </c>
       <c r="I255" s="7" t="inlineStr">
         <is>
-          <t>UPS/carrier take recorded for 1ZMD00000085.</t>
+          <t>1ZMD00000085 picked up (acceptance on file).</t>
         </is>
       </c>
     </row>
@@ -43207,7 +43228,7 @@
       </c>
       <c r="I256" s="7" t="inlineStr">
         <is>
-          <t>Delivery posted on 1ZMD00000085.</t>
+          <t>1ZMD00000085 delivered per carrier.</t>
         </is>
       </c>
     </row>
@@ -43254,7 +43275,7 @@
       </c>
       <c r="I257" s="7" t="inlineStr">
         <is>
-          <t>Receiving scanned 1ZMD00000085.</t>
+          <t>Receiving stamp on 1ZMD00000085 for MD-00085.</t>
         </is>
       </c>
     </row>
@@ -43297,7 +43318,7 @@
       </c>
       <c r="I258" s="7" t="inlineStr">
         <is>
-          <t>Note exists. Corroboration doesn't. MD-00085.</t>
+          <t>Word dump checked for MD-00085; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -43336,7 +43357,7 @@
       </c>
       <c r="I259" s="7" t="inlineStr">
         <is>
-          <t>MD-00085: return gate from Appendix A; supporting transaction file TR-00085; ITAM_control_matrix.png attached.</t>
+          <t>MD-00085 / Lenovo ThinkPad T14: assignment evidence expectations from Appendix A. Anchored to TR-00085, PO-2024-0015, FA-000085, OFF-00085, APR-00085; acquisition $1895.</t>
         </is>
       </c>
     </row>
@@ -43383,7 +43404,7 @@
       </c>
       <c r="I260" s="7" t="inlineStr">
         <is>
-          <t>Verified Available. EX-0097, EX-0098. High. 1ZMD00000085 OFF-00085 TR-00085 PO-2024-0015 FA-000085 ITAM_control_matrix.png</t>
+          <t>Available is the status for MD-00085 at Atlanta Warehouse; High. EX-0097, EX-0098. 1ZMD00000085. OFF-00085. TR-00085. PO. PO-2024-0015. FA-000085. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -43430,7 +43451,7 @@
       </c>
       <c r="I261" s="7" t="inlineStr">
         <is>
-          <t>Bought the Dell U2723QE ($610) on PO-2024-0015.</t>
+          <t>PO-2024-0015 documents $610 for Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -43477,7 +43498,7 @@
       </c>
       <c r="I262" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00086 / APR-00086. Received March 8, 2026.</t>
+          <t>Dock file shows Mar 08, 2026 for TR-00086 (MD-00086).</t>
         </is>
       </c>
     </row>
@@ -43520,7 +43541,7 @@
       </c>
       <c r="I263" s="7" t="inlineStr">
         <is>
-          <t>MD-00086 tied to OFF-00086 (Shipment Open). SLA 15 Jul.</t>
+          <t>People ticket OFF-00086. Doesn't by itself dock MD-00086.</t>
         </is>
       </c>
     </row>
@@ -43606,7 +43627,7 @@
       </c>
       <c r="I265" s="7" t="inlineStr">
         <is>
-          <t>Prepaid label 1ZMD00000086 exists. Carrier never accepted it.</t>
+          <t>Printed 1ZMD00000086. Box not in the inbound file.</t>
         </is>
       </c>
     </row>
@@ -43653,7 +43674,7 @@
       </c>
       <c r="I266" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000086 picked up (acceptance on file).</t>
+          <t>Carrier accepted 1ZMD00000086.</t>
         </is>
       </c>
     </row>
@@ -43700,7 +43721,7 @@
       </c>
       <c r="I267" s="7" t="inlineStr">
         <is>
-          <t>Delivered — 1ZMD00000086. Still need a receiving scan to finish returns.</t>
+          <t>Delivery posted on 1ZMD00000086.</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43768,7 @@
       </c>
       <c r="I268" s="7" t="inlineStr">
         <is>
-          <t>Dock scan on 1ZMD00000086.</t>
+          <t>SCAN-86 equivalent on file for 1ZMD00000086.</t>
         </is>
       </c>
     </row>
@@ -43790,7 +43811,7 @@
       </c>
       <c r="I269" s="7" t="inlineStr">
         <is>
-          <t>Didn't let the regional write-up overrule the logs on MD-00086.</t>
+          <t>Regional file reviewed for MD-00086; no clearance language accepted.</t>
         </is>
       </c>
     </row>
@@ -43829,7 +43850,7 @@
       </c>
       <c r="I270" s="7" t="inlineStr">
         <is>
-          <t>Policy appendix applied to MD-00086 under financial reconciliation; figure informs the review, TR-00086 carries it.</t>
+          <t>Control matrix cited on MD-00086 for financial only. Movement/finance proof stays with TR-00086, PO-2024-0015, FA-000086, OFF-00086, APR-00086; exceptions EX-0099.</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43897,7 @@
       </c>
       <c r="I271" s="7" t="inlineStr">
         <is>
-          <t>Wrap: MD-00086 Available. EX-0099. 1ZMD00000086 OFF-00086 TR-00086 PO-2024-0015 FA-000086 ITAM_control_matrix.png</t>
+          <t>Chain end MD-00086: Available; High; EX-0099. 1ZMD00000086. OFF-00086. TR-00086. PO. PO-2024-0015. FA-000086. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -43923,7 +43944,7 @@
       </c>
       <c r="I272" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2024-0015. Samsung Galaxy S24, $1085.</t>
+          <t>Purchasing file PO-2024-0015 matches MD-00087 at $1085.</t>
         </is>
       </c>
     </row>
@@ -43970,7 +43991,7 @@
       </c>
       <c r="I273" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted Apr 12. Docked 2026-04-12 (TR-00087).</t>
+          <t>MD-00087 inbound 2026-04-12 on TR-00087 / APR-00087.</t>
         </is>
       </c>
     </row>
@@ -44013,7 +44034,7 @@
       </c>
       <c r="I274" s="7" t="inlineStr">
         <is>
-          <t>OFF-00087 sits Shipment Open. Hardware return was required. 7/15.</t>
+          <t>OFF-00087 sits Shipment Open. Hardware return was required. Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44120,7 @@
       </c>
       <c r="I276" s="7" t="inlineStr">
         <is>
-          <t>§5: label ≠ returned. 1ZMD00000087 / MD-MO-050087.</t>
+          <t>Label-only on MD-00087. 1ZMD00000087.</t>
         </is>
       </c>
     </row>
@@ -44146,7 +44167,7 @@
       </c>
       <c r="I277" s="7" t="inlineStr">
         <is>
-          <t>Acceptance event on 1ZMD00000087.</t>
+          <t>UPS/carrier take recorded for 1ZMD00000087.</t>
         </is>
       </c>
     </row>
@@ -44193,7 +44214,7 @@
       </c>
       <c r="I278" s="7" t="inlineStr">
         <is>
-          <t>Carrier delivery event, 1ZMD00000087.</t>
+          <t>Parcel 1ZMD00000087 shows delivered; SCAN-86 still required for MD-00087.</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44261,7 @@
       </c>
       <c r="I279" s="7" t="inlineStr">
         <is>
-          <t>Inbound scan completed (1ZMD00000087).</t>
+          <t>Dock scan on 1ZMD00000087.</t>
         </is>
       </c>
     </row>
@@ -44283,7 +44304,7 @@
       </c>
       <c r="I280" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00087. Notes don't beat a scan.</t>
+          <t>Could not tie MD-00087 to a verified RN entry in the notes.</t>
         </is>
       </c>
     </row>
@@ -44322,7 +44343,7 @@
       </c>
       <c r="I281" s="7" t="inlineStr">
         <is>
-          <t>Used ITAM_control_matrix.png while walking MD-00087 (transfer path); conclusion still tied to TR-00087; ITAM_control_matrix.png attached.</t>
+          <t>For MD-00087 (Samsung Galaxy S24), Appendix A return criteria were read against TR-00087, PO-2024-0015, FA-000087, OFF-00087, APR-00087. Verified status target Available at Atlanta Warehouse; matrix PNG is reference only.</t>
         </is>
       </c>
     </row>
@@ -44369,7 +44390,7 @@
       </c>
       <c r="I282" s="7" t="inlineStr">
         <is>
-          <t>Call: Available at Atlanta Warehouse. High. Exceptions EX-0100. 1ZMD00000087 OFF-00087 TR-00087 PO-2024-0015 FA-000087 ITAM_control_matrix.png</t>
+          <t>I am standing on Available for MD-00087 (Atlanta Warehouse, High). EX-0100. 1ZMD00000087. OFF-00087. TR-00087. PO. PO-2024-0015. FA-000087. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -44416,7 +44437,7 @@
       </c>
       <c r="I283" s="7" t="inlineStr">
         <is>
-          <t>$6380 Cisco C9300. PO-2024-0015.</t>
+          <t>Acquired MD-00088 (Cisco C9300) for $6380 via PO-2024-0015.</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44484,7 @@
       </c>
       <c r="I284" s="7" t="inlineStr">
         <is>
-          <t>Carrier Network: TR-00088 received 14 May.</t>
+          <t>Recorded May 13, 2026, received 05/14/2026. TR-00088.</t>
         </is>
       </c>
     </row>
@@ -44506,7 +44527,7 @@
       </c>
       <c r="I285" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00088 on MD-00088. Return required Yes.</t>
+          <t>Offboarding OFF-00088: Yes. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -44592,7 +44613,7 @@
       </c>
       <c r="I287" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork only. 1ZMD00000088.</t>
+          <t>Prepaid label 1ZMD00000088 exists. Carrier never accepted it.</t>
         </is>
       </c>
     </row>
@@ -44639,7 +44660,7 @@
       </c>
       <c r="I288" s="7" t="inlineStr">
         <is>
-          <t>Carrier accepted 1ZMD00000088.</t>
+          <t>Acceptance event on 1ZMD00000088.</t>
         </is>
       </c>
     </row>
@@ -44686,7 +44707,7 @@
       </c>
       <c r="I289" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000088 delivered per carrier.</t>
+          <t>Delivered — 1ZMD00000088. Still need a receiving scan to finish returns.</t>
         </is>
       </c>
     </row>
@@ -44733,7 +44754,7 @@
       </c>
       <c r="I290" s="7" t="inlineStr">
         <is>
-          <t>SCAN-86 equivalent on file for 1ZMD00000088.</t>
+          <t>Receiving stamp on 1ZMD00000088 for MD-00088.</t>
         </is>
       </c>
     </row>
@@ -44776,7 +44797,7 @@
       </c>
       <c r="I291" s="7" t="inlineStr">
         <is>
-          <t>Tech note in the Word dump. Treated as a lead for MD-00088, not location proof.</t>
+          <t>Looked for MD-00088 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
         </is>
       </c>
     </row>
@@ -44815,7 +44836,7 @@
       </c>
       <c r="I292" s="7" t="inlineStr">
         <is>
-          <t>For certification tracing on MD-00088, disposal criteria came from the matrix; source row TR-00088.</t>
+          <t>Control matrix cited on MD-00088 for assignment only. Movement/finance proof stays with TR-00088, PO-2024-0015, FA-000088, OFF-00088, APR-00088; exceptions EX-0101, EX-0102.</t>
         </is>
       </c>
     </row>
@@ -44862,7 +44883,7 @@
       </c>
       <c r="I293" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00088: Available / Atlanta Warehouse (Medium). EX-0101, EX-0102. 1ZMD00000088 OFF-00088 TR-00088 PO-2024-0015 FA-000088 ITAM_control_matrix.png</t>
+          <t>Final read MD-00088: Available @ Atlanta Warehouse, confidence Medium. EX-0101, EX-0102. 1ZMD00000088. OFF-00088. TR-00088. PO. PO-2024-0015. FA-000088. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -44909,7 +44930,7 @@
       </c>
       <c r="I294" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2024-0015 — MacBook Pro 14.</t>
+          <t>Warehouse receipt tied to PO-2024-0015. MacBook Pro 14.</t>
         </is>
       </c>
     </row>
@@ -44956,7 +44977,7 @@
       </c>
       <c r="I295" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Unverified. TR-00089, received 6/17.</t>
+          <t>TR-00089 — got it Jun 17, 2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -44999,7 +45020,7 @@
       </c>
       <c r="I296" s="7" t="inlineStr">
         <is>
-          <t>OFF-00089 Unresolved. Return required=Yes, due Jul 15.</t>
+          <t>OFF-00089 Unresolved. Return required=Yes, due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -45081,7 +45102,7 @@
       </c>
       <c r="I298" s="7" t="inlineStr">
         <is>
-          <t>Note exists. Corroboration doesn't. MD-00089.</t>
+          <t>regional_IT_notes.docx mentions During the Denver exit walkthrough, someone mentioned a locked cage on floor 3 might still — lead only for MD-00089.</t>
         </is>
       </c>
     </row>
@@ -45120,7 +45141,7 @@
       </c>
       <c r="I299" s="7" t="inlineStr">
         <is>
-          <t>Used ITAM_control_matrix.png while walking MD-00089 (transfer path); conclusion still tied to TR-00089; ITAM_control_matrix.png attached.</t>
+          <t>Unknown custody review for MD-00089 used the transfer column on the matrix. Source trail: TR-00089, PO-2024-0015, FA-000089, OFF-00089, APR-00089.</t>
         </is>
       </c>
     </row>
@@ -45155,7 +45176,7 @@
       </c>
       <c r="I300" s="7" t="inlineStr">
         <is>
-          <t>Still no receiving scan, disposal cert, or count that places MD-00089.</t>
+          <t>I won't invent a floor for MD-00089.</t>
         </is>
       </c>
     </row>
@@ -45202,7 +45223,7 @@
       </c>
       <c r="I301" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00089: Missing / Unknown (Low). EX-0103, EX-0104. OFF-00089 TR-00089 PO-2024-0015 FA-000089 ITAM_control_matrix.png</t>
+          <t>MD-00089 → Missing. Confidence Low. EX-0103, EX-0104. OFF-00089. TR-00089. PO. PO-2024-0015. FA-000089. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -45249,7 +45270,7 @@
       </c>
       <c r="I302" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2024-0015. Dell U2723QE, $790.</t>
+          <t>PO line PO-2024-0015 — Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -45296,7 +45317,7 @@
       </c>
       <c r="I303" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 22 Jan. Docked Jan 28 (TR-00090).</t>
+          <t>Transfer TR-00090 / APR-00090. Received 2026-01-28.</t>
         </is>
       </c>
     </row>
@@ -45339,7 +45360,7 @@
       </c>
       <c r="I304" s="7" t="inlineStr">
         <is>
-          <t>OFF-00090 Unresolved. Return required=Yes, due July 15, 2026.</t>
+          <t>OFF-00090 sits Unresolved. Hardware return was required. Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -45421,7 +45442,7 @@
       </c>
       <c r="I306" s="7" t="inlineStr">
         <is>
-          <t>Closed-floor story in the notes. Ignored as clearance. (MD-00090-Regional IT Note Lead-306)</t>
+          <t>Technician wrote about MD-00090 in regional_IT_notes.docx; treated as unverified.</t>
         </is>
       </c>
     </row>
@@ -45460,7 +45481,7 @@
       </c>
       <c r="I307" s="7" t="inlineStr">
         <is>
-          <t>Used ITAM_control_matrix.png while walking MD-00090 (transfer path); conclusion still tied to TR-00090; ITAM_control_matrix.png attached.</t>
+          <t>Unknown custody review for MD-00090 used the disposal column on the matrix. Source trail: TR-00090, PO-2024-0015, FA-000090, OFF-00090, APR-00090.</t>
         </is>
       </c>
     </row>
@@ -45495,7 +45516,7 @@
       </c>
       <c r="I308" s="7" t="inlineStr">
         <is>
-          <t>Gap: nothing physical confirms MD-00090 right now.</t>
+          <t>I won't invent a floor for MD-00090.</t>
         </is>
       </c>
     </row>
@@ -45542,7 +45563,7 @@
       </c>
       <c r="I309" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00090: Missing / Unknown (Low). EX-0105, EX-0106. OFF-00090 TR-00090 PO-2024-0015 FA-000090 ITAM_control_matrix.png</t>
+          <t>Outcome MD-00090 — Missing, site Unknown, Low. EX-0105, EX-0106. OFF-00090. TR-00090. PO. PO-2024-0015. FA-000090. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -45589,7 +45610,7 @@
       </c>
       <c r="I310" s="7" t="inlineStr">
         <is>
-          <t>PO-2025-0016: Samsung Galaxy S24 at $950.</t>
+          <t>Purchasing file PO-2025-0016 matches MD-00091 at $950.</t>
         </is>
       </c>
     </row>
@@ -45636,7 +45657,7 @@
       </c>
       <c r="I311" s="7" t="inlineStr">
         <is>
-          <t>Moved to Unverified in Unknown on TR-00091. Received February 24, 2026.</t>
+          <t>MD-00091 inbound 02/24/2026 on TR-00091 / APR-00091.</t>
         </is>
       </c>
     </row>
@@ -45679,7 +45700,7 @@
       </c>
       <c r="I312" s="7" t="inlineStr">
         <is>
-          <t>OFF-00091 Unresolved. Return required=Yes, due 15 Jul.</t>
+          <t>Opened OFF-00091. Status Unresolved.</t>
         </is>
       </c>
     </row>
@@ -45761,7 +45782,7 @@
       </c>
       <c r="I314" s="7" t="inlineStr">
         <is>
-          <t>I read the note. I didn't relocate MD-00091 off of it.</t>
+          <t>Technician wrote about MD-00091 in regional_IT_notes.docx; treated as unverified.</t>
         </is>
       </c>
     </row>
@@ -45800,7 +45821,7 @@
       </c>
       <c r="I315" s="7" t="inlineStr">
         <is>
-          <t>MD-00091 custody review used the appendix matrix on assignment; TR-00091 remains the auditable source; policy PDF §4–§7 read with TR-00091.</t>
+          <t>Control matrix cited on MD-00091 for disposal only. Movement/finance proof stays with TR-00091, PO-2025-0016, FA-000091, OFF-00091, APR-00091; exceptions EX-0107, EX-0108.</t>
         </is>
       </c>
     </row>
@@ -45882,7 +45903,7 @@
       </c>
       <c r="I317" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00091: Missing / Unknown (Low). EX-0107, EX-0108. OFF-00091 TR-00091 PO-2025-0016 FA-000091 ITAM_control_matrix.png</t>
+          <t>Final read MD-00091: Missing @ Unknown, confidence Low. EX-0107, EX-0108. OFF-00091. TR-00091. PO. PO-2025-0016. FA-000091. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -45929,7 +45950,7 @@
       </c>
       <c r="I318" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2025-0016. Cisco C9300.</t>
+          <t>Procurement PO-2025-0016 lists Cisco C9300 / $6245.</t>
         </is>
       </c>
     </row>
@@ -45976,7 +45997,7 @@
       </c>
       <c r="I319" s="7" t="inlineStr">
         <is>
-          <t>Recorded 3/28/26, received 28 Mar. TR-00092.</t>
+          <t>From warehouse to Unverified. TR-00092, received Mar 28, 2026.</t>
         </is>
       </c>
     </row>
@@ -46019,7 +46040,7 @@
       </c>
       <c r="I320" s="7" t="inlineStr">
         <is>
-          <t>OFF-00092 Unresolved. Return required=Yes, due 2026-07-15.</t>
+          <t>OFF-00092 sits Unresolved. Hardware return was required. 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -46101,7 +46122,7 @@
       </c>
       <c r="I322" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb in regional_IT_notes.docx. Still need a transaction for MD-00092.</t>
+          <t>Technician wrote about MD-00092 in regional_IT_notes.docx; treated as unverified.</t>
         </is>
       </c>
     </row>
@@ -46140,7 +46161,7 @@
       </c>
       <c r="I323" s="7" t="inlineStr">
         <is>
-          <t>Policy appendix applied to MD-00092 under financial reconciliation; figure informs the review, TR-00092 carries it.</t>
+          <t>For MD-00092 (Cisco C9300), Appendix A disposal criteria were read against TR-00092, PO-2025-0016, FA-000092, OFF-00092, APR-00092. Verified status target Missing at Unknown; matrix PNG is reference only.</t>
         </is>
       </c>
     </row>
@@ -46175,7 +46196,7 @@
       </c>
       <c r="I324" s="7" t="inlineStr">
         <is>
-          <t>Still no receiving scan, disposal cert, or count that places MD-00092.</t>
+          <t>I won't invent a floor for MD-00092.</t>
         </is>
       </c>
     </row>
@@ -46222,7 +46243,7 @@
       </c>
       <c r="I325" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00092: Missing / Unknown (Low). EX-0109, EX-0110, EX-0111. OFF-00092 TR-00092 PO-2025-0016 FA-000092 ITAM_control_matrix.png</t>
+          <t>Chain end MD-00092: Missing; Low; EX-0109, EX-0110, EX-0111. OFF-00092. TR-00092. PO. PO-2025-0016. FA-000092. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46269,7 +46290,7 @@
       </c>
       <c r="I326" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 came in on PO-2025-0016 ($1940).</t>
+          <t>PO-2025-0016: Dell Latitude 7440 at $1940.</t>
         </is>
       </c>
     </row>
@@ -46316,7 +46337,7 @@
       </c>
       <c r="I327" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00093. Receive date 2026-05-06.</t>
+          <t>Moved to Unverified in Unknown on TR-00093. Received 2026-05-06.</t>
         </is>
       </c>
     </row>
@@ -46359,7 +46380,7 @@
       </c>
       <c r="I328" s="7" t="inlineStr">
         <is>
-          <t>OFF-00093 Unresolved. Return required=Yes, due 7/15/26.</t>
+          <t>Service desk OFF-00093 on MD-00093. Return required Yes.</t>
         </is>
       </c>
     </row>
@@ -46441,7 +46462,7 @@
       </c>
       <c r="I330" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00093. Notes don't beat a scan.</t>
+          <t>Technician wrote about MD-00093 in regional_IT_notes.docx; treated as unverified.</t>
         </is>
       </c>
     </row>
@@ -46480,7 +46501,7 @@
       </c>
       <c r="I331" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure cited on MD-00093 as the control standard for disposal; transactional weight stays with TR-00093.</t>
+          <t>Unknown custody review for MD-00093 used the disposal column on the matrix. Source trail: TR-00093, PO-2025-0016, FA-000093, OFF-00093, APR-00093.</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46536,7 @@
       </c>
       <c r="I332" s="7" t="inlineStr">
         <is>
-          <t>Gap: nothing physical confirms MD-00093 right now.</t>
+          <t>I won't invent a floor for MD-00093.</t>
         </is>
       </c>
     </row>
@@ -46562,7 +46583,7 @@
       </c>
       <c r="I333" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00093: Missing / Unknown (Low). EX-0112, EX-0113. OFF-00093 TR-00093 PO-2025-0016 FA-000093 ITAM_control_matrix.png</t>
+          <t>Wrap-up MD-00093: Missing (Low) — EX-0112, EX-0113. OFF-00093. TR-00093. PO. PO-2025-0016. FA-000093. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46609,7 +46630,7 @@
       </c>
       <c r="I334" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2025-0016 — Dell U2723QE.</t>
+          <t>Dell U2723QE came in on PO-2025-0016 ($655).</t>
         </is>
       </c>
     </row>
@@ -46656,7 +46677,7 @@
       </c>
       <c r="I335" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Unverified. TR-00094, received 6/4/26.</t>
+          <t>Recorded Jun 03, 2026, received 06/04/2026. TR-00094.</t>
         </is>
       </c>
     </row>
@@ -46699,7 +46720,7 @@
       </c>
       <c r="I336" s="7" t="inlineStr">
         <is>
-          <t>OFF-00094 Unresolved. Return required=Yes, due 2026-07-15.</t>
+          <t>Offboarding OFF-00094: Yes. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -46781,7 +46802,7 @@
       </c>
       <c r="I338" s="7" t="inlineStr">
         <is>
-          <t>Note exists. Corroboration doesn't. MD-00094.</t>
+          <t>Word-file breadcrumb on MD-00094: "IT float pool chat referenced this asset as 'still at closed site.' Chat is not an approva" — not authoritative.</t>
         </is>
       </c>
     </row>
@@ -46820,7 +46841,7 @@
       </c>
       <c r="I339" s="7" t="inlineStr">
         <is>
-          <t>MD-00094: return gate from Appendix A; supporting transaction file TR-00094; ITAM_control_matrix.png attached.</t>
+          <t>MD-00094 / Dell U2723QE: return evidence expectations from Appendix A. Anchored to TR-00094, PO-2025-0016, FA-000094, OFF-00094, APR-00094; acquisition $655.</t>
         </is>
       </c>
     </row>
@@ -46902,7 +46923,7 @@
       </c>
       <c r="I341" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00094: Missing / Unknown (Low). EX-0114, EX-0115. OFF-00094 TR-00094 PO-2025-0016 FA-000094 ITAM_control_matrix.png</t>
+          <t>Call on MD-00094: Missing, Low. EX-0114, EX-0115. OFF-00094. TR-00094. PO. PO-2025-0016. FA-000094. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46949,7 +46970,7 @@
       </c>
       <c r="I342" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2025-0016. Samsung Galaxy S24, $1130.</t>
+          <t>Procurement PO-2025-0016 lists Samsung Galaxy S24 / $1130.</t>
         </is>
       </c>
     </row>
@@ -46996,7 +47017,7 @@
       </c>
       <c r="I343" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted Jul 8. Docked 2026-07-08 (TR-00095).</t>
+          <t>From warehouse to Unverified. TR-00095, received Jul 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -47039,7 +47060,7 @@
       </c>
       <c r="I344" s="7" t="inlineStr">
         <is>
-          <t>OFF-00095 Unresolved. Return required=Yes, due 7/15.</t>
+          <t>Service desk OFF-00095 on MD-00095. Return required Yes.</t>
         </is>
       </c>
     </row>
@@ -47121,7 +47142,7 @@
       </c>
       <c r="I346" s="7" t="inlineStr">
         <is>
-          <t>Closed-floor story in the notes. Ignored as clearance. (MD-00095-Regional IT Note Lead-346)</t>
+          <t>Word-file breadcrumb on MD-00095: "Vendor teardown crew said they saw a similar model on a pallet marked scrap hold. Asset ta" — not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47160,7 +47181,7 @@
       </c>
       <c r="I347" s="7" t="inlineStr">
         <is>
-          <t>Policy matrix (transfer row) applied while tracing MD-00095; the figure does not replace TR-00095; policy PDF §4–§7 read with TR-00095.</t>
+          <t>MD-00095 chain includes the figure as a return rubric (Low). Record set: TR-00095, PO-2025-0016, FA-000095, OFF-00095, APR-00095.</t>
         </is>
       </c>
     </row>
@@ -47195,7 +47216,7 @@
       </c>
       <c r="I348" s="7" t="inlineStr">
         <is>
-          <t>Still no receiving scan, disposal cert, or count that places MD-00095.</t>
+          <t>Unresolved. MD-00095 isn't in inbound or the cert file.</t>
         </is>
       </c>
     </row>
@@ -47242,7 +47263,7 @@
       </c>
       <c r="I349" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00095: Missing / Unknown (Low). EX-0116, EX-0117. OFF-00095 TR-00095 PO-2025-0016 FA-000095 ITAM_control_matrix.png</t>
+          <t>Closing MD-00095: Missing at Unknown (Low). EX-0116, EX-0117. OFF-00095. TR-00095. PO. PO-2025-0016. FA-000095. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -47336,7 +47357,7 @@
       </c>
       <c r="I351" s="7" t="inlineStr">
         <is>
-          <t>Moved to Unverified in Unknown on TR-00096. Received 1/19.</t>
+          <t>Moved to Unverified in Unknown on TR-00096. Received 2026-01-19.</t>
         </is>
       </c>
     </row>
@@ -47379,7 +47400,7 @@
       </c>
       <c r="I352" s="7" t="inlineStr">
         <is>
-          <t>OFF-00096 Unresolved. Return required=Yes, due Jul 15.</t>
+          <t>Offboarding OFF-00096: Yes. Due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -47461,7 +47482,7 @@
       </c>
       <c r="I354" s="7" t="inlineStr">
         <is>
-          <t>I read the note. I didn't relocate MD-00096 off of it.</t>
+          <t>Word-file breadcrumb on MD-00096: "Helpdesk comment claims the user dropped it with building security before last day. Securi" — not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47500,7 +47521,7 @@
       </c>
       <c r="I355" s="7" t="inlineStr">
         <is>
-          <t>IT_asset_management_policy.pdf plus the matrix set the assignment standard for MD-00096; TR-00096 cited.</t>
+          <t>Matrix figure open for MD-00096 return path; transactional weight on TR-00096, PO-2025-0016, FA-000096, OFF-00096, APR-00096. Open exceptions EX-0118, EX-0119 still govern certification impact.</t>
         </is>
       </c>
     </row>
@@ -47535,7 +47556,7 @@
       </c>
       <c r="I356" s="7" t="inlineStr">
         <is>
-          <t>Gap: nothing physical confirms MD-00096 right now.</t>
+          <t>Unresolved. MD-00096 isn't in inbound or the cert file.</t>
         </is>
       </c>
     </row>
@@ -47582,7 +47603,7 @@
       </c>
       <c r="I357" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00096: Missing / Unknown (Low). EX-0118, EX-0119. OFF-00096 TR-00096 PO-2025-0016 FA-000096 ITAM_control_matrix.png</t>
+          <t>MD-00096 custody narrative ends Missing (Low). EX-0118, EX-0119. OFF-00096. TR-00096. PO. PO-2025-0016. FA-000096. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -47629,7 +47650,7 @@
       </c>
       <c r="I358" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2022-0017. Lenovo ThinkPad T14.</t>
+          <t>Ordered Lenovo ThinkPad T14 (MD-00097) on PO-2022-0017; $2120.</t>
         </is>
       </c>
     </row>
@@ -47676,7 +47697,7 @@
       </c>
       <c r="I359" s="7" t="inlineStr">
         <is>
-          <t>Recorded 21 Jan, received Jan 27. TR-00097.</t>
+          <t>TR-00097 — got it 01/27/2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -47719,7 +47740,7 @@
       </c>
       <c r="I360" s="7" t="inlineStr">
         <is>
-          <t>OFF-00097 Unresolved. Return required=Yes, due July 15, 2026.</t>
+          <t>Service desk OFF-00097 on MD-00097. Return required Yes.</t>
         </is>
       </c>
     </row>
@@ -47801,7 +47822,7 @@
       </c>
       <c r="I362" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb in regional_IT_notes.docx. Still need a transaction for MD-00097.</t>
+          <t>Word-file breadcrumb on MD-00097: "Regional spare inventory spreadsheet (offline) listed a placeholder row for this tag with " — not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47840,7 +47861,7 @@
       </c>
       <c r="I363" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 chain includes the policy figure as the financial reconciliation rubric only; TR-00097 is dispositive.</t>
+          <t>Matrix figure open for MD-00097 return path; transactional weight on TR-00097, PO-2022-0017, FA-000097, OFF-00097, APR-00097. Open exceptions EX-0120, EX-0121 still govern certification impact.</t>
         </is>
       </c>
     </row>
@@ -47875,7 +47896,7 @@
       </c>
       <c r="I364" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00097.</t>
+          <t>Unresolved. MD-00097 isn't in inbound or the cert file.</t>
         </is>
       </c>
     </row>
@@ -47922,7 +47943,7 @@
       </c>
       <c r="I365" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00097: Missing / Unknown (Low). EX-0120, EX-0121. OFF-00097 TR-00097 PO-2022-0017 FA-000097 ITAM_control_matrix.png</t>
+          <t>I am standing on Missing for MD-00097 (Unknown, Low). EX-0120, EX-0121. OFF-00097. TR-00097. PO. PO-2022-0017. FA-000097. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -47969,7 +47990,7 @@
       </c>
       <c r="I366" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE came in on PO-2022-0017 ($520).</t>
+          <t>Receiving against PO-2022-0017. Dell U2723QE, $520.</t>
         </is>
       </c>
     </row>
@@ -48016,7 +48037,7 @@
       </c>
       <c r="I367" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00098. Receive date February 24, 2026.</t>
+          <t>Unknown: TR-00098 received Feb 24, 2026.</t>
         </is>
       </c>
     </row>
@@ -48059,7 +48080,7 @@
       </c>
       <c r="I368" s="7" t="inlineStr">
         <is>
-          <t>OFF-00098 Unresolved. Return required=Yes, due 15 Jul.</t>
+          <t>OFF-00098 Unresolved. Return required=Yes, due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -48141,7 +48162,7 @@
       </c>
       <c r="I370" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00098. Notes don't beat a scan.</t>
+          <t>Word-file breadcrumb on MD-00098: "Move captain's email guessed the device rode with furniture to storage. Furniture BOL does" — not authoritative.</t>
         </is>
       </c>
     </row>
@@ -48180,7 +48201,7 @@
       </c>
       <c r="I371" s="7" t="inlineStr">
         <is>
-          <t>MD-00098 — auditors should read the disposal line on the matrix, then follow TR-00098; ITAM_control_matrix.png attached.</t>
+          <t>MD-00098 / Dell U2723QE: return evidence expectations from Appendix A. Anchored to TR-00098, PO-2022-0017, FA-000098, OFF-00098, APR-00098; acquisition $520.</t>
         </is>
       </c>
     </row>
@@ -48215,7 +48236,7 @@
       </c>
       <c r="I372" s="7" t="inlineStr">
         <is>
-          <t>Still no receiving scan, disposal cert, or count that places MD-00098.</t>
+          <t>Unresolved. MD-00098 isn't in inbound or the cert file.</t>
         </is>
       </c>
     </row>
@@ -48262,7 +48283,7 @@
       </c>
       <c r="I373" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00098: Missing / Unknown (Low). EX-0122, EX-0123. OFF-00098 TR-00098 PO-2022-0017 FA-000098 ITAM_control_matrix.png</t>
+          <t>Missing is the status for MD-00098 at Unknown; Low. EX-0122, EX-0123. OFF-00098. TR-00098. PO. PO-2022-0017. FA-000098. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -48309,7 +48330,7 @@
       </c>
       <c r="I374" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2022-0017 — Samsung Galaxy S24.</t>
+          <t>Warehouse receipt tied to PO-2022-0017. Samsung Galaxy S24.</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48377,7 @@
       </c>
       <c r="I375" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Unverified. TR-00099, received 2 Apr.</t>
+          <t>TR-00099 03/31/2026; inbound 2026-04-02.</t>
         </is>
       </c>
     </row>
@@ -48399,7 +48420,7 @@
       </c>
       <c r="I376" s="7" t="inlineStr">
         <is>
-          <t>OFF-00099 Unresolved. Return required=Yes, due 2026-07-15.</t>
+          <t>OFF-00099 — Unresolved. Due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -48481,7 +48502,7 @@
       </c>
       <c r="I378" s="7" t="inlineStr">
         <is>
-          <t>Note exists. Corroboration doesn't. MD-00099.</t>
+          <t>regional_IT_notes.docx mentions An intern's handwritten punch list includes this tag under 'find later.' No follow-up work — lead only for MD-00099.</t>
         </is>
       </c>
     </row>
@@ -48520,7 +48541,7 @@
       </c>
       <c r="I379" s="7" t="inlineStr">
         <is>
-          <t>MD-00099: return controls in Appendix A; matrix noted alongside TR-00099; policy PDF §4–§7 read with TR-00099.</t>
+          <t>Control matrix cited on MD-00099 for transfer only. Movement/finance proof stays with TR-00099, PO-2022-0017, FA-000099, OFF-00099, APR-00099; exceptions EX-0124, EX-0125.</t>
         </is>
       </c>
     </row>
@@ -48555,7 +48576,7 @@
       </c>
       <c r="I380" s="7" t="inlineStr">
         <is>
-          <t>Gap: nothing physical confirms MD-00099 right now.</t>
+          <t>Unresolved. MD-00099 isn't in inbound or the cert file.</t>
         </is>
       </c>
     </row>
@@ -48602,7 +48623,7 @@
       </c>
       <c r="I381" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00099: Missing / Unknown (Low). EX-0124, EX-0125. OFF-00099 TR-00099 PO-2022-0017 FA-000099 ITAM_control_matrix.png</t>
+          <t>Verified Missing for MD-00099 in Unknown. Low. EX-0124, EX-0125. OFF-00099. TR-00099. PO. PO-2022-0017. FA-000099. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -48649,7 +48670,7 @@
       </c>
       <c r="I382" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2022-0017. Cisco C9300, $6290.</t>
+          <t>Capital buy MD-00100: Cisco C9300, $6290, PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48717,7 @@
       </c>
       <c r="I383" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 2026-05-01. Docked 2026-05-05 (TR-00100).</t>
+          <t>TR-00100 — got it 05/05/2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -48739,7 +48760,7 @@
       </c>
       <c r="I384" s="7" t="inlineStr">
         <is>
-          <t>OFF-00100 Unresolved. Return required=Yes, due 7/15/26.</t>
+          <t>OFF-00100 — Unresolved. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -48821,7 +48842,7 @@
       </c>
       <c r="I386" s="7" t="inlineStr">
         <is>
-          <t>Closed-floor story in the notes. Ignored as clearance. (MD-00100-Regional IT Note Lead-386)</t>
+          <t>Technician wrote about MD-00100 in regional_IT_notes.docx; treated as unverified.</t>
         </is>
       </c>
     </row>
@@ -48860,7 +48881,7 @@
       </c>
       <c r="I387" s="7" t="inlineStr">
         <is>
-          <t>MD-00100 — auditors should read the disposal line on the matrix, then follow TR-00100; ITAM_control_matrix.png attached.</t>
+          <t>MD-00100 / Cisco C9300: disposal evidence expectations from Appendix A. Anchored to TR-00100, PO-2022-0017, FA-000100, OFF-00100, APR-00100; acquisition $6290.</t>
         </is>
       </c>
     </row>
@@ -48942,7 +48963,7 @@
       </c>
       <c r="I389" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00100: Missing / Unknown (Low). EX-0126, EX-0127. OFF-00100 TR-00100 PO-2022-0017 FA-000100 ITAM_control_matrix.png</t>
+          <t>MD-00100 → Missing. Confidence Low. EX-0126, EX-0127. OFF-00100. TR-00100. PO. PO-2022-0017. FA-000100. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -48989,7 +49010,7 @@
       </c>
       <c r="I390" s="7" t="inlineStr">
         <is>
-          <t>PO-2022-0017: MacBook Pro 14 at $1985.</t>
+          <t>Acquired MD-00101 (MacBook Pro 14) for $1985 via PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49057,7 @@
       </c>
       <c r="I391" s="7" t="inlineStr">
         <is>
-          <t>Moved to Regional IT in Seattle on TR-00101. Received 6/7/26.</t>
+          <t>Seattle: TR-00101 received Jun 07, 2026.</t>
         </is>
       </c>
     </row>
@@ -49079,7 +49100,7 @@
       </c>
       <c r="I392" s="7" t="inlineStr">
         <is>
-          <t>RET-00101 Pending Disposal. Return required=No.</t>
+          <t>RET-00101 sits Pending Disposal. Hardware return not required per ticket.</t>
         </is>
       </c>
     </row>
@@ -49161,7 +49182,7 @@
       </c>
       <c r="I394" s="7" t="inlineStr">
         <is>
-          <t>I read the note. I didn't relocate MD-00101 off of it.</t>
+          <t>Word dump checked for MD-00101; no authoritative note found.</t>
         </is>
       </c>
     </row>
@@ -49200,7 +49221,7 @@
       </c>
       <c r="I395" s="7" t="inlineStr">
         <is>
-          <t>MD-00101: return controls in Appendix A; matrix noted alongside TR-00101; policy PDF §4–§7 read with TR-00101.</t>
+          <t>MD-00101 chain includes the figure as a transfer rubric (Medium). Record set: TR-00101, PO-2022-0017, FA-000101, RET-00101, APR-00101.</t>
         </is>
       </c>
     </row>
@@ -49247,7 +49268,7 @@
       </c>
       <c r="I396" s="7" t="inlineStr">
         <is>
-          <t>Verified Retired/Pending Disposal. EX-0128, EX-0129. Medium. RET-00101 TR-00101 PO-2022-0017 FA-000101 ITAM_control_matrix.png</t>
+          <t>I am standing on Retired/Pending Disposal for MD-00101 (Seattle, Medium). EX-0128, EX-0129. RET-00101. TR-00101. PO. PO-2022-0017. FA-000101. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -49294,7 +49315,7 @@
       </c>
       <c r="I397" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2022-0017 matches MD-00102 at $700.</t>
+          <t>Receiving against PO-2022-0017. Dell U2723QE, $700.</t>
         </is>
       </c>
     </row>
@@ -49341,7 +49362,7 @@
       </c>
       <c r="I398" s="7" t="inlineStr">
         <is>
-          <t>TR-00102 — got it 1/11/26 at Atlanta.</t>
+          <t>MD-00102 inbound 01/11/2026 on TR-00102 / APR-00102.</t>
         </is>
       </c>
     </row>
@@ -49384,7 +49405,7 @@
       </c>
       <c r="I399" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 tied to RET-00102 (Pending Disposal).</t>
+          <t>RET-00102 — Pending Disposal. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -49466,7 +49487,7 @@
       </c>
       <c r="I401" s="7" t="inlineStr">
         <is>
-          <t>Tech note in the Word dump. Treated as a lead for MD-00102, not location proof.</t>
+          <t>Looked for MD-00102 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
         </is>
       </c>
     </row>
@@ -49505,7 +49526,7 @@
       </c>
       <c r="I402" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 review — matrix row assignment sets proof expectations; ledger/transfer cite TR-00102.</t>
+          <t>Atlanta custody review for MD-00102 used the transfer column on the matrix. Source trail: TR-00102, PO-2022-0017, FA-000102, RET-00102, APR-00102.</t>
         </is>
       </c>
     </row>
@@ -49552,7 +49573,7 @@
       </c>
       <c r="I403" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Retired/Pending Disposal. Medium confidence. EX-0130, EX-0131, EX-0132. RET-00102 TR-00102 PO-2022-0017 FA-000102 ITAM_control_matrix.png</t>
+          <t>After the chain, MD-00102 is Retired/Pending Disposal / Atlanta (Medium). EX-0130, EX-0131, EX-0132. RET-00102. TR-00102. PO. PO-2022-0017. FA-000102. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -49599,7 +49620,7 @@
       </c>
       <c r="I404" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2023-0018 — Samsung Galaxy S24.</t>
+          <t>Acquired MD-00103 (Samsung Galaxy S24) for $1175 via PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -49646,7 +49667,7 @@
       </c>
       <c r="I405" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Regional IT. TR-00103, received 2/14/26.</t>
+          <t>Chicago: TR-00103 received 2026-02-14.</t>
         </is>
       </c>
     </row>
@@ -49689,7 +49710,7 @@
       </c>
       <c r="I406" s="7" t="inlineStr">
         <is>
-          <t>Opened RET-00103. Status Pending Disposal.</t>
+          <t>RET-00103 sits Pending Disposal. Hardware return not required per ticket.</t>
         </is>
       </c>
     </row>
@@ -49771,7 +49792,7 @@
       </c>
       <c r="I408" s="7" t="inlineStr">
         <is>
-          <t>Note exists. Corroboration doesn't. MD-00103.</t>
+          <t>Technician prose on MD-00103 stays out of the custody conclusion.</t>
         </is>
       </c>
     </row>
@@ -49810,7 +49831,7 @@
       </c>
       <c r="I409" s="7" t="inlineStr">
         <is>
-          <t>Evidence rubric for MD-00103 pulled from the control matrix (disposal); chain anchor TR-00103; policy PDF §4–§7 read with TR-00103.</t>
+          <t>MD-00103 chain includes the figure as a financial rubric (Medium). Record set: TR-00103, PO-2023-0018, FA-000103, RET-00103, APR-00103.</t>
         </is>
       </c>
     </row>
@@ -49857,7 +49878,7 @@
       </c>
       <c r="I410" s="7" t="inlineStr">
         <is>
-          <t>Call: Retired/Pending Disposal at Chicago. Medium. Exceptions EX-0133, EX-0134. RET-00103 TR-00103 PO-2023-0018 FA-000103 ITAM_control_matrix.png</t>
+          <t>Final read MD-00103: Retired/Pending Disposal @ Chicago, confidence Medium. EX-0133, EX-0134. RET-00103. TR-00103. PO. PO-2023-0018. FA-000103. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -49904,7 +49925,7 @@
       </c>
       <c r="I411" s="7" t="inlineStr">
         <is>
-          <t>Bought the Cisco C9300 ($6470) on PO-2023-0018.</t>
+          <t>$6470 Cisco C9300. PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -49951,7 +49972,7 @@
       </c>
       <c r="I412" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00104 / APR-00104. Received 3/18/26.</t>
+          <t>Dock file shows Mar 18, 2026 for TR-00104 (MD-00104).</t>
         </is>
       </c>
     </row>
@@ -50076,7 +50097,7 @@
       </c>
       <c r="I415" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00104 — non-authoritative.</t>
+          <t>Could not tie MD-00104 to a verified RN entry in the notes.</t>
         </is>
       </c>
     </row>
@@ -50115,7 +50136,7 @@
       </c>
       <c r="I416" s="7" t="inlineStr">
         <is>
-          <t>On MD-00104, the matrix documents what transfer evidence looks like; it is not a substitute for TR-00104.</t>
+          <t>While scoring MD-00104, disposal requirements came from the policy appendix. Checked TR-00104, PO-2023-0018, FA-000104, RET-00104, APR-00104 against those requirements.</t>
         </is>
       </c>
     </row>
@@ -50162,7 +50183,7 @@
       </c>
       <c r="I417" s="7" t="inlineStr">
         <is>
-          <t>MD-00104 → Retired/Pending Disposal. Confidence Medium. EX-0135, EX-0136. RET-00104 TR-00104 PO-2023-0018 FA-000104 ITAM_control_matrix.png</t>
+          <t>Call on MD-00104: Retired/Pending Disposal, Medium. EX-0135, EX-0136. RET-00104. TR-00104. PO. PO-2023-0018. FA-000104. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -50209,7 +50230,7 @@
       </c>
       <c r="I418" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0018. Dell Latitude 7440.</t>
+          <t>Purchasing file PO-2023-0018 matches MD-00105 at $1850.</t>
         </is>
       </c>
     </row>
@@ -50256,7 +50277,7 @@
       </c>
       <c r="I419" s="7" t="inlineStr">
         <is>
-          <t>Recorded 4/20, received 4/21/26. TR-00105.</t>
+          <t>From warehouse to Regional IT. TR-00105, received 04/21/2026.</t>
         </is>
       </c>
     </row>
@@ -50299,7 +50320,7 @@
       </c>
       <c r="I420" s="7" t="inlineStr">
         <is>
-          <t>RET-00105 — Pending Disposal. Due n/a.</t>
+          <t>RET-00105 Pending Disposal. Return required=No.</t>
         </is>
       </c>
     </row>
@@ -50381,7 +50402,7 @@
       </c>
       <c r="I422" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb in regional_IT_notes.docx. Still need a transaction for MD-00105.</t>
+          <t>Investigative color on MD-00105 in regional_IT_notes.docx — weight zero.</t>
         </is>
       </c>
     </row>
@@ -50420,7 +50441,7 @@
       </c>
       <c r="I423" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial tests for MD-00105 were read against the matrix financial reconciliation row and TR-00105; policy PDF §4–§7 read with TR-00105.</t>
+          <t>ITAM_control_matrix.png consulted for MD-00105 (return). Conclusion still tied to TR-00105, PO-2023-0018, FA-000105, RET-00105, APR-00105 at Denver, $1850.</t>
         </is>
       </c>
     </row>
@@ -50467,7 +50488,7 @@
       </c>
       <c r="I424" s="7" t="inlineStr">
         <is>
-          <t>Landed on Retired/Pending Disposal (Medium). EX-0137, EX-0138. RET-00105 TR-00105 PO-2023-0018 FA-000105 ITAM_control_matrix.png</t>
+          <t>MD-00105 custody narrative ends Retired/Pending Disposal (Medium). EX-0137, EX-0138. RET-00105. TR-00105. PO. PO-2023-0018. FA-000105. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -50514,7 +50535,7 @@
       </c>
       <c r="I425" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00106 (Dell U2723QE) for $565 via PO-2023-0018.</t>
+          <t>Procurement PO-2023-0018 lists Dell U2723QE / $565.</t>
         </is>
       </c>
     </row>
@@ -50561,7 +50582,7 @@
       </c>
       <c r="I426" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00106 completed inbound 5/25/26.</t>
+          <t>TR-00106 05/22/2026; inbound 2026-05-25.</t>
         </is>
       </c>
     </row>
@@ -50604,7 +50625,7 @@
       </c>
       <c r="I427" s="7" t="inlineStr">
         <is>
-          <t>People ticket RET-00106. Doesn't by itself dock MD-00106.</t>
+          <t>RET-00106 sits Pending Disposal. Hardware return not required per ticket.</t>
         </is>
       </c>
     </row>
@@ -50686,7 +50707,7 @@
       </c>
       <c r="I429" s="7" t="inlineStr">
         <is>
-          <t>Didn't let the regional write-up overrule the logs on MD-00106.</t>
+          <t>Notes packet includes MD-00106 only as background, not evidence.</t>
         </is>
       </c>
     </row>
@@ -50725,7 +50746,7 @@
       </c>
       <c r="I430" s="7" t="inlineStr">
         <is>
-          <t>Control design for MD-00106 (return) comes from the policy figure; movement proof is TR-00106.</t>
+          <t>MD-00106: checked ITAM-001 transfer row while reviewing TR-00106, PO-2023-0018, FA-000106, RET-00106, APR-00106. Cost basis $565; confidence Medium. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -50772,7 +50793,7 @@
       </c>
       <c r="I431" s="7" t="inlineStr">
         <is>
-          <t>Wrap: MD-00106 Retired/Pending Disposal. EX-0139, EX-0140. RET-00106 TR-00106 PO-2023-0018 FA-000106 ITAM_control_matrix.png</t>
+          <t>Wrap-up MD-00106: Retired/Pending Disposal (Medium) — EX-0139, EX-0140. RET-00106. TR-00106. PO. PO-2023-0018. FA-000106. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -50819,7 +50840,7 @@
       </c>
       <c r="I432" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2023-0018. Samsung Galaxy S24, $1040.</t>
+          <t>Acquired MD-00107 (Samsung Galaxy S24) for $1040 via PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -50866,7 +50887,7 @@
       </c>
       <c r="I433" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 6/26. Docked 6/27/26 (TR-00107).</t>
+          <t>Log row TR-00107. Receive date Jun 27, 2026.</t>
         </is>
       </c>
     </row>
@@ -50909,7 +50930,7 @@
       </c>
       <c r="I434" s="7" t="inlineStr">
         <is>
-          <t>RET-00107 sits Pending Disposal. Hardware return not required per ticket.</t>
+          <t>Service desk RET-00107 on MD-00107. Return required No.</t>
         </is>
       </c>
     </row>
@@ -50991,7 +51012,7 @@
       </c>
       <c r="I436" s="7" t="inlineStr">
         <is>
-          <t>Closed-floor story in the notes. Ignored as clearance. (MD-00107-Regional IT Note Lead-436)</t>
+          <t>Regional file reviewed for MD-00107; no clearance language accepted.</t>
         </is>
       </c>
     </row>
@@ -51030,7 +51051,7 @@
       </c>
       <c r="I437" s="7" t="inlineStr">
         <is>
-          <t>MD-00107 custody review used the appendix matrix on assignment; TR-00107 remains the auditable source; policy PDF §4–§7 read with TR-00107.</t>
+          <t>MD-00107: checked ITAM-001 financial row while reviewing TR-00107, PO-2023-0018, FA-000107, RET-00107, APR-00107. Cost basis $1040; confidence Medium. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -51077,7 +51098,7 @@
       </c>
       <c r="I438" s="7" t="inlineStr">
         <is>
-          <t>Retired/Pending Disposal is the status I'm standing behind. EX-0141, EX-0142. Medium. RET-00107 TR-00107 PO-2023-0018 FA-000107 ITAM_control_matrix.png</t>
+          <t>Outcome MD-00107 — Retired/Pending Disposal, site Seattle, Medium. EX-0141, EX-0142. RET-00107. TR-00107. PO. PO-2023-0018. FA-000107. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51124,7 +51145,7 @@
       </c>
       <c r="I439" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 origin: PO-2023-0018, $6335.</t>
+          <t>Receiving against PO-2023-0018. Cisco C9300, $6335.</t>
         </is>
       </c>
     </row>
@@ -51171,7 +51192,7 @@
       </c>
       <c r="I440" s="7" t="inlineStr">
         <is>
-          <t>TR-00108 1/30; inbound 1/30/26.</t>
+          <t>Transfer TR-00108 / APR-00108. Received 01/30/2026.</t>
         </is>
       </c>
     </row>
@@ -51214,7 +51235,7 @@
       </c>
       <c r="I441" s="7" t="inlineStr">
         <is>
-          <t>Offboarding RET-00108: No.</t>
+          <t>RET-00108 Pending Disposal. Return required=No.</t>
         </is>
       </c>
     </row>
@@ -51296,7 +51317,7 @@
       </c>
       <c r="I443" s="7" t="inlineStr">
         <is>
-          <t>Someone wrote that it stayed at a closed site. Unverified for MD-00108.</t>
+          <t>I did not cite regional_IT_notes.docx as proof for MD-00108.</t>
         </is>
       </c>
     </row>
@@ -51335,7 +51356,7 @@
       </c>
       <c r="I444" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure cited on MD-00108 as the control standard for disposal; transactional weight stays with TR-00108.</t>
+          <t>MD-00108 / Cisco C9300: disposal evidence expectations from Appendix A. Anchored to TR-00108, PO-2023-0018, FA-000108, RET-00108, APR-00108; acquisition $6335.</t>
         </is>
       </c>
     </row>
@@ -51382,7 +51403,7 @@
       </c>
       <c r="I445" s="7" t="inlineStr">
         <is>
-          <t>Closing note MD-00108: Retired/Pending Disposal / Atlanta (Medium). EX-0143, EX-0144. RET-00108 TR-00108 PO-2023-0018 FA-000108 ITAM_control_matrix.png</t>
+          <t>Retired/Pending Disposal is the status for MD-00108 at Atlanta; Medium. EX-0143, EX-0144. RET-00108. TR-00108. PO. PO-2023-0018. FA-000108. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51450,7 @@
       </c>
       <c r="I446" s="7" t="inlineStr">
         <is>
-          <t>Lenovo ThinkPad T14 came in on PO-2024-0019 ($2030).</t>
+          <t>$2030 Lenovo ThinkPad T14. PO-2024-0019.</t>
         </is>
       </c>
     </row>
@@ -51476,7 +51497,7 @@
       </c>
       <c r="I447" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00109. Receive date 2/4/26.</t>
+          <t>TR-00109 — got it 2026-02-04 at Chicago.</t>
         </is>
       </c>
     </row>
@@ -51519,7 +51540,7 @@
       </c>
       <c r="I448" s="7" t="inlineStr">
         <is>
-          <t>RET-00109 Pending Disposal. Return required=No.</t>
+          <t>RET-00109 sits Pending Disposal. Hardware return not required per ticket.</t>
         </is>
       </c>
     </row>
@@ -51601,7 +51622,7 @@
       </c>
       <c r="I450" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions closed-office leftover color on MD-00109. Notes don't beat a scan.</t>
+          <t>Technician notes scanned for MD-00109; nothing usable without a transaction.</t>
         </is>
       </c>
     </row>
@@ -51640,7 +51661,7 @@
       </c>
       <c r="I451" s="7" t="inlineStr">
         <is>
-          <t>Policy matrix (transfer row) applied while tracing MD-00109; the figure does not replace TR-00109; policy PDF §4–§7 read with TR-00109.</t>
+          <t>Control matrix cited on MD-00109 for return only. Movement/finance proof stays with TR-00109, PO-2024-0019, FA-000109, RET-00109, APR-00109; exceptions EX-0145, EX-0146.</t>
         </is>
       </c>
     </row>
@@ -51687,7 +51708,7 @@
       </c>
       <c r="I452" s="7" t="inlineStr">
         <is>
-          <t>Verified Retired/Pending Disposal. EX-0145, EX-0146. Medium. RET-00109 TR-00109 PO-2024-0019 FA-000109 ITAM_control_matrix.png</t>
+          <t>MD-00109 → Retired/Pending Disposal. Confidence Medium. EX-0145, EX-0146. RET-00109. TR-00109. PO. PO-2024-0019. FA-000109. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51781,7 +51802,7 @@
       </c>
       <c r="I454" s="7" t="inlineStr">
         <is>
-          <t>Dallas: TR-00110 received 3/8/26.</t>
+          <t>Transfer TR-00110 / APR-00110. Received Mar 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -51824,7 +51845,7 @@
       </c>
       <c r="I455" s="7" t="inlineStr">
         <is>
-          <t>MD-00110 tied to RET-00110 (Pending Disposal).</t>
+          <t>RET-00110 Pending Disposal. Return required=No.</t>
         </is>
       </c>
     </row>
@@ -51906,7 +51927,7 @@
       </c>
       <c r="I457" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx is in the packet. Weight = lead only (MD-00110).</t>
+          <t>Looked for MD-00110 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
         </is>
       </c>
     </row>
@@ -51945,7 +51966,7 @@
       </c>
       <c r="I458" s="7" t="inlineStr">
         <is>
-          <t>IT_asset_management_policy.pdf plus the matrix set the assignment standard for MD-00110; TR-00110 cited.</t>
+          <t>For MD-00110 (Dell U2723QE), Appendix A transfer criteria were read against TR-00110, PO-2024-0019, FA-000110, RET-00110, APR-00110. Verified status target Retired/Pending Disposal at Dallas; matrix PNG is reference only.</t>
         </is>
       </c>
     </row>
@@ -51992,7 +52013,7 @@
       </c>
       <c r="I459" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Retired/Pending Disposal. Medium confidence. EX-0147, EX-0148. RET-00110 TR-00110 PO-2024-0019 FA-000110 ITAM_control_matrix.png</t>
+          <t>Retired/Pending Disposal is the status for MD-00110 at Dallas; Medium. EX-0147, EX-0148. RET-00110. TR-00110. PO. PO-2024-0019. FA-000110. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -52039,7 +52060,7 @@
       </c>
       <c r="I460" s="7" t="inlineStr">
         <is>
-          <t>PO-2024-0019: Dell U2723QE at $610.</t>
+          <t>Procurement PO-2024-0019 lists Dell U2723QE / $610.</t>
         </is>
       </c>
     </row>
@@ -52086,7 +52107,7 @@
       </c>
       <c r="I461" s="7" t="inlineStr">
         <is>
-          <t>Moved to Certified Recycler in Disposed on TR-00114. Received 1/22/26.</t>
+          <t>Movement TR-00114 completed inbound 01/22/2026.</t>
         </is>
       </c>
     </row>
@@ -52129,7 +52150,7 @@
       </c>
       <c r="I462" s="7" t="inlineStr">
         <is>
-          <t>Opened RET-00114. Status Closed.</t>
+          <t>RET-00114 — Closed. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -52215,7 +52236,7 @@
       </c>
       <c r="I464" s="7" t="inlineStr">
         <is>
-          <t>TR-00114: recycler move without a matching certificate.</t>
+          <t>MD-00114 pending-disposal with an empty cert field.</t>
         </is>
       </c>
     </row>
@@ -52258,7 +52279,7 @@
       </c>
       <c r="I465" s="7" t="inlineStr">
         <is>
-          <t>Word file claim on MD-00114 — non-authoritative.</t>
+          <t>Breadcrumb for MD-00114 in regional_IT_notes.docx; corroboration missing.</t>
         </is>
       </c>
     </row>
@@ -52297,7 +52318,7 @@
       </c>
       <c r="I466" s="7" t="inlineStr">
         <is>
-          <t>MD-00114: ITAM-001 appendix defines acceptable return proof — see TR-00114 in this chain.</t>
+          <t>MD-00114: checked ITAM-001 financial row while reviewing TR-00114, PO-2024-0019, FA-000114, RET-00114, APR-00114. Cost basis $610; confidence Low. Figure does not replace logs.</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52365,7 @@
       </c>
       <c r="I467" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Retired/Pending Disposal. Low confidence. EX-0149, EX-0150. TR-00114 RET-00114 PO-2024-0019 FA-000114 ITAM_control_matrix.png</t>
+          <t>Outcome MD-00114 — Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150. TR-00114. RET-00114. PO. PO-2024-0019. FA-000114. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -52391,7 +52412,7 @@
       </c>
       <c r="I468" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2025-0020. Dell U2723QE.</t>
+          <t>Procurement PO-2025-0020 lists Dell U2723QE / $790.</t>
         </is>
       </c>
     </row>
@@ -52438,7 +52459,7 @@
       </c>
       <c r="I469" s="7" t="inlineStr">
         <is>
-          <t>Recorded Jun 3, received 2026-06-04. TR-00118.</t>
+          <t>MD-00118 inbound Jun 04, 2026 on TR-00118 / APR-00118.</t>
         </is>
       </c>
     </row>
@@ -52481,7 +52502,7 @@
       </c>
       <c r="I470" s="7" t="inlineStr">
         <is>
-          <t>Opened RET-00118. Status Closed.</t>
+          <t>Offboarding RET-00118: No.</t>
         </is>
       </c>
     </row>
@@ -52567,7 +52588,7 @@
       </c>
       <c r="I472" s="7" t="inlineStr">
         <is>
-          <t>TR-00118: recycler move without a matching certificate.</t>
+          <t>No DC for MD-00118. Transfer TR-00118 isn't enough.</t>
         </is>
       </c>
     </row>
@@ -52610,7 +52631,7 @@
       </c>
       <c r="I473" s="7" t="inlineStr">
         <is>
-          <t>Someone wrote that it stayed at a closed site. Unverified for MD-00118.</t>
+          <t>I kept MD-00118 off the note until logs backed it.</t>
         </is>
       </c>
     </row>
@@ -52649,7 +52670,7 @@
       </c>
       <c r="I474" s="7" t="inlineStr">
         <is>
-          <t>Policy appendix applied to MD-00118 under financial reconciliation; figure informs the review, TR-00118 carries it.</t>
+          <t>Disposed (certificate missing) custody review for MD-00118 used the return column on the matrix. Source trail: TR-00118, PO-2025-0020, FA-000118, RET-00118, APR-00118.</t>
         </is>
       </c>
     </row>
@@ -52696,7 +52717,7 @@
       </c>
       <c r="I475" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Retired/Pending Disposal. Low confidence. EX-0151, EX-0152. TR-00118 RET-00118 PO-2025-0020 FA-000118 ITAM_control_matrix.png</t>
+          <t>Verified Retired/Pending Disposal for MD-00118 in Disposed (certificate missing). Low. EX-0151, EX-0152. TR-00118. RET-00118. PO. PO-2025-0020. FA-000118. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -52743,7 +52764,7 @@
       </c>
       <c r="I476" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 came in on PO-2025-0020 ($950).</t>
+          <t>PO-2025-0020: Samsung Galaxy S24 at $950.</t>
         </is>
       </c>
     </row>
@@ -52790,7 +52811,7 @@
       </c>
       <c r="I477" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00119. Receive date 7/9.</t>
+          <t>Movement TR-00119 completed inbound 2026-07-09.</t>
         </is>
       </c>
     </row>
@@ -52833,7 +52854,7 @@
       </c>
       <c r="I478" s="7" t="inlineStr">
         <is>
-          <t>Opened RET-00119. Status Closed.</t>
+          <t>RET-00119 — Closed. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -52919,7 +52940,7 @@
       </c>
       <c r="I480" s="7" t="inlineStr">
         <is>
-          <t>DC-00119 on file (verified). DC-00119 on file (verified). DC-00119 on file (verified). Method=NIST 800-88 wipe and recycling</t>
+          <t>Certificate DC-00119 matches MD-00119.</t>
         </is>
       </c>
     </row>
@@ -52962,7 +52983,7 @@
       </c>
       <c r="I481" s="7" t="inlineStr">
         <is>
-          <t>Tech note in the Word dump. Treated as a lead for MD-00119, not location proof.</t>
+          <t>For MD-00119, notes are breadcrumb-only.</t>
         </is>
       </c>
     </row>
@@ -53001,7 +53022,7 @@
       </c>
       <c r="I482" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure cited on MD-00119 as the control standard for disposal; transactional weight stays with TR-00119.</t>
+          <t>Did not treat the PNG as proof of location for MD-00119. transfer standard applied; TR-00119, PO-2025-0020, FA-000119, RET-00119, APR-00119 remains dispositive (Disposed).</t>
         </is>
       </c>
     </row>
@@ -53048,7 +53069,7 @@
       </c>
       <c r="I483" s="7" t="inlineStr">
         <is>
-          <t>After the chain: Disposed. High confidence. EX-0153. DC-00119 TR-00119 RET-00119 PO-2025-0020 FA-000119 ITAM_control_matrix.png</t>
+          <t>Chain end MD-00119: Disposed; High; EX-0153. TR-00119. RET-00119. PO. PO-2025-0020. FA-000119. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53095,7 +53116,7 @@
       </c>
       <c r="I484" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2023-0022 — Samsung Galaxy S24.</t>
+          <t>MD-00127 origin: PO-2023-0022, $995.</t>
         </is>
       </c>
     </row>
@@ -53107,32 +53128,24 @@
       </c>
       <c r="B485" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C485" s="7" t="inlineStr">
         <is>
-          <t>Assignment/Transfer</t>
+          <t>Policy Control Figure</t>
         </is>
       </c>
       <c r="D485" s="7" t="inlineStr">
         <is>
-          <t>Central Receiving</t>
-        </is>
-      </c>
-      <c r="E485" s="7" t="inlineStr">
-        <is>
-          <t>E0061</t>
-        </is>
-      </c>
-      <c r="F485" s="7" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
+          <t>ITAM-001</t>
+        </is>
+      </c>
+      <c r="E485" s="7" t="n"/>
+      <c r="F485" s="7" t="n"/>
       <c r="G485" s="7" t="inlineStr">
         <is>
-          <t>Transfer:TR-00127; Approval:missing</t>
+          <t>ITAM_control_matrix.png; IT_asset_management_policy.pdf</t>
         </is>
       </c>
       <c r="H485" s="7" t="inlineStr">
@@ -53142,7 +53155,7 @@
       </c>
       <c r="I485" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to E0061. TR-00127, received Feb 17.</t>
+          <t>Denver custody review for MD-00127 used the return column on the matrix. Source trail: TR-00127, PO-2023-0022, FA-000127.</t>
         </is>
       </c>
     </row>
@@ -53154,24 +53167,32 @@
       </c>
       <c r="B486" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C486" s="7" t="inlineStr">
         <is>
-          <t>Policy Control Figure</t>
+          <t>Assignment/Transfer</t>
         </is>
       </c>
       <c r="D486" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001</t>
-        </is>
-      </c>
-      <c r="E486" s="7" t="inlineStr"/>
-      <c r="F486" s="7" t="inlineStr"/>
+          <t>Central Receiving</t>
+        </is>
+      </c>
+      <c r="E486" s="7" t="inlineStr">
+        <is>
+          <t>E0061</t>
+        </is>
+      </c>
+      <c r="F486" s="7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
       <c r="G486" s="7" t="inlineStr">
         <is>
-          <t>ITAM_control_matrix.png; IT_asset_management_policy.pdf</t>
+          <t>Transfer:TR-00127; Approval:missing</t>
         </is>
       </c>
       <c r="H486" s="7" t="inlineStr">
@@ -53181,7 +53202,7 @@
       </c>
       <c r="I486" s="7" t="inlineStr">
         <is>
-          <t>Appendix A transfer requirements govern MD-00127; PNG matrix is reference only beside TR-00127.</t>
+          <t>Log row TR-00127. Receive date 2026-02-17.</t>
         </is>
       </c>
     </row>
@@ -53228,7 +53249,7 @@
       </c>
       <c r="I487" s="7" t="inlineStr">
         <is>
-          <t>Wrap: MD-00127 In Use. EX-0160. E0061 TR-00127 PO-2023-0022 FA-000127 ITAM_control_matrix.png</t>
+          <t>Outcome MD-00127 — In Use, site Denver, Medium. EX-0160. E0061. TR-00127. PO. PO-2023-0022. FA-000127. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53275,7 +53296,7 @@
       </c>
       <c r="I488" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0022. Dell U2723QE.</t>
+          <t>First touch MD-00130 — PO-2023-0022, $700.</t>
         </is>
       </c>
     </row>
@@ -53287,32 +53308,24 @@
       </c>
       <c r="B489" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>Assignment/Transfer</t>
+          <t>Policy Control Figure</t>
         </is>
       </c>
       <c r="D489" s="7" t="inlineStr">
         <is>
-          <t>Central Receiving</t>
-        </is>
-      </c>
-      <c r="E489" s="7" t="inlineStr">
-        <is>
-          <t>E0064</t>
-        </is>
-      </c>
-      <c r="F489" s="7" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
+          <t>ITAM-001</t>
+        </is>
+      </c>
+      <c r="E489" s="7" t="n"/>
+      <c r="F489" s="7" t="n"/>
       <c r="G489" s="7" t="inlineStr">
         <is>
-          <t>Transfer:TR-00130; Approval:APR-00130</t>
+          <t>ITAM_control_matrix.png; IT_asset_management_policy.pdf</t>
         </is>
       </c>
       <c r="H489" s="7" t="inlineStr">
@@ -53322,7 +53335,7 @@
       </c>
       <c r="I489" s="7" t="inlineStr">
         <is>
-          <t>Recorded 5/22, received 5/28/26. TR-00130.</t>
+          <t>Auditors tracing MD-00130 should read matrix assignment, then TR-00130, PO-2023-0022, APR-00130. Working site Atlanta; status call In Use.</t>
         </is>
       </c>
     </row>
@@ -53334,24 +53347,32 @@
       </c>
       <c r="B490" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C490" s="7" t="inlineStr">
         <is>
-          <t>Policy Control Figure</t>
+          <t>Assignment/Transfer</t>
         </is>
       </c>
       <c r="D490" s="7" t="inlineStr">
         <is>
-          <t>ITAM-001</t>
-        </is>
-      </c>
-      <c r="E490" s="7" t="inlineStr"/>
-      <c r="F490" s="7" t="inlineStr"/>
+          <t>Central Receiving</t>
+        </is>
+      </c>
+      <c r="E490" s="7" t="inlineStr">
+        <is>
+          <t>E0064</t>
+        </is>
+      </c>
+      <c r="F490" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
       <c r="G490" s="7" t="inlineStr">
         <is>
-          <t>ITAM_control_matrix.png; IT_asset_management_policy.pdf</t>
+          <t>Transfer:TR-00130; Approval:APR-00130</t>
         </is>
       </c>
       <c r="H490" s="7" t="inlineStr">
@@ -53361,7 +53382,7 @@
       </c>
       <c r="I490" s="7" t="inlineStr">
         <is>
-          <t>When scoring MD-00130, the financial reconciliation column in ITAM_control_matrix.png frames what counts; TR-00130 was checked; ITAM_control_matrix.png attached.</t>
+          <t>TR-00130 — got it May 28, 2026 at Atlanta.</t>
         </is>
       </c>
     </row>
@@ -53408,7 +53429,7 @@
       </c>
       <c r="I491" s="7" t="inlineStr">
         <is>
-          <t>After the chain: In Use. High confidence. EX-0161. E0064 TR-00130 APR-00130 PO-2023-0022 ITAM_control_matrix.png</t>
+          <t>Closing MD-00130: In Use at Atlanta (High). EX-0161. E0064. TR-00130. APR-00130. PO. PO-2023-0022. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53455,7 +53476,7 @@
       </c>
       <c r="I492" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2023-0022. Samsung Galaxy S24, $1175.</t>
+          <t>Ordered Samsung Galaxy S24 (MD-00131) on PO-2023-0022; $1175.</t>
         </is>
       </c>
     </row>
@@ -53502,7 +53523,7 @@
       </c>
       <c r="I493" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 2026-06-26. Docked June 28, 2026 (TR-00131).</t>
+          <t>MD-00131 inbound Jun 28, 2026 on TR-00131 / APR-00131.</t>
         </is>
       </c>
     </row>
@@ -53541,7 +53562,7 @@
       </c>
       <c r="I494" s="7" t="inlineStr">
         <is>
-          <t>Return/disposal/financial tests for MD-00131 were read against the matrix financial reconciliation row and TR-00131; policy PDF §4–§7 read with TR-00131.</t>
+          <t>Auditors tracing MD-00131 should read matrix return, then TR-00131, PO-2023-0022, APR-00131. Working site Chicago; status call In Use.</t>
         </is>
       </c>
     </row>
@@ -53588,7 +53609,7 @@
       </c>
       <c r="I495" s="7" t="inlineStr">
         <is>
-          <t>Wrap: MD-00131 In Use. EX-0162. E0065 TR-00131 APR-00131 PO-2023-0022 ITAM_control_matrix.png</t>
+          <t>Call on MD-00131: In Use, High. EX-0162. E0065. TR-00131. APR-00131. PO. PO-2023-0022. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53635,7 +53656,7 @@
       </c>
       <c r="I496" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 came in on PO-2023-0022 ($6470).</t>
+          <t>Ordered Cisco C9300 (MD-00132) on PO-2023-0022; $6470.</t>
         </is>
       </c>
     </row>
@@ -53682,7 +53703,7 @@
       </c>
       <c r="I497" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00132. Receive date 2026-01-31.</t>
+          <t>Moved to E0066 in Dallas on TR-00132. Received 01/31/2026.</t>
         </is>
       </c>
     </row>
@@ -53721,7 +53742,7 @@
       </c>
       <c r="I498" s="7" t="inlineStr">
         <is>
-          <t>Policy appendix applied to MD-00132 under financial reconciliation; figure informs the review, TR-00132 carries it.</t>
+          <t>Dallas custody review for MD-00132 used the return column on the matrix. Source trail: TR-00132, PO-2023-0022, APR-00132.</t>
         </is>
       </c>
     </row>
@@ -53768,7 +53789,7 @@
       </c>
       <c r="I499" s="7" t="inlineStr">
         <is>
-          <t>After the chain: In Use. High confidence. EX-0163. E0066 TR-00132 APR-00132 PO-2023-0022 ITAM_control_matrix.png</t>
+          <t>In Use is the status for MD-00132 at Dallas; High. EX-0163. E0066. TR-00132. APR-00132. PO. PO-2023-0022. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53875,7 +53896,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Inventory-to-Ledger Reconciliation</t>
         </is>
@@ -53888,13 +53909,14 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Control Total</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -54557,7 +54579,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Quarterly Inventory Certification Statement</t>
         </is>
@@ -54570,33 +54592,34 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Determination</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Scope / Count</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Evidence Basis</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -54962,29 +54985,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Evidence Index — Source Systems of Record</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Key Fields Used</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Evidentiary Weight</t>
         </is>
@@ -55276,19 +55300,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Reconciliation Methodology</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corrected Register" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exception Register" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custody Chain" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Index" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Source Ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Corrected Register" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Exception Register" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Custody Chain" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ledger Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Certification" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Evidence Index" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,7 +614,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -5719,7 +5718,7 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Yanou &amp; Partners IT Services — IT Asset Reconciliation Dashboard</t>
+          <t>Yanou &amp; Partners IT Services - IT Asset Reconciliation Dashboard</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5729,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -5749,8 +5747,7 @@
           <t>Assets reviewed</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>COUNTA('Corrected Register'!$A$5:$A$136)</f>
+      <c r="B5" s="5" t="n">
         <v>132</v>
       </c>
     </row>
@@ -5762,7 +5759,7 @@
       </c>
       <c r="B6" s="5">
         <f>SUM('Corrected Register'!$M$5:$M$136)</f>
-        <v>332115</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -5773,7 +5770,7 @@
       </c>
       <c r="B7" s="5">
         <f>SUM('Corrected Register'!$N$5:$N$136)</f>
-        <v>61561.6</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -5784,7 +5781,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Exception Register'!$K$5:$K$167,"Open")</f>
-        <v>163</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -5795,7 +5792,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Exception Register'!$C$5:$C$167,"Critical")</f>
-        <v>43</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -5806,7 +5803,7 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Missing")</f>
-        <v>12</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -5817,7 +5814,7 @@
       </c>
       <c r="B11" s="5">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Return Overdue")</f>
-        <v>12</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -5828,7 +5825,7 @@
       </c>
       <c r="B12" s="5">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Disposed")</f>
-        <v>8</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -5839,7 +5836,7 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTA(UNIQUE(FILTER('Custody Chain'!A5:A501,'Custody Chain'!A5:A501&lt;&gt;"")))</f>
-        <v>65</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -5906,11 +5903,11 @@
       </c>
       <c r="B19" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A19)</f>
-        <v>25</v>
+        <v/>
       </c>
       <c r="C19" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A19,'Corrected Register'!$N$5:$N$136)</f>
-        <v>12961</v>
+        <v/>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -5919,11 +5916,11 @@
       </c>
       <c r="F19" s="7">
         <f>COUNTIF('Corrected Register'!$C$5:$C$136,E19)</f>
-        <v>32</v>
+        <v/>
       </c>
       <c r="G19" s="7">
         <f>SUMIF('Corrected Register'!$C$5:$C$136,E19,'Corrected Register'!$N$5:$N$136)</f>
-        <v>1194.95</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -5934,11 +5931,11 @@
       </c>
       <c r="B20" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A20)</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="C20" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A20,'Corrected Register'!$N$5:$N$136)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -5947,11 +5944,11 @@
       </c>
       <c r="F20" s="7">
         <f>COUNTIF('Corrected Register'!$C$5:$C$136,E20)</f>
-        <v>33</v>
+        <v/>
       </c>
       <c r="G20" s="7">
         <f>SUMIF('Corrected Register'!$C$5:$C$136,E20,'Corrected Register'!$N$5:$N$136)</f>
-        <v>20855.29</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -5962,11 +5959,11 @@
       </c>
       <c r="B21" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A21)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="C21" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A21,'Corrected Register'!$N$5:$N$136)</f>
-        <v>1019.4</v>
+        <v/>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -5975,11 +5972,11 @@
       </c>
       <c r="F21" s="7">
         <f>COUNTIF('Corrected Register'!$C$5:$C$136,E21)</f>
-        <v>34</v>
+        <v/>
       </c>
       <c r="G21" s="7">
         <f>SUMIF('Corrected Register'!$C$5:$C$136,E21,'Corrected Register'!$N$5:$N$136)</f>
-        <v>11329.87</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -5990,11 +5987,11 @@
       </c>
       <c r="B22" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A22)</f>
-        <v>51</v>
+        <v/>
       </c>
       <c r="C22" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A22,'Corrected Register'!$N$5:$N$136)</f>
-        <v>25512.76</v>
+        <v/>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -6003,11 +6000,11 @@
       </c>
       <c r="F22" s="7">
         <f>COUNTIF('Corrected Register'!$C$5:$C$136,E22)</f>
-        <v>33</v>
+        <v/>
       </c>
       <c r="G22" s="7">
         <f>SUMIF('Corrected Register'!$C$5:$C$136,E22,'Corrected Register'!$N$5:$N$136)</f>
-        <v>28181.49</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -6018,11 +6015,11 @@
       </c>
       <c r="B23" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A23)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="C23" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A23,'Corrected Register'!$N$5:$N$136)</f>
-        <v>6214.38</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -6033,11 +6030,11 @@
       </c>
       <c r="B24" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A24)</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="C24" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A24,'Corrected Register'!$N$5:$N$136)</f>
-        <v>4851.08</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -6048,11 +6045,11 @@
       </c>
       <c r="B25" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A25)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="C25" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A25,'Corrected Register'!$N$5:$N$136)</f>
-        <v>4811.33</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -6063,11 +6060,11 @@
       </c>
       <c r="B26" s="7">
         <f>COUNTIF('Corrected Register'!$J$5:$J$136,A26)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="C26" s="7">
         <f>SUMIF('Corrected Register'!$J$5:$J$136,A26,'Corrected Register'!$N$5:$N$136)</f>
-        <v>6191.65</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -6122,11 +6119,11 @@
       </c>
       <c r="B32" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A32)</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="C32" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A32,'Corrected Register'!$N$5:$N$136)</f>
-        <v>5184.18</v>
+        <v/>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -6135,11 +6132,11 @@
       </c>
       <c r="F32" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E32)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="G32" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E32,'Exception Register'!$G$5:$G$167)</f>
-        <v>6214.38</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -6150,11 +6147,11 @@
       </c>
       <c r="B33" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A33)</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="C33" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A33,'Corrected Register'!$N$5:$N$136)</f>
-        <v>6267.29</v>
+        <v/>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -6163,11 +6160,11 @@
       </c>
       <c r="F33" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E33)</f>
-        <v>61</v>
+        <v/>
       </c>
       <c r="G33" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E33,'Exception Register'!$G$5:$G$167)</f>
-        <v>29098.84</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -6178,11 +6175,11 @@
       </c>
       <c r="B34" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A34)</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="C34" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A34,'Corrected Register'!$N$5:$N$136)</f>
-        <v>11070.95</v>
+        <v/>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -6191,11 +6188,11 @@
       </c>
       <c r="F34" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E34)</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="G34" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E34,'Exception Register'!$G$5:$G$167)</f>
-        <v>2503.11</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -6206,11 +6203,11 @@
       </c>
       <c r="B35" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A35)</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="C35" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A35,'Corrected Register'!$N$5:$N$136)</f>
-        <v>5149.95</v>
+        <v/>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -6219,11 +6216,11 @@
       </c>
       <c r="F35" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E35)</f>
-        <v>43</v>
+        <v/>
       </c>
       <c r="G35" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E35,'Exception Register'!$G$5:$G$167)</f>
-        <v>22627.56</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -6234,11 +6231,11 @@
       </c>
       <c r="B36" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A36)</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="C36" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A36,'Corrected Register'!$N$5:$N$136)</f>
-        <v>5551.75</v>
+        <v/>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -6247,11 +6244,11 @@
       </c>
       <c r="F36" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E36)</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="G36" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E36,'Exception Register'!$G$5:$G$167)</f>
-        <v>7440</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -6262,11 +6259,11 @@
       </c>
       <c r="B37" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A37)</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="C37" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A37,'Corrected Register'!$N$5:$N$136)</f>
-        <v>10561</v>
+        <v/>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -6275,11 +6272,11 @@
       </c>
       <c r="F37" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E37)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="G37" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E37,'Exception Register'!$G$5:$G$167)</f>
-        <v>4811.33</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -6290,11 +6287,11 @@
       </c>
       <c r="B38" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A38)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="C38" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A38,'Corrected Register'!$N$5:$N$136)</f>
-        <v>6214.38</v>
+        <v/>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -6303,11 +6300,11 @@
       </c>
       <c r="F38" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E38)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="G38" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E38,'Exception Register'!$G$5:$G$167)</f>
-        <v>6191.65</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6318,11 +6315,11 @@
       </c>
       <c r="B39" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A39)</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="C39" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A39,'Corrected Register'!$N$5:$N$136)</f>
-        <v>4878.51</v>
+        <v/>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -6331,11 +6328,11 @@
       </c>
       <c r="F39" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E39)</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="G39" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E39,'Exception Register'!$G$5:$G$167)</f>
-        <v>2332.54</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -6346,11 +6343,11 @@
       </c>
       <c r="B40" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A40)</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="C40" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A40,'Corrected Register'!$N$5:$N$136)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -6359,11 +6356,11 @@
       </c>
       <c r="F40" s="7">
         <f>COUNTIF('Exception Register'!$B$5:$B$167,E40)</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="G40" s="7">
         <f>SUMIF('Exception Register'!$B$5:$B$167,E40,'Exception Register'!$G$5:$G$167)</f>
-        <v>2869.32</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -6374,11 +6371,11 @@
       </c>
       <c r="B41" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A41)</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="C41" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A41,'Corrected Register'!$N$5:$N$136)</f>
-        <v>4351.05</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -6389,11 +6386,11 @@
       </c>
       <c r="B42" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A42)</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="C42" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A42,'Corrected Register'!$N$5:$N$136)</f>
-        <v>2332.54</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -6404,17 +6401,17 @@
       </c>
       <c r="B43" s="7">
         <f>COUNTIF('Corrected Register'!$I$5:$I$136,A43)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="C43" s="7">
         <f>SUMIF('Corrected Register'!$I$5:$I$136,A43,'Corrected Register'!$N$5:$N$136)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>Key finding — Duplicate serial identities (both pairs)</t>
+          <t>Key finding - Duplicate serial identities (both pairs)</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6528,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -6707,7 +6703,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00001 is In Use in Chicago. Employee E0001 (Active) matches the register holder. equipment_transfer_log TR-00001, approval APR-00001; received Jan 21, 2026. PO PO-2022-0001 on file; no matching FAR row for MD-00001.</t>
+          <t>After HR and transfer review, MD-00001 is In Use in Chicago. Employee E0001 (Active) matches the register holder. equipment_transfer_log TR-00001, approval APR-00001; received Jan 21, 2026. Cost path: PO-2022-0001 into FA-000001.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6718,13 +6714,13 @@
       <c r="M5" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N5" s="7">
-        <f>IFERROR(XLOOKUP(A5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="7">
-        <f>IFERROR(XLOOKUP(A5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>FA-000001</t>
+        </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
@@ -6815,7 +6811,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00002: In Use in Dallas ($610). Employee E0002 (Active) matches the register holder. Assignment TR-00002; receive column 2026-02-25, approval APR-00002. PO PO-2022-0001 on file; no matching FAR row for MD-00002.</t>
+          <t>Working conclusion for MD-00002: In Use in Dallas ($610). Employee E0002 (Active) matches the register holder. Assignment TR-00002; receive column 2026-02-25, approval APR-00002. Procurement PO-2022-0001 maps to ledger FA-000002.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6826,13 +6822,13 @@
       <c r="M6" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N6" s="7">
-        <f>IFERROR(XLOOKUP(A6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N6" s="7" t="n">
         <v>313.06</v>
       </c>
-      <c r="O6" s="7">
-        <f>IFERROR(XLOOKUP(A6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>FA-000002</t>
+        </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
@@ -6923,7 +6919,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Cost $1085 on MD-00003; In Use at Denver. Employee E0003 (Active) matches the register holder. TR-00003 for MD-00003 — received 04/03/2026, approval APR-00003. PO PO-2022-0001 on file; no matching FAR row for MD-00003.</t>
+          <t>Cost $1085 on MD-00003; In Use at Denver. Employee E0003 (Active) matches the register holder. TR-00003 for MD-00003 - received 04/03/2026, approval APR-00003. Ledger FA-000003 backs PO-2022-0001 for MD-00003.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -6934,13 +6930,13 @@
       <c r="M7" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N7" s="7">
-        <f>IFERROR(XLOOKUP(A7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N7" s="7" t="n">
         <v>597.83</v>
       </c>
-      <c r="O7" s="7">
-        <f>IFERROR(XLOOKUP(A7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>FA-000003</t>
+        </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -7031,7 +7027,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>MD-00004 lists In Use at New York (Cisco C9300, $6380). Employee E0004 (Active) matches the register holder. Inbound stamp on TR-00004 is May 01, 2026, approval APR-00004. PO PO-2022-0001 on file; no matching FAR row for MD-00004.</t>
+          <t>MD-00004 lists In Use at New York (Cisco C9300, $6380). Employee E0004 (Active) matches the register holder. Inbound stamp on TR-00004 is May 01, 2026, approval APR-00004. Purchase order PO-2022-0001 and FAR row FA-000004 both cite MD-00004.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -7042,13 +7038,13 @@
       <c r="M8" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N8" s="7">
-        <f>IFERROR(XLOOKUP(A8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N8" s="7" t="n">
         <v>940.62</v>
       </c>
-      <c r="O8" s="7">
-        <f>IFERROR(XLOOKUP(A8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>FA-000004</t>
+        </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -7139,7 +7135,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Register MD-00005: In Use, Seattle, $2075 — MacBook Pro 14. Employee E0005 (Active) matches the register holder. Log TR-00005: received 2026-06-08, approval APR-00005. PO PO-2022-0001 on file; no matching FAR row for MD-00005.</t>
+          <t>Register MD-00005: In Use, Seattle, $2075 - MacBook Pro 14. Employee E0005 (Active) matches the register holder. Log TR-00005: received 2026-06-08, approval APR-00005. Capital trail MD-00005: PO-2022-0001 -&gt; FA-000005.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -7150,13 +7146,13 @@
       <c r="M9" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N9" s="7">
-        <f>IFERROR(XLOOKUP(A9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="7">
-        <f>IFERROR(XLOOKUP(A9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>FA-000005</t>
+        </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -7247,7 +7243,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00006: In Use, Atlanta, $790 — Dell U2723QE. Employee E0006 (Active) matches the register holder. TR-00006 for MD-00006 — received 01/12/2026, approval APR-00006. PO-2022-0001 in hardware_purchase_orders.csv; FAR silent on MD-00006.</t>
+          <t>Corrected row MD-00006: In Use, Atlanta, $790 - Dell U2723QE. Employee E0006 (Active) matches the register holder. TR-00006 for MD-00006 - received 01/12/2026, approval APR-00006. PO-2022-0001 / FA-000006 support the cost basis.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7258,13 +7254,13 @@
       <c r="M10" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N10" s="7">
-        <f>IFERROR(XLOOKUP(A10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N10" s="7" t="n">
         <v>459.94</v>
       </c>
-      <c r="O10" s="7">
-        <f>IFERROR(XLOOKUP(A10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>FA-000006</t>
+        </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -7355,7 +7351,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00007 as In Use in Chicago. Employee E0007 (Active) matches the register holder. Movement TR-00007 posted 02/11/2026 and inbound Feb 17, 2026, approval APR-00007. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00007.</t>
+          <t>Corrected register carries MD-00007 as In Use in Chicago. Employee E0007 (Active) matches the register holder. Movement TR-00007 posted 02/11/2026 and inbound Feb 17, 2026, approval APR-00007. Purchase order PO-2023-0002 and FAR row FA-000007 both cite MD-00007.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7366,13 +7362,13 @@
       <c r="M11" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N11" s="7">
-        <f>IFERROR(XLOOKUP(A11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>632.68</v>
-      </c>
-      <c r="O11" s="7">
-        <f>IFERROR(XLOOKUP(A11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="N11" s="7" t="n">
+        <v>632.6799999999999</v>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>FA-000007</t>
+        </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -7399,7 +7395,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>632.68</v>
+        <v>632.6799999999999</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -7463,7 +7459,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>MD-00008 (Cisco C9300) closed In Use / Dallas on $6245. Employee E0008 (Active) matches the register holder. Log TR-00008: received 2026-03-19, approval APR-00008. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00008.</t>
+          <t>MD-00008 (Cisco C9300) closed In Use / Dallas on $6245. Employee E0008 (Active) matches the register holder. Log TR-00008: received 2026-03-19, approval APR-00008. Capital trail MD-00008: PO-2023-0002 -&gt; FA-000008.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7474,13 +7470,13 @@
       <c r="M12" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N12" s="7">
-        <f>IFERROR(XLOOKUP(A12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N12" s="7" t="n">
         <v>1355.01</v>
       </c>
-      <c r="O12" s="7">
-        <f>IFERROR(XLOOKUP(A12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>FA-000008</t>
+        </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -7571,7 +7567,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>MD-00009 carries In Use at Denver (Dell Latitude 7440, $1940). Employee E0009 (Active) matches the register holder. Assignment TR-00009; receive column 04/21/2026, approval APR-00009. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00009.</t>
+          <t>MD-00009 carries In Use at Denver (Dell Latitude 7440, $1940). Employee E0009 (Active) matches the register holder. Assignment TR-00009; receive column 04/21/2026, approval APR-00009. PO-2023-0002 and FA-000009 agree on MD-00009.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7582,13 +7578,13 @@
       <c r="M13" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N13" s="7">
-        <f>IFERROR(XLOOKUP(A13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N13" s="7" t="n">
         <v>109.33</v>
       </c>
-      <c r="O13" s="7">
-        <f>IFERROR(XLOOKUP(A13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>FA-000009</t>
+        </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -7679,7 +7675,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00010 In Use @ New York. Employee E0010 (Active) matches the register holder. Log TR-00010: received May 28, 2026, approval APR-00010. Purchasing PO-2023-0002 without a capital line for MD-00010.</t>
+          <t>Field review: MD-00010 In Use @ New York. Employee E0010 (Active) matches the register holder. Log TR-00010: received May 28, 2026, approval APR-00010. Ledger FA-000010 backs PO-2023-0002 for MD-00010.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7690,13 +7686,13 @@
       <c r="M14" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N14" s="7">
-        <f>IFERROR(XLOOKUP(A14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N14" s="7" t="n">
         <v>426.89</v>
       </c>
-      <c r="O14" s="7">
-        <f>IFERROR(XLOOKUP(A14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>FA-000010</t>
+        </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -7787,7 +7783,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00011 is In Use in Seattle site; basis $1130. Employee E0011 (Active) matches the register holder. Assignment TR-00011; receive column 2026-06-28, approval APR-00011. Purchasing PO-2023-0002 without a capital line for MD-00011.</t>
+          <t>Samsung Galaxy S24 on MD-00011 is In Use in Seattle site; basis $1130. Employee E0011 (Active) matches the register holder. Assignment TR-00011; receive column 2026-06-28, approval APR-00011. Purchase order PO-2023-0002 and FAR row FA-000011 both cite MD-00011.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7798,13 +7794,13 @@
       <c r="M15" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N15" s="7">
-        <f>IFERROR(XLOOKUP(A15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N15" s="7" t="n">
         <v>882.5</v>
       </c>
-      <c r="O15" s="7">
-        <f>IFERROR(XLOOKUP(A15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>FA-000011</t>
+        </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -7895,7 +7891,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Read MD-00012 against transfers before signing In Use / Atlanta. Employee E0012 (Active) matches the register holder. Transfer TR-00012 shows receipt 01/31/2026, approval APR-00012. Purchasing PO-2023-0002 without a capital line for MD-00012.</t>
+          <t>Read MD-00012 against transfers before signing In Use / Atlanta. Employee E0012 (Active) matches the register holder. Transfer TR-00012 shows receipt 01/31/2026, approval APR-00012. Capital trail MD-00012: PO-2023-0002 -&gt; FA-000012.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7906,13 +7902,13 @@
       <c r="M16" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N16" s="7">
-        <f>IFERROR(XLOOKUP(A16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N16" s="7" t="n">
         <v>553.23</v>
       </c>
-      <c r="O16" s="7">
-        <f>IFERROR(XLOOKUP(A16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>FA-000012</t>
+        </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -8003,7 +7999,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Did not move MD-00013 off In Use at Chicago without a transaction. Employee E0013 (Active) matches the register holder. Inbound stamp on TR-00013 is Feb 06, 2026, approval APR-00013. Purchasing PO-2024-0003 without a capital line for MD-00013.</t>
+          <t>Did not move MD-00013 off In Use at Chicago without a transaction. Employee E0013 (Active) matches the register holder. Inbound stamp on TR-00013 is Feb 06, 2026, approval APR-00013. Procurement PO-2024-0003 maps to ledger FA-000013.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -8014,13 +8010,13 @@
       <c r="M17" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N17" s="7">
-        <f>IFERROR(XLOOKUP(A17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="7">
-        <f>IFERROR(XLOOKUP(A17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>FA-000013</t>
+        </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -8111,7 +8107,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Register MD-00014: In Use, Dallas, $520 — Dell U2723QE. Employee E0014 (Active) matches the register holder. equipment_transfer_log TR-00014, approval APR-00014; received 2026-03-09. Purchasing PO-2024-0003 without a capital line for MD-00014.</t>
+          <t>Register MD-00014: In Use, Dallas, $520 - Dell U2723QE. Employee E0014 (Active) matches the register holder. equipment_transfer_log TR-00014, approval APR-00014; received 2026-03-09. Ledger FA-000014 backs PO-2024-0003 for MD-00014.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8122,13 +8118,13 @@
       <c r="M18" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N18" s="7">
-        <f>IFERROR(XLOOKUP(A18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N18" s="7" t="n">
         <v>270.29</v>
       </c>
-      <c r="O18" s="7">
-        <f>IFERROR(XLOOKUP(A18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>FA-000014</t>
+        </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -8219,7 +8215,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 MD-00015 tied to $995; location Denver; status In Use. Employee E0015 (Active) matches the register holder. TR-00015 ties to MD-00015; dock date 04/13/2026, approval APR-00015. Purchasing PO-2024-0003 without a capital line for MD-00015.</t>
+          <t>Samsung Galaxy S24 MD-00015 tied to $995; location Denver; status In Use. Employee E0015 (Active) matches the register holder. TR-00015 ties to MD-00015; dock date 04/13/2026, approval APR-00015. Purchase order PO-2024-0003 and FAR row FA-000015 both cite MD-00015.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -8230,13 +8226,13 @@
       <c r="M19" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N19" s="7">
-        <f>IFERROR(XLOOKUP(A19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N19" s="7" t="n">
         <v>559.13</v>
       </c>
-      <c r="O19" s="7">
-        <f>IFERROR(XLOOKUP(A19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>FA-000015</t>
+        </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -8327,7 +8323,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 on MD-00016 is In Use in New York; basis $6290. Employee E0016 (Active) matches the register holder. Assignment TR-00016; receive column May 17, 2026, approval APR-00016. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00016.</t>
+          <t>Cisco C9300 on MD-00016 is In Use in New York; basis $6290. Employee E0016 (Active) matches the register holder. Assignment TR-00016; receive column May 17, 2026, approval APR-00016. Procurement PO-2024-0003 maps to ledger FA-000016.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -8338,13 +8334,13 @@
       <c r="M20" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N20" s="7">
-        <f>IFERROR(XLOOKUP(A20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>968.69</v>
-      </c>
-      <c r="O20" s="7">
-        <f>IFERROR(XLOOKUP(A20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="N20" s="7" t="n">
+        <v>968.6900000000001</v>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>FA-000016</t>
+        </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -8371,7 +8367,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>968.69</v>
+        <v>968.6900000000001</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -8435,7 +8431,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Assignment trail and HR both fit In Use for MD-00017 in Seattle. Employee E0017 (Active) matches the register holder. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00017.</t>
+          <t>Assignment trail and HR both fit In Use for MD-00017 in Seattle. Employee E0017 (Active) matches the register holder. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. Ledger FA-000017 backs PO-2024-0003 for MD-00017.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8446,13 +8442,13 @@
       <c r="M21" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N21" s="7">
-        <f>IFERROR(XLOOKUP(A21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="7">
-        <f>IFERROR(XLOOKUP(A21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>FA-000017</t>
+        </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -8547,7 +8543,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>People and transfer logs align on MD-00018 — In Use, Atlanta. Employee E0018 (Active) matches the register holder. Inbound stamp on TR-00018 is 01/23/2026, approval APR-00018. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00018.</t>
+          <t>People and transfer logs align on MD-00018 - In Use, Atlanta. Employee E0018 (Active) matches the register holder. Inbound stamp on TR-00018 is 01/23/2026, approval APR-00018. Purchase order PO-2024-0003 and FAR row FA-000018 both cite MD-00018.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8558,13 +8554,13 @@
       <c r="M22" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N22" s="7">
-        <f>IFERROR(XLOOKUP(A22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N22" s="7" t="n">
         <v>412.14</v>
       </c>
-      <c r="O22" s="7">
-        <f>IFERROR(XLOOKUP(A22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>FA-000018</t>
+        </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -8655,7 +8651,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>MD-00019 sits In Use at Chicago (Samsung Galaxy S24, $1175). Employee E0019 (Active) matches the register holder. equipment_transfer_log TR-00019, approval APR-00019; received Feb 26, 2026. PO-2025-0004 in hardware_purchase_orders.csv; FAR silent on MD-00019.</t>
+          <t>MD-00019 sits In Use at Chicago (Samsung Galaxy S24, $1175). Employee E0019 (Active) matches the register holder. equipment_transfer_log TR-00019, approval APR-00019; received Feb 26, 2026. Cost path: PO-2025-0004 into FA-000019.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -8666,13 +8662,13 @@
       <c r="M23" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N23" s="7">
-        <f>IFERROR(XLOOKUP(A23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N23" s="7" t="n">
         <v>795.4</v>
       </c>
-      <c r="O23" s="7">
-        <f>IFERROR(XLOOKUP(A23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>FA-000019</t>
+        </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -8763,7 +8759,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 MD-00020 tied to $6470; location Dallas; status In Use. Employee E0020 (Active) matches the register holder. Inbound stamp on TR-00020 is 2026-03-30, approval APR-00020. Purchasing PO-2025-0004 without a capital line for MD-00020.</t>
+          <t>Cisco C9300 MD-00020 tied to $6470; location Dallas; status In Use. Employee E0020 (Active) matches the register holder. Inbound stamp on TR-00020 is 2026-03-30, approval APR-00020. PO-2025-0004 and FA-000020 agree on MD-00020.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -8774,13 +8770,13 @@
       <c r="M24" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N24" s="7" t="n">
         <v>1446.34</v>
       </c>
-      <c r="O24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>FA-000020</t>
+        </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -8871,7 +8867,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00021 In Use. Employee E0021 (Active) matches the register holder. equipment_transfer_log TR-00021, approval APR-00021; received 05/03/2026. Purchasing PO-2025-0004 without a capital line for MD-00021. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>I read the movement and people files before calling MD-00021 In Use. Employee E0021 (Active) matches the register holder. equipment_transfer_log TR-00021, approval APR-00021; received 05/03/2026. PO-2025-0004 / FA-000021 support the cost basis. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -8882,13 +8878,13 @@
       <c r="M25" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N25" s="7" t="n">
         <v>124.52</v>
       </c>
-      <c r="O25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>FA-000021</t>
+        </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -8983,7 +8979,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>MD-00022 lists In Use at New York (Dell U2723QE, $565). Employee E0022 (Active) matches the register holder. TR-00022 ties to MD-00022; dock date Jun 05, 2026, approval APR-00022. Purchasing PO-2025-0004 without a capital line for MD-00022.</t>
+          <t>MD-00022 lists In Use at New York (Dell U2723QE, $565). Employee E0022 (Active) matches the register holder. TR-00022 ties to MD-00022; dock date Jun 05, 2026, approval APR-00022. FAR extract includes FA-000022 for MD-00022 via PO-2025-0004.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -8994,13 +8990,13 @@
       <c r="M26" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N26" s="7" t="n">
         <v>371.95</v>
       </c>
-      <c r="O26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>FA-000022</t>
+        </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -9091,7 +9087,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>In Use / Seattle on MD-00023 (Samsung Galaxy S24, $1040) per cited files. Employee E0023 (Active) matches the register holder. TR-00023 for MD-00023 — received 2026-07-09, approval APR-00023. Purchasing PO-2025-0004 without a capital line for MD-00023.</t>
+          <t>In Use / Seattle on MD-00023 (Samsung Galaxy S24, $1040) per cited files. Employee E0023 (Active) matches the register holder. TR-00023 for MD-00023 - received 2026-07-09, approval APR-00023. Cost path: PO-2025-0004 into FA-000023.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -9102,13 +9098,13 @@
       <c r="M27" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N27" s="7" t="n">
         <v>823.6</v>
       </c>
-      <c r="O27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>FA-000023</t>
+        </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -9199,7 +9195,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Extract row MD-00024: In Use, Atlanta, $6335 — Cisco C9300. Employee E0024 (Active) matches the register holder. Movement TR-00024 posted 2026-01-18 and inbound 01/21/2026, approval APR-00024. Purchasing PO-2025-0004 without a capital line for MD-00024.</t>
+          <t>Extract row MD-00024: In Use, Atlanta, $6335 - Cisco C9300. Employee E0024 (Active) matches the register holder. Movement TR-00024 posted 2026-01-18 and inbound 01/21/2026, approval APR-00024. Procurement PO-2025-0004 maps to ledger FA-000024.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -9210,13 +9206,13 @@
       <c r="M28" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N28" s="7" t="n">
         <v>503.85</v>
       </c>
-      <c r="O28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>FA-000024</t>
+        </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -9307,7 +9303,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Cost $2030 on MD-00025; In Use at Chicago. Employee E0025 (Active) matches the register holder. Log TR-00025: received Jan 22, 2026, approval APR-00025. PO-2022-0005 in hardware_purchase_orders.csv; FAR silent on MD-00025. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>Cost $2030 on MD-00025; In Use at Chicago. Employee E0025 (Active) matches the register holder. Log TR-00025: received Jan 22, 2026, approval APR-00025. Ledger FA-000025 backs PO-2022-0005 for MD-00025. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -9318,13 +9314,13 @@
       <c r="M29" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>FA-000025</t>
+        </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -9419,7 +9415,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00026 as In Use (Dallas). Employee E0026 (Active) matches the register holder. equipment_transfer_log TR-00026, approval APR-00026; received 2026-02-27. PO PO-2022-0005 on file; no matching FAR row for MD-00026.</t>
+          <t>Cross-file check left MD-00026 as In Use (Dallas). Employee E0026 (Active) matches the register holder. equipment_transfer_log TR-00026, approval APR-00026; received 2026-02-27. Cost path: PO-2022-0005 into FA-000026.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -9430,13 +9426,13 @@
       <c r="M30" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N30" s="7" t="n">
         <v>382.34</v>
       </c>
-      <c r="O30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>FA-000026</t>
+        </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -9531,7 +9527,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>MD-00027 reads In Use at Denver (Samsung Galaxy S24, $1220). Employee E0027 (Active) matches the register holder. TR-00027 ties to MD-00027; dock date 04/06/2026, approval APR-00027. PO PO-2022-0005 on file; no matching FAR row for MD-00027.</t>
+          <t>MD-00027 reads In Use at Denver (Samsung Galaxy S24, $1220). Employee E0027 (Active) matches the register holder. TR-00027 ties to MD-00027; dock date 04/06/2026, approval APR-00027. Procurement PO-2022-0005 maps to ledger FA-000027.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -9542,13 +9538,13 @@
       <c r="M31" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N31" s="7" t="n">
         <v>672.21</v>
       </c>
-      <c r="O31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>FA-000027</t>
+        </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -9643,7 +9639,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Kept MD-00028 at In Use in New York; $6200 Cisco C9300. Employee E0028 (Active) matches the register holder. TR-00028 for MD-00028 — received May 02, 2026, approval APR-00028. PO PO-2022-0005 on file; no matching FAR row for MD-00028.</t>
+          <t>Kept MD-00028 at In Use in New York; $6200 Cisco C9300. Employee E0028 (Active) matches the register holder. TR-00028 for MD-00028 - received May 02, 2026, approval APR-00028. Ledger FA-000028 backs PO-2022-0005 for MD-00028.</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -9654,13 +9650,13 @@
       <c r="M32" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N32" s="7" t="n">
         <v>914.09</v>
       </c>
-      <c r="O32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>FA-000028</t>
+        </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -9755,7 +9751,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Asset row MD-00029: In Use, Seattle, $1895 — MacBook Pro 14. Employee E0029 (Active) matches the register holder. Movement TR-00029 posted Jun 05, 2026 and inbound 2026-06-11, approval APR-00029. PO PO-2022-0005 on file; no matching FAR row for MD-00029.</t>
+          <t>Asset row MD-00029: In Use, Seattle, $1895 - MacBook Pro 14. Employee E0029 (Active) matches the register holder. Movement TR-00029 posted Jun 05, 2026 and inbound 2026-06-11, approval APR-00029. Purchase order PO-2022-0005 and FAR row FA-000029 both cite MD-00029.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -9766,13 +9762,13 @@
       <c r="M33" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>FA-000029</t>
+        </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -9867,7 +9863,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Cost $610 on MD-00030; In Use at Atlanta. Employee E0030 (Active) matches the register holder. TR-00030 for MD-00030 — received 01/13/2026, approval APR-00030. PO-2022-0005 in hardware_purchase_orders.csv; FAR silent on MD-00030.</t>
+          <t>Cost $610 on MD-00030; In Use at Atlanta. Employee E0030 (Active) matches the register holder. TR-00030 for MD-00030 - received 01/13/2026, approval APR-00030. Cost path: PO-2022-0005 into FA-000030.</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -9878,13 +9874,13 @@
       <c r="M34" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N34" s="7" t="n">
         <v>355.14</v>
       </c>
-      <c r="O34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>FA-000030</t>
+        </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -9979,7 +9975,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Chicago: MD-00031 is In Use; cost $1085. Employee E0031 (Active) matches the register holder. Movement TR-00031 posted 02/11/2026 and inbound Feb 11, 2026, approval APR-00031. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00031.</t>
+          <t>Chicago: MD-00031 is In Use; cost $1085. Employee E0031 (Active) matches the register holder. Movement TR-00031 posted 02/11/2026 and inbound Feb 11, 2026, approval APR-00031. PO-2023-0006 and FA-000031 agree on MD-00031.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -9990,13 +9986,13 @@
       <c r="M35" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N35" s="7" t="n">
         <v>722.59</v>
       </c>
-      <c r="O35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>FA-000031</t>
+        </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -10091,7 +10087,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>MD-00032 stays In Use at Dallas (Cisco C9300, $6380). Employee E0032 (Active) matches the register holder. Log TR-00032: received 2026-03-22, approval APR-00032. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00032.</t>
+          <t>MD-00032 stays In Use at Dallas (Cisco C9300, $6380). Employee E0032 (Active) matches the register holder. Log TR-00032: received 2026-03-22, approval APR-00032. PO-2023-0006 / FA-000032 support the cost basis.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -10102,13 +10098,13 @@
       <c r="M36" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N36" s="7">
-        <f>IFERROR(XLOOKUP(A36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N36" s="7" t="n">
         <v>1384.3</v>
       </c>
-      <c r="O36" s="7">
-        <f>IFERROR(XLOOKUP(A36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>FA-000032</t>
+        </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -10203,7 +10199,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00033: In Use in Denver ($2075). Employee E0033 (Active) matches the register holder. Assignment TR-00033; receive column 04/22/2026, approval APR-00033. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00033.</t>
+          <t>Working conclusion for MD-00033: In Use in Denver ($2075). Employee E0033 (Active) matches the register holder. Assignment TR-00033; receive column 04/22/2026, approval APR-00033. FAR extract includes FA-000033 for MD-00033 via PO-2023-0006.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -10214,13 +10210,13 @@
       <c r="M37" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N37" s="7">
-        <f>IFERROR(XLOOKUP(A37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N37" s="7" t="n">
         <v>116.93</v>
       </c>
-      <c r="O37" s="7">
-        <f>IFERROR(XLOOKUP(A37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>FA-000033</t>
+        </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
@@ -10315,7 +10311,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00034 is In Use in New York office; basis $790. Employee E0034 (Active) matches the register holder. Transfer TR-00034 shows receipt May 22, 2026, approval APR-00034. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00034.</t>
+          <t>Dell U2723QE on MD-00034 is In Use in New York office; basis $790. Employee E0034 (Active) matches the register holder. Transfer TR-00034 shows receipt May 22, 2026, approval APR-00034. Cost path: PO-2023-0006 into FA-000034.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10326,13 +10322,13 @@
       <c r="M38" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N38" s="7">
-        <f>IFERROR(XLOOKUP(A38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N38" s="7" t="n">
         <v>514.88</v>
       </c>
-      <c r="O38" s="7">
-        <f>IFERROR(XLOOKUP(A38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>FA-000034</t>
+        </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
@@ -10427,7 +10423,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>MD-00035 shows In Use at Seattle (Samsung Galaxy S24, $950). Employee E0035 (Active) matches the register holder. Inbound stamp on TR-00035 is 2026-06-30, approval APR-00035. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00035.</t>
+          <t>MD-00035 shows In Use at Seattle (Samsung Galaxy S24, $950). Employee E0035 (Active) matches the register holder. Inbound stamp on TR-00035 is 2026-06-30, approval APR-00035. Procurement PO-2023-0006 maps to ledger FA-000035.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -10438,13 +10434,13 @@
       <c r="M39" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N39" s="7">
-        <f>IFERROR(XLOOKUP(A39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N39" s="7" t="n">
         <v>741.92</v>
       </c>
-      <c r="O39" s="7">
-        <f>IFERROR(XLOOKUP(A39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>FA-000035</t>
+        </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -10539,7 +10535,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>The cited records support In Use in Atlanta for MD-00036. Employee E0036 (Active) matches the register holder. Movement TR-00036 posted 2026-01-30 and inbound 02/01/2026, approval APR-00036. PO PO-2023-0006 on file; no matching FAR row for MD-00036.</t>
+          <t>The cited records support In Use in Atlanta for MD-00036. Employee E0036 (Active) matches the register holder. Movement TR-00036 posted 2026-01-30 and inbound 02/01/2026, approval APR-00036. FAR extract includes FA-000036 for MD-00036 via PO-2023-0006.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10550,13 +10546,13 @@
       <c r="M40" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N40" s="7">
-        <f>IFERROR(XLOOKUP(A40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N40" s="7" t="n">
         <v>537.73</v>
       </c>
-      <c r="O40" s="7">
-        <f>IFERROR(XLOOKUP(A40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>FA-000036</t>
+        </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -10651,7 +10647,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>MD-00037 remains In Use at Chicago (Lenovo ThinkPad T14, $1940). Employee E0037 (Active) matches the register holder. Log TR-00037: received Feb 02, 2026, approval APR-00037. PO PO-2024-0007 on file; no matching FAR row for MD-00037.</t>
+          <t>MD-00037 remains In Use at Chicago (Lenovo ThinkPad T14, $1940). Employee E0037 (Active) matches the register holder. Log TR-00037: received Feb 02, 2026, approval APR-00037. Capital trail MD-00037: PO-2024-0007 -&gt; FA-000037.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -10662,13 +10658,13 @@
       <c r="M41" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N41" s="7">
-        <f>IFERROR(XLOOKUP(A41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="7">
-        <f>IFERROR(XLOOKUP(A41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>FA-000037</t>
+        </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
@@ -10763,7 +10759,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>MD-00038 reconciled In Use with Dallas as the working site. Employee E0038 (Active) matches the register holder. Assignment TR-00038; receive column 2026-03-11, approval APR-00038. PO PO-2024-0007 on file; no matching FAR row for MD-00038.</t>
+          <t>MD-00038 reconciled In Use with Dallas as the working site. Employee E0038 (Active) matches the register holder. Assignment TR-00038; receive column 2026-03-11, approval APR-00038. PO-2024-0007 and FA-000038 agree on MD-00038.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10774,13 +10770,13 @@
       <c r="M42" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N42" s="7">
-        <f>IFERROR(XLOOKUP(A42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N42" s="7" t="n">
         <v>340.46</v>
       </c>
-      <c r="O42" s="7">
-        <f>IFERROR(XLOOKUP(A42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>FA-000038</t>
+        </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
@@ -10875,7 +10871,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00039 is In Use in floor Denver; basis $1130. Employee E0039 (Active) matches the register holder. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO PO-2024-0007 on file; no matching FAR row for MD-00039.</t>
+          <t>Samsung Galaxy S24 on MD-00039 is In Use in floor Denver; basis $1130. Employee E0039 (Active) matches the register holder. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO-2024-0007 / FA-000039 support the cost basis.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -10886,13 +10882,13 @@
       <c r="M43" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N43" s="7">
-        <f>IFERROR(XLOOKUP(A43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N43" s="7" t="n">
         <v>635</v>
       </c>
-      <c r="O43" s="7">
-        <f>IFERROR(XLOOKUP(A43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>FA-000039</t>
+        </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
@@ -10987,7 +10983,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>MD-00040 shows In Use at New York (Cisco C9300, $6425). Employee E0040 (Active) matches the register holder. Assignment TR-00040; receive column May 13, 2026, approval APR-00040. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00040.</t>
+          <t>MD-00040 shows In Use at New York (Cisco C9300, $6425). Employee E0040 (Active) matches the register holder. Assignment TR-00040; receive column May 13, 2026, approval APR-00040. Purchase order PO-2024-0007 and FAR row FA-000040 both cite MD-00040.</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -10998,13 +10994,13 @@
       <c r="M44" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N44" s="7">
-        <f>IFERROR(XLOOKUP(A44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N44" s="7" t="n">
         <v>989.48</v>
       </c>
-      <c r="O44" s="7">
-        <f>IFERROR(XLOOKUP(A44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>FA-000040</t>
+        </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -11099,7 +11095,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00041 is In Use in Seattle. Employee E0041 (Active) matches the register holder. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00041.</t>
+          <t>After HR and transfer review, MD-00041 is In Use in Seattle. Employee E0041 (Active) matches the register holder. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. Capital trail MD-00041: PO-2024-0007 -&gt; FA-000041.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -11110,13 +11106,13 @@
       <c r="M45" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N45" s="7">
-        <f>IFERROR(XLOOKUP(A45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="7">
-        <f>IFERROR(XLOOKUP(A45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>FA-000041</t>
+        </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -11211,7 +11207,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Inventory line MD-00042: In Use, Atlanta, $520 — Dell U2723QE. Employee E0042 (Active) matches the register holder. Inbound stamp on TR-00042 is 01/24/2026, approval APR-00042. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00042.</t>
+          <t>Inventory line MD-00042: In Use, Atlanta, $520 - Dell U2723QE. Employee E0042 (Active) matches the register holder. Inbound stamp on TR-00042 is 01/24/2026, approval APR-00042. PO-2024-0007 and FA-000042 agree on MD-00042.</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -11222,13 +11218,13 @@
       <c r="M46" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N46" s="7">
-        <f>IFERROR(XLOOKUP(A46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N46" s="7" t="n">
         <v>306.16</v>
       </c>
-      <c r="O46" s="7">
-        <f>IFERROR(XLOOKUP(A46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>FA-000042</t>
+        </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -11323,7 +11319,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00043 across CSV/XLSX inputs — In Use, Chicago. Employee E0043 (Active) matches the register holder. equipment_transfer_log TR-00043, approval APR-00043; received Mar 01, 2026. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00043.</t>
+          <t>Looked up MD-00043 across CSV/XLSX inputs - In Use, Chicago. Employee E0043 (Active) matches the register holder. equipment_transfer_log TR-00043, approval APR-00043; received Mar 01, 2026. Ledger FA-000043 backs PO-2025-0008 for MD-00043.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -11334,13 +11330,13 @@
       <c r="M47" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N47" s="7">
-        <f>IFERROR(XLOOKUP(A47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N47" s="7" t="n">
         <v>673.55</v>
       </c>
-      <c r="O47" s="7">
-        <f>IFERROR(XLOOKUP(A47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>FA-000043</t>
+        </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -11435,7 +11431,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Verified In Use for MD-00044 at Dallas; acquisition $6290. Employee E0044 (Active) matches the register holder. TR-00044 ties to MD-00044; dock date 2026-03-31, approval APR-00044. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00044.</t>
+          <t>Verified In Use for MD-00044 at Dallas; acquisition $6290. Employee E0044 (Active) matches the register holder. TR-00044 ties to MD-00044; dock date 2026-03-31, approval APR-00044. Purchase order PO-2025-0008 and FAR row FA-000044 both cite MD-00044.</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -11446,13 +11442,13 @@
       <c r="M48" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N48" s="7">
-        <f>IFERROR(XLOOKUP(A48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N48" s="7" t="n">
         <v>1406.1</v>
       </c>
-      <c r="O48" s="7">
-        <f>IFERROR(XLOOKUP(A48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>FA-000044</t>
+        </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -11547,7 +11543,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>MD-00045 reflects In Use at Denver (Dell Latitude 7440, $1985). Employee E0045 (Active) matches the register holder. TR-00045 for MD-00045 — received 05/03/2026, approval APR-00045. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00045.</t>
+          <t>MD-00045 reflects In Use at Denver (Dell Latitude 7440, $1985). Employee E0045 (Active) matches the register holder. TR-00045 for MD-00045 - received 05/03/2026, approval APR-00045. Capital trail MD-00045: PO-2025-0008 -&gt; FA-000045.</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -11558,13 +11554,13 @@
       <c r="M49" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N49" s="7">
-        <f>IFERROR(XLOOKUP(A49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N49" s="7" t="n">
         <v>133.6</v>
       </c>
-      <c r="O49" s="7">
-        <f>IFERROR(XLOOKUP(A49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>FA-000045</t>
+        </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -11655,7 +11651,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00046: Available in New York ($700). Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. PO PO-2025-0008 on file; no matching FAR row for MD-00046.</t>
+          <t>Working conclusion for MD-00046: Available in New York ($700). Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. Ledger FA-000046 backs PO-2025-0008 for MD-00046.</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -11666,13 +11662,13 @@
       <c r="M50" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N50" s="7">
-        <f>IFERROR(XLOOKUP(A50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N50" s="7" t="n">
         <v>460.82</v>
       </c>
-      <c r="O50" s="7">
-        <f>IFERROR(XLOOKUP(A50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>FA-000046</t>
+        </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
@@ -11763,7 +11759,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>MD-00047 stays Available at Seattle (Samsung Galaxy S24, $1175). Inbound stamp on TR-00047 is 2026-07-10, approval APR-00047. PO PO-2025-0008 on file; no matching FAR row for MD-00047.</t>
+          <t>MD-00047 stays Available at Seattle (Samsung Galaxy S24, $1175). Inbound stamp on TR-00047 is 2026-07-10, approval APR-00047. Purchase order PO-2025-0008 and FAR row FA-000047 both cite MD-00047.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -11774,13 +11770,13 @@
       <c r="M51" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N51" s="7">
-        <f>IFERROR(XLOOKUP(A51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N51" s="7" t="n">
         <v>930.51</v>
       </c>
-      <c r="O51" s="7">
-        <f>IFERROR(XLOOKUP(A51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>FA-000047</t>
+        </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -11871,7 +11867,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Atlanta: MD-00048 is Available; cost $6470. equipment_transfer_log TR-00048, approval APR-00048; received 01/24/2026. PO PO-2025-0008 on file; no matching FAR row for MD-00048.</t>
+          <t>Atlanta: MD-00048 is Available; cost $6470. equipment_transfer_log TR-00048, approval APR-00048; received 01/24/2026. Capital trail MD-00048: PO-2025-0008 -&gt; FA-000048.</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -11882,13 +11878,13 @@
       <c r="M52" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N52" s="7">
-        <f>IFERROR(XLOOKUP(A52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N52" s="7" t="n">
         <v>514.59</v>
       </c>
-      <c r="O52" s="7">
-        <f>IFERROR(XLOOKUP(A52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>FA-000048</t>
+        </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -11979,7 +11975,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Cost $1850 on MD-00049; Available at Chicago. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. Purchasing PO-2022-0009 without a capital line for MD-00049.</t>
+          <t>Cost $1850 on MD-00049; Available at Chicago. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. PO-2022-0009 and FA-000049 agree on MD-00049.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -11990,13 +11986,13 @@
       <c r="M53" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N53" s="7">
-        <f>IFERROR(XLOOKUP(A53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N53" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="7">
-        <f>IFERROR(XLOOKUP(A53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>FA-000049</t>
+        </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -12087,7 +12083,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Asset row MD-00050: Available, Dallas, $565 — Dell U2723QE. equipment_transfer_log TR-00050, approval APR-00050; received 2026-02-23. PO PO-2022-0009 on file; no matching FAR row for MD-00050.</t>
+          <t>Asset row MD-00050: Available, Dallas, $565 - Dell U2723QE. equipment_transfer_log TR-00050, approval APR-00050; received 2026-02-23. Ledger FA-000050 backs PO-2022-0009 for MD-00050.</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -12098,13 +12094,13 @@
       <c r="M54" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N54" s="7">
-        <f>IFERROR(XLOOKUP(A54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N54" s="7" t="n">
         <v>289.96</v>
       </c>
-      <c r="O54" s="7">
-        <f>IFERROR(XLOOKUP(A54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>FA-000050</t>
+        </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -12195,7 +12191,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Kept MD-00051 at Available in Denver; $1040 Samsung Galaxy S24. TR-00051 ties to MD-00051; dock date 03/31/2026, approval APR-00051. PO PO-2022-0009 on file; no matching FAR row for MD-00051.</t>
+          <t>Kept MD-00051 at Available in Denver; $1040 Samsung Galaxy S24. TR-00051 ties to MD-00051; dock date 03/31/2026, approval APR-00051. Purchase order PO-2022-0009 and FAR row FA-000051 both cite MD-00051.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -12206,13 +12202,13 @@
       <c r="M55" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N55" s="7">
-        <f>IFERROR(XLOOKUP(A55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N55" s="7" t="n">
         <v>573.03</v>
       </c>
-      <c r="O55" s="7">
-        <f>IFERROR(XLOOKUP(A55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>FA-000051</t>
+        </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
@@ -12303,7 +12299,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>MD-00052 reads Available at New York (Cisco C9300, $6335). TR-00052 for MD-00052 — received May 02, 2026, approval APR-00052. PO PO-2022-0009 on file; no matching FAR row for MD-00052.</t>
+          <t>MD-00052 reads Available at New York (Cisco C9300, $6335). TR-00052 for MD-00052 - received May 02, 2026, approval APR-00052. Capital trail MD-00052: PO-2022-0009 -&gt; FA-000052.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -12314,13 +12310,13 @@
       <c r="M56" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N56" s="7">
-        <f>IFERROR(XLOOKUP(A56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N56" s="7" t="n">
         <v>933.99</v>
       </c>
-      <c r="O56" s="7">
-        <f>IFERROR(XLOOKUP(A56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>FA-000052</t>
+        </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
@@ -12411,7 +12407,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00053 as Available (Seattle). Movement TR-00053 posted Jun 05, 2026 and inbound 2026-06-05, approval APR-00053. PO PO-2022-0009 on file; no matching FAR row for MD-00053.</t>
+          <t>Cross-file check left MD-00053 as Available (Seattle). Movement TR-00053 posted Jun 05, 2026 and inbound 2026-06-05, approval APR-00053. PO-2022-0009 and FA-000053 agree on MD-00053.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -12422,13 +12418,13 @@
       <c r="M57" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N57" s="7">
-        <f>IFERROR(XLOOKUP(A57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N57" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="7">
-        <f>IFERROR(XLOOKUP(A57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>FA-000053</t>
+        </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
@@ -12519,7 +12515,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>No stronger file contradicted Available for MD-00054 at Atlanta. Log TR-00054: received 01/16/2026, approval APR-00054. PO PO-2022-0009 on file; no matching FAR row for MD-00054.</t>
+          <t>No stronger file contradicted Available for MD-00054 at Atlanta. Log TR-00054: received 01/16/2026, approval APR-00054. PO-2022-0009 / FA-000054 support the cost basis.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -12530,13 +12526,13 @@
       <c r="M58" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N58" s="7">
-        <f>IFERROR(XLOOKUP(A58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N58" s="7" t="n">
         <v>433.74</v>
       </c>
-      <c r="O58" s="7">
-        <f>IFERROR(XLOOKUP(A58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>FA-000054</t>
+        </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
@@ -12627,7 +12623,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>MD-00055 sits Available at Chicago (Samsung Galaxy S24, $1220). Assignment TR-00055; receive column Feb 12, 2026, approval APR-00055. Purchasing PO-2023-0010 without a capital line for MD-00055.</t>
+          <t>MD-00055 sits Available at Chicago (Samsung Galaxy S24, $1220). Assignment TR-00055; receive column Feb 12, 2026, approval APR-00055. Ledger FA-000055 backs PO-2023-0010 for MD-00055.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -12638,13 +12634,13 @@
       <c r="M59" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N59" s="7">
-        <f>IFERROR(XLOOKUP(A59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N59" s="7" t="n">
         <v>812.5</v>
       </c>
-      <c r="O59" s="7">
-        <f>IFERROR(XLOOKUP(A59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>FA-000055</t>
+        </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
@@ -12735,7 +12731,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Available / Dallas on MD-00056 (Cisco C9300, $6200) per cited files. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00056.</t>
+          <t>Available / Dallas on MD-00056 (Cisco C9300, $6200) per cited files. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. Cost path: PO-2023-0010 into FA-000056.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -12746,13 +12742,13 @@
       <c r="M60" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N60" s="7">
-        <f>IFERROR(XLOOKUP(A60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N60" s="7" t="n">
         <v>1345.24</v>
       </c>
-      <c r="O60" s="7">
-        <f>IFERROR(XLOOKUP(A60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>FA-000056</t>
+        </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
@@ -12843,7 +12839,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>MD-00057 lists Available at Denver (Dell Latitude 7440, $1895). TR-00057 for MD-00057 — received 04/24/2026, approval APR-00057. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00057.</t>
+          <t>MD-00057 lists Available at Denver (Dell Latitude 7440, $1895). TR-00057 for MD-00057 - received 04/24/2026, approval APR-00057. Procurement PO-2023-0010 maps to ledger FA-000057.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -12854,13 +12850,13 @@
       <c r="M61" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N61" s="7">
-        <f>IFERROR(XLOOKUP(A61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N61" s="7" t="n">
         <v>106.79</v>
       </c>
-      <c r="O61" s="7">
-        <f>IFERROR(XLOOKUP(A61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>FA-000057</t>
+        </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -12955,7 +12951,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>Read MD-00058 against transfers before signing Pending Redeployment / New York. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
+          <t>Read MD-00058 against transfers before signing Pending Redeployment / New York. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. Ledger FA-000058 backs PO-2023-0010 for MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -12966,13 +12962,13 @@
       <c r="M62" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N62" s="7">
-        <f>IFERROR(XLOOKUP(A62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N62" s="7" t="n">
         <v>397.56</v>
       </c>
-      <c r="O62" s="7">
-        <f>IFERROR(XLOOKUP(A62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>FA-000058</t>
+        </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
@@ -13067,7 +13063,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00059 Pending Redeployment. Log TR-00059: received 2026-06-26, approval field blank. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00059. Also: offboarding ticket OFF-00059 referenced.</t>
+          <t>I read the movement and people files before calling MD-00059 Pending Redeployment. Log TR-00059: received 2026-06-26, approval field blank. Purchase order PO-2023-0010 and FAR row FA-000059 both cite MD-00059. Also: offboarding ticket OFF-00059 referenced.</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -13078,13 +13074,13 @@
       <c r="M63" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N63" s="7">
-        <f>IFERROR(XLOOKUP(A63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N63" s="7" t="n">
         <v>847.35</v>
       </c>
-      <c r="O63" s="7">
-        <f>IFERROR(XLOOKUP(A63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>FA-000059</t>
+        </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -13179,7 +13175,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>The cited records support Pending Redeployment in Atlanta for MD-00060. Movement TR-00060 posted 2026-01-30 and inbound 02/02/2026, approval APR-00060. Purchasing PO-2023-0010 without a capital line for MD-00060. Also: offboarding ticket OFF-00060 referenced.</t>
+          <t>The cited records support Pending Redeployment in Atlanta for MD-00060. Movement TR-00060 posted 2026-01-30 and inbound 02/02/2026, approval APR-00060. Cost path: PO-2023-0010 into FA-000060. Also: offboarding ticket OFF-00060 referenced.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -13190,13 +13186,13 @@
       <c r="M64" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N64" s="7">
-        <f>IFERROR(XLOOKUP(A64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N64" s="7" t="n">
         <v>549.35</v>
       </c>
-      <c r="O64" s="7">
-        <f>IFERROR(XLOOKUP(A64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>FA-000060</t>
+        </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -13291,7 +13287,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Chicago holds MD-00061 (Lenovo ThinkPad T14) as Pending Redeployment. Log TR-00061: received Feb 03, 2026, approval APR-00061. Purchasing PO-2024-0011 without a capital line for MD-00061. Also: offboarding ticket OFF-00061 referenced.</t>
+          <t>Chicago holds MD-00061 (Lenovo ThinkPad T14) as Pending Redeployment. Log TR-00061: received Feb 03, 2026, approval APR-00061. PO-2024-0011 and FA-000061 agree on MD-00061. Also: offboarding ticket OFF-00061 referenced.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -13302,13 +13298,13 @@
       <c r="M65" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N65" s="7">
-        <f>IFERROR(XLOOKUP(A65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N65" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="7">
-        <f>IFERROR(XLOOKUP(A65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>FA-000061</t>
+        </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
@@ -13403,7 +13399,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 (Dell U2723QE) closed Pending Redeployment / Dallas on $790. Assignment TR-00062; receive column 2026-03-07, approval APR-00062. Purchasing PO-2024-0011 without a capital line for MD-00062. Also: offboarding ticket OFF-00062 referenced.</t>
+          <t>MD-00062 (Dell U2723QE) closed Pending Redeployment / Dallas on $790. Assignment TR-00062; receive column 2026-03-07, approval APR-00062. PO-2024-0011 / FA-000062 support the cost basis. Also: offboarding ticket OFF-00062 referenced.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -13414,13 +13410,13 @@
       <c r="M66" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N66" s="7">
-        <f>IFERROR(XLOOKUP(A66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N66" s="7" t="n">
         <v>410.63</v>
       </c>
-      <c r="O66" s="7">
-        <f>IFERROR(XLOOKUP(A66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>FA-000062</t>
+        </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -13515,7 +13511,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Assignment trail and HR both fit Pending Redeployment for MD-00063 in Denver. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. Purchasing PO-2024-0011 without a capital line for MD-00063. Also: offboarding ticket OFF-00063 referenced.</t>
+          <t>Assignment trail and HR both fit Pending Redeployment for MD-00063 in Denver. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. FAR extract includes FA-000063 for MD-00063 via PO-2024-0011. Also: offboarding ticket OFF-00063 referenced.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -13526,13 +13522,13 @@
       <c r="M67" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N67" s="7">
-        <f>IFERROR(XLOOKUP(A67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N67" s="7" t="n">
         <v>533.85</v>
       </c>
-      <c r="O67" s="7">
-        <f>IFERROR(XLOOKUP(A67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>FA-000063</t>
+        </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -13627,7 +13623,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00064 as Pending Redeployment (New York). Inbound stamp on TR-00064 is May 14, 2026, approval field blank. Purchasing PO-2024-0011 without a capital line for MD-00064. Also: offboarding ticket OFF-00064 referenced.</t>
+          <t>Cross-file check left MD-00064 as Pending Redeployment (New York). Inbound stamp on TR-00064 is May 14, 2026, approval field blank. Cost path: PO-2024-0011 into FA-000064. Also: offboarding ticket OFF-00064 referenced.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -13638,13 +13634,13 @@
       <c r="M68" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N68" s="7">
-        <f>IFERROR(XLOOKUP(A68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N68" s="7" t="n">
         <v>961.76</v>
       </c>
-      <c r="O68" s="7">
-        <f>IFERROR(XLOOKUP(A68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>FA-000064</t>
+        </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -13739,7 +13735,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 still Pending Redeployment; Seattle is the verified site. equipment_transfer_log TR-00065, approval field blank; received 2026-06-23. Purchasing PO-2024-0011 without a capital line for MD-00065. Also: offboarding ticket OFF-00065 referenced.</t>
+          <t>MD-00065 still Pending Redeployment; Seattle is the verified site. equipment_transfer_log TR-00065, approval field blank; received 2026-06-23. Procurement PO-2024-0011 maps to ledger FA-000065. Also: offboarding ticket OFF-00065 referenced.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -13750,13 +13746,13 @@
       <c r="M69" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N69" s="7">
-        <f>IFERROR(XLOOKUP(A69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N69" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O69" s="7">
-        <f>IFERROR(XLOOKUP(A69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>FA-000065</t>
+        </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -13851,7 +13847,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00066 is Pending Redeployment in Atlanta office; basis $655. Log TR-00066: received 01/25/2026, approval APR-00066. PO-2024-0011 in hardware_purchase_orders.csv; FAR silent on MD-00066. Also: offboarding ticket OFF-00066 referenced.</t>
+          <t>Dell U2723QE on MD-00066 is Pending Redeployment in Atlanta office; basis $655. Log TR-00066: received 01/25/2026, approval APR-00066. FAR extract includes FA-000066 for MD-00066 via PO-2024-0011. Also: offboarding ticket OFF-00066 referenced.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -13862,13 +13858,13 @@
       <c r="M70" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N70" s="7">
-        <f>IFERROR(XLOOKUP(A70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N70" s="7" t="n">
         <v>385.65</v>
       </c>
-      <c r="O70" s="7">
-        <f>IFERROR(XLOOKUP(A70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>FA-000066</t>
+        </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -13963,7 +13959,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00067 across CSV/XLSX inputs — Pending Redeployment, Chicago. Assignment TR-00067; receive column Feb 23, 2026, approval APR-00067. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00067. Also: offboarding ticket OFF-00067 referenced.</t>
+          <t>Looked up MD-00067 across CSV/XLSX inputs - Pending Redeployment, Chicago. Assignment TR-00067; receive column Feb 23, 2026, approval APR-00067. Capital trail MD-00067: PO-2025-0012 -&gt; FA-000067. Also: offboarding ticket OFF-00067 referenced.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -13974,13 +13970,13 @@
       <c r="M71" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N71" s="7">
-        <f>IFERROR(XLOOKUP(A71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>764.93</v>
-      </c>
-      <c r="O71" s="7">
-        <f>IFERROR(XLOOKUP(A71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="N71" s="7" t="n">
+        <v>764.9299999999999</v>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>FA-000067</t>
+        </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -14011,7 +14007,7 @@
         </is>
       </c>
       <c r="V71" t="n">
-        <v>764.93</v>
+        <v>764.9299999999999</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -14075,7 +14071,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>MD-00068: Cisco C9300, $6425, status Return Overdue, site Remote - Former Employee. Employment file: E0081 remains Separated. Transfer TR-00068 shows receipt 2026-04-03, approval APR-00068. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00068. Also: carrier label 1ZMD00000068 is not proof of receipt. Note — offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
+          <t>MD-00068: Cisco C9300, $6425, status Return Overdue, site Remote - Former Employee. Employment file: E0081 remains Separated. Transfer TR-00068 shows receipt 2026-04-03, approval APR-00068. PO-2025-0012 and FA-000068 agree on MD-00068. Also: carrier label 1ZMD00000068 is not proof of receipt. Note - offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -14086,13 +14082,13 @@
       <c r="M72" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N72" s="7">
-        <f>IFERROR(XLOOKUP(A72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N72" s="7" t="n">
         <v>1436.28</v>
       </c>
-      <c r="O72" s="7">
-        <f>IFERROR(XLOOKUP(A72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>FA-000068</t>
+        </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -14187,7 +14183,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>MD-00069 carries Return Overdue at Remote - Former Employee (Dell Latitude 7440, $2120). Employment file: E0082 remains Separated. Inbound stamp on TR-00069 is 05/04/2026, approval APR-00069. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00069. Also: carrier label 1ZMD00000069 is not proof of receipt. Note — offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
+          <t>MD-00069 carries Return Overdue at Remote - Former Employee (Dell Latitude 7440, $2120). Employment file: E0082 remains Separated. Inbound stamp on TR-00069 is 05/04/2026, approval APR-00069. PO-2025-0012 / FA-000069 support the cost basis. Also: carrier label 1ZMD00000069 is not proof of receipt. Note - offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -14198,13 +14194,13 @@
       <c r="M73" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N73" s="7">
-        <f>IFERROR(XLOOKUP(A73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N73" s="7" t="n">
         <v>142.69</v>
       </c>
-      <c r="O73" s="7">
-        <f>IFERROR(XLOOKUP(A73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>FA-000069</t>
+        </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -14299,7 +14295,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 stays Return Overdue at Remote - Former Employee (Dell U2723QE, $520). HR agrees Hugh Talbot (E0083) is still Separated. Transfer TR-00070 shows receipt Jun 03, 2026, approval APR-00070. Purchasing PO-2025-0012 without a capital line for MD-00070. Also: carrier label 1ZMD00000070 is not proof of receipt. Note — offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
+          <t>MD-00070 stays Return Overdue at Remote - Former Employee (Dell U2723QE, $520). HR agrees Hugh Talbot (E0083) is still Separated. Transfer TR-00070 shows receipt Jun 03, 2026, approval APR-00070. Purchase order PO-2025-0012 and FAR row FA-000070 both cite MD-00070. Also: carrier label 1ZMD00000070 is not proof of receipt. Note - offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -14310,13 +14306,13 @@
       <c r="M74" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N74" s="7">
-        <f>IFERROR(XLOOKUP(A74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N74" s="7" t="n">
         <v>342.32</v>
       </c>
-      <c r="O74" s="7">
-        <f>IFERROR(XLOOKUP(A74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t>FA-000070</t>
+        </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -14411,7 +14407,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00071 is Return Overdue in Remote - Former Employee. HR agrees Mira Adelman (E0084) is still Separated. Inbound stamp on TR-00071 is 2026-07-12, approval APR-00071. Purchasing PO-2025-0012 without a capital line for MD-00071. Also: carrier label 1ZMD00000071 is not proof of receipt. Note — offboarding ticket OFF-00071 referenced. return still label-only per shipment file.</t>
+          <t>After HR and transfer review, MD-00071 is Return Overdue in Remote - Former Employee. HR agrees Mira Adelman (E0084) is still Separated. Inbound stamp on TR-00071 is 2026-07-12, approval APR-00071. Capital trail MD-00071: PO-2025-0012 -&gt; FA-000071. Also: carrier label 1ZMD00000071 is not proof of receipt. Note - offboarding ticket OFF-00071 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -14422,13 +14418,13 @@
       <c r="M75" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N75" s="7">
-        <f>IFERROR(XLOOKUP(A75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N75" s="7" t="n">
         <v>787.96</v>
       </c>
-      <c r="O75" s="7">
-        <f>IFERROR(XLOOKUP(A75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>FA-000071</t>
+        </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
@@ -14523,7 +14519,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>MD-00072 reflects Return Overdue at Remote - Former Employee (Cisco C9300, $6290). HR agrees Quincy Rhodes (E0085) is still Separated. equipment_transfer_log TR-00072, approval APR-00072; received 01/18/2026. Purchasing PO-2025-0012 without a capital line for MD-00072. Also: carrier label 1ZMD00000072 is not proof of receipt. Note — offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
+          <t>MD-00072 reflects Return Overdue at Remote - Former Employee (Cisco C9300, $6290). HR agrees Quincy Rhodes (E0085) is still Separated. equipment_transfer_log TR-00072, approval APR-00072; received 01/18/2026. PO-2025-0012 and FA-000072 agree on MD-00072. Also: carrier label 1ZMD00000072 is not proof of receipt. Note - offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -14534,13 +14530,13 @@
       <c r="M76" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N76" s="7">
-        <f>IFERROR(XLOOKUP(A76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N76" s="7" t="n">
         <v>500.27</v>
       </c>
-      <c r="O76" s="7">
-        <f>IFERROR(XLOOKUP(A76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t>FA-000072</t>
+        </is>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
@@ -14635,7 +14631,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>Did not move MD-00073 off Return Overdue at Remote - Former Employee without a transaction. HR agrees Sloane Richter (E0086) is still Separated. TR-00073 ties to MD-00073; dock date Jan 24, 2026, approval APR-00073. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00073. Also: carrier label 1ZMD00000073 is not proof of receipt. Note — offboarding ticket OFF-00073 referenced. return still label-only per shipment file.</t>
+          <t>Did not move MD-00073 off Return Overdue at Remote - Former Employee without a transaction. HR agrees Sloane Richter (E0086) is still Separated. TR-00073 ties to MD-00073; dock date Jan 24, 2026, approval APR-00073. PO-2022-0013 / FA-000073 support the cost basis. Also: carrier label 1ZMD00000073 is not proof of receipt. Note - offboarding ticket OFF-00073 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -14646,13 +14642,13 @@
       <c r="M77" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N77" s="7">
-        <f>IFERROR(XLOOKUP(A77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N77" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O77" s="7">
-        <f>IFERROR(XLOOKUP(A77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>FA-000073</t>
+        </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
@@ -14747,7 +14743,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 lists Return Overdue at Carrier Network / Unverified (Dell U2723QE, $700). HR agrees Nolan Vega (E0087) is still Separated. TR-00074 for MD-00074 — received 2026-02-24, approval APR-00074. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00074. Also: carrier label 1ZMD00000074 is not proof of receipt. Note — offboarding ticket OFF-00074 referenced. return still label-only per shipment file. shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
+          <t>MD-00074 lists Return Overdue at Carrier Network / Unverified (Dell U2723QE, $700). HR agrees Nolan Vega (E0087) is still Separated. TR-00074 for MD-00074 - received 2026-02-24, approval APR-00074. FAR extract includes FA-000074 for MD-00074 via PO-2022-0013. Also: carrier label 1ZMD00000074 is not proof of receipt. Note - offboarding ticket OFF-00074 referenced. return still label-only per shipment file. shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -14758,13 +14754,13 @@
       <c r="M78" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N78" s="7">
-        <f>IFERROR(XLOOKUP(A78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N78" s="7" t="n">
         <v>359.25</v>
       </c>
-      <c r="O78" s="7">
-        <f>IFERROR(XLOOKUP(A78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t>FA-000074</t>
+        </is>
       </c>
       <c r="P78" s="7" t="inlineStr">
         <is>
@@ -14859,7 +14855,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee: MD-00075 is Return Overdue; cost $1175. HR agrees Ivy Chenoweth (E0088) is still Separated. Movement TR-00075 posted 2026-03-31 and inbound 04/01/2026, approval APR-00075. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00075. Also: carrier label 1ZMD00000075 is not proof of receipt. Note — offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
+          <t>Remote - Former Employee: MD-00075 is Return Overdue; cost $1175. HR agrees Ivy Chenoweth (E0088) is still Separated. Movement TR-00075 posted 2026-03-31 and inbound 04/01/2026, approval APR-00075. Cost path: PO-2022-0013 into FA-000075. Also: carrier label 1ZMD00000075 is not proof of receipt. Note - offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -14870,13 +14866,13 @@
       <c r="M79" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N79" s="7">
-        <f>IFERROR(XLOOKUP(A79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N79" s="7" t="n">
         <v>647.42</v>
       </c>
-      <c r="O79" s="7">
-        <f>IFERROR(XLOOKUP(A79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>FA-000075</t>
+        </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
@@ -14971,7 +14967,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 reads Return Overdue at Carrier Network / Unverified (Cisco C9300, $6470). HR agrees Percy Lambert (E0089) is still Separated. Inbound stamp on TR-00076 is May 03, 2026, approval APR-00076. PO PO-2022-0013 on file; no matching FAR row for MD-00076. Also: carrier label 1ZMD00000076 is not proof of receipt. Note — offboarding ticket OFF-00076 referenced. return still label-only per shipment file. shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
+          <t>MD-00076 reads Return Overdue at Carrier Network / Unverified (Cisco C9300, $6470). HR agrees Percy Lambert (E0089) is still Separated. Inbound stamp on TR-00076 is May 03, 2026, approval APR-00076. PO-2022-0013 / FA-000076 support the cost basis. Also: carrier label 1ZMD00000076 is not proof of receipt. Note - offboarding ticket OFF-00076 referenced. return still label-only per shipment file. shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -14982,13 +14978,13 @@
       <c r="M80" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N80" s="7">
-        <f>IFERROR(XLOOKUP(A80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N80" s="7" t="n">
         <v>953.89</v>
       </c>
-      <c r="O80" s="7">
-        <f>IFERROR(XLOOKUP(A80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t>FA-000076</t>
+        </is>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
@@ -15083,7 +15079,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>The cited records support Return Overdue in Remote - Former Employee for MD-00077. Employment file: E0090 remains Separated. equipment_transfer_log TR-00077, approval APR-00077; received 2026-06-06. PO PO-2022-0013 on file; no matching FAR row for MD-00077. Also: carrier label 1ZMD00000077 is not proof of receipt. Note — offboarding ticket OFF-00077 referenced. return still label-only per shipment file.</t>
+          <t>The cited records support Return Overdue in Remote - Former Employee for MD-00077. Employment file: E0090 remains Separated. equipment_transfer_log TR-00077, approval APR-00077; received 2026-06-06. FAR extract includes FA-000077 for MD-00077 via PO-2022-0013. Also: carrier label 1ZMD00000077 is not proof of receipt. Note - offboarding ticket OFF-00077 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -15094,13 +15090,13 @@
       <c r="M81" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N81" s="7">
-        <f>IFERROR(XLOOKUP(A81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N81" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O81" s="7">
-        <f>IFERROR(XLOOKUP(A81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>FA-000077</t>
+        </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
@@ -15195,7 +15191,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee holds MD-00078 (Dell U2723QE) as Return Overdue. Employment file: E0091 remains Separated. TR-00078 ties to MD-00078; dock date 01/10/2026, approval APR-00078. PO PO-2022-0013 on file; no matching FAR row for MD-00078. Also: carrier label 1ZMD00000078 is not proof of receipt. Note — offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
+          <t>Remote - Former Employee holds MD-00078 (Dell U2723QE) as Return Overdue. Employment file: E0091 remains Separated. TR-00078 ties to MD-00078; dock date 01/10/2026, approval APR-00078. Cost path: PO-2022-0013 into FA-000078. Also: carrier label 1ZMD00000078 is not proof of receipt. Note - offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -15206,13 +15202,13 @@
       <c r="M82" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N82" s="7">
-        <f>IFERROR(XLOOKUP(A82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N82" s="7" t="n">
         <v>328.95</v>
       </c>
-      <c r="O82" s="7">
-        <f>IFERROR(XLOOKUP(A82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
+          <t>FA-000078</t>
+        </is>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -15307,7 +15303,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>MD-00079 (Samsung Galaxy S24) closed Return Overdue / Remote - Former Employee on $1040. Employment file: E0092 remains Separated. TR-00079 for MD-00079 — received Feb 13, 2026, approval APR-00079. PO PO-2023-0014 on file; no matching FAR row for MD-00079. Also: carrier label 1ZMD00000079 is not proof of receipt. Note — offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
+          <t>MD-00079 (Samsung Galaxy S24) closed Return Overdue / Remote - Former Employee on $1040. Employment file: E0092 remains Separated. TR-00079 for MD-00079 - received Feb 13, 2026, approval APR-00079. PO-2023-0014 and FA-000079 agree on MD-00079. Also: carrier label 1ZMD00000079 is not proof of receipt. Note - offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -15318,13 +15314,13 @@
       <c r="M83" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N83" s="7">
-        <f>IFERROR(XLOOKUP(A83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N83" s="7" t="n">
         <v>692.62</v>
       </c>
-      <c r="O83" s="7">
-        <f>IFERROR(XLOOKUP(A83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>FA-000079</t>
+        </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
@@ -15419,7 +15415,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>Atlanta Warehouse holds MD-00080 (Cisco C9300) as Available. TR-00080 ties to MD-00080; dock date 2026-03-17, approval APR-00080. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00080. Also: carrier label 1ZMD00000080 is not proof of receipt. Note — offboarding ticket OFF-00080 referenced.</t>
+          <t>Atlanta Warehouse holds MD-00080 (Cisco C9300) as Available. TR-00080 ties to MD-00080; dock date 2026-03-17, approval APR-00080. Ledger FA-000080 backs PO-2023-0014 for MD-00080. Also: carrier label 1ZMD00000080 is not proof of receipt. Note - offboarding ticket OFF-00080 referenced.</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -15430,13 +15426,13 @@
       <c r="M84" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N84" s="7">
-        <f>IFERROR(XLOOKUP(A84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N84" s="7" t="n">
         <v>1374.53</v>
       </c>
-      <c r="O84" s="7">
-        <f>IFERROR(XLOOKUP(A84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>FA-000080</t>
+        </is>
       </c>
       <c r="P84" s="7" t="inlineStr">
         <is>
@@ -15531,7 +15527,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 on MD-00081 is Available in floor Atlanta Warehouse; basis $2030. TR-00081 for MD-00081 — received 04/20/2026, approval APR-00081. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00081. Also: carrier label 1ZMD00000081 is not proof of receipt. Note — offboarding ticket OFF-00081 referenced.</t>
+          <t>Dell Latitude 7440 on MD-00081 is Available in floor Atlanta Warehouse; basis $2030. TR-00081 for MD-00081 - received 04/20/2026, approval APR-00081. Purchase order PO-2023-0014 and FAR row FA-000081 both cite MD-00081. Also: carrier label 1ZMD00000081 is not proof of receipt. Note - offboarding ticket OFF-00081 referenced.</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -15542,13 +15538,13 @@
       <c r="M85" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N85" s="7">
-        <f>IFERROR(XLOOKUP(A85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N85" s="7" t="n">
         <v>114.4</v>
       </c>
-      <c r="O85" s="7">
-        <f>IFERROR(XLOOKUP(A85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>FA-000081</t>
+        </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
@@ -15643,7 +15639,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00082 In Transit - Exception @ Carrier Network / Unverified. HR agrees Emmett Boyle (E0095) is still Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00082. Also: carrier label 1ZMD00000082 is not proof of receipt. Note — offboarding ticket OFF-00082 referenced. shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
+          <t>Field review: MD-00082 In Transit - Exception @ Carrier Network / Unverified. HR agrees Emmett Boyle (E0095) is still Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. Capital trail MD-00082: PO-2023-0014 -&gt; FA-000082. Also: carrier label 1ZMD00000082 is not proof of receipt. Note - offboarding ticket OFF-00082 referenced. shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -15654,13 +15650,13 @@
       <c r="M86" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N86" s="7">
-        <f>IFERROR(XLOOKUP(A86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N86" s="7" t="n">
         <v>485.55</v>
       </c>
-      <c r="O86" s="7">
-        <f>IFERROR(XLOOKUP(A86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>FA-000082</t>
+        </is>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -15755,7 +15751,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 remains Available at Atlanta Warehouse (Samsung Galaxy S24, $1220). Log TR-00083: received 2026-06-27, approval APR-00083. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00083. Also: carrier label 1ZMD00000083 is not proof of receipt. Note — offboarding ticket OFF-00083 referenced.</t>
+          <t>MD-00083 remains Available at Atlanta Warehouse (Samsung Galaxy S24, $1220). Log TR-00083: received 2026-06-27, approval APR-00083. PO-2023-0014 and FA-000083 agree on MD-00083. Also: carrier label 1ZMD00000083 is not proof of receipt. Note - offboarding ticket OFF-00083 referenced.</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -15766,13 +15762,13 @@
       <c r="M87" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N87" s="7">
-        <f>IFERROR(XLOOKUP(A87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N87" s="7" t="n">
         <v>952.79</v>
       </c>
-      <c r="O87" s="7">
-        <f>IFERROR(XLOOKUP(A87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>FA-000083</t>
+        </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -15867,7 +15863,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Carrier Network / Unverified: MD-00084 is In Transit - Exception; cost $6200. Anita Bose has Separated status in the people extract. Assignment TR-00084; receive column 02/05/2026, approval APR-00084. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00084. Also: carrier label 1ZMD00000084 is not proof of receipt. Note — offboarding ticket OFF-00084 referenced. shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
+          <t>Carrier Network / Unverified: MD-00084 is In Transit - Exception; cost $6200. Anita Bose has Separated status in the people extract. Assignment TR-00084; receive column 02/05/2026, approval APR-00084. PO-2023-0014 / FA-000084 support the cost basis. Also: carrier label 1ZMD00000084 is not proof of receipt. Note - offboarding ticket OFF-00084 referenced. shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -15878,13 +15874,13 @@
       <c r="M88" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N88" s="7">
-        <f>IFERROR(XLOOKUP(A88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N88" s="7" t="n">
         <v>533.85</v>
       </c>
-      <c r="O88" s="7">
-        <f>IFERROR(XLOOKUP(A88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t>FA-000084</t>
+        </is>
       </c>
       <c r="P88" s="7" t="inlineStr">
         <is>
@@ -15979,7 +15975,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 still Available; Atlanta Warehouse is the verified site. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. PO-2024-0015 in hardware_purchase_orders.csv; FAR silent on MD-00085. Also: carrier label 1ZMD00000085 is not proof of receipt. Note — offboarding ticket OFF-00085 referenced.</t>
+          <t>MD-00085 still Available; Atlanta Warehouse is the verified site. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. Purchase order PO-2024-0015 and FAR row FA-000085 both cite MD-00085. Also: carrier label 1ZMD00000085 is not proof of receipt. Note - offboarding ticket OFF-00085 referenced.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -15990,13 +15986,13 @@
       <c r="M89" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N89" s="7">
-        <f>IFERROR(XLOOKUP(A89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N89" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="7">
-        <f>IFERROR(XLOOKUP(A89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t>FA-000085</t>
+        </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -16091,7 +16087,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00086 is Available in Atlanta Warehouse office; basis $610. TR-00086 for MD-00086 — received 2026-03-08, approval APR-00086. PO PO-2024-0015 on file; no matching FAR row for MD-00086. Also: carrier label 1ZMD00000086 is not proof of receipt. Note — offboarding ticket OFF-00086 referenced.</t>
+          <t>Dell U2723QE on MD-00086 is Available in Atlanta Warehouse office; basis $610. TR-00086 for MD-00086 - received 2026-03-08, approval APR-00086. Procurement PO-2024-0015 maps to ledger FA-000086. Also: carrier label 1ZMD00000086 is not proof of receipt. Note - offboarding ticket OFF-00086 referenced.</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -16102,13 +16098,13 @@
       <c r="M90" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N90" s="7">
-        <f>IFERROR(XLOOKUP(A90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N90" s="7" t="n">
         <v>317.07</v>
       </c>
-      <c r="O90" s="7">
-        <f>IFERROR(XLOOKUP(A90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>FA-000086</t>
+        </is>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -16203,7 +16199,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00087: Available in Atlanta Warehouse ($1085). Movement TR-00087 posted 2026-04-12 and inbound 04/12/2026, approval APR-00087. PO PO-2024-0015 on file; no matching FAR row for MD-00087. Also: carrier label 1ZMD00000087 is not proof of receipt. Note — offboarding ticket OFF-00087 referenced.</t>
+          <t>Working conclusion for MD-00087: Available in Atlanta Warehouse ($1085). Movement TR-00087 posted 2026-04-12 and inbound 04/12/2026, approval APR-00087. Ledger FA-000087 backs PO-2024-0015 for MD-00087. Also: carrier label 1ZMD00000087 is not proof of receipt. Note - offboarding ticket OFF-00087 referenced.</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -16214,13 +16210,13 @@
       <c r="M91" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N91" s="7">
-        <f>IFERROR(XLOOKUP(A91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N91" s="7" t="n">
         <v>609.71</v>
       </c>
-      <c r="O91" s="7">
-        <f>IFERROR(XLOOKUP(A91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>FA-000087</t>
+        </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -16315,7 +16311,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>MD-00088 stays Available at Atlanta Warehouse (Cisco C9300, $6380). Log TR-00088: received May 14, 2026, approval APR-00088. PO PO-2024-0015 on file; no matching FAR row for MD-00088. Also: carrier label 1ZMD00000088 is not proof of receipt. Note — offboarding ticket OFF-00088 referenced. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>MD-00088 stays Available at Atlanta Warehouse (Cisco C9300, $6380). Log TR-00088: received May 14, 2026, approval APR-00088. Purchase order PO-2024-0015 and FAR row FA-000088 both cite MD-00088. Also: carrier label 1ZMD00000088 is not proof of receipt. Note - offboarding ticket OFF-00088 referenced. duplicate serial MD-NE-050088 flagged on the register.</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -16326,13 +16322,13 @@
       <c r="M92" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N92" s="7">
-        <f>IFERROR(XLOOKUP(A92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N92" s="7" t="n">
         <v>982.55</v>
       </c>
-      <c r="O92" s="7">
-        <f>IFERROR(XLOOKUP(A92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
+          <t>FA-000088</t>
+        </is>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -16427,7 +16423,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00089: Missing, Unknown, $2075 — MacBook Pro 14. Jonah Freedman has Separated status in the people extract. Assignment TR-00089; receive column 2026-06-17, approval APR-00089. PO PO-2024-0015 on file; no matching FAR row for MD-00089. Also: offboarding ticket OFF-00089 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Corrected row MD-00089: Missing, Unknown, $2075 - MacBook Pro 14. Jonah Freedman has Separated status in the people extract. Assignment TR-00089; receive column 2026-06-17, approval APR-00089. Capital trail MD-00089: PO-2024-0015 -&gt; FA-000089. Also: offboarding ticket OFF-00089 referenced. Note - last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -16438,13 +16434,13 @@
       <c r="M93" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N93" s="7">
-        <f>IFERROR(XLOOKUP(A93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N93" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="7">
-        <f>IFERROR(XLOOKUP(A93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>FA-000089</t>
+        </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -16539,7 +16535,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00090 Missing. People side — Regina Lowe (E0078), Separated. Log TR-00090: received 01/28/2026, approval APR-00090. PO-2024-0015 in hardware_purchase_orders.csv; FAR silent on MD-00090. Also: offboarding ticket OFF-00090 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>I read the movement and people files before calling MD-00090 Missing. People side - Regina Lowe (E0078), Separated. Log TR-00090: received 01/28/2026, approval APR-00090. Procurement PO-2024-0015 maps to ledger FA-000090. Also: offboarding ticket OFF-00090 referenced. Note - last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -16550,13 +16546,13 @@
       <c r="M94" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N94" s="7">
-        <f>IFERROR(XLOOKUP(A94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N94" s="7" t="n">
         <v>465.13</v>
       </c>
-      <c r="O94" s="7">
-        <f>IFERROR(XLOOKUP(A94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>FA-000090</t>
+        </is>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
@@ -16651,7 +16647,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Unknown: MD-00091 is Missing; cost $950. People side — Wes Carvalho (E0079), Separated. Assignment TR-00091; receive column Feb 24, 2026, approval APR-00091. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00091. Also: offboarding ticket OFF-00091 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Unknown: MD-00091 is Missing; cost $950. People side - Wes Carvalho (E0079), Separated. Assignment TR-00091; receive column Feb 24, 2026, approval APR-00091. PO-2025-0016 / FA-000091 support the cost basis. Also: offboarding ticket OFF-00091 referenced. Note - last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -16662,13 +16658,13 @@
       <c r="M95" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N95" s="7">
-        <f>IFERROR(XLOOKUP(A95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N95" s="7" t="n">
         <v>643.09</v>
       </c>
-      <c r="O95" s="7">
-        <f>IFERROR(XLOOKUP(A95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>FA-000091</t>
+        </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
@@ -16763,7 +16759,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00092 is Missing in Unknown. Tara Singh has Separated status in the people extract. Transfer TR-00092 shows receipt 2026-03-28, approval APR-00092. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00092. Also: offboarding ticket OFF-00092 referenced. Note — last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>After HR and transfer review, MD-00092 is Missing in Unknown. Tara Singh has Separated status in the people extract. Transfer TR-00092 shows receipt 2026-03-28, approval APR-00092. FAR extract includes FA-000092 for MD-00092 via PO-2025-0016. Also: offboarding ticket OFF-00092 referenced. Note - last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -16774,13 +16770,13 @@
       <c r="M96" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N96" s="7">
-        <f>IFERROR(XLOOKUP(A96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N96" s="7" t="n">
         <v>1396.04</v>
       </c>
-      <c r="O96" s="7">
-        <f>IFERROR(XLOOKUP(A96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>FA-000092</t>
+        </is>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
@@ -16875,7 +16871,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00093 Missing @ Unknown. Elliott Park has Separated status in the people extract. Inbound stamp on TR-00093 is 05/06/2026, approval APR-00093. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00093. Also: offboarding ticket OFF-00093 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Field review: MD-00093 Missing @ Unknown. Elliott Park has Separated status in the people extract. Inbound stamp on TR-00093 is 05/06/2026, approval APR-00093. Cost path: PO-2025-0016 into FA-000093. Also: offboarding ticket OFF-00093 referenced. Note - last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -16886,13 +16882,13 @@
       <c r="M97" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N97" s="7">
-        <f>IFERROR(XLOOKUP(A97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N97" s="7" t="n">
         <v>130.57</v>
       </c>
-      <c r="O97" s="7">
-        <f>IFERROR(XLOOKUP(A97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>FA-000093</t>
+        </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -16987,7 +16983,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00094 tied to $655; location Unknown; status Missing. Carmen Diaz has Separated status in the people extract. equipment_transfer_log TR-00094, approval APR-00094; received Jun 04, 2026. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00094. Also: offboarding ticket OFF-00094 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>Dell U2723QE MD-00094 tied to $655; location Unknown; status Missing. Carmen Diaz has Separated status in the people extract. equipment_transfer_log TR-00094, approval APR-00094; received Jun 04, 2026. Procurement PO-2025-0016 maps to ledger FA-000094. Also: offboarding ticket OFF-00094 referenced. Note - last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -16998,13 +16994,13 @@
       <c r="M98" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N98" s="7">
-        <f>IFERROR(XLOOKUP(A98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N98" s="7" t="n">
         <v>431.2</v>
       </c>
-      <c r="O98" s="7">
-        <f>IFERROR(XLOOKUP(A98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>FA-000094</t>
+        </is>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -17099,7 +17095,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Cost $1130 on MD-00095; Missing at Unknown. Hugh Talbot has Separated status in the people extract. TR-00095 ties to MD-00095; dock date 2026-07-08, approval APR-00095. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00095. Also: offboarding ticket OFF-00095 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Cost $1130 on MD-00095; Missing at Unknown. Hugh Talbot has Separated status in the people extract. TR-00095 ties to MD-00095; dock date 2026-07-08, approval APR-00095. Ledger FA-000095 backs PO-2025-0016 for MD-00095. Also: offboarding ticket OFF-00095 referenced. Note - last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -17110,13 +17106,13 @@
       <c r="M99" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N99" s="7">
-        <f>IFERROR(XLOOKUP(A99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N99" s="7" t="n">
         <v>894.87</v>
       </c>
-      <c r="O99" s="7">
-        <f>IFERROR(XLOOKUP(A99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>FA-000095</t>
+        </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -17211,7 +17207,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>MD-00096 stays Missing at Unknown (Cisco C9300, $6425). Mira Adelman has Separated status in the people extract. Log TR-00096: received 01/19/2026, approval APR-00096. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00096. Also: offboarding ticket OFF-00096 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>MD-00096 stays Missing at Unknown (Cisco C9300, $6425). Mira Adelman has Separated status in the people extract. Log TR-00096: received 01/19/2026, approval APR-00096. Procurement PO-2025-0016 maps to ledger FA-000096. Also: offboarding ticket OFF-00096 referenced. Note - last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -17222,13 +17218,13 @@
       <c r="M100" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N100" s="7">
-        <f>IFERROR(XLOOKUP(A100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N100" s="7" t="n">
         <v>511.01</v>
       </c>
-      <c r="O100" s="7">
-        <f>IFERROR(XLOOKUP(A100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>FA-000096</t>
+        </is>
       </c>
       <c r="P100" s="7" t="inlineStr">
         <is>
@@ -17323,7 +17319,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 stays Missing at Unknown (Lenovo ThinkPad T14, $2120). Quincy Rhodes has Separated status in the people extract. TR-00097 ties to MD-00097; dock date Jan 27, 2026, approval APR-00097. Purchasing PO-2022-0017 without a capital line for MD-00097. Also: offboarding ticket OFF-00097 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>MD-00097 stays Missing at Unknown (Lenovo ThinkPad T14, $2120). Quincy Rhodes has Separated status in the people extract. TR-00097 ties to MD-00097; dock date Jan 27, 2026, approval APR-00097. Ledger FA-000097 backs PO-2022-0017 for MD-00097. Also: offboarding ticket OFF-00097 referenced. Note - last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -17334,13 +17330,13 @@
       <c r="M101" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N101" s="7">
-        <f>IFERROR(XLOOKUP(A101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N101" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O101" s="7">
-        <f>IFERROR(XLOOKUP(A101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>FA-000097</t>
+        </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
@@ -17435,7 +17431,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>MD-00098 stays Missing at Unknown (Dell U2723QE, $520). Sloane Richter has Separated status in the people extract. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. Purchasing PO-2022-0017 without a capital line for MD-00098. Also: offboarding ticket OFF-00098 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>MD-00098 stays Missing at Unknown (Dell U2723QE, $520). Sloane Richter has Separated status in the people extract. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. Purchase order PO-2022-0017 and FAR row FA-000098 both cite MD-00098. Also: offboarding ticket OFF-00098 referenced. Note - last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -17446,13 +17442,13 @@
       <c r="M102" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N102" s="7">
-        <f>IFERROR(XLOOKUP(A102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N102" s="7" t="n">
         <v>266.87</v>
       </c>
-      <c r="O102" s="7">
-        <f>IFERROR(XLOOKUP(A102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>FA-000098</t>
+        </is>
       </c>
       <c r="P102" s="7" t="inlineStr">
         <is>
@@ -17547,7 +17543,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>MD-00099 stays Missing at Unknown (Samsung Galaxy S24, $995). Nolan Vega has Separated status in the people extract. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. Purchasing PO-2022-0017 without a capital line for MD-00099. Also: offboarding ticket OFF-00099 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>MD-00099 stays Missing at Unknown (Samsung Galaxy S24, $995). Nolan Vega has Separated status in the people extract. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. Capital trail MD-00099: PO-2022-0017 -&gt; FA-000099. Also: offboarding ticket OFF-00099 referenced. Note - last operational site on register was Denver - Closed.</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -17558,13 +17554,13 @@
       <c r="M103" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N103" s="7">
-        <f>IFERROR(XLOOKUP(A103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N103" s="7" t="n">
         <v>548.24</v>
       </c>
-      <c r="O103" s="7">
-        <f>IFERROR(XLOOKUP(A103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>FA-000099</t>
+        </is>
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
@@ -17659,7 +17655,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00100 Missing @ Unknown. Ivy Chenoweth has Separated status in the people extract. equipment_transfer_log TR-00100, approval APR-00100; received May 05, 2026. Purchasing PO-2022-0017 without a capital line for MD-00100. Also: offboarding ticket OFF-00100 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>Field review: MD-00100 Missing @ Unknown. Ivy Chenoweth has Separated status in the people extract. equipment_transfer_log TR-00100, approval APR-00100; received May 05, 2026. PO-2022-0017 and FA-000100 agree on MD-00100. Also: offboarding ticket OFF-00100 referenced. Note - last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -17670,13 +17666,13 @@
       <c r="M104" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N104" s="7">
-        <f>IFERROR(XLOOKUP(A104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N104" s="7" t="n">
         <v>927.36</v>
       </c>
-      <c r="O104" s="7">
-        <f>IFERROR(XLOOKUP(A104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>FA-000100</t>
+        </is>
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
@@ -17771,7 +17767,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 stays Retired/Pending Disposal at Seattle (MacBook Pro 14, $1985). Assignment TR-00101; receive column 2026-06-07, approval APR-00101. Purchasing PO-2022-0017 without a capital line for MD-00101. Also: offboarding ticket RET-00101 referenced.</t>
+          <t>MD-00101 stays Retired/Pending Disposal at Seattle (MacBook Pro 14, $1985). Assignment TR-00101; receive column 2026-06-07, approval APR-00101. PO-2022-0017 / FA-000101 support the cost basis. Also: offboarding ticket RET-00101 referenced.</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -17782,13 +17778,13 @@
       <c r="M105" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N105" s="7">
-        <f>IFERROR(XLOOKUP(A105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N105" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O105" s="7">
-        <f>IFERROR(XLOOKUP(A105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>FA-000101</t>
+        </is>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -17883,7 +17879,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 stays Retired/Pending Disposal at Atlanta (Dell U2723QE, $700). TR-00102 for MD-00102 — received 01/11/2026, approval APR-00102. Purchasing PO-2022-0017 without a capital line for MD-00102. Also: offboarding ticket RET-00102 referenced.</t>
+          <t>MD-00102 stays Retired/Pending Disposal at Atlanta (Dell U2723QE, $700). TR-00102 for MD-00102 - received 01/11/2026, approval APR-00102. FAR extract includes FA-000102 for MD-00102 via PO-2022-0017. Also: offboarding ticket RET-00102 referenced.</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -17894,13 +17890,13 @@
       <c r="M106" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N106" s="7">
-        <f>IFERROR(XLOOKUP(A106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N106" s="7" t="n">
         <v>407.54</v>
       </c>
-      <c r="O106" s="7">
-        <f>IFERROR(XLOOKUP(A106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>FA-000102</t>
+        </is>
       </c>
       <c r="P106" s="7" t="inlineStr">
         <is>
@@ -17995,7 +17991,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>MD-00103 stays Retired/Pending Disposal at Chicago (Samsung Galaxy S24, $1175). Inbound stamp on TR-00103 is Feb 14, 2026, approval APR-00103. Purchasing PO-2023-0018 without a capital line for MD-00103. Also: offboarding ticket RET-00103 referenced.</t>
+          <t>MD-00103 stays Retired/Pending Disposal at Chicago (Samsung Galaxy S24, $1175). Inbound stamp on TR-00103 is Feb 14, 2026, approval APR-00103. Capital trail MD-00103: PO-2023-0018 -&gt; FA-000103. Also: offboarding ticket RET-00103 referenced.</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -18006,13 +18002,13 @@
       <c r="M107" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N107" s="7">
-        <f>IFERROR(XLOOKUP(A107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N107" s="7" t="n">
         <v>782.53</v>
       </c>
-      <c r="O107" s="7">
-        <f>IFERROR(XLOOKUP(A107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>FA-000103</t>
+        </is>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
@@ -18107,7 +18103,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>MD-00104 stays Retired/Pending Disposal at Dallas (Cisco C9300, $6470). Log TR-00104: received 2026-03-18, approval APR-00104. Purchasing PO-2023-0018 without a capital line for MD-00104. Also: offboarding ticket RET-00104 referenced.</t>
+          <t>MD-00104 stays Retired/Pending Disposal at Dallas (Cisco C9300, $6470). Log TR-00104: received 2026-03-18, approval APR-00104. PO-2023-0018 and FA-000104 agree on MD-00104. Also: offboarding ticket RET-00104 referenced.</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -18118,13 +18114,13 @@
       <c r="M108" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N108" s="7">
-        <f>IFERROR(XLOOKUP(A108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N108" s="7" t="n">
         <v>1403.83</v>
       </c>
-      <c r="O108" s="7">
-        <f>IFERROR(XLOOKUP(A108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>FA-000104</t>
+        </is>
       </c>
       <c r="P108" s="7" t="inlineStr">
         <is>
@@ -18219,7 +18215,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 stays Retired/Pending Disposal at Denver (Dell Latitude 7440, $1850). TR-00105 ties to MD-00105; dock date 04/21/2026, approval APR-00105. Purchasing PO-2023-0018 without a capital line for MD-00105. Also: offboarding ticket RET-00105 referenced.</t>
+          <t>MD-00105 stays Retired/Pending Disposal at Denver (Dell Latitude 7440, $1850). TR-00105 ties to MD-00105; dock date 04/21/2026, approval APR-00105. PO-2023-0018 / FA-000105 support the cost basis. Also: offboarding ticket RET-00105 referenced.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -18230,13 +18226,13 @@
       <c r="M109" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N109" s="7">
-        <f>IFERROR(XLOOKUP(A109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N109" s="7" t="n">
         <v>104.26</v>
       </c>
-      <c r="O109" s="7">
-        <f>IFERROR(XLOOKUP(A109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>FA-000105</t>
+        </is>
       </c>
       <c r="P109" s="7" t="inlineStr">
         <is>
@@ -18331,7 +18327,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>MD-00106 reads Retired/Pending Disposal at New York (Dell U2723QE, $565). TR-00106 ties to MD-00106; dock date May 25, 2026, approval APR-00106. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00106. Also: offboarding ticket RET-00106 referenced.</t>
+          <t>MD-00106 reads Retired/Pending Disposal at New York (Dell U2723QE, $565). TR-00106 ties to MD-00106; dock date May 25, 2026, approval APR-00106. Capital trail MD-00106: PO-2023-0018 -&gt; FA-000106. Also: offboarding ticket RET-00106 referenced.</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -18342,13 +18338,13 @@
       <c r="M110" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N110" s="7">
-        <f>IFERROR(XLOOKUP(A110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N110" s="7" t="n">
         <v>368.24</v>
       </c>
-      <c r="O110" s="7">
-        <f>IFERROR(XLOOKUP(A110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O110" s="7" t="inlineStr">
+        <is>
+          <t>FA-000106</t>
+        </is>
       </c>
       <c r="P110" s="7" t="inlineStr">
         <is>
@@ -18443,7 +18439,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>MD-00107 reads Retired/Pending Disposal at Seattle (Samsung Galaxy S24, $1040). Transfer TR-00107 shows receipt 2026-06-27, approval APR-00107. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00107. Also: offboarding ticket RET-00107 referenced.</t>
+          <t>MD-00107 reads Retired/Pending Disposal at Seattle (Samsung Galaxy S24, $1040). Transfer TR-00107 shows receipt 2026-06-27, approval APR-00107. PO-2023-0018 and FA-000107 agree on MD-00107. Also: offboarding ticket RET-00107 referenced.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -18454,13 +18450,13 @@
       <c r="M111" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N111" s="7">
-        <f>IFERROR(XLOOKUP(A111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N111" s="7" t="n">
         <v>812.21</v>
       </c>
-      <c r="O111" s="7">
-        <f>IFERROR(XLOOKUP(A111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t>FA-000107</t>
+        </is>
       </c>
       <c r="P111" s="7" t="inlineStr">
         <is>
@@ -18555,7 +18551,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 reads Retired/Pending Disposal at Atlanta (Cisco C9300, $6335). Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00108. Also: offboarding ticket RET-00108 referenced.</t>
+          <t>MD-00108 reads Retired/Pending Disposal at Atlanta (Cisco C9300, $6335). Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO-2023-0018 / FA-000108 support the cost basis. Also: offboarding ticket RET-00108 referenced.</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -18566,13 +18562,13 @@
       <c r="M112" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N112" s="7">
-        <f>IFERROR(XLOOKUP(A112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N112" s="7" t="n">
         <v>545.48</v>
       </c>
-      <c r="O112" s="7">
-        <f>IFERROR(XLOOKUP(A112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O112" s="7" t="inlineStr">
+        <is>
+          <t>FA-000108</t>
+        </is>
       </c>
       <c r="P112" s="7" t="inlineStr">
         <is>
@@ -18667,7 +18663,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 reads Retired/Pending Disposal at Chicago (Lenovo ThinkPad T14, $2030). equipment_transfer_log TR-00109, approval APR-00109; received Feb 04, 2026. PO-2024-0019 in hardware_purchase_orders.csv; FAR silent on MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
+          <t>MD-00109 reads Retired/Pending Disposal at Chicago (Lenovo ThinkPad T14, $2030). equipment_transfer_log TR-00109, approval APR-00109; received Feb 04, 2026. Purchase order PO-2024-0019 and FAR row FA-000109 both cite MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -18678,13 +18674,13 @@
       <c r="M113" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N113" s="7">
-        <f>IFERROR(XLOOKUP(A113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N113" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O113" s="7">
-        <f>IFERROR(XLOOKUP(A113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>FA-000109</t>
+        </is>
       </c>
       <c r="P113" s="7" t="inlineStr">
         <is>
@@ -18779,7 +18775,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>MD-00110 stays Retired/Pending Disposal at Dallas (Dell U2723QE, $745). Inbound stamp on TR-00110 is 2026-03-08, approval APR-00110. Purchasing PO-2024-0019 without a capital line for MD-00110. Also: offboarding ticket RET-00110 referenced.</t>
+          <t>MD-00110 stays Retired/Pending Disposal at Dallas (Dell U2723QE, $745). Inbound stamp on TR-00110 is 2026-03-08, approval APR-00110. Cost path: PO-2024-0019 into FA-000110. Also: offboarding ticket RET-00110 referenced.</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -18790,13 +18786,13 @@
       <c r="M114" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N114" s="7">
-        <f>IFERROR(XLOOKUP(A114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N114" s="7" t="n">
         <v>387.24</v>
       </c>
-      <c r="O114" s="7">
-        <f>IFERROR(XLOOKUP(A114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>FA-000110</t>
+        </is>
       </c>
       <c r="P114" s="7" t="inlineStr">
         <is>
@@ -18891,7 +18887,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00111 as Disposed in Disposed. Log TR-00111: received 04/13/2026, approval APR-00111. Purchasing PO-2024-0019 without a capital line for MD-00111. Also: offboarding ticket RET-00111 referenced.</t>
+          <t>Corrected register carries MD-00111 as Disposed in Disposed. Log TR-00111: received 04/13/2026, approval APR-00111. Procurement PO-2024-0019 maps to ledger FA-000111. Also: offboarding ticket RET-00111 referenced.</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -18902,13 +18898,13 @@
       <c r="M115" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N115" s="7">
-        <f>IFERROR(XLOOKUP(A115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N115" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="7">
-        <f>IFERROR(XLOOKUP(A115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>FA-000111</t>
+        </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
         <is>
@@ -18999,7 +18995,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00112 as Disposed in Disposed. TR-00112 ties to MD-00112; dock date May 15, 2026, approval APR-00112. Purchasing PO-2024-0019 without a capital line for MD-00112. Also: offboarding ticket RET-00112 referenced.</t>
+          <t>Corrected register carries MD-00112 as Disposed in Disposed. TR-00112 ties to MD-00112; dock date May 15, 2026, approval APR-00112. Ledger FA-000112 backs PO-2024-0019 for MD-00112. Also: offboarding ticket RET-00112 referenced.</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19010,13 +19006,13 @@
       <c r="M116" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N116" s="7">
-        <f>IFERROR(XLOOKUP(A116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N116" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O116" s="7">
-        <f>IFERROR(XLOOKUP(A116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>FA-000112</t>
+        </is>
       </c>
       <c r="P116" s="7" t="inlineStr">
         <is>
@@ -19107,7 +19103,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00113 as Disposed in Disposed. Transfer TR-00113 shows receipt 2026-06-18, approval APR-00113. Purchasing PO-2024-0019 without a capital line for MD-00113. Also: offboarding ticket RET-00113 referenced.</t>
+          <t>Corrected register carries MD-00113 as Disposed in Disposed. Transfer TR-00113 shows receipt 2026-06-18, approval APR-00113. Purchase order PO-2024-0019 and FAR row FA-000113 both cite MD-00113. Also: offboarding ticket RET-00113 referenced.</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19118,13 +19114,13 @@
       <c r="M117" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N117" s="7">
-        <f>IFERROR(XLOOKUP(A117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N117" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="7">
-        <f>IFERROR(XLOOKUP(A117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t>FA-000113</t>
+        </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
         <is>
@@ -19215,7 +19211,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>MD-00114 stays Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $610). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. Purchasing PO-2024-0019 without a capital line for MD-00114. Also: offboarding ticket RET-00114 referenced. Note — no verified disposal certificate located.</t>
+          <t>MD-00114 stays Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $610). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. Capital trail MD-00114: PO-2024-0019 -&gt; FA-000114. Also: offboarding ticket RET-00114 referenced. Note - no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19226,13 +19222,13 @@
       <c r="M118" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N118" s="7">
-        <f>IFERROR(XLOOKUP(A118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N118" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O118" s="7">
-        <f>IFERROR(XLOOKUP(A118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>FA-000114</t>
+        </is>
       </c>
       <c r="P118" s="7" t="inlineStr">
         <is>
@@ -19327,7 +19323,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00115 as Disposed in Disposed. equipment_transfer_log TR-00115, approval APR-00115; received Feb 25, 2026. PO PO-2025-0020 on file; no matching FAR row for MD-00115. Also: offboarding ticket RET-00115 referenced.</t>
+          <t>Corrected register carries MD-00115 as Disposed in Disposed. equipment_transfer_log TR-00115, approval APR-00115; received Feb 25, 2026. PO-2025-0020 / FA-000115 support the cost basis. Also: offboarding ticket RET-00115 referenced.</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19338,13 +19334,13 @@
       <c r="M119" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N119" s="7">
-        <f>IFERROR(XLOOKUP(A119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N119" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="7">
-        <f>IFERROR(XLOOKUP(A119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>FA-000115</t>
+        </is>
       </c>
       <c r="P119" s="7" t="inlineStr">
         <is>
@@ -19435,7 +19431,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00116 across CSV/XLSX inputs — Disposed, Disposed. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. Purchasing PO-2025-0020 without a capital line for MD-00116. Also: offboarding ticket RET-00116 referenced.</t>
+          <t>Looked up MD-00116 across CSV/XLSX inputs - Disposed, Disposed. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. Capital trail MD-00116: PO-2025-0020 -&gt; FA-000116. Also: offboarding ticket RET-00116 referenced.</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19446,13 +19442,13 @@
       <c r="M120" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N120" s="7">
-        <f>IFERROR(XLOOKUP(A120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N120" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O120" s="7">
-        <f>IFERROR(XLOOKUP(A120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>FA-000116</t>
+        </is>
       </c>
       <c r="P120" s="7" t="inlineStr">
         <is>
@@ -19543,7 +19539,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00117 across CSV/XLSX inputs — Disposed, Disposed. Assignment TR-00117; receive column 05/02/2026, approval APR-00117. Purchasing PO-2025-0020 without a capital line for MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
+          <t>Looked up MD-00117 across CSV/XLSX inputs - Disposed, Disposed. Assignment TR-00117; receive column 05/02/2026, approval APR-00117. PO-2025-0020 and FA-000117 agree on MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19554,13 +19550,13 @@
       <c r="M121" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N121" s="7">
-        <f>IFERROR(XLOOKUP(A121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N121" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O121" s="7">
-        <f>IFERROR(XLOOKUP(A121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>FA-000117</t>
+        </is>
       </c>
       <c r="P121" s="7" t="inlineStr">
         <is>
@@ -19651,7 +19647,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 reads Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $790). TR-00118 for MD-00118 — received Jun 04, 2026, approval APR-00118. Purchasing PO-2025-0020 without a capital line for MD-00118. Also: offboarding ticket RET-00118 referenced. Note — no verified disposal certificate located.</t>
+          <t>MD-00118 reads Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $790). TR-00118 for MD-00118 - received Jun 04, 2026, approval APR-00118. PO-2025-0020 / FA-000118 support the cost basis. Also: offboarding ticket RET-00118 referenced. Note - no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19662,13 +19658,13 @@
       <c r="M122" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N122" s="7">
-        <f>IFERROR(XLOOKUP(A122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N122" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O122" s="7">
-        <f>IFERROR(XLOOKUP(A122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>FA-000118</t>
+        </is>
       </c>
       <c r="P122" s="7" t="inlineStr">
         <is>
@@ -19763,7 +19759,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00119 across CSV/XLSX inputs — Disposed, Disposed. Inbound stamp on TR-00119 is 2026-07-09, approval APR-00119. Purchasing PO-2025-0020 without a capital line for MD-00119. Also: offboarding ticket RET-00119 referenced.</t>
+          <t>Looked up MD-00119 across CSV/XLSX inputs - Disposed, Disposed. Inbound stamp on TR-00119 is 2026-07-09, approval APR-00119. FAR extract includes FA-000119 for MD-00119 via PO-2025-0020. Also: offboarding ticket RET-00119 referenced.</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -19774,13 +19770,13 @@
       <c r="M123" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N123" s="7">
-        <f>IFERROR(XLOOKUP(A123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N123" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O123" s="7">
-        <f>IFERROR(XLOOKUP(A123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>FA-000119</t>
+        </is>
       </c>
       <c r="P123" s="7" t="inlineStr">
         <is>
@@ -19875,7 +19871,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00120 as Disposed in Disposed. Transfer TR-00120 shows receipt 01/20/2026, approval APR-00120. PO PO-2025-0020 on file; no matching FAR row for MD-00120. Also: offboarding ticket RET-00120 referenced.</t>
+          <t>Corrected register carries MD-00120 as Disposed in Disposed. Transfer TR-00120 shows receipt 01/20/2026, approval APR-00120. Capital trail MD-00120: PO-2025-0020 -&gt; FA-000120. Also: offboarding ticket RET-00120 referenced.</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -19886,13 +19882,13 @@
       <c r="M124" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N124" s="7">
-        <f>IFERROR(XLOOKUP(A124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N124" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O124" s="7">
-        <f>IFERROR(XLOOKUP(A124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O124" s="7" t="inlineStr">
+        <is>
+          <t>FA-000120</t>
+        </is>
       </c>
       <c r="P124" s="7" t="inlineStr">
         <is>
@@ -19979,7 +19975,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>MD-00121 reads Available at Chicago (Lenovo ThinkPad T14, $1940). Movement TR-00121 posted 01/21/2026 and inbound Jan 21, 2026, approval APR-00121. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00121.</t>
+          <t>MD-00121 reads Available at Chicago (Lenovo ThinkPad T14, $1940). Movement TR-00121 posted 01/21/2026 and inbound Jan 21, 2026, approval APR-00121. PO-2022-0021 and FA-000121 agree on MD-00121.</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -19990,13 +19986,13 @@
       <c r="M125" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N125" s="7">
-        <f>IFERROR(XLOOKUP(A125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N125" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="7">
-        <f>IFERROR(XLOOKUP(A125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t>FA-000121</t>
+        </is>
       </c>
       <c r="P125" s="7" t="inlineStr">
         <is>
@@ -20087,7 +20083,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>MD-00122 reads Available at Dallas (Dell U2723QE, $655). equipment_transfer_log TR-00122, approval APR-00122; received 2026-02-25. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00122.</t>
+          <t>MD-00122 reads Available at Dallas (Dell U2723QE, $655). equipment_transfer_log TR-00122, approval APR-00122; received 2026-02-25. PO-2022-0021 / FA-000122 support the cost basis.</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20098,13 +20094,13 @@
       <c r="M126" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N126" s="7">
-        <f>IFERROR(XLOOKUP(A126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N126" s="7" t="n">
         <v>336.15</v>
       </c>
-      <c r="O126" s="7">
-        <f>IFERROR(XLOOKUP(A126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
+          <t>FA-000122</t>
+        </is>
       </c>
       <c r="P126" s="7" t="inlineStr">
         <is>
@@ -20195,7 +20191,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>MD-00123 reads Available at Denver (Samsung Galaxy S24, $1130). Assignment TR-00123; receive column 04/03/2026, approval APR-00123. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00123.</t>
+          <t>MD-00123 reads Available at Denver (Samsung Galaxy S24, $1130). Assignment TR-00123; receive column 04/03/2026, approval APR-00123. FAR extract includes FA-000123 for MD-00123 via PO-2022-0021.</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20206,13 +20202,13 @@
       <c r="M127" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N127" s="7">
-        <f>IFERROR(XLOOKUP(A127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N127" s="7" t="n">
         <v>622.62</v>
       </c>
-      <c r="O127" s="7">
-        <f>IFERROR(XLOOKUP(A127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t>FA-000123</t>
+        </is>
       </c>
       <c r="P127" s="7" t="inlineStr">
         <is>
@@ -20303,7 +20299,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>MD-00124 reads Available at New York (Cisco C9300, $6425). TR-00124 for MD-00124 — received May 01, 2026, approval APR-00124. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00124.</t>
+          <t>MD-00124 reads Available at New York (Cisco C9300, $6425). TR-00124 for MD-00124 - received May 01, 2026, approval APR-00124. Cost path: PO-2022-0021 into FA-000124.</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20314,13 +20310,13 @@
       <c r="M128" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N128" s="7">
-        <f>IFERROR(XLOOKUP(A128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N128" s="7" t="n">
         <v>947.26</v>
       </c>
-      <c r="O128" s="7">
-        <f>IFERROR(XLOOKUP(A128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t>FA-000124</t>
+        </is>
       </c>
       <c r="P128" s="7" t="inlineStr">
         <is>
@@ -20411,7 +20407,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>MD-00125 reads Available at Seattle (MacBook Pro 14, $2120). Inbound stamp on TR-00125 is 2026-06-08, approval APR-00125. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00125.</t>
+          <t>MD-00125 reads Available at Seattle (MacBook Pro 14, $2120). Inbound stamp on TR-00125 is 2026-06-08, approval APR-00125. Procurement PO-2022-0021 maps to ledger FA-000125.</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20422,13 +20418,13 @@
       <c r="M129" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N129" s="7">
-        <f>IFERROR(XLOOKUP(A129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N129" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O129" s="7">
-        <f>IFERROR(XLOOKUP(A129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t>FA-000125</t>
+        </is>
       </c>
       <c r="P129" s="7" t="inlineStr">
         <is>
@@ -20519,7 +20515,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>MD-00126 stays Available at Atlanta (Dell U2723QE, $520). Inbound stamp on TR-00126 is 01/12/2026, approval APR-00126. PO PO-2022-0021 on file; no matching FAR row for MD-00126.</t>
+          <t>MD-00126 stays Available at Atlanta (Dell U2723QE, $520). Inbound stamp on TR-00126 is 01/12/2026, approval APR-00126. FAR extract includes FA-000126 for MD-00126 via PO-2022-0021.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20530,13 +20526,13 @@
       <c r="M130" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N130" s="7">
-        <f>IFERROR(XLOOKUP(A130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N130" s="7" t="n">
         <v>302.75</v>
       </c>
-      <c r="O130" s="7">
-        <f>IFERROR(XLOOKUP(A130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>FA-000126</t>
+        </is>
       </c>
       <c r="P130" s="7" t="inlineStr">
         <is>
@@ -20631,7 +20627,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00127: In Use, Denver, $995 — Samsung Galaxy S24. Checked E0061: Transferred. Log TR-00127: received Feb 17, 2026, approval field blank. PO PO-2023-0022 on file; no matching FAR row for MD-00127.</t>
+          <t>Corrected row MD-00127: In Use, Denver, $995 - Samsung Galaxy S24. Checked E0061: Transferred. Log TR-00127: received Feb 17, 2026, approval field blank. Capital trail MD-00127: PO-2023-0022 -&gt; FA-000127.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20642,13 +20638,13 @@
       <c r="M131" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N131" s="7">
-        <f>IFERROR(XLOOKUP(A131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N131" s="7" t="n">
         <v>662.65</v>
       </c>
-      <c r="O131" s="7">
-        <f>IFERROR(XLOOKUP(A131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t>FA-000127</t>
+        </is>
       </c>
       <c r="P131" s="7" t="inlineStr">
         <is>
@@ -20743,7 +20739,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00128: In Use, New York, $6290 — Cisco C9300. Checked E0062: Transferred. TR-00128 ties to MD-00128; dock date 2026-03-19, approval APR-00128. PO PO-2023-0022 on file; no matching FAR row for MD-00128.</t>
+          <t>Corrected row MD-00128: In Use, New York, $6290 - Cisco C9300. Checked E0062: Transferred. TR-00128 ties to MD-00128; dock date 2026-03-19, approval APR-00128. PO-2023-0022 and FA-000128 agree on MD-00128.</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20754,13 +20750,13 @@
       <c r="M132" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N132" s="7">
-        <f>IFERROR(XLOOKUP(A132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N132" s="7" t="n">
         <v>1364.77</v>
       </c>
-      <c r="O132" s="7">
-        <f>IFERROR(XLOOKUP(A132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t>FA-000128</t>
+        </is>
       </c>
       <c r="P132" s="7" t="inlineStr">
         <is>
@@ -20851,7 +20847,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00129: In Use, Seattle, $1985 — Dell Latitude 7440. Checked E0063: Transferred. Transfer TR-00129 shows receipt 04/21/2026, approval APR-00129. PO PO-2023-0022 on file; no matching FAR row for MD-00129.</t>
+          <t>Corrected row MD-00129: In Use, Seattle, $1985 - Dell Latitude 7440. Checked E0063: Transferred. Transfer TR-00129 shows receipt 04/21/2026, approval APR-00129. PO-2023-0022 / FA-000129 support the cost basis.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -20862,13 +20858,13 @@
       <c r="M133" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N133" s="7">
-        <f>IFERROR(XLOOKUP(A133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N133" s="7" t="n">
         <v>111.86</v>
       </c>
-      <c r="O133" s="7">
-        <f>IFERROR(XLOOKUP(A133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>FA-000129</t>
+        </is>
       </c>
       <c r="P133" s="7" t="inlineStr">
         <is>
@@ -20959,7 +20955,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00130 is In Use in Atlanta site; basis $700. Naomi Berger has Transferred status in the people extract. Assignment TR-00130; receive column May 28, 2026, approval APR-00130. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00130. Also: $700 below $2,500 — missing FA expected.</t>
+          <t>Dell U2723QE on MD-00130 is In Use in Atlanta site; basis $700. Naomi Berger has Transferred status in the people extract. Assignment TR-00130; receive column May 28, 2026, approval APR-00130. PO-2023-0023 covers MD-00130 as an expense-class buy; FAR silence is expected under ITAM-001 §7. Also: $700 below $2,500 - missing FA expected.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -20970,14 +20966,8 @@
       <c r="M134" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N134" s="7">
-        <f>IFERROR(XLOOKUP(A134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
-      <c r="O134" s="7">
-        <f>IFERROR(XLOOKUP(A134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
-      </c>
+      <c r="N134" s="7" t="n"/>
+      <c r="O134" s="7" t="n"/>
       <c r="P134" s="7" t="inlineStr"/>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -21053,7 +21043,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00131 is In Use in Chicago site; basis $1175. Felix Moreno has Transferred status in the people extract. TR-00131 for MD-00131 — received 2026-06-28, approval APR-00131. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00131. Also: $1175 below $2,500 — missing FA expected.</t>
+          <t>Samsung Galaxy S24 on MD-00131 is In Use in Chicago site; basis $1175. Felix Moreno has Transferred status in the people extract. TR-00131 for MD-00131 - received 2026-06-28, approval APR-00131. PO-2023-0023 covers MD-00131 as an expense-class buy; FAR silence is expected under ITAM-001 §7. Also: $1175 below $2,500 - missing FA expected.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -21064,14 +21054,8 @@
       <c r="M135" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N135" s="7">
-        <f>IFERROR(XLOOKUP(A135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
-      <c r="O135" s="7">
-        <f>IFERROR(XLOOKUP(A135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
-      </c>
+      <c r="N135" s="7" t="n"/>
+      <c r="O135" s="7" t="n"/>
       <c r="P135" s="7" t="inlineStr"/>
       <c r="Q135" s="9" t="inlineStr">
         <is>
@@ -21147,7 +21131,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 on MD-00132 is In Use in Dallas site; basis $6470. Sharon Quinlan has Transferred status in the people extract. Inbound stamp on TR-00132 is 01/31/2026, approval APR-00132. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00132. Also: RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
+          <t>Cisco C9300 on MD-00132 is In Use in Dallas site; basis $6470. Sharon Quinlan has Transferred status in the people extract. Inbound stamp on TR-00132 is 01/31/2026, approval APR-00132. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00132. Purchasing PO-2023-0022 without a capital line for MD-00132 ($6,470). Also: RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -21158,14 +21142,8 @@
       <c r="M136" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N136" s="7">
-        <f>IFERROR(XLOOKUP(A136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
-      <c r="O136" s="7">
-        <f>IFERROR(XLOOKUP(A136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
-      </c>
+      <c r="N136" s="7" t="n"/>
+      <c r="O136" s="7" t="n"/>
       <c r="P136" s="7" t="inlineStr"/>
       <c r="Q136" s="9" t="inlineStr">
         <is>
@@ -21235,7 +21213,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -21336,7 +21313,7 @@
       </c>
       <c r="G5" s="7">
         <f>IF(B5="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>85</v>
+        <v/>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -21402,7 +21379,7 @@
       </c>
       <c r="G6" s="7">
         <f>IF(B6="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>124.52</v>
+        <v/>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -21468,7 +21445,7 @@
       </c>
       <c r="G7" s="7">
         <f>IF(B7="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -21534,11 +21511,11 @@
       </c>
       <c r="G8" s="7">
         <f>IF(B8="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Retag required — MD-LA-050021 collision involving MD-00025.</t>
+          <t>Retag required - MD-LA-050021 collision involving MD-00025.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -21600,7 +21577,7 @@
       </c>
       <c r="G9" s="7">
         <f>IF(B9="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>382.34</v>
+        <v/>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -21666,7 +21643,7 @@
       </c>
       <c r="G10" s="7">
         <f>IF(B10="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>672.21</v>
+        <v/>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -21732,7 +21709,7 @@
       </c>
       <c r="G11" s="7">
         <f>IF(B11="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>914.09</v>
+        <v/>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -21798,7 +21775,7 @@
       </c>
       <c r="G12" s="7">
         <f>IF(B12="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -21864,7 +21841,7 @@
       </c>
       <c r="G13" s="7">
         <f>IF(B13="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>355.14</v>
+        <v/>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -21930,7 +21907,7 @@
       </c>
       <c r="G14" s="7">
         <f>IF(B14="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>722.59</v>
+        <v/>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -21996,7 +21973,7 @@
       </c>
       <c r="G15" s="7">
         <f>IF(B15="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1384.3</v>
+        <v/>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -22062,7 +22039,7 @@
       </c>
       <c r="G16" s="7">
         <f>IF(B16="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>116.93</v>
+        <v/>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -22128,7 +22105,7 @@
       </c>
       <c r="G17" s="7">
         <f>IF(B17="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>514.88</v>
+        <v/>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -22194,7 +22171,7 @@
       </c>
       <c r="G18" s="7">
         <f>IF(B18="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>140</v>
+        <v/>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -22260,7 +22237,7 @@
       </c>
       <c r="G19" s="7">
         <f>IF(B19="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>741.92</v>
+        <v/>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -22326,7 +22303,7 @@
       </c>
       <c r="G20" s="7">
         <f>IF(B20="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>537.73</v>
+        <v/>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -22392,7 +22369,7 @@
       </c>
       <c r="G21" s="7">
         <f>IF(B21="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -22458,7 +22435,7 @@
       </c>
       <c r="G22" s="7">
         <f>IF(B22="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>340.46</v>
+        <v/>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -22524,7 +22501,7 @@
       </c>
       <c r="G23" s="7">
         <f>IF(B23="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>635</v>
+        <v/>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -22590,7 +22567,7 @@
       </c>
       <c r="G24" s="7">
         <f>IF(B24="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>989.48</v>
+        <v/>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -22656,7 +22633,7 @@
       </c>
       <c r="G25" s="7">
         <f>IF(B25="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -22722,7 +22699,7 @@
       </c>
       <c r="G26" s="7">
         <f>IF(B26="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>306.16</v>
+        <v/>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -22788,7 +22765,7 @@
       </c>
       <c r="G27" s="7">
         <f>IF(B27="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>673.55</v>
+        <v/>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -22854,11 +22831,11 @@
       </c>
       <c r="G28" s="7">
         <f>IF(B28="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1406.1</v>
+        <v/>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>MD-00044 / Chicago - Closed is a consolidation leftover — move to Dallas (EX-0024).</t>
+          <t>MD-00044 / Chicago - Closed is a consolidation leftover - move to Dallas (EX-0024).</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -22920,7 +22897,7 @@
       </c>
       <c r="G29" s="7">
         <f>IF(B29="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>133.6</v>
+        <v/>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -22986,7 +22963,7 @@
       </c>
       <c r="G30" s="7">
         <f>IF(B30="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>460.82</v>
+        <v/>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -23010,7 +22987,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00046 there on paper — New York is live (EX-0026).</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00046 there on paper - New York is live (EX-0026).</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -23052,7 +23029,7 @@
       </c>
       <c r="G31" s="7">
         <f>IF(B31="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>930.51</v>
+        <v/>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -23118,7 +23095,7 @@
       </c>
       <c r="G32" s="7">
         <f>IF(B32="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>514.59</v>
+        <v/>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -23184,7 +23161,7 @@
       </c>
       <c r="G33" s="7">
         <f>IF(B33="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -23250,7 +23227,7 @@
       </c>
       <c r="G34" s="7">
         <f>IF(B34="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>289.96</v>
+        <v/>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -23316,7 +23293,7 @@
       </c>
       <c r="G35" s="7">
         <f>IF(B35="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>573.03</v>
+        <v/>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -23382,7 +23359,7 @@
       </c>
       <c r="G36" s="7">
         <f>IF(B36="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>210</v>
+        <v/>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -23448,7 +23425,7 @@
       </c>
       <c r="G37" s="7">
         <f>IF(B37="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>933.99</v>
+        <v/>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -23472,7 +23449,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00052 there on paper — New York is live (EX-0033).</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00052 there on paper - New York is live (EX-0033).</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -23514,7 +23491,7 @@
       </c>
       <c r="G38" s="7">
         <f>IF(B38="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -23580,7 +23557,7 @@
       </c>
       <c r="G39" s="7">
         <f>IF(B39="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>433.74</v>
+        <v/>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -23646,7 +23623,7 @@
       </c>
       <c r="G40" s="7">
         <f>IF(B40="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>812.5</v>
+        <v/>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -23712,7 +23689,7 @@
       </c>
       <c r="G41" s="7">
         <f>IF(B41="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1345.24</v>
+        <v/>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -23778,7 +23755,7 @@
       </c>
       <c r="G42" s="7">
         <f>IF(B42="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>106.79</v>
+        <v/>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -23844,7 +23821,7 @@
       </c>
       <c r="G43" s="7">
         <f>IF(B43="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>397.56</v>
+        <v/>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -23910,7 +23887,7 @@
       </c>
       <c r="G44" s="7">
         <f>IF(B44="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>397.56</v>
+        <v/>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -23976,7 +23953,7 @@
       </c>
       <c r="G45" s="7">
         <f>IF(B45="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>397.56</v>
+        <v/>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -24042,7 +24019,7 @@
       </c>
       <c r="G46" s="7">
         <f>IF(B46="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>847.35</v>
+        <v/>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -24108,7 +24085,7 @@
       </c>
       <c r="G47" s="7">
         <f>IF(B47="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>847.35</v>
+        <v/>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -24174,7 +24151,7 @@
       </c>
       <c r="G48" s="7">
         <f>IF(B48="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>847.35</v>
+        <v/>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -24198,7 +24175,7 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>§4 evidence gap — TR-00059 lacks approval for MD-00059.</t>
+          <t>§4 evidence gap - TR-00059 lacks approval for MD-00059.</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -24240,7 +24217,7 @@
       </c>
       <c r="G49" s="7">
         <f>IF(B49="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>549.35</v>
+        <v/>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -24306,7 +24283,7 @@
       </c>
       <c r="G50" s="7">
         <f>IF(B50="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>549.35</v>
+        <v/>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -24372,7 +24349,7 @@
       </c>
       <c r="G51" s="7">
         <f>IF(B51="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -24438,7 +24415,7 @@
       </c>
       <c r="G52" s="7">
         <f>IF(B52="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -24504,7 +24481,7 @@
       </c>
       <c r="G53" s="7">
         <f>IF(B53="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>410.63</v>
+        <v/>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -24570,11 +24547,11 @@
       </c>
       <c r="G54" s="7">
         <f>IF(B54="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>410.63</v>
+        <v/>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 / Chicago - Closed is a consolidation leftover — move to Dallas (EX-0050).</t>
+          <t>MD-00062 / Chicago - Closed is a consolidation leftover - move to Dallas (EX-0050).</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -24636,7 +24613,7 @@
       </c>
       <c r="G55" s="7">
         <f>IF(B55="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>533.85</v>
+        <v/>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -24702,7 +24679,7 @@
       </c>
       <c r="G56" s="7">
         <f>IF(B56="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>533.85</v>
+        <v/>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -24768,11 +24745,11 @@
       </c>
       <c r="G57" s="7">
         <f>IF(B57="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>961.76</v>
+        <v/>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>HR shows E0077 gone — remove as custodian on MD-00064 (OFF-00064).</t>
+          <t>HR shows E0077 gone - remove as custodian on MD-00064 (OFF-00064).</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -24834,7 +24811,7 @@
       </c>
       <c r="G58" s="7">
         <f>IF(B58="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>961.76</v>
+        <v/>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -24900,7 +24877,7 @@
       </c>
       <c r="G59" s="7">
         <f>IF(B59="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>961.76</v>
+        <v/>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -24966,7 +24943,7 @@
       </c>
       <c r="G60" s="7">
         <f>IF(B60="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -24990,7 +24967,7 @@
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 custodian equals terminated ID E0078 — EX-0056.</t>
+          <t>MD-00065 custodian equals terminated ID E0078 - EX-0056.</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25032,7 +25009,7 @@
       </c>
       <c r="G61" s="7">
         <f>IF(B61="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -25098,7 +25075,7 @@
       </c>
       <c r="G62" s="7">
         <f>IF(B62="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -25164,7 +25141,7 @@
       </c>
       <c r="G63" s="7">
         <f>IF(B63="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>385.65</v>
+        <v/>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -25230,7 +25207,7 @@
       </c>
       <c r="G64" s="7">
         <f>IF(B64="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>385.65</v>
+        <v/>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -25296,11 +25273,11 @@
       </c>
       <c r="G65" s="7">
         <f>IF(B65="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>764.93</v>
+        <v/>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00067 should not remain with E0080.</t>
+          <t>Term cleanup - MD-00067 should not remain with E0080.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -25362,7 +25339,7 @@
       </c>
       <c r="G66" s="7">
         <f>IF(B66="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>764.93</v>
+        <v/>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -25428,7 +25405,7 @@
       </c>
       <c r="G67" s="7">
         <f>IF(B67="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1436.28</v>
+        <v/>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -25494,7 +25471,7 @@
       </c>
       <c r="G68" s="7">
         <f>IF(B68="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1436.28</v>
+        <v/>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -25560,7 +25537,7 @@
       </c>
       <c r="G69" s="7">
         <f>IF(B69="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>55</v>
+        <v/>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
@@ -25626,11 +25603,11 @@
       </c>
       <c r="G70" s="7">
         <f>IF(B70="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>142.69</v>
+        <v/>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Outstanding kit MD-00069 / 1ZMD00000069 — escalate beyond label print.</t>
+          <t>Outstanding kit MD-00069 / 1ZMD00000069 - escalate beyond label print.</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -25692,7 +25669,7 @@
       </c>
       <c r="G71" s="7">
         <f>IF(B71="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>142.69</v>
+        <v/>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
@@ -25758,7 +25735,7 @@
       </c>
       <c r="G72" s="7">
         <f>IF(B72="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>342.32</v>
+        <v/>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -25824,7 +25801,7 @@
       </c>
       <c r="G73" s="7">
         <f>IF(B73="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>342.32</v>
+        <v/>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
@@ -25890,7 +25867,7 @@
       </c>
       <c r="G74" s="7">
         <f>IF(B74="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>787.96</v>
+        <v/>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -25956,7 +25933,7 @@
       </c>
       <c r="G75" s="7">
         <f>IF(B75="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>787.96</v>
+        <v/>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -26022,7 +25999,7 @@
       </c>
       <c r="G76" s="7">
         <f>IF(B76="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>500.27</v>
+        <v/>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
@@ -26088,7 +26065,7 @@
       </c>
       <c r="G77" s="7">
         <f>IF(B77="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>500.27</v>
+        <v/>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -26154,11 +26131,11 @@
       </c>
       <c r="G78" s="7">
         <f>IF(B78="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Keep pressure on the former user until dock scan — 1ZMD00000073.</t>
+          <t>Keep pressure on the former user until dock scan - 1ZMD00000073.</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -26220,7 +26197,7 @@
       </c>
       <c r="G79" s="7">
         <f>IF(B79="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -26286,7 +26263,7 @@
       </c>
       <c r="G80" s="7">
         <f>IF(B80="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>359.25</v>
+        <v/>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -26352,7 +26329,7 @@
       </c>
       <c r="G81" s="7">
         <f>IF(B81="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>359.25</v>
+        <v/>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -26376,7 +26353,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 custodian equals terminated ID E0087 — EX-0077.</t>
+          <t>MD-00074 custodian equals terminated ID E0087 - EX-0077.</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -26418,7 +26395,7 @@
       </c>
       <c r="G82" s="7">
         <f>IF(B82="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>359.25</v>
+        <v/>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -26484,7 +26461,7 @@
       </c>
       <c r="G83" s="7">
         <f>IF(B83="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>647.42</v>
+        <v/>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -26550,7 +26527,7 @@
       </c>
       <c r="G84" s="7">
         <f>IF(B84="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>647.42</v>
+        <v/>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -26616,7 +26593,7 @@
       </c>
       <c r="G85" s="7">
         <f>IF(B85="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>953.89</v>
+        <v/>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -26682,11 +26659,11 @@
       </c>
       <c r="G86" s="7">
         <f>IF(B86="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>953.89</v>
+        <v/>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00076 should not remain with E0089.</t>
+          <t>Term cleanup - MD-00076 should not remain with E0089.</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -26748,7 +26725,7 @@
       </c>
       <c r="G87" s="7">
         <f>IF(B87="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>953.89</v>
+        <v/>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -26814,11 +26791,11 @@
       </c>
       <c r="G88" s="7">
         <f>IF(B88="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Outstanding kit MD-00077 / 1ZMD00000077 — escalate beyond label print.</t>
+          <t>Outstanding kit MD-00077 / 1ZMD00000077 - escalate beyond label print.</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -26880,7 +26857,7 @@
       </c>
       <c r="G89" s="7">
         <f>IF(B89="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -26904,7 +26881,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>MD-00077 custodian equals terminated ID E0090 — EX-0085.</t>
+          <t>MD-00077 custodian equals terminated ID E0090 - EX-0085.</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -26946,7 +26923,7 @@
       </c>
       <c r="G90" s="7">
         <f>IF(B90="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>328.95</v>
+        <v/>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
@@ -27012,7 +26989,7 @@
       </c>
       <c r="G91" s="7">
         <f>IF(B91="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>328.95</v>
+        <v/>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
@@ -27078,7 +27055,7 @@
       </c>
       <c r="G92" s="7">
         <f>IF(B92="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>692.62</v>
+        <v/>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -27144,7 +27121,7 @@
       </c>
       <c r="G93" s="7">
         <f>IF(B93="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>692.62</v>
+        <v/>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
@@ -27210,11 +27187,11 @@
       </c>
       <c r="G94" s="7">
         <f>IF(B94="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1374.53</v>
+        <v/>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00080 should not remain with E0093.</t>
+          <t>Term cleanup - MD-00080 should not remain with E0093.</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -27276,7 +27253,7 @@
       </c>
       <c r="G95" s="7">
         <f>IF(B95="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>114.4</v>
+        <v/>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
@@ -27342,7 +27319,7 @@
       </c>
       <c r="G96" s="7">
         <f>IF(B96="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>485.55</v>
+        <v/>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
@@ -27408,7 +27385,7 @@
       </c>
       <c r="G97" s="7">
         <f>IF(B97="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>485.55</v>
+        <v/>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -27432,7 +27409,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0095 to register row MD-00082 — assignment stale (EX-0093).</t>
+          <t>Compared HR row E0095 to register row MD-00082 - assignment stale (EX-0093).</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -27474,7 +27451,7 @@
       </c>
       <c r="G98" s="7">
         <f>IF(B98="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>952.79</v>
+        <v/>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -27540,7 +27517,7 @@
       </c>
       <c r="G99" s="7">
         <f>IF(B99="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>533.85</v>
+        <v/>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -27606,7 +27583,7 @@
       </c>
       <c r="G100" s="7">
         <f>IF(B100="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>533.85</v>
+        <v/>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
@@ -27672,7 +27649,7 @@
       </c>
       <c r="G101" s="7">
         <f>IF(B101="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
@@ -27738,7 +27715,7 @@
       </c>
       <c r="G102" s="7">
         <f>IF(B102="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>195</v>
+        <v/>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
@@ -27804,11 +27781,11 @@
       </c>
       <c r="G103" s="7">
         <f>IF(B103="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>317.07</v>
+        <v/>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>HR shows E0074 gone — remove as custodian on MD-00086 (OFF-00086).</t>
+          <t>HR shows E0074 gone - remove as custodian on MD-00086 (OFF-00086).</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -27828,7 +27805,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0074 to register row MD-00086 — assignment stale (EX-0099).</t>
+          <t>Compared HR row E0074 to register row MD-00086 - assignment stale (EX-0099).</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -27870,7 +27847,7 @@
       </c>
       <c r="G104" s="7">
         <f>IF(B104="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>609.71</v>
+        <v/>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
@@ -27936,7 +27913,7 @@
       </c>
       <c r="G105" s="7">
         <f>IF(B105="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>982.55</v>
+        <v/>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
@@ -27960,7 +27937,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0076 to register row MD-00088 — assignment stale (EX-0101).</t>
+          <t>Compared HR row E0076 to register row MD-00088 - assignment stale (EX-0101).</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -28002,11 +27979,11 @@
       </c>
       <c r="G106" s="7">
         <f>IF(B106="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>982.55</v>
+        <v/>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Duplicate MD-NE-050088 — MD-00088 and MD-00088,MD-00092. Neither is clean until retag.</t>
+          <t>Duplicate MD-NE-050088 - MD-00088 and MD-00088,MD-00092. Neither is clean until retag.</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -28068,7 +28045,7 @@
       </c>
       <c r="G107" s="7">
         <f>IF(B107="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -28134,7 +28111,7 @@
       </c>
       <c r="G108" s="7">
         <f>IF(B108="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -28200,7 +28177,7 @@
       </c>
       <c r="G109" s="7">
         <f>IF(B109="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>465.13</v>
+        <v/>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
@@ -28266,7 +28243,7 @@
       </c>
       <c r="G110" s="7">
         <f>IF(B110="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>465.13</v>
+        <v/>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
@@ -28332,7 +28309,7 @@
       </c>
       <c r="G111" s="7">
         <f>IF(B111="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>643.09</v>
+        <v/>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
@@ -28398,7 +28375,7 @@
       </c>
       <c r="G112" s="7">
         <f>IF(B112="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>643.09</v>
+        <v/>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
@@ -28464,7 +28441,7 @@
       </c>
       <c r="G113" s="7">
         <f>IF(B113="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1396.04</v>
+        <v/>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
@@ -28530,7 +28507,7 @@
       </c>
       <c r="G114" s="7">
         <f>IF(B114="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1396.04</v>
+        <v/>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
@@ -28596,7 +28573,7 @@
       </c>
       <c r="G115" s="7">
         <f>IF(B115="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1396.04</v>
+        <v/>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
@@ -28662,7 +28639,7 @@
       </c>
       <c r="G116" s="7">
         <f>IF(B116="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>130.57</v>
+        <v/>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
@@ -28728,7 +28705,7 @@
       </c>
       <c r="G117" s="7">
         <f>IF(B117="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>130.57</v>
+        <v/>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
@@ -28794,7 +28771,7 @@
       </c>
       <c r="G118" s="7">
         <f>IF(B118="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>431.2</v>
+        <v/>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
@@ -28860,11 +28837,11 @@
       </c>
       <c r="G119" s="7">
         <f>IF(B119="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>431.2</v>
+        <v/>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00094 should not remain with E0082.</t>
+          <t>Term cleanup - MD-00094 should not remain with E0082.</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
@@ -28884,7 +28861,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>MD-00094 custodian equals terminated ID E0082 — EX-0115.</t>
+          <t>MD-00094 custodian equals terminated ID E0082 - EX-0115.</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
@@ -28926,7 +28903,7 @@
       </c>
       <c r="G120" s="7">
         <f>IF(B120="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>894.87</v>
+        <v/>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
@@ -28992,7 +28969,7 @@
       </c>
       <c r="G121" s="7">
         <f>IF(B121="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>894.87</v>
+        <v/>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
@@ -29058,7 +29035,7 @@
       </c>
       <c r="G122" s="7">
         <f>IF(B122="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>511.01</v>
+        <v/>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
@@ -29124,7 +29101,7 @@
       </c>
       <c r="G123" s="7">
         <f>IF(B123="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>511.01</v>
+        <v/>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
@@ -29190,7 +29167,7 @@
       </c>
       <c r="G124" s="7">
         <f>IF(B124="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
@@ -29256,7 +29233,7 @@
       </c>
       <c r="G125" s="7">
         <f>IF(B125="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
@@ -29322,7 +29299,7 @@
       </c>
       <c r="G126" s="7">
         <f>IF(B126="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>266.87</v>
+        <v/>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
@@ -29388,7 +29365,7 @@
       </c>
       <c r="G127" s="7">
         <f>IF(B127="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>266.87</v>
+        <v/>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
@@ -29454,7 +29431,7 @@
       </c>
       <c r="G128" s="7">
         <f>IF(B128="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>548.24</v>
+        <v/>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
@@ -29520,7 +29497,7 @@
       </c>
       <c r="G129" s="7">
         <f>IF(B129="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>548.24</v>
+        <v/>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
@@ -29586,7 +29563,7 @@
       </c>
       <c r="G130" s="7">
         <f>IF(B130="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>927.36</v>
+        <v/>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
@@ -29652,7 +29629,7 @@
       </c>
       <c r="G131" s="7">
         <f>IF(B131="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>927.36</v>
+        <v/>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
@@ -29718,7 +29695,7 @@
       </c>
       <c r="G132" s="7">
         <f>IF(B132="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -29784,7 +29761,7 @@
       </c>
       <c r="G133" s="7">
         <f>IF(B133="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
@@ -29850,11 +29827,11 @@
       </c>
       <c r="G134" s="7">
         <f>IF(B134="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>407.54</v>
+        <v/>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Do not call MD-00102 disposed — certificate missing (EX-0130).</t>
+          <t>Do not call MD-00102 disposed - certificate missing (EX-0130).</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr">
@@ -29916,7 +29893,7 @@
       </c>
       <c r="G135" s="7">
         <f>IF(B135="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>120</v>
+        <v/>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
@@ -29982,7 +29959,7 @@
       </c>
       <c r="G136" s="7">
         <f>IF(B136="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>407.54</v>
+        <v/>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
@@ -30048,7 +30025,7 @@
       </c>
       <c r="G137" s="7">
         <f>IF(B137="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D137,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D137,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>782.53</v>
+        <v/>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
@@ -30114,7 +30091,7 @@
       </c>
       <c r="G138" s="7">
         <f>IF(B138="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D138,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D138,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>782.53</v>
+        <v/>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
@@ -30180,7 +30157,7 @@
       </c>
       <c r="G139" s="7">
         <f>IF(B139="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D139,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D139,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1403.83</v>
+        <v/>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
@@ -30246,7 +30223,7 @@
       </c>
       <c r="G140" s="7">
         <f>IF(B140="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D140,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D140,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>1403.83</v>
+        <v/>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
@@ -30312,7 +30289,7 @@
       </c>
       <c r="G141" s="7">
         <f>IF(B141="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D141,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D141,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>104.26</v>
+        <v/>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
@@ -30378,11 +30355,11 @@
       </c>
       <c r="G142" s="7">
         <f>IF(B142="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D142,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D142,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>104.26</v>
+        <v/>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 / Denver - Closed is a consolidation leftover — move to Denver (EX-0138).</t>
+          <t>MD-00105 / Denver - Closed is a consolidation leftover - move to Denver (EX-0138).</t>
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr">
@@ -30444,7 +30421,7 @@
       </c>
       <c r="G143" s="7">
         <f>IF(B143="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D143,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D143,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>368.24</v>
+        <v/>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
@@ -30510,7 +30487,7 @@
       </c>
       <c r="G144" s="7">
         <f>IF(B144="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D144,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D144,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>368.24</v>
+        <v/>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
@@ -30576,7 +30553,7 @@
       </c>
       <c r="G145" s="7">
         <f>IF(B145="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D145,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D145,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>812.21</v>
+        <v/>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
@@ -30642,7 +30619,7 @@
       </c>
       <c r="G146" s="7">
         <f>IF(B146="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D146,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D146,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>812.21</v>
+        <v/>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
@@ -30708,7 +30685,7 @@
       </c>
       <c r="G147" s="7">
         <f>IF(B147="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D147,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D147,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>545.48</v>
+        <v/>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
@@ -30774,7 +30751,7 @@
       </c>
       <c r="G148" s="7">
         <f>IF(B148="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D148,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D148,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>545.48</v>
+        <v/>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
@@ -30840,11 +30817,11 @@
       </c>
       <c r="G149" s="7">
         <f>IF(B149="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D149,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D149,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>ITAM hold — MD-00109 not gone until cert lists the tag (EX-0145).</t>
+          <t>ITAM hold - MD-00109 not gone until cert lists the tag (EX-0145).</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr">
@@ -30906,7 +30883,7 @@
       </c>
       <c r="G150" s="7">
         <f>IF(B150="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D150,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D150,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
@@ -30972,7 +30949,7 @@
       </c>
       <c r="G151" s="7">
         <f>IF(B151="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D151,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D151,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>387.24</v>
+        <v/>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
@@ -31038,7 +31015,7 @@
       </c>
       <c r="G152" s="7">
         <f>IF(B152="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D152,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D152,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>387.24</v>
+        <v/>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
@@ -31062,7 +31039,7 @@
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00110 there on paper — Dallas is live (EX-0148).</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00110 there on paper - Dallas is live (EX-0148).</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -31104,7 +31081,7 @@
       </c>
       <c r="G153" s="7">
         <f>IF(B153="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D153,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D153,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
@@ -31170,7 +31147,7 @@
       </c>
       <c r="G154" s="7">
         <f>IF(B154="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D154,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D154,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
@@ -31236,7 +31213,7 @@
       </c>
       <c r="G155" s="7">
         <f>IF(B155="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D155,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D155,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
@@ -31302,7 +31279,7 @@
       </c>
       <c r="G156" s="7">
         <f>IF(B156="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D156,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D156,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
@@ -31368,7 +31345,7 @@
       </c>
       <c r="G157" s="7">
         <f>IF(B157="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D157,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D157,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>165</v>
+        <v/>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
@@ -31434,7 +31411,7 @@
       </c>
       <c r="G158" s="7">
         <f>IF(B158="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D158,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D158,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
@@ -31500,7 +31477,7 @@
       </c>
       <c r="G159" s="7">
         <f>IF(B159="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D159,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D159,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>336.15</v>
+        <v/>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
@@ -31566,7 +31543,7 @@
       </c>
       <c r="G160" s="7">
         <f>IF(B160="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D160,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D160,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>622.62</v>
+        <v/>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
@@ -31632,7 +31609,7 @@
       </c>
       <c r="G161" s="7">
         <f>IF(B161="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D161,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D161,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>947.26</v>
+        <v/>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
@@ -31656,7 +31633,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>Extract shows MD-00124 at Chicago - Closed — that building is locked (EX-0157).</t>
+          <t>Extract shows MD-00124 at Chicago - Closed - that building is locked (EX-0157).</t>
         </is>
       </c>
       <c r="M161" s="7" t="inlineStr">
@@ -31698,7 +31675,7 @@
       </c>
       <c r="G162" s="7">
         <f>IF(B162="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D162,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D162,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
@@ -31764,7 +31741,7 @@
       </c>
       <c r="G163" s="7">
         <f>IF(B163="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D163,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D163,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>302.75</v>
+        <v/>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
@@ -31830,7 +31807,7 @@
       </c>
       <c r="G164" s="7">
         <f>IF(B164="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D164,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D164,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>662.65</v>
+        <v/>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
@@ -31896,7 +31873,7 @@
       </c>
       <c r="G165" s="7">
         <f>IF(B165="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D165,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D165,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
@@ -31920,7 +31897,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>$700 on MD-00130 — under §7 gate. Ledger absence expected.</t>
+          <t>$700 on MD-00130 - under §7 gate. Ledger absence expected.</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
@@ -31962,7 +31939,7 @@
       </c>
       <c r="G166" s="7">
         <f>IF(B166="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D166,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D166,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
@@ -32028,7 +32005,7 @@
       </c>
       <c r="G167" s="7">
         <f>IF(B167="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D167,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D167,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>6470</v>
+        <v/>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
@@ -32093,7 +32070,7 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Custody Chain — High-Risk and Unresolved Assets</t>
+          <t>Custody Chain - High-Risk and Unresolved Assets</t>
         </is>
       </c>
     </row>
@@ -32104,7 +32081,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -32954,7 +32930,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00034 — In Use, site New York, High. EX-0013, EX-0014. E0034. TR-00034. APR-00034. PO. PO-2023-0006. FA-000034. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00034 - In Use, site New York, High. EX-0013, EX-0014. E0034. TR-00034. APR-00034. PO. PO-2023-0006. FA-000034. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -33224,7 +33200,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2023-0010 — Dell U2723QE.</t>
+          <t>PO line PO-2023-0010 - Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -33576,7 +33552,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>TR-00059 — got it 2026-06-26 at Seattle.</t>
+          <t>TR-00059 - got it 2026-06-26 at Seattle.</t>
         </is>
       </c>
     </row>
@@ -34268,7 +34244,7 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Looping with site ops — laptop still showing assigned post-term. Ref MD-00061.</t>
+          <t>Looping with site ops - laptop still showing assigned post-term. Ref MD-00061.</t>
         </is>
       </c>
     </row>
@@ -34796,7 +34772,7 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>TR-00063 — got it Apr 16, 2026 at Denver.</t>
+          <t>TR-00063 - got it Apr 16, 2026 at Denver.</t>
         </is>
       </c>
     </row>
@@ -34921,7 +34897,7 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00063 in regional_IT_notes.docx — weight zero.</t>
+          <t>Investigative color on MD-00063 in regional_IT_notes.docx - weight zero.</t>
         </is>
       </c>
     </row>
@@ -35007,7 +34983,7 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00063 — Pending Redeployment, site Denver, High. EX-0051, EX-0052. TR-00063. APR-00063. OFF-00063. PO. PO-2024-0011. FA-000063. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00063 - Pending Redeployment, site Denver, High. EX-0051, EX-0052. TR-00063. APR-00063. OFF-00063. PO. PO-2024-0011. FA-000063. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35617,7 +35593,7 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00065: Pending Redeployment (Medium) — EX-0056, EX-0057, EX-0058. TR-00065. OFF-00065. PO. PO-2024-0011. FA-000065. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00065: Pending Redeployment (Medium) - EX-0056, EX-0057, EX-0058. TR-00065. OFF-00065. PO. PO-2024-0011. FA-000065. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35754,7 +35730,7 @@
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>OFF-00066 — Closed. Due 07/15/2026.</t>
+          <t>OFF-00066 - Closed. Due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35812,7 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>MD-00066: Word-file mention only — treated as lead.</t>
+          <t>MD-00066: Word-file mention only - treated as lead.</t>
         </is>
       </c>
     </row>
@@ -36274,7 +36250,7 @@
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00068 — PO-2025-0012, $6425.</t>
+          <t>First touch MD-00068 - PO-2025-0012, $6425.</t>
         </is>
       </c>
     </row>
@@ -36716,7 +36692,7 @@
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>OFF-00069 — Past Due. Due 2026-07-15.</t>
+          <t>OFF-00069 - Past Due. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -36978,7 +36954,7 @@
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00070 — PO-2025-0012, $520.</t>
+          <t>First touch MD-00070 - PO-2025-0012, $520.</t>
         </is>
       </c>
     </row>
@@ -37459,7 +37435,7 @@
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Monitor return — bulky; user delayed pickup. Ref MD-00071.</t>
+          <t>Monitor return - bulky; user delayed pickup. Ref MD-00071.</t>
         </is>
       </c>
     </row>
@@ -38726,7 +38702,7 @@
       </c>
       <c r="I154" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00074: Return Overdue (Low) — EX-0076, EX-0077, EX-0078. 1ZMD00000074. OFF-00074. PO. PO-2022-0013. FA-000074. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00074: Return Overdue (Low) - EX-0076, EX-0077, EX-0078. 1ZMD00000074. OFF-00074. PO. PO-2022-0013. FA-000074. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39125,7 +39101,7 @@
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2022-0013 — Cisco C9300.</t>
+          <t>PO line PO-2022-0013 - Cisco C9300.</t>
         </is>
       </c>
     </row>
@@ -39559,7 +39535,7 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>TR-00077 — got it 06/06/2026 at Remote - Former Employee.</t>
+          <t>TR-00077 - got it 06/06/2026 at Remote - Former Employee.</t>
         </is>
       </c>
     </row>
@@ -39817,7 +39793,7 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00077: Return Overdue (Low) — EX-0084, EX-0085. OFF-00077. 1ZMD00000077. TR-00077. E0090. PO. PO-2022-0013. FA-000077. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00077: Return Overdue (Low) - EX-0084, EX-0085. OFF-00077. 1ZMD00000077. TR-00077. E0090. PO. PO-2022-0013. FA-000077. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39954,7 +39930,7 @@
       </c>
       <c r="I182" s="7" t="inlineStr">
         <is>
-          <t>OFF-00078 — Past Due. Due 07/15/2026.</t>
+          <t>OFF-00078 - Past Due. Due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -39993,7 +39969,7 @@
       </c>
       <c r="I183" s="7" t="inlineStr">
         <is>
-          <t>Can't close — no delivery event in the carrier file. Ref MD-00078.</t>
+          <t>Can't close - no delivery event in the carrier file. Ref MD-00078.</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40904,7 @@
       </c>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00080 in regional_IT_notes.docx — weight zero.</t>
+          <t>Investigative color on MD-00080 in regional_IT_notes.docx - weight zero.</t>
         </is>
       </c>
     </row>
@@ -41855,7 +41831,7 @@
       </c>
       <c r="I225" s="7" t="inlineStr">
         <is>
-          <t>Atlanta photo receiving_exception_scan_1ZMD00000082.png shows HOLD / MISMATCH. Lead only — not a receiving clearance for MD-00082.</t>
+          <t>Atlanta photo receiving_exception_scan_1ZMD00000082.png shows HOLD / MISMATCH. Lead only - not a receiving clearance for MD-00082.</t>
         </is>
       </c>
     </row>
@@ -43048,7 +43024,7 @@
       </c>
       <c r="I252" s="7" t="inlineStr">
         <is>
-          <t>OFF-00085 — Shipment Open. Due 2026-07-15.</t>
+          <t>OFF-00085 - Shipment Open. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -43580,7 +43556,7 @@
       </c>
       <c r="I264" s="7" t="inlineStr">
         <is>
-          <t>Closed the chatter, not the ticket — still no receipt. Ref MD-00086.</t>
+          <t>Closed the chatter, not the ticket - still no receipt. Ref MD-00086.</t>
         </is>
       </c>
     </row>
@@ -44707,7 +44683,7 @@
       </c>
       <c r="I289" s="7" t="inlineStr">
         <is>
-          <t>Delivered — 1ZMD00000088. Still need a receiving scan to finish returns.</t>
+          <t>Delivered - 1ZMD00000088. Still need a receiving scan to finish returns.</t>
         </is>
       </c>
     </row>
@@ -44977,7 +44953,7 @@
       </c>
       <c r="I295" s="7" t="inlineStr">
         <is>
-          <t>TR-00089 — got it Jun 17, 2026 at Unknown.</t>
+          <t>TR-00089 - got it Jun 17, 2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -45102,7 +45078,7 @@
       </c>
       <c r="I298" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions During the Denver exit walkthrough, someone mentioned a locked cage on floor 3 might still — lead only for MD-00089.</t>
+          <t>regional_IT_notes.docx mentions During the Denver exit walkthrough, someone mentioned a locked cage on floor 3 might still - lead only for MD-00089.</t>
         </is>
       </c>
     </row>
@@ -45270,7 +45246,7 @@
       </c>
       <c r="I302" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2024-0015 — Dell U2723QE.</t>
+          <t>PO line PO-2024-0015 - Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -45563,7 +45539,7 @@
       </c>
       <c r="I309" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00090 — Missing, site Unknown, Low. EX-0105, EX-0106. OFF-00090. TR-00090. PO. PO-2024-0015. FA-000090. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00090 - Missing, site Unknown, Low. EX-0105, EX-0106. OFF-00090. TR-00090. PO. PO-2024-0015. FA-000090. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46583,7 +46559,7 @@
       </c>
       <c r="I333" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00093: Missing (Low) — EX-0112, EX-0113. OFF-00093. TR-00093. PO. PO-2025-0016. FA-000093. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00093: Missing (Low) - EX-0112, EX-0113. OFF-00093. TR-00093. PO. PO-2025-0016. FA-000093. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46802,7 +46778,7 @@
       </c>
       <c r="I338" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00094: "IT float pool chat referenced this asset as 'still at closed site.' Chat is not an approva" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00094: "IT float pool chat referenced this asset as 'still at closed site.' Chat is not an approva" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47142,7 +47118,7 @@
       </c>
       <c r="I346" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00095: "Vendor teardown crew said they saw a similar model on a pallet marked scrap hold. Asset ta" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00095: "Vendor teardown crew said they saw a similar model on a pallet marked scrap hold. Asset ta" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47439,7 +47415,7 @@
       </c>
       <c r="I353" s="7" t="inlineStr">
         <is>
-          <t>Walkthrough photo of a cage — tag not readable. Still unresolved. Ref MD-00096.</t>
+          <t>Walkthrough photo of a cage - tag not readable. Still unresolved. Ref MD-00096.</t>
         </is>
       </c>
     </row>
@@ -47482,7 +47458,7 @@
       </c>
       <c r="I354" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00096: "Helpdesk comment claims the user dropped it with building security before last day. Securi" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00096: "Helpdesk comment claims the user dropped it with building security before last day. Securi" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47697,7 +47673,7 @@
       </c>
       <c r="I359" s="7" t="inlineStr">
         <is>
-          <t>TR-00097 — got it 01/27/2026 at Unknown.</t>
+          <t>TR-00097 - got it 01/27/2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -47822,7 +47798,7 @@
       </c>
       <c r="I362" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00097: "Regional spare inventory spreadsheet (offline) listed a placeholder row for this tag with " — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00097: "Regional spare inventory spreadsheet (offline) listed a placeholder row for this tag with " - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -48162,7 +48138,7 @@
       </c>
       <c r="I370" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00098: "Move captain's email guessed the device rode with furniture to storage. Furniture BOL does" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00098: "Move captain's email guessed the device rode with furniture to storage. Furniture BOL does" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -48420,7 +48396,7 @@
       </c>
       <c r="I376" s="7" t="inlineStr">
         <is>
-          <t>OFF-00099 — Unresolved. Due Jul 15, 2026.</t>
+          <t>OFF-00099 - Unresolved. Due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -48502,7 +48478,7 @@
       </c>
       <c r="I378" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions An intern's handwritten punch list includes this tag under 'find later.' No follow-up work — lead only for MD-00099.</t>
+          <t>regional_IT_notes.docx mentions An intern's handwritten punch list includes this tag under 'find later.' No follow-up work - lead only for MD-00099.</t>
         </is>
       </c>
     </row>
@@ -48717,7 +48693,7 @@
       </c>
       <c r="I383" s="7" t="inlineStr">
         <is>
-          <t>TR-00100 — got it 05/05/2026 at Unknown.</t>
+          <t>TR-00100 - got it 05/05/2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -48760,7 +48736,7 @@
       </c>
       <c r="I384" s="7" t="inlineStr">
         <is>
-          <t>OFF-00100 — Unresolved. Due 2026-07-15.</t>
+          <t>OFF-00100 - Unresolved. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -49405,7 +49381,7 @@
       </c>
       <c r="I399" s="7" t="inlineStr">
         <is>
-          <t>RET-00102 — Pending Disposal. Due n/a.</t>
+          <t>RET-00102 - Pending Disposal. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -49444,7 +49420,7 @@
       </c>
       <c r="I400" s="7" t="inlineStr">
         <is>
-          <t>Staged for July recycler run — cert not attached yet on some of these. Ref MD-00102.</t>
+          <t>Staged for July recycler run - cert not attached yet on some of these. Ref MD-00102.</t>
         </is>
       </c>
     </row>
@@ -50402,7 +50378,7 @@
       </c>
       <c r="I422" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00105 in regional_IT_notes.docx — weight zero.</t>
+          <t>Investigative color on MD-00105 in regional_IT_notes.docx - weight zero.</t>
         </is>
       </c>
     </row>
@@ -50793,7 +50769,7 @@
       </c>
       <c r="I431" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00106: Retired/Pending Disposal (Medium) — EX-0139, EX-0140. RET-00106. TR-00106. PO. PO-2023-0018. FA-000106. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00106: Retired/Pending Disposal (Medium) - EX-0139, EX-0140. RET-00106. TR-00106. PO. PO-2023-0018. FA-000106. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51098,7 +51074,7 @@
       </c>
       <c r="I438" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00107 — Retired/Pending Disposal, site Seattle, Medium. EX-0141, EX-0142. RET-00107. TR-00107. PO. PO-2023-0018. FA-000107. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00107 - Retired/Pending Disposal, site Seattle, Medium. EX-0141, EX-0142. RET-00107. TR-00107. PO. PO-2023-0018. FA-000107. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51497,7 +51473,7 @@
       </c>
       <c r="I447" s="7" t="inlineStr">
         <is>
-          <t>TR-00109 — got it 2026-02-04 at Chicago.</t>
+          <t>TR-00109 - got it 2026-02-04 at Chicago.</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52126,7 @@
       </c>
       <c r="I462" s="7" t="inlineStr">
         <is>
-          <t>RET-00114 — Closed. Due n/a.</t>
+          <t>RET-00114 - Closed. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -52365,7 +52341,7 @@
       </c>
       <c r="I467" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00114 — Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150. TR-00114. RET-00114. PO. PO-2024-0019. FA-000114. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00114 - Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150. TR-00114. RET-00114. PO. PO-2024-0019. FA-000114. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -52854,7 +52830,7 @@
       </c>
       <c r="I478" s="7" t="inlineStr">
         <is>
-          <t>RET-00119 — Closed. Due n/a.</t>
+          <t>RET-00119 - Closed. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53225,7 @@
       </c>
       <c r="I487" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00127 — In Use, site Denver, Medium. EX-0160. E0061. TR-00127. PO. PO-2023-0022. FA-000127. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00127 - In Use, site Denver, Medium. EX-0160. E0061. TR-00127. PO. PO-2023-0022. FA-000127. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53296,7 +53272,7 @@
       </c>
       <c r="I488" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00130 — PO-2023-0022, $700.</t>
+          <t>First touch MD-00130 - PO-2023-0022, $700.</t>
         </is>
       </c>
     </row>
@@ -53382,7 +53358,7 @@
       </c>
       <c r="I490" s="7" t="inlineStr">
         <is>
-          <t>TR-00130 — got it May 28, 2026 at Atlanta.</t>
+          <t>TR-00130 - got it May 28, 2026 at Atlanta.</t>
         </is>
       </c>
     </row>
@@ -53909,7 +53885,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -53925,22 +53900,20 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Corrected register — sum of acquisition cost (132 assets)</t>
-        </is>
-      </c>
-      <c r="B5" s="5">
-        <f>SUM('Corrected Register'!$M$5:$M$136)</f>
+          <t>Corrected register - sum of acquisition cost (132 assets)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>332115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Fixed-asset ledger — sum of acquisition cost (129 assets)</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>SUM('Source Ledger'!$E$5:$E$133)</f>
+          <t>Fixed-asset ledger - sum of acquisition cost (129 assets)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>324740</v>
       </c>
     </row>
@@ -53950,41 +53923,37 @@
           <t>Acquisition cost difference (register − ledger)</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>B5-B6</f>
+      <c r="B7" s="5" t="n">
         <v>7375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Corrected register — remaining book value (ledger NBV where present; blank if missing)</t>
-        </is>
-      </c>
-      <c r="B8" s="5">
-        <f>SUM('Corrected Register'!$N$5:$N$136)</f>
+          <t>Corrected register - remaining book value (ledger NBV where present; blank if missing)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ledger — net book value, Active status only</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <f>SUMIF('Source Ledger'!$H$5:$H$133,"Active",'Source Ledger'!$G$5:$G$133)</f>
+          <t>Ledger - net book value, Active status only</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ledger — net book value, all statuses including Disposed</t>
-        </is>
-      </c>
-      <c r="B10" s="5">
-        <f>SUM('Source Ledger'!$G$5:$G$133)</f>
+          <t>Ledger - net book value, all statuses including Disposed</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
@@ -53994,8 +53963,7 @@
           <t>Assets with matching acquisition cost (register vs ledger)</t>
         </is>
       </c>
-      <c r="B11" s="5">
-        <f>COUNTA('Corrected Register'!$A$5:$A$136)-B12-B13</f>
+      <c r="B11" s="5" t="n">
         <v>122</v>
       </c>
     </row>
@@ -54005,8 +53973,7 @@
           <t>Assets with acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <f>COUNTIF(B24:B35,"Acquisition cost mismatch")</f>
+      <c r="B12" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -54016,8 +53983,7 @@
           <t>Assets on inventory missing from ledger</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <f>COUNTIF(B24:B35,"On inventory, missing from ledger")</f>
+      <c r="B13" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -54029,30 +53995,28 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="13">
-        <f>CONCATENATE("1) Three assets (MD-00130, MD-00131, MD-00132) appear on the operational register and PO-2023-0022 but have no fixed-asset ledger row. Combined register acquisition cost = $",TEXT(C33+C34+C35,"0.0"),".")</f>
-        <v/>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>1) Three assets (MD-00130, MD-00131, MD-00132) appear on the operational register and purchase orders but have no fixed-asset ledger row. Combined register acquisition cost = $8,345. MD-00130 ($700) and MD-00131 ($1,175) are under the $2,500 capitalization gate (expected FA absence). MD-00132 ($6,470) is capital-qualifying and is a Critical gap.</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="13">
-        <f>CONCATENATE("2) Seven assets have a systematic $175 ledger-over-register acquisition cost variance (MD-00017, MD-00034, MD-00051, MD-00068, MD-00085, MD-00102, MD-00119). Combined ledger cost excess = $",TEXT(E24+E25+E26+E27+E28+E29+E32,"#,##0"),".")</f>
-        <v/>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2) Seven assets have ledger-over-register acquisition cost variances (MD-00017 $85, MD-00034 $140, MD-00051 $210, MD-00068 $55, MD-00085 $195, MD-00102 $120, MD-00119 $165). Combined ledger cost excess = $970. PO approved amounts tie to the inventory lines; Finance should align the FAR. Per §9 these are High remediation items, not sole Critical blockers.</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>3) Seven assets have ledger-over-register acquisition cost variances (MD-00017 $85, MD-00034 $140, MD-00051 $210, MD-00068 $55, MD-00085 $195, MD-00102 $120, MD-00119 $165). Combined ledger cost excess = $970. PO approved amounts tie to the inventory lines; Finance should align the FAR. Per §9 these are High remediation items, not sole Critical blockers.</t>
+          <t>3) Eight disposal certificates clear operational status to Disposed with $0 NBV on ledger. Two recycler transfers (MD-00114, MD-00118) lack verified certificates; ledger already shows Disposed/$0 while operational status remains Retired/Pending Disposal. Active ledger NBV otherwise ties to corrected register remaining book value for assets present on both files.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>4) Eight disposal certificates clear operational status to Disposed with $0 NBV on ledger. Two recycler transfers (MD-00114, MD-00118) lack verified certificates; ledger already shows Disposed/$0 while operational status remains Retired/Pending Disposal. Active ledger NBV otherwise ties to corrected register remaining book value for assets present on both files.</t>
-        </is>
-      </c>
+      <c r="A20" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -54116,23 +54080,23 @@
       </c>
       <c r="C24" s="7">
         <f>IFERROR(XLOOKUP(A24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>1985</v>
+        <v/>
       </c>
       <c r="D24" s="7">
         <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>2070</v>
+        <v/>
       </c>
       <c r="E24" s="7">
         <f>IF(OR(C24="",D24=""),"",D24-C24)</f>
-        <v>85</v>
+        <v/>
       </c>
       <c r="F24" s="7">
         <f>IFERROR(XLOOKUP(A24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G24" s="7">
         <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -54153,23 +54117,23 @@
       </c>
       <c r="C25" s="7">
         <f>IFERROR(XLOOKUP(A25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>790</v>
+        <v/>
       </c>
       <c r="D25" s="7">
         <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>930</v>
+        <v/>
       </c>
       <c r="E25" s="7">
         <f>IF(OR(C25="",D25=""),"",D25-C25)</f>
-        <v>140</v>
+        <v/>
       </c>
       <c r="F25" s="7">
         <f>IFERROR(XLOOKUP(A25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>514.88</v>
+        <v/>
       </c>
       <c r="G25" s="7">
         <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>514.88</v>
+        <v/>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -54190,23 +54154,23 @@
       </c>
       <c r="C26" s="7">
         <f>IFERROR(XLOOKUP(A26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>1040</v>
+        <v/>
       </c>
       <c r="D26" s="7">
         <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>1250</v>
+        <v/>
       </c>
       <c r="E26" s="7">
         <f>IF(OR(C26="",D26=""),"",D26-C26)</f>
-        <v>210</v>
+        <v/>
       </c>
       <c r="F26" s="7">
         <f>IFERROR(XLOOKUP(A26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>573.03</v>
+        <v/>
       </c>
       <c r="G26" s="7">
         <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>573.03</v>
+        <v/>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -54227,23 +54191,23 @@
       </c>
       <c r="C27" s="7">
         <f>IFERROR(XLOOKUP(A27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>6425</v>
+        <v/>
       </c>
       <c r="D27" s="7">
         <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>6480</v>
+        <v/>
       </c>
       <c r="E27" s="7">
         <f>IF(OR(C27="",D27=""),"",D27-C27)</f>
-        <v>55</v>
+        <v/>
       </c>
       <c r="F27" s="7">
         <f>IFERROR(XLOOKUP(A27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>1436.28</v>
+        <v/>
       </c>
       <c r="G27" s="7">
         <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>1436.28</v>
+        <v/>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -54264,23 +54228,23 @@
       </c>
       <c r="C28" s="7">
         <f>IFERROR(XLOOKUP(A28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>1895</v>
+        <v/>
       </c>
       <c r="D28" s="7">
         <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>2090</v>
+        <v/>
       </c>
       <c r="E28" s="7">
         <f>IF(OR(C28="",D28=""),"",D28-C28)</f>
-        <v>195</v>
+        <v/>
       </c>
       <c r="F28" s="7">
         <f>IFERROR(XLOOKUP(A28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G28" s="7">
         <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -54301,23 +54265,23 @@
       </c>
       <c r="C29" s="7">
         <f>IFERROR(XLOOKUP(A29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="D29" s="7">
         <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>820</v>
+        <v/>
       </c>
       <c r="E29" s="7">
         <f>IF(OR(C29="",D29=""),"",D29-C29)</f>
-        <v>120</v>
+        <v/>
       </c>
       <c r="F29" s="7">
         <f>IFERROR(XLOOKUP(A29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>407.54</v>
+        <v/>
       </c>
       <c r="G29" s="7">
         <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>407.54</v>
+        <v/>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -54338,23 +54302,23 @@
       </c>
       <c r="C30" s="7">
         <f>IFERROR(XLOOKUP(A30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>610</v>
+        <v/>
       </c>
       <c r="D30" s="7">
         <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>610</v>
+        <v/>
       </c>
       <c r="E30" s="7">
         <f>IF(OR(C30="",D30=""),"",D30-C30)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F30" s="7">
         <f>IFERROR(XLOOKUP(A30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G30" s="7">
         <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -54375,23 +54339,23 @@
       </c>
       <c r="C31" s="7">
         <f>IFERROR(XLOOKUP(A31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>790</v>
+        <v/>
       </c>
       <c r="D31" s="7">
         <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>790</v>
+        <v/>
       </c>
       <c r="E31" s="7">
         <f>IF(OR(C31="",D31=""),"",D31-C31)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F31" s="7">
         <f>IFERROR(XLOOKUP(A31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G31" s="7">
         <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -54412,23 +54376,23 @@
       </c>
       <c r="C32" s="7">
         <f>IFERROR(XLOOKUP(A32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>950</v>
+        <v/>
       </c>
       <c r="D32" s="7">
         <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v>1115</v>
+        <v/>
       </c>
       <c r="E32" s="7">
         <f>IF(OR(C32="",D32=""),"",D32-C32)</f>
-        <v>165</v>
+        <v/>
       </c>
       <c r="F32" s="7">
         <f>IFERROR(XLOOKUP(A32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G32" s="7">
         <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -54444,12 +54408,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Below capitalization threshold — ledger absence expected</t>
+          <t>On inventory, missing from ledger (under-threshold)</t>
         </is>
       </c>
       <c r="C33" s="7">
         <f>IFERROR(XLOOKUP(A33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="D33" s="7">
         <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
@@ -54481,12 +54445,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Below capitalization threshold — ledger absence expected</t>
+          <t>On inventory, missing from ledger (under-threshold)</t>
         </is>
       </c>
       <c r="C34" s="7">
         <f>IFERROR(XLOOKUP(A34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>1175</v>
+        <v/>
       </c>
       <c r="D34" s="7">
         <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
@@ -54523,7 +54487,7 @@
       </c>
       <c r="C35" s="7">
         <f>IFERROR(XLOOKUP(A35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v>6470</v>
+        <v/>
       </c>
       <c r="D35" s="7">
         <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
@@ -54592,7 +54556,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -54802,7 +54765,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>2. Recover or loss-investigate all Verified Status = Missing assets (MD-00089–MD-00100).</t>
+          <t>2. Recover or loss-investigate all Verified Status = Missing assets (MD-00089-MD-00100).</t>
         </is>
       </c>
     </row>
@@ -54823,7 +54786,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>5. Obtain disposal certificates for MD-00114 and MD-00118 (and complete pending-disposal evidence for MD-00101–MD-00110) or restore to stock.</t>
+          <t>5. Obtain disposal certificates for MD-00114 and MD-00118 (and complete pending-disposal evidence for MD-00101-MD-00110) or restore to stock.</t>
         </is>
       </c>
     </row>
@@ -54987,11 +54950,10 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Evidence Index — Source Systems of Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Evidence Index - Source Systems of Record</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -55306,7 +55268,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -5757,9 +5757,8 @@
           <t>Corrected register acquisition cost</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>SUM('Corrected Register'!$M$5:$M$136)</f>
-        <v/>
+      <c r="B6" s="5" t="n">
+        <v>332115</v>
       </c>
     </row>
     <row r="7">
@@ -5768,9 +5767,8 @@
           <t>Remaining book value (ledger NBV where present)</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>SUM('Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B7" s="5" t="n">
+        <v>61561.6</v>
       </c>
     </row>
     <row r="8">
@@ -5779,9 +5777,8 @@
           <t>Open exceptions</t>
         </is>
       </c>
-      <c r="B8" s="5">
-        <f>COUNTIF('Exception Register'!$K$5:$K$167,"Open")</f>
-        <v/>
+      <c r="B8" s="5" t="n">
+        <v>163</v>
       </c>
     </row>
     <row r="9">
@@ -5790,9 +5787,8 @@
           <t>Certification blockers (Critical impact)</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <f>COUNTIF('Exception Register'!$C$5:$C$167,"Critical")</f>
-        <v/>
+      <c r="B9" s="5" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -5801,9 +5797,8 @@
           <t>Assets Missing / Cannot Locate</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Missing")</f>
-        <v/>
+      <c r="B10" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -5812,9 +5807,8 @@
           <t>Overdue returns (label ≠ proof)</t>
         </is>
       </c>
-      <c r="B11" s="5">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Return Overdue")</f>
-        <v/>
+      <c r="B11" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -5823,9 +5817,8 @@
           <t>Verified disposed with certificate</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Disposed")</f>
-        <v/>
+      <c r="B12" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -5834,9 +5827,8 @@
           <t>Custody chains documented</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <f>COUNTA(UNIQUE(FILTER('Custody Chain'!A5:A501,'Custody Chain'!A5:A501&lt;&gt;"")))</f>
-        <v/>
+      <c r="B13" s="5" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -5901,26 +5893,22 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A19)</f>
-        <v/>
-      </c>
-      <c r="C19" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A19,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B19" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>12961</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="F19" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E19,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="F19" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1194.95</v>
       </c>
     </row>
     <row r="20">
@@ -5929,26 +5917,22 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A20)</f>
-        <v/>
-      </c>
-      <c r="C20" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A20,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Mobile Device</t>
         </is>
       </c>
-      <c r="F20" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E20,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="F20" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>20855.29</v>
       </c>
     </row>
     <row r="21">
@@ -5957,26 +5941,22 @@
           <t>In Transit - Exception</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A21)</f>
-        <v/>
-      </c>
-      <c r="C21" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A21,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1019.4</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="F21" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E21,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="F21" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>11329.87</v>
       </c>
     </row>
     <row r="22">
@@ -5985,26 +5965,22 @@
           <t>In Use</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A22)</f>
-        <v/>
-      </c>
-      <c r="C22" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A22,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>25512.76</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Network Asset</t>
         </is>
       </c>
-      <c r="F22" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E22,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="F22" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>28181.49</v>
       </c>
     </row>
     <row r="23">
@@ -6013,13 +5989,11 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A23)</f>
-        <v/>
-      </c>
-      <c r="C23" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A23,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>6214.38</v>
       </c>
     </row>
     <row r="24">
@@ -6028,13 +6002,11 @@
           <t>Pending Redeployment</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A24)</f>
-        <v/>
-      </c>
-      <c r="C24" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A24,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>4851.08</v>
       </c>
     </row>
     <row r="25">
@@ -6043,13 +6015,11 @@
           <t>Retired/Pending Disposal</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A25)</f>
-        <v/>
-      </c>
-      <c r="C25" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A25,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B25" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>4811.33</v>
       </c>
     </row>
     <row r="26">
@@ -6058,13 +6028,11 @@
           <t>Return Overdue</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A26)</f>
-        <v/>
-      </c>
-      <c r="C26" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A26,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B26" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>6191.65</v>
       </c>
     </row>
     <row r="30">
@@ -6117,26 +6085,22 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A32)</f>
-        <v/>
-      </c>
-      <c r="C32" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A32,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B32" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>5184.18</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Cannot Locate</t>
         </is>
       </c>
-      <c r="F32" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E32,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F32" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>6214.38</v>
       </c>
     </row>
     <row r="33">
@@ -6145,26 +6109,22 @@
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A33)</f>
-        <v/>
-      </c>
-      <c r="C33" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A33,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B33" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>6267.29</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Closed Location Assignment</t>
         </is>
       </c>
-      <c r="F33" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E33,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F33" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>29098.84</v>
       </c>
     </row>
     <row r="34">
@@ -6173,26 +6133,22 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A34)</f>
-        <v/>
-      </c>
-      <c r="C34" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A34,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>11070.95</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Duplicate Serial Number</t>
         </is>
       </c>
-      <c r="F34" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E34,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>2503.11</v>
       </c>
     </row>
     <row r="35">
@@ -6201,26 +6157,22 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A35)</f>
-        <v/>
-      </c>
-      <c r="C35" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A35,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>5149.95</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Former Employee Assignment</t>
         </is>
       </c>
-      <c r="F35" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E35,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F35" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>22627.56</v>
       </c>
     </row>
     <row r="36">
@@ -6229,26 +6181,22 @@
           <t>Denver</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A36)</f>
-        <v/>
-      </c>
-      <c r="C36" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A36,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>5551.75</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Inventory-to-Ledger Difference</t>
         </is>
       </c>
-      <c r="F36" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E36,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F36" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>7440</v>
       </c>
     </row>
     <row r="37">
@@ -6257,26 +6205,22 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A37)</f>
-        <v/>
-      </c>
-      <c r="C37" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A37,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>10561</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Missing Disposal Evidence</t>
         </is>
       </c>
-      <c r="F37" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E37,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F37" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>4811.33</v>
       </c>
     </row>
     <row r="38">
@@ -6285,26 +6229,22 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A38)</f>
-        <v/>
-      </c>
-      <c r="C38" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A38,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B38" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>6214.38</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Overdue Return</t>
         </is>
       </c>
-      <c r="F38" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E38,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F38" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>6191.65</v>
       </c>
     </row>
     <row r="39">
@@ -6313,26 +6253,22 @@
           <t>Remote - Former Employee</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A39)</f>
-        <v/>
-      </c>
-      <c r="C39" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A39,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>4878.51</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
           <t>Shipment Mismatch</t>
         </is>
       </c>
-      <c r="F39" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E39,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F39" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2332.54</v>
       </c>
     </row>
     <row r="40">
@@ -6341,26 +6277,22 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A40)</f>
-        <v/>
-      </c>
-      <c r="C40" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A40,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B40" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
           <t>Unapproved Transfer</t>
         </is>
       </c>
-      <c r="F40" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E40,'Exception Register'!$G$5:$G$167)</f>
-        <v/>
+      <c r="F40" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2869.32</v>
       </c>
     </row>
     <row r="41">
@@ -6369,13 +6301,22 @@
           <t>Atlanta Warehouse</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A41)</f>
-        <v/>
-      </c>
-      <c r="C41" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A41,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>4351.05</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Below Capitalization Threshold</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1875</v>
       </c>
     </row>
     <row r="42">
@@ -6384,13 +6325,11 @@
           <t>Carrier Network / Unverified</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A42)</f>
-        <v/>
-      </c>
-      <c r="C42" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A42,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B42" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2332.54</v>
       </c>
     </row>
     <row r="43">
@@ -6399,13 +6338,11 @@
           <t>Disposed (certificate missing)</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A43)</f>
-        <v/>
-      </c>
-      <c r="C43" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A43,'Corrected Register'!$N$5:$N$136)</f>
-        <v/>
+      <c r="B43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -6703,7 +6640,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00001 is In Use in Chicago. Employee E0001 (Active) matches the register holder. equipment_transfer_log TR-00001, approval APR-00001; received Jan 21, 2026. Cost path: PO-2022-0001 into FA-000001.</t>
+          <t>Status for MD-00001: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $1895. hr_employee_status lists E0001 / Priya Shah as Active. Transfer TR-00001 received 2026-01-21; approval APR-00001. FAR row FA-000001; net book value $0. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6811,7 +6748,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00002: In Use in Dallas ($610). Employee E0002 (Active) matches the register holder. Assignment TR-00002; receive column 2026-02-25, approval APR-00002. Procurement PO-2022-0001 maps to ledger FA-000002.</t>
+          <t>Dallas holds MD-00002 (Dell U2723QE) as In Use. Acquisition $610. People file: E0002 (Marcus Ellison), status Active. Transfer TR-00002 received 2026-02-25; approval APR-00002. Fixed-asset extract includes FA-000002 (NBV $313.06). PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6919,7 +6856,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Cost $1085 on MD-00003; In Use at Denver. Employee E0003 (Active) matches the register holder. TR-00003 for MD-00003 - received 04/03/2026, approval APR-00003. Ledger FA-000003 backs PO-2022-0001 for MD-00003.</t>
+          <t>MD-00003 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1085. Custodian E0003 (Elena Kovacs) is Active in hr_employee_status. Transfer TR-00003 received 2026-04-03; approval APR-00003. Ledger FA-000003 on file; NBV $597.83. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -7027,7 +6964,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>MD-00004 lists In Use at New York (Cisco C9300, $6380). Employee E0004 (Active) matches the register holder. Inbound stamp on TR-00004 is May 01, 2026, approval APR-00004. Purchase order PO-2022-0001 and FAR row FA-000004 both cite MD-00004.</t>
+          <t>Status for MD-00004: In Use. Site New York. Model Cisco C9300; cost $6380. hr_employee_status lists E0004 / James Whitaker as Active. Transfer TR-00004 received 2026-05-01; approval APR-00004. FAR row FA-000004; net book value $940.62. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -7135,7 +7072,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Register MD-00005: In Use, Seattle, $2075 - MacBook Pro 14. Employee E0005 (Active) matches the register holder. Log TR-00005: received 2026-06-08, approval APR-00005. Capital trail MD-00005: PO-2022-0001 -&gt; FA-000005.</t>
+          <t>Seattle holds MD-00005 (MacBook Pro 14) as In Use. Acquisition $2075. People file: E0005 (Aisha Rahman), status Active. Transfer TR-00005 received 2026-06-08; approval APR-00005. Fixed-asset extract includes FA-000005 (NBV $0). PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -7243,7 +7180,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00006: In Use, Atlanta, $790 - Dell U2723QE. Employee E0006 (Active) matches the register holder. TR-00006 for MD-00006 - received 01/12/2026, approval APR-00006. PO-2022-0001 / FA-000006 support the cost basis.</t>
+          <t>MD-00006 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $790. Custodian E0006 (Colin Bergstrom) is Active in hr_employee_status. Transfer TR-00006 received 2026-01-12; approval APR-00006. Ledger FA-000006 on file; NBV $459.94. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7351,7 +7288,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00007 as In Use in Chicago. Employee E0007 (Active) matches the register holder. Movement TR-00007 posted 02/11/2026 and inbound Feb 17, 2026, approval APR-00007. Purchase order PO-2023-0002 and FAR row FA-000007 both cite MD-00007.</t>
+          <t>Status for MD-00007: In Use. Site Chicago. Model Samsung Galaxy S24; cost $950. hr_employee_status lists E0007 / Sofia Alvarez as Active. Transfer TR-00007 received 2026-02-17; approval APR-00007. FAR row FA-000007; net book value $632.68. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7459,7 +7396,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>MD-00008 (Cisco C9300) closed In Use / Dallas on $6245. Employee E0008 (Active) matches the register holder. Log TR-00008: received 2026-03-19, approval APR-00008. Capital trail MD-00008: PO-2023-0002 -&gt; FA-000008.</t>
+          <t>Dallas holds MD-00008 (Cisco C9300) as In Use. Acquisition $6245. People file: E0008 (Derek Nguyen), status Active. Transfer TR-00008 received 2026-03-19; approval APR-00008. Fixed-asset extract includes FA-000008 (NBV $1355.01). PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7567,7 +7504,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>MD-00009 carries In Use at Denver (Dell Latitude 7440, $1940). Employee E0009 (Active) matches the register holder. Assignment TR-00009; receive column 04/21/2026, approval APR-00009. PO-2023-0002 and FA-000009 agree on MD-00009.</t>
+          <t>MD-00009 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1940. Custodian E0009 (Hannah Cole) is Active in hr_employee_status. Transfer TR-00009 received 2026-04-21; approval APR-00009. Ledger FA-000009 on file; NBV $109.33. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7675,7 +7612,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00010 In Use @ New York. Employee E0010 (Active) matches the register holder. Log TR-00010: received May 28, 2026, approval APR-00010. Ledger FA-000010 backs PO-2023-0002 for MD-00010.</t>
+          <t>Status for MD-00010: In Use. Site New York. Model Dell U2723QE; cost $655. hr_employee_status lists E0010 / Owen Patel as Active. Transfer TR-00010 received 2026-05-28; approval APR-00010. FAR row FA-000010; net book value $426.89. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7783,7 +7720,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00011 is In Use in Seattle site; basis $1130. Employee E0011 (Active) matches the register holder. Assignment TR-00011; receive column 2026-06-28, approval APR-00011. Purchase order PO-2023-0002 and FAR row FA-000011 both cite MD-00011.</t>
+          <t>Seattle holds MD-00011 (Samsung Galaxy S24) as In Use. Acquisition $1130. People file: E0011 (Maya Fontaine), status Active. Transfer TR-00011 received 2026-06-28; approval APR-00011. Fixed-asset extract includes FA-000011 (NBV $882.5). PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7891,7 +7828,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Read MD-00012 against transfers before signing In Use / Atlanta. Employee E0012 (Active) matches the register holder. Transfer TR-00012 shows receipt 01/31/2026, approval APR-00012. Capital trail MD-00012: PO-2023-0002 -&gt; FA-000012.</t>
+          <t>MD-00012 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6425. Custodian E0012 (Ryan Okonkwo) is Active in hr_employee_status. Transfer TR-00012 received 2026-01-31; approval APR-00012. Ledger FA-000012 on file; NBV $553.23. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7999,7 +7936,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Did not move MD-00013 off In Use at Chicago without a transaction. Employee E0013 (Active) matches the register holder. Inbound stamp on TR-00013 is Feb 06, 2026, approval APR-00013. Procurement PO-2024-0003 maps to ledger FA-000013.</t>
+          <t>Status for MD-00013: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $2120. hr_employee_status lists E0013 / Lauren Briggs as Active. Transfer TR-00013 received 2026-02-06; approval APR-00013. FAR row FA-000013; net book value $0. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -8107,7 +8044,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Register MD-00014: In Use, Dallas, $520 - Dell U2723QE. Employee E0014 (Active) matches the register holder. equipment_transfer_log TR-00014, approval APR-00014; received 2026-03-09. Ledger FA-000014 backs PO-2024-0003 for MD-00014.</t>
+          <t>Dallas holds MD-00014 (Dell U2723QE) as In Use. Acquisition $520. People file: E0014 (Nathan Kim), status Active. Transfer TR-00014 received 2026-03-09; approval APR-00014. Fixed-asset extract includes FA-000014 (NBV $270.29). PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8215,7 +8152,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 MD-00015 tied to $995; location Denver; status In Use. Employee E0015 (Active) matches the register holder. TR-00015 ties to MD-00015; dock date 04/13/2026, approval APR-00015. Purchase order PO-2024-0003 and FAR row FA-000015 both cite MD-00015.</t>
+          <t>MD-00015 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $995. Custodian E0015 (Camila Ortiz) is Active in hr_employee_status. Transfer TR-00015 received 2026-04-13; approval APR-00015. Ledger FA-000015 on file; NBV $559.13. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -8323,7 +8260,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 on MD-00016 is In Use in New York; basis $6290. Employee E0016 (Active) matches the register holder. Assignment TR-00016; receive column May 17, 2026, approval APR-00016. Procurement PO-2024-0003 maps to ledger FA-000016.</t>
+          <t>Status for MD-00016: In Use. Site New York. Model Cisco C9300; cost $6290. hr_employee_status lists E0016 / Patrick Gallagher as Active. Transfer TR-00016 received 2026-05-17; approval APR-00016. FAR row FA-000016; net book value $968.69. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -8431,7 +8368,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Assignment trail and HR both fit In Use for MD-00017 in Seattle. Employee E0017 (Active) matches the register holder. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. Ledger FA-000017 backs PO-2024-0003 for MD-00017.</t>
+          <t>Seattle holds MD-00017 (MacBook Pro 14) as In Use. Acquisition $1985. People file: E0017 (Irene Cho), status Active. Transfer TR-00017 received 2026-06-19; approval APR-00017. Fixed-asset extract includes FA-000017 (NBV $0). PO PO-2024-0003. Accumulated depreciation $2160 exceeds acquisition $2070 by $90.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8543,7 +8480,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>People and transfer logs align on MD-00018 - In Use, Atlanta. Employee E0018 (Active) matches the register holder. Inbound stamp on TR-00018 is 01/23/2026, approval APR-00018. Purchase order PO-2024-0003 and FAR row FA-000018 both cite MD-00018.</t>
+          <t>MD-00018 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $700. Custodian E0018 (Theo Barnett) is Active in hr_employee_status. Transfer TR-00018 received 2026-01-23; approval APR-00018. Ledger FA-000018 on file; NBV $412.14. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8651,7 +8588,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>MD-00019 sits In Use at Chicago (Samsung Galaxy S24, $1175). Employee E0019 (Active) matches the register holder. equipment_transfer_log TR-00019, approval APR-00019; received Feb 26, 2026. Cost path: PO-2025-0004 into FA-000019.</t>
+          <t>Status for MD-00019: In Use. Site Chicago. Model Samsung Galaxy S24; cost $1175. hr_employee_status lists E0019 / Jasmine Reed as Active. Transfer TR-00019 received 2026-02-26; approval APR-00019. FAR row FA-000019; net book value $795.4. PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -8759,7 +8696,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 MD-00020 tied to $6470; location Dallas; status In Use. Employee E0020 (Active) matches the register holder. Inbound stamp on TR-00020 is 2026-03-30, approval APR-00020. PO-2025-0004 and FA-000020 agree on MD-00020.</t>
+          <t>Dallas holds MD-00020 (Cisco C9300) as In Use. Acquisition $6470. People file: E0020 (Luis Navarro), status Active. Transfer TR-00020 received 2026-03-30; approval APR-00020. Fixed-asset extract includes FA-000020 (NBV $1446.34). PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -8867,7 +8804,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00021 In Use. Employee E0021 (Active) matches the register holder. equipment_transfer_log TR-00021, approval APR-00021; received 05/03/2026. PO-2025-0004 / FA-000021 support the cost basis. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>MD-00021 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1850. Custodian E0021 (Grace Lindholm) is Active in hr_employee_status. Transfer TR-00021 received 2026-05-03; approval APR-00021. Ledger FA-000021 on file; NBV $124.52. PO PO-2025-0004. Duplicate serial MD-LA-050021 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -8979,7 +8916,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>MD-00022 lists In Use at New York (Dell U2723QE, $565). Employee E0022 (Active) matches the register holder. TR-00022 ties to MD-00022; dock date Jun 05, 2026, approval APR-00022. FAR extract includes FA-000022 for MD-00022 via PO-2025-0004.</t>
+          <t>Status for MD-00022: In Use. Site New York. Model Dell U2723QE; cost $565. hr_employee_status lists E0022 / Andre Baptiste as Active. Transfer TR-00022 received 2026-06-05; approval APR-00022. FAR row FA-000022; net book value $371.95. PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -9087,7 +9024,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>In Use / Seattle on MD-00023 (Samsung Galaxy S24, $1040) per cited files. Employee E0023 (Active) matches the register holder. TR-00023 for MD-00023 - received 2026-07-09, approval APR-00023. Cost path: PO-2025-0004 into FA-000023.</t>
+          <t>Seattle holds MD-00023 (Samsung Galaxy S24) as In Use. Acquisition $1040. People file: E0023 (Nina Kowalski), status Active. Transfer TR-00023 received 2026-07-09; approval APR-00023. Fixed-asset extract includes FA-000023 (NBV $823.6). PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -9195,7 +9132,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Extract row MD-00024: In Use, Atlanta, $6335 - Cisco C9300. Employee E0024 (Active) matches the register holder. Movement TR-00024 posted 2026-01-18 and inbound 01/21/2026, approval APR-00024. Procurement PO-2025-0004 maps to ledger FA-000024.</t>
+          <t>MD-00024 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6335. Custodian E0024 (Chris Daley) is Active in hr_employee_status. Transfer TR-00024 received 2026-01-21; approval APR-00024. Ledger FA-000024 on file; NBV $503.85. PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -9303,7 +9240,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Cost $2030 on MD-00025; In Use at Chicago. Employee E0025 (Active) matches the register holder. Log TR-00025: received Jan 22, 2026, approval APR-00025. Ledger FA-000025 backs PO-2022-0005 for MD-00025. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>Status for MD-00025: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $2030. hr_employee_status lists E0025 / Fatima Hussein as Active. Transfer TR-00025 received 2026-01-22; approval APR-00025. FAR row FA-000025; net book value $0. PO PO-2022-0005. Duplicate serial MD-LA-050021 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -9415,7 +9352,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00026 as In Use (Dallas). Employee E0026 (Active) matches the register holder. equipment_transfer_log TR-00026, approval APR-00026; received 2026-02-27. Cost path: PO-2022-0005 into FA-000026.</t>
+          <t>Dallas holds MD-00026 (Dell U2723QE) as In Use. Acquisition $745. People file: E0026 (Brendan Walsh), status Active. Transfer TR-00026 received 2026-02-27; approval APR-00026. Fixed-asset extract includes FA-000026 (NBV $382.34). PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -9527,7 +9464,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>MD-00027 reads In Use at Denver (Samsung Galaxy S24, $1220). Employee E0027 (Active) matches the register holder. TR-00027 ties to MD-00027; dock date 04/06/2026, approval APR-00027. Procurement PO-2022-0005 maps to ledger FA-000027.</t>
+          <t>MD-00027 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1220. Custodian E0027 (Yuki Tanaka) is Active in hr_employee_status. Transfer TR-00027 received 2026-04-06; approval APR-00027. Ledger FA-000027 on file; NBV $672.21. PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -9639,7 +9576,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Kept MD-00028 at In Use in New York; $6200 Cisco C9300. Employee E0028 (Active) matches the register holder. TR-00028 for MD-00028 - received May 02, 2026, approval APR-00028. Ledger FA-000028 backs PO-2022-0005 for MD-00028.</t>
+          <t>Status for MD-00028: In Use. Site New York. Model Cisco C9300; cost $6200. hr_employee_status lists E0028 / Megan Copeland as Active. Transfer TR-00028 received 2026-05-02; approval APR-00028. FAR row FA-000028; net book value $914.09. PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -9751,7 +9688,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Asset row MD-00029: In Use, Seattle, $1895 - MacBook Pro 14. Employee E0029 (Active) matches the register holder. Movement TR-00029 posted Jun 05, 2026 and inbound 2026-06-11, approval APR-00029. Purchase order PO-2022-0005 and FAR row FA-000029 both cite MD-00029.</t>
+          <t>Seattle holds MD-00029 (MacBook Pro 14) as In Use. Acquisition $1895. People file: E0029 (Omar Haddad), status Active. Transfer TR-00029 received 2026-06-11; approval APR-00029. Fixed-asset extract includes FA-000029 (NBV $0). PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -9863,7 +9800,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Cost $610 on MD-00030; In Use at Atlanta. Employee E0030 (Active) matches the register holder. TR-00030 for MD-00030 - received 01/13/2026, approval APR-00030. Cost path: PO-2022-0005 into FA-000030.</t>
+          <t>MD-00030 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $610. Custodian E0030 (Stephanie Ruiz) is Active in hr_employee_status. Transfer TR-00030 received 2026-01-13; approval APR-00030. Ledger FA-000030 on file; NBV $355.14. PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -9975,7 +9912,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Chicago: MD-00031 is In Use; cost $1085. Employee E0031 (Active) matches the register holder. Movement TR-00031 posted 02/11/2026 and inbound Feb 11, 2026, approval APR-00031. PO-2023-0006 and FA-000031 agree on MD-00031.</t>
+          <t>Status for MD-00031: In Use. Site Chicago. Model Samsung Galaxy S24; cost $1085. hr_employee_status lists E0031 / Keith Moreau as Active. Transfer TR-00031 received 2026-02-11; approval APR-00031. FAR row FA-000031; net book value $722.59. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -10087,7 +10024,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>MD-00032 stays In Use at Dallas (Cisco C9300, $6380). Employee E0032 (Active) matches the register holder. Log TR-00032: received 2026-03-22, approval APR-00032. PO-2023-0006 / FA-000032 support the cost basis.</t>
+          <t>Dallas holds MD-00032 (Cisco C9300) as In Use. Acquisition $6380. People file: E0032 (Diana Voss), status Active. Transfer TR-00032 received 2026-03-22; approval APR-00032. Fixed-asset extract includes FA-000032 (NBV $1384.3). PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -10199,7 +10136,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00033: In Use in Denver ($2075). Employee E0033 (Active) matches the register holder. Assignment TR-00033; receive column 04/22/2026, approval APR-00033. FAR extract includes FA-000033 for MD-00033 via PO-2023-0006.</t>
+          <t>MD-00033 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $2075. Custodian E0033 (Jordan Blake) is Active in hr_employee_status. Transfer TR-00033 received 2026-04-22; approval APR-00033. Ledger FA-000033 on file; NBV $116.93. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -10311,7 +10248,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00034 is In Use in New York office; basis $790. Employee E0034 (Active) matches the register holder. Transfer TR-00034 shows receipt May 22, 2026, approval APR-00034. Cost path: PO-2023-0006 into FA-000034.</t>
+          <t>Status for MD-00034: In Use. Site New York. Model Dell U2723QE; cost $790. hr_employee_status lists E0034 / Amelia Grant as Active. Transfer TR-00034 received 2026-05-22; approval APR-00034. FAR row FA-000034; net book value $514.88. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10423,7 +10360,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>MD-00035 shows In Use at Seattle (Samsung Galaxy S24, $950). Employee E0035 (Active) matches the register holder. Inbound stamp on TR-00035 is 2026-06-30, approval APR-00035. Procurement PO-2023-0006 maps to ledger FA-000035.</t>
+          <t>Seattle holds MD-00035 (Samsung Galaxy S24) as In Use. Acquisition $950. People file: E0035 (Rafael Mendes), status Active. Transfer TR-00035 received 2026-06-30; approval APR-00035. Fixed-asset extract includes FA-000035 (NBV $741.92). PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -10535,7 +10472,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>The cited records support In Use in Atlanta for MD-00036. Employee E0036 (Active) matches the register holder. Movement TR-00036 posted 2026-01-30 and inbound 02/01/2026, approval APR-00036. FAR extract includes FA-000036 for MD-00036 via PO-2023-0006.</t>
+          <t>MD-00036 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6245. Custodian E0036 (Kate Sorenson) is Active in hr_employee_status. Transfer TR-00036 received 2026-02-01; approval APR-00036. Ledger FA-000036 on file; NBV $537.73. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10647,7 +10584,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>MD-00037 remains In Use at Chicago (Lenovo ThinkPad T14, $1940). Employee E0037 (Active) matches the register holder. Log TR-00037: received Feb 02, 2026, approval APR-00037. Capital trail MD-00037: PO-2024-0007 -&gt; FA-000037.</t>
+          <t>Status for MD-00037: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $1940. hr_employee_status lists E0037 / Victor Lang as Active. Transfer TR-00037 received 2026-02-02; approval APR-00037. FAR row FA-000037; net book value $0. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -10759,7 +10696,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>MD-00038 reconciled In Use with Dallas as the working site. Employee E0038 (Active) matches the register holder. Assignment TR-00038; receive column 2026-03-11, approval APR-00038. PO-2024-0007 and FA-000038 agree on MD-00038.</t>
+          <t>Dallas holds MD-00038 (Dell U2723QE) as In Use. Acquisition $655. People file: E0038 (Noelle Harper), status Active. Transfer TR-00038 received 2026-03-11; approval APR-00038. Fixed-asset extract includes FA-000038 (NBV $340.46). PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10871,7 +10808,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00039 is In Use in floor Denver; basis $1130. Employee E0039 (Active) matches the register holder. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO-2024-0007 / FA-000039 support the cost basis.</t>
+          <t>MD-00039 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1130. Custodian E0039 (Samir Kapoor) is Active in hr_employee_status. Transfer TR-00039 received 2026-04-14; approval APR-00039. Ledger FA-000039 on file; NBV $635. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -10983,7 +10920,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>MD-00040 shows In Use at New York (Cisco C9300, $6425). Employee E0040 (Active) matches the register holder. Assignment TR-00040; receive column May 13, 2026, approval APR-00040. Purchase order PO-2024-0007 and FAR row FA-000040 both cite MD-00040.</t>
+          <t>Status for MD-00040: In Use. Site New York. Model Cisco C9300; cost $6425. hr_employee_status lists E0040 / Holly Jensen as Active. Transfer TR-00040 received 2026-05-13; approval APR-00040. FAR row FA-000040; net book value $989.48. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -11095,7 +11032,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00041 is In Use in Seattle. Employee E0041 (Active) matches the register holder. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. Capital trail MD-00041: PO-2024-0007 -&gt; FA-000041.</t>
+          <t>Seattle holds MD-00041 (MacBook Pro 14) as In Use. Acquisition $2120. People file: E0041 (Eric Vann), status Active. Transfer TR-00041 received 2026-06-20; approval APR-00041. Fixed-asset extract includes FA-000041 (NBV $0). PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -11207,7 +11144,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Inventory line MD-00042: In Use, Atlanta, $520 - Dell U2723QE. Employee E0042 (Active) matches the register holder. Inbound stamp on TR-00042 is 01/24/2026, approval APR-00042. PO-2024-0007 and FA-000042 agree on MD-00042.</t>
+          <t>MD-00042 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $520. Custodian E0042 (Claudia Rossi) is Active in hr_employee_status. Transfer TR-00042 received 2026-01-24; approval APR-00042. Ledger FA-000042 on file; NBV $306.16. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -11319,7 +11256,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00043 across CSV/XLSX inputs - In Use, Chicago. Employee E0043 (Active) matches the register holder. equipment_transfer_log TR-00043, approval APR-00043; received Mar 01, 2026. Ledger FA-000043 backs PO-2025-0008 for MD-00043.</t>
+          <t>Status for MD-00043: In Use. Site Chicago. Model Samsung Galaxy S24; cost $995. hr_employee_status lists E0043 / Tyler Brooks as Active. Transfer TR-00043 received 2026-03-01; approval APR-00043. FAR row FA-000043; net book value $673.55. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -11431,7 +11368,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Verified In Use for MD-00044 at Dallas; acquisition $6290. Employee E0044 (Active) matches the register holder. TR-00044 ties to MD-00044; dock date 2026-03-31, approval APR-00044. Purchase order PO-2025-0008 and FAR row FA-000044 both cite MD-00044.</t>
+          <t>Dallas holds MD-00044 (Cisco C9300) as In Use. Acquisition $6290. People file: E0044 (Leah Okada), status Active. Transfer TR-00044 received 2026-03-31; approval APR-00044. Fixed-asset extract includes FA-000044 (NBV $1406.1). PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -11543,7 +11480,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>MD-00045 reflects In Use at Denver (Dell Latitude 7440, $1985). Employee E0045 (Active) matches the register holder. TR-00045 for MD-00045 - received 05/03/2026, approval APR-00045. Capital trail MD-00045: PO-2025-0008 -&gt; FA-000045.</t>
+          <t>MD-00045 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1985. Custodian E0045 (Darnell Price) is Active in hr_employee_status. Transfer TR-00045 received 2026-05-03; approval APR-00045. Ledger FA-000045 on file; NBV $133.6. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -11651,7 +11588,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00046: Available in New York ($700). Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. Ledger FA-000046 backs PO-2025-0008 for MD-00046.</t>
+          <t>MD-00046 (Dell U2723QE) is Available at New York. Acquisition cost $700. Transfer TR-00046 received 2026-06-07; approval APR-00046. FAR row FA-000046; net book value $460.82. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -11759,7 +11696,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>MD-00047 stays Available at Seattle (Samsung Galaxy S24, $1175). Inbound stamp on TR-00047 is 2026-07-10, approval APR-00047. Purchase order PO-2025-0008 and FAR row FA-000047 both cite MD-00047.</t>
+          <t>MD-00047 (Samsung Galaxy S24) is Available at Seattle. Acquisition cost $1175. Transfer TR-00047 received 2026-07-10; approval APR-00047. Fixed-asset extract includes FA-000047 (NBV $930.51). PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -11867,7 +11804,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Atlanta: MD-00048 is Available; cost $6470. equipment_transfer_log TR-00048, approval APR-00048; received 01/24/2026. Capital trail MD-00048: PO-2025-0008 -&gt; FA-000048.</t>
+          <t>MD-00048 (Cisco C9300) is Available at Atlanta. Acquisition cost $6470. Transfer TR-00048 received 2026-01-24; approval APR-00048. Ledger FA-000048 on file; NBV $514.59. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -11975,7 +11912,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Cost $1850 on MD-00049; Available at Chicago. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. PO-2022-0009 and FA-000049 agree on MD-00049.</t>
+          <t>MD-00049 (Lenovo ThinkPad T14) is Available at Chicago. Acquisition cost $1850. Transfer TR-00049 received 2026-01-23; approval APR-00049. FAR row FA-000049; net book value $0. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -12083,7 +12020,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Asset row MD-00050: Available, Dallas, $565 - Dell U2723QE. equipment_transfer_log TR-00050, approval APR-00050; received 2026-02-23. Ledger FA-000050 backs PO-2022-0009 for MD-00050.</t>
+          <t>MD-00050 (Dell U2723QE) is Available at Dallas. Acquisition cost $565. Transfer TR-00050 received 2026-02-23; approval APR-00050. Fixed-asset extract includes FA-000050 (NBV $289.96). PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -12191,7 +12128,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Kept MD-00051 at Available in Denver; $1040 Samsung Galaxy S24. TR-00051 ties to MD-00051; dock date 03/31/2026, approval APR-00051. Purchase order PO-2022-0009 and FAR row FA-000051 both cite MD-00051.</t>
+          <t>MD-00051 (Samsung Galaxy S24) is Available at Denver. Acquisition cost $1040. Transfer TR-00051 received 2026-03-31; approval APR-00051. Ledger FA-000051 on file; NBV $573.03. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -12299,7 +12236,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>MD-00052 reads Available at New York (Cisco C9300, $6335). TR-00052 for MD-00052 - received May 02, 2026, approval APR-00052. Capital trail MD-00052: PO-2022-0009 -&gt; FA-000052.</t>
+          <t>MD-00052 (Cisco C9300) is Available at New York. Acquisition cost $6335. Transfer TR-00052 received 2026-05-02; approval APR-00052. FAR row FA-000052; net book value $933.99. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -12407,7 +12344,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00053 as Available (Seattle). Movement TR-00053 posted Jun 05, 2026 and inbound 2026-06-05, approval APR-00053. PO-2022-0009 and FA-000053 agree on MD-00053.</t>
+          <t>MD-00053 (MacBook Pro 14) is Available at Seattle. Acquisition cost $2030. Transfer TR-00053 received 2026-06-05; approval APR-00053. Fixed-asset extract includes FA-000053 (NBV $0). PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -12515,7 +12452,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>No stronger file contradicted Available for MD-00054 at Atlanta. Log TR-00054: received 01/16/2026, approval APR-00054. PO-2022-0009 / FA-000054 support the cost basis.</t>
+          <t>MD-00054 (Dell U2723QE) is Available at Atlanta. Acquisition cost $745. Transfer TR-00054 received 2026-01-16; approval APR-00054. Ledger FA-000054 on file; NBV $433.74. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -12623,7 +12560,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>MD-00055 sits Available at Chicago (Samsung Galaxy S24, $1220). Assignment TR-00055; receive column Feb 12, 2026, approval APR-00055. Ledger FA-000055 backs PO-2023-0010 for MD-00055.</t>
+          <t>MD-00055 (Samsung Galaxy S24) is Available at Chicago. Acquisition cost $1220. Transfer TR-00055 received 2026-02-12; approval APR-00055. FAR row FA-000055; net book value $812.5. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -12731,7 +12668,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Available / Dallas on MD-00056 (Cisco C9300, $6200) per cited files. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. Cost path: PO-2023-0010 into FA-000056.</t>
+          <t>MD-00056 (Cisco C9300) is Available at Dallas. Acquisition cost $6200. Transfer TR-00056 received 2026-03-16; approval APR-00056. Fixed-asset extract includes FA-000056 (NBV $1345.24). PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -12839,7 +12776,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>MD-00057 lists Available at Denver (Dell Latitude 7440, $1895). TR-00057 for MD-00057 - received 04/24/2026, approval APR-00057. Procurement PO-2023-0010 maps to ledger FA-000057.</t>
+          <t>MD-00057 (Dell Latitude 7440) is Available at Denver. Acquisition cost $1895. Transfer TR-00057 received 2026-04-24; approval APR-00057. Ledger FA-000057 on file; NBV $106.79. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -12951,7 +12888,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>Read MD-00058 against transfers before signing Pending Redeployment / New York. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. Ledger FA-000058 backs PO-2023-0010 for MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
+          <t>MD-00058 (Dell U2723QE) is Pending Redeployment at New York. Acquisition cost $610. Transfer TR-00058 received 2026-05-23; approval blank. FAR row FA-000058; net book value $397.56. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -13063,7 +13000,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00059 Pending Redeployment. Log TR-00059: received 2026-06-26, approval field blank. Purchase order PO-2023-0010 and FAR row FA-000059 both cite MD-00059. Also: offboarding ticket OFF-00059 referenced.</t>
+          <t>MD-00059 (Samsung Galaxy S24) is Pending Redeployment at Seattle. Acquisition cost $1085. Transfer TR-00059 received 2026-06-26; approval blank. Fixed-asset extract includes FA-000059 (NBV $847.35). PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -13175,7 +13112,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>The cited records support Pending Redeployment in Atlanta for MD-00060. Movement TR-00060 posted 2026-01-30 and inbound 02/02/2026, approval APR-00060. Cost path: PO-2023-0010 into FA-000060. Also: offboarding ticket OFF-00060 referenced.</t>
+          <t>MD-00060 (Cisco C9300) is Pending Redeployment at Atlanta. Acquisition cost $6380. Transfer TR-00060 received 2026-02-02; approval APR-00060. Ledger FA-000060 on file; NBV $549.35. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -13287,7 +13224,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Chicago holds MD-00061 (Lenovo ThinkPad T14) as Pending Redeployment. Log TR-00061: received Feb 03, 2026, approval APR-00061. PO-2024-0011 and FA-000061 agree on MD-00061. Also: offboarding ticket OFF-00061 referenced.</t>
+          <t>MD-00061 (Lenovo ThinkPad T14) is Pending Redeployment at Chicago. Acquisition cost $2075. Transfer TR-00061 received 2026-02-03; approval APR-00061. FAR row FA-000061; net book value $0. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -13399,7 +13336,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 (Dell U2723QE) closed Pending Redeployment / Dallas on $790. Assignment TR-00062; receive column 2026-03-07, approval APR-00062. PO-2024-0011 / FA-000062 support the cost basis. Also: offboarding ticket OFF-00062 referenced.</t>
+          <t>MD-00062 (Dell U2723QE) is Pending Redeployment at Dallas. Acquisition cost $790. Transfer TR-00062 received 2026-03-07; approval APR-00062. Fixed-asset extract includes FA-000062 (NBV $410.63). PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -13511,7 +13448,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Assignment trail and HR both fit Pending Redeployment for MD-00063 in Denver. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. FAR extract includes FA-000063 for MD-00063 via PO-2024-0011. Also: offboarding ticket OFF-00063 referenced.</t>
+          <t>MD-00063 (Samsung Galaxy S24) is Pending Redeployment at Denver. Acquisition cost $950. Transfer TR-00063 received 2026-04-16; approval APR-00063. Ledger FA-000063 on file; NBV $533.85. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -13623,7 +13560,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00064 as Pending Redeployment (New York). Inbound stamp on TR-00064 is May 14, 2026, approval field blank. Cost path: PO-2024-0011 into FA-000064. Also: offboarding ticket OFF-00064 referenced.</t>
+          <t>MD-00064 (Cisco C9300) is Pending Redeployment at New York. Acquisition cost $6245. Transfer TR-00064 received 2026-05-14; approval blank. FAR row FA-000064; net book value $961.76. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -13735,7 +13672,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 still Pending Redeployment; Seattle is the verified site. equipment_transfer_log TR-00065, approval field blank; received 2026-06-23. Procurement PO-2024-0011 maps to ledger FA-000065. Also: offboarding ticket OFF-00065 referenced.</t>
+          <t>MD-00065 (MacBook Pro 14) is Pending Redeployment at Seattle. Acquisition cost $1940. Transfer TR-00065 received 2026-06-23; approval blank. Fixed-asset extract includes FA-000065 (NBV $0). PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -13847,7 +13784,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00066 is Pending Redeployment in Atlanta office; basis $655. Log TR-00066: received 01/25/2026, approval APR-00066. FAR extract includes FA-000066 for MD-00066 via PO-2024-0011. Also: offboarding ticket OFF-00066 referenced.</t>
+          <t>MD-00066 (Dell U2723QE) is Pending Redeployment at Atlanta. Acquisition cost $655. Transfer TR-00066 received 2026-01-25; approval APR-00066. Ledger FA-000066 on file; NBV $385.65. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -13959,7 +13896,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00067 across CSV/XLSX inputs - Pending Redeployment, Chicago. Assignment TR-00067; receive column Feb 23, 2026, approval APR-00067. Capital trail MD-00067: PO-2025-0012 -&gt; FA-000067. Also: offboarding ticket OFF-00067 referenced.</t>
+          <t>MD-00067 (Samsung Galaxy S24) is Pending Redeployment at Chicago. Acquisition cost $1130. Transfer TR-00067 received 2026-02-23; approval APR-00067. FAR row FA-000067; net book value $764.93. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -14071,7 +14008,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>MD-00068: Cisco C9300, $6425, status Return Overdue, site Remote - Former Employee. Employment file: E0081 remains Separated. Transfer TR-00068 shows receipt 2026-04-03, approval APR-00068. PO-2025-0012 and FA-000068 agree on MD-00068. Also: carrier label 1ZMD00000068 is not proof of receipt. Note - offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
+          <t>Offboarding return for MD-00068 lacks complete shipment proof; status remains Return Overdue. People file: E0081 (Elliott Park), status Separated. Transfer TR-00068 received 2026-04-03; approval APR-00068. Service desk ticket OFF-00068 on file. Fixed-asset extract includes FA-000068 (NBV $1436.28). PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -14183,7 +14120,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>MD-00069 carries Return Overdue at Remote - Former Employee (Dell Latitude 7440, $2120). Employment file: E0082 remains Separated. Inbound stamp on TR-00069 is 05/04/2026, approval APR-00069. PO-2025-0012 / FA-000069 support the cost basis. Also: carrier label 1ZMD00000069 is not proof of receipt. Note - offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00069 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0082 (Carmen Diaz) is Separated in hr_employee_status. Transfer TR-00069 received 2026-05-04; approval APR-00069. Service desk ticket OFF-00069 on file. Ledger FA-000069 on file; NBV $142.69. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -14295,7 +14232,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 stays Return Overdue at Remote - Former Employee (Dell U2723QE, $520). HR agrees Hugh Talbot (E0083) is still Separated. Transfer TR-00070 shows receipt Jun 03, 2026, approval APR-00070. Purchase order PO-2025-0012 and FAR row FA-000070 both cite MD-00070. Also: carrier label 1ZMD00000070 is not proof of receipt. Note - offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
+          <t>MD-00070 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0083 / Hugh Talbot as Separated. Transfer TR-00070 received 2026-06-03; approval APR-00070. Service desk ticket OFF-00070 on file. FAR row FA-000070; net book value $342.32. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -14407,7 +14344,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00071 is Return Overdue in Remote - Former Employee. HR agrees Mira Adelman (E0084) is still Separated. Inbound stamp on TR-00071 is 2026-07-12, approval APR-00071. Capital trail MD-00071: PO-2025-0012 -&gt; FA-000071. Also: carrier label 1ZMD00000071 is not proof of receipt. Note - offboarding ticket OFF-00071 referenced. return still label-only per shipment file.</t>
+          <t>Offboarding return for MD-00071 lacks complete shipment proof; status remains Return Overdue. People file: E0084 (Mira Adelman), status Separated. Transfer TR-00071 received 2026-07-12; approval APR-00071. Service desk ticket OFF-00071 on file. Fixed-asset extract includes FA-000071 (NBV $787.96). PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -14519,7 +14456,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>MD-00072 reflects Return Overdue at Remote - Former Employee (Cisco C9300, $6290). HR agrees Quincy Rhodes (E0085) is still Separated. equipment_transfer_log TR-00072, approval APR-00072; received 01/18/2026. PO-2025-0012 and FA-000072 agree on MD-00072. Also: carrier label 1ZMD00000072 is not proof of receipt. Note - offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00072 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0085 (Quincy Rhodes) is Separated in hr_employee_status. Transfer TR-00072 received 2026-01-18; approval APR-00072. Service desk ticket OFF-00072 on file. Ledger FA-000072 on file; NBV $500.27. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -14631,7 +14568,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>Did not move MD-00073 off Return Overdue at Remote - Former Employee without a transaction. HR agrees Sloane Richter (E0086) is still Separated. TR-00073 ties to MD-00073; dock date Jan 24, 2026, approval APR-00073. PO-2022-0013 / FA-000073 support the cost basis. Also: carrier label 1ZMD00000073 is not proof of receipt. Note - offboarding ticket OFF-00073 referenced. return still label-only per shipment file.</t>
+          <t>MD-00073 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0086 / Sloane Richter as Separated. Transfer TR-00073 received 2026-01-24; approval APR-00073. Service desk ticket OFF-00073 on file. FAR row FA-000073; net book value $0. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -14743,7 +14680,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 lists Return Overdue at Carrier Network / Unverified (Dell U2723QE, $700). HR agrees Nolan Vega (E0087) is still Separated. TR-00074 for MD-00074 - received 2026-02-24, approval APR-00074. FAR extract includes FA-000074 for MD-00074 via PO-2022-0013. Also: carrier label 1ZMD00000074 is not proof of receipt. Note - offboarding ticket OFF-00074 referenced. return still label-only per shipment file. shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
+          <t>Offboarding return for MD-00074 lacks complete shipment proof; status remains Return Overdue. People file: E0087 (Nolan Vega), status Separated. Transfer TR-00074 received 2026-02-24; approval APR-00074. Service desk ticket OFF-00074 on file. Fixed-asset extract includes FA-000074 (NBV $359.25). PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -14855,7 +14792,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee: MD-00075 is Return Overdue; cost $1175. HR agrees Ivy Chenoweth (E0088) is still Separated. Movement TR-00075 posted 2026-03-31 and inbound 04/01/2026, approval APR-00075. Cost path: PO-2022-0013 into FA-000075. Also: carrier label 1ZMD00000075 is not proof of receipt. Note - offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00075 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0088 (Ivy Chenoweth) is Separated in hr_employee_status. Transfer TR-00075 received 2026-04-01; approval APR-00075. Service desk ticket OFF-00075 on file. Ledger FA-000075 on file; NBV $647.42. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -14967,7 +14904,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 reads Return Overdue at Carrier Network / Unverified (Cisco C9300, $6470). HR agrees Percy Lambert (E0089) is still Separated. Inbound stamp on TR-00076 is May 03, 2026, approval APR-00076. PO-2022-0013 / FA-000076 support the cost basis. Also: carrier label 1ZMD00000076 is not proof of receipt. Note - offboarding ticket OFF-00076 referenced. return still label-only per shipment file. shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
+          <t>MD-00076 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0089 / Percy Lambert as Separated. Transfer TR-00076 received 2026-05-03; approval APR-00076. Service desk ticket OFF-00076 on file. FAR row FA-000076; net book value $953.89. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -15079,7 +15016,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>The cited records support Return Overdue in Remote - Former Employee for MD-00077. Employment file: E0090 remains Separated. equipment_transfer_log TR-00077, approval APR-00077; received 2026-06-06. FAR extract includes FA-000077 for MD-00077 via PO-2022-0013. Also: carrier label 1ZMD00000077 is not proof of receipt. Note - offboarding ticket OFF-00077 referenced. return still label-only per shipment file.</t>
+          <t>Offboarding return for MD-00077 lacks complete shipment proof; status remains Return Overdue. People file: E0090 (Dana Ghosh), status Separated. Transfer TR-00077 received 2026-06-06; approval APR-00077. Service desk ticket OFF-00077 on file. Fixed-asset extract includes FA-000077 (NBV $0). PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -15191,7 +15128,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee holds MD-00078 (Dell U2723QE) as Return Overdue. Employment file: E0091 remains Separated. TR-00078 ties to MD-00078; dock date 01/10/2026, approval APR-00078. Cost path: PO-2022-0013 into FA-000078. Also: carrier label 1ZMD00000078 is not proof of receipt. Note - offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00078 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0091 (Harlan Smith) is Separated in hr_employee_status. Transfer TR-00078 received 2026-01-10; approval APR-00078. Service desk ticket OFF-00078 on file. Ledger FA-000078 on file; NBV $328.95. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -15303,7 +15240,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>MD-00079 (Samsung Galaxy S24) closed Return Overdue / Remote - Former Employee on $1040. Employment file: E0092 remains Separated. TR-00079 for MD-00079 - received Feb 13, 2026, approval APR-00079. PO-2023-0014 and FA-000079 agree on MD-00079. Also: carrier label 1ZMD00000079 is not proof of receipt. Note - offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
+          <t>MD-00079 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0092 / June Okoye as Separated. Transfer TR-00079 received 2026-02-13; approval APR-00079. Service desk ticket OFF-00079 on file. FAR row FA-000079; net book value $692.62. PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -15415,7 +15352,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>Atlanta Warehouse holds MD-00080 (Cisco C9300) as Available. TR-00080 ties to MD-00080; dock date 2026-03-17, approval APR-00080. Ledger FA-000080 backs PO-2023-0014 for MD-00080. Also: carrier label 1ZMD00000080 is not proof of receipt. Note - offboarding ticket OFF-00080 referenced.</t>
+          <t>MD-00080 (Cisco C9300) is Available at Atlanta Warehouse. Acquisition cost $6335. Transfer TR-00080 received 2026-03-17; approval APR-00080. Fixed-asset extract includes FA-000080 (NBV $1374.53). PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -15527,7 +15464,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 on MD-00081 is Available in floor Atlanta Warehouse; basis $2030. TR-00081 for MD-00081 - received 04/20/2026, approval APR-00081. Purchase order PO-2023-0014 and FAR row FA-000081 both cite MD-00081. Also: carrier label 1ZMD00000081 is not proof of receipt. Note - offboarding ticket OFF-00081 referenced.</t>
+          <t>MD-00081 (Dell Latitude 7440) is Available at Atlanta Warehouse. Acquisition cost $2030. Transfer TR-00081 received 2026-04-20; approval APR-00081. Ledger FA-000081 on file; NBV $114.4. PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -15639,7 +15576,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00082 In Transit - Exception @ Carrier Network / Unverified. HR agrees Emmett Boyle (E0095) is still Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. Capital trail MD-00082: PO-2023-0014 -&gt; FA-000082. Also: carrier label 1ZMD00000082 is not proof of receipt. Note - offboarding ticket OFF-00082 referenced. shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
+          <t>MD-00082 is In Transit - Exception at Carrier Network / Unverified; shipment documentation is incomplete. hr_employee_status lists E0095 / Emmett Boyle as Separated. Transfer TR-00082 received 2026-05-24; approval APR-00082. Service desk ticket OFF-00082 on file. FAR row FA-000082; net book value $485.55. PO PO-2023-0014. Tracking 1ZMD00000082 receiving scan shows MISMATCH-0082 vs MD-MO-050082.</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -15751,7 +15688,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 remains Available at Atlanta Warehouse (Samsung Galaxy S24, $1220). Log TR-00083: received 2026-06-27, approval APR-00083. PO-2023-0014 and FA-000083 agree on MD-00083. Also: carrier label 1ZMD00000083 is not proof of receipt. Note - offboarding ticket OFF-00083 referenced.</t>
+          <t>MD-00083 (Samsung Galaxy S24) is Available at Atlanta Warehouse. Acquisition cost $1220. Transfer TR-00083 received 2026-06-27; approval APR-00083. Fixed-asset extract includes FA-000083 (NBV $952.79). PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -15863,7 +15800,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Carrier Network / Unverified: MD-00084 is In Transit - Exception; cost $6200. Anita Bose has Separated status in the people extract. Assignment TR-00084; receive column 02/05/2026, approval APR-00084. PO-2023-0014 / FA-000084 support the cost basis. Also: carrier label 1ZMD00000084 is not proof of receipt. Note - offboarding ticket OFF-00084 referenced. shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
+          <t>MD-00084 is In Transit - Exception at Carrier Network / Unverified; shipment documentation is incomplete. Custodian E0072 (Anita Bose) is Separated in hr_employee_status. Transfer TR-00084 received 2026-02-05; approval APR-00084. Service desk ticket OFF-00084 on file. Ledger FA-000084 on file; NBV $533.85. PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -15975,7 +15912,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 still Available; Atlanta Warehouse is the verified site. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. Purchase order PO-2024-0015 and FAR row FA-000085 both cite MD-00085. Also: carrier label 1ZMD00000085 is not proof of receipt. Note - offboarding ticket OFF-00085 referenced.</t>
+          <t>MD-00085 (Lenovo ThinkPad T14) is Available at Atlanta Warehouse. Acquisition cost $1895. Transfer TR-00085 received 2026-02-03; approval APR-00085. FAR row FA-000085; net book value $0. PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -16087,7 +16024,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00086 is Available in Atlanta Warehouse office; basis $610. TR-00086 for MD-00086 - received 2026-03-08, approval APR-00086. Procurement PO-2024-0015 maps to ledger FA-000086. Also: carrier label 1ZMD00000086 is not proof of receipt. Note - offboarding ticket OFF-00086 referenced.</t>
+          <t>MD-00086 (Dell U2723QE) is Available at Atlanta Warehouse. Acquisition cost $610. Transfer TR-00086 received 2026-03-08; approval APR-00086. Fixed-asset extract includes FA-000086 (NBV $317.07). PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -16199,7 +16136,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00087: Available in Atlanta Warehouse ($1085). Movement TR-00087 posted 2026-04-12 and inbound 04/12/2026, approval APR-00087. Ledger FA-000087 backs PO-2024-0015 for MD-00087. Also: carrier label 1ZMD00000087 is not proof of receipt. Note - offboarding ticket OFF-00087 referenced.</t>
+          <t>MD-00087 (Samsung Galaxy S24) is Available at Atlanta Warehouse. Acquisition cost $1085. Transfer TR-00087 received 2026-04-12; approval APR-00087. Ledger FA-000087 on file; NBV $609.71. PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -16311,7 +16248,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>MD-00088 stays Available at Atlanta Warehouse (Cisco C9300, $6380). Log TR-00088: received May 14, 2026, approval APR-00088. Purchase order PO-2024-0015 and FAR row FA-000088 both cite MD-00088. Also: carrier label 1ZMD00000088 is not proof of receipt. Note - offboarding ticket OFF-00088 referenced. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>MD-00088 (Cisco C9300) is Available at Atlanta Warehouse. Acquisition cost $6380. Transfer TR-00088 received 2026-05-14; approval APR-00088. FAR row FA-000088; net book value $982.55. PO PO-2024-0015. Duplicate serial MD-NE-050088 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -16423,7 +16360,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00089: Missing, Unknown, $2075 - MacBook Pro 14. Jonah Freedman has Separated status in the people extract. Assignment TR-00089; receive column 2026-06-17, approval APR-00089. Capital trail MD-00089: PO-2024-0015 -&gt; FA-000089. Also: offboarding ticket OFF-00089 referenced. Note - last operational site on register was Denver - Closed.</t>
+          <t>Cannot confirm custody of MD-00089 at this time; register last pointed to Unknown. People file: E0077 (Jonah Freedman), status Separated. Transfer TR-00089 received 2026-06-17; approval APR-00089. Service desk ticket OFF-00089 on file. Fixed-asset extract includes FA-000089 (NBV $0). PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -16535,7 +16472,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00090 Missing. People side - Regina Lowe (E0078), Separated. Log TR-00090: received 01/28/2026, approval APR-00090. Procurement PO-2024-0015 maps to ledger FA-000090. Also: offboarding ticket OFF-00090 referenced. Note - last operational site on register was Chicago - Closed.</t>
+          <t>No confirmed location for MD-00090 (Dell U2723QE); last recorded site was Unknown. Custodian E0078 (Regina Lowe) is Separated in hr_employee_status. Transfer TR-00090 received 2026-01-28; approval APR-00090. Service desk ticket OFF-00090 on file. Ledger FA-000090 on file; NBV $465.13. PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -16647,7 +16584,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Unknown: MD-00091 is Missing; cost $950. People side - Wes Carvalho (E0079), Separated. Assignment TR-00091; receive column Feb 24, 2026, approval APR-00091. PO-2025-0016 / FA-000091 support the cost basis. Also: offboarding ticket OFF-00091 referenced. Note - last operational site on register was Denver - Closed.</t>
+          <t>MD-00091 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0079 / Wes Carvalho as Separated. Transfer TR-00091 received 2026-02-24; approval APR-00091. Service desk ticket OFF-00091 on file. FAR row FA-000091; net book value $643.09. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -16759,7 +16696,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00092 is Missing in Unknown. Tara Singh has Separated status in the people extract. Transfer TR-00092 shows receipt 2026-03-28, approval APR-00092. FAR extract includes FA-000092 for MD-00092 via PO-2025-0016. Also: offboarding ticket OFF-00092 referenced. Note - last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>Cannot confirm custody of MD-00092 at this time; register last pointed to Unknown. People file: E0080 (Tara Singh), status Separated. Transfer TR-00092 received 2026-03-28; approval APR-00092. Service desk ticket OFF-00092 on file. Fixed-asset extract includes FA-000092 (NBV $1396.04). PO PO-2025-0016. Duplicate serial MD-NE-050088 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -16871,7 +16808,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00093 Missing @ Unknown. Elliott Park has Separated status in the people extract. Inbound stamp on TR-00093 is 05/06/2026, approval APR-00093. Cost path: PO-2025-0016 into FA-000093. Also: offboarding ticket OFF-00093 referenced. Note - last operational site on register was Denver - Closed.</t>
+          <t>No confirmed location for MD-00093 (Dell Latitude 7440); last recorded site was Unknown. Custodian E0081 (Elliott Park) is Separated in hr_employee_status. Transfer TR-00093 received 2026-05-06; approval APR-00093. Service desk ticket OFF-00093 on file. Ledger FA-000093 on file; NBV $130.57. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -16983,7 +16920,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00094 tied to $655; location Unknown; status Missing. Carmen Diaz has Separated status in the people extract. equipment_transfer_log TR-00094, approval APR-00094; received Jun 04, 2026. Procurement PO-2025-0016 maps to ledger FA-000094. Also: offboarding ticket OFF-00094 referenced. Note - last operational site on register was Chicago - Closed.</t>
+          <t>MD-00094 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0082 / Carmen Diaz as Separated. Transfer TR-00094 received 2026-06-04; approval APR-00094. Service desk ticket OFF-00094 on file. FAR row FA-000094; net book value $431.2. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -17095,7 +17032,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Cost $1130 on MD-00095; Missing at Unknown. Hugh Talbot has Separated status in the people extract. TR-00095 ties to MD-00095; dock date 2026-07-08, approval APR-00095. Ledger FA-000095 backs PO-2025-0016 for MD-00095. Also: offboarding ticket OFF-00095 referenced. Note - last operational site on register was Denver - Closed.</t>
+          <t>Cannot confirm custody of MD-00095 at this time; register last pointed to Unknown. People file: E0083 (Hugh Talbot), status Separated. Transfer TR-00095 received 2026-07-08; approval APR-00095. Service desk ticket OFF-00095 on file. Fixed-asset extract includes FA-000095 (NBV $894.87). PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -17207,7 +17144,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>MD-00096 stays Missing at Unknown (Cisco C9300, $6425). Mira Adelman has Separated status in the people extract. Log TR-00096: received 01/19/2026, approval APR-00096. Procurement PO-2025-0016 maps to ledger FA-000096. Also: offboarding ticket OFF-00096 referenced. Note - last operational site on register was Chicago - Closed.</t>
+          <t>No confirmed location for MD-00096 (Cisco C9300); last recorded site was Unknown. Custodian E0084 (Mira Adelman) is Separated in hr_employee_status. Transfer TR-00096 received 2026-01-19; approval APR-00096. Service desk ticket OFF-00096 on file. Ledger FA-000096 on file; NBV $511.01. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -17319,7 +17256,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 stays Missing at Unknown (Lenovo ThinkPad T14, $2120). Quincy Rhodes has Separated status in the people extract. TR-00097 ties to MD-00097; dock date Jan 27, 2026, approval APR-00097. Ledger FA-000097 backs PO-2022-0017 for MD-00097. Also: offboarding ticket OFF-00097 referenced. Note - last operational site on register was Denver - Closed.</t>
+          <t>MD-00097 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0085 / Quincy Rhodes as Separated. Transfer TR-00097 received 2026-01-27; approval APR-00097. Service desk ticket OFF-00097 on file. FAR row FA-000097; net book value $0. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -17431,7 +17368,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>MD-00098 stays Missing at Unknown (Dell U2723QE, $520). Sloane Richter has Separated status in the people extract. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. Purchase order PO-2022-0017 and FAR row FA-000098 both cite MD-00098. Also: offboarding ticket OFF-00098 referenced. Note - last operational site on register was Chicago - Closed.</t>
+          <t>Cannot confirm custody of MD-00098 at this time; register last pointed to Unknown. People file: E0086 (Sloane Richter), status Separated. Transfer TR-00098 received 2026-02-24; approval APR-00098. Service desk ticket OFF-00098 on file. Fixed-asset extract includes FA-000098 (NBV $266.87). PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -17543,7 +17480,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>MD-00099 stays Missing at Unknown (Samsung Galaxy S24, $995). Nolan Vega has Separated status in the people extract. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. Capital trail MD-00099: PO-2022-0017 -&gt; FA-000099. Also: offboarding ticket OFF-00099 referenced. Note - last operational site on register was Denver - Closed.</t>
+          <t>No confirmed location for MD-00099 (Samsung Galaxy S24); last recorded site was Unknown. Custodian E0087 (Nolan Vega) is Separated in hr_employee_status. Transfer TR-00099 received 2026-04-02; approval APR-00099. Service desk ticket OFF-00099 on file. Ledger FA-000099 on file; NBV $548.24. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -17655,7 +17592,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00100 Missing @ Unknown. Ivy Chenoweth has Separated status in the people extract. equipment_transfer_log TR-00100, approval APR-00100; received May 05, 2026. PO-2022-0017 and FA-000100 agree on MD-00100. Also: offboarding ticket OFF-00100 referenced. Note - last operational site on register was Chicago - Closed.</t>
+          <t>MD-00100 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0088 / Ivy Chenoweth as Separated. Transfer TR-00100 received 2026-05-05; approval APR-00100. Service desk ticket OFF-00100 on file. FAR row FA-000100; net book value $927.36. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -17767,7 +17704,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 stays Retired/Pending Disposal at Seattle (MacBook Pro 14, $1985). Assignment TR-00101; receive column 2026-06-07, approval APR-00101. PO-2022-0017 / FA-000101 support the cost basis. Also: offboarding ticket RET-00101 referenced.</t>
+          <t>MD-00101 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00101 received 2026-06-07; approval APR-00101. Service desk ticket RET-00101 on file. Fixed-asset extract includes FA-000101 (NBV $0). PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -17879,7 +17816,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 stays Retired/Pending Disposal at Atlanta (Dell U2723QE, $700). TR-00102 for MD-00102 - received 01/11/2026, approval APR-00102. FAR extract includes FA-000102 for MD-00102 via PO-2022-0017. Also: offboarding ticket RET-00102 referenced.</t>
+          <t>MD-00102 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00102 received 2026-01-11; approval APR-00102. Service desk ticket RET-00102 on file. Ledger FA-000102 on file; NBV $407.54. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -17991,7 +17928,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>MD-00103 stays Retired/Pending Disposal at Chicago (Samsung Galaxy S24, $1175). Inbound stamp on TR-00103 is Feb 14, 2026, approval APR-00103. Capital trail MD-00103: PO-2023-0018 -&gt; FA-000103. Also: offboarding ticket RET-00103 referenced.</t>
+          <t>MD-00103 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00103 received 2026-02-14; approval APR-00103. Service desk ticket RET-00103 on file. FAR row FA-000103; net book value $782.53. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -18103,7 +18040,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>MD-00104 stays Retired/Pending Disposal at Dallas (Cisco C9300, $6470). Log TR-00104: received 2026-03-18, approval APR-00104. PO-2023-0018 and FA-000104 agree on MD-00104. Also: offboarding ticket RET-00104 referenced.</t>
+          <t>MD-00104 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00104 received 2026-03-18; approval APR-00104. Service desk ticket RET-00104 on file. Fixed-asset extract includes FA-000104 (NBV $1403.83). PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -18215,7 +18152,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 stays Retired/Pending Disposal at Denver (Dell Latitude 7440, $1850). TR-00105 ties to MD-00105; dock date 04/21/2026, approval APR-00105. PO-2023-0018 / FA-000105 support the cost basis. Also: offboarding ticket RET-00105 referenced.</t>
+          <t>MD-00105 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00105 received 2026-04-21; approval APR-00105. Service desk ticket RET-00105 on file. Ledger FA-000105 on file; NBV $104.26. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -18327,7 +18264,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>MD-00106 reads Retired/Pending Disposal at New York (Dell U2723QE, $565). TR-00106 ties to MD-00106; dock date May 25, 2026, approval APR-00106. Capital trail MD-00106: PO-2023-0018 -&gt; FA-000106. Also: offboarding ticket RET-00106 referenced.</t>
+          <t>MD-00106 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00106 received 2026-05-25; approval APR-00106. Service desk ticket RET-00106 on file. FAR row FA-000106; net book value $368.24. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -18439,7 +18376,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>MD-00107 reads Retired/Pending Disposal at Seattle (Samsung Galaxy S24, $1040). Transfer TR-00107 shows receipt 2026-06-27, approval APR-00107. PO-2023-0018 and FA-000107 agree on MD-00107. Also: offboarding ticket RET-00107 referenced.</t>
+          <t>MD-00107 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00107 received 2026-06-27; approval APR-00107. Service desk ticket RET-00107 on file. Fixed-asset extract includes FA-000107 (NBV $812.21). PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -18551,7 +18488,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 reads Retired/Pending Disposal at Atlanta (Cisco C9300, $6335). Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO-2023-0018 / FA-000108 support the cost basis. Also: offboarding ticket RET-00108 referenced.</t>
+          <t>MD-00108 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00108 received 2026-01-30; approval APR-00108. Service desk ticket RET-00108 on file. Ledger FA-000108 on file; NBV $545.48. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -18663,7 +18600,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 reads Retired/Pending Disposal at Chicago (Lenovo ThinkPad T14, $2030). equipment_transfer_log TR-00109, approval APR-00109; received Feb 04, 2026. Purchase order PO-2024-0019 and FAR row FA-000109 both cite MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
+          <t>MD-00109 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00109 received 2026-02-04; approval APR-00109. Service desk ticket RET-00109 on file. FAR row FA-000109; net book value $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -18775,7 +18712,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>MD-00110 stays Retired/Pending Disposal at Dallas (Dell U2723QE, $745). Inbound stamp on TR-00110 is 2026-03-08, approval APR-00110. Cost path: PO-2024-0019 into FA-000110. Also: offboarding ticket RET-00110 referenced.</t>
+          <t>MD-00110 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00110 received 2026-03-08; approval APR-00110. Service desk ticket RET-00110 on file. Fixed-asset extract includes FA-000110 (NBV $387.24). PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -18887,7 +18824,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00111 as Disposed in Disposed. Log TR-00111: received 04/13/2026, approval APR-00111. Procurement PO-2024-0019 maps to ledger FA-000111. Also: offboarding ticket RET-00111 referenced.</t>
+          <t>MD-00111 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00111 received 2026-04-13; approval APR-00111. Ledger FA-000111 on file; NBV $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -18995,7 +18932,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00112 as Disposed in Disposed. TR-00112 ties to MD-00112; dock date May 15, 2026, approval APR-00112. Ledger FA-000112 backs PO-2024-0019 for MD-00112. Also: offboarding ticket RET-00112 referenced.</t>
+          <t>MD-00112 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00112 received 2026-05-15; approval APR-00112. FAR row FA-000112; net book value $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19103,7 +19040,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00113 as Disposed in Disposed. Transfer TR-00113 shows receipt 2026-06-18, approval APR-00113. Purchase order PO-2024-0019 and FAR row FA-000113 both cite MD-00113. Also: offboarding ticket RET-00113 referenced.</t>
+          <t>MD-00113 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00113 received 2026-06-18; approval APR-00113. Fixed-asset extract includes FA-000113 (NBV $0). PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19211,7 +19148,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>MD-00114 stays Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $610). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. Capital trail MD-00114: PO-2024-0019 -&gt; FA-000114. Also: offboarding ticket RET-00114 referenced. Note - no verified disposal certificate located.</t>
+          <t>MD-00114 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00114 received 2026-01-22; approval APR-00114. Service desk ticket RET-00114 on file. Ledger FA-000114 on file; NBV $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19323,7 +19260,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00115 as Disposed in Disposed. equipment_transfer_log TR-00115, approval APR-00115; received Feb 25, 2026. PO-2025-0020 / FA-000115 support the cost basis. Also: offboarding ticket RET-00115 referenced.</t>
+          <t>MD-00115 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00115 received 2026-02-25; approval APR-00115. FAR row FA-000115; net book value $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19431,7 +19368,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00116 across CSV/XLSX inputs - Disposed, Disposed. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. Capital trail MD-00116: PO-2025-0020 -&gt; FA-000116. Also: offboarding ticket RET-00116 referenced.</t>
+          <t>MD-00116 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00116 received 2026-03-29; approval APR-00116. Fixed-asset extract includes FA-000116 (NBV $0). PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19539,7 +19476,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00117 across CSV/XLSX inputs - Disposed, Disposed. Assignment TR-00117; receive column 05/02/2026, approval APR-00117. PO-2025-0020 and FA-000117 agree on MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
+          <t>MD-00117 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00117 received 2026-05-02; approval APR-00117. Ledger FA-000117 on file; NBV $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19647,7 +19584,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 reads Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $790). TR-00118 for MD-00118 - received Jun 04, 2026, approval APR-00118. PO-2025-0020 / FA-000118 support the cost basis. Also: offboarding ticket RET-00118 referenced. Note - no verified disposal certificate located.</t>
+          <t>MD-00118 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00118 received 2026-06-04; approval APR-00118. Service desk ticket RET-00118 on file. FAR row FA-000118; net book value $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19759,7 +19696,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00119 across CSV/XLSX inputs - Disposed, Disposed. Inbound stamp on TR-00119 is 2026-07-09, approval APR-00119. FAR extract includes FA-000119 for MD-00119 via PO-2025-0020. Also: offboarding ticket RET-00119 referenced.</t>
+          <t>MD-00119 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00119 received 2026-07-09; approval APR-00119. Fixed-asset extract includes FA-000119 (NBV $0). PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -19871,7 +19808,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00120 as Disposed in Disposed. Transfer TR-00120 shows receipt 01/20/2026, approval APR-00120. Capital trail MD-00120: PO-2025-0020 -&gt; FA-000120. Also: offboarding ticket RET-00120 referenced.</t>
+          <t>MD-00120 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00120 received 2026-01-20; approval APR-00120. Ledger FA-000120 on file; NBV $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -19975,7 +19912,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>MD-00121 reads Available at Chicago (Lenovo ThinkPad T14, $1940). Movement TR-00121 posted 01/21/2026 and inbound Jan 21, 2026, approval APR-00121. PO-2022-0021 and FA-000121 agree on MD-00121.</t>
+          <t>MD-00121 (Lenovo ThinkPad T14) is Available at Chicago. Acquisition cost $1940. Transfer TR-00121 received 2026-01-21; approval APR-00121. FAR row FA-000121; net book value $0. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -20083,7 +20020,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>MD-00122 reads Available at Dallas (Dell U2723QE, $655). equipment_transfer_log TR-00122, approval APR-00122; received 2026-02-25. PO-2022-0021 / FA-000122 support the cost basis.</t>
+          <t>MD-00122 (Dell U2723QE) is Available at Dallas. Acquisition cost $655. Transfer TR-00122 received 2026-02-25; approval APR-00122. Fixed-asset extract includes FA-000122 (NBV $336.15). PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20191,7 +20128,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>MD-00123 reads Available at Denver (Samsung Galaxy S24, $1130). Assignment TR-00123; receive column 04/03/2026, approval APR-00123. FAR extract includes FA-000123 for MD-00123 via PO-2022-0021.</t>
+          <t>MD-00123 (Samsung Galaxy S24) is Available at Denver. Acquisition cost $1130. Transfer TR-00123 received 2026-04-03; approval APR-00123. Ledger FA-000123 on file; NBV $622.62. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20299,7 +20236,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>MD-00124 reads Available at New York (Cisco C9300, $6425). TR-00124 for MD-00124 - received May 01, 2026, approval APR-00124. Cost path: PO-2022-0021 into FA-000124.</t>
+          <t>MD-00124 (Cisco C9300) is Available at New York. Acquisition cost $6425. Transfer TR-00124 received 2026-05-01; approval APR-00124. FAR row FA-000124; net book value $947.26. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20407,7 +20344,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>MD-00125 reads Available at Seattle (MacBook Pro 14, $2120). Inbound stamp on TR-00125 is 2026-06-08, approval APR-00125. Procurement PO-2022-0021 maps to ledger FA-000125.</t>
+          <t>MD-00125 (MacBook Pro 14) is Available at Seattle. Acquisition cost $2120. Transfer TR-00125 received 2026-06-08; approval APR-00125. Fixed-asset extract includes FA-000125 (NBV $0). PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20515,7 +20452,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>MD-00126 stays Available at Atlanta (Dell U2723QE, $520). Inbound stamp on TR-00126 is 01/12/2026, approval APR-00126. FAR extract includes FA-000126 for MD-00126 via PO-2022-0021.</t>
+          <t>MD-00126 (Dell U2723QE) is Available at Atlanta. Acquisition cost $520. Transfer TR-00126 received 2026-01-12; approval APR-00126. Ledger FA-000126 on file; NBV $302.75. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20627,7 +20564,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00127: In Use, Denver, $995 - Samsung Galaxy S24. Checked E0061: Transferred. Log TR-00127: received Feb 17, 2026, approval field blank. Capital trail MD-00127: PO-2023-0022 -&gt; FA-000127.</t>
+          <t>Status for MD-00127: In Use. Site Denver. Model Samsung Galaxy S24; cost $995. hr_employee_status lists E0061 / Liam Keane as Transferred. Transfer TR-00127 received 2026-02-17; approval blank. FAR row FA-000127; net book value $662.65. PO PO-2023-0022.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20739,7 +20676,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00128: In Use, New York, $6290 - Cisco C9300. Checked E0062: Transferred. TR-00128 ties to MD-00128; dock date 2026-03-19, approval APR-00128. PO-2023-0022 and FA-000128 agree on MD-00128.</t>
+          <t>New York holds MD-00128 (Cisco C9300) as In Use. Acquisition $6290. People file: E0062 (Bianca Silva), status Transferred. Transfer TR-00128 received 2026-03-19; approval APR-00128. Fixed-asset extract includes FA-000128 (NBV $1364.77). PO PO-2023-0022.</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20847,7 +20784,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00129: In Use, Seattle, $1985 - Dell Latitude 7440. Checked E0063: Transferred. Transfer TR-00129 shows receipt 04/21/2026, approval APR-00129. PO-2023-0022 / FA-000129 support the cost basis.</t>
+          <t>MD-00129 (Dell Latitude 7440) is In Use at Seattle. Acquisition cost $1985. Custodian E0063 (Greg Hollis) is Transferred in hr_employee_status. Transfer TR-00129 received 2026-04-21; approval APR-00129. Ledger FA-000129 on file; NBV $111.86. PO PO-2023-0022.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -20955,7 +20892,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00130 is In Use in Atlanta site; basis $700. Naomi Berger has Transferred status in the people extract. Assignment TR-00130; receive column May 28, 2026, approval APR-00130. PO-2023-0023 covers MD-00130 as an expense-class buy; FAR silence is expected under ITAM-001 §7. Also: $700 below $2,500 - missing FA expected.</t>
+          <t>Status for MD-00130: In Use. Site Atlanta. Model Dell U2723QE; cost $700. hr_employee_status lists E0064 / Naomi Berger as Transferred. Transfer TR-00130 received 2026-05-28; approval APR-00130. PO PO-2023-0023 (capitalization_approved=No); $700 below $2,500 so FAR absence is expected under ITAM-001 section 7.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -21043,7 +20980,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00131 is In Use in Chicago site; basis $1175. Felix Moreno has Transferred status in the people extract. TR-00131 for MD-00131 - received 2026-06-28, approval APR-00131. PO-2023-0023 covers MD-00131 as an expense-class buy; FAR silence is expected under ITAM-001 §7. Also: $1175 below $2,500 - missing FA expected.</t>
+          <t>Chicago holds MD-00131 (Samsung Galaxy S24) as In Use. Acquisition $1175. People file: E0065 (Felix Moreno), status Transferred. Transfer TR-00131 received 2026-06-28; approval APR-00131. PO PO-2023-0023 (capitalization_approved=No); $1175 below $2,500 so FAR absence is expected under ITAM-001 section 7.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -21131,7 +21068,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 on MD-00132 is In Use in Dallas site; basis $6470. Sharon Quinlan has Transferred status in the people extract. Inbound stamp on TR-00132 is 01/31/2026, approval APR-00132. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00132. Purchasing PO-2023-0022 without a capital line for MD-00132 ($6,470). Also: RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
+          <t>MD-00132 (Cisco C9300) is In Use at Dallas. Acquisition cost $6470. Custodian E0066 (Sharon Quinlan) is Transferred in hr_employee_status. Transfer TR-00132 received 2026-01-31; approval APR-00132. PO PO-2023-0022; $6470 exceeds $2,500 with no FA row. RN-0132 under-threshold claim rejected.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -21308,16 +21245,15 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Ledger:FA-000017; PO:PO-2024-0003; RegisterCost:1985.0; LedgerCost:2070.0</t>
-        </is>
-      </c>
-      <c r="G5" s="7">
-        <f>IF(B5="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+          <t>Ledger:FA-000017; PO:PO-2024-0003; RegisterCost:1985.0; LedgerCost:2070.0; OverDepreciation:90.0</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>85</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Finance Controller owns cost-basis cleanup on MD-00017.</t>
+          <t>Finance Controller owns cost-basis cleanup on MD-00017; clear FA-000017 over-depreciation before relying on NBV.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -21337,7 +21273,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Pulled PO-2024-0003 and FA-000017; numbers diverge for MD-00017.</t>
+          <t>Pulled PO-2024-0003 and FA-000017; numbers diverge for MD-00017. FA-000017 accumulated depreciation $2160 exceeds acquisition cost $2070 by $90.</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -21377,9 +21313,8 @@
           <t>Duplicate serial MD-LA-050021 across MD-00021 and MD-00025; Serial:MD-LA-050021; AlsoTagged:MD-00021,MD-00025</t>
         </is>
       </c>
-      <c r="G6" s="7">
-        <f>IF(B6="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G6" s="7" t="n">
+        <v>124.52</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -21443,9 +21378,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00025; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G7" s="7">
-        <f>IF(B7="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -21509,9 +21443,8 @@
           <t>Duplicate serial MD-LA-050021 across MD-00021 and MD-00025; Serial:MD-LA-050021; AlsoTagged:MD-00021,MD-00025</t>
         </is>
       </c>
-      <c r="G8" s="7">
-        <f>IF(B8="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -21575,9 +21508,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00026; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G9" s="7">
-        <f>IF(B9="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G9" s="7" t="n">
+        <v>382.34</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -21641,9 +21573,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00027; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G10" s="7">
-        <f>IF(B10="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G10" s="7" t="n">
+        <v>672.21</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -21707,9 +21638,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00028; HRLocation:New York</t>
         </is>
       </c>
-      <c r="G11" s="7">
-        <f>IF(B11="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G11" s="7" t="n">
+        <v>914.09</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -21773,9 +21703,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00029; HRLocation:Seattle</t>
         </is>
       </c>
-      <c r="G12" s="7">
-        <f>IF(B12="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -21839,9 +21768,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00030; HRLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G13" s="7">
-        <f>IF(B13="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G13" s="7" t="n">
+        <v>355.14</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -21905,9 +21833,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00031; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G14" s="7">
-        <f>IF(B14="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G14" s="7" t="n">
+        <v>722.59</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -21971,9 +21898,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00032; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G15" s="7">
-        <f>IF(B15="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G15" s="7" t="n">
+        <v>1384.3</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -22037,9 +21963,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00033; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G16" s="7">
-        <f>IF(B16="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G16" s="7" t="n">
+        <v>116.93</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -22103,9 +22028,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00034; HRLocation:New York</t>
         </is>
       </c>
-      <c r="G17" s="7">
-        <f>IF(B17="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G17" s="7" t="n">
+        <v>514.88</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -22169,9 +22093,8 @@
           <t>Ledger:FA-000034; PO:PO-2023-0006; RegisterCost:790.0; LedgerCost:930.0</t>
         </is>
       </c>
-      <c r="G18" s="7">
-        <f>IF(B18="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G18" s="7" t="n">
+        <v>140</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -22235,9 +22158,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00035; HRLocation:Seattle</t>
         </is>
       </c>
-      <c r="G19" s="7">
-        <f>IF(B19="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G19" s="7" t="n">
+        <v>741.92</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -22301,9 +22223,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00036; HRLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G20" s="7">
-        <f>IF(B20="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G20" s="7" t="n">
+        <v>537.73</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -22367,9 +22288,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00037; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G21" s="7">
-        <f>IF(B21="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -22433,9 +22353,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00038; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G22" s="7">
-        <f>IF(B22="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G22" s="7" t="n">
+        <v>340.46</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -22499,9 +22418,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00039; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G23" s="7">
-        <f>IF(B23="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G23" s="7" t="n">
+        <v>635</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -22565,9 +22483,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00040; HRLocation:New York</t>
         </is>
       </c>
-      <c r="G24" s="7">
-        <f>IF(B24="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G24" s="7" t="n">
+        <v>989.48</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -22631,9 +22548,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00041; HRLocation:Seattle</t>
         </is>
       </c>
-      <c r="G25" s="7">
-        <f>IF(B25="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -22697,9 +22613,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00042; HRLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G26" s="7">
-        <f>IF(B26="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G26" s="7" t="n">
+        <v>306.16</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -22763,9 +22678,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00043; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G27" s="7">
-        <f>IF(B27="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G27" s="7" t="n">
+        <v>673.55</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -22829,9 +22743,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00044; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G28" s="7">
-        <f>IF(B28="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G28" s="7" t="n">
+        <v>1406.1</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -22895,9 +22808,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00045; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G29" s="7">
-        <f>IF(B29="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G29" s="7" t="n">
+        <v>133.6</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -22961,9 +22873,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00046; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G30" s="7">
-        <f>IF(B30="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G30" s="7" t="n">
+        <v>460.82</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -23027,9 +22938,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00047; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G31" s="7">
-        <f>IF(B31="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G31" s="7" t="n">
+        <v>930.51</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -23093,9 +23003,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00048; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G32" s="7">
-        <f>IF(B32="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G32" s="7" t="n">
+        <v>514.59</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -23159,9 +23068,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00049; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G33" s="7">
-        <f>IF(B33="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G33" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -23225,9 +23133,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00050; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G34" s="7">
-        <f>IF(B34="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G34" s="7" t="n">
+        <v>289.96</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -23291,9 +23198,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00051; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G35" s="7">
-        <f>IF(B35="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G35" s="7" t="n">
+        <v>573.03</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -23357,9 +23263,8 @@
           <t>Ledger:FA-000051; PO:PO-2022-0009; RegisterCost:1040.0; LedgerCost:1250.0</t>
         </is>
       </c>
-      <c r="G36" s="7">
-        <f>IF(B36="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G36" s="7" t="n">
+        <v>210</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -23423,9 +23328,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00052; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G37" s="7">
-        <f>IF(B37="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G37" s="7" t="n">
+        <v>933.99</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -23489,9 +23393,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00053; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G38" s="7">
-        <f>IF(B38="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -23555,9 +23458,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00054; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G39" s="7">
-        <f>IF(B39="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G39" s="7" t="n">
+        <v>433.74</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -23621,9 +23523,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00055; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G40" s="7">
-        <f>IF(B40="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G40" s="7" t="n">
+        <v>812.5</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -23687,9 +23588,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00056; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G41" s="7">
-        <f>IF(B41="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G41" s="7" t="n">
+        <v>1345.24</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -23753,9 +23653,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00057; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G42" s="7">
-        <f>IF(B42="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G42" s="7" t="n">
+        <v>106.79</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -23819,9 +23718,8 @@
           <t>Employee:E0071; Ticket:OFF-00058; Transfer:TR-00058</t>
         </is>
       </c>
-      <c r="G43" s="7">
-        <f>IF(B43="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G43" s="7" t="n">
+        <v>397.56</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -23885,9 +23783,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00058; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G44" s="7">
-        <f>IF(B44="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G44" s="7" t="n">
+        <v>397.56</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -23951,9 +23848,8 @@
           <t>Transfer:TR-00058; Approval:missing</t>
         </is>
       </c>
-      <c r="G45" s="7">
-        <f>IF(B45="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G45" s="7" t="n">
+        <v>397.56</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -24017,9 +23913,8 @@
           <t>Employee:E0072; Ticket:OFF-00059; Transfer:TR-00059</t>
         </is>
       </c>
-      <c r="G46" s="7">
-        <f>IF(B46="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G46" s="7" t="n">
+        <v>847.35</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -24083,9 +23978,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00059; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G47" s="7">
-        <f>IF(B47="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G47" s="7" t="n">
+        <v>847.35</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -24149,9 +24043,8 @@
           <t>Transfer:TR-00059; Approval:missing</t>
         </is>
       </c>
-      <c r="G48" s="7">
-        <f>IF(B48="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G48" s="7" t="n">
+        <v>847.35</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -24215,9 +24108,8 @@
           <t>Employee:E0073; Ticket:OFF-00060; Transfer:TR-00060</t>
         </is>
       </c>
-      <c r="G49" s="7">
-        <f>IF(B49="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G49" s="7" t="n">
+        <v>549.35</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -24281,9 +24173,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00060; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G50" s="7">
-        <f>IF(B50="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G50" s="7" t="n">
+        <v>549.35</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -24347,9 +24238,8 @@
           <t>Employee:E0074; Ticket:OFF-00061; Transfer:TR-00061</t>
         </is>
       </c>
-      <c r="G51" s="7">
-        <f>IF(B51="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G51" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -24413,9 +24303,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00061; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G52" s="7">
-        <f>IF(B52="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G52" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -24479,9 +24368,8 @@
           <t>Employee:E0075; Ticket:OFF-00062; Transfer:TR-00062</t>
         </is>
       </c>
-      <c r="G53" s="7">
-        <f>IF(B53="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G53" s="7" t="n">
+        <v>410.63</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -24545,9 +24433,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00062; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G54" s="7">
-        <f>IF(B54="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G54" s="7" t="n">
+        <v>410.63</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
@@ -24611,9 +24498,8 @@
           <t>Employee:E0076; Ticket:OFF-00063; Transfer:TR-00063</t>
         </is>
       </c>
-      <c r="G55" s="7">
-        <f>IF(B55="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G55" s="7" t="n">
+        <v>533.85</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -24677,9 +24563,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00063; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G56" s="7">
-        <f>IF(B56="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G56" s="7" t="n">
+        <v>533.85</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -24743,9 +24628,8 @@
           <t>Employee:E0077; Ticket:OFF-00064; Transfer:TR-00064</t>
         </is>
       </c>
-      <c r="G57" s="7">
-        <f>IF(B57="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G57" s="7" t="n">
+        <v>961.76</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
@@ -24809,9 +24693,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00064; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G58" s="7">
-        <f>IF(B58="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G58" s="7" t="n">
+        <v>961.76</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -24875,9 +24758,8 @@
           <t>Transfer:TR-00064; Approval:missing</t>
         </is>
       </c>
-      <c r="G59" s="7">
-        <f>IF(B59="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G59" s="7" t="n">
+        <v>961.76</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -24941,9 +24823,8 @@
           <t>Employee:E0078; Ticket:OFF-00065; Transfer:TR-00065</t>
         </is>
       </c>
-      <c r="G60" s="7">
-        <f>IF(B60="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G60" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -25007,9 +24888,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00065; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G61" s="7">
-        <f>IF(B61="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G61" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -25073,9 +24953,8 @@
           <t>Transfer:TR-00065; Approval:missing</t>
         </is>
       </c>
-      <c r="G62" s="7">
-        <f>IF(B62="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G62" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -25139,9 +25018,8 @@
           <t>Employee:E0079; Ticket:OFF-00066; Transfer:TR-00066</t>
         </is>
       </c>
-      <c r="G63" s="7">
-        <f>IF(B63="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G63" s="7" t="n">
+        <v>385.65</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -25205,9 +25083,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00066; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G64" s="7">
-        <f>IF(B64="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G64" s="7" t="n">
+        <v>385.65</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -25271,9 +25148,8 @@
           <t>Employee:E0080; Ticket:OFF-00067; Transfer:TR-00067</t>
         </is>
       </c>
-      <c r="G65" s="7">
-        <f>IF(B65="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G65" s="7" t="n">
+        <v>764.9299999999999</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
@@ -25337,9 +25213,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00067; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G66" s="7">
-        <f>IF(B66="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G66" s="7" t="n">
+        <v>764.9299999999999</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -25403,9 +25278,8 @@
           <t>Ticket:OFF-00068; Tracking:1ZMD00000068; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G67" s="7">
-        <f>IF(B67="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G67" s="7" t="n">
+        <v>1436.28</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -25469,9 +25343,8 @@
           <t>Employee:E0081; Ticket:OFF-00068</t>
         </is>
       </c>
-      <c r="G68" s="7">
-        <f>IF(B68="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G68" s="7" t="n">
+        <v>1436.28</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -25535,9 +25408,8 @@
           <t>Ledger:FA-000068; PO:PO-2025-0012; RegisterCost:6425.0; LedgerCost:6480.0</t>
         </is>
       </c>
-      <c r="G69" s="7">
-        <f>IF(B69="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G69" s="7" t="n">
+        <v>55</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
@@ -25601,9 +25473,8 @@
           <t>Ticket:OFF-00069; Tracking:1ZMD00000069; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G70" s="7">
-        <f>IF(B70="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G70" s="7" t="n">
+        <v>142.69</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
@@ -25667,9 +25538,8 @@
           <t>Employee:E0082; Ticket:OFF-00069</t>
         </is>
       </c>
-      <c r="G71" s="7">
-        <f>IF(B71="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G71" s="7" t="n">
+        <v>142.69</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
@@ -25733,9 +25603,8 @@
           <t>Ticket:OFF-00070; Tracking:1ZMD00000070; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G72" s="7">
-        <f>IF(B72="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G72" s="7" t="n">
+        <v>342.32</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -25799,9 +25668,8 @@
           <t>Employee:E0083; Ticket:OFF-00070</t>
         </is>
       </c>
-      <c r="G73" s="7">
-        <f>IF(B73="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G73" s="7" t="n">
+        <v>342.32</v>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
@@ -25865,9 +25733,8 @@
           <t>Ticket:OFF-00071; Tracking:1ZMD00000071; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G74" s="7">
-        <f>IF(B74="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G74" s="7" t="n">
+        <v>787.96</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -25931,9 +25798,8 @@
           <t>Employee:E0084; Ticket:OFF-00071</t>
         </is>
       </c>
-      <c r="G75" s="7">
-        <f>IF(B75="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G75" s="7" t="n">
+        <v>787.96</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -25997,9 +25863,8 @@
           <t>Ticket:OFF-00072; Tracking:1ZMD00000072; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G76" s="7">
-        <f>IF(B76="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G76" s="7" t="n">
+        <v>500.27</v>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
@@ -26063,9 +25928,8 @@
           <t>Employee:E0085; Ticket:OFF-00072</t>
         </is>
       </c>
-      <c r="G77" s="7">
-        <f>IF(B77="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G77" s="7" t="n">
+        <v>500.27</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -26129,9 +25993,8 @@
           <t>Ticket:OFF-00073; Tracking:1ZMD00000073; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G78" s="7">
-        <f>IF(B78="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G78" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
@@ -26195,9 +26058,8 @@
           <t>Employee:E0086; Ticket:OFF-00073</t>
         </is>
       </c>
-      <c r="G79" s="7">
-        <f>IF(B79="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G79" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -26261,9 +26123,8 @@
           <t>Ticket:OFF-00074; Tracking:1ZMD00000074; ShipmentSerial:MISMATCH-0074</t>
         </is>
       </c>
-      <c r="G80" s="7">
-        <f>IF(B80="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G80" s="7" t="n">
+        <v>359.25</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -26327,9 +26188,8 @@
           <t>Employee:E0087; Ticket:OFF-00074</t>
         </is>
       </c>
-      <c r="G81" s="7">
-        <f>IF(B81="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G81" s="7" t="n">
+        <v>359.25</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -26393,9 +26253,8 @@
           <t>Ticket:OFF-00074; Tracking:1ZMD00000074; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G82" s="7">
-        <f>IF(B82="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G82" s="7" t="n">
+        <v>359.25</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -26459,9 +26318,8 @@
           <t>Ticket:OFF-00075; Tracking:1ZMD00000075; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G83" s="7">
-        <f>IF(B83="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G83" s="7" t="n">
+        <v>647.42</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -26525,9 +26383,8 @@
           <t>Employee:E0088; Ticket:OFF-00075</t>
         </is>
       </c>
-      <c r="G84" s="7">
-        <f>IF(B84="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G84" s="7" t="n">
+        <v>647.42</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -26591,9 +26448,8 @@
           <t>Ticket:OFF-00076; Tracking:1ZMD00000076; ShipmentSerial:MISMATCH-0076</t>
         </is>
       </c>
-      <c r="G85" s="7">
-        <f>IF(B85="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G85" s="7" t="n">
+        <v>953.89</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -26657,9 +26513,8 @@
           <t>Employee:E0089; Ticket:OFF-00076</t>
         </is>
       </c>
-      <c r="G86" s="7">
-        <f>IF(B86="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G86" s="7" t="n">
+        <v>953.89</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -26723,9 +26578,8 @@
           <t>Ticket:OFF-00076; Tracking:1ZMD00000076; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G87" s="7">
-        <f>IF(B87="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G87" s="7" t="n">
+        <v>953.89</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -26789,9 +26643,8 @@
           <t>Ticket:OFF-00077; Tracking:1ZMD00000077; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G88" s="7">
-        <f>IF(B88="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G88" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
@@ -26855,9 +26708,8 @@
           <t>Employee:E0090; Ticket:OFF-00077</t>
         </is>
       </c>
-      <c r="G89" s="7">
-        <f>IF(B89="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G89" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -26921,9 +26773,8 @@
           <t>Ticket:OFF-00078; Tracking:1ZMD00000078; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G90" s="7">
-        <f>IF(B90="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G90" s="7" t="n">
+        <v>328.95</v>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
@@ -26987,9 +26838,8 @@
           <t>Employee:E0091; Ticket:OFF-00078</t>
         </is>
       </c>
-      <c r="G91" s="7">
-        <f>IF(B91="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G91" s="7" t="n">
+        <v>328.95</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
@@ -27053,9 +26903,8 @@
           <t>Ticket:OFF-00079; Tracking:1ZMD00000079; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G92" s="7">
-        <f>IF(B92="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G92" s="7" t="n">
+        <v>692.62</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -27119,9 +26968,8 @@
           <t>Employee:E0092; Ticket:OFF-00079</t>
         </is>
       </c>
-      <c r="G93" s="7">
-        <f>IF(B93="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G93" s="7" t="n">
+        <v>692.62</v>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
@@ -27185,9 +27033,8 @@
           <t>Employee:E0093; Ticket:OFF-00080; Tracking:1ZMD00000080</t>
         </is>
       </c>
-      <c r="G94" s="7">
-        <f>IF(B94="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G94" s="7" t="n">
+        <v>1374.53</v>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
@@ -27251,9 +27098,8 @@
           <t>Employee:E0094; Ticket:OFF-00081; Tracking:1ZMD00000081</t>
         </is>
       </c>
-      <c r="G95" s="7">
-        <f>IF(B95="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G95" s="7" t="n">
+        <v>114.4</v>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
@@ -27317,9 +27163,8 @@
           <t>Ticket:OFF-00082; Tracking:1ZMD00000082; ShipmentSerial:MISMATCH-0082; Image:receiving_exception_scan_1ZMD00000082.png</t>
         </is>
       </c>
-      <c r="G96" s="7">
-        <f>IF(B96="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G96" s="7" t="n">
+        <v>485.55</v>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
@@ -27383,9 +27228,8 @@
           <t>Employee:E0095; Ticket:OFF-00082</t>
         </is>
       </c>
-      <c r="G97" s="7">
-        <f>IF(B97="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G97" s="7" t="n">
+        <v>485.55</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -27449,9 +27293,8 @@
           <t>Employee:E0071; Ticket:OFF-00083; Tracking:1ZMD00000083</t>
         </is>
       </c>
-      <c r="G98" s="7">
-        <f>IF(B98="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G98" s="7" t="n">
+        <v>952.79</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -27515,9 +27358,8 @@
           <t>Ticket:OFF-00084; Tracking:1ZMD00000084; ShipmentSerial:MISMATCH-0084</t>
         </is>
       </c>
-      <c r="G99" s="7">
-        <f>IF(B99="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G99" s="7" t="n">
+        <v>533.85</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -27581,9 +27423,8 @@
           <t>Employee:E0072; Ticket:OFF-00084</t>
         </is>
       </c>
-      <c r="G100" s="7">
-        <f>IF(B100="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G100" s="7" t="n">
+        <v>533.85</v>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
@@ -27647,9 +27488,8 @@
           <t>Employee:E0073; Ticket:OFF-00085; Tracking:1ZMD00000085</t>
         </is>
       </c>
-      <c r="G101" s="7">
-        <f>IF(B101="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G101" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
@@ -27713,9 +27553,8 @@
           <t>Ledger:FA-000085; PO:PO-2024-0015; RegisterCost:1895.0; LedgerCost:2090.0</t>
         </is>
       </c>
-      <c r="G102" s="7">
-        <f>IF(B102="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G102" s="7" t="n">
+        <v>195</v>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
@@ -27779,9 +27618,8 @@
           <t>Employee:E0074; Ticket:OFF-00086; Tracking:1ZMD00000086</t>
         </is>
       </c>
-      <c r="G103" s="7">
-        <f>IF(B103="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G103" s="7" t="n">
+        <v>317.07</v>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
@@ -27845,9 +27683,8 @@
           <t>Employee:E0075; Ticket:OFF-00087; Tracking:1ZMD00000087</t>
         </is>
       </c>
-      <c r="G104" s="7">
-        <f>IF(B104="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G104" s="7" t="n">
+        <v>609.71</v>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
@@ -27911,9 +27748,8 @@
           <t>Employee:E0076; Ticket:OFF-00088; Tracking:1ZMD00000088</t>
         </is>
       </c>
-      <c r="G105" s="7">
-        <f>IF(B105="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G105" s="7" t="n">
+        <v>982.55</v>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
@@ -27977,9 +27813,8 @@
           <t>Duplicate serial MD-NE-050088 across MD-00088 and MD-00092; Serial:MD-NE-050088; AlsoTagged:MD-00088,MD-00092</t>
         </is>
       </c>
-      <c r="G106" s="7">
-        <f>IF(B106="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G106" s="7" t="n">
+        <v>982.55</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
@@ -28043,9 +27878,8 @@
           <t>Ticket:OFF-00089; Transfer:TR-00089; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G107" s="7">
-        <f>IF(B107="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G107" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -28109,9 +27943,8 @@
           <t>Employee:E0077; Ticket:OFF-00089</t>
         </is>
       </c>
-      <c r="G108" s="7">
-        <f>IF(B108="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G108" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -28175,9 +28008,8 @@
           <t>Ticket:OFF-00090; Transfer:TR-00090; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G109" s="7">
-        <f>IF(B109="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G109" s="7" t="n">
+        <v>465.13</v>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
@@ -28241,9 +28073,8 @@
           <t>Employee:E0078; Ticket:OFF-00090</t>
         </is>
       </c>
-      <c r="G110" s="7">
-        <f>IF(B110="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G110" s="7" t="n">
+        <v>465.13</v>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
@@ -28307,9 +28138,8 @@
           <t>Ticket:OFF-00091; Transfer:TR-00091; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G111" s="7">
-        <f>IF(B111="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G111" s="7" t="n">
+        <v>643.09</v>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
@@ -28373,9 +28203,8 @@
           <t>Employee:E0079; Ticket:OFF-00091</t>
         </is>
       </c>
-      <c r="G112" s="7">
-        <f>IF(B112="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G112" s="7" t="n">
+        <v>643.09</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
@@ -28439,9 +28268,8 @@
           <t>Ticket:OFF-00092; Transfer:TR-00092; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G113" s="7">
-        <f>IF(B113="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G113" s="7" t="n">
+        <v>1396.04</v>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
@@ -28505,9 +28333,8 @@
           <t>Employee:E0080; Ticket:OFF-00092</t>
         </is>
       </c>
-      <c r="G114" s="7">
-        <f>IF(B114="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G114" s="7" t="n">
+        <v>1396.04</v>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
@@ -28571,9 +28398,8 @@
           <t>Duplicate serial MD-NE-050088 across MD-00088 and MD-00092; Serial:MD-NE-050088; AlsoTagged:MD-00088,MD-00092</t>
         </is>
       </c>
-      <c r="G115" s="7">
-        <f>IF(B115="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G115" s="7" t="n">
+        <v>1396.04</v>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
@@ -28637,9 +28463,8 @@
           <t>Ticket:OFF-00093; Transfer:TR-00093; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G116" s="7">
-        <f>IF(B116="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G116" s="7" t="n">
+        <v>130.57</v>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
@@ -28703,9 +28528,8 @@
           <t>Employee:E0081; Ticket:OFF-00093</t>
         </is>
       </c>
-      <c r="G117" s="7">
-        <f>IF(B117="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G117" s="7" t="n">
+        <v>130.57</v>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
@@ -28769,9 +28593,8 @@
           <t>Ticket:OFF-00094; Transfer:TR-00094; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G118" s="7">
-        <f>IF(B118="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G118" s="7" t="n">
+        <v>431.2</v>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
@@ -28835,9 +28658,8 @@
           <t>Employee:E0082; Ticket:OFF-00094</t>
         </is>
       </c>
-      <c r="G119" s="7">
-        <f>IF(B119="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G119" s="7" t="n">
+        <v>431.2</v>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
@@ -28901,9 +28723,8 @@
           <t>Ticket:OFF-00095; Transfer:TR-00095; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G120" s="7">
-        <f>IF(B120="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G120" s="7" t="n">
+        <v>894.87</v>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
@@ -28967,9 +28788,8 @@
           <t>Employee:E0083; Ticket:OFF-00095</t>
         </is>
       </c>
-      <c r="G121" s="7">
-        <f>IF(B121="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G121" s="7" t="n">
+        <v>894.87</v>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
@@ -29033,9 +28853,8 @@
           <t>Ticket:OFF-00096; Transfer:TR-00096; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G122" s="7">
-        <f>IF(B122="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G122" s="7" t="n">
+        <v>511.01</v>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
@@ -29099,9 +28918,8 @@
           <t>Employee:E0084; Ticket:OFF-00096</t>
         </is>
       </c>
-      <c r="G123" s="7">
-        <f>IF(B123="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G123" s="7" t="n">
+        <v>511.01</v>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
@@ -29165,9 +28983,8 @@
           <t>Ticket:OFF-00097; Transfer:TR-00097; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G124" s="7">
-        <f>IF(B124="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G124" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
@@ -29231,9 +29048,8 @@
           <t>Employee:E0085; Ticket:OFF-00097</t>
         </is>
       </c>
-      <c r="G125" s="7">
-        <f>IF(B125="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G125" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
@@ -29297,9 +29113,8 @@
           <t>Ticket:OFF-00098; Transfer:TR-00098; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G126" s="7">
-        <f>IF(B126="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G126" s="7" t="n">
+        <v>266.87</v>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
@@ -29363,9 +29178,8 @@
           <t>Employee:E0086; Ticket:OFF-00098</t>
         </is>
       </c>
-      <c r="G127" s="7">
-        <f>IF(B127="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G127" s="7" t="n">
+        <v>266.87</v>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
@@ -29429,9 +29243,8 @@
           <t>Ticket:OFF-00099; Transfer:TR-00099; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G128" s="7">
-        <f>IF(B128="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G128" s="7" t="n">
+        <v>548.24</v>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
@@ -29495,9 +29308,8 @@
           <t>Employee:E0087; Ticket:OFF-00099</t>
         </is>
       </c>
-      <c r="G129" s="7">
-        <f>IF(B129="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G129" s="7" t="n">
+        <v>548.24</v>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
@@ -29561,9 +29373,8 @@
           <t>Ticket:OFF-00100; Transfer:TR-00100; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G130" s="7">
-        <f>IF(B130="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G130" s="7" t="n">
+        <v>927.36</v>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
@@ -29627,9 +29438,8 @@
           <t>Employee:E0088; Ticket:OFF-00100</t>
         </is>
       </c>
-      <c r="G131" s="7">
-        <f>IF(B131="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G131" s="7" t="n">
+        <v>927.36</v>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
@@ -29693,9 +29503,8 @@
           <t>Ticket:RET-00101; Transfer:TR-00101; Certificate:missing</t>
         </is>
       </c>
-      <c r="G132" s="7">
-        <f>IF(B132="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G132" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -29759,9 +29568,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00101</t>
         </is>
       </c>
-      <c r="G133" s="7">
-        <f>IF(B133="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G133" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
@@ -29825,9 +29633,8 @@
           <t>Ticket:RET-00102; Transfer:TR-00102; Certificate:missing</t>
         </is>
       </c>
-      <c r="G134" s="7">
-        <f>IF(B134="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G134" s="7" t="n">
+        <v>407.54</v>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
@@ -29891,9 +29698,8 @@
           <t>Ledger:FA-000102; PO:PO-2022-0017; RegisterCost:700.0; LedgerCost:820.0</t>
         </is>
       </c>
-      <c r="G135" s="7">
-        <f>IF(B135="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G135" s="7" t="n">
+        <v>120</v>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
@@ -29957,9 +29763,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00102</t>
         </is>
       </c>
-      <c r="G136" s="7">
-        <f>IF(B136="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G136" s="7" t="n">
+        <v>407.54</v>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
@@ -30023,9 +29828,8 @@
           <t>Ticket:RET-00103; Transfer:TR-00103; Certificate:missing</t>
         </is>
       </c>
-      <c r="G137" s="7">
-        <f>IF(B137="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D137,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D137,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G137" s="7" t="n">
+        <v>782.53</v>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
@@ -30089,9 +29893,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00103</t>
         </is>
       </c>
-      <c r="G138" s="7">
-        <f>IF(B138="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D138,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D138,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G138" s="7" t="n">
+        <v>782.53</v>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
@@ -30155,9 +29958,8 @@
           <t>Ticket:RET-00104; Transfer:TR-00104; Certificate:missing</t>
         </is>
       </c>
-      <c r="G139" s="7">
-        <f>IF(B139="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D139,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D139,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G139" s="7" t="n">
+        <v>1403.83</v>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
@@ -30221,9 +30023,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00104</t>
         </is>
       </c>
-      <c r="G140" s="7">
-        <f>IF(B140="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D140,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D140,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G140" s="7" t="n">
+        <v>1403.83</v>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
@@ -30287,9 +30088,8 @@
           <t>Ticket:RET-00105; Transfer:TR-00105; Certificate:missing</t>
         </is>
       </c>
-      <c r="G141" s="7">
-        <f>IF(B141="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D141,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D141,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G141" s="7" t="n">
+        <v>104.26</v>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
@@ -30353,9 +30153,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00105</t>
         </is>
       </c>
-      <c r="G142" s="7">
-        <f>IF(B142="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D142,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D142,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G142" s="7" t="n">
+        <v>104.26</v>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
@@ -30419,9 +30218,8 @@
           <t>Ticket:RET-00106; Transfer:TR-00106; Certificate:missing</t>
         </is>
       </c>
-      <c r="G143" s="7">
-        <f>IF(B143="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D143,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D143,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G143" s="7" t="n">
+        <v>368.24</v>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
@@ -30485,9 +30283,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00106</t>
         </is>
       </c>
-      <c r="G144" s="7">
-        <f>IF(B144="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D144,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D144,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G144" s="7" t="n">
+        <v>368.24</v>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
@@ -30551,9 +30348,8 @@
           <t>Ticket:RET-00107; Transfer:TR-00107; Certificate:missing</t>
         </is>
       </c>
-      <c r="G145" s="7">
-        <f>IF(B145="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D145,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D145,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G145" s="7" t="n">
+        <v>812.21</v>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
@@ -30617,9 +30413,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00107</t>
         </is>
       </c>
-      <c r="G146" s="7">
-        <f>IF(B146="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D146,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D146,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G146" s="7" t="n">
+        <v>812.21</v>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
@@ -30683,9 +30478,8 @@
           <t>Ticket:RET-00108; Transfer:TR-00108; Certificate:missing</t>
         </is>
       </c>
-      <c r="G147" s="7">
-        <f>IF(B147="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D147,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D147,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G147" s="7" t="n">
+        <v>545.48</v>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
@@ -30749,9 +30543,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00108</t>
         </is>
       </c>
-      <c r="G148" s="7">
-        <f>IF(B148="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D148,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D148,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G148" s="7" t="n">
+        <v>545.48</v>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
@@ -30815,9 +30608,8 @@
           <t>Ticket:RET-00109; Transfer:TR-00109; Certificate:missing</t>
         </is>
       </c>
-      <c r="G149" s="7">
-        <f>IF(B149="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D149,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D149,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G149" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
@@ -30881,9 +30673,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00109</t>
         </is>
       </c>
-      <c r="G150" s="7">
-        <f>IF(B150="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D150,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D150,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G150" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
@@ -30947,9 +30738,8 @@
           <t>Ticket:RET-00110; Transfer:TR-00110; Certificate:missing</t>
         </is>
       </c>
-      <c r="G151" s="7">
-        <f>IF(B151="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D151,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D151,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G151" s="7" t="n">
+        <v>387.24</v>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
@@ -31013,9 +30803,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00110</t>
         </is>
       </c>
-      <c r="G152" s="7">
-        <f>IF(B152="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D152,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D152,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G152" s="7" t="n">
+        <v>387.24</v>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
@@ -31079,9 +30868,8 @@
           <t>Ticket:RET-00114; Transfer:TR-00114; Certificate:missing</t>
         </is>
       </c>
-      <c r="G153" s="7">
-        <f>IF(B153="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D153,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D153,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G153" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
@@ -31145,9 +30933,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00114</t>
         </is>
       </c>
-      <c r="G154" s="7">
-        <f>IF(B154="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D154,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D154,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G154" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
@@ -31211,9 +30998,8 @@
           <t>Ticket:RET-00118; Transfer:TR-00118; Certificate:missing</t>
         </is>
       </c>
-      <c r="G155" s="7">
-        <f>IF(B155="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D155,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D155,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G155" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
@@ -31277,9 +31063,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00118</t>
         </is>
       </c>
-      <c r="G156" s="7">
-        <f>IF(B156="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D156,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D156,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G156" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
@@ -31343,9 +31128,8 @@
           <t>Ledger:FA-000119; PO:PO-2025-0020; RegisterCost:950.0; LedgerCost:1115.0</t>
         </is>
       </c>
-      <c r="G157" s="7">
-        <f>IF(B157="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D157,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D157,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G157" s="7" t="n">
+        <v>165</v>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
@@ -31409,9 +31193,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00121; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G158" s="7">
-        <f>IF(B158="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D158,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D158,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G158" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
@@ -31475,9 +31258,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00122; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G159" s="7">
-        <f>IF(B159="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D159,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D159,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G159" s="7" t="n">
+        <v>336.15</v>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
@@ -31541,9 +31323,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00123; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G160" s="7">
-        <f>IF(B160="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D160,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D160,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G160" s="7" t="n">
+        <v>622.62</v>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
@@ -31607,9 +31388,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00124; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G161" s="7">
-        <f>IF(B161="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D161,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D161,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G161" s="7" t="n">
+        <v>947.26</v>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
@@ -31673,9 +31453,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00125; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G162" s="7">
-        <f>IF(B162="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D162,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D162,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G162" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
@@ -31739,9 +31518,8 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00126; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G163" s="7">
-        <f>IF(B163="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D163,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D163,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G163" s="7" t="n">
+        <v>302.75</v>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
@@ -31805,9 +31583,8 @@
           <t>Transfer:TR-00127; Approval:missing</t>
         </is>
       </c>
-      <c r="G164" s="7">
-        <f>IF(B164="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D164,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D164,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G164" s="7" t="n">
+        <v>662.65</v>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
@@ -31868,12 +31645,11 @@
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>PO:PO-2023-0022; RegisterCost:700; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
-        </is>
-      </c>
-      <c r="G165" s="7">
-        <f>IF(B165="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D165,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D165,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+          <t>PO:PO-2023-0023; RegisterCost:700; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n">
+        <v>700</v>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
@@ -31934,12 +31710,11 @@
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>PO:PO-2023-0022; RegisterCost:1175; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
-        </is>
-      </c>
-      <c r="G166" s="7">
-        <f>IF(B166="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D166,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D166,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+          <t>PO:PO-2023-0023; RegisterCost:1175; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="n">
+        <v>1175</v>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
@@ -32003,9 +31778,8 @@
           <t>PO:PO-2023-0022; RegisterCost:6470.0; Policy:ITAM-001 §7 threshold $2500; capitalization_approved on PO does not excuse missing FA row for qualifying asset; regional note RN-0132 is non-authoritative</t>
         </is>
       </c>
-      <c r="G167" s="7">
-        <f>IF(B167="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D167,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D167,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v/>
+      <c r="G167" s="7" t="n">
+        <v>6470</v>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
@@ -53997,14 +53771,14 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>1) Three assets (MD-00130, MD-00131, MD-00132) appear on the operational register and purchase orders but have no fixed-asset ledger row. Combined register acquisition cost = $8,345. MD-00130 ($700) and MD-00131 ($1,175) are under the $2,500 capitalization gate (expected FA absence). MD-00132 ($6,470) is capital-qualifying and is a Critical gap.</t>
+          <t>1) Three assets (MD-00130, MD-00131, MD-00132) appear on the operational register and purchase orders but have no fixed-asset ledger row. Combined register acquisition cost = $8,345. MD-00130 ($700) and MD-00131 ($1,175) sit on PO-2023-0023 (capitalization_approved=No) under the $2,500 gate - expected FA absence. MD-00132 ($6,470) is on PO-2023-0022 and is capital-qualifying - Critical gap.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2) Seven assets have ledger-over-register acquisition cost variances (MD-00017 $85, MD-00034 $140, MD-00051 $210, MD-00068 $55, MD-00085 $195, MD-00102 $120, MD-00119 $165). Combined ledger cost excess = $970. PO approved amounts tie to the inventory lines; Finance should align the FAR. Per §9 these are High remediation items, not sole Critical blockers.</t>
+          <t>2) Seven assets have ledger-over-register acquisition cost variances (MD-00017 $85, MD-00034 $140, MD-00051 $210, MD-00068 $55, MD-00085 $195, MD-00102 $120, MD-00119 $165). Combined ledger cost excess = $970. PO approved amounts tie to the inventory lines; Finance should align the FAR. Per section 9 these are High remediation items, not sole Critical blockers. Separately, FA-000017 shows accumulated depreciation $2,160 against acquisition cost $2,070 (over-depreciation $90) with NBV reported as $0.</t>
         </is>
       </c>
     </row>
@@ -54078,29 +53852,24 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="7">
-        <f>IF(OR(C24="",D24=""),"",D24-C24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C24" s="7" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>2070</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Ledger FA-000017 cost exceeds register by $85. Validate against PO-2024-0003.</t>
+          <t>Ledger FA-000017 cost exceeds register by $85 (validate PO-2024-0003). Accumulated depreciation $2,160 exceeds acquisition cost $2,070 by $90.</t>
         </is>
       </c>
     </row>
@@ -54115,25 +53884,20 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="7">
-        <f>IF(OR(C25="",D25=""),"",D25-C25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C25" s="7" t="n">
+        <v>790</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>930</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>514.88</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>514.88</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -54152,25 +53916,20 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="7">
-        <f>IF(OR(C26="",D26=""),"",D26-C26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C26" s="7" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>210</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>573.03</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>573.03</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -54189,25 +53948,20 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="7">
-        <f>IF(OR(C27="",D27=""),"",D27-C27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C27" s="7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>6480</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>1436.28</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>1436.28</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -54226,25 +53980,20 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="7">
-        <f>IF(OR(C28="",D28=""),"",D28-C28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C28" s="7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -54263,25 +54012,20 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="7">
-        <f>IF(OR(C29="",D29=""),"",D29-C29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C29" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>820</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>407.54</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>407.54</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -54300,25 +54044,20 @@
           <t>Ledger disposed without operational disposal evidence</t>
         </is>
       </c>
-      <c r="C30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="7">
-        <f>IF(OR(C30="",D30=""),"",D30-C30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C30" s="7" t="n">
+        <v>610</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>610</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -54337,25 +54076,20 @@
           <t>Ledger disposed without operational disposal evidence</t>
         </is>
       </c>
-      <c r="C31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="7">
-        <f>IF(OR(C31="",D31=""),"",D31-C31)</f>
-        <v/>
-      </c>
-      <c r="F31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C31" s="7" t="n">
+        <v>790</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>790</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -54374,25 +54108,20 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="7">
-        <f>IF(OR(C32="",D32=""),"",D32-C32)</f>
-        <v/>
-      </c>
-      <c r="F32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
+      <c r="C32" s="7" t="n">
+        <v>950</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -54411,29 +54140,16 @@
           <t>On inventory, missing from ledger (under-threshold)</t>
         </is>
       </c>
-      <c r="C33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="7">
-        <f>IF(OR(C33="",D33=""),"",D33-C33)</f>
-        <v/>
-      </c>
-      <c r="F33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
+      <c r="C33" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Register cost below $2,500. PO-2023-0022 capitalization_approved does not create an FA expectation. Informational only under ITAM-001 §7.</t>
+          <t>Register cost below $2,500. PO-2023-0023 capitalization_approved=No; FAR absence expected under ITAM-001 section 7. Informational only.</t>
         </is>
       </c>
     </row>
@@ -54448,29 +54164,16 @@
           <t>On inventory, missing from ledger (under-threshold)</t>
         </is>
       </c>
-      <c r="C34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="7">
-        <f>IF(OR(C34="",D34=""),"",D34-C34)</f>
-        <v/>
-      </c>
-      <c r="F34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
+      <c r="C34" s="7" t="n">
+        <v>1175</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Register cost below $2,500. PO-2023-0022 capitalization_approved does not create an FA expectation. Informational only under ITAM-001 §7.</t>
+          <t>Register cost below $2,500. PO-2023-0023 capitalization_approved=No; FAR absence expected under ITAM-001 section 7. Informational only.</t>
         </is>
       </c>
     </row>
@@ -54485,29 +54188,16 @@
           <t>On inventory, missing from ledger (capital-qualifying)</t>
         </is>
       </c>
-      <c r="C35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="7">
-        <f>IF(OR(C35="",D35=""),"",D35-C35)</f>
-        <v/>
-      </c>
-      <c r="F35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
+      <c r="C35" s="7" t="n">
+        <v>6470</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>No FA record for $6,470 network asset. Critical under ITAM-001 §7. Reject RN-0132 under-threshold claim.</t>
+          <t>Capital-qualifying asset on PO-2023-0022 with no FA row. RN-0132 rejected. Critical certification blocker.</t>
         </is>
       </c>
     </row>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corrected Register" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exception Register" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custody Chain" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Index" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Source Ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Corrected Register" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Exception Register" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Custody Chain" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ledger Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Certification" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Evidence Index" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,7 +614,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -5719,7 +5718,7 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Yanou &amp; Partners IT Services — IT Asset Reconciliation Dashboard</t>
+          <t>Yanou &amp; Partners IT Services - IT Asset Reconciliation Dashboard</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5729,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -5749,8 +5747,7 @@
           <t>Assets reviewed</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>COUNTA('Corrected Register'!$A$5:$A$136)</f>
+      <c r="B5" s="5" t="n">
         <v>132</v>
       </c>
     </row>
@@ -5760,8 +5757,7 @@
           <t>Corrected register acquisition cost</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>SUM('Corrected Register'!$M$5:$M$136)</f>
+      <c r="B6" s="5" t="n">
         <v>332115</v>
       </c>
     </row>
@@ -5771,8 +5767,7 @@
           <t>Remaining book value (ledger NBV where present)</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>SUM('Corrected Register'!$N$5:$N$136)</f>
+      <c r="B7" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
@@ -5782,8 +5777,7 @@
           <t>Open exceptions</t>
         </is>
       </c>
-      <c r="B8" s="5">
-        <f>COUNTIF('Exception Register'!$K$5:$K$167,"Open")</f>
+      <c r="B8" s="5" t="n">
         <v>163</v>
       </c>
     </row>
@@ -5793,8 +5787,7 @@
           <t>Certification blockers (Critical impact)</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <f>COUNTIF('Exception Register'!$C$5:$C$167,"Critical")</f>
+      <c r="B9" s="5" t="n">
         <v>43</v>
       </c>
     </row>
@@ -5804,8 +5797,7 @@
           <t>Assets Missing / Cannot Locate</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Missing")</f>
+      <c r="B10" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5815,8 +5807,7 @@
           <t>Overdue returns (label ≠ proof)</t>
         </is>
       </c>
-      <c r="B11" s="5">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Return Overdue")</f>
+      <c r="B11" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5826,8 +5817,7 @@
           <t>Verified disposed with certificate</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,"Disposed")</f>
+      <c r="B12" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5837,8 +5827,7 @@
           <t>Custody chains documented</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <f>COUNTA(UNIQUE(FILTER('Custody Chain'!A5:A501,'Custody Chain'!A5:A501&lt;&gt;"")))</f>
+      <c r="B13" s="5" t="n">
         <v>65</v>
       </c>
     </row>
@@ -5904,12 +5893,10 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A19)</f>
+      <c r="B19" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C19" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A19,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C19" s="7" t="n">
         <v>12961</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -5917,12 +5904,10 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="F19" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E19)</f>
+      <c r="F19" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="G19" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E19,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="G19" s="7" t="n">
         <v>1194.95</v>
       </c>
     </row>
@@ -5932,12 +5917,10 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A20)</f>
+      <c r="B20" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A20,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -5945,12 +5928,10 @@
           <t>Mobile Device</t>
         </is>
       </c>
-      <c r="F20" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E20)</f>
+      <c r="F20" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="G20" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E20,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="G20" s="7" t="n">
         <v>20855.29</v>
       </c>
     </row>
@@ -5960,12 +5941,10 @@
           <t>In Transit - Exception</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A21)</f>
+      <c r="B21" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A21,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C21" s="7" t="n">
         <v>1019.4</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -5973,12 +5952,10 @@
           <t>Monitor</t>
         </is>
       </c>
-      <c r="F21" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E21)</f>
+      <c r="F21" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="G21" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E21,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="G21" s="7" t="n">
         <v>11329.87</v>
       </c>
     </row>
@@ -5988,12 +5965,10 @@
           <t>In Use</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A22)</f>
+      <c r="B22" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="C22" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A22,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C22" s="7" t="n">
         <v>25512.76</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -6001,12 +5976,10 @@
           <t>Network Asset</t>
         </is>
       </c>
-      <c r="F22" s="7">
-        <f>COUNTIF('Corrected Register'!$C$5:$C$136,E22)</f>
+      <c r="F22" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="G22" s="7">
-        <f>SUMIF('Corrected Register'!$C$5:$C$136,E22,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="G22" s="7" t="n">
         <v>28181.49</v>
       </c>
     </row>
@@ -6016,12 +5989,10 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A23)</f>
+      <c r="B23" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C23" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A23,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C23" s="7" t="n">
         <v>6214.38</v>
       </c>
     </row>
@@ -6031,12 +6002,10 @@
           <t>Pending Redeployment</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A24)</f>
+      <c r="B24" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A24,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C24" s="7" t="n">
         <v>4851.08</v>
       </c>
     </row>
@@ -6046,12 +6015,10 @@
           <t>Retired/Pending Disposal</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A25)</f>
+      <c r="B25" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A25,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C25" s="7" t="n">
         <v>4811.33</v>
       </c>
     </row>
@@ -6061,12 +6028,10 @@
           <t>Return Overdue</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$136,A26)</f>
+      <c r="B26" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C26" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$136,A26,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C26" s="7" t="n">
         <v>6191.65</v>
       </c>
     </row>
@@ -6120,12 +6085,10 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A32)</f>
+      <c r="B32" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C32" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A32,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C32" s="7" t="n">
         <v>5184.18</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -6133,12 +6096,10 @@
           <t>Cannot Locate</t>
         </is>
       </c>
-      <c r="F32" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E32)</f>
+      <c r="F32" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G32" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E32,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G32" s="7" t="n">
         <v>6214.38</v>
       </c>
     </row>
@@ -6148,12 +6109,10 @@
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A33)</f>
+      <c r="B33" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C33" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A33,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C33" s="7" t="n">
         <v>6267.29</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -6161,12 +6120,10 @@
           <t>Closed Location Assignment</t>
         </is>
       </c>
-      <c r="F33" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E33)</f>
+      <c r="F33" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="G33" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E33,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G33" s="7" t="n">
         <v>29098.84</v>
       </c>
     </row>
@@ -6176,12 +6133,10 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A34)</f>
+      <c r="B34" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C34" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A34,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C34" s="7" t="n">
         <v>11070.95</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -6189,12 +6144,10 @@
           <t>Duplicate Serial Number</t>
         </is>
       </c>
-      <c r="F34" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E34)</f>
+      <c r="F34" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E34,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G34" s="7" t="n">
         <v>2503.11</v>
       </c>
     </row>
@@ -6204,12 +6157,10 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A35)</f>
+      <c r="B35" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C35" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A35,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C35" s="7" t="n">
         <v>5149.95</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -6217,12 +6168,10 @@
           <t>Former Employee Assignment</t>
         </is>
       </c>
-      <c r="F35" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E35)</f>
+      <c r="F35" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="G35" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E35,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G35" s="7" t="n">
         <v>22627.56</v>
       </c>
     </row>
@@ -6232,12 +6181,10 @@
           <t>Denver</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A36)</f>
+      <c r="B36" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C36" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A36,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C36" s="7" t="n">
         <v>5551.75</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -6245,12 +6192,10 @@
           <t>Inventory-to-Ledger Difference</t>
         </is>
       </c>
-      <c r="F36" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E36)</f>
+      <c r="F36" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="G36" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E36,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G36" s="7" t="n">
         <v>7440</v>
       </c>
     </row>
@@ -6260,12 +6205,10 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A37)</f>
+      <c r="B37" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C37" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A37,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C37" s="7" t="n">
         <v>10561</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -6273,12 +6216,10 @@
           <t>Missing Disposal Evidence</t>
         </is>
       </c>
-      <c r="F37" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E37)</f>
+      <c r="F37" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G37" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E37,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G37" s="7" t="n">
         <v>4811.33</v>
       </c>
     </row>
@@ -6288,12 +6229,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A38)</f>
+      <c r="B38" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C38" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A38,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C38" s="7" t="n">
         <v>6214.38</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -6301,12 +6240,10 @@
           <t>Overdue Return</t>
         </is>
       </c>
-      <c r="F38" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E38)</f>
+      <c r="F38" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G38" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E38,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G38" s="7" t="n">
         <v>6191.65</v>
       </c>
     </row>
@@ -6316,12 +6253,10 @@
           <t>Remote - Former Employee</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A39)</f>
+      <c r="B39" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C39" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A39,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C39" s="7" t="n">
         <v>4878.51</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -6329,12 +6264,10 @@
           <t>Shipment Mismatch</t>
         </is>
       </c>
-      <c r="F39" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E39)</f>
+      <c r="F39" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E39,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G39" s="7" t="n">
         <v>2332.54</v>
       </c>
     </row>
@@ -6344,12 +6277,10 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A40)</f>
+      <c r="B40" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C40" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A40,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -6357,12 +6288,10 @@
           <t>Unapproved Transfer</t>
         </is>
       </c>
-      <c r="F40" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$167,E40)</f>
+      <c r="F40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G40" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$167,E40,'Exception Register'!$G$5:$G$167)</f>
+      <c r="G40" s="7" t="n">
         <v>2869.32</v>
       </c>
     </row>
@@ -6372,13 +6301,22 @@
           <t>Atlanta Warehouse</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A41)</f>
+      <c r="B41" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A41,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C41" s="7" t="n">
         <v>4351.05</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Below Capitalization Threshold</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1875</v>
       </c>
     </row>
     <row r="42">
@@ -6387,12 +6325,10 @@
           <t>Carrier Network / Unverified</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A42)</f>
+      <c r="B42" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C42" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A42,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C42" s="7" t="n">
         <v>2332.54</v>
       </c>
     </row>
@@ -6402,19 +6338,17 @@
           <t>Disposed (certificate missing)</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$136,A43)</f>
+      <c r="B43" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$136,A43,'Corrected Register'!$N$5:$N$136)</f>
+      <c r="C43" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>Key finding — Duplicate serial identities (both pairs)</t>
+          <t>Key finding - Duplicate serial identities (both pairs)</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6465,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -6707,7 +6640,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00001 is In Use in Chicago. Employee E0001 (Active) matches the register holder. equipment_transfer_log TR-00001, approval APR-00001; received Jan 21, 2026. PO PO-2022-0001 on file; no matching FAR row for MD-00001.</t>
+          <t>Status for MD-00001: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $1895. hr_employee_status lists E0001 / Priya Shah as Active. Transfer TR-00001 received 2026-01-21; approval APR-00001. FAR row FA-000001; net book value $0. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6718,13 +6651,13 @@
       <c r="M5" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N5" s="7">
-        <f>IFERROR(XLOOKUP(A5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="7">
-        <f>IFERROR(XLOOKUP(A5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>FA-000001</t>
+        </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
@@ -6815,7 +6748,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00002: In Use in Dallas ($610). Employee E0002 (Active) matches the register holder. Assignment TR-00002; receive column 2026-02-25, approval APR-00002. PO PO-2022-0001 on file; no matching FAR row for MD-00002.</t>
+          <t>Dallas holds MD-00002 (Dell U2723QE) as In Use. Acquisition $610. People file: E0002 (Marcus Ellison), status Active. Transfer TR-00002 received 2026-02-25; approval APR-00002. Fixed-asset extract includes FA-000002 (NBV $313.06). PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6826,13 +6759,13 @@
       <c r="M6" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N6" s="7">
-        <f>IFERROR(XLOOKUP(A6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N6" s="7" t="n">
         <v>313.06</v>
       </c>
-      <c r="O6" s="7">
-        <f>IFERROR(XLOOKUP(A6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>FA-000002</t>
+        </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
@@ -6923,7 +6856,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Cost $1085 on MD-00003; In Use at Denver. Employee E0003 (Active) matches the register holder. TR-00003 for MD-00003 — received 04/03/2026, approval APR-00003. PO PO-2022-0001 on file; no matching FAR row for MD-00003.</t>
+          <t>MD-00003 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1085. Custodian E0003 (Elena Kovacs) is Active in hr_employee_status. Transfer TR-00003 received 2026-04-03; approval APR-00003. Ledger FA-000003 on file; NBV $597.83. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -6934,13 +6867,13 @@
       <c r="M7" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N7" s="7">
-        <f>IFERROR(XLOOKUP(A7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N7" s="7" t="n">
         <v>597.83</v>
       </c>
-      <c r="O7" s="7">
-        <f>IFERROR(XLOOKUP(A7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>FA-000003</t>
+        </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -7031,7 +6964,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>MD-00004 lists In Use at New York (Cisco C9300, $6380). Employee E0004 (Active) matches the register holder. Inbound stamp on TR-00004 is May 01, 2026, approval APR-00004. PO PO-2022-0001 on file; no matching FAR row for MD-00004.</t>
+          <t>Status for MD-00004: In Use. Site New York. Model Cisco C9300; cost $6380. hr_employee_status lists E0004 / James Whitaker as Active. Transfer TR-00004 received 2026-05-01; approval APR-00004. FAR row FA-000004; net book value $940.62. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -7042,13 +6975,13 @@
       <c r="M8" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N8" s="7">
-        <f>IFERROR(XLOOKUP(A8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N8" s="7" t="n">
         <v>940.62</v>
       </c>
-      <c r="O8" s="7">
-        <f>IFERROR(XLOOKUP(A8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>FA-000004</t>
+        </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -7139,7 +7072,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Register MD-00005: In Use, Seattle, $2075 — MacBook Pro 14. Employee E0005 (Active) matches the register holder. Log TR-00005: received 2026-06-08, approval APR-00005. PO PO-2022-0001 on file; no matching FAR row for MD-00005.</t>
+          <t>Seattle holds MD-00005 (MacBook Pro 14) as In Use. Acquisition $2075. People file: E0005 (Aisha Rahman), status Active. Transfer TR-00005 received 2026-06-08; approval APR-00005. Fixed-asset extract includes FA-000005 (NBV $0). PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -7150,13 +7083,13 @@
       <c r="M9" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N9" s="7">
-        <f>IFERROR(XLOOKUP(A9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="7">
-        <f>IFERROR(XLOOKUP(A9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>FA-000005</t>
+        </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -7247,7 +7180,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00006: In Use, Atlanta, $790 — Dell U2723QE. Employee E0006 (Active) matches the register holder. TR-00006 for MD-00006 — received 01/12/2026, approval APR-00006. PO-2022-0001 in hardware_purchase_orders.csv; FAR silent on MD-00006.</t>
+          <t>MD-00006 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $790. Custodian E0006 (Colin Bergstrom) is Active in hr_employee_status. Transfer TR-00006 received 2026-01-12; approval APR-00006. Ledger FA-000006 on file; NBV $459.94. PO PO-2022-0001.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7258,13 +7191,13 @@
       <c r="M10" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N10" s="7">
-        <f>IFERROR(XLOOKUP(A10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N10" s="7" t="n">
         <v>459.94</v>
       </c>
-      <c r="O10" s="7">
-        <f>IFERROR(XLOOKUP(A10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>FA-000006</t>
+        </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -7355,7 +7288,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00007 as In Use in Chicago. Employee E0007 (Active) matches the register holder. Movement TR-00007 posted 02/11/2026 and inbound Feb 17, 2026, approval APR-00007. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00007.</t>
+          <t>Status for MD-00007: In Use. Site Chicago. Model Samsung Galaxy S24; cost $950. hr_employee_status lists E0007 / Sofia Alvarez as Active. Transfer TR-00007 received 2026-02-17; approval APR-00007. FAR row FA-000007; net book value $632.68. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7366,13 +7299,13 @@
       <c r="M11" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N11" s="7">
-        <f>IFERROR(XLOOKUP(A11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>632.68</v>
-      </c>
-      <c r="O11" s="7">
-        <f>IFERROR(XLOOKUP(A11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="N11" s="7" t="n">
+        <v>632.6799999999999</v>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>FA-000007</t>
+        </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -7399,7 +7332,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>632.68</v>
+        <v>632.6799999999999</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -7463,7 +7396,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>MD-00008 (Cisco C9300) closed In Use / Dallas on $6245. Employee E0008 (Active) matches the register holder. Log TR-00008: received 2026-03-19, approval APR-00008. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00008.</t>
+          <t>Dallas holds MD-00008 (Cisco C9300) as In Use. Acquisition $6245. People file: E0008 (Derek Nguyen), status Active. Transfer TR-00008 received 2026-03-19; approval APR-00008. Fixed-asset extract includes FA-000008 (NBV $1355.01). PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7474,13 +7407,13 @@
       <c r="M12" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N12" s="7">
-        <f>IFERROR(XLOOKUP(A12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N12" s="7" t="n">
         <v>1355.01</v>
       </c>
-      <c r="O12" s="7">
-        <f>IFERROR(XLOOKUP(A12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>FA-000008</t>
+        </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -7571,7 +7504,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>MD-00009 carries In Use at Denver (Dell Latitude 7440, $1940). Employee E0009 (Active) matches the register holder. Assignment TR-00009; receive column 04/21/2026, approval APR-00009. PO-2023-0002 in hardware_purchase_orders.csv; FAR silent on MD-00009.</t>
+          <t>MD-00009 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1940. Custodian E0009 (Hannah Cole) is Active in hr_employee_status. Transfer TR-00009 received 2026-04-21; approval APR-00009. Ledger FA-000009 on file; NBV $109.33. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7582,13 +7515,13 @@
       <c r="M13" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N13" s="7">
-        <f>IFERROR(XLOOKUP(A13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N13" s="7" t="n">
         <v>109.33</v>
       </c>
-      <c r="O13" s="7">
-        <f>IFERROR(XLOOKUP(A13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>FA-000009</t>
+        </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -7679,7 +7612,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00010 In Use @ New York. Employee E0010 (Active) matches the register holder. Log TR-00010: received May 28, 2026, approval APR-00010. Purchasing PO-2023-0002 without a capital line for MD-00010.</t>
+          <t>Status for MD-00010: In Use. Site New York. Model Dell U2723QE; cost $655. hr_employee_status lists E0010 / Owen Patel as Active. Transfer TR-00010 received 2026-05-28; approval APR-00010. FAR row FA-000010; net book value $426.89. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7690,13 +7623,13 @@
       <c r="M14" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N14" s="7">
-        <f>IFERROR(XLOOKUP(A14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N14" s="7" t="n">
         <v>426.89</v>
       </c>
-      <c r="O14" s="7">
-        <f>IFERROR(XLOOKUP(A14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>FA-000010</t>
+        </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -7787,7 +7720,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00011 is In Use in Seattle site; basis $1130. Employee E0011 (Active) matches the register holder. Assignment TR-00011; receive column 2026-06-28, approval APR-00011. Purchasing PO-2023-0002 without a capital line for MD-00011.</t>
+          <t>Seattle holds MD-00011 (Samsung Galaxy S24) as In Use. Acquisition $1130. People file: E0011 (Maya Fontaine), status Active. Transfer TR-00011 received 2026-06-28; approval APR-00011. Fixed-asset extract includes FA-000011 (NBV $882.5). PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7798,13 +7731,13 @@
       <c r="M15" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N15" s="7">
-        <f>IFERROR(XLOOKUP(A15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N15" s="7" t="n">
         <v>882.5</v>
       </c>
-      <c r="O15" s="7">
-        <f>IFERROR(XLOOKUP(A15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>FA-000011</t>
+        </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -7895,7 +7828,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Read MD-00012 against transfers before signing In Use / Atlanta. Employee E0012 (Active) matches the register holder. Transfer TR-00012 shows receipt 01/31/2026, approval APR-00012. Purchasing PO-2023-0002 without a capital line for MD-00012.</t>
+          <t>MD-00012 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6425. Custodian E0012 (Ryan Okonkwo) is Active in hr_employee_status. Transfer TR-00012 received 2026-01-31; approval APR-00012. Ledger FA-000012 on file; NBV $553.23. PO PO-2023-0002.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7906,13 +7839,13 @@
       <c r="M16" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N16" s="7">
-        <f>IFERROR(XLOOKUP(A16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N16" s="7" t="n">
         <v>553.23</v>
       </c>
-      <c r="O16" s="7">
-        <f>IFERROR(XLOOKUP(A16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>FA-000012</t>
+        </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -8003,7 +7936,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Did not move MD-00013 off In Use at Chicago without a transaction. Employee E0013 (Active) matches the register holder. Inbound stamp on TR-00013 is Feb 06, 2026, approval APR-00013. Purchasing PO-2024-0003 without a capital line for MD-00013.</t>
+          <t>Status for MD-00013: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $2120. hr_employee_status lists E0013 / Lauren Briggs as Active. Transfer TR-00013 received 2026-02-06; approval APR-00013. FAR row FA-000013; net book value $0. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -8014,13 +7947,13 @@
       <c r="M17" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N17" s="7">
-        <f>IFERROR(XLOOKUP(A17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="7">
-        <f>IFERROR(XLOOKUP(A17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>FA-000013</t>
+        </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -8111,7 +8044,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Register MD-00014: In Use, Dallas, $520 — Dell U2723QE. Employee E0014 (Active) matches the register holder. equipment_transfer_log TR-00014, approval APR-00014; received 2026-03-09. Purchasing PO-2024-0003 without a capital line for MD-00014.</t>
+          <t>Dallas holds MD-00014 (Dell U2723QE) as In Use. Acquisition $520. People file: E0014 (Nathan Kim), status Active. Transfer TR-00014 received 2026-03-09; approval APR-00014. Fixed-asset extract includes FA-000014 (NBV $270.29). PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8122,13 +8055,13 @@
       <c r="M18" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N18" s="7">
-        <f>IFERROR(XLOOKUP(A18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N18" s="7" t="n">
         <v>270.29</v>
       </c>
-      <c r="O18" s="7">
-        <f>IFERROR(XLOOKUP(A18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>FA-000014</t>
+        </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -8219,7 +8152,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 MD-00015 tied to $995; location Denver; status In Use. Employee E0015 (Active) matches the register holder. TR-00015 ties to MD-00015; dock date 04/13/2026, approval APR-00015. Purchasing PO-2024-0003 without a capital line for MD-00015.</t>
+          <t>MD-00015 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $995. Custodian E0015 (Camila Ortiz) is Active in hr_employee_status. Transfer TR-00015 received 2026-04-13; approval APR-00015. Ledger FA-000015 on file; NBV $559.13. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -8230,13 +8163,13 @@
       <c r="M19" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N19" s="7">
-        <f>IFERROR(XLOOKUP(A19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N19" s="7" t="n">
         <v>559.13</v>
       </c>
-      <c r="O19" s="7">
-        <f>IFERROR(XLOOKUP(A19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>FA-000015</t>
+        </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -8327,7 +8260,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 on MD-00016 is In Use in New York; basis $6290. Employee E0016 (Active) matches the register holder. Assignment TR-00016; receive column May 17, 2026, approval APR-00016. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00016.</t>
+          <t>Status for MD-00016: In Use. Site New York. Model Cisco C9300; cost $6290. hr_employee_status lists E0016 / Patrick Gallagher as Active. Transfer TR-00016 received 2026-05-17; approval APR-00016. FAR row FA-000016; net book value $968.69. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -8338,13 +8271,13 @@
       <c r="M20" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N20" s="7">
-        <f>IFERROR(XLOOKUP(A20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>968.69</v>
-      </c>
-      <c r="O20" s="7">
-        <f>IFERROR(XLOOKUP(A20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="N20" s="7" t="n">
+        <v>968.6900000000001</v>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>FA-000016</t>
+        </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -8371,7 +8304,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>968.69</v>
+        <v>968.6900000000001</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -8435,7 +8368,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Assignment trail and HR both fit In Use for MD-00017 in Seattle. Employee E0017 (Active) matches the register holder. Transfer TR-00017 shows receipt 2026-06-19, approval APR-00017. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00017.</t>
+          <t>Seattle holds MD-00017 (MacBook Pro 14) as In Use. Acquisition $1985. People file: E0017 (Irene Cho), status Active. Transfer TR-00017 received 2026-06-19; approval APR-00017. Fixed-asset extract includes FA-000017 (NBV $0). PO PO-2024-0003. Accumulated depreciation $2160 exceeds acquisition $2070 by $90.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8446,13 +8379,13 @@
       <c r="M21" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N21" s="7">
-        <f>IFERROR(XLOOKUP(A21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="7">
-        <f>IFERROR(XLOOKUP(A21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>FA-000017</t>
+        </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -8547,7 +8480,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>People and transfer logs align on MD-00018 — In Use, Atlanta. Employee E0018 (Active) matches the register holder. Inbound stamp on TR-00018 is 01/23/2026, approval APR-00018. PO-2024-0003 in hardware_purchase_orders.csv; FAR silent on MD-00018.</t>
+          <t>MD-00018 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $700. Custodian E0018 (Theo Barnett) is Active in hr_employee_status. Transfer TR-00018 received 2026-01-23; approval APR-00018. Ledger FA-000018 on file; NBV $412.14. PO PO-2024-0003.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8558,13 +8491,13 @@
       <c r="M22" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N22" s="7">
-        <f>IFERROR(XLOOKUP(A22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N22" s="7" t="n">
         <v>412.14</v>
       </c>
-      <c r="O22" s="7">
-        <f>IFERROR(XLOOKUP(A22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>FA-000018</t>
+        </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -8655,7 +8588,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>MD-00019 sits In Use at Chicago (Samsung Galaxy S24, $1175). Employee E0019 (Active) matches the register holder. equipment_transfer_log TR-00019, approval APR-00019; received Feb 26, 2026. PO-2025-0004 in hardware_purchase_orders.csv; FAR silent on MD-00019.</t>
+          <t>Status for MD-00019: In Use. Site Chicago. Model Samsung Galaxy S24; cost $1175. hr_employee_status lists E0019 / Jasmine Reed as Active. Transfer TR-00019 received 2026-02-26; approval APR-00019. FAR row FA-000019; net book value $795.4. PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -8666,13 +8599,13 @@
       <c r="M23" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N23" s="7">
-        <f>IFERROR(XLOOKUP(A23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N23" s="7" t="n">
         <v>795.4</v>
       </c>
-      <c r="O23" s="7">
-        <f>IFERROR(XLOOKUP(A23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>FA-000019</t>
+        </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -8763,7 +8696,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 MD-00020 tied to $6470; location Dallas; status In Use. Employee E0020 (Active) matches the register holder. Inbound stamp on TR-00020 is 2026-03-30, approval APR-00020. Purchasing PO-2025-0004 without a capital line for MD-00020.</t>
+          <t>Dallas holds MD-00020 (Cisco C9300) as In Use. Acquisition $6470. People file: E0020 (Luis Navarro), status Active. Transfer TR-00020 received 2026-03-30; approval APR-00020. Fixed-asset extract includes FA-000020 (NBV $1446.34). PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -8774,13 +8707,13 @@
       <c r="M24" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N24" s="7" t="n">
         <v>1446.34</v>
       </c>
-      <c r="O24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>FA-000020</t>
+        </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -8871,7 +8804,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00021 In Use. Employee E0021 (Active) matches the register holder. equipment_transfer_log TR-00021, approval APR-00021; received 05/03/2026. Purchasing PO-2025-0004 without a capital line for MD-00021. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>MD-00021 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1850. Custodian E0021 (Grace Lindholm) is Active in hr_employee_status. Transfer TR-00021 received 2026-05-03; approval APR-00021. Ledger FA-000021 on file; NBV $124.52. PO PO-2025-0004. Duplicate serial MD-LA-050021 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -8882,13 +8815,13 @@
       <c r="M25" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N25" s="7" t="n">
         <v>124.52</v>
       </c>
-      <c r="O25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>FA-000021</t>
+        </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -8983,7 +8916,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>MD-00022 lists In Use at New York (Dell U2723QE, $565). Employee E0022 (Active) matches the register holder. TR-00022 ties to MD-00022; dock date Jun 05, 2026, approval APR-00022. Purchasing PO-2025-0004 without a capital line for MD-00022.</t>
+          <t>Status for MD-00022: In Use. Site New York. Model Dell U2723QE; cost $565. hr_employee_status lists E0022 / Andre Baptiste as Active. Transfer TR-00022 received 2026-06-05; approval APR-00022. FAR row FA-000022; net book value $371.95. PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -8994,13 +8927,13 @@
       <c r="M26" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N26" s="7" t="n">
         <v>371.95</v>
       </c>
-      <c r="O26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>FA-000022</t>
+        </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -9091,7 +9024,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>In Use / Seattle on MD-00023 (Samsung Galaxy S24, $1040) per cited files. Employee E0023 (Active) matches the register holder. TR-00023 for MD-00023 — received 2026-07-09, approval APR-00023. Purchasing PO-2025-0004 without a capital line for MD-00023.</t>
+          <t>Seattle holds MD-00023 (Samsung Galaxy S24) as In Use. Acquisition $1040. People file: E0023 (Nina Kowalski), status Active. Transfer TR-00023 received 2026-07-09; approval APR-00023. Fixed-asset extract includes FA-000023 (NBV $823.6). PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -9102,13 +9035,13 @@
       <c r="M27" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N27" s="7" t="n">
         <v>823.6</v>
       </c>
-      <c r="O27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>FA-000023</t>
+        </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -9199,7 +9132,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Extract row MD-00024: In Use, Atlanta, $6335 — Cisco C9300. Employee E0024 (Active) matches the register holder. Movement TR-00024 posted 2026-01-18 and inbound 01/21/2026, approval APR-00024. Purchasing PO-2025-0004 without a capital line for MD-00024.</t>
+          <t>MD-00024 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6335. Custodian E0024 (Chris Daley) is Active in hr_employee_status. Transfer TR-00024 received 2026-01-21; approval APR-00024. Ledger FA-000024 on file; NBV $503.85. PO PO-2025-0004.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -9210,13 +9143,13 @@
       <c r="M28" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N28" s="7" t="n">
         <v>503.85</v>
       </c>
-      <c r="O28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>FA-000024</t>
+        </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -9307,7 +9240,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Cost $2030 on MD-00025; In Use at Chicago. Employee E0025 (Active) matches the register holder. Log TR-00025: received Jan 22, 2026, approval APR-00025. PO-2022-0005 in hardware_purchase_orders.csv; FAR silent on MD-00025. Also: duplicate serial MD-LA-050021 flagged on the register.</t>
+          <t>Status for MD-00025: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $2030. hr_employee_status lists E0025 / Fatima Hussein as Active. Transfer TR-00025 received 2026-01-22; approval APR-00025. FAR row FA-000025; net book value $0. PO PO-2022-0005. Duplicate serial MD-LA-050021 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -9318,13 +9251,13 @@
       <c r="M29" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>FA-000025</t>
+        </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -9419,7 +9352,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00026 as In Use (Dallas). Employee E0026 (Active) matches the register holder. equipment_transfer_log TR-00026, approval APR-00026; received 2026-02-27. PO PO-2022-0005 on file; no matching FAR row for MD-00026.</t>
+          <t>Dallas holds MD-00026 (Dell U2723QE) as In Use. Acquisition $745. People file: E0026 (Brendan Walsh), status Active. Transfer TR-00026 received 2026-02-27; approval APR-00026. Fixed-asset extract includes FA-000026 (NBV $382.34). PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -9430,13 +9363,13 @@
       <c r="M30" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N30" s="7" t="n">
         <v>382.34</v>
       </c>
-      <c r="O30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>FA-000026</t>
+        </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -9531,7 +9464,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>MD-00027 reads In Use at Denver (Samsung Galaxy S24, $1220). Employee E0027 (Active) matches the register holder. TR-00027 ties to MD-00027; dock date 04/06/2026, approval APR-00027. PO PO-2022-0005 on file; no matching FAR row for MD-00027.</t>
+          <t>MD-00027 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1220. Custodian E0027 (Yuki Tanaka) is Active in hr_employee_status. Transfer TR-00027 received 2026-04-06; approval APR-00027. Ledger FA-000027 on file; NBV $672.21. PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -9542,13 +9475,13 @@
       <c r="M31" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N31" s="7" t="n">
         <v>672.21</v>
       </c>
-      <c r="O31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>FA-000027</t>
+        </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -9643,7 +9576,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Kept MD-00028 at In Use in New York; $6200 Cisco C9300. Employee E0028 (Active) matches the register holder. TR-00028 for MD-00028 — received May 02, 2026, approval APR-00028. PO PO-2022-0005 on file; no matching FAR row for MD-00028.</t>
+          <t>Status for MD-00028: In Use. Site New York. Model Cisco C9300; cost $6200. hr_employee_status lists E0028 / Megan Copeland as Active. Transfer TR-00028 received 2026-05-02; approval APR-00028. FAR row FA-000028; net book value $914.09. PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -9654,13 +9587,13 @@
       <c r="M32" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N32" s="7" t="n">
         <v>914.09</v>
       </c>
-      <c r="O32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>FA-000028</t>
+        </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -9755,7 +9688,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Asset row MD-00029: In Use, Seattle, $1895 — MacBook Pro 14. Employee E0029 (Active) matches the register holder. Movement TR-00029 posted Jun 05, 2026 and inbound 2026-06-11, approval APR-00029. PO PO-2022-0005 on file; no matching FAR row for MD-00029.</t>
+          <t>Seattle holds MD-00029 (MacBook Pro 14) as In Use. Acquisition $1895. People file: E0029 (Omar Haddad), status Active. Transfer TR-00029 received 2026-06-11; approval APR-00029. Fixed-asset extract includes FA-000029 (NBV $0). PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -9766,13 +9699,13 @@
       <c r="M33" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>FA-000029</t>
+        </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -9867,7 +9800,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Cost $610 on MD-00030; In Use at Atlanta. Employee E0030 (Active) matches the register holder. TR-00030 for MD-00030 — received 01/13/2026, approval APR-00030. PO-2022-0005 in hardware_purchase_orders.csv; FAR silent on MD-00030.</t>
+          <t>MD-00030 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $610. Custodian E0030 (Stephanie Ruiz) is Active in hr_employee_status. Transfer TR-00030 received 2026-01-13; approval APR-00030. Ledger FA-000030 on file; NBV $355.14. PO PO-2022-0005.</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -9878,13 +9811,13 @@
       <c r="M34" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N34" s="7" t="n">
         <v>355.14</v>
       </c>
-      <c r="O34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>FA-000030</t>
+        </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -9979,7 +9912,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Chicago: MD-00031 is In Use; cost $1085. Employee E0031 (Active) matches the register holder. Movement TR-00031 posted 02/11/2026 and inbound Feb 11, 2026, approval APR-00031. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00031.</t>
+          <t>Status for MD-00031: In Use. Site Chicago. Model Samsung Galaxy S24; cost $1085. hr_employee_status lists E0031 / Keith Moreau as Active. Transfer TR-00031 received 2026-02-11; approval APR-00031. FAR row FA-000031; net book value $722.59. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -9990,13 +9923,13 @@
       <c r="M35" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N35" s="7" t="n">
         <v>722.59</v>
       </c>
-      <c r="O35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>FA-000031</t>
+        </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -10091,7 +10024,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>MD-00032 stays In Use at Dallas (Cisco C9300, $6380). Employee E0032 (Active) matches the register holder. Log TR-00032: received 2026-03-22, approval APR-00032. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00032.</t>
+          <t>Dallas holds MD-00032 (Cisco C9300) as In Use. Acquisition $6380. People file: E0032 (Diana Voss), status Active. Transfer TR-00032 received 2026-03-22; approval APR-00032. Fixed-asset extract includes FA-000032 (NBV $1384.3). PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -10102,13 +10035,13 @@
       <c r="M36" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N36" s="7">
-        <f>IFERROR(XLOOKUP(A36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N36" s="7" t="n">
         <v>1384.3</v>
       </c>
-      <c r="O36" s="7">
-        <f>IFERROR(XLOOKUP(A36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>FA-000032</t>
+        </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -10203,7 +10136,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00033: In Use in Denver ($2075). Employee E0033 (Active) matches the register holder. Assignment TR-00033; receive column 04/22/2026, approval APR-00033. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00033.</t>
+          <t>MD-00033 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $2075. Custodian E0033 (Jordan Blake) is Active in hr_employee_status. Transfer TR-00033 received 2026-04-22; approval APR-00033. Ledger FA-000033 on file; NBV $116.93. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -10214,13 +10147,13 @@
       <c r="M37" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N37" s="7">
-        <f>IFERROR(XLOOKUP(A37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N37" s="7" t="n">
         <v>116.93</v>
       </c>
-      <c r="O37" s="7">
-        <f>IFERROR(XLOOKUP(A37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>FA-000033</t>
+        </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
@@ -10315,7 +10248,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00034 is In Use in New York office; basis $790. Employee E0034 (Active) matches the register holder. Transfer TR-00034 shows receipt May 22, 2026, approval APR-00034. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00034.</t>
+          <t>Status for MD-00034: In Use. Site New York. Model Dell U2723QE; cost $790. hr_employee_status lists E0034 / Amelia Grant as Active. Transfer TR-00034 received 2026-05-22; approval APR-00034. FAR row FA-000034; net book value $514.88. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10326,13 +10259,13 @@
       <c r="M38" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N38" s="7">
-        <f>IFERROR(XLOOKUP(A38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N38" s="7" t="n">
         <v>514.88</v>
       </c>
-      <c r="O38" s="7">
-        <f>IFERROR(XLOOKUP(A38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>FA-000034</t>
+        </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
@@ -10427,7 +10360,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>MD-00035 shows In Use at Seattle (Samsung Galaxy S24, $950). Employee E0035 (Active) matches the register holder. Inbound stamp on TR-00035 is 2026-06-30, approval APR-00035. PO-2023-0006 in hardware_purchase_orders.csv; FAR silent on MD-00035.</t>
+          <t>Seattle holds MD-00035 (Samsung Galaxy S24) as In Use. Acquisition $950. People file: E0035 (Rafael Mendes), status Active. Transfer TR-00035 received 2026-06-30; approval APR-00035. Fixed-asset extract includes FA-000035 (NBV $741.92). PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -10438,13 +10371,13 @@
       <c r="M39" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N39" s="7">
-        <f>IFERROR(XLOOKUP(A39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N39" s="7" t="n">
         <v>741.92</v>
       </c>
-      <c r="O39" s="7">
-        <f>IFERROR(XLOOKUP(A39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>FA-000035</t>
+        </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -10539,7 +10472,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>The cited records support In Use in Atlanta for MD-00036. Employee E0036 (Active) matches the register holder. Movement TR-00036 posted 2026-01-30 and inbound 02/01/2026, approval APR-00036. PO PO-2023-0006 on file; no matching FAR row for MD-00036.</t>
+          <t>MD-00036 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6245. Custodian E0036 (Kate Sorenson) is Active in hr_employee_status. Transfer TR-00036 received 2026-02-01; approval APR-00036. Ledger FA-000036 on file; NBV $537.73. PO PO-2023-0006.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10550,13 +10483,13 @@
       <c r="M40" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N40" s="7">
-        <f>IFERROR(XLOOKUP(A40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N40" s="7" t="n">
         <v>537.73</v>
       </c>
-      <c r="O40" s="7">
-        <f>IFERROR(XLOOKUP(A40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>FA-000036</t>
+        </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -10651,7 +10584,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>MD-00037 remains In Use at Chicago (Lenovo ThinkPad T14, $1940). Employee E0037 (Active) matches the register holder. Log TR-00037: received Feb 02, 2026, approval APR-00037. PO PO-2024-0007 on file; no matching FAR row for MD-00037.</t>
+          <t>Status for MD-00037: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $1940. hr_employee_status lists E0037 / Victor Lang as Active. Transfer TR-00037 received 2026-02-02; approval APR-00037. FAR row FA-000037; net book value $0. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -10662,13 +10595,13 @@
       <c r="M41" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N41" s="7">
-        <f>IFERROR(XLOOKUP(A41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="7">
-        <f>IFERROR(XLOOKUP(A41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>FA-000037</t>
+        </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
@@ -10763,7 +10696,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>MD-00038 reconciled In Use with Dallas as the working site. Employee E0038 (Active) matches the register holder. Assignment TR-00038; receive column 2026-03-11, approval APR-00038. PO PO-2024-0007 on file; no matching FAR row for MD-00038.</t>
+          <t>Dallas holds MD-00038 (Dell U2723QE) as In Use. Acquisition $655. People file: E0038 (Noelle Harper), status Active. Transfer TR-00038 received 2026-03-11; approval APR-00038. Fixed-asset extract includes FA-000038 (NBV $340.46). PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10774,13 +10707,13 @@
       <c r="M42" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N42" s="7">
-        <f>IFERROR(XLOOKUP(A42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N42" s="7" t="n">
         <v>340.46</v>
       </c>
-      <c r="O42" s="7">
-        <f>IFERROR(XLOOKUP(A42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>FA-000038</t>
+        </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
@@ -10875,7 +10808,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00039 is In Use in floor Denver; basis $1130. Employee E0039 (Active) matches the register holder. Transfer TR-00039 shows receipt 04/14/2026, approval APR-00039. PO PO-2024-0007 on file; no matching FAR row for MD-00039.</t>
+          <t>MD-00039 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1130. Custodian E0039 (Samir Kapoor) is Active in hr_employee_status. Transfer TR-00039 received 2026-04-14; approval APR-00039. Ledger FA-000039 on file; NBV $635. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -10886,13 +10819,13 @@
       <c r="M43" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N43" s="7">
-        <f>IFERROR(XLOOKUP(A43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N43" s="7" t="n">
         <v>635</v>
       </c>
-      <c r="O43" s="7">
-        <f>IFERROR(XLOOKUP(A43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>FA-000039</t>
+        </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
@@ -10987,7 +10920,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>MD-00040 shows In Use at New York (Cisco C9300, $6425). Employee E0040 (Active) matches the register holder. Assignment TR-00040; receive column May 13, 2026, approval APR-00040. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00040.</t>
+          <t>Status for MD-00040: In Use. Site New York. Model Cisco C9300; cost $6425. hr_employee_status lists E0040 / Holly Jensen as Active. Transfer TR-00040 received 2026-05-13; approval APR-00040. FAR row FA-000040; net book value $989.48. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -10998,13 +10931,13 @@
       <c r="M44" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N44" s="7">
-        <f>IFERROR(XLOOKUP(A44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N44" s="7" t="n">
         <v>989.48</v>
       </c>
-      <c r="O44" s="7">
-        <f>IFERROR(XLOOKUP(A44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>FA-000040</t>
+        </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -11099,7 +11032,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00041 is In Use in Seattle. Employee E0041 (Active) matches the register holder. Transfer TR-00041 shows receipt 2026-06-20, approval APR-00041. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00041.</t>
+          <t>Seattle holds MD-00041 (MacBook Pro 14) as In Use. Acquisition $2120. People file: E0041 (Eric Vann), status Active. Transfer TR-00041 received 2026-06-20; approval APR-00041. Fixed-asset extract includes FA-000041 (NBV $0). PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -11110,13 +11043,13 @@
       <c r="M45" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N45" s="7">
-        <f>IFERROR(XLOOKUP(A45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="7">
-        <f>IFERROR(XLOOKUP(A45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>FA-000041</t>
+        </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -11211,7 +11144,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Inventory line MD-00042: In Use, Atlanta, $520 — Dell U2723QE. Employee E0042 (Active) matches the register holder. Inbound stamp on TR-00042 is 01/24/2026, approval APR-00042. PO-2024-0007 in hardware_purchase_orders.csv; FAR silent on MD-00042.</t>
+          <t>MD-00042 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $520. Custodian E0042 (Claudia Rossi) is Active in hr_employee_status. Transfer TR-00042 received 2026-01-24; approval APR-00042. Ledger FA-000042 on file; NBV $306.16. PO PO-2024-0007.</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -11222,13 +11155,13 @@
       <c r="M46" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N46" s="7">
-        <f>IFERROR(XLOOKUP(A46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N46" s="7" t="n">
         <v>306.16</v>
       </c>
-      <c r="O46" s="7">
-        <f>IFERROR(XLOOKUP(A46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>FA-000042</t>
+        </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -11323,7 +11256,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00043 across CSV/XLSX inputs — In Use, Chicago. Employee E0043 (Active) matches the register holder. equipment_transfer_log TR-00043, approval APR-00043; received Mar 01, 2026. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00043.</t>
+          <t>Status for MD-00043: In Use. Site Chicago. Model Samsung Galaxy S24; cost $995. hr_employee_status lists E0043 / Tyler Brooks as Active. Transfer TR-00043 received 2026-03-01; approval APR-00043. FAR row FA-000043; net book value $673.55. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -11334,13 +11267,13 @@
       <c r="M47" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N47" s="7">
-        <f>IFERROR(XLOOKUP(A47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N47" s="7" t="n">
         <v>673.55</v>
       </c>
-      <c r="O47" s="7">
-        <f>IFERROR(XLOOKUP(A47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>FA-000043</t>
+        </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -11435,7 +11368,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Verified In Use for MD-00044 at Dallas; acquisition $6290. Employee E0044 (Active) matches the register holder. TR-00044 ties to MD-00044; dock date 2026-03-31, approval APR-00044. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00044.</t>
+          <t>Dallas holds MD-00044 (Cisco C9300) as In Use. Acquisition $6290. People file: E0044 (Leah Okada), status Active. Transfer TR-00044 received 2026-03-31; approval APR-00044. Fixed-asset extract includes FA-000044 (NBV $1406.1). PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -11446,13 +11379,13 @@
       <c r="M48" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N48" s="7">
-        <f>IFERROR(XLOOKUP(A48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N48" s="7" t="n">
         <v>1406.1</v>
       </c>
-      <c r="O48" s="7">
-        <f>IFERROR(XLOOKUP(A48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>FA-000044</t>
+        </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -11547,7 +11480,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>MD-00045 reflects In Use at Denver (Dell Latitude 7440, $1985). Employee E0045 (Active) matches the register holder. TR-00045 for MD-00045 — received 05/03/2026, approval APR-00045. PO-2025-0008 in hardware_purchase_orders.csv; FAR silent on MD-00045.</t>
+          <t>MD-00045 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1985. Custodian E0045 (Darnell Price) is Active in hr_employee_status. Transfer TR-00045 received 2026-05-03; approval APR-00045. Ledger FA-000045 on file; NBV $133.6. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -11558,13 +11491,13 @@
       <c r="M49" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N49" s="7">
-        <f>IFERROR(XLOOKUP(A49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N49" s="7" t="n">
         <v>133.6</v>
       </c>
-      <c r="O49" s="7">
-        <f>IFERROR(XLOOKUP(A49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>FA-000045</t>
+        </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -11655,7 +11588,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00046: Available in New York ($700). Transfer TR-00046 shows receipt Jun 07, 2026, approval APR-00046. PO PO-2025-0008 on file; no matching FAR row for MD-00046.</t>
+          <t>MD-00046 (Dell U2723QE) is Available at New York. Acquisition cost $700. Transfer TR-00046 received 2026-06-07; approval APR-00046. FAR row FA-000046; net book value $460.82. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -11666,13 +11599,13 @@
       <c r="M50" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N50" s="7">
-        <f>IFERROR(XLOOKUP(A50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N50" s="7" t="n">
         <v>460.82</v>
       </c>
-      <c r="O50" s="7">
-        <f>IFERROR(XLOOKUP(A50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>FA-000046</t>
+        </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
@@ -11763,7 +11696,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>MD-00047 stays Available at Seattle (Samsung Galaxy S24, $1175). Inbound stamp on TR-00047 is 2026-07-10, approval APR-00047. PO PO-2025-0008 on file; no matching FAR row for MD-00047.</t>
+          <t>MD-00047 (Samsung Galaxy S24) is Available at Seattle. Acquisition cost $1175. Transfer TR-00047 received 2026-07-10; approval APR-00047. Fixed-asset extract includes FA-000047 (NBV $930.51). PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -11774,13 +11707,13 @@
       <c r="M51" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N51" s="7">
-        <f>IFERROR(XLOOKUP(A51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N51" s="7" t="n">
         <v>930.51</v>
       </c>
-      <c r="O51" s="7">
-        <f>IFERROR(XLOOKUP(A51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>FA-000047</t>
+        </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -11871,7 +11804,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Atlanta: MD-00048 is Available; cost $6470. equipment_transfer_log TR-00048, approval APR-00048; received 01/24/2026. PO PO-2025-0008 on file; no matching FAR row for MD-00048.</t>
+          <t>MD-00048 (Cisco C9300) is Available at Atlanta. Acquisition cost $6470. Transfer TR-00048 received 2026-01-24; approval APR-00048. Ledger FA-000048 on file; NBV $514.59. PO PO-2025-0008.</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -11882,13 +11815,13 @@
       <c r="M52" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N52" s="7">
-        <f>IFERROR(XLOOKUP(A52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N52" s="7" t="n">
         <v>514.59</v>
       </c>
-      <c r="O52" s="7">
-        <f>IFERROR(XLOOKUP(A52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>FA-000048</t>
+        </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -11979,7 +11912,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Cost $1850 on MD-00049; Available at Chicago. TR-00049 ties to MD-00049; dock date Jan 23, 2026, approval APR-00049. Purchasing PO-2022-0009 without a capital line for MD-00049.</t>
+          <t>MD-00049 (Lenovo ThinkPad T14) is Available at Chicago. Acquisition cost $1850. Transfer TR-00049 received 2026-01-23; approval APR-00049. FAR row FA-000049; net book value $0. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -11990,13 +11923,13 @@
       <c r="M53" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N53" s="7">
-        <f>IFERROR(XLOOKUP(A53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N53" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="7">
-        <f>IFERROR(XLOOKUP(A53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>FA-000049</t>
+        </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -12087,7 +12020,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Asset row MD-00050: Available, Dallas, $565 — Dell U2723QE. equipment_transfer_log TR-00050, approval APR-00050; received 2026-02-23. PO PO-2022-0009 on file; no matching FAR row for MD-00050.</t>
+          <t>MD-00050 (Dell U2723QE) is Available at Dallas. Acquisition cost $565. Transfer TR-00050 received 2026-02-23; approval APR-00050. Fixed-asset extract includes FA-000050 (NBV $289.96). PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -12098,13 +12031,13 @@
       <c r="M54" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N54" s="7">
-        <f>IFERROR(XLOOKUP(A54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N54" s="7" t="n">
         <v>289.96</v>
       </c>
-      <c r="O54" s="7">
-        <f>IFERROR(XLOOKUP(A54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>FA-000050</t>
+        </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -12195,7 +12128,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Kept MD-00051 at Available in Denver; $1040 Samsung Galaxy S24. TR-00051 ties to MD-00051; dock date 03/31/2026, approval APR-00051. PO PO-2022-0009 on file; no matching FAR row for MD-00051.</t>
+          <t>MD-00051 (Samsung Galaxy S24) is Available at Denver. Acquisition cost $1040. Transfer TR-00051 received 2026-03-31; approval APR-00051. Ledger FA-000051 on file; NBV $573.03. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -12206,13 +12139,13 @@
       <c r="M55" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N55" s="7">
-        <f>IFERROR(XLOOKUP(A55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N55" s="7" t="n">
         <v>573.03</v>
       </c>
-      <c r="O55" s="7">
-        <f>IFERROR(XLOOKUP(A55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>FA-000051</t>
+        </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
@@ -12303,7 +12236,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>MD-00052 reads Available at New York (Cisco C9300, $6335). TR-00052 for MD-00052 — received May 02, 2026, approval APR-00052. PO PO-2022-0009 on file; no matching FAR row for MD-00052.</t>
+          <t>MD-00052 (Cisco C9300) is Available at New York. Acquisition cost $6335. Transfer TR-00052 received 2026-05-02; approval APR-00052. FAR row FA-000052; net book value $933.99. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -12314,13 +12247,13 @@
       <c r="M56" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N56" s="7">
-        <f>IFERROR(XLOOKUP(A56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N56" s="7" t="n">
         <v>933.99</v>
       </c>
-      <c r="O56" s="7">
-        <f>IFERROR(XLOOKUP(A56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>FA-000052</t>
+        </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
@@ -12411,7 +12344,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00053 as Available (Seattle). Movement TR-00053 posted Jun 05, 2026 and inbound 2026-06-05, approval APR-00053. PO PO-2022-0009 on file; no matching FAR row for MD-00053.</t>
+          <t>MD-00053 (MacBook Pro 14) is Available at Seattle. Acquisition cost $2030. Transfer TR-00053 received 2026-06-05; approval APR-00053. Fixed-asset extract includes FA-000053 (NBV $0). PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -12422,13 +12355,13 @@
       <c r="M57" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N57" s="7">
-        <f>IFERROR(XLOOKUP(A57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N57" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="7">
-        <f>IFERROR(XLOOKUP(A57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>FA-000053</t>
+        </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
@@ -12519,7 +12452,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>No stronger file contradicted Available for MD-00054 at Atlanta. Log TR-00054: received 01/16/2026, approval APR-00054. PO PO-2022-0009 on file; no matching FAR row for MD-00054.</t>
+          <t>MD-00054 (Dell U2723QE) is Available at Atlanta. Acquisition cost $745. Transfer TR-00054 received 2026-01-16; approval APR-00054. Ledger FA-000054 on file; NBV $433.74. PO PO-2022-0009.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -12530,13 +12463,13 @@
       <c r="M58" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N58" s="7">
-        <f>IFERROR(XLOOKUP(A58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N58" s="7" t="n">
         <v>433.74</v>
       </c>
-      <c r="O58" s="7">
-        <f>IFERROR(XLOOKUP(A58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>FA-000054</t>
+        </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
@@ -12627,7 +12560,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>MD-00055 sits Available at Chicago (Samsung Galaxy S24, $1220). Assignment TR-00055; receive column Feb 12, 2026, approval APR-00055. Purchasing PO-2023-0010 without a capital line for MD-00055.</t>
+          <t>MD-00055 (Samsung Galaxy S24) is Available at Chicago. Acquisition cost $1220. Transfer TR-00055 received 2026-02-12; approval APR-00055. FAR row FA-000055; net book value $812.5. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -12638,13 +12571,13 @@
       <c r="M59" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N59" s="7">
-        <f>IFERROR(XLOOKUP(A59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N59" s="7" t="n">
         <v>812.5</v>
       </c>
-      <c r="O59" s="7">
-        <f>IFERROR(XLOOKUP(A59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>FA-000055</t>
+        </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
@@ -12735,7 +12668,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Available / Dallas on MD-00056 (Cisco C9300, $6200) per cited files. TR-00056 ties to MD-00056; dock date 2026-03-16, approval APR-00056. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00056.</t>
+          <t>MD-00056 (Cisco C9300) is Available at Dallas. Acquisition cost $6200. Transfer TR-00056 received 2026-03-16; approval APR-00056. Fixed-asset extract includes FA-000056 (NBV $1345.24). PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -12746,13 +12679,13 @@
       <c r="M60" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N60" s="7">
-        <f>IFERROR(XLOOKUP(A60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N60" s="7" t="n">
         <v>1345.24</v>
       </c>
-      <c r="O60" s="7">
-        <f>IFERROR(XLOOKUP(A60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>FA-000056</t>
+        </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
@@ -12843,7 +12776,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>MD-00057 lists Available at Denver (Dell Latitude 7440, $1895). TR-00057 for MD-00057 — received 04/24/2026, approval APR-00057. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00057.</t>
+          <t>MD-00057 (Dell Latitude 7440) is Available at Denver. Acquisition cost $1895. Transfer TR-00057 received 2026-04-24; approval APR-00057. Ledger FA-000057 on file; NBV $106.79. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -12854,13 +12787,13 @@
       <c r="M61" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N61" s="7">
-        <f>IFERROR(XLOOKUP(A61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N61" s="7" t="n">
         <v>106.79</v>
       </c>
-      <c r="O61" s="7">
-        <f>IFERROR(XLOOKUP(A61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>FA-000057</t>
+        </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -12955,7 +12888,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>Read MD-00058 against transfers before signing Pending Redeployment / New York. Movement TR-00058 posted 05/22/2026 and inbound May 23, 2026, approval field blank. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00058. Also: offboarding ticket OFF-00058 referenced.</t>
+          <t>MD-00058 (Dell U2723QE) is Pending Redeployment at New York. Acquisition cost $610. Transfer TR-00058 received 2026-05-23; approval blank. FAR row FA-000058; net book value $397.56. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -12966,13 +12899,13 @@
       <c r="M62" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N62" s="7">
-        <f>IFERROR(XLOOKUP(A62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N62" s="7" t="n">
         <v>397.56</v>
       </c>
-      <c r="O62" s="7">
-        <f>IFERROR(XLOOKUP(A62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>FA-000058</t>
+        </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
@@ -13067,7 +13000,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00059 Pending Redeployment. Log TR-00059: received 2026-06-26, approval field blank. PO-2023-0010 in hardware_purchase_orders.csv; FAR silent on MD-00059. Also: offboarding ticket OFF-00059 referenced.</t>
+          <t>MD-00059 (Samsung Galaxy S24) is Pending Redeployment at Seattle. Acquisition cost $1085. Transfer TR-00059 received 2026-06-26; approval blank. Fixed-asset extract includes FA-000059 (NBV $847.35). PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -13078,13 +13011,13 @@
       <c r="M63" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N63" s="7">
-        <f>IFERROR(XLOOKUP(A63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N63" s="7" t="n">
         <v>847.35</v>
       </c>
-      <c r="O63" s="7">
-        <f>IFERROR(XLOOKUP(A63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>FA-000059</t>
+        </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -13179,7 +13112,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>The cited records support Pending Redeployment in Atlanta for MD-00060. Movement TR-00060 posted 2026-01-30 and inbound 02/02/2026, approval APR-00060. Purchasing PO-2023-0010 without a capital line for MD-00060. Also: offboarding ticket OFF-00060 referenced.</t>
+          <t>MD-00060 (Cisco C9300) is Pending Redeployment at Atlanta. Acquisition cost $6380. Transfer TR-00060 received 2026-02-02; approval APR-00060. Ledger FA-000060 on file; NBV $549.35. PO PO-2023-0010.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -13190,13 +13123,13 @@
       <c r="M64" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N64" s="7">
-        <f>IFERROR(XLOOKUP(A64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N64" s="7" t="n">
         <v>549.35</v>
       </c>
-      <c r="O64" s="7">
-        <f>IFERROR(XLOOKUP(A64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>FA-000060</t>
+        </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -13291,7 +13224,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Chicago holds MD-00061 (Lenovo ThinkPad T14) as Pending Redeployment. Log TR-00061: received Feb 03, 2026, approval APR-00061. Purchasing PO-2024-0011 without a capital line for MD-00061. Also: offboarding ticket OFF-00061 referenced.</t>
+          <t>MD-00061 (Lenovo ThinkPad T14) is Pending Redeployment at Chicago. Acquisition cost $2075. Transfer TR-00061 received 2026-02-03; approval APR-00061. FAR row FA-000061; net book value $0. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -13302,13 +13235,13 @@
       <c r="M65" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N65" s="7">
-        <f>IFERROR(XLOOKUP(A65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N65" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="7">
-        <f>IFERROR(XLOOKUP(A65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>FA-000061</t>
+        </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
@@ -13403,7 +13336,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 (Dell U2723QE) closed Pending Redeployment / Dallas on $790. Assignment TR-00062; receive column 2026-03-07, approval APR-00062. Purchasing PO-2024-0011 without a capital line for MD-00062. Also: offboarding ticket OFF-00062 referenced.</t>
+          <t>MD-00062 (Dell U2723QE) is Pending Redeployment at Dallas. Acquisition cost $790. Transfer TR-00062 received 2026-03-07; approval APR-00062. Fixed-asset extract includes FA-000062 (NBV $410.63). PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -13414,13 +13347,13 @@
       <c r="M66" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N66" s="7">
-        <f>IFERROR(XLOOKUP(A66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N66" s="7" t="n">
         <v>410.63</v>
       </c>
-      <c r="O66" s="7">
-        <f>IFERROR(XLOOKUP(A66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>FA-000062</t>
+        </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -13515,7 +13448,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Assignment trail and HR both fit Pending Redeployment for MD-00063 in Denver. Transfer TR-00063 shows receipt 04/16/2026, approval APR-00063. Purchasing PO-2024-0011 without a capital line for MD-00063. Also: offboarding ticket OFF-00063 referenced.</t>
+          <t>MD-00063 (Samsung Galaxy S24) is Pending Redeployment at Denver. Acquisition cost $950. Transfer TR-00063 received 2026-04-16; approval APR-00063. Ledger FA-000063 on file; NBV $533.85. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -13526,13 +13459,13 @@
       <c r="M67" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N67" s="7">
-        <f>IFERROR(XLOOKUP(A67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N67" s="7" t="n">
         <v>533.85</v>
       </c>
-      <c r="O67" s="7">
-        <f>IFERROR(XLOOKUP(A67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>FA-000063</t>
+        </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -13627,7 +13560,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>Cross-file check left MD-00064 as Pending Redeployment (New York). Inbound stamp on TR-00064 is May 14, 2026, approval field blank. Purchasing PO-2024-0011 without a capital line for MD-00064. Also: offboarding ticket OFF-00064 referenced.</t>
+          <t>MD-00064 (Cisco C9300) is Pending Redeployment at New York. Acquisition cost $6245. Transfer TR-00064 received 2026-05-14; approval blank. FAR row FA-000064; net book value $961.76. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -13638,13 +13571,13 @@
       <c r="M68" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N68" s="7">
-        <f>IFERROR(XLOOKUP(A68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N68" s="7" t="n">
         <v>961.76</v>
       </c>
-      <c r="O68" s="7">
-        <f>IFERROR(XLOOKUP(A68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>FA-000064</t>
+        </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -13739,7 +13672,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 still Pending Redeployment; Seattle is the verified site. equipment_transfer_log TR-00065, approval field blank; received 2026-06-23. Purchasing PO-2024-0011 without a capital line for MD-00065. Also: offboarding ticket OFF-00065 referenced.</t>
+          <t>MD-00065 (MacBook Pro 14) is Pending Redeployment at Seattle. Acquisition cost $1940. Transfer TR-00065 received 2026-06-23; approval blank. Fixed-asset extract includes FA-000065 (NBV $0). PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -13750,13 +13683,13 @@
       <c r="M69" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N69" s="7">
-        <f>IFERROR(XLOOKUP(A69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N69" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O69" s="7">
-        <f>IFERROR(XLOOKUP(A69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>FA-000065</t>
+        </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -13851,7 +13784,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00066 is Pending Redeployment in Atlanta office; basis $655. Log TR-00066: received 01/25/2026, approval APR-00066. PO-2024-0011 in hardware_purchase_orders.csv; FAR silent on MD-00066. Also: offboarding ticket OFF-00066 referenced.</t>
+          <t>MD-00066 (Dell U2723QE) is Pending Redeployment at Atlanta. Acquisition cost $655. Transfer TR-00066 received 2026-01-25; approval APR-00066. Ledger FA-000066 on file; NBV $385.65. PO PO-2024-0011.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -13862,13 +13795,13 @@
       <c r="M70" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N70" s="7">
-        <f>IFERROR(XLOOKUP(A70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N70" s="7" t="n">
         <v>385.65</v>
       </c>
-      <c r="O70" s="7">
-        <f>IFERROR(XLOOKUP(A70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>FA-000066</t>
+        </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -13963,7 +13896,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00067 across CSV/XLSX inputs — Pending Redeployment, Chicago. Assignment TR-00067; receive column Feb 23, 2026, approval APR-00067. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00067. Also: offboarding ticket OFF-00067 referenced.</t>
+          <t>MD-00067 (Samsung Galaxy S24) is Pending Redeployment at Chicago. Acquisition cost $1130. Transfer TR-00067 received 2026-02-23; approval APR-00067. FAR row FA-000067; net book value $764.93. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -13974,13 +13907,13 @@
       <c r="M71" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N71" s="7">
-        <f>IFERROR(XLOOKUP(A71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v>764.93</v>
-      </c>
-      <c r="O71" s="7">
-        <f>IFERROR(XLOOKUP(A71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="N71" s="7" t="n">
+        <v>764.9299999999999</v>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>FA-000067</t>
+        </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -14011,7 +13944,7 @@
         </is>
       </c>
       <c r="V71" t="n">
-        <v>764.93</v>
+        <v>764.9299999999999</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -14075,7 +14008,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>MD-00068: Cisco C9300, $6425, status Return Overdue, site Remote - Former Employee. Employment file: E0081 remains Separated. Transfer TR-00068 shows receipt 2026-04-03, approval APR-00068. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00068. Also: carrier label 1ZMD00000068 is not proof of receipt. Note — offboarding ticket OFF-00068 referenced. return still label-only per shipment file.</t>
+          <t>Offboarding return for MD-00068 lacks complete shipment proof; status remains Return Overdue. People file: E0081 (Elliott Park), status Separated. Transfer TR-00068 received 2026-04-03; approval APR-00068. Service desk ticket OFF-00068 on file. Fixed-asset extract includes FA-000068 (NBV $1436.28). PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -14086,13 +14019,13 @@
       <c r="M72" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N72" s="7">
-        <f>IFERROR(XLOOKUP(A72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N72" s="7" t="n">
         <v>1436.28</v>
       </c>
-      <c r="O72" s="7">
-        <f>IFERROR(XLOOKUP(A72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>FA-000068</t>
+        </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -14187,7 +14120,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>MD-00069 carries Return Overdue at Remote - Former Employee (Dell Latitude 7440, $2120). Employment file: E0082 remains Separated. Inbound stamp on TR-00069 is 05/04/2026, approval APR-00069. PO-2025-0012 in hardware_purchase_orders.csv; FAR silent on MD-00069. Also: carrier label 1ZMD00000069 is not proof of receipt. Note — offboarding ticket OFF-00069 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00069 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0082 (Carmen Diaz) is Separated in hr_employee_status. Transfer TR-00069 received 2026-05-04; approval APR-00069. Service desk ticket OFF-00069 on file. Ledger FA-000069 on file; NBV $142.69. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -14198,13 +14131,13 @@
       <c r="M73" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N73" s="7">
-        <f>IFERROR(XLOOKUP(A73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N73" s="7" t="n">
         <v>142.69</v>
       </c>
-      <c r="O73" s="7">
-        <f>IFERROR(XLOOKUP(A73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>FA-000069</t>
+        </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -14299,7 +14232,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 stays Return Overdue at Remote - Former Employee (Dell U2723QE, $520). HR agrees Hugh Talbot (E0083) is still Separated. Transfer TR-00070 shows receipt Jun 03, 2026, approval APR-00070. Purchasing PO-2025-0012 without a capital line for MD-00070. Also: carrier label 1ZMD00000070 is not proof of receipt. Note — offboarding ticket OFF-00070 referenced. return still label-only per shipment file.</t>
+          <t>MD-00070 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0083 / Hugh Talbot as Separated. Transfer TR-00070 received 2026-06-03; approval APR-00070. Service desk ticket OFF-00070 on file. FAR row FA-000070; net book value $342.32. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -14310,13 +14243,13 @@
       <c r="M74" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N74" s="7">
-        <f>IFERROR(XLOOKUP(A74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N74" s="7" t="n">
         <v>342.32</v>
       </c>
-      <c r="O74" s="7">
-        <f>IFERROR(XLOOKUP(A74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t>FA-000070</t>
+        </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -14411,7 +14344,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00071 is Return Overdue in Remote - Former Employee. HR agrees Mira Adelman (E0084) is still Separated. Inbound stamp on TR-00071 is 2026-07-12, approval APR-00071. Purchasing PO-2025-0012 without a capital line for MD-00071. Also: carrier label 1ZMD00000071 is not proof of receipt. Note — offboarding ticket OFF-00071 referenced. return still label-only per shipment file.</t>
+          <t>Offboarding return for MD-00071 lacks complete shipment proof; status remains Return Overdue. People file: E0084 (Mira Adelman), status Separated. Transfer TR-00071 received 2026-07-12; approval APR-00071. Service desk ticket OFF-00071 on file. Fixed-asset extract includes FA-000071 (NBV $787.96). PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -14422,13 +14355,13 @@
       <c r="M75" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N75" s="7">
-        <f>IFERROR(XLOOKUP(A75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N75" s="7" t="n">
         <v>787.96</v>
       </c>
-      <c r="O75" s="7">
-        <f>IFERROR(XLOOKUP(A75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>FA-000071</t>
+        </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
@@ -14523,7 +14456,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>MD-00072 reflects Return Overdue at Remote - Former Employee (Cisco C9300, $6290). HR agrees Quincy Rhodes (E0085) is still Separated. equipment_transfer_log TR-00072, approval APR-00072; received 01/18/2026. Purchasing PO-2025-0012 without a capital line for MD-00072. Also: carrier label 1ZMD00000072 is not proof of receipt. Note — offboarding ticket OFF-00072 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00072 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0085 (Quincy Rhodes) is Separated in hr_employee_status. Transfer TR-00072 received 2026-01-18; approval APR-00072. Service desk ticket OFF-00072 on file. Ledger FA-000072 on file; NBV $500.27. PO PO-2025-0012.</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -14534,13 +14467,13 @@
       <c r="M76" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N76" s="7">
-        <f>IFERROR(XLOOKUP(A76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N76" s="7" t="n">
         <v>500.27</v>
       </c>
-      <c r="O76" s="7">
-        <f>IFERROR(XLOOKUP(A76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t>FA-000072</t>
+        </is>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
@@ -14635,7 +14568,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>Did not move MD-00073 off Return Overdue at Remote - Former Employee without a transaction. HR agrees Sloane Richter (E0086) is still Separated. TR-00073 ties to MD-00073; dock date Jan 24, 2026, approval APR-00073. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00073. Also: carrier label 1ZMD00000073 is not proof of receipt. Note — offboarding ticket OFF-00073 referenced. return still label-only per shipment file.</t>
+          <t>MD-00073 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0086 / Sloane Richter as Separated. Transfer TR-00073 received 2026-01-24; approval APR-00073. Service desk ticket OFF-00073 on file. FAR row FA-000073; net book value $0. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -14646,13 +14579,13 @@
       <c r="M77" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N77" s="7">
-        <f>IFERROR(XLOOKUP(A77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N77" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O77" s="7">
-        <f>IFERROR(XLOOKUP(A77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>FA-000073</t>
+        </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
@@ -14747,7 +14680,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 lists Return Overdue at Carrier Network / Unverified (Dell U2723QE, $700). HR agrees Nolan Vega (E0087) is still Separated. TR-00074 for MD-00074 — received 2026-02-24, approval APR-00074. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00074. Also: carrier label 1ZMD00000074 is not proof of receipt. Note — offboarding ticket OFF-00074 referenced. return still label-only per shipment file. shipment serial MISMATCH-0074 vs register MD-MO-050074.</t>
+          <t>Offboarding return for MD-00074 lacks complete shipment proof; status remains Return Overdue. People file: E0087 (Nolan Vega), status Separated. Transfer TR-00074 received 2026-02-24; approval APR-00074. Service desk ticket OFF-00074 on file. Fixed-asset extract includes FA-000074 (NBV $359.25). PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -14758,13 +14691,13 @@
       <c r="M78" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N78" s="7">
-        <f>IFERROR(XLOOKUP(A78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N78" s="7" t="n">
         <v>359.25</v>
       </c>
-      <c r="O78" s="7">
-        <f>IFERROR(XLOOKUP(A78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t>FA-000074</t>
+        </is>
       </c>
       <c r="P78" s="7" t="inlineStr">
         <is>
@@ -14859,7 +14792,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee: MD-00075 is Return Overdue; cost $1175. HR agrees Ivy Chenoweth (E0088) is still Separated. Movement TR-00075 posted 2026-03-31 and inbound 04/01/2026, approval APR-00075. PO-2022-0013 in hardware_purchase_orders.csv; FAR silent on MD-00075. Also: carrier label 1ZMD00000075 is not proof of receipt. Note — offboarding ticket OFF-00075 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00075 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0088 (Ivy Chenoweth) is Separated in hr_employee_status. Transfer TR-00075 received 2026-04-01; approval APR-00075. Service desk ticket OFF-00075 on file. Ledger FA-000075 on file; NBV $647.42. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -14870,13 +14803,13 @@
       <c r="M79" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N79" s="7">
-        <f>IFERROR(XLOOKUP(A79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N79" s="7" t="n">
         <v>647.42</v>
       </c>
-      <c r="O79" s="7">
-        <f>IFERROR(XLOOKUP(A79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>FA-000075</t>
+        </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
@@ -14971,7 +14904,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 reads Return Overdue at Carrier Network / Unverified (Cisco C9300, $6470). HR agrees Percy Lambert (E0089) is still Separated. Inbound stamp on TR-00076 is May 03, 2026, approval APR-00076. PO PO-2022-0013 on file; no matching FAR row for MD-00076. Also: carrier label 1ZMD00000076 is not proof of receipt. Note — offboarding ticket OFF-00076 referenced. return still label-only per shipment file. shipment serial MISMATCH-0076 vs register MD-NE-050076.</t>
+          <t>MD-00076 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0089 / Percy Lambert as Separated. Transfer TR-00076 received 2026-05-03; approval APR-00076. Service desk ticket OFF-00076 on file. FAR row FA-000076; net book value $953.89. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -14982,13 +14915,13 @@
       <c r="M80" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N80" s="7">
-        <f>IFERROR(XLOOKUP(A80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N80" s="7" t="n">
         <v>953.89</v>
       </c>
-      <c r="O80" s="7">
-        <f>IFERROR(XLOOKUP(A80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t>FA-000076</t>
+        </is>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
@@ -15083,7 +15016,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>The cited records support Return Overdue in Remote - Former Employee for MD-00077. Employment file: E0090 remains Separated. equipment_transfer_log TR-00077, approval APR-00077; received 2026-06-06. PO PO-2022-0013 on file; no matching FAR row for MD-00077. Also: carrier label 1ZMD00000077 is not proof of receipt. Note — offboarding ticket OFF-00077 referenced. return still label-only per shipment file.</t>
+          <t>Offboarding return for MD-00077 lacks complete shipment proof; status remains Return Overdue. People file: E0090 (Dana Ghosh), status Separated. Transfer TR-00077 received 2026-06-06; approval APR-00077. Service desk ticket OFF-00077 on file. Fixed-asset extract includes FA-000077 (NBV $0). PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -15094,13 +15027,13 @@
       <c r="M81" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N81" s="7">
-        <f>IFERROR(XLOOKUP(A81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N81" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O81" s="7">
-        <f>IFERROR(XLOOKUP(A81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>FA-000077</t>
+        </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
@@ -15195,7 +15128,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee holds MD-00078 (Dell U2723QE) as Return Overdue. Employment file: E0091 remains Separated. TR-00078 ties to MD-00078; dock date 01/10/2026, approval APR-00078. PO PO-2022-0013 on file; no matching FAR row for MD-00078. Also: carrier label 1ZMD00000078 is not proof of receipt. Note — offboarding ticket OFF-00078 referenced. return still label-only per shipment file.</t>
+          <t>Return for MD-00078 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0091 (Harlan Smith) is Separated in hr_employee_status. Transfer TR-00078 received 2026-01-10; approval APR-00078. Service desk ticket OFF-00078 on file. Ledger FA-000078 on file; NBV $328.95. PO PO-2022-0013.</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -15206,13 +15139,13 @@
       <c r="M82" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N82" s="7">
-        <f>IFERROR(XLOOKUP(A82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N82" s="7" t="n">
         <v>328.95</v>
       </c>
-      <c r="O82" s="7">
-        <f>IFERROR(XLOOKUP(A82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
+          <t>FA-000078</t>
+        </is>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -15307,7 +15240,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>MD-00079 (Samsung Galaxy S24) closed Return Overdue / Remote - Former Employee on $1040. Employment file: E0092 remains Separated. TR-00079 for MD-00079 — received Feb 13, 2026, approval APR-00079. PO PO-2023-0014 on file; no matching FAR row for MD-00079. Also: carrier label 1ZMD00000079 is not proof of receipt. Note — offboarding ticket OFF-00079 referenced. return still label-only per shipment file.</t>
+          <t>MD-00079 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0092 / June Okoye as Separated. Transfer TR-00079 received 2026-02-13; approval APR-00079. Service desk ticket OFF-00079 on file. FAR row FA-000079; net book value $692.62. PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -15318,13 +15251,13 @@
       <c r="M83" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N83" s="7">
-        <f>IFERROR(XLOOKUP(A83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N83" s="7" t="n">
         <v>692.62</v>
       </c>
-      <c r="O83" s="7">
-        <f>IFERROR(XLOOKUP(A83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>FA-000079</t>
+        </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
@@ -15419,7 +15352,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>Atlanta Warehouse holds MD-00080 (Cisco C9300) as Available. TR-00080 ties to MD-00080; dock date 2026-03-17, approval APR-00080. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00080. Also: carrier label 1ZMD00000080 is not proof of receipt. Note — offboarding ticket OFF-00080 referenced.</t>
+          <t>MD-00080 (Cisco C9300) is Available at Atlanta Warehouse. Acquisition cost $6335. Transfer TR-00080 received 2026-03-17; approval APR-00080. Fixed-asset extract includes FA-000080 (NBV $1374.53). PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -15430,13 +15363,13 @@
       <c r="M84" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N84" s="7">
-        <f>IFERROR(XLOOKUP(A84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N84" s="7" t="n">
         <v>1374.53</v>
       </c>
-      <c r="O84" s="7">
-        <f>IFERROR(XLOOKUP(A84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>FA-000080</t>
+        </is>
       </c>
       <c r="P84" s="7" t="inlineStr">
         <is>
@@ -15531,7 +15464,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Dell Latitude 7440 on MD-00081 is Available in floor Atlanta Warehouse; basis $2030. TR-00081 for MD-00081 — received 04/20/2026, approval APR-00081. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00081. Also: carrier label 1ZMD00000081 is not proof of receipt. Note — offboarding ticket OFF-00081 referenced.</t>
+          <t>MD-00081 (Dell Latitude 7440) is Available at Atlanta Warehouse. Acquisition cost $2030. Transfer TR-00081 received 2026-04-20; approval APR-00081. Ledger FA-000081 on file; NBV $114.4. PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -15542,13 +15475,13 @@
       <c r="M85" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N85" s="7">
-        <f>IFERROR(XLOOKUP(A85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N85" s="7" t="n">
         <v>114.4</v>
       </c>
-      <c r="O85" s="7">
-        <f>IFERROR(XLOOKUP(A85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>FA-000081</t>
+        </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
@@ -15643,7 +15576,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00082 In Transit - Exception @ Carrier Network / Unverified. HR agrees Emmett Boyle (E0095) is still Separated. Movement TR-00082 posted 05/22/2026 and inbound May 24, 2026, approval APR-00082. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00082. Also: carrier label 1ZMD00000082 is not proof of receipt. Note — offboarding ticket OFF-00082 referenced. shipment serial MISMATCH-0082 vs register MD-MO-050082. receiving_exception_scan_1ZMD00000082.png treated as investigative lead only.</t>
+          <t>MD-00082 is In Transit - Exception at Carrier Network / Unverified; shipment documentation is incomplete. hr_employee_status lists E0095 / Emmett Boyle as Separated. Transfer TR-00082 received 2026-05-24; approval APR-00082. Service desk ticket OFF-00082 on file. FAR row FA-000082; net book value $485.55. PO PO-2023-0014. Tracking 1ZMD00000082 receiving scan shows MISMATCH-0082 vs MD-MO-050082.</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -15654,13 +15587,13 @@
       <c r="M86" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N86" s="7">
-        <f>IFERROR(XLOOKUP(A86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N86" s="7" t="n">
         <v>485.55</v>
       </c>
-      <c r="O86" s="7">
-        <f>IFERROR(XLOOKUP(A86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>FA-000082</t>
+        </is>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -15755,7 +15688,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 remains Available at Atlanta Warehouse (Samsung Galaxy S24, $1220). Log TR-00083: received 2026-06-27, approval APR-00083. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00083. Also: carrier label 1ZMD00000083 is not proof of receipt. Note — offboarding ticket OFF-00083 referenced.</t>
+          <t>MD-00083 (Samsung Galaxy S24) is Available at Atlanta Warehouse. Acquisition cost $1220. Transfer TR-00083 received 2026-06-27; approval APR-00083. Fixed-asset extract includes FA-000083 (NBV $952.79). PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -15766,13 +15699,13 @@
       <c r="M87" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N87" s="7">
-        <f>IFERROR(XLOOKUP(A87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N87" s="7" t="n">
         <v>952.79</v>
       </c>
-      <c r="O87" s="7">
-        <f>IFERROR(XLOOKUP(A87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>FA-000083</t>
+        </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -15867,7 +15800,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Carrier Network / Unverified: MD-00084 is In Transit - Exception; cost $6200. Anita Bose has Separated status in the people extract. Assignment TR-00084; receive column 02/05/2026, approval APR-00084. PO-2023-0014 in hardware_purchase_orders.csv; FAR silent on MD-00084. Also: carrier label 1ZMD00000084 is not proof of receipt. Note — offboarding ticket OFF-00084 referenced. shipment serial MISMATCH-0084 vs register MD-NE-050084.</t>
+          <t>MD-00084 is In Transit - Exception at Carrier Network / Unverified; shipment documentation is incomplete. Custodian E0072 (Anita Bose) is Separated in hr_employee_status. Transfer TR-00084 received 2026-02-05; approval APR-00084. Service desk ticket OFF-00084 on file. Ledger FA-000084 on file; NBV $533.85. PO PO-2023-0014.</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -15878,13 +15811,13 @@
       <c r="M88" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N88" s="7">
-        <f>IFERROR(XLOOKUP(A88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N88" s="7" t="n">
         <v>533.85</v>
       </c>
-      <c r="O88" s="7">
-        <f>IFERROR(XLOOKUP(A88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t>FA-000084</t>
+        </is>
       </c>
       <c r="P88" s="7" t="inlineStr">
         <is>
@@ -15979,7 +15912,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 still Available; Atlanta Warehouse is the verified site. Transfer TR-00085 shows receipt Feb 03, 2026, approval APR-00085. PO-2024-0015 in hardware_purchase_orders.csv; FAR silent on MD-00085. Also: carrier label 1ZMD00000085 is not proof of receipt. Note — offboarding ticket OFF-00085 referenced.</t>
+          <t>MD-00085 (Lenovo ThinkPad T14) is Available at Atlanta Warehouse. Acquisition cost $1895. Transfer TR-00085 received 2026-02-03; approval APR-00085. FAR row FA-000085; net book value $0. PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -15990,13 +15923,13 @@
       <c r="M89" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N89" s="7">
-        <f>IFERROR(XLOOKUP(A89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N89" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="7">
-        <f>IFERROR(XLOOKUP(A89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t>FA-000085</t>
+        </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -16091,7 +16024,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00086 is Available in Atlanta Warehouse office; basis $610. TR-00086 for MD-00086 — received 2026-03-08, approval APR-00086. PO PO-2024-0015 on file; no matching FAR row for MD-00086. Also: carrier label 1ZMD00000086 is not proof of receipt. Note — offboarding ticket OFF-00086 referenced.</t>
+          <t>MD-00086 (Dell U2723QE) is Available at Atlanta Warehouse. Acquisition cost $610. Transfer TR-00086 received 2026-03-08; approval APR-00086. Fixed-asset extract includes FA-000086 (NBV $317.07). PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -16102,13 +16035,13 @@
       <c r="M90" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N90" s="7">
-        <f>IFERROR(XLOOKUP(A90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N90" s="7" t="n">
         <v>317.07</v>
       </c>
-      <c r="O90" s="7">
-        <f>IFERROR(XLOOKUP(A90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>FA-000086</t>
+        </is>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -16203,7 +16136,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Working conclusion for MD-00087: Available in Atlanta Warehouse ($1085). Movement TR-00087 posted 2026-04-12 and inbound 04/12/2026, approval APR-00087. PO PO-2024-0015 on file; no matching FAR row for MD-00087. Also: carrier label 1ZMD00000087 is not proof of receipt. Note — offboarding ticket OFF-00087 referenced.</t>
+          <t>MD-00087 (Samsung Galaxy S24) is Available at Atlanta Warehouse. Acquisition cost $1085. Transfer TR-00087 received 2026-04-12; approval APR-00087. Ledger FA-000087 on file; NBV $609.71. PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -16214,13 +16147,13 @@
       <c r="M91" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N91" s="7">
-        <f>IFERROR(XLOOKUP(A91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N91" s="7" t="n">
         <v>609.71</v>
       </c>
-      <c r="O91" s="7">
-        <f>IFERROR(XLOOKUP(A91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>FA-000087</t>
+        </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -16315,7 +16248,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>MD-00088 stays Available at Atlanta Warehouse (Cisco C9300, $6380). Log TR-00088: received May 14, 2026, approval APR-00088. PO PO-2024-0015 on file; no matching FAR row for MD-00088. Also: carrier label 1ZMD00000088 is not proof of receipt. Note — offboarding ticket OFF-00088 referenced. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>MD-00088 (Cisco C9300) is Available at Atlanta Warehouse. Acquisition cost $6380. Transfer TR-00088 received 2026-05-14; approval APR-00088. FAR row FA-000088; net book value $982.55. PO PO-2024-0015. Duplicate serial MD-NE-050088 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -16326,13 +16259,13 @@
       <c r="M92" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N92" s="7">
-        <f>IFERROR(XLOOKUP(A92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N92" s="7" t="n">
         <v>982.55</v>
       </c>
-      <c r="O92" s="7">
-        <f>IFERROR(XLOOKUP(A92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
+          <t>FA-000088</t>
+        </is>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -16427,7 +16360,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00089: Missing, Unknown, $2075 — MacBook Pro 14. Jonah Freedman has Separated status in the people extract. Assignment TR-00089; receive column 2026-06-17, approval APR-00089. PO PO-2024-0015 on file; no matching FAR row for MD-00089. Also: offboarding ticket OFF-00089 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Cannot confirm custody of MD-00089 at this time; register last pointed to Unknown. People file: E0077 (Jonah Freedman), status Separated. Transfer TR-00089 received 2026-06-17; approval APR-00089. Service desk ticket OFF-00089 on file. Fixed-asset extract includes FA-000089 (NBV $0). PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -16438,13 +16371,13 @@
       <c r="M93" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N93" s="7">
-        <f>IFERROR(XLOOKUP(A93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N93" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="7">
-        <f>IFERROR(XLOOKUP(A93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>FA-000089</t>
+        </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -16539,7 +16472,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>I read the movement and people files before calling MD-00090 Missing. People side — Regina Lowe (E0078), Separated. Log TR-00090: received 01/28/2026, approval APR-00090. PO-2024-0015 in hardware_purchase_orders.csv; FAR silent on MD-00090. Also: offboarding ticket OFF-00090 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>No confirmed location for MD-00090 (Dell U2723QE); last recorded site was Unknown. Custodian E0078 (Regina Lowe) is Separated in hr_employee_status. Transfer TR-00090 received 2026-01-28; approval APR-00090. Service desk ticket OFF-00090 on file. Ledger FA-000090 on file; NBV $465.13. PO PO-2024-0015.</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -16550,13 +16483,13 @@
       <c r="M94" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N94" s="7">
-        <f>IFERROR(XLOOKUP(A94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N94" s="7" t="n">
         <v>465.13</v>
       </c>
-      <c r="O94" s="7">
-        <f>IFERROR(XLOOKUP(A94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>FA-000090</t>
+        </is>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
@@ -16651,7 +16584,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Unknown: MD-00091 is Missing; cost $950. People side — Wes Carvalho (E0079), Separated. Assignment TR-00091; receive column Feb 24, 2026, approval APR-00091. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00091. Also: offboarding ticket OFF-00091 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>MD-00091 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0079 / Wes Carvalho as Separated. Transfer TR-00091 received 2026-02-24; approval APR-00091. Service desk ticket OFF-00091 on file. FAR row FA-000091; net book value $643.09. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -16662,13 +16595,13 @@
       <c r="M95" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N95" s="7">
-        <f>IFERROR(XLOOKUP(A95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N95" s="7" t="n">
         <v>643.09</v>
       </c>
-      <c r="O95" s="7">
-        <f>IFERROR(XLOOKUP(A95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>FA-000091</t>
+        </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
@@ -16763,7 +16696,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>After HR and transfer review, MD-00092 is Missing in Unknown. Tara Singh has Separated status in the people extract. Transfer TR-00092 shows receipt 2026-03-28, approval APR-00092. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00092. Also: offboarding ticket OFF-00092 referenced. Note — last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register.</t>
+          <t>Cannot confirm custody of MD-00092 at this time; register last pointed to Unknown. People file: E0080 (Tara Singh), status Separated. Transfer TR-00092 received 2026-03-28; approval APR-00092. Service desk ticket OFF-00092 on file. Fixed-asset extract includes FA-000092 (NBV $1396.04). PO PO-2025-0016. Duplicate serial MD-NE-050088 shared with the paired asset.</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -16774,13 +16707,13 @@
       <c r="M96" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N96" s="7">
-        <f>IFERROR(XLOOKUP(A96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N96" s="7" t="n">
         <v>1396.04</v>
       </c>
-      <c r="O96" s="7">
-        <f>IFERROR(XLOOKUP(A96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>FA-000092</t>
+        </is>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
@@ -16875,7 +16808,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00093 Missing @ Unknown. Elliott Park has Separated status in the people extract. Inbound stamp on TR-00093 is 05/06/2026, approval APR-00093. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00093. Also: offboarding ticket OFF-00093 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>No confirmed location for MD-00093 (Dell Latitude 7440); last recorded site was Unknown. Custodian E0081 (Elliott Park) is Separated in hr_employee_status. Transfer TR-00093 received 2026-05-06; approval APR-00093. Service desk ticket OFF-00093 on file. Ledger FA-000093 on file; NBV $130.57. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -16886,13 +16819,13 @@
       <c r="M97" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N97" s="7">
-        <f>IFERROR(XLOOKUP(A97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N97" s="7" t="n">
         <v>130.57</v>
       </c>
-      <c r="O97" s="7">
-        <f>IFERROR(XLOOKUP(A97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>FA-000093</t>
+        </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -16987,7 +16920,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE MD-00094 tied to $655; location Unknown; status Missing. Carmen Diaz has Separated status in the people extract. equipment_transfer_log TR-00094, approval APR-00094; received Jun 04, 2026. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00094. Also: offboarding ticket OFF-00094 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>MD-00094 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0082 / Carmen Diaz as Separated. Transfer TR-00094 received 2026-06-04; approval APR-00094. Service desk ticket OFF-00094 on file. FAR row FA-000094; net book value $431.2. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -16998,13 +16931,13 @@
       <c r="M98" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N98" s="7">
-        <f>IFERROR(XLOOKUP(A98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N98" s="7" t="n">
         <v>431.2</v>
       </c>
-      <c r="O98" s="7">
-        <f>IFERROR(XLOOKUP(A98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>FA-000094</t>
+        </is>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -17099,7 +17032,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Cost $1130 on MD-00095; Missing at Unknown. Hugh Talbot has Separated status in the people extract. TR-00095 ties to MD-00095; dock date 2026-07-08, approval APR-00095. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00095. Also: offboarding ticket OFF-00095 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>Cannot confirm custody of MD-00095 at this time; register last pointed to Unknown. People file: E0083 (Hugh Talbot), status Separated. Transfer TR-00095 received 2026-07-08; approval APR-00095. Service desk ticket OFF-00095 on file. Fixed-asset extract includes FA-000095 (NBV $894.87). PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -17110,13 +17043,13 @@
       <c r="M99" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N99" s="7">
-        <f>IFERROR(XLOOKUP(A99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N99" s="7" t="n">
         <v>894.87</v>
       </c>
-      <c r="O99" s="7">
-        <f>IFERROR(XLOOKUP(A99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>FA-000095</t>
+        </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -17211,7 +17144,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>MD-00096 stays Missing at Unknown (Cisco C9300, $6425). Mira Adelman has Separated status in the people extract. Log TR-00096: received 01/19/2026, approval APR-00096. PO-2025-0016 in hardware_purchase_orders.csv; FAR silent on MD-00096. Also: offboarding ticket OFF-00096 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>No confirmed location for MD-00096 (Cisco C9300); last recorded site was Unknown. Custodian E0084 (Mira Adelman) is Separated in hr_employee_status. Transfer TR-00096 received 2026-01-19; approval APR-00096. Service desk ticket OFF-00096 on file. Ledger FA-000096 on file; NBV $511.01. PO PO-2025-0016.</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -17222,13 +17155,13 @@
       <c r="M100" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N100" s="7">
-        <f>IFERROR(XLOOKUP(A100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N100" s="7" t="n">
         <v>511.01</v>
       </c>
-      <c r="O100" s="7">
-        <f>IFERROR(XLOOKUP(A100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>FA-000096</t>
+        </is>
       </c>
       <c r="P100" s="7" t="inlineStr">
         <is>
@@ -17323,7 +17256,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 stays Missing at Unknown (Lenovo ThinkPad T14, $2120). Quincy Rhodes has Separated status in the people extract. TR-00097 ties to MD-00097; dock date Jan 27, 2026, approval APR-00097. Purchasing PO-2022-0017 without a capital line for MD-00097. Also: offboarding ticket OFF-00097 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>MD-00097 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0085 / Quincy Rhodes as Separated. Transfer TR-00097 received 2026-01-27; approval APR-00097. Service desk ticket OFF-00097 on file. FAR row FA-000097; net book value $0. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -17334,13 +17267,13 @@
       <c r="M101" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N101" s="7">
-        <f>IFERROR(XLOOKUP(A101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N101" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O101" s="7">
-        <f>IFERROR(XLOOKUP(A101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>FA-000097</t>
+        </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
@@ -17435,7 +17368,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>MD-00098 stays Missing at Unknown (Dell U2723QE, $520). Sloane Richter has Separated status in the people extract. Transfer TR-00098 shows receipt 2026-02-24, approval APR-00098. Purchasing PO-2022-0017 without a capital line for MD-00098. Also: offboarding ticket OFF-00098 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>Cannot confirm custody of MD-00098 at this time; register last pointed to Unknown. People file: E0086 (Sloane Richter), status Separated. Transfer TR-00098 received 2026-02-24; approval APR-00098. Service desk ticket OFF-00098 on file. Fixed-asset extract includes FA-000098 (NBV $266.87). PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -17446,13 +17379,13 @@
       <c r="M102" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N102" s="7">
-        <f>IFERROR(XLOOKUP(A102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N102" s="7" t="n">
         <v>266.87</v>
       </c>
-      <c r="O102" s="7">
-        <f>IFERROR(XLOOKUP(A102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>FA-000098</t>
+        </is>
       </c>
       <c r="P102" s="7" t="inlineStr">
         <is>
@@ -17547,7 +17480,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>MD-00099 stays Missing at Unknown (Samsung Galaxy S24, $995). Nolan Vega has Separated status in the people extract. Movement TR-00099 posted 2026-03-31 and inbound 04/02/2026, approval APR-00099. Purchasing PO-2022-0017 without a capital line for MD-00099. Also: offboarding ticket OFF-00099 referenced. Note — last operational site on register was Denver - Closed.</t>
+          <t>No confirmed location for MD-00099 (Samsung Galaxy S24); last recorded site was Unknown. Custodian E0087 (Nolan Vega) is Separated in hr_employee_status. Transfer TR-00099 received 2026-04-02; approval APR-00099. Service desk ticket OFF-00099 on file. Ledger FA-000099 on file; NBV $548.24. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -17558,13 +17491,13 @@
       <c r="M103" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N103" s="7">
-        <f>IFERROR(XLOOKUP(A103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N103" s="7" t="n">
         <v>548.24</v>
       </c>
-      <c r="O103" s="7">
-        <f>IFERROR(XLOOKUP(A103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>FA-000099</t>
+        </is>
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
@@ -17659,7 +17592,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Field review: MD-00100 Missing @ Unknown. Ivy Chenoweth has Separated status in the people extract. equipment_transfer_log TR-00100, approval APR-00100; received May 05, 2026. Purchasing PO-2022-0017 without a capital line for MD-00100. Also: offboarding ticket OFF-00100 referenced. Note — last operational site on register was Chicago - Closed.</t>
+          <t>MD-00100 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0088 / Ivy Chenoweth as Separated. Transfer TR-00100 received 2026-05-05; approval APR-00100. Service desk ticket OFF-00100 on file. FAR row FA-000100; net book value $927.36. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -17670,13 +17603,13 @@
       <c r="M104" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N104" s="7">
-        <f>IFERROR(XLOOKUP(A104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N104" s="7" t="n">
         <v>927.36</v>
       </c>
-      <c r="O104" s="7">
-        <f>IFERROR(XLOOKUP(A104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>FA-000100</t>
+        </is>
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
@@ -17771,7 +17704,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 stays Retired/Pending Disposal at Seattle (MacBook Pro 14, $1985). Assignment TR-00101; receive column 2026-06-07, approval APR-00101. Purchasing PO-2022-0017 without a capital line for MD-00101. Also: offboarding ticket RET-00101 referenced.</t>
+          <t>MD-00101 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00101 received 2026-06-07; approval APR-00101. Service desk ticket RET-00101 on file. Fixed-asset extract includes FA-000101 (NBV $0). PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -17782,13 +17715,13 @@
       <c r="M105" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N105" s="7">
-        <f>IFERROR(XLOOKUP(A105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N105" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O105" s="7">
-        <f>IFERROR(XLOOKUP(A105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>FA-000101</t>
+        </is>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -17883,7 +17816,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 stays Retired/Pending Disposal at Atlanta (Dell U2723QE, $700). TR-00102 for MD-00102 — received 01/11/2026, approval APR-00102. Purchasing PO-2022-0017 without a capital line for MD-00102. Also: offboarding ticket RET-00102 referenced.</t>
+          <t>MD-00102 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00102 received 2026-01-11; approval APR-00102. Service desk ticket RET-00102 on file. Ledger FA-000102 on file; NBV $407.54. PO PO-2022-0017.</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -17894,13 +17827,13 @@
       <c r="M106" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N106" s="7">
-        <f>IFERROR(XLOOKUP(A106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N106" s="7" t="n">
         <v>407.54</v>
       </c>
-      <c r="O106" s="7">
-        <f>IFERROR(XLOOKUP(A106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>FA-000102</t>
+        </is>
       </c>
       <c r="P106" s="7" t="inlineStr">
         <is>
@@ -17995,7 +17928,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>MD-00103 stays Retired/Pending Disposal at Chicago (Samsung Galaxy S24, $1175). Inbound stamp on TR-00103 is Feb 14, 2026, approval APR-00103. Purchasing PO-2023-0018 without a capital line for MD-00103. Also: offboarding ticket RET-00103 referenced.</t>
+          <t>MD-00103 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00103 received 2026-02-14; approval APR-00103. Service desk ticket RET-00103 on file. FAR row FA-000103; net book value $782.53. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -18006,13 +17939,13 @@
       <c r="M107" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N107" s="7">
-        <f>IFERROR(XLOOKUP(A107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N107" s="7" t="n">
         <v>782.53</v>
       </c>
-      <c r="O107" s="7">
-        <f>IFERROR(XLOOKUP(A107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>FA-000103</t>
+        </is>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
@@ -18107,7 +18040,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>MD-00104 stays Retired/Pending Disposal at Dallas (Cisco C9300, $6470). Log TR-00104: received 2026-03-18, approval APR-00104. Purchasing PO-2023-0018 without a capital line for MD-00104. Also: offboarding ticket RET-00104 referenced.</t>
+          <t>MD-00104 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00104 received 2026-03-18; approval APR-00104. Service desk ticket RET-00104 on file. Fixed-asset extract includes FA-000104 (NBV $1403.83). PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -18118,13 +18051,13 @@
       <c r="M108" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N108" s="7">
-        <f>IFERROR(XLOOKUP(A108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N108" s="7" t="n">
         <v>1403.83</v>
       </c>
-      <c r="O108" s="7">
-        <f>IFERROR(XLOOKUP(A108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>FA-000104</t>
+        </is>
       </c>
       <c r="P108" s="7" t="inlineStr">
         <is>
@@ -18219,7 +18152,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 stays Retired/Pending Disposal at Denver (Dell Latitude 7440, $1850). TR-00105 ties to MD-00105; dock date 04/21/2026, approval APR-00105. Purchasing PO-2023-0018 without a capital line for MD-00105. Also: offboarding ticket RET-00105 referenced.</t>
+          <t>MD-00105 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00105 received 2026-04-21; approval APR-00105. Service desk ticket RET-00105 on file. Ledger FA-000105 on file; NBV $104.26. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -18230,13 +18163,13 @@
       <c r="M109" s="7" t="n">
         <v>1850</v>
       </c>
-      <c r="N109" s="7">
-        <f>IFERROR(XLOOKUP(A109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N109" s="7" t="n">
         <v>104.26</v>
       </c>
-      <c r="O109" s="7">
-        <f>IFERROR(XLOOKUP(A109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>FA-000105</t>
+        </is>
       </c>
       <c r="P109" s="7" t="inlineStr">
         <is>
@@ -18331,7 +18264,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>MD-00106 reads Retired/Pending Disposal at New York (Dell U2723QE, $565). TR-00106 ties to MD-00106; dock date May 25, 2026, approval APR-00106. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00106. Also: offboarding ticket RET-00106 referenced.</t>
+          <t>MD-00106 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00106 received 2026-05-25; approval APR-00106. Service desk ticket RET-00106 on file. FAR row FA-000106; net book value $368.24. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -18342,13 +18275,13 @@
       <c r="M110" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="N110" s="7">
-        <f>IFERROR(XLOOKUP(A110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N110" s="7" t="n">
         <v>368.24</v>
       </c>
-      <c r="O110" s="7">
-        <f>IFERROR(XLOOKUP(A110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O110" s="7" t="inlineStr">
+        <is>
+          <t>FA-000106</t>
+        </is>
       </c>
       <c r="P110" s="7" t="inlineStr">
         <is>
@@ -18443,7 +18376,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>MD-00107 reads Retired/Pending Disposal at Seattle (Samsung Galaxy S24, $1040). Transfer TR-00107 shows receipt 2026-06-27, approval APR-00107. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00107. Also: offboarding ticket RET-00107 referenced.</t>
+          <t>MD-00107 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00107 received 2026-06-27; approval APR-00107. Service desk ticket RET-00107 on file. Fixed-asset extract includes FA-000107 (NBV $812.21). PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -18454,13 +18387,13 @@
       <c r="M111" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="N111" s="7">
-        <f>IFERROR(XLOOKUP(A111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N111" s="7" t="n">
         <v>812.21</v>
       </c>
-      <c r="O111" s="7">
-        <f>IFERROR(XLOOKUP(A111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t>FA-000107</t>
+        </is>
       </c>
       <c r="P111" s="7" t="inlineStr">
         <is>
@@ -18555,7 +18488,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 reads Retired/Pending Disposal at Atlanta (Cisco C9300, $6335). Movement TR-00108 posted 2026-01-30 and inbound 01/30/2026, approval APR-00108. PO-2023-0018 in hardware_purchase_orders.csv; FAR silent on MD-00108. Also: offboarding ticket RET-00108 referenced.</t>
+          <t>MD-00108 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00108 received 2026-01-30; approval APR-00108. Service desk ticket RET-00108 on file. Ledger FA-000108 on file; NBV $545.48. PO PO-2023-0018.</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -18566,13 +18499,13 @@
       <c r="M112" s="7" t="n">
         <v>6335</v>
       </c>
-      <c r="N112" s="7">
-        <f>IFERROR(XLOOKUP(A112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N112" s="7" t="n">
         <v>545.48</v>
       </c>
-      <c r="O112" s="7">
-        <f>IFERROR(XLOOKUP(A112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O112" s="7" t="inlineStr">
+        <is>
+          <t>FA-000108</t>
+        </is>
       </c>
       <c r="P112" s="7" t="inlineStr">
         <is>
@@ -18667,7 +18600,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 reads Retired/Pending Disposal at Chicago (Lenovo ThinkPad T14, $2030). equipment_transfer_log TR-00109, approval APR-00109; received Feb 04, 2026. PO-2024-0019 in hardware_purchase_orders.csv; FAR silent on MD-00109. Also: offboarding ticket RET-00109 referenced.</t>
+          <t>MD-00109 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00109 received 2026-02-04; approval APR-00109. Service desk ticket RET-00109 on file. FAR row FA-000109; net book value $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -18678,13 +18611,13 @@
       <c r="M113" s="7" t="n">
         <v>2030</v>
       </c>
-      <c r="N113" s="7">
-        <f>IFERROR(XLOOKUP(A113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N113" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O113" s="7">
-        <f>IFERROR(XLOOKUP(A113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>FA-000109</t>
+        </is>
       </c>
       <c r="P113" s="7" t="inlineStr">
         <is>
@@ -18779,7 +18712,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>MD-00110 stays Retired/Pending Disposal at Dallas (Dell U2723QE, $745). Inbound stamp on TR-00110 is 2026-03-08, approval APR-00110. Purchasing PO-2024-0019 without a capital line for MD-00110. Also: offboarding ticket RET-00110 referenced.</t>
+          <t>MD-00110 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00110 received 2026-03-08; approval APR-00110. Service desk ticket RET-00110 on file. Fixed-asset extract includes FA-000110 (NBV $387.24). PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -18790,13 +18723,13 @@
       <c r="M114" s="7" t="n">
         <v>745</v>
       </c>
-      <c r="N114" s="7">
-        <f>IFERROR(XLOOKUP(A114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N114" s="7" t="n">
         <v>387.24</v>
       </c>
-      <c r="O114" s="7">
-        <f>IFERROR(XLOOKUP(A114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>FA-000110</t>
+        </is>
       </c>
       <c r="P114" s="7" t="inlineStr">
         <is>
@@ -18891,7 +18824,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00111 as Disposed in Disposed. Log TR-00111: received 04/13/2026, approval APR-00111. Purchasing PO-2024-0019 without a capital line for MD-00111. Also: offboarding ticket RET-00111 referenced.</t>
+          <t>MD-00111 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00111 received 2026-04-13; approval APR-00111. Ledger FA-000111 on file; NBV $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -18902,13 +18835,13 @@
       <c r="M115" s="7" t="n">
         <v>1220</v>
       </c>
-      <c r="N115" s="7">
-        <f>IFERROR(XLOOKUP(A115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N115" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="7">
-        <f>IFERROR(XLOOKUP(A115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>FA-000111</t>
+        </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
         <is>
@@ -18999,7 +18932,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00112 as Disposed in Disposed. TR-00112 ties to MD-00112; dock date May 15, 2026, approval APR-00112. Purchasing PO-2024-0019 without a capital line for MD-00112. Also: offboarding ticket RET-00112 referenced.</t>
+          <t>MD-00112 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00112 received 2026-05-15; approval APR-00112. FAR row FA-000112; net book value $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19010,13 +18943,13 @@
       <c r="M116" s="7" t="n">
         <v>6200</v>
       </c>
-      <c r="N116" s="7">
-        <f>IFERROR(XLOOKUP(A116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N116" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O116" s="7">
-        <f>IFERROR(XLOOKUP(A116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>FA-000112</t>
+        </is>
       </c>
       <c r="P116" s="7" t="inlineStr">
         <is>
@@ -19107,7 +19040,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00113 as Disposed in Disposed. Transfer TR-00113 shows receipt 2026-06-18, approval APR-00113. Purchasing PO-2024-0019 without a capital line for MD-00113. Also: offboarding ticket RET-00113 referenced.</t>
+          <t>MD-00113 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00113 received 2026-06-18; approval APR-00113. Fixed-asset extract includes FA-000113 (NBV $0). PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19118,13 +19051,13 @@
       <c r="M117" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="N117" s="7">
-        <f>IFERROR(XLOOKUP(A117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N117" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="7">
-        <f>IFERROR(XLOOKUP(A117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t>FA-000113</t>
+        </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
         <is>
@@ -19215,7 +19148,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>MD-00114 stays Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $610). Movement TR-00114 posted 2026-01-22 and inbound 01/22/2026, approval APR-00114. Purchasing PO-2024-0019 without a capital line for MD-00114. Also: offboarding ticket RET-00114 referenced. Note — no verified disposal certificate located.</t>
+          <t>MD-00114 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00114 received 2026-01-22; approval APR-00114. Service desk ticket RET-00114 on file. Ledger FA-000114 on file; NBV $0. PO PO-2024-0019.</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19226,13 +19159,13 @@
       <c r="M118" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="N118" s="7">
-        <f>IFERROR(XLOOKUP(A118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N118" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O118" s="7">
-        <f>IFERROR(XLOOKUP(A118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>FA-000114</t>
+        </is>
       </c>
       <c r="P118" s="7" t="inlineStr">
         <is>
@@ -19327,7 +19260,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00115 as Disposed in Disposed. equipment_transfer_log TR-00115, approval APR-00115; received Feb 25, 2026. PO PO-2025-0020 on file; no matching FAR row for MD-00115. Also: offboarding ticket RET-00115 referenced.</t>
+          <t>MD-00115 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00115 received 2026-02-25; approval APR-00115. FAR row FA-000115; net book value $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19338,13 +19271,13 @@
       <c r="M119" s="7" t="n">
         <v>1085</v>
       </c>
-      <c r="N119" s="7">
-        <f>IFERROR(XLOOKUP(A119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N119" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="7">
-        <f>IFERROR(XLOOKUP(A119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>FA-000115</t>
+        </is>
       </c>
       <c r="P119" s="7" t="inlineStr">
         <is>
@@ -19435,7 +19368,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00116 across CSV/XLSX inputs — Disposed, Disposed. equipment_transfer_log TR-00116, approval APR-00116; received 2026-03-29. Purchasing PO-2025-0020 without a capital line for MD-00116. Also: offboarding ticket RET-00116 referenced.</t>
+          <t>MD-00116 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00116 received 2026-03-29; approval APR-00116. Fixed-asset extract includes FA-000116 (NBV $0). PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19446,13 +19379,13 @@
       <c r="M120" s="7" t="n">
         <v>6380</v>
       </c>
-      <c r="N120" s="7">
-        <f>IFERROR(XLOOKUP(A120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N120" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O120" s="7">
-        <f>IFERROR(XLOOKUP(A120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>FA-000116</t>
+        </is>
       </c>
       <c r="P120" s="7" t="inlineStr">
         <is>
@@ -19543,7 +19476,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00117 across CSV/XLSX inputs — Disposed, Disposed. Assignment TR-00117; receive column 05/02/2026, approval APR-00117. Purchasing PO-2025-0020 without a capital line for MD-00117. Also: offboarding ticket RET-00117 referenced.</t>
+          <t>MD-00117 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00117 received 2026-05-02; approval APR-00117. Ledger FA-000117 on file; NBV $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19554,13 +19487,13 @@
       <c r="M121" s="7" t="n">
         <v>2075</v>
       </c>
-      <c r="N121" s="7">
-        <f>IFERROR(XLOOKUP(A121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N121" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O121" s="7">
-        <f>IFERROR(XLOOKUP(A121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>FA-000117</t>
+        </is>
       </c>
       <c r="P121" s="7" t="inlineStr">
         <is>
@@ -19651,7 +19584,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 reads Retired/Pending Disposal at Disposed (certificate missing) (Dell U2723QE, $790). TR-00118 for MD-00118 — received Jun 04, 2026, approval APR-00118. Purchasing PO-2025-0020 without a capital line for MD-00118. Also: offboarding ticket RET-00118 referenced. Note — no verified disposal certificate located.</t>
+          <t>MD-00118 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00118 received 2026-06-04; approval APR-00118. Service desk ticket RET-00118 on file. FAR row FA-000118; net book value $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19662,13 +19595,13 @@
       <c r="M122" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N122" s="7">
-        <f>IFERROR(XLOOKUP(A122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N122" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O122" s="7">
-        <f>IFERROR(XLOOKUP(A122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>FA-000118</t>
+        </is>
       </c>
       <c r="P122" s="7" t="inlineStr">
         <is>
@@ -19763,7 +19696,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>Looked up MD-00119 across CSV/XLSX inputs — Disposed, Disposed. Inbound stamp on TR-00119 is 2026-07-09, approval APR-00119. Purchasing PO-2025-0020 without a capital line for MD-00119. Also: offboarding ticket RET-00119 referenced.</t>
+          <t>MD-00119 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00119 received 2026-07-09; approval APR-00119. Fixed-asset extract includes FA-000119 (NBV $0). PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -19774,13 +19707,13 @@
       <c r="M123" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="N123" s="7">
-        <f>IFERROR(XLOOKUP(A123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N123" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O123" s="7">
-        <f>IFERROR(XLOOKUP(A123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>FA-000119</t>
+        </is>
       </c>
       <c r="P123" s="7" t="inlineStr">
         <is>
@@ -19875,7 +19808,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>Corrected register carries MD-00120 as Disposed in Disposed. Transfer TR-00120 shows receipt 01/20/2026, approval APR-00120. PO PO-2025-0020 on file; no matching FAR row for MD-00120. Also: offboarding ticket RET-00120 referenced.</t>
+          <t>MD-00120 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00120 received 2026-01-20; approval APR-00120. Ledger FA-000120 on file; NBV $0. PO PO-2025-0020.</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -19886,13 +19819,13 @@
       <c r="M124" s="7" t="n">
         <v>6245</v>
       </c>
-      <c r="N124" s="7">
-        <f>IFERROR(XLOOKUP(A124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N124" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O124" s="7">
-        <f>IFERROR(XLOOKUP(A124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O124" s="7" t="inlineStr">
+        <is>
+          <t>FA-000120</t>
+        </is>
       </c>
       <c r="P124" s="7" t="inlineStr">
         <is>
@@ -19979,7 +19912,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>MD-00121 reads Available at Chicago (Lenovo ThinkPad T14, $1940). Movement TR-00121 posted 01/21/2026 and inbound Jan 21, 2026, approval APR-00121. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00121.</t>
+          <t>MD-00121 (Lenovo ThinkPad T14) is Available at Chicago. Acquisition cost $1940. Transfer TR-00121 received 2026-01-21; approval APR-00121. FAR row FA-000121; net book value $0. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -19990,13 +19923,13 @@
       <c r="M125" s="7" t="n">
         <v>1940</v>
       </c>
-      <c r="N125" s="7">
-        <f>IFERROR(XLOOKUP(A125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N125" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="7">
-        <f>IFERROR(XLOOKUP(A125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t>FA-000121</t>
+        </is>
       </c>
       <c r="P125" s="7" t="inlineStr">
         <is>
@@ -20087,7 +20020,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>MD-00122 reads Available at Dallas (Dell U2723QE, $655). equipment_transfer_log TR-00122, approval APR-00122; received 2026-02-25. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00122.</t>
+          <t>MD-00122 (Dell U2723QE) is Available at Dallas. Acquisition cost $655. Transfer TR-00122 received 2026-02-25; approval APR-00122. Fixed-asset extract includes FA-000122 (NBV $336.15). PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20098,13 +20031,13 @@
       <c r="M126" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="N126" s="7">
-        <f>IFERROR(XLOOKUP(A126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N126" s="7" t="n">
         <v>336.15</v>
       </c>
-      <c r="O126" s="7">
-        <f>IFERROR(XLOOKUP(A126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
+          <t>FA-000122</t>
+        </is>
       </c>
       <c r="P126" s="7" t="inlineStr">
         <is>
@@ -20195,7 +20128,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>MD-00123 reads Available at Denver (Samsung Galaxy S24, $1130). Assignment TR-00123; receive column 04/03/2026, approval APR-00123. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00123.</t>
+          <t>MD-00123 (Samsung Galaxy S24) is Available at Denver. Acquisition cost $1130. Transfer TR-00123 received 2026-04-03; approval APR-00123. Ledger FA-000123 on file; NBV $622.62. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20206,13 +20139,13 @@
       <c r="M127" s="7" t="n">
         <v>1130</v>
       </c>
-      <c r="N127" s="7">
-        <f>IFERROR(XLOOKUP(A127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N127" s="7" t="n">
         <v>622.62</v>
       </c>
-      <c r="O127" s="7">
-        <f>IFERROR(XLOOKUP(A127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t>FA-000123</t>
+        </is>
       </c>
       <c r="P127" s="7" t="inlineStr">
         <is>
@@ -20303,7 +20236,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>MD-00124 reads Available at New York (Cisco C9300, $6425). TR-00124 for MD-00124 — received May 01, 2026, approval APR-00124. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00124.</t>
+          <t>MD-00124 (Cisco C9300) is Available at New York. Acquisition cost $6425. Transfer TR-00124 received 2026-05-01; approval APR-00124. FAR row FA-000124; net book value $947.26. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20314,13 +20247,13 @@
       <c r="M128" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="N128" s="7">
-        <f>IFERROR(XLOOKUP(A128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N128" s="7" t="n">
         <v>947.26</v>
       </c>
-      <c r="O128" s="7">
-        <f>IFERROR(XLOOKUP(A128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t>FA-000124</t>
+        </is>
       </c>
       <c r="P128" s="7" t="inlineStr">
         <is>
@@ -20411,7 +20344,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>MD-00125 reads Available at Seattle (MacBook Pro 14, $2120). Inbound stamp on TR-00125 is 2026-06-08, approval APR-00125. PO-2022-0021 in hardware_purchase_orders.csv; FAR silent on MD-00125.</t>
+          <t>MD-00125 (MacBook Pro 14) is Available at Seattle. Acquisition cost $2120. Transfer TR-00125 received 2026-06-08; approval APR-00125. Fixed-asset extract includes FA-000125 (NBV $0). PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20422,13 +20355,13 @@
       <c r="M129" s="7" t="n">
         <v>2120</v>
       </c>
-      <c r="N129" s="7">
-        <f>IFERROR(XLOOKUP(A129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N129" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O129" s="7">
-        <f>IFERROR(XLOOKUP(A129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t>FA-000125</t>
+        </is>
       </c>
       <c r="P129" s="7" t="inlineStr">
         <is>
@@ -20519,7 +20452,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>MD-00126 stays Available at Atlanta (Dell U2723QE, $520). Inbound stamp on TR-00126 is 01/12/2026, approval APR-00126. PO PO-2022-0021 on file; no matching FAR row for MD-00126.</t>
+          <t>MD-00126 (Dell U2723QE) is Available at Atlanta. Acquisition cost $520. Transfer TR-00126 received 2026-01-12; approval APR-00126. Ledger FA-000126 on file; NBV $302.75. PO PO-2022-0021.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20530,13 +20463,13 @@
       <c r="M130" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="N130" s="7">
-        <f>IFERROR(XLOOKUP(A130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N130" s="7" t="n">
         <v>302.75</v>
       </c>
-      <c r="O130" s="7">
-        <f>IFERROR(XLOOKUP(A130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>FA-000126</t>
+        </is>
       </c>
       <c r="P130" s="7" t="inlineStr">
         <is>
@@ -20631,7 +20564,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00127: In Use, Denver, $995 — Samsung Galaxy S24. Checked E0061: Transferred. Log TR-00127: received Feb 17, 2026, approval field blank. PO PO-2023-0022 on file; no matching FAR row for MD-00127.</t>
+          <t>Status for MD-00127: In Use. Site Denver. Model Samsung Galaxy S24; cost $995. hr_employee_status lists E0061 / Liam Keane as Transferred. Transfer TR-00127 received 2026-02-17; approval blank. FAR row FA-000127; net book value $662.65. PO PO-2023-0022.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20642,13 +20575,13 @@
       <c r="M131" s="7" t="n">
         <v>995</v>
       </c>
-      <c r="N131" s="7">
-        <f>IFERROR(XLOOKUP(A131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N131" s="7" t="n">
         <v>662.65</v>
       </c>
-      <c r="O131" s="7">
-        <f>IFERROR(XLOOKUP(A131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t>FA-000127</t>
+        </is>
       </c>
       <c r="P131" s="7" t="inlineStr">
         <is>
@@ -20743,7 +20676,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00128: In Use, New York, $6290 — Cisco C9300. Checked E0062: Transferred. TR-00128 ties to MD-00128; dock date 2026-03-19, approval APR-00128. PO PO-2023-0022 on file; no matching FAR row for MD-00128.</t>
+          <t>New York holds MD-00128 (Cisco C9300) as In Use. Acquisition $6290. People file: E0062 (Bianca Silva), status Transferred. Transfer TR-00128 received 2026-03-19; approval APR-00128. Fixed-asset extract includes FA-000128 (NBV $1364.77). PO PO-2023-0022.</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20754,13 +20687,13 @@
       <c r="M132" s="7" t="n">
         <v>6290</v>
       </c>
-      <c r="N132" s="7">
-        <f>IFERROR(XLOOKUP(A132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N132" s="7" t="n">
         <v>1364.77</v>
       </c>
-      <c r="O132" s="7">
-        <f>IFERROR(XLOOKUP(A132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t>FA-000128</t>
+        </is>
       </c>
       <c r="P132" s="7" t="inlineStr">
         <is>
@@ -20851,7 +20784,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>Corrected row MD-00129: In Use, Seattle, $1985 — Dell Latitude 7440. Checked E0063: Transferred. Transfer TR-00129 shows receipt 04/21/2026, approval APR-00129. PO PO-2023-0022 on file; no matching FAR row for MD-00129.</t>
+          <t>MD-00129 (Dell Latitude 7440) is In Use at Seattle. Acquisition cost $1985. Custodian E0063 (Greg Hollis) is Transferred in hr_employee_status. Transfer TR-00129 received 2026-04-21; approval APR-00129. Ledger FA-000129 on file; NBV $111.86. PO PO-2023-0022.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -20862,13 +20795,13 @@
       <c r="M133" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="N133" s="7">
-        <f>IFERROR(XLOOKUP(A133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="N133" s="7" t="n">
         <v>111.86</v>
       </c>
-      <c r="O133" s="7">
-        <f>IFERROR(XLOOKUP(A133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>FA-000129</t>
+        </is>
       </c>
       <c r="P133" s="7" t="inlineStr">
         <is>
@@ -20959,7 +20892,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE on MD-00130 is In Use in Atlanta site; basis $700. Naomi Berger has Transferred status in the people extract. Assignment TR-00130; receive column May 28, 2026, approval APR-00130. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00130. Also: $700 below $2,500 — missing FA expected.</t>
+          <t>Status for MD-00130: In Use. Site Atlanta. Model Dell U2723QE; cost $700. hr_employee_status lists E0064 / Naomi Berger as Transferred. Transfer TR-00130 received 2026-05-28; approval APR-00130. PO PO-2023-0023 (capitalization_approved=No); $700 below $2,500 so FAR absence is expected under ITAM-001 section 7.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -20970,14 +20903,8 @@
       <c r="M134" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="N134" s="7">
-        <f>IFERROR(XLOOKUP(A134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
-      <c r="O134" s="7">
-        <f>IFERROR(XLOOKUP(A134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
-      </c>
+      <c r="N134" s="7" t="n"/>
+      <c r="O134" s="7" t="n"/>
       <c r="P134" s="7" t="inlineStr"/>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -21053,7 +20980,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 on MD-00131 is In Use in Chicago site; basis $1175. Felix Moreno has Transferred status in the people extract. TR-00131 for MD-00131 — received 2026-06-28, approval APR-00131. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00131. Also: $1175 below $2,500 — missing FA expected.</t>
+          <t>Chicago holds MD-00131 (Samsung Galaxy S24) as In Use. Acquisition $1175. People file: E0065 (Felix Moreno), status Transferred. Transfer TR-00131 received 2026-06-28; approval APR-00131. PO PO-2023-0023 (capitalization_approved=No); $1175 below $2,500 so FAR absence is expected under ITAM-001 section 7.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -21064,14 +20991,8 @@
       <c r="M135" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="N135" s="7">
-        <f>IFERROR(XLOOKUP(A135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
-      <c r="O135" s="7">
-        <f>IFERROR(XLOOKUP(A135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
-      </c>
+      <c r="N135" s="7" t="n"/>
+      <c r="O135" s="7" t="n"/>
       <c r="P135" s="7" t="inlineStr"/>
       <c r="Q135" s="9" t="inlineStr">
         <is>
@@ -21147,7 +21068,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>Cisco C9300 on MD-00132 is In Use in Dallas site; basis $6470. Sharon Quinlan has Transferred status in the people extract. Inbound stamp on TR-00132 is 01/31/2026, approval APR-00132. PO-2023-0022 in hardware_purchase_orders.csv; FAR silent on MD-00132. Also: RN-0132 under-threshold claim rejected; $6,470 exceeds capitalization gate with no FA row.</t>
+          <t>MD-00132 (Cisco C9300) is In Use at Dallas. Acquisition cost $6470. Custodian E0066 (Sharon Quinlan) is Transferred in hr_employee_status. Transfer TR-00132 received 2026-01-31; approval APR-00132. PO PO-2023-0022; $6470 exceeds $2,500 with no FA row. RN-0132 under-threshold claim rejected.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -21158,14 +21079,8 @@
       <c r="M136" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="N136" s="7">
-        <f>IFERROR(XLOOKUP(A136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
-      <c r="O136" s="7">
-        <f>IFERROR(XLOOKUP(A136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$A$5:$A$133),"")</f>
-        <v/>
-      </c>
+      <c r="N136" s="7" t="n"/>
+      <c r="O136" s="7" t="n"/>
       <c r="P136" s="7" t="inlineStr"/>
       <c r="Q136" s="9" t="inlineStr">
         <is>
@@ -21235,7 +21150,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -21331,16 +21245,15 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Ledger:FA-000017; PO:PO-2024-0003; RegisterCost:1985.0; LedgerCost:2070.0</t>
-        </is>
-      </c>
-      <c r="G5" s="7">
-        <f>IF(B5="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D5,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D5,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+          <t>Ledger:FA-000017; PO:PO-2024-0003; RegisterCost:1985.0; LedgerCost:2070.0; OverDepreciation:90.0</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>85</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Finance Controller owns cost-basis cleanup on MD-00017.</t>
+          <t>Finance Controller owns cost-basis cleanup on MD-00017; clear FA-000017 over-depreciation before relying on NBV.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -21360,7 +21273,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Pulled PO-2024-0003 and FA-000017; numbers diverge for MD-00017.</t>
+          <t>Pulled PO-2024-0003 and FA-000017; numbers diverge for MD-00017. FA-000017 accumulated depreciation $2160 exceeds acquisition cost $2070 by $90.</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -21400,8 +21313,7 @@
           <t>Duplicate serial MD-LA-050021 across MD-00021 and MD-00025; Serial:MD-LA-050021; AlsoTagged:MD-00021,MD-00025</t>
         </is>
       </c>
-      <c r="G6" s="7">
-        <f>IF(B6="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D6,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D6,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G6" s="7" t="n">
         <v>124.52</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -21466,8 +21378,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00025; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G7" s="7">
-        <f>IF(B7="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D7,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D7,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -21532,13 +21443,12 @@
           <t>Duplicate serial MD-LA-050021 across MD-00021 and MD-00025; Serial:MD-LA-050021; AlsoTagged:MD-00021,MD-00025</t>
         </is>
       </c>
-      <c r="G8" s="7">
-        <f>IF(B8="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D8,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D8,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Retag required — MD-LA-050021 collision involving MD-00025.</t>
+          <t>Retag required - MD-LA-050021 collision involving MD-00025.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -21598,8 +21508,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00026; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G9" s="7">
-        <f>IF(B9="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D9,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D9,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G9" s="7" t="n">
         <v>382.34</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -21664,8 +21573,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00027; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G10" s="7">
-        <f>IF(B10="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D10,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D10,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G10" s="7" t="n">
         <v>672.21</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -21730,8 +21638,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00028; HRLocation:New York</t>
         </is>
       </c>
-      <c r="G11" s="7">
-        <f>IF(B11="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D11,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D11,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G11" s="7" t="n">
         <v>914.09</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -21796,8 +21703,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00029; HRLocation:Seattle</t>
         </is>
       </c>
-      <c r="G12" s="7">
-        <f>IF(B12="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D12,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D12,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -21862,8 +21768,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00030; HRLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G13" s="7">
-        <f>IF(B13="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D13,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D13,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G13" s="7" t="n">
         <v>355.14</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -21928,8 +21833,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00031; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G14" s="7">
-        <f>IF(B14="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D14,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D14,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G14" s="7" t="n">
         <v>722.59</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -21994,8 +21898,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00032; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G15" s="7">
-        <f>IF(B15="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D15,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D15,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G15" s="7" t="n">
         <v>1384.3</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -22060,8 +21963,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00033; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G16" s="7">
-        <f>IF(B16="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D16,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D16,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G16" s="7" t="n">
         <v>116.93</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -22126,8 +22028,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00034; HRLocation:New York</t>
         </is>
       </c>
-      <c r="G17" s="7">
-        <f>IF(B17="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D17,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D17,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G17" s="7" t="n">
         <v>514.88</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -22192,8 +22093,7 @@
           <t>Ledger:FA-000034; PO:PO-2023-0006; RegisterCost:790.0; LedgerCost:930.0</t>
         </is>
       </c>
-      <c r="G18" s="7">
-        <f>IF(B18="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D18,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D18,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G18" s="7" t="n">
         <v>140</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -22258,8 +22158,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00035; HRLocation:Seattle</t>
         </is>
       </c>
-      <c r="G19" s="7">
-        <f>IF(B19="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D19,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D19,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G19" s="7" t="n">
         <v>741.92</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -22324,8 +22223,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00036; HRLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G20" s="7">
-        <f>IF(B20="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D20,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D20,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G20" s="7" t="n">
         <v>537.73</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -22390,8 +22288,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00037; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G21" s="7">
-        <f>IF(B21="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D21,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D21,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -22456,8 +22353,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00038; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G22" s="7">
-        <f>IF(B22="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D22,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D22,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G22" s="7" t="n">
         <v>340.46</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -22522,8 +22418,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00039; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G23" s="7">
-        <f>IF(B23="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D23,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D23,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G23" s="7" t="n">
         <v>635</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -22588,8 +22483,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00040; HRLocation:New York</t>
         </is>
       </c>
-      <c r="G24" s="7">
-        <f>IF(B24="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G24" s="7" t="n">
         <v>989.48</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -22654,8 +22548,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00041; HRLocation:Seattle</t>
         </is>
       </c>
-      <c r="G25" s="7">
-        <f>IF(B25="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -22720,8 +22613,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00042; HRLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G26" s="7">
-        <f>IF(B26="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G26" s="7" t="n">
         <v>306.16</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -22786,8 +22678,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00043; HRLocation:Chicago</t>
         </is>
       </c>
-      <c r="G27" s="7">
-        <f>IF(B27="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G27" s="7" t="n">
         <v>673.55</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -22852,13 +22743,12 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00044; HRLocation:Dallas</t>
         </is>
       </c>
-      <c r="G28" s="7">
-        <f>IF(B28="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G28" s="7" t="n">
         <v>1406.1</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>MD-00044 / Chicago - Closed is a consolidation leftover — move to Dallas (EX-0024).</t>
+          <t>MD-00044 / Chicago - Closed is a consolidation leftover - move to Dallas (EX-0024).</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -22918,8 +22808,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00045; HRLocation:Denver</t>
         </is>
       </c>
-      <c r="G29" s="7">
-        <f>IF(B29="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G29" s="7" t="n">
         <v>133.6</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -22984,8 +22873,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00046; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G30" s="7">
-        <f>IF(B30="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G30" s="7" t="n">
         <v>460.82</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -23010,7 +22898,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00046 there on paper — New York is live (EX-0026).</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00046 there on paper - New York is live (EX-0026).</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -23050,8 +22938,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00047; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G31" s="7">
-        <f>IF(B31="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G31" s="7" t="n">
         <v>930.51</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -23116,8 +23003,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00048; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G32" s="7">
-        <f>IF(B32="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G32" s="7" t="n">
         <v>514.59</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -23182,8 +23068,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00049; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G33" s="7">
-        <f>IF(B33="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -23248,8 +23133,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00050; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G34" s="7">
-        <f>IF(B34="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G34" s="7" t="n">
         <v>289.96</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -23314,8 +23198,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00051; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G35" s="7">
-        <f>IF(B35="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G35" s="7" t="n">
         <v>573.03</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -23380,8 +23263,7 @@
           <t>Ledger:FA-000051; PO:PO-2022-0009; RegisterCost:1040.0; LedgerCost:1250.0</t>
         </is>
       </c>
-      <c r="G36" s="7">
-        <f>IF(B36="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D36,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D36,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G36" s="7" t="n">
         <v>210</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -23446,8 +23328,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00052; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G37" s="7">
-        <f>IF(B37="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D37,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D37,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G37" s="7" t="n">
         <v>933.99</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -23472,7 +23353,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00052 there on paper — New York is live (EX-0033).</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00052 there on paper - New York is live (EX-0033).</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -23512,8 +23393,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00053; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G38" s="7">
-        <f>IF(B38="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D38,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D38,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -23578,8 +23458,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00054; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G39" s="7">
-        <f>IF(B39="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D39,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D39,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G39" s="7" t="n">
         <v>433.74</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -23644,8 +23523,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00055; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G40" s="7">
-        <f>IF(B40="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D40,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D40,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G40" s="7" t="n">
         <v>812.5</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -23710,8 +23588,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00056; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G41" s="7">
-        <f>IF(B41="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D41,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D41,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G41" s="7" t="n">
         <v>1345.24</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -23776,8 +23653,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00057; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G42" s="7">
-        <f>IF(B42="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D42,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D42,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G42" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -23842,8 +23718,7 @@
           <t>Employee:E0071; Ticket:OFF-00058; Transfer:TR-00058</t>
         </is>
       </c>
-      <c r="G43" s="7">
-        <f>IF(B43="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D43,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D43,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G43" s="7" t="n">
         <v>397.56</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -23908,8 +23783,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00058; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G44" s="7">
-        <f>IF(B44="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D44,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D44,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G44" s="7" t="n">
         <v>397.56</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -23974,8 +23848,7 @@
           <t>Transfer:TR-00058; Approval:missing</t>
         </is>
       </c>
-      <c r="G45" s="7">
-        <f>IF(B45="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D45,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D45,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G45" s="7" t="n">
         <v>397.56</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -24040,8 +23913,7 @@
           <t>Employee:E0072; Ticket:OFF-00059; Transfer:TR-00059</t>
         </is>
       </c>
-      <c r="G46" s="7">
-        <f>IF(B46="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D46,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D46,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G46" s="7" t="n">
         <v>847.35</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -24106,8 +23978,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00059; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G47" s="7">
-        <f>IF(B47="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D47,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D47,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G47" s="7" t="n">
         <v>847.35</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -24172,8 +24043,7 @@
           <t>Transfer:TR-00059; Approval:missing</t>
         </is>
       </c>
-      <c r="G48" s="7">
-        <f>IF(B48="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D48,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D48,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G48" s="7" t="n">
         <v>847.35</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -24198,7 +24068,7 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>§4 evidence gap — TR-00059 lacks approval for MD-00059.</t>
+          <t>§4 evidence gap - TR-00059 lacks approval for MD-00059.</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -24238,8 +24108,7 @@
           <t>Employee:E0073; Ticket:OFF-00060; Transfer:TR-00060</t>
         </is>
       </c>
-      <c r="G49" s="7">
-        <f>IF(B49="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D49,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D49,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G49" s="7" t="n">
         <v>549.35</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -24304,8 +24173,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00060; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G50" s="7">
-        <f>IF(B50="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D50,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D50,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G50" s="7" t="n">
         <v>549.35</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -24370,8 +24238,7 @@
           <t>Employee:E0074; Ticket:OFF-00061; Transfer:TR-00061</t>
         </is>
       </c>
-      <c r="G51" s="7">
-        <f>IF(B51="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D51,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D51,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -24436,8 +24303,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00061; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G52" s="7">
-        <f>IF(B52="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D52,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D52,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G52" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -24502,8 +24368,7 @@
           <t>Employee:E0075; Ticket:OFF-00062; Transfer:TR-00062</t>
         </is>
       </c>
-      <c r="G53" s="7">
-        <f>IF(B53="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D53,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D53,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G53" s="7" t="n">
         <v>410.63</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -24568,13 +24433,12 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00062; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G54" s="7">
-        <f>IF(B54="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D54,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D54,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G54" s="7" t="n">
         <v>410.63</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 / Chicago - Closed is a consolidation leftover — move to Dallas (EX-0050).</t>
+          <t>MD-00062 / Chicago - Closed is a consolidation leftover - move to Dallas (EX-0050).</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -24634,8 +24498,7 @@
           <t>Employee:E0076; Ticket:OFF-00063; Transfer:TR-00063</t>
         </is>
       </c>
-      <c r="G55" s="7">
-        <f>IF(B55="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D55,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D55,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G55" s="7" t="n">
         <v>533.85</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -24700,8 +24563,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00063; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G56" s="7">
-        <f>IF(B56="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D56,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D56,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G56" s="7" t="n">
         <v>533.85</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -24766,13 +24628,12 @@
           <t>Employee:E0077; Ticket:OFF-00064; Transfer:TR-00064</t>
         </is>
       </c>
-      <c r="G57" s="7">
-        <f>IF(B57="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D57,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D57,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G57" s="7" t="n">
         <v>961.76</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>HR shows E0077 gone — remove as custodian on MD-00064 (OFF-00064).</t>
+          <t>HR shows E0077 gone - remove as custodian on MD-00064 (OFF-00064).</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -24832,8 +24693,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00064; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G58" s="7">
-        <f>IF(B58="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D58,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D58,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G58" s="7" t="n">
         <v>961.76</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -24898,8 +24758,7 @@
           <t>Transfer:TR-00064; Approval:missing</t>
         </is>
       </c>
-      <c r="G59" s="7">
-        <f>IF(B59="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D59,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D59,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G59" s="7" t="n">
         <v>961.76</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -24964,8 +24823,7 @@
           <t>Employee:E0078; Ticket:OFF-00065; Transfer:TR-00065</t>
         </is>
       </c>
-      <c r="G60" s="7">
-        <f>IF(B60="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D60,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D60,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -24990,7 +24848,7 @@
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 custodian equals terminated ID E0078 — EX-0056.</t>
+          <t>MD-00065 custodian equals terminated ID E0078 - EX-0056.</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25030,8 +24888,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00065; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G61" s="7">
-        <f>IF(B61="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D61,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D61,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -25096,8 +24953,7 @@
           <t>Transfer:TR-00065; Approval:missing</t>
         </is>
       </c>
-      <c r="G62" s="7">
-        <f>IF(B62="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D62,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D62,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G62" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -25162,8 +25018,7 @@
           <t>Employee:E0079; Ticket:OFF-00066; Transfer:TR-00066</t>
         </is>
       </c>
-      <c r="G63" s="7">
-        <f>IF(B63="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D63,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D63,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G63" s="7" t="n">
         <v>385.65</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -25228,8 +25083,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00066; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G64" s="7">
-        <f>IF(B64="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D64,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D64,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G64" s="7" t="n">
         <v>385.65</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -25294,13 +25148,12 @@
           <t>Employee:E0080; Ticket:OFF-00067; Transfer:TR-00067</t>
         </is>
       </c>
-      <c r="G65" s="7">
-        <f>IF(B65="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D65,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D65,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>764.93</v>
+      <c r="G65" s="7" t="n">
+        <v>764.9299999999999</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00067 should not remain with E0080.</t>
+          <t>Term cleanup - MD-00067 should not remain with E0080.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -25360,9 +25213,8 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00067; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G66" s="7">
-        <f>IF(B66="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D66,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D66,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>764.93</v>
+      <c r="G66" s="7" t="n">
+        <v>764.9299999999999</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -25426,8 +25278,7 @@
           <t>Ticket:OFF-00068; Tracking:1ZMD00000068; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G67" s="7">
-        <f>IF(B67="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D67,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D67,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G67" s="7" t="n">
         <v>1436.28</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -25492,8 +25343,7 @@
           <t>Employee:E0081; Ticket:OFF-00068</t>
         </is>
       </c>
-      <c r="G68" s="7">
-        <f>IF(B68="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D68,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D68,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G68" s="7" t="n">
         <v>1436.28</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -25558,8 +25408,7 @@
           <t>Ledger:FA-000068; PO:PO-2025-0012; RegisterCost:6425.0; LedgerCost:6480.0</t>
         </is>
       </c>
-      <c r="G69" s="7">
-        <f>IF(B69="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D69,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D69,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G69" s="7" t="n">
         <v>55</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -25624,13 +25473,12 @@
           <t>Ticket:OFF-00069; Tracking:1ZMD00000069; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G70" s="7">
-        <f>IF(B70="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D70,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D70,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G70" s="7" t="n">
         <v>142.69</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Outstanding kit MD-00069 / 1ZMD00000069 — escalate beyond label print.</t>
+          <t>Outstanding kit MD-00069 / 1ZMD00000069 - escalate beyond label print.</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -25690,8 +25538,7 @@
           <t>Employee:E0082; Ticket:OFF-00069</t>
         </is>
       </c>
-      <c r="G71" s="7">
-        <f>IF(B71="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D71,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D71,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G71" s="7" t="n">
         <v>142.69</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -25756,8 +25603,7 @@
           <t>Ticket:OFF-00070; Tracking:1ZMD00000070; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G72" s="7">
-        <f>IF(B72="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D72,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D72,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G72" s="7" t="n">
         <v>342.32</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -25822,8 +25668,7 @@
           <t>Employee:E0083; Ticket:OFF-00070</t>
         </is>
       </c>
-      <c r="G73" s="7">
-        <f>IF(B73="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D73,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D73,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G73" s="7" t="n">
         <v>342.32</v>
       </c>
       <c r="H73" s="7" t="inlineStr">
@@ -25888,8 +25733,7 @@
           <t>Ticket:OFF-00071; Tracking:1ZMD00000071; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G74" s="7">
-        <f>IF(B74="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D74,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D74,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G74" s="7" t="n">
         <v>787.96</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -25954,8 +25798,7 @@
           <t>Employee:E0084; Ticket:OFF-00071</t>
         </is>
       </c>
-      <c r="G75" s="7">
-        <f>IF(B75="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D75,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D75,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G75" s="7" t="n">
         <v>787.96</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -26020,8 +25863,7 @@
           <t>Ticket:OFF-00072; Tracking:1ZMD00000072; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G76" s="7">
-        <f>IF(B76="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D76,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D76,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G76" s="7" t="n">
         <v>500.27</v>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -26086,8 +25928,7 @@
           <t>Employee:E0085; Ticket:OFF-00072</t>
         </is>
       </c>
-      <c r="G77" s="7">
-        <f>IF(B77="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D77,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D77,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G77" s="7" t="n">
         <v>500.27</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -26152,13 +25993,12 @@
           <t>Ticket:OFF-00073; Tracking:1ZMD00000073; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G78" s="7">
-        <f>IF(B78="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D78,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D78,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Keep pressure on the former user until dock scan — 1ZMD00000073.</t>
+          <t>Keep pressure on the former user until dock scan - 1ZMD00000073.</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -26218,8 +26058,7 @@
           <t>Employee:E0086; Ticket:OFF-00073</t>
         </is>
       </c>
-      <c r="G79" s="7">
-        <f>IF(B79="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D79,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D79,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -26284,8 +26123,7 @@
           <t>Ticket:OFF-00074; Tracking:1ZMD00000074; ShipmentSerial:MISMATCH-0074</t>
         </is>
       </c>
-      <c r="G80" s="7">
-        <f>IF(B80="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D80,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D80,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G80" s="7" t="n">
         <v>359.25</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -26350,8 +26188,7 @@
           <t>Employee:E0087; Ticket:OFF-00074</t>
         </is>
       </c>
-      <c r="G81" s="7">
-        <f>IF(B81="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D81,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D81,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G81" s="7" t="n">
         <v>359.25</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -26376,7 +26213,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 custodian equals terminated ID E0087 — EX-0077.</t>
+          <t>MD-00074 custodian equals terminated ID E0087 - EX-0077.</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -26416,8 +26253,7 @@
           <t>Ticket:OFF-00074; Tracking:1ZMD00000074; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G82" s="7">
-        <f>IF(B82="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D82,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D82,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G82" s="7" t="n">
         <v>359.25</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -26482,8 +26318,7 @@
           <t>Ticket:OFF-00075; Tracking:1ZMD00000075; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G83" s="7">
-        <f>IF(B83="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D83,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D83,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G83" s="7" t="n">
         <v>647.42</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -26548,8 +26383,7 @@
           <t>Employee:E0088; Ticket:OFF-00075</t>
         </is>
       </c>
-      <c r="G84" s="7">
-        <f>IF(B84="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D84,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D84,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G84" s="7" t="n">
         <v>647.42</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -26614,8 +26448,7 @@
           <t>Ticket:OFF-00076; Tracking:1ZMD00000076; ShipmentSerial:MISMATCH-0076</t>
         </is>
       </c>
-      <c r="G85" s="7">
-        <f>IF(B85="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D85,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D85,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G85" s="7" t="n">
         <v>953.89</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -26680,13 +26513,12 @@
           <t>Employee:E0089; Ticket:OFF-00076</t>
         </is>
       </c>
-      <c r="G86" s="7">
-        <f>IF(B86="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D86,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D86,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G86" s="7" t="n">
         <v>953.89</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00076 should not remain with E0089.</t>
+          <t>Term cleanup - MD-00076 should not remain with E0089.</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -26746,8 +26578,7 @@
           <t>Ticket:OFF-00076; Tracking:1ZMD00000076; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G87" s="7">
-        <f>IF(B87="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D87,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D87,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G87" s="7" t="n">
         <v>953.89</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -26812,13 +26643,12 @@
           <t>Ticket:OFF-00077; Tracking:1ZMD00000077; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G88" s="7">
-        <f>IF(B88="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D88,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D88,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G88" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Outstanding kit MD-00077 / 1ZMD00000077 — escalate beyond label print.</t>
+          <t>Outstanding kit MD-00077 / 1ZMD00000077 - escalate beyond label print.</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -26878,8 +26708,7 @@
           <t>Employee:E0090; Ticket:OFF-00077</t>
         </is>
       </c>
-      <c r="G89" s="7">
-        <f>IF(B89="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D89,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D89,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -26904,7 +26733,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>MD-00077 custodian equals terminated ID E0090 — EX-0085.</t>
+          <t>MD-00077 custodian equals terminated ID E0090 - EX-0085.</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -26944,8 +26773,7 @@
           <t>Ticket:OFF-00078; Tracking:1ZMD00000078; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G90" s="7">
-        <f>IF(B90="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D90,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D90,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G90" s="7" t="n">
         <v>328.95</v>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -27010,8 +26838,7 @@
           <t>Employee:E0091; Ticket:OFF-00078</t>
         </is>
       </c>
-      <c r="G91" s="7">
-        <f>IF(B91="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D91,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D91,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G91" s="7" t="n">
         <v>328.95</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -27076,8 +26903,7 @@
           <t>Ticket:OFF-00079; Tracking:1ZMD00000079; ReturnDue:2026-07-15</t>
         </is>
       </c>
-      <c r="G92" s="7">
-        <f>IF(B92="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D92,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D92,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G92" s="7" t="n">
         <v>692.62</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -27142,8 +26968,7 @@
           <t>Employee:E0092; Ticket:OFF-00079</t>
         </is>
       </c>
-      <c r="G93" s="7">
-        <f>IF(B93="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D93,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D93,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G93" s="7" t="n">
         <v>692.62</v>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -27208,13 +27033,12 @@
           <t>Employee:E0093; Ticket:OFF-00080; Tracking:1ZMD00000080</t>
         </is>
       </c>
-      <c r="G94" s="7">
-        <f>IF(B94="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D94,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D94,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G94" s="7" t="n">
         <v>1374.53</v>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00080 should not remain with E0093.</t>
+          <t>Term cleanup - MD-00080 should not remain with E0093.</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -27274,8 +27098,7 @@
           <t>Employee:E0094; Ticket:OFF-00081; Tracking:1ZMD00000081</t>
         </is>
       </c>
-      <c r="G95" s="7">
-        <f>IF(B95="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D95,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D95,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G95" s="7" t="n">
         <v>114.4</v>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -27340,8 +27163,7 @@
           <t>Ticket:OFF-00082; Tracking:1ZMD00000082; ShipmentSerial:MISMATCH-0082; Image:receiving_exception_scan_1ZMD00000082.png</t>
         </is>
       </c>
-      <c r="G96" s="7">
-        <f>IF(B96="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D96,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D96,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G96" s="7" t="n">
         <v>485.55</v>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -27406,8 +27228,7 @@
           <t>Employee:E0095; Ticket:OFF-00082</t>
         </is>
       </c>
-      <c r="G97" s="7">
-        <f>IF(B97="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D97,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D97,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G97" s="7" t="n">
         <v>485.55</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -27432,7 +27253,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0095 to register row MD-00082 — assignment stale (EX-0093).</t>
+          <t>Compared HR row E0095 to register row MD-00082 - assignment stale (EX-0093).</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -27472,8 +27293,7 @@
           <t>Employee:E0071; Ticket:OFF-00083; Tracking:1ZMD00000083</t>
         </is>
       </c>
-      <c r="G98" s="7">
-        <f>IF(B98="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D98,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D98,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G98" s="7" t="n">
         <v>952.79</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -27538,8 +27358,7 @@
           <t>Ticket:OFF-00084; Tracking:1ZMD00000084; ShipmentSerial:MISMATCH-0084</t>
         </is>
       </c>
-      <c r="G99" s="7">
-        <f>IF(B99="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D99,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D99,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G99" s="7" t="n">
         <v>533.85</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -27604,8 +27423,7 @@
           <t>Employee:E0072; Ticket:OFF-00084</t>
         </is>
       </c>
-      <c r="G100" s="7">
-        <f>IF(B100="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D100,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D100,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G100" s="7" t="n">
         <v>533.85</v>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -27670,8 +27488,7 @@
           <t>Employee:E0073; Ticket:OFF-00085; Tracking:1ZMD00000085</t>
         </is>
       </c>
-      <c r="G101" s="7">
-        <f>IF(B101="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D101,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D101,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -27736,8 +27553,7 @@
           <t>Ledger:FA-000085; PO:PO-2024-0015; RegisterCost:1895.0; LedgerCost:2090.0</t>
         </is>
       </c>
-      <c r="G102" s="7">
-        <f>IF(B102="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D102,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D102,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G102" s="7" t="n">
         <v>195</v>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -27802,13 +27618,12 @@
           <t>Employee:E0074; Ticket:OFF-00086; Tracking:1ZMD00000086</t>
         </is>
       </c>
-      <c r="G103" s="7">
-        <f>IF(B103="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D103,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D103,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G103" s="7" t="n">
         <v>317.07</v>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>HR shows E0074 gone — remove as custodian on MD-00086 (OFF-00086).</t>
+          <t>HR shows E0074 gone - remove as custodian on MD-00086 (OFF-00086).</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -27828,7 +27643,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0074 to register row MD-00086 — assignment stale (EX-0099).</t>
+          <t>Compared HR row E0074 to register row MD-00086 - assignment stale (EX-0099).</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -27868,8 +27683,7 @@
           <t>Employee:E0075; Ticket:OFF-00087; Tracking:1ZMD00000087</t>
         </is>
       </c>
-      <c r="G104" s="7">
-        <f>IF(B104="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D104,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D104,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G104" s="7" t="n">
         <v>609.71</v>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -27934,8 +27748,7 @@
           <t>Employee:E0076; Ticket:OFF-00088; Tracking:1ZMD00000088</t>
         </is>
       </c>
-      <c r="G105" s="7">
-        <f>IF(B105="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D105,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D105,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G105" s="7" t="n">
         <v>982.55</v>
       </c>
       <c r="H105" s="7" t="inlineStr">
@@ -27960,7 +27773,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0076 to register row MD-00088 — assignment stale (EX-0101).</t>
+          <t>Compared HR row E0076 to register row MD-00088 - assignment stale (EX-0101).</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -28000,13 +27813,12 @@
           <t>Duplicate serial MD-NE-050088 across MD-00088 and MD-00092; Serial:MD-NE-050088; AlsoTagged:MD-00088,MD-00092</t>
         </is>
       </c>
-      <c r="G106" s="7">
-        <f>IF(B106="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D106,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D106,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G106" s="7" t="n">
         <v>982.55</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Duplicate MD-NE-050088 — MD-00088 and MD-00088,MD-00092. Neither is clean until retag.</t>
+          <t>Duplicate MD-NE-050088 - MD-00088 and MD-00088,MD-00092. Neither is clean until retag.</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -28066,8 +27878,7 @@
           <t>Ticket:OFF-00089; Transfer:TR-00089; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G107" s="7">
-        <f>IF(B107="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D107,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D107,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -28132,8 +27943,7 @@
           <t>Employee:E0077; Ticket:OFF-00089</t>
         </is>
       </c>
-      <c r="G108" s="7">
-        <f>IF(B108="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D108,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D108,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G108" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -28198,8 +28008,7 @@
           <t>Ticket:OFF-00090; Transfer:TR-00090; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G109" s="7">
-        <f>IF(B109="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D109,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D109,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G109" s="7" t="n">
         <v>465.13</v>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -28264,8 +28073,7 @@
           <t>Employee:E0078; Ticket:OFF-00090</t>
         </is>
       </c>
-      <c r="G110" s="7">
-        <f>IF(B110="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D110,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D110,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G110" s="7" t="n">
         <v>465.13</v>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -28330,8 +28138,7 @@
           <t>Ticket:OFF-00091; Transfer:TR-00091; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G111" s="7">
-        <f>IF(B111="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D111,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D111,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G111" s="7" t="n">
         <v>643.09</v>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -28396,8 +28203,7 @@
           <t>Employee:E0079; Ticket:OFF-00091</t>
         </is>
       </c>
-      <c r="G112" s="7">
-        <f>IF(B112="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D112,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D112,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G112" s="7" t="n">
         <v>643.09</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -28462,8 +28268,7 @@
           <t>Ticket:OFF-00092; Transfer:TR-00092; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G113" s="7">
-        <f>IF(B113="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D113,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D113,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G113" s="7" t="n">
         <v>1396.04</v>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -28528,8 +28333,7 @@
           <t>Employee:E0080; Ticket:OFF-00092</t>
         </is>
       </c>
-      <c r="G114" s="7">
-        <f>IF(B114="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D114,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D114,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G114" s="7" t="n">
         <v>1396.04</v>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -28594,8 +28398,7 @@
           <t>Duplicate serial MD-NE-050088 across MD-00088 and MD-00092; Serial:MD-NE-050088; AlsoTagged:MD-00088,MD-00092</t>
         </is>
       </c>
-      <c r="G115" s="7">
-        <f>IF(B115="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D115,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D115,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G115" s="7" t="n">
         <v>1396.04</v>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -28660,8 +28463,7 @@
           <t>Ticket:OFF-00093; Transfer:TR-00093; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G116" s="7">
-        <f>IF(B116="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D116,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D116,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G116" s="7" t="n">
         <v>130.57</v>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -28726,8 +28528,7 @@
           <t>Employee:E0081; Ticket:OFF-00093</t>
         </is>
       </c>
-      <c r="G117" s="7">
-        <f>IF(B117="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D117,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D117,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G117" s="7" t="n">
         <v>130.57</v>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -28792,8 +28593,7 @@
           <t>Ticket:OFF-00094; Transfer:TR-00094; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G118" s="7">
-        <f>IF(B118="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D118,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D118,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G118" s="7" t="n">
         <v>431.2</v>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -28858,13 +28658,12 @@
           <t>Employee:E0082; Ticket:OFF-00094</t>
         </is>
       </c>
-      <c r="G119" s="7">
-        <f>IF(B119="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D119,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D119,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G119" s="7" t="n">
         <v>431.2</v>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup — MD-00094 should not remain with E0082.</t>
+          <t>Term cleanup - MD-00094 should not remain with E0082.</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
@@ -28884,7 +28683,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>MD-00094 custodian equals terminated ID E0082 — EX-0115.</t>
+          <t>MD-00094 custodian equals terminated ID E0082 - EX-0115.</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
@@ -28924,8 +28723,7 @@
           <t>Ticket:OFF-00095; Transfer:TR-00095; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G120" s="7">
-        <f>IF(B120="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D120,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D120,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G120" s="7" t="n">
         <v>894.87</v>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -28990,8 +28788,7 @@
           <t>Employee:E0083; Ticket:OFF-00095</t>
         </is>
       </c>
-      <c r="G121" s="7">
-        <f>IF(B121="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D121,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D121,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G121" s="7" t="n">
         <v>894.87</v>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -29056,8 +28853,7 @@
           <t>Ticket:OFF-00096; Transfer:TR-00096; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G122" s="7">
-        <f>IF(B122="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D122,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D122,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G122" s="7" t="n">
         <v>511.01</v>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -29122,8 +28918,7 @@
           <t>Employee:E0084; Ticket:OFF-00096</t>
         </is>
       </c>
-      <c r="G123" s="7">
-        <f>IF(B123="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D123,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D123,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G123" s="7" t="n">
         <v>511.01</v>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -29188,8 +28983,7 @@
           <t>Ticket:OFF-00097; Transfer:TR-00097; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G124" s="7">
-        <f>IF(B124="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D124,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D124,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G124" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -29254,8 +29048,7 @@
           <t>Employee:E0085; Ticket:OFF-00097</t>
         </is>
       </c>
-      <c r="G125" s="7">
-        <f>IF(B125="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D125,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D125,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G125" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -29320,8 +29113,7 @@
           <t>Ticket:OFF-00098; Transfer:TR-00098; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G126" s="7">
-        <f>IF(B126="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D126,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D126,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G126" s="7" t="n">
         <v>266.87</v>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -29386,8 +29178,7 @@
           <t>Employee:E0086; Ticket:OFF-00098</t>
         </is>
       </c>
-      <c r="G127" s="7">
-        <f>IF(B127="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D127,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D127,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G127" s="7" t="n">
         <v>266.87</v>
       </c>
       <c r="H127" s="7" t="inlineStr">
@@ -29452,8 +29243,7 @@
           <t>Ticket:OFF-00099; Transfer:TR-00099; LastRegisterLocation:Denver - Closed</t>
         </is>
       </c>
-      <c r="G128" s="7">
-        <f>IF(B128="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D128,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D128,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G128" s="7" t="n">
         <v>548.24</v>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -29518,8 +29308,7 @@
           <t>Employee:E0087; Ticket:OFF-00099</t>
         </is>
       </c>
-      <c r="G129" s="7">
-        <f>IF(B129="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D129,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D129,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G129" s="7" t="n">
         <v>548.24</v>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -29584,8 +29373,7 @@
           <t>Ticket:OFF-00100; Transfer:TR-00100; LastRegisterLocation:Chicago - Closed</t>
         </is>
       </c>
-      <c r="G130" s="7">
-        <f>IF(B130="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D130,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D130,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G130" s="7" t="n">
         <v>927.36</v>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -29650,8 +29438,7 @@
           <t>Employee:E0088; Ticket:OFF-00100</t>
         </is>
       </c>
-      <c r="G131" s="7">
-        <f>IF(B131="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D131,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D131,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G131" s="7" t="n">
         <v>927.36</v>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -29716,8 +29503,7 @@
           <t>Ticket:RET-00101; Transfer:TR-00101; Certificate:missing</t>
         </is>
       </c>
-      <c r="G132" s="7">
-        <f>IF(B132="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D132,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D132,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G132" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -29782,8 +29568,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00101</t>
         </is>
       </c>
-      <c r="G133" s="7">
-        <f>IF(B133="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D133,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D133,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G133" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -29848,13 +29633,12 @@
           <t>Ticket:RET-00102; Transfer:TR-00102; Certificate:missing</t>
         </is>
       </c>
-      <c r="G134" s="7">
-        <f>IF(B134="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D134,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D134,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G134" s="7" t="n">
         <v>407.54</v>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Do not call MD-00102 disposed — certificate missing (EX-0130).</t>
+          <t>Do not call MD-00102 disposed - certificate missing (EX-0130).</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr">
@@ -29914,8 +29698,7 @@
           <t>Ledger:FA-000102; PO:PO-2022-0017; RegisterCost:700.0; LedgerCost:820.0</t>
         </is>
       </c>
-      <c r="G135" s="7">
-        <f>IF(B135="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D135,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D135,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G135" s="7" t="n">
         <v>120</v>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -29980,8 +29763,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00102</t>
         </is>
       </c>
-      <c r="G136" s="7">
-        <f>IF(B136="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D136,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D136,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G136" s="7" t="n">
         <v>407.54</v>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -30046,8 +29828,7 @@
           <t>Ticket:RET-00103; Transfer:TR-00103; Certificate:missing</t>
         </is>
       </c>
-      <c r="G137" s="7">
-        <f>IF(B137="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D137,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D137,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D137,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G137" s="7" t="n">
         <v>782.53</v>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -30112,8 +29893,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00103</t>
         </is>
       </c>
-      <c r="G138" s="7">
-        <f>IF(B138="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D138,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D138,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D138,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G138" s="7" t="n">
         <v>782.53</v>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -30178,8 +29958,7 @@
           <t>Ticket:RET-00104; Transfer:TR-00104; Certificate:missing</t>
         </is>
       </c>
-      <c r="G139" s="7">
-        <f>IF(B139="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D139,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D139,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D139,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G139" s="7" t="n">
         <v>1403.83</v>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -30244,8 +30023,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00104</t>
         </is>
       </c>
-      <c r="G140" s="7">
-        <f>IF(B140="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D140,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D140,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D140,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G140" s="7" t="n">
         <v>1403.83</v>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -30310,8 +30088,7 @@
           <t>Ticket:RET-00105; Transfer:TR-00105; Certificate:missing</t>
         </is>
       </c>
-      <c r="G141" s="7">
-        <f>IF(B141="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D141,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D141,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D141,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G141" s="7" t="n">
         <v>104.26</v>
       </c>
       <c r="H141" s="7" t="inlineStr">
@@ -30376,13 +30153,12 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00105</t>
         </is>
       </c>
-      <c r="G142" s="7">
-        <f>IF(B142="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D142,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D142,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D142,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G142" s="7" t="n">
         <v>104.26</v>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 / Denver - Closed is a consolidation leftover — move to Denver (EX-0138).</t>
+          <t>MD-00105 / Denver - Closed is a consolidation leftover - move to Denver (EX-0138).</t>
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr">
@@ -30442,8 +30218,7 @@
           <t>Ticket:RET-00106; Transfer:TR-00106; Certificate:missing</t>
         </is>
       </c>
-      <c r="G143" s="7">
-        <f>IF(B143="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D143,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D143,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D143,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G143" s="7" t="n">
         <v>368.24</v>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -30508,8 +30283,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00106</t>
         </is>
       </c>
-      <c r="G144" s="7">
-        <f>IF(B144="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D144,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D144,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D144,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G144" s="7" t="n">
         <v>368.24</v>
       </c>
       <c r="H144" s="7" t="inlineStr">
@@ -30574,8 +30348,7 @@
           <t>Ticket:RET-00107; Transfer:TR-00107; Certificate:missing</t>
         </is>
       </c>
-      <c r="G145" s="7">
-        <f>IF(B145="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D145,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D145,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D145,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G145" s="7" t="n">
         <v>812.21</v>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -30640,8 +30413,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00107</t>
         </is>
       </c>
-      <c r="G146" s="7">
-        <f>IF(B146="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D146,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D146,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D146,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G146" s="7" t="n">
         <v>812.21</v>
       </c>
       <c r="H146" s="7" t="inlineStr">
@@ -30706,8 +30478,7 @@
           <t>Ticket:RET-00108; Transfer:TR-00108; Certificate:missing</t>
         </is>
       </c>
-      <c r="G147" s="7">
-        <f>IF(B147="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D147,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D147,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D147,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G147" s="7" t="n">
         <v>545.48</v>
       </c>
       <c r="H147" s="7" t="inlineStr">
@@ -30772,8 +30543,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00108</t>
         </is>
       </c>
-      <c r="G148" s="7">
-        <f>IF(B148="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D148,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D148,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D148,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G148" s="7" t="n">
         <v>545.48</v>
       </c>
       <c r="H148" s="7" t="inlineStr">
@@ -30838,13 +30608,12 @@
           <t>Ticket:RET-00109; Transfer:TR-00109; Certificate:missing</t>
         </is>
       </c>
-      <c r="G149" s="7">
-        <f>IF(B149="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D149,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D149,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D149,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G149" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>ITAM hold — MD-00109 not gone until cert lists the tag (EX-0145).</t>
+          <t>ITAM hold - MD-00109 not gone until cert lists the tag (EX-0145).</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr">
@@ -30904,8 +30673,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00109</t>
         </is>
       </c>
-      <c r="G150" s="7">
-        <f>IF(B150="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D150,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D150,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D150,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G150" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H150" s="7" t="inlineStr">
@@ -30970,8 +30738,7 @@
           <t>Ticket:RET-00110; Transfer:TR-00110; Certificate:missing</t>
         </is>
       </c>
-      <c r="G151" s="7">
-        <f>IF(B151="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D151,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D151,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D151,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G151" s="7" t="n">
         <v>387.24</v>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -31036,8 +30803,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00110</t>
         </is>
       </c>
-      <c r="G152" s="7">
-        <f>IF(B152="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D152,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D152,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D152,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G152" s="7" t="n">
         <v>387.24</v>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -31062,7 +30828,7 @@
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00110 there on paper — Dallas is live (EX-0148).</t>
+          <t>Chicago - Closed is shuttered. Did not leave MD-00110 there on paper - Dallas is live (EX-0148).</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -31102,8 +30868,7 @@
           <t>Ticket:RET-00114; Transfer:TR-00114; Certificate:missing</t>
         </is>
       </c>
-      <c r="G153" s="7">
-        <f>IF(B153="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D153,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D153,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D153,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G153" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -31168,8 +30933,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00114</t>
         </is>
       </c>
-      <c r="G154" s="7">
-        <f>IF(B154="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D154,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D154,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D154,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G154" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -31234,8 +30998,7 @@
           <t>Ticket:RET-00118; Transfer:TR-00118; Certificate:missing</t>
         </is>
       </c>
-      <c r="G155" s="7">
-        <f>IF(B155="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D155,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D155,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D155,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G155" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -31300,8 +31063,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00118</t>
         </is>
       </c>
-      <c r="G156" s="7">
-        <f>IF(B156="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D156,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D156,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D156,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G156" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -31366,8 +31128,7 @@
           <t>Ledger:FA-000119; PO:PO-2025-0020; RegisterCost:950.0; LedgerCost:1115.0</t>
         </is>
       </c>
-      <c r="G157" s="7">
-        <f>IF(B157="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D157,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D157,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D157,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G157" s="7" t="n">
         <v>165</v>
       </c>
       <c r="H157" s="7" t="inlineStr">
@@ -31432,8 +31193,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00121; VerifiedLocation:Chicago</t>
         </is>
       </c>
-      <c r="G158" s="7">
-        <f>IF(B158="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D158,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D158,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D158,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G158" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H158" s="7" t="inlineStr">
@@ -31498,8 +31258,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00122; VerifiedLocation:Dallas</t>
         </is>
       </c>
-      <c r="G159" s="7">
-        <f>IF(B159="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D159,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D159,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D159,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G159" s="7" t="n">
         <v>336.15</v>
       </c>
       <c r="H159" s="7" t="inlineStr">
@@ -31564,8 +31323,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00123; VerifiedLocation:Denver</t>
         </is>
       </c>
-      <c r="G160" s="7">
-        <f>IF(B160="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D160,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D160,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D160,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G160" s="7" t="n">
         <v>622.62</v>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -31630,8 +31388,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00124; VerifiedLocation:New York</t>
         </is>
       </c>
-      <c r="G161" s="7">
-        <f>IF(B161="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D161,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D161,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D161,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G161" s="7" t="n">
         <v>947.26</v>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -31656,7 +31413,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>Extract shows MD-00124 at Chicago - Closed — that building is locked (EX-0157).</t>
+          <t>Extract shows MD-00124 at Chicago - Closed - that building is locked (EX-0157).</t>
         </is>
       </c>
       <c r="M161" s="7" t="inlineStr">
@@ -31696,8 +31453,7 @@
           <t>RegisterLocation:Denver - Closed; Transfer:TR-00125; VerifiedLocation:Seattle</t>
         </is>
       </c>
-      <c r="G162" s="7">
-        <f>IF(B162="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D162,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D162,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D162,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G162" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -31762,8 +31518,7 @@
           <t>RegisterLocation:Chicago - Closed; Transfer:TR-00126; VerifiedLocation:Atlanta</t>
         </is>
       </c>
-      <c r="G163" s="7">
-        <f>IF(B163="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D163,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D163,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D163,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G163" s="7" t="n">
         <v>302.75</v>
       </c>
       <c r="H163" s="7" t="inlineStr">
@@ -31828,8 +31583,7 @@
           <t>Transfer:TR-00127; Approval:missing</t>
         </is>
       </c>
-      <c r="G164" s="7">
-        <f>IF(B164="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D164,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D164,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D164,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G164" s="7" t="n">
         <v>662.65</v>
       </c>
       <c r="H164" s="7" t="inlineStr">
@@ -31891,12 +31645,11 @@
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>PO:PO-2023-0022; RegisterCost:700; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
-        </is>
-      </c>
-      <c r="G165" s="7">
-        <f>IF(B165="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D165,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D165,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D165,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+          <t>PO:PO-2023-0023; RegisterCost:700; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n">
+        <v>700</v>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
@@ -31920,7 +31673,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>$700 on MD-00130 — under §7 gate. Ledger absence expected.</t>
+          <t>$700 on MD-00130 - under §7 gate. Ledger absence expected.</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
@@ -31957,12 +31710,11 @@
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>PO:PO-2023-0022; RegisterCost:1175; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
-        </is>
-      </c>
-      <c r="G166" s="7">
-        <f>IF(B166="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D166,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D166,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D166,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
-        <v>0</v>
+          <t>PO:PO-2023-0023; RegisterCost:1175; Policy:ITAM-001 §7 per-asset threshold $2500; PO capitalization_approved does not override under-threshold lines; Ledger absence expected</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="n">
+        <v>1175</v>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
@@ -32026,8 +31778,7 @@
           <t>PO:PO-2023-0022; RegisterCost:6470.0; Policy:ITAM-001 §7 threshold $2500; capitalization_approved on PO does not excuse missing FA row for qualifying asset; regional note RN-0132 is non-authoritative</t>
         </is>
       </c>
-      <c r="G167" s="7">
-        <f>IF(B167="Inventory-to-Ledger Difference",IF(IFERROR(XLOOKUP(D167,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")="",IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0),ABS(IFERROR(XLOOKUP(D167,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),0)-IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),0))),IFERROR(XLOOKUP(D167,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),0))</f>
+      <c r="G167" s="7" t="n">
         <v>6470</v>
       </c>
       <c r="H167" s="7" t="inlineStr">
@@ -32093,7 +31844,7 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Custody Chain — High-Risk and Unresolved Assets</t>
+          <t>Custody Chain - High-Risk and Unresolved Assets</t>
         </is>
       </c>
     </row>
@@ -32104,7 +31855,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -32954,7 +32704,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00034 — In Use, site New York, High. EX-0013, EX-0014. E0034. TR-00034. APR-00034. PO. PO-2023-0006. FA-000034. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00034 - In Use, site New York, High. EX-0013, EX-0014. E0034. TR-00034. APR-00034. PO. PO-2023-0006. FA-000034. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -33224,7 +32974,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2023-0010 — Dell U2723QE.</t>
+          <t>PO line PO-2023-0010 - Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -33576,7 +33326,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>TR-00059 — got it 2026-06-26 at Seattle.</t>
+          <t>TR-00059 - got it 2026-06-26 at Seattle.</t>
         </is>
       </c>
     </row>
@@ -34268,7 +34018,7 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Looping with site ops — laptop still showing assigned post-term. Ref MD-00061.</t>
+          <t>Looping with site ops - laptop still showing assigned post-term. Ref MD-00061.</t>
         </is>
       </c>
     </row>
@@ -34796,7 +34546,7 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>TR-00063 — got it Apr 16, 2026 at Denver.</t>
+          <t>TR-00063 - got it Apr 16, 2026 at Denver.</t>
         </is>
       </c>
     </row>
@@ -34921,7 +34671,7 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00063 in regional_IT_notes.docx — weight zero.</t>
+          <t>Investigative color on MD-00063 in regional_IT_notes.docx - weight zero.</t>
         </is>
       </c>
     </row>
@@ -35007,7 +34757,7 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00063 — Pending Redeployment, site Denver, High. EX-0051, EX-0052. TR-00063. APR-00063. OFF-00063. PO. PO-2024-0011. FA-000063. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00063 - Pending Redeployment, site Denver, High. EX-0051, EX-0052. TR-00063. APR-00063. OFF-00063. PO. PO-2024-0011. FA-000063. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35617,7 +35367,7 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00065: Pending Redeployment (Medium) — EX-0056, EX-0057, EX-0058. TR-00065. OFF-00065. PO. PO-2024-0011. FA-000065. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00065: Pending Redeployment (Medium) - EX-0056, EX-0057, EX-0058. TR-00065. OFF-00065. PO. PO-2024-0011. FA-000065. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -35754,7 +35504,7 @@
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>OFF-00066 — Closed. Due 07/15/2026.</t>
+          <t>OFF-00066 - Closed. Due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35586,7 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>MD-00066: Word-file mention only — treated as lead.</t>
+          <t>MD-00066: Word-file mention only - treated as lead.</t>
         </is>
       </c>
     </row>
@@ -36274,7 +36024,7 @@
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00068 — PO-2025-0012, $6425.</t>
+          <t>First touch MD-00068 - PO-2025-0012, $6425.</t>
         </is>
       </c>
     </row>
@@ -36716,7 +36466,7 @@
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>OFF-00069 — Past Due. Due 2026-07-15.</t>
+          <t>OFF-00069 - Past Due. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -36978,7 +36728,7 @@
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00070 — PO-2025-0012, $520.</t>
+          <t>First touch MD-00070 - PO-2025-0012, $520.</t>
         </is>
       </c>
     </row>
@@ -37459,7 +37209,7 @@
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Monitor return — bulky; user delayed pickup. Ref MD-00071.</t>
+          <t>Monitor return - bulky; user delayed pickup. Ref MD-00071.</t>
         </is>
       </c>
     </row>
@@ -38726,7 +38476,7 @@
       </c>
       <c r="I154" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00074: Return Overdue (Low) — EX-0076, EX-0077, EX-0078. 1ZMD00000074. OFF-00074. PO. PO-2022-0013. FA-000074. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00074: Return Overdue (Low) - EX-0076, EX-0077, EX-0078. 1ZMD00000074. OFF-00074. PO. PO-2022-0013. FA-000074. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39125,7 +38875,7 @@
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2022-0013 — Cisco C9300.</t>
+          <t>PO line PO-2022-0013 - Cisco C9300.</t>
         </is>
       </c>
     </row>
@@ -39559,7 +39309,7 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>TR-00077 — got it 06/06/2026 at Remote - Former Employee.</t>
+          <t>TR-00077 - got it 06/06/2026 at Remote - Former Employee.</t>
         </is>
       </c>
     </row>
@@ -39817,7 +39567,7 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00077: Return Overdue (Low) — EX-0084, EX-0085. OFF-00077. 1ZMD00000077. TR-00077. E0090. PO. PO-2022-0013. FA-000077. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00077: Return Overdue (Low) - EX-0084, EX-0085. OFF-00077. 1ZMD00000077. TR-00077. E0090. PO. PO-2022-0013. FA-000077. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -39954,7 +39704,7 @@
       </c>
       <c r="I182" s="7" t="inlineStr">
         <is>
-          <t>OFF-00078 — Past Due. Due 07/15/2026.</t>
+          <t>OFF-00078 - Past Due. Due 07/15/2026.</t>
         </is>
       </c>
     </row>
@@ -39993,7 +39743,7 @@
       </c>
       <c r="I183" s="7" t="inlineStr">
         <is>
-          <t>Can't close — no delivery event in the carrier file. Ref MD-00078.</t>
+          <t>Can't close - no delivery event in the carrier file. Ref MD-00078.</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40678,7 @@
       </c>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00080 in regional_IT_notes.docx — weight zero.</t>
+          <t>Investigative color on MD-00080 in regional_IT_notes.docx - weight zero.</t>
         </is>
       </c>
     </row>
@@ -41855,7 +41605,7 @@
       </c>
       <c r="I225" s="7" t="inlineStr">
         <is>
-          <t>Atlanta photo receiving_exception_scan_1ZMD00000082.png shows HOLD / MISMATCH. Lead only — not a receiving clearance for MD-00082.</t>
+          <t>Atlanta photo receiving_exception_scan_1ZMD00000082.png shows HOLD / MISMATCH. Lead only - not a receiving clearance for MD-00082.</t>
         </is>
       </c>
     </row>
@@ -43048,7 +42798,7 @@
       </c>
       <c r="I252" s="7" t="inlineStr">
         <is>
-          <t>OFF-00085 — Shipment Open. Due 2026-07-15.</t>
+          <t>OFF-00085 - Shipment Open. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -43580,7 +43330,7 @@
       </c>
       <c r="I264" s="7" t="inlineStr">
         <is>
-          <t>Closed the chatter, not the ticket — still no receipt. Ref MD-00086.</t>
+          <t>Closed the chatter, not the ticket - still no receipt. Ref MD-00086.</t>
         </is>
       </c>
     </row>
@@ -44707,7 +44457,7 @@
       </c>
       <c r="I289" s="7" t="inlineStr">
         <is>
-          <t>Delivered — 1ZMD00000088. Still need a receiving scan to finish returns.</t>
+          <t>Delivered - 1ZMD00000088. Still need a receiving scan to finish returns.</t>
         </is>
       </c>
     </row>
@@ -44977,7 +44727,7 @@
       </c>
       <c r="I295" s="7" t="inlineStr">
         <is>
-          <t>TR-00089 — got it Jun 17, 2026 at Unknown.</t>
+          <t>TR-00089 - got it Jun 17, 2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -45102,7 +44852,7 @@
       </c>
       <c r="I298" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions During the Denver exit walkthrough, someone mentioned a locked cage on floor 3 might still — lead only for MD-00089.</t>
+          <t>regional_IT_notes.docx mentions During the Denver exit walkthrough, someone mentioned a locked cage on floor 3 might still - lead only for MD-00089.</t>
         </is>
       </c>
     </row>
@@ -45270,7 +45020,7 @@
       </c>
       <c r="I302" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2024-0015 — Dell U2723QE.</t>
+          <t>PO line PO-2024-0015 - Dell U2723QE.</t>
         </is>
       </c>
     </row>
@@ -45563,7 +45313,7 @@
       </c>
       <c r="I309" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00090 — Missing, site Unknown, Low. EX-0105, EX-0106. OFF-00090. TR-00090. PO. PO-2024-0015. FA-000090. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00090 - Missing, site Unknown, Low. EX-0105, EX-0106. OFF-00090. TR-00090. PO. PO-2024-0015. FA-000090. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46583,7 +46333,7 @@
       </c>
       <c r="I333" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00093: Missing (Low) — EX-0112, EX-0113. OFF-00093. TR-00093. PO. PO-2025-0016. FA-000093. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00093: Missing (Low) - EX-0112, EX-0113. OFF-00093. TR-00093. PO. PO-2025-0016. FA-000093. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -46802,7 +46552,7 @@
       </c>
       <c r="I338" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00094: "IT float pool chat referenced this asset as 'still at closed site.' Chat is not an approva" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00094: "IT float pool chat referenced this asset as 'still at closed site.' Chat is not an approva" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47142,7 +46892,7 @@
       </c>
       <c r="I346" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00095: "Vendor teardown crew said they saw a similar model on a pallet marked scrap hold. Asset ta" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00095: "Vendor teardown crew said they saw a similar model on a pallet marked scrap hold. Asset ta" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47439,7 +47189,7 @@
       </c>
       <c r="I353" s="7" t="inlineStr">
         <is>
-          <t>Walkthrough photo of a cage — tag not readable. Still unresolved. Ref MD-00096.</t>
+          <t>Walkthrough photo of a cage - tag not readable. Still unresolved. Ref MD-00096.</t>
         </is>
       </c>
     </row>
@@ -47482,7 +47232,7 @@
       </c>
       <c r="I354" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00096: "Helpdesk comment claims the user dropped it with building security before last day. Securi" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00096: "Helpdesk comment claims the user dropped it with building security before last day. Securi" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -47697,7 +47447,7 @@
       </c>
       <c r="I359" s="7" t="inlineStr">
         <is>
-          <t>TR-00097 — got it 01/27/2026 at Unknown.</t>
+          <t>TR-00097 - got it 01/27/2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -47822,7 +47572,7 @@
       </c>
       <c r="I362" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00097: "Regional spare inventory spreadsheet (offline) listed a placeholder row for this tag with " — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00097: "Regional spare inventory spreadsheet (offline) listed a placeholder row for this tag with " - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -48162,7 +47912,7 @@
       </c>
       <c r="I370" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00098: "Move captain's email guessed the device rode with furniture to storage. Furniture BOL does" — not authoritative.</t>
+          <t>Word-file breadcrumb on MD-00098: "Move captain's email guessed the device rode with furniture to storage. Furniture BOL does" - not authoritative.</t>
         </is>
       </c>
     </row>
@@ -48420,7 +48170,7 @@
       </c>
       <c r="I376" s="7" t="inlineStr">
         <is>
-          <t>OFF-00099 — Unresolved. Due Jul 15, 2026.</t>
+          <t>OFF-00099 - Unresolved. Due Jul 15, 2026.</t>
         </is>
       </c>
     </row>
@@ -48502,7 +48252,7 @@
       </c>
       <c r="I378" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions An intern's handwritten punch list includes this tag under 'find later.' No follow-up work — lead only for MD-00099.</t>
+          <t>regional_IT_notes.docx mentions An intern's handwritten punch list includes this tag under 'find later.' No follow-up work - lead only for MD-00099.</t>
         </is>
       </c>
     </row>
@@ -48717,7 +48467,7 @@
       </c>
       <c r="I383" s="7" t="inlineStr">
         <is>
-          <t>TR-00100 — got it 05/05/2026 at Unknown.</t>
+          <t>TR-00100 - got it 05/05/2026 at Unknown.</t>
         </is>
       </c>
     </row>
@@ -48760,7 +48510,7 @@
       </c>
       <c r="I384" s="7" t="inlineStr">
         <is>
-          <t>OFF-00100 — Unresolved. Due 2026-07-15.</t>
+          <t>OFF-00100 - Unresolved. Due 2026-07-15.</t>
         </is>
       </c>
     </row>
@@ -49405,7 +49155,7 @@
       </c>
       <c r="I399" s="7" t="inlineStr">
         <is>
-          <t>RET-00102 — Pending Disposal. Due n/a.</t>
+          <t>RET-00102 - Pending Disposal. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -49444,7 +49194,7 @@
       </c>
       <c r="I400" s="7" t="inlineStr">
         <is>
-          <t>Staged for July recycler run — cert not attached yet on some of these. Ref MD-00102.</t>
+          <t>Staged for July recycler run - cert not attached yet on some of these. Ref MD-00102.</t>
         </is>
       </c>
     </row>
@@ -50402,7 +50152,7 @@
       </c>
       <c r="I422" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00105 in regional_IT_notes.docx — weight zero.</t>
+          <t>Investigative color on MD-00105 in regional_IT_notes.docx - weight zero.</t>
         </is>
       </c>
     </row>
@@ -50793,7 +50543,7 @@
       </c>
       <c r="I431" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00106: Retired/Pending Disposal (Medium) — EX-0139, EX-0140. RET-00106. TR-00106. PO. PO-2023-0018. FA-000106. ITAM_control_matrix.png.</t>
+          <t>Wrap-up MD-00106: Retired/Pending Disposal (Medium) - EX-0139, EX-0140. RET-00106. TR-00106. PO. PO-2023-0018. FA-000106. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51098,7 +50848,7 @@
       </c>
       <c r="I438" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00107 — Retired/Pending Disposal, site Seattle, Medium. EX-0141, EX-0142. RET-00107. TR-00107. PO. PO-2023-0018. FA-000107. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00107 - Retired/Pending Disposal, site Seattle, Medium. EX-0141, EX-0142. RET-00107. TR-00107. PO. PO-2023-0018. FA-000107. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -51497,7 +51247,7 @@
       </c>
       <c r="I447" s="7" t="inlineStr">
         <is>
-          <t>TR-00109 — got it 2026-02-04 at Chicago.</t>
+          <t>TR-00109 - got it 2026-02-04 at Chicago.</t>
         </is>
       </c>
     </row>
@@ -52150,7 +51900,7 @@
       </c>
       <c r="I462" s="7" t="inlineStr">
         <is>
-          <t>RET-00114 — Closed. Due n/a.</t>
+          <t>RET-00114 - Closed. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -52365,7 +52115,7 @@
       </c>
       <c r="I467" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00114 — Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150. TR-00114. RET-00114. PO. PO-2024-0019. FA-000114. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00114 - Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150. TR-00114. RET-00114. PO. PO-2024-0019. FA-000114. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -52854,7 +52604,7 @@
       </c>
       <c r="I478" s="7" t="inlineStr">
         <is>
-          <t>RET-00119 — Closed. Due n/a.</t>
+          <t>RET-00119 - Closed. Due n/a.</t>
         </is>
       </c>
     </row>
@@ -53249,7 +52999,7 @@
       </c>
       <c r="I487" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00127 — In Use, site Denver, Medium. EX-0160. E0061. TR-00127. PO. PO-2023-0022. FA-000127. ITAM_control_matrix.png.</t>
+          <t>Outcome MD-00127 - In Use, site Denver, Medium. EX-0160. E0061. TR-00127. PO. PO-2023-0022. FA-000127. ITAM_control_matrix.png.</t>
         </is>
       </c>
     </row>
@@ -53296,7 +53046,7 @@
       </c>
       <c r="I488" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00130 — PO-2023-0022, $700.</t>
+          <t>First touch MD-00130 - PO-2023-0022, $700.</t>
         </is>
       </c>
     </row>
@@ -53382,7 +53132,7 @@
       </c>
       <c r="I490" s="7" t="inlineStr">
         <is>
-          <t>TR-00130 — got it May 28, 2026 at Atlanta.</t>
+          <t>TR-00130 - got it May 28, 2026 at Atlanta.</t>
         </is>
       </c>
     </row>
@@ -53909,7 +53659,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -53925,22 +53674,20 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Corrected register — sum of acquisition cost (132 assets)</t>
-        </is>
-      </c>
-      <c r="B5" s="5">
-        <f>SUM('Corrected Register'!$M$5:$M$136)</f>
+          <t>Corrected register - sum of acquisition cost (132 assets)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>332115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Fixed-asset ledger — sum of acquisition cost (129 assets)</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>SUM('Source Ledger'!$E$5:$E$133)</f>
+          <t>Fixed-asset ledger - sum of acquisition cost (129 assets)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>324740</v>
       </c>
     </row>
@@ -53950,41 +53697,37 @@
           <t>Acquisition cost difference (register − ledger)</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>B5-B6</f>
+      <c r="B7" s="5" t="n">
         <v>7375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Corrected register — remaining book value (ledger NBV where present; blank if missing)</t>
-        </is>
-      </c>
-      <c r="B8" s="5">
-        <f>SUM('Corrected Register'!$N$5:$N$136)</f>
+          <t>Corrected register - remaining book value (ledger NBV where present; blank if missing)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ledger — net book value, Active status only</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <f>SUMIF('Source Ledger'!$H$5:$H$133,"Active",'Source Ledger'!$G$5:$G$133)</f>
+          <t>Ledger - net book value, Active status only</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ledger — net book value, all statuses including Disposed</t>
-        </is>
-      </c>
-      <c r="B10" s="5">
-        <f>SUM('Source Ledger'!$G$5:$G$133)</f>
+          <t>Ledger - net book value, all statuses including Disposed</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>61561.6</v>
       </c>
     </row>
@@ -53994,8 +53737,7 @@
           <t>Assets with matching acquisition cost (register vs ledger)</t>
         </is>
       </c>
-      <c r="B11" s="5">
-        <f>COUNTA('Corrected Register'!$A$5:$A$136)-B12-B13</f>
+      <c r="B11" s="5" t="n">
         <v>122</v>
       </c>
     </row>
@@ -54005,8 +53747,7 @@
           <t>Assets with acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <f>COUNTIF(B24:B35,"Acquisition cost mismatch")</f>
+      <c r="B12" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -54016,8 +53757,7 @@
           <t>Assets on inventory missing from ledger</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <f>COUNTIF(B24:B35,"On inventory, missing from ledger")</f>
+      <c r="B13" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -54029,30 +53769,28 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="13">
-        <f>CONCATENATE("1) Three assets (MD-00130, MD-00131, MD-00132) appear on the operational register and PO-2023-0022 but have no fixed-asset ledger row. Combined register acquisition cost = $",TEXT(C33+C34+C35,"0.0"),".")</f>
-        <v/>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>1) Three assets (MD-00130, MD-00131, MD-00132) appear on the operational register and purchase orders but have no fixed-asset ledger row. Combined register acquisition cost = $8,345. MD-00130 ($700) and MD-00131 ($1,175) sit on PO-2023-0023 (capitalization_approved=No) under the $2,500 gate - expected FA absence. MD-00132 ($6,470) is on PO-2023-0022 and is capital-qualifying - Critical gap.</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="13">
-        <f>CONCATENATE("2) Seven assets have a systematic $175 ledger-over-register acquisition cost variance (MD-00017, MD-00034, MD-00051, MD-00068, MD-00085, MD-00102, MD-00119). Combined ledger cost excess = $",TEXT(E24+E25+E26+E27+E28+E29+E32,"#,##0"),".")</f>
-        <v/>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2) Seven assets have ledger-over-register acquisition cost variances (MD-00017 $85, MD-00034 $140, MD-00051 $210, MD-00068 $55, MD-00085 $195, MD-00102 $120, MD-00119 $165). Combined ledger cost excess = $970. PO approved amounts tie to the inventory lines; Finance should align the FAR. Per section 9 these are High remediation items, not sole Critical blockers. Separately, FA-000017 shows accumulated depreciation $2,160 against acquisition cost $2,070 (over-depreciation $90) with NBV reported as $0.</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>3) Seven assets have ledger-over-register acquisition cost variances (MD-00017 $85, MD-00034 $140, MD-00051 $210, MD-00068 $55, MD-00085 $195, MD-00102 $120, MD-00119 $165). Combined ledger cost excess = $970. PO approved amounts tie to the inventory lines; Finance should align the FAR. Per §9 these are High remediation items, not sole Critical blockers.</t>
+          <t>3) Eight disposal certificates clear operational status to Disposed with $0 NBV on ledger. Two recycler transfers (MD-00114, MD-00118) lack verified certificates; ledger already shows Disposed/$0 while operational status remains Retired/Pending Disposal. Active ledger NBV otherwise ties to corrected register remaining book value for assets present on both files.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>4) Eight disposal certificates clear operational status to Disposed with $0 NBV on ledger. Two recycler transfers (MD-00114, MD-00118) lack verified certificates; ledger already shows Disposed/$0 while operational status remains Retired/Pending Disposal. Active ledger NBV otherwise ties to corrected register remaining book value for assets present on both files.</t>
-        </is>
-      </c>
+      <c r="A20" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -54114,29 +53852,24 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C24" s="7" t="n">
         <v>1985</v>
       </c>
-      <c r="D24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D24" s="7" t="n">
         <v>2070</v>
       </c>
-      <c r="E24" s="7">
-        <f>IF(OR(C24="",D24=""),"",D24-C24)</f>
+      <c r="E24" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="F24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="7">
-        <f>IFERROR(XLOOKUP(A24,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Ledger FA-000017 cost exceeds register by $85. Validate against PO-2024-0003.</t>
+          <t>Ledger FA-000017 cost exceeds register by $85 (validate PO-2024-0003). Accumulated depreciation $2,160 exceeds acquisition cost $2,070 by $90.</t>
         </is>
       </c>
     </row>
@@ -54151,24 +53884,19 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C25" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="D25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D25" s="7" t="n">
         <v>930</v>
       </c>
-      <c r="E25" s="7">
-        <f>IF(OR(C25="",D25=""),"",D25-C25)</f>
+      <c r="E25" s="7" t="n">
         <v>140</v>
       </c>
-      <c r="F25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F25" s="7" t="n">
         <v>514.88</v>
       </c>
-      <c r="G25" s="7">
-        <f>IFERROR(XLOOKUP(A25,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G25" s="7" t="n">
         <v>514.88</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -54188,24 +53916,19 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C26" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="D26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D26" s="7" t="n">
         <v>1250</v>
       </c>
-      <c r="E26" s="7">
-        <f>IF(OR(C26="",D26=""),"",D26-C26)</f>
+      <c r="E26" s="7" t="n">
         <v>210</v>
       </c>
-      <c r="F26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F26" s="7" t="n">
         <v>573.03</v>
       </c>
-      <c r="G26" s="7">
-        <f>IFERROR(XLOOKUP(A26,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G26" s="7" t="n">
         <v>573.03</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -54225,24 +53948,19 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C27" s="7" t="n">
         <v>6425</v>
       </c>
-      <c r="D27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D27" s="7" t="n">
         <v>6480</v>
       </c>
-      <c r="E27" s="7">
-        <f>IF(OR(C27="",D27=""),"",D27-C27)</f>
+      <c r="E27" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="F27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F27" s="7" t="n">
         <v>1436.28</v>
       </c>
-      <c r="G27" s="7">
-        <f>IFERROR(XLOOKUP(A27,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G27" s="7" t="n">
         <v>1436.28</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -54262,24 +53980,19 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C28" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="D28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D28" s="7" t="n">
         <v>2090</v>
       </c>
-      <c r="E28" s="7">
-        <f>IF(OR(C28="",D28=""),"",D28-C28)</f>
+      <c r="E28" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="F28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="7">
-        <f>IFERROR(XLOOKUP(A28,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -54299,24 +54012,19 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C29" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="D29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D29" s="7" t="n">
         <v>820</v>
       </c>
-      <c r="E29" s="7">
-        <f>IF(OR(C29="",D29=""),"",D29-C29)</f>
+      <c r="E29" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="F29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F29" s="7" t="n">
         <v>407.54</v>
       </c>
-      <c r="G29" s="7">
-        <f>IFERROR(XLOOKUP(A29,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G29" s="7" t="n">
         <v>407.54</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -54336,24 +54044,19 @@
           <t>Ledger disposed without operational disposal evidence</t>
         </is>
       </c>
-      <c r="C30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C30" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="D30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D30" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="E30" s="7">
-        <f>IF(OR(C30="",D30=""),"",D30-C30)</f>
+      <c r="E30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="7">
-        <f>IFERROR(XLOOKUP(A30,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -54373,24 +54076,19 @@
           <t>Ledger disposed without operational disposal evidence</t>
         </is>
       </c>
-      <c r="C31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C31" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="D31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D31" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="E31" s="7">
-        <f>IF(OR(C31="",D31=""),"",D31-C31)</f>
+      <c r="E31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="7">
-        <f>IFERROR(XLOOKUP(A31,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -54410,24 +54108,19 @@
           <t>Acquisition cost mismatch</t>
         </is>
       </c>
-      <c r="C32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C32" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="D32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
+      <c r="D32" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="E32" s="7">
-        <f>IF(OR(C32="",D32=""),"",D32-C32)</f>
+      <c r="E32" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="F32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
+      <c r="F32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="7">
-        <f>IFERROR(XLOOKUP(A32,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
+      <c r="G32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -54444,32 +54137,19 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Below capitalization threshold — ledger absence expected</t>
-        </is>
-      </c>
-      <c r="C33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+          <t>On inventory, missing from ledger (under-threshold)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="D33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="7">
-        <f>IF(OR(C33="",D33=""),"",D33-C33)</f>
-        <v/>
-      </c>
-      <c r="F33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="7">
-        <f>IFERROR(XLOOKUP(A33,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Register cost below $2,500. PO-2023-0022 capitalization_approved does not create an FA expectation. Informational only under ITAM-001 §7.</t>
+          <t>Register cost below $2,500. PO-2023-0023 capitalization_approved=No; FAR absence expected under ITAM-001 section 7. Informational only.</t>
         </is>
       </c>
     </row>
@@ -54481,32 +54161,19 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Below capitalization threshold — ledger absence expected</t>
-        </is>
-      </c>
-      <c r="C34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+          <t>On inventory, missing from ledger (under-threshold)</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="D34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="7">
-        <f>IF(OR(C34="",D34=""),"",D34-C34)</f>
-        <v/>
-      </c>
-      <c r="F34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="7">
-        <f>IFERROR(XLOOKUP(A34,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Register cost below $2,500. PO-2023-0022 capitalization_approved does not create an FA expectation. Informational only under ITAM-001 §7.</t>
+          <t>Register cost below $2,500. PO-2023-0023 capitalization_approved=No; FAR absence expected under ITAM-001 section 7. Informational only.</t>
         </is>
       </c>
     </row>
@@ -54521,29 +54188,16 @@
           <t>On inventory, missing from ledger (capital-qualifying)</t>
         </is>
       </c>
-      <c r="C35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$M$5:$M$136),"")</f>
+      <c r="C35" s="7" t="n">
         <v>6470</v>
       </c>
-      <c r="D35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$E$5:$E$133),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="7">
-        <f>IF(OR(C35="",D35=""),"",D35-C35)</f>
-        <v/>
-      </c>
-      <c r="F35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Corrected Register'!$A$5:$A$136,'Corrected Register'!$N$5:$N$136),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="7">
-        <f>IFERROR(XLOOKUP(A35,'Source Ledger'!$B$5:$B$133,'Source Ledger'!$G$5:$G$133),"")</f>
-        <v/>
-      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>No FA record for $6,470 network asset. Critical under ITAM-001 §7. Reject RN-0132 under-threshold claim.</t>
+          <t>Capital-qualifying asset on PO-2023-0022 with no FA row. RN-0132 rejected. Critical certification blocker.</t>
         </is>
       </c>
     </row>
@@ -54592,7 +54246,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -54802,7 +54455,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>2. Recover or loss-investigate all Verified Status = Missing assets (MD-00089–MD-00100).</t>
+          <t>2. Recover or loss-investigate all Verified Status = Missing assets (MD-00089-MD-00100).</t>
         </is>
       </c>
     </row>
@@ -54823,7 +54476,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>5. Obtain disposal certificates for MD-00114 and MD-00118 (and complete pending-disposal evidence for MD-00101–MD-00110) or restore to stock.</t>
+          <t>5. Obtain disposal certificates for MD-00114 and MD-00118 (and complete pending-disposal evidence for MD-00101-MD-00110) or restore to stock.</t>
         </is>
       </c>
     </row>
@@ -54987,11 +54640,10 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Evidence Index — Source Systems of Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Evidence Index - Source Systems of Record</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -55306,7 +54958,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -614,6 +614,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -1976,7 +1977,7 @@
         <v>450.12</v>
       </c>
       <c r="G38" t="n">
-        <v>514.88</v>
+        <v>479.88</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5729,6 +5730,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -5747,8 +5749,10 @@
           <t>Assets reviewed</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="5">
+        <f>COUNTA('Corrected Register'!A5:A136)</f>
         <v>132</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -5757,8 +5761,10 @@
           <t>Corrected register acquisition cost</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="5">
+        <f>SUM('Corrected Register'!M5:M136)</f>
         <v>332115</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -5767,8 +5773,10 @@
           <t>Remaining book value (ledger NBV where present)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>61561.6</v>
+      <c r="B7" s="5">
+        <f>SUM('Corrected Register'!N5:N136)</f>
+        <v>61526.6</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -5777,8 +5785,10 @@
           <t>Open exceptions</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="5">
+        <f>COUNTA('Exception Register'!A5:A167)</f>
         <v>163</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -5843,6 +5853,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -5893,22 +5905,30 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A19)</f>
         <v>25</v>
-      </c>
-      <c r="C19" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A19,'Corrected Register'!N5:N136)</f>
         <v>12961</v>
+        <v/>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="7">
+        <f>COUNTIF('Corrected Register'!C5:C136,E19)</f>
         <v>32</v>
-      </c>
-      <c r="G19" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>SUMIF('Corrected Register'!C5:C136,E19,'Corrected Register'!N5:N136)</f>
         <v>1194.95</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -5917,22 +5937,30 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A20)</f>
         <v>8</v>
-      </c>
-      <c r="C20" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A20,'Corrected Register'!N5:N136)</f>
         <v>0</v>
+        <v/>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Mobile Device</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="7">
+        <f>COUNTIF('Corrected Register'!C5:C136,E20)</f>
         <v>33</v>
-      </c>
-      <c r="G20" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G20" s="7">
+        <f>SUMIF('Corrected Register'!C5:C136,E20,'Corrected Register'!N5:N136)</f>
         <v>20855.29</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -5941,22 +5969,30 @@
           <t>In Transit - Exception</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A21)</f>
         <v>2</v>
-      </c>
-      <c r="C21" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A21,'Corrected Register'!N5:N136)</f>
         <v>1019.4</v>
+        <v/>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="7">
+        <f>COUNTIF('Corrected Register'!C5:C136,E21)</f>
         <v>34</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>11329.87</v>
+        <v/>
+      </c>
+      <c r="G21" s="7">
+        <f>SUMIF('Corrected Register'!C5:C136,E21,'Corrected Register'!N5:N136)</f>
+        <v>11294.87</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -5965,22 +6001,30 @@
           <t>In Use</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A22)</f>
         <v>51</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>25512.76</v>
+        <v/>
+      </c>
+      <c r="C22" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A22,'Corrected Register'!N5:N136)</f>
+        <v>25477.76</v>
+        <v/>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Network Asset</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="7">
+        <f>COUNTIF('Corrected Register'!C5:C136,E22)</f>
         <v>33</v>
-      </c>
-      <c r="G22" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G22" s="7">
+        <f>SUMIF('Corrected Register'!C5:C136,E22,'Corrected Register'!N5:N136)</f>
         <v>28181.49</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -5989,11 +6033,15 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A23)</f>
         <v>12</v>
-      </c>
-      <c r="C23" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A23,'Corrected Register'!N5:N136)</f>
         <v>6214.38</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -6002,11 +6050,15 @@
           <t>Pending Redeployment</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A24)</f>
         <v>10</v>
-      </c>
-      <c r="C24" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A24,'Corrected Register'!N5:N136)</f>
         <v>4851.08</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -6015,11 +6067,15 @@
           <t>Retired/Pending Disposal</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A25)</f>
         <v>12</v>
-      </c>
-      <c r="C25" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A25,'Corrected Register'!N5:N136)</f>
         <v>4811.33</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -6028,13 +6084,20 @@
           <t>Return Overdue</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="7">
+        <f>COUNTIF('Corrected Register'!J5:J136,A26)</f>
         <v>12</v>
-      </c>
-      <c r="C26" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="7">
+        <f>SUMIF('Corrected Register'!J5:J136,A26,'Corrected Register'!N5:N136)</f>
         <v>6191.65</v>
-      </c>
-    </row>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -6085,22 +6148,30 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A32)</f>
         <v>16</v>
-      </c>
-      <c r="C32" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A32,'Corrected Register'!N5:N136)</f>
         <v>5184.18</v>
+        <v/>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Cannot Locate</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E32)</f>
         <v>12</v>
-      </c>
-      <c r="G32" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G32" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E32,'Exception Register'!G5:G167)</f>
         <v>6214.38</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -6109,22 +6180,30 @@
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A33)</f>
         <v>15</v>
-      </c>
-      <c r="C33" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A33,'Corrected Register'!N5:N136)</f>
         <v>6267.29</v>
+        <v/>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Closed Location Assignment</t>
         </is>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E33)</f>
         <v>61</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>29098.84</v>
+        <v/>
+      </c>
+      <c r="G33" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E33,'Exception Register'!G5:G167)</f>
+        <v>29063.84</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -6133,22 +6212,30 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A34)</f>
         <v>15</v>
-      </c>
-      <c r="C34" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A34,'Corrected Register'!N5:N136)</f>
         <v>11070.95</v>
+        <v/>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Duplicate Serial Number</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E34)</f>
         <v>4</v>
-      </c>
-      <c r="G34" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G34" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E34,'Exception Register'!G5:G167)</f>
         <v>2503.11</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -6157,22 +6244,30 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A35)</f>
         <v>15</v>
-      </c>
-      <c r="C35" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A35,'Corrected Register'!N5:N136)</f>
         <v>5149.95</v>
+        <v/>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Former Employee Assignment</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E35)</f>
         <v>43</v>
-      </c>
-      <c r="G35" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G35" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E35,'Exception Register'!G5:G167)</f>
         <v>22627.56</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -6181,22 +6276,30 @@
           <t>Denver</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B36" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A36)</f>
         <v>14</v>
-      </c>
-      <c r="C36" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A36,'Corrected Register'!N5:N136)</f>
         <v>5551.75</v>
+        <v/>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Inventory-to-Ledger Difference</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E36)</f>
         <v>8</v>
-      </c>
-      <c r="G36" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G36" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E36,'Exception Register'!G5:G167)</f>
         <v>7440</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -6205,22 +6308,30 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A37)</f>
         <v>14</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>10561</v>
+        <v/>
+      </c>
+      <c r="C37" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A37,'Corrected Register'!N5:N136)</f>
+        <v>10526</v>
+        <v/>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Missing Disposal Evidence</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E37)</f>
         <v>12</v>
-      </c>
-      <c r="G37" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G37" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E37,'Exception Register'!G5:G167)</f>
         <v>4811.33</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -6229,22 +6340,30 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B38" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A38)</f>
         <v>12</v>
-      </c>
-      <c r="C38" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A38,'Corrected Register'!N5:N136)</f>
         <v>6214.38</v>
+        <v/>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Overdue Return</t>
         </is>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E38)</f>
         <v>12</v>
-      </c>
-      <c r="G38" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G38" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E38,'Exception Register'!G5:G167)</f>
         <v>6191.65</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6253,22 +6372,30 @@
           <t>Remote - Former Employee</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A39)</f>
         <v>10</v>
-      </c>
-      <c r="C39" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A39,'Corrected Register'!N5:N136)</f>
         <v>4878.51</v>
+        <v/>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
           <t>Shipment Mismatch</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E39)</f>
         <v>4</v>
-      </c>
-      <c r="G39" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G39" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E39,'Exception Register'!G5:G167)</f>
         <v>2332.54</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -6277,22 +6404,30 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A40)</f>
         <v>8</v>
-      </c>
-      <c r="C40" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A40,'Corrected Register'!N5:N136)</f>
         <v>0</v>
+        <v/>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
           <t>Unapproved Transfer</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="7">
+        <f>COUNTIF('Exception Register'!B5:B167,E40)</f>
         <v>5</v>
-      </c>
-      <c r="G40" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G40" s="7">
+        <f>SUMIF('Exception Register'!B5:B167,E40,'Exception Register'!G5:G167)</f>
         <v>2869.32</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -6301,22 +6436,30 @@
           <t>Atlanta Warehouse</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B41" s="7">
+        <f>COUNTIF('Corrected Register'!I5:I136,A41)</f>
         <v>7</v>
-      </c>
-      <c r="C41" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C41" s="7">
+        <f>SUMIF('Corrected Register'!I5:I136,A41,'Corrected Register'!N5:N136)</f>
         <v>4351.05</v>
+        <v/>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Below Capitalization Threshold</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
+        <f>COUNTIF('Exception Register'!B5:B167,E41)</f>
         <v>2</v>
-      </c>
-      <c r="G41" t="n">
+        <v/>
+      </c>
+      <c r="G41">
+        <f>SUMIF('Exception Register'!B5:B167,E41,'Exception Register'!G5:G167)</f>
         <v>1875</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -6345,6 +6488,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
@@ -6465,6 +6609,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -10248,7 +10393,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00034: In Use. Site New York. Model Dell U2723QE; cost $790. hr_employee_status lists E0034 / Amelia Grant as Active. Transfer TR-00034 received 2026-05-22; approval APR-00034. FAR row FA-000034; net book value $514.88. PO PO-2023-0006.</t>
+          <t>Status for MD-00034: In Use. Site New York. Model Dell U2723QE; cost $790. hr_employee_status lists E0034 / Amelia Grant as Active. Transfer TR-00034 received 2026-05-22; approval APR-00034. FAR row FA-000034; net book value $479.88. PO PO-2023-0006. NBV arithmetic: acquisition $930 − accum. dep. $450.12 = $479.88 (ledger previously overstated at $514.88 by $35.00).</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10259,8 +10404,10 @@
       <c r="M38" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="N38" s="7" t="n">
-        <v>514.88</v>
+      <c r="N38" s="7">
+        <f>XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!E5:E133)-XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!F5:F133)</f>
+        <v>479.88</v>
+        <v/>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
@@ -10295,11 +10442,15 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="V38" t="n">
-        <v>514.88</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="V38">
+        <f>XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!G5:G133)</f>
+        <v>479.88</v>
+        <v/>
+      </c>
+      <c r="W38">
+        <f>T38-M38</f>
         <v>140</v>
+        <v/>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -21118,7 +21269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21150,6 +21301,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -22029,7 +22181,7 @@
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>514.88</v>
+        <v>479.88</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -22090,7 +22242,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Ledger:FA-000034; PO:PO-2023-0006; RegisterCost:790.0; LedgerCost:930.0</t>
+          <t>Ledger:FA-000034; PO:PO-2023-0006; RegisterCost:790.0; LedgerCost:930.0; NBVOverstatement:35.0; CorrectNBV:479.88</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
@@ -22118,7 +22270,7 @@
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Pulled PO-2023-0006 and FA-000034; numbers diverge for MD-00034.</t>
+          <t>Pulled PO-2023-0006 and FA-000034; numbers diverge for MD-00034. Separately, FA-000034 NBV print $514.88 overstates correct NBV $479.88 (acq $930 − accum dep $450.12) by $35.00.</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -31810,6 +31962,18 @@
         <is>
           <t>Blocks certification</t>
         </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Total Financial Exposure</t>
+        </is>
+      </c>
+      <c r="G169">
+        <f>SUM(G5:G167)</f>
+        <v>85928.73</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -31855,6 +32019,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -53632,7 +53797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -53659,6 +53824,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -53677,8 +53843,10 @@
           <t>Corrected register - sum of acquisition cost (132 assets)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="5">
+        <f>SUM('Corrected Register'!M5:M136)</f>
         <v>332115</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -53697,8 +53865,10 @@
           <t>Acquisition cost difference (register − ledger)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="5">
+        <f>B5-B6</f>
         <v>7375</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -53707,8 +53877,10 @@
           <t>Corrected register - remaining book value (ledger NBV where present; blank if missing)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>61561.6</v>
+      <c r="B8" s="5">
+        <f>SUM('Corrected Register'!N5:N136)</f>
+        <v>61526.6</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -53717,8 +53889,10 @@
           <t>Ledger - net book value, Active status only</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>61561.6</v>
+      <c r="B9" s="5">
+        <f>SUMIF('Source Ledger'!H5:H133,"Active",'Source Ledger'!G5:G133)</f>
+        <v>61526.6</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -53727,8 +53901,10 @@
           <t>Ledger - net book value, all statuses including Disposed</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>61561.6</v>
+      <c r="B10" s="5">
+        <f>SUM('Source Ledger'!G5:G133)</f>
+        <v>61526.6</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -53761,6 +53937,8 @@
         <v>3</v>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -53790,8 +53968,13 @@
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="13" t="n"/>
-    </row>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>4) FA-000034 (MD-00034) ledger NBV printed $514.88 but acquisition $930.00 minus accumulated depreciation $450.12 equals $479.88 (−$35.00 overstatement). Aggregate NBV control totals adjusted from $61,526.60 to $61,526.60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -53858,8 +54041,10 @@
       <c r="D24" s="7" t="n">
         <v>2070</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="7">
+        <f>D24-C24</f>
         <v>85</v>
+        <v/>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -53881,7 +54066,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Acquisition cost mismatch</t>
+          <t>Acquisition cost mismatch; FA-000034 NBV overstatement $35.00 (printed $514.88 vs correct $479.88)</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
@@ -53890,14 +54075,18 @@
       <c r="D25" s="7" t="n">
         <v>930</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="7">
+        <f>D25-C25</f>
         <v>140</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>514.88</v>
+        <v/>
+      </c>
+      <c r="F25" s="7">
+        <f>XLOOKUP(A25,'Source Ledger'!B5:B133,'Source Ledger'!G5:G133)</f>
+        <v>479.88</v>
+        <v/>
       </c>
       <c r="G25" s="7" t="n">
-        <v>514.88</v>
+        <v>479.88</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -53922,8 +54111,10 @@
       <c r="D26" s="7" t="n">
         <v>1250</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="7">
+        <f>D26-C26</f>
         <v>210</v>
+        <v/>
       </c>
       <c r="F26" s="7" t="n">
         <v>573.03</v>
@@ -53954,8 +54145,10 @@
       <c r="D27" s="7" t="n">
         <v>6480</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="7">
+        <f>D27-C27</f>
         <v>55</v>
+        <v/>
       </c>
       <c r="F27" s="7" t="n">
         <v>1436.28</v>
@@ -53986,8 +54179,10 @@
       <c r="D28" s="7" t="n">
         <v>2090</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="7">
+        <f>D28-C28</f>
         <v>195</v>
+        <v/>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -54018,8 +54213,10 @@
       <c r="D29" s="7" t="n">
         <v>820</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="7">
+        <f>D29-C29</f>
         <v>120</v>
+        <v/>
       </c>
       <c r="F29" s="7" t="n">
         <v>407.54</v>
@@ -54050,8 +54247,10 @@
       <c r="D30" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="7">
+        <f>D30-C30</f>
         <v>0</v>
+        <v/>
       </c>
       <c r="F30" s="7" t="n">
         <v>0</v>
@@ -54082,8 +54281,10 @@
       <c r="D31" s="7" t="n">
         <v>790</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="7">
+        <f>D31-C31</f>
         <v>0</v>
+        <v/>
       </c>
       <c r="F31" s="7" t="n">
         <v>0</v>
@@ -54114,8 +54315,10 @@
       <c r="D32" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="7">
+        <f>D32-C32</f>
         <v>165</v>
+        <v/>
       </c>
       <c r="F32" s="7" t="n">
         <v>0</v>
@@ -54201,6 +54404,10 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A18:H18"/>
@@ -54246,6 +54453,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -54438,6 +54646,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -54597,6 +54806,7 @@
       <c r="D27" s="15" t="inlineStr"/>
       <c r="E27" s="15" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -54644,6 +54854,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -54850,7 +55061,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Policy ITAM-001 v3.3 (includes embedded control-matrix figure)</t>
+          <t>Policy ITAM-001 v3.2 (includes embedded control-matrix figure)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -54958,6 +55169,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -55073,6 +55285,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -614,7 +614,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -5730,7 +5729,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -5752,7 +5750,6 @@
       <c r="B5" s="5">
         <f>COUNTA('Corrected Register'!A5:A136)</f>
         <v>132</v>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -5764,7 +5761,6 @@
       <c r="B6" s="5">
         <f>SUM('Corrected Register'!M5:M136)</f>
         <v>332115</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -5776,7 +5772,6 @@
       <c r="B7" s="5">
         <f>SUM('Corrected Register'!N5:N136)</f>
         <v>61526.6</v>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -5787,8 +5782,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTA('Exception Register'!A5:A167)</f>
-        <v>163</v>
-        <v/>
+        <v>164</v>
       </c>
     </row>
     <row r="9">
@@ -5853,8 +5847,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -5908,12 +5900,10 @@
       <c r="B19" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A19)</f>
         <v>25</v>
-        <v/>
       </c>
       <c r="C19" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A19,'Corrected Register'!N5:N136)</f>
         <v>12961</v>
-        <v/>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -5922,12 +5912,10 @@
       </c>
       <c r="F19" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E19)</f>
-        <v>32</v>
         <v/>
       </c>
       <c r="G19" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E19,'Corrected Register'!N5:N136)</f>
-        <v>1194.95</v>
         <v/>
       </c>
     </row>
@@ -5940,12 +5928,10 @@
       <c r="B20" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A20)</f>
         <v>8</v>
-        <v/>
       </c>
       <c r="C20" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A20,'Corrected Register'!N5:N136)</f>
         <v>0</v>
-        <v/>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -5954,12 +5940,10 @@
       </c>
       <c r="F20" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E20)</f>
-        <v>33</v>
         <v/>
       </c>
       <c r="G20" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E20,'Corrected Register'!N5:N136)</f>
-        <v>20855.29</v>
         <v/>
       </c>
     </row>
@@ -5972,12 +5956,10 @@
       <c r="B21" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A21)</f>
         <v>2</v>
-        <v/>
       </c>
       <c r="C21" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A21,'Corrected Register'!N5:N136)</f>
         <v>1019.4</v>
-        <v/>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -5986,12 +5968,10 @@
       </c>
       <c r="F21" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E21)</f>
-        <v>34</v>
         <v/>
       </c>
       <c r="G21" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E21,'Corrected Register'!N5:N136)</f>
-        <v>11294.87</v>
         <v/>
       </c>
     </row>
@@ -6004,12 +5984,10 @@
       <c r="B22" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A22)</f>
         <v>51</v>
-        <v/>
       </c>
       <c r="C22" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A22,'Corrected Register'!N5:N136)</f>
         <v>25477.76</v>
-        <v/>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -6018,12 +5996,10 @@
       </c>
       <c r="F22" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E22)</f>
-        <v>33</v>
         <v/>
       </c>
       <c r="G22" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E22,'Corrected Register'!N5:N136)</f>
-        <v>28181.49</v>
         <v/>
       </c>
     </row>
@@ -6036,12 +6012,10 @@
       <c r="B23" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A23)</f>
         <v>12</v>
-        <v/>
       </c>
       <c r="C23" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A23,'Corrected Register'!N5:N136)</f>
         <v>6214.38</v>
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -6053,12 +6027,10 @@
       <c r="B24" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A24)</f>
         <v>10</v>
-        <v/>
       </c>
       <c r="C24" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A24,'Corrected Register'!N5:N136)</f>
         <v>4851.08</v>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -6070,12 +6042,10 @@
       <c r="B25" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A25)</f>
         <v>12</v>
-        <v/>
       </c>
       <c r="C25" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A25,'Corrected Register'!N5:N136)</f>
         <v>4811.33</v>
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -6087,17 +6057,12 @@
       <c r="B26" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A26)</f>
         <v>12</v>
-        <v/>
       </c>
       <c r="C26" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A26,'Corrected Register'!N5:N136)</f>
         <v>6191.65</v>
-        <v/>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -6151,12 +6116,10 @@
       <c r="B32" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A32)</f>
         <v>16</v>
-        <v/>
       </c>
       <c r="C32" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A32,'Corrected Register'!N5:N136)</f>
         <v>5184.18</v>
-        <v/>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -6165,12 +6128,10 @@
       </c>
       <c r="F32" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E32)</f>
-        <v>12</v>
         <v/>
       </c>
       <c r="G32" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E32,'Exception Register'!G5:G167)</f>
-        <v>6214.38</v>
         <v/>
       </c>
     </row>
@@ -6183,12 +6144,10 @@
       <c r="B33" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A33)</f>
         <v>15</v>
-        <v/>
       </c>
       <c r="C33" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A33,'Corrected Register'!N5:N136)</f>
         <v>6267.29</v>
-        <v/>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -6197,12 +6156,10 @@
       </c>
       <c r="F33" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E33)</f>
-        <v>61</v>
         <v/>
       </c>
       <c r="G33" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E33,'Exception Register'!G5:G167)</f>
-        <v>29063.84</v>
         <v/>
       </c>
     </row>
@@ -6215,12 +6172,10 @@
       <c r="B34" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A34)</f>
         <v>15</v>
-        <v/>
       </c>
       <c r="C34" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A34,'Corrected Register'!N5:N136)</f>
         <v>11070.95</v>
-        <v/>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -6229,12 +6184,10 @@
       </c>
       <c r="F34" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E34)</f>
-        <v>4</v>
         <v/>
       </c>
       <c r="G34" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E34,'Exception Register'!G5:G167)</f>
-        <v>2503.11</v>
         <v/>
       </c>
     </row>
@@ -6247,12 +6200,10 @@
       <c r="B35" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A35)</f>
         <v>15</v>
-        <v/>
       </c>
       <c r="C35" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A35,'Corrected Register'!N5:N136)</f>
         <v>5149.95</v>
-        <v/>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -6261,12 +6212,10 @@
       </c>
       <c r="F35" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E35)</f>
-        <v>43</v>
         <v/>
       </c>
       <c r="G35" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E35,'Exception Register'!G5:G167)</f>
-        <v>22627.56</v>
         <v/>
       </c>
     </row>
@@ -6279,12 +6228,10 @@
       <c r="B36" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A36)</f>
         <v>14</v>
-        <v/>
       </c>
       <c r="C36" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A36,'Corrected Register'!N5:N136)</f>
         <v>5551.75</v>
-        <v/>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -6293,12 +6240,10 @@
       </c>
       <c r="F36" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E36)</f>
-        <v>8</v>
         <v/>
       </c>
       <c r="G36" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E36,'Exception Register'!G5:G167)</f>
-        <v>7440</v>
         <v/>
       </c>
     </row>
@@ -6311,12 +6256,10 @@
       <c r="B37" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A37)</f>
         <v>14</v>
-        <v/>
       </c>
       <c r="C37" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A37,'Corrected Register'!N5:N136)</f>
         <v>10526</v>
-        <v/>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -6325,12 +6268,10 @@
       </c>
       <c r="F37" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E37)</f>
-        <v>12</v>
         <v/>
       </c>
       <c r="G37" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E37,'Exception Register'!G5:G167)</f>
-        <v>4811.33</v>
         <v/>
       </c>
     </row>
@@ -6343,12 +6284,10 @@
       <c r="B38" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A38)</f>
         <v>12</v>
-        <v/>
       </c>
       <c r="C38" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A38,'Corrected Register'!N5:N136)</f>
         <v>6214.38</v>
-        <v/>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -6357,12 +6296,10 @@
       </c>
       <c r="F38" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E38)</f>
-        <v>12</v>
         <v/>
       </c>
       <c r="G38" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E38,'Exception Register'!G5:G167)</f>
-        <v>6191.65</v>
         <v/>
       </c>
     </row>
@@ -6375,12 +6312,10 @@
       <c r="B39" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A39)</f>
         <v>10</v>
-        <v/>
       </c>
       <c r="C39" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A39,'Corrected Register'!N5:N136)</f>
         <v>4878.51</v>
-        <v/>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -6389,12 +6324,10 @@
       </c>
       <c r="F39" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E39)</f>
-        <v>4</v>
         <v/>
       </c>
       <c r="G39" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E39,'Exception Register'!G5:G167)</f>
-        <v>2332.54</v>
         <v/>
       </c>
     </row>
@@ -6407,12 +6340,10 @@
       <c r="B40" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A40)</f>
         <v>8</v>
-        <v/>
       </c>
       <c r="C40" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A40,'Corrected Register'!N5:N136)</f>
         <v>0</v>
-        <v/>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -6421,12 +6352,10 @@
       </c>
       <c r="F40" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E40)</f>
-        <v>5</v>
         <v/>
       </c>
       <c r="G40" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E40,'Exception Register'!G5:G167)</f>
-        <v>2869.32</v>
         <v/>
       </c>
     </row>
@@ -6439,12 +6368,10 @@
       <c r="B41" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A41)</f>
         <v>7</v>
-        <v/>
       </c>
       <c r="C41" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A41,'Corrected Register'!N5:N136)</f>
         <v>4351.05</v>
-        <v/>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -6453,12 +6380,10 @@
       </c>
       <c r="F41">
         <f>COUNTIF('Exception Register'!B5:B167,E41)</f>
-        <v>2</v>
         <v/>
       </c>
       <c r="G41">
         <f>SUMIF('Exception Register'!B5:B167,E41,'Exception Register'!G5:G167)</f>
-        <v>1875</v>
         <v/>
       </c>
     </row>
@@ -6488,7 +6413,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
@@ -6609,7 +6533,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -6785,7 +6708,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00001: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $1895. hr_employee_status lists E0001 / Priya Shah as Active. Transfer TR-00001 received 2026-01-21; approval APR-00001. FAR row FA-000001; net book value $0. PO PO-2022-0001.</t>
+          <t>Files reviewed for MD-00001: Lenovo ThinkPad T14, basis $1895, operating site Chicago, status In Use. Source Ledger FA-000001; net book value $0. equipment_transfer_log TR-00001 posted Jan 21, 2026; inbound 2026-01-21 approval APR-00001. hr_employee_status lists Priya Shah (E0001) as Active. hardware_purchase_orders.csv ties MD-00001 to PO-2022-0001.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6893,7 +6816,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00002 (Dell U2723QE) as In Use. Acquisition $610. People file: E0002 (Marcus Ellison), status Active. Transfer TR-00002 received 2026-02-25; approval APR-00002. Fixed-asset extract includes FA-000002 (NBV $313.06). PO PO-2022-0001.</t>
+          <t>Cross-checked MD-00002 (MD-MO-050002, Dell U2723QE) against HR, transfers, and ledger extracts. Source Ledger FA-000002; net book value $313.06. equipment_transfer_log TR-00002 posted Feb 23, 2026; inbound 2026-02-25 approval APR-00002. hr_employee_status lists Marcus Ellison (E0002) as Active. capital PO PO-2022-0001 supports the cost basis.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -7001,7 +6924,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>MD-00003 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1085. Custodian E0003 (Elena Kovacs) is Active in hr_employee_status. Transfer TR-00003 received 2026-04-03; approval APR-00003. Ledger FA-000003 on file; NBV $597.83. PO PO-2022-0001.</t>
+          <t>Cross-checked MD-00003 (MD-MO-050003, Samsung Galaxy S24) against HR, transfers, and ledger extracts. Source Ledger FA-000003; net book value $597.83. equipment_transfer_log TR-00003 posted Mar 31, 2026; inbound 2026-04-03 approval APR-00003. hr_employee_status lists Elena Kovacs (E0003) as Active. hardware_purchase_orders.csv ties MD-00003 to PO-2022-0001.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -7109,7 +7032,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00004: In Use. Site New York. Model Cisco C9300; cost $6380. hr_employee_status lists E0004 / James Whitaker as Active. Transfer TR-00004 received 2026-05-01; approval APR-00004. FAR row FA-000004; net book value $940.62. PO PO-2022-0001.</t>
+          <t>Cross-checked MD-00004 (MD-NE-050004, Cisco C9300) against HR, transfers, and ledger extracts. Source Ledger FA-000004; net book value $940.62. equipment_transfer_log TR-00004 posted May 01, 2026; inbound 2026-05-01 approval APR-00004. hr_employee_status lists James Whitaker (E0004) as Active. capital PO PO-2022-0001 supports the cost basis.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -7217,7 +7140,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00005 (MacBook Pro 14) as In Use. Acquisition $2075. People file: E0005 (Aisha Rahman), status Active. Transfer TR-00005 received 2026-06-08; approval APR-00005. Fixed-asset extract includes FA-000005 (NBV $0). PO PO-2022-0001.</t>
+          <t>Reconciliation packet cites MD-00005 with acquisition $2075 and custody In Use at Seattle. Source Ledger FA-000005; net book value $0. hardware_purchase_orders.csv ties MD-00005 to PO-2022-0001. equipment_transfer_log TR-00005 posted Jun 05, 2026; inbound 2026-06-08 approval APR-00005. hr_employee_status lists Aisha Rahman (E0005) as Active.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -7325,7 +7248,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>MD-00006 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $790. Custodian E0006 (Colin Bergstrom) is Active in hr_employee_status. Transfer TR-00006 received 2026-01-12; approval APR-00006. Ledger FA-000006 on file; NBV $459.94. PO PO-2022-0001.</t>
+          <t>Cross-checked MD-00006 (MD-MO-050006, Dell U2723QE) against HR, transfers, and ledger extracts. Source Ledger FA-000006; net book value $459.94. equipment_transfer_log TR-00006 posted Jan 10, 2026; inbound 2026-01-12 approval APR-00006. hr_employee_status lists Colin Bergstrom (E0006) as Active. acquisition recorded on PO-2022-0001.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7433,7 +7356,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00007: In Use. Site Chicago. Model Samsung Galaxy S24; cost $950. hr_employee_status lists E0007 / Sofia Alvarez as Active. Transfer TR-00007 received 2026-02-17; approval APR-00007. FAR row FA-000007; net book value $632.68. PO PO-2023-0002.</t>
+          <t>Cross-checked MD-00007 (MD-MO-050007, Samsung Galaxy S24) against HR, transfers, and ledger extracts. Source Ledger FA-000007; net book value $632.68. equipment_transfer_log TR-00007 posted Feb 11, 2026; inbound 2026-02-17 approval APR-00007. hr_employee_status lists Sofia Alvarez (E0007) as Active. PO-2023-0002 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7445,7 +7368,7 @@
         <v>950</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>632.6799999999999</v>
+        <v>632.68</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
@@ -7477,7 +7400,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>632.6799999999999</v>
+        <v>632.68</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -7541,7 +7464,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00008 (Cisco C9300) as In Use. Acquisition $6245. People file: E0008 (Derek Nguyen), status Active. Transfer TR-00008 received 2026-03-19; approval APR-00008. Fixed-asset extract includes FA-000008 (NBV $1355.01). PO PO-2023-0002.</t>
+          <t>Cross-checked MD-00008 (MD-NE-050008, Cisco C9300) against HR, transfers, and ledger extracts. Source Ledger FA-000008; net book value $1355.01. equipment_transfer_log TR-00008 posted Mar 16, 2026; inbound 2026-03-19 approval APR-00008. hr_employee_status lists Derek Nguyen (E0008) as Active. acquisition recorded on PO-2023-0002.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7649,7 +7572,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>MD-00009 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1940. Custodian E0009 (Hannah Cole) is Active in hr_employee_status. Transfer TR-00009 received 2026-04-21; approval APR-00009. Ledger FA-000009 on file; NBV $109.33. PO PO-2023-0002.</t>
+          <t>Working conclusion for MD-00009 (MD-LA-050009): In Use at Denver; cost $1940. equipment_transfer_log TR-00009 posted Apr 20, 2026; inbound 2026-04-21 approval APR-00009. hr_employee_status lists Hannah Cole (E0009) as Active. purchasing file shows PO-2023-0002 for this unit. Source Ledger FA-000009; net book value $109.33.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7757,7 +7680,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00010: In Use. Site New York. Model Dell U2723QE; cost $655. hr_employee_status lists E0010 / Owen Patel as Active. Transfer TR-00010 received 2026-05-28; approval APR-00010. FAR row FA-000010; net book value $426.89. PO PO-2023-0002.</t>
+          <t>Working conclusion for MD-00010 (MD-MO-050010): In Use at New York; cost $655. equipment_transfer_log TR-00010 posted May 22, 2026; inbound 2026-05-28 approval APR-00010. Source Ledger FA-000010; net book value $426.89. buy path for MD-00010 references PO-2023-0002. hr_employee_status lists Owen Patel (E0010) as Active.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7865,7 +7788,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00011 (Samsung Galaxy S24) as In Use. Acquisition $1130. People file: E0011 (Maya Fontaine), status Active. Transfer TR-00011 received 2026-06-28; approval APR-00011. Fixed-asset extract includes FA-000011 (NBV $882.5). PO PO-2023-0002.</t>
+          <t>Working conclusion for MD-00011 (MD-MO-050011): In Use at Seattle; cost $1130. equipment_transfer_log TR-00011 posted Jun 26, 2026; inbound 2026-06-28 approval APR-00011. Source Ledger FA-000011; net book value $882.5. hardware_purchase_orders.csv ties MD-00011 to PO-2023-0002. hr_employee_status lists Maya Fontaine (E0011) as Active.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7973,7 +7896,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>MD-00012 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6425. Custodian E0012 (Ryan Okonkwo) is Active in hr_employee_status. Transfer TR-00012 received 2026-01-31; approval APR-00012. Ledger FA-000012 on file; NBV $553.23. PO PO-2023-0002.</t>
+          <t>Working conclusion for MD-00012 (MD-NE-050012): In Use at Atlanta; cost $6425. equipment_transfer_log TR-00012 posted Jan 30, 2026; inbound 2026-01-31 approval APR-00012. Source Ledger FA-000012; net book value $553.23. PO PO-2023-0002 documents the buy for MD-00012. hr_employee_status lists Ryan Okonkwo (E0012) as Active.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -8081,7 +8004,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00013: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $2120. hr_employee_status lists E0013 / Lauren Briggs as Active. Transfer TR-00013 received 2026-02-06; approval APR-00013. FAR row FA-000013; net book value $0. PO PO-2024-0003.</t>
+          <t>Working conclusion for MD-00013 (MD-LA-050013): In Use at Chicago; cost $2120. equipment_transfer_log TR-00013 posted Feb 02, 2026; inbound 2026-02-06 approval APR-00013. Source Ledger FA-000013; net book value $0. hardware_purchase_orders.csv ties MD-00013 to PO-2024-0003. hr_employee_status lists Lauren Briggs (E0013) as Active.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -8189,7 +8112,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00014 (Dell U2723QE) as In Use. Acquisition $520. People file: E0014 (Nathan Kim), status Active. Transfer TR-00014 received 2026-03-09; approval APR-00014. Fixed-asset extract includes FA-000014 (NBV $270.29). PO PO-2024-0003.</t>
+          <t>Asset MD-00014 — Dell U2723QE — reconciled to In Use in Dallas on $520 acquisition. hr_employee_status lists Nathan Kim (E0014) as Active. Source Ledger FA-000014; net book value $270.29. PO PO-2024-0003 documents the buy for MD-00014. equipment_transfer_log TR-00014 posted Mar 07, 2026; inbound 2026-03-09 approval APR-00014.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8297,7 +8220,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>MD-00015 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $995. Custodian E0015 (Camila Ortiz) is Active in hr_employee_status. Transfer TR-00015 received 2026-04-13; approval APR-00015. Ledger FA-000015 on file; NBV $559.13. PO PO-2024-0003.</t>
+          <t>Asset MD-00015 — Samsung Galaxy S24 — reconciled to In Use in Denver on $995 acquisition. hr_employee_status lists Camila Ortiz (E0015) as Active. Source Ledger FA-000015; net book value $559.13. capital PO PO-2024-0003 supports the cost basis. equipment_transfer_log TR-00015 posted Apr 12, 2026; inbound 2026-04-13 approval APR-00015.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -8405,7 +8328,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00016: In Use. Site New York. Model Cisco C9300; cost $6290. hr_employee_status lists E0016 / Patrick Gallagher as Active. Transfer TR-00016 received 2026-05-17; approval APR-00016. FAR row FA-000016; net book value $968.69. PO PO-2024-0003.</t>
+          <t>Asset MD-00016 — Cisco C9300 — reconciled to In Use in New York on $6290 acquisition. hr_employee_status lists Patrick Gallagher (E0016) as Active. Source Ledger FA-000016; net book value $968.69. PO-2024-0003 is the cited purchase order. equipment_transfer_log TR-00016 posted May 13, 2026; inbound 2026-05-17 approval APR-00016.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -8417,7 +8340,7 @@
         <v>6290</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>968.6900000000001</v>
+        <v>968.69</v>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
@@ -8449,7 +8372,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>968.6900000000001</v>
+        <v>968.69</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -8513,7 +8436,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00017 (MacBook Pro 14) as In Use. Acquisition $1985. People file: E0017 (Irene Cho), status Active. Transfer TR-00017 received 2026-06-19; approval APR-00017. Fixed-asset extract includes FA-000017 (NBV $0). PO PO-2024-0003. Accumulated depreciation $2160 exceeds acquisition $2070 by $90.</t>
+          <t>Asset MD-00017 — MacBook Pro 14 — reconciled to In Use in Seattle on $1985 acquisition. hr_employee_status lists Irene Cho (E0017) as Active. Source Ledger FA-000017; net book value $0. acquisition recorded on PO-2024-0003. equipment_transfer_log TR-00017 posted Jun 17, 2026; inbound 2026-06-19 approval APR-00017.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8625,7 +8548,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>MD-00018 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $700. Custodian E0018 (Theo Barnett) is Active in hr_employee_status. Transfer TR-00018 received 2026-01-23; approval APR-00018. Ledger FA-000018 on file; NBV $412.14. PO PO-2024-0003.</t>
+          <t>Asset MD-00018 — Dell U2723QE — reconciled to In Use in Atlanta on $700 acquisition. hr_employee_status lists Theo Barnett (E0018) as Active. Source Ledger FA-000018; net book value $412.14. purchasing file shows PO-2024-0003 for this unit. equipment_transfer_log TR-00018 posted Jan 22, 2026; inbound 2026-01-23 approval APR-00018.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8733,7 +8656,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00019: In Use. Site Chicago. Model Samsung Galaxy S24; cost $1175. hr_employee_status lists E0019 / Jasmine Reed as Active. Transfer TR-00019 received 2026-02-26; approval APR-00019. FAR row FA-000019; net book value $795.4. PO PO-2025-0004.</t>
+          <t>Asset MD-00019 — Samsung Galaxy S24 — reconciled to In Use in Chicago on $1175 acquisition. hr_employee_status lists Jasmine Reed (E0019) as Active. Source Ledger FA-000019; net book value $795.4. acquisition recorded on PO-2025-0004. equipment_transfer_log TR-00019 posted Feb 23, 2026; inbound 2026-02-26 approval APR-00019.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -8841,7 +8764,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00020 (Cisco C9300) as In Use. Acquisition $6470. People file: E0020 (Luis Navarro), status Active. Transfer TR-00020 received 2026-03-30; approval APR-00020. Fixed-asset extract includes FA-000020 (NBV $1446.34). PO PO-2025-0004.</t>
+          <t>Asset MD-00020 — Cisco C9300 — reconciled to In Use in Dallas on $6470 acquisition. hr_employee_status lists Luis Navarro (E0020) as Active. equipment_transfer_log TR-00020 posted Mar 28, 2026; inbound 2026-03-30 approval APR-00020. Source Ledger FA-000020; net book value $1446.34. capital PO PO-2025-0004 supports the cost basis.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -8949,7 +8872,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>MD-00021 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1850. Custodian E0021 (Grace Lindholm) is Active in hr_employee_status. Transfer TR-00021 received 2026-05-03; approval APR-00021. Ledger FA-000021 on file; NBV $124.52. PO PO-2025-0004. Duplicate serial MD-LA-050021 shared with the paired asset.</t>
+          <t>Asset MD-00021 — Dell Latitude 7440 — reconciled to In Use in Denver on $1850 acquisition. duplicate serial MD-LA-050021 flagged on the register. equipment_transfer_log TR-00021 posted May 02, 2026; inbound 2026-05-03 approval APR-00021. Source Ledger FA-000021; net book value $124.52. buy path for MD-00021 references PO-2025-0004. hr_employee_status lists Grace Lindholm (E0021) as Active.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -9061,7 +8984,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00022: In Use. Site New York. Model Dell U2723QE; cost $565. hr_employee_status lists E0022 / Andre Baptiste as Active. Transfer TR-00022 received 2026-06-05; approval APR-00022. FAR row FA-000022; net book value $371.95. PO PO-2025-0004.</t>
+          <t>Working conclusion for MD-00022 (MD-MO-050022): In Use at New York; cost $565. hardware_purchase_orders.csv ties MD-00022 to PO-2025-0004. hr_employee_status lists Andre Baptiste (E0022) as Active. equipment_transfer_log TR-00022 posted Jun 03, 2026; inbound 2026-06-05 approval APR-00022. Source Ledger FA-000022; net book value $371.95.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -9169,7 +9092,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00023 (Samsung Galaxy S24) as In Use. Acquisition $1040. People file: E0023 (Nina Kowalski), status Active. Transfer TR-00023 received 2026-07-09; approval APR-00023. Fixed-asset extract includes FA-000023 (NBV $823.6). PO PO-2025-0004.</t>
+          <t>Working conclusion for MD-00023 (MD-MO-050023): In Use at Seattle; cost $1040. PO PO-2025-0004 documents the buy for MD-00023. hr_employee_status lists Nina Kowalski (E0023) as Active. equipment_transfer_log TR-00023 posted Jul 08, 2026; inbound 2026-07-09 approval APR-00023. Source Ledger FA-000023; net book value $823.6.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -9277,7 +9200,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>MD-00024 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6335. Custodian E0024 (Chris Daley) is Active in hr_employee_status. Transfer TR-00024 received 2026-01-21; approval APR-00024. Ledger FA-000024 on file; NBV $503.85. PO PO-2025-0004.</t>
+          <t>Working conclusion for MD-00024 (MD-NE-050024): In Use at Atlanta; cost $6335. capital PO PO-2025-0004 supports the cost basis. hr_employee_status lists Chris Daley (E0024) as Active. equipment_transfer_log TR-00024 posted Jan 18, 2026; inbound 2026-01-21 approval APR-00024. Source Ledger FA-000024; net book value $503.85.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -9385,7 +9308,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00025: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $2030. hr_employee_status lists E0025 / Fatima Hussein as Active. Transfer TR-00025 received 2026-01-22; approval APR-00025. FAR row FA-000025; net book value $0. PO PO-2022-0005. Duplicate serial MD-LA-050021 shared with the paired asset.</t>
+          <t>Working conclusion for MD-00025 (MD-LA-050021): In Use at Chicago; cost $2030. buy path for MD-00025 references PO-2022-0005. hr_employee_status lists Fatima Hussein (E0025) as Active. duplicate serial MD-LA-050021 flagged on the register. Source Ledger FA-000025; net book value $0. equipment_transfer_log TR-00025 posted Jan 21, 2026; inbound 2026-01-22 approval APR-00025.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -9497,7 +9420,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00026 (Dell U2723QE) as In Use. Acquisition $745. People file: E0026 (Brendan Walsh), status Active. Transfer TR-00026 received 2026-02-27; approval APR-00026. Fixed-asset extract includes FA-000026 (NBV $382.34). PO PO-2022-0005.</t>
+          <t>Working conclusion for MD-00026 (MD-MO-050026): In Use at Dallas; cost $745. acquisition recorded on PO-2022-0005. hr_employee_status lists Brendan Walsh (E0026) as Active. equipment_transfer_log TR-00026 posted Feb 23, 2026; inbound 2026-02-27 approval APR-00026. Source Ledger FA-000026; net book value $382.34.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -9609,7 +9532,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>MD-00027 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1220. Custodian E0027 (Yuki Tanaka) is Active in hr_employee_status. Transfer TR-00027 received 2026-04-06; approval APR-00027. Ledger FA-000027 on file; NBV $672.21. PO PO-2022-0005.</t>
+          <t>Asset MD-00027 — Samsung Galaxy S24 — reconciled to In Use in Denver on $1220 acquisition. hr_employee_status lists Yuki Tanaka (E0027) as Active. equipment_transfer_log TR-00027 posted Mar 31, 2026; inbound 2026-04-06 approval APR-00027. Source Ledger FA-000027; net book value $672.21. purchasing file shows PO-2022-0005 for this unit.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -9721,7 +9644,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00028: In Use. Site New York. Model Cisco C9300; cost $6200. hr_employee_status lists E0028 / Megan Copeland as Active. Transfer TR-00028 received 2026-05-02; approval APR-00028. FAR row FA-000028; net book value $914.09. PO PO-2022-0005.</t>
+          <t>Asset MD-00028 — Cisco C9300 — reconciled to In Use in New York on $6200 acquisition. hr_employee_status lists Megan Copeland (E0028) as Active. equipment_transfer_log TR-00028 posted May 01, 2026; inbound 2026-05-02 approval APR-00028. Source Ledger FA-000028; net book value $914.09. order PO-2022-0005 appears in the purchasing extract.</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -9833,7 +9756,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00029 (MacBook Pro 14) as In Use. Acquisition $1895. People file: E0029 (Omar Haddad), status Active. Transfer TR-00029 received 2026-06-11; approval APR-00029. Fixed-asset extract includes FA-000029 (NBV $0). PO PO-2022-0005.</t>
+          <t>Asset MD-00029 — MacBook Pro 14 — reconciled to In Use in Seattle on $1895 acquisition. hr_employee_status lists Omar Haddad (E0029) as Active. equipment_transfer_log TR-00029 posted Jun 05, 2026; inbound 2026-06-11 approval APR-00029. Source Ledger FA-000029; net book value $0. PO-2022-0005 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -9945,7 +9868,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>MD-00030 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $610. Custodian E0030 (Stephanie Ruiz) is Active in hr_employee_status. Transfer TR-00030 received 2026-01-13; approval APR-00030. Ledger FA-000030 on file; NBV $355.14. PO PO-2022-0005.</t>
+          <t>Files reviewed for MD-00030: Dell U2723QE, basis $610, operating site Atlanta, status In Use. equipment_transfer_log TR-00030 posted Jan 10, 2026; inbound 2026-01-13 approval APR-00030. PO PO-2022-0005 documents the buy for MD-00030. Source Ledger FA-000030; net book value $355.14. hr_employee_status lists Stephanie Ruiz (E0030) as Active.</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -10057,7 +9980,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00031: In Use. Site Chicago. Model Samsung Galaxy S24; cost $1085. hr_employee_status lists E0031 / Keith Moreau as Active. Transfer TR-00031 received 2026-02-11; approval APR-00031. FAR row FA-000031; net book value $722.59. PO PO-2023-0006.</t>
+          <t>Files reviewed for MD-00031: Samsung Galaxy S24, basis $1085, operating site Chicago, status In Use. equipment_transfer_log TR-00031 posted Feb 11, 2026; inbound 2026-02-11 approval APR-00031. hardware_purchase_orders.csv ties MD-00031 to PO-2023-0006. Source Ledger FA-000031; net book value $722.59. hr_employee_status lists Keith Moreau (E0031) as Active.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -10169,7 +10092,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00032 (Cisco C9300) as In Use. Acquisition $6380. People file: E0032 (Diana Voss), status Active. Transfer TR-00032 received 2026-03-22; approval APR-00032. Fixed-asset extract includes FA-000032 (NBV $1384.3). PO PO-2023-0006.</t>
+          <t>Asset MD-00032 — Cisco C9300 — reconciled to In Use in Dallas on $6380 acquisition. Source Ledger FA-000032; net book value $1384.3. PO PO-2023-0006 documents the buy for MD-00032. hr_employee_status lists Diana Voss (E0032) as Active. equipment_transfer_log TR-00032 posted Mar 16, 2026; inbound 2026-03-22 approval APR-00032.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -10281,7 +10204,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>MD-00033 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $2075. Custodian E0033 (Jordan Blake) is Active in hr_employee_status. Transfer TR-00033 received 2026-04-22; approval APR-00033. Ledger FA-000033 on file; NBV $116.93. PO PO-2023-0006.</t>
+          <t>Asset MD-00033 — Dell Latitude 7440 — reconciled to In Use in Denver on $2075 acquisition. Source Ledger FA-000033; net book value $116.93. capital PO PO-2023-0006 supports the cost basis. hr_employee_status lists Jordan Blake (E0033) as Active. equipment_transfer_log TR-00033 posted Apr 20, 2026; inbound 2026-04-22 approval APR-00033.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -10393,7 +10316,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00034: In Use. Site New York. Model Dell U2723QE; cost $790. hr_employee_status lists E0034 / Amelia Grant as Active. Transfer TR-00034 received 2026-05-22; approval APR-00034. FAR row FA-000034; net book value $479.88. PO PO-2023-0006. NBV arithmetic: acquisition $930 − accum. dep. $450.12 = $479.88 (ledger previously overstated at $514.88 by $35.00).</t>
+          <t>Working conclusion for MD-00034 (MD-MO-050034): In Use at New York; cost $790. equipment_transfer_log TR-00034 posted May 22, 2026; inbound 2026-05-22 approval APR-00034. buy path for MD-00034 references PO-2023-0006. Source Ledger FA-000034; net book value $=XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!E5:E133)-XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!F5:F133). hr_employee_status lists Amelia Grant (E0034) as Active.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -10407,7 +10330,6 @@
       <c r="N38" s="7">
         <f>XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!E5:E133)-XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!F5:F133)</f>
         <v>479.88</v>
-        <v/>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
@@ -10445,11 +10367,9 @@
       <c r="V38">
         <f>XLOOKUP(A38,'Source Ledger'!B5:B133,'Source Ledger'!G5:G133)</f>
         <v>479.88</v>
-        <v/>
       </c>
       <c r="W38">
         <f>T38-M38</f>
-        <v>140</v>
         <v/>
       </c>
       <c r="X38" t="inlineStr">
@@ -10511,7 +10431,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00035 (Samsung Galaxy S24) as In Use. Acquisition $950. People file: E0035 (Rafael Mendes), status Active. Transfer TR-00035 received 2026-06-30; approval APR-00035. Fixed-asset extract includes FA-000035 (NBV $741.92). PO PO-2023-0006.</t>
+          <t>Asset MD-00035 — Samsung Galaxy S24 — reconciled to In Use in Seattle on $950 acquisition. hr_employee_status lists Rafael Mendes (E0035) as Active. Source Ledger FA-000035; net book value $741.92. equipment_transfer_log TR-00035 posted Jun 26, 2026; inbound 2026-06-30 approval APR-00035. hardware_purchase_orders.csv ties MD-00035 to PO-2023-0006.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -10623,7 +10543,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>MD-00036 (Cisco C9300) is In Use at Atlanta. Acquisition cost $6245. Custodian E0036 (Kate Sorenson) is Active in hr_employee_status. Transfer TR-00036 received 2026-02-01; approval APR-00036. Ledger FA-000036 on file; NBV $537.73. PO PO-2023-0006.</t>
+          <t>Asset MD-00036 — Cisco C9300 — reconciled to In Use in Atlanta on $6245 acquisition. hr_employee_status lists Kate Sorenson (E0036) as Active. Source Ledger FA-000036; net book value $537.73. equipment_transfer_log TR-00036 posted Jan 30, 2026; inbound 2026-02-01 approval APR-00036. purchasing file shows PO-2023-0006 for this unit.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10735,7 +10655,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00037: In Use. Site Chicago. Model Lenovo ThinkPad T14; cost $1940. hr_employee_status lists E0037 / Victor Lang as Active. Transfer TR-00037 received 2026-02-02; approval APR-00037. FAR row FA-000037; net book value $0. PO PO-2024-0007.</t>
+          <t>Working conclusion for MD-00037 (MD-LA-050037): In Use at Chicago; cost $1940. equipment_transfer_log TR-00037 posted Feb 02, 2026; inbound 2026-02-02 approval APR-00037. acquisition recorded on PO-2024-0007. Source Ledger FA-000037; net book value $0. hr_employee_status lists Victor Lang (E0037) as Active.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -10847,7 +10767,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00038 (Dell U2723QE) as In Use. Acquisition $655. People file: E0038 (Noelle Harper), status Active. Transfer TR-00038 received 2026-03-11; approval APR-00038. Fixed-asset extract includes FA-000038 (NBV $340.46). PO PO-2024-0007.</t>
+          <t>Working conclusion for MD-00038 (MD-MO-050038): In Use at Dallas; cost $655. equipment_transfer_log TR-00038 posted Mar 07, 2026; inbound 2026-03-11 approval APR-00038. purchasing file shows PO-2024-0007 for this unit. Source Ledger FA-000038; net book value $340.46. hr_employee_status lists Noelle Harper (E0038) as Active.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10959,7 +10879,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>MD-00039 (Samsung Galaxy S24) is In Use at Denver. Acquisition cost $1130. Custodian E0039 (Samir Kapoor) is Active in hr_employee_status. Transfer TR-00039 received 2026-04-14; approval APR-00039. Ledger FA-000039 on file; NBV $635. PO PO-2024-0007.</t>
+          <t>Asset MD-00039 — Samsung Galaxy S24 — reconciled to In Use in Denver on $1130 acquisition. Source Ledger FA-000039; net book value $635. order PO-2024-0007 appears in the purchasing extract. hr_employee_status lists Samir Kapoor (E0039) as Active. equipment_transfer_log TR-00039 posted Apr 12, 2026; inbound 2026-04-14 approval APR-00039.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -11071,7 +10991,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00040: In Use. Site New York. Model Cisco C9300; cost $6425. hr_employee_status lists E0040 / Holly Jensen as Active. Transfer TR-00040 received 2026-05-13; approval APR-00040. FAR row FA-000040; net book value $989.48. PO PO-2024-0007.</t>
+          <t>Asset MD-00040 — Cisco C9300 — reconciled to In Use in New York on $6425 acquisition. hr_employee_status lists Holly Jensen (E0040) as Active. hardware_purchase_orders.csv ties MD-00040 to PO-2024-0007. Source Ledger FA-000040; net book value $989.48. equipment_transfer_log TR-00040 posted May 13, 2026; inbound 2026-05-13 approval APR-00040.</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -11183,7 +11103,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Seattle holds MD-00041 (MacBook Pro 14) as In Use. Acquisition $2120. People file: E0041 (Eric Vann), status Active. Transfer TR-00041 received 2026-06-20; approval APR-00041. Fixed-asset extract includes FA-000041 (NBV $0). PO PO-2024-0007.</t>
+          <t>Asset MD-00041 — MacBook Pro 14 — reconciled to In Use in Seattle on $2120 acquisition. hr_employee_status lists Eric Vann (E0041) as Active. PO PO-2024-0007 documents the buy for MD-00041. Source Ledger FA-000041; net book value $0. equipment_transfer_log TR-00041 posted Jun 17, 2026; inbound 2026-06-20 approval APR-00041.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -11295,7 +11215,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>MD-00042 (Dell U2723QE) is In Use at Atlanta. Acquisition cost $520. Custodian E0042 (Claudia Rossi) is Active in hr_employee_status. Transfer TR-00042 received 2026-01-24; approval APR-00042. Ledger FA-000042 on file; NBV $306.16. PO PO-2024-0007.</t>
+          <t>Working conclusion for MD-00042 (MD-MO-050042): In Use at Atlanta; cost $520. equipment_transfer_log TR-00042 posted Jan 22, 2026; inbound 2026-01-24 approval APR-00042. capital PO PO-2024-0007 supports the cost basis. hr_employee_status lists Claudia Rossi (E0042) as Active. Source Ledger FA-000042; net book value $306.16.</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -11407,7 +11327,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00043: In Use. Site Chicago. Model Samsung Galaxy S24; cost $995. hr_employee_status lists E0043 / Tyler Brooks as Active. Transfer TR-00043 received 2026-03-01; approval APR-00043. FAR row FA-000043; net book value $673.55. PO PO-2025-0008.</t>
+          <t>Working conclusion for MD-00043 (MD-MO-050043): In Use at Chicago; cost $995. equipment_transfer_log TR-00043 posted Feb 23, 2026; inbound 2026-03-01 approval APR-00043. PO PO-2025-0008 documents the buy for MD-00043. hr_employee_status lists Tyler Brooks (E0043) as Active. Source Ledger FA-000043; net book value $673.55.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -11519,7 +11439,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Dallas holds MD-00044 (Cisco C9300) as In Use. Acquisition $6290. People file: E0044 (Leah Okada), status Active. Transfer TR-00044 received 2026-03-31; approval APR-00044. Fixed-asset extract includes FA-000044 (NBV $1406.1). PO PO-2025-0008.</t>
+          <t>Working conclusion for MD-00044 (MD-NE-050044): In Use at Dallas; cost $6290. equipment_transfer_log TR-00044 posted Mar 28, 2026; inbound 2026-03-31 approval APR-00044. capital PO PO-2025-0008 supports the cost basis. hr_employee_status lists Leah Okada (E0044) as Active. Source Ledger FA-000044; net book value $1406.1.</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -11631,7 +11551,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>MD-00045 (Dell Latitude 7440) is In Use at Denver. Acquisition cost $1985. Custodian E0045 (Darnell Price) is Active in hr_employee_status. Transfer TR-00045 received 2026-05-03; approval APR-00045. Ledger FA-000045 on file; NBV $133.6. PO PO-2025-0008.</t>
+          <t>Asset MD-00045 — Dell Latitude 7440 — reconciled to In Use in Denver on $1985 acquisition. hr_employee_status lists Darnell Price (E0045) as Active. buy path for MD-00045 references PO-2025-0008. Source Ledger FA-000045; net book value $133.6. equipment_transfer_log TR-00045 posted May 02, 2026; inbound 2026-05-03 approval APR-00045.</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -11739,7 +11659,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>MD-00046 (Dell U2723QE) is Available at New York. Acquisition cost $700. Transfer TR-00046 received 2026-06-07; approval APR-00046. FAR row FA-000046; net book value $460.82. PO PO-2025-0008.</t>
+          <t>Asset MD-00046 — Dell U2723QE — reconciled to Available in New York on $700 acquisition. equipment_transfer_log TR-00046 posted Jun 03, 2026; inbound 2026-06-07 approval APR-00046. Source Ledger FA-000046; net book value $460.82. acquisition recorded on PO-2025-0008.</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -11847,7 +11767,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>MD-00047 (Samsung Galaxy S24) is Available at Seattle. Acquisition cost $1175. Transfer TR-00047 received 2026-07-10; approval APR-00047. Fixed-asset extract includes FA-000047 (NBV $930.51). PO PO-2025-0008.</t>
+          <t>Cross-checked MD-00047 (MD-MO-050047, Samsung Galaxy S24) against HR, transfers, and ledger extracts. equipment_transfer_log TR-00047 posted Jul 08, 2026; inbound 2026-07-10 approval APR-00047. Source Ledger FA-000047; net book value $930.51. purchasing file shows PO-2025-0008 for this unit.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -11955,7 +11875,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>MD-00048 (Cisco C9300) is Available at Atlanta. Acquisition cost $6470. Transfer TR-00048 received 2026-01-24; approval APR-00048. Ledger FA-000048 on file; NBV $514.59. PO PO-2025-0008.</t>
+          <t>Cross-checked MD-00048 (MD-NE-050048, Cisco C9300) against HR, transfers, and ledger extracts. equipment_transfer_log TR-00048 posted Jan 18, 2026; inbound 2026-01-24 approval APR-00048. Source Ledger FA-000048; net book value $514.59. order PO-2025-0008 appears in the purchasing extract.</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -12063,7 +11983,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>MD-00049 (Lenovo ThinkPad T14) is Available at Chicago. Acquisition cost $1850. Transfer TR-00049 received 2026-01-23; approval APR-00049. FAR row FA-000049; net book value $0. PO PO-2022-0009.</t>
+          <t>Cross-checked MD-00049 (MD-LA-050049, Lenovo ThinkPad T14) against HR, transfers, and ledger extracts. equipment_transfer_log TR-00049 posted Jan 21, 2026; inbound 2026-01-23 approval APR-00049. Source Ledger FA-000049; net book value $0. PO-2022-0009 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -12171,7 +12091,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>MD-00050 (Dell U2723QE) is Available at Dallas. Acquisition cost $565. Transfer TR-00050 received 2026-02-23; approval APR-00050. Fixed-asset extract includes FA-000050 (NBV $289.96). PO PO-2022-0009.</t>
+          <t>Working conclusion for MD-00050 (MD-MO-050050): Available at Dallas; cost $565. Source Ledger FA-000050; net book value $289.96. equipment_transfer_log TR-00050 posted Feb 23, 2026; inbound 2026-02-23 approval APR-00050. PO PO-2022-0009 documents the buy for MD-00050.</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -12279,7 +12199,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>MD-00051 (Samsung Galaxy S24) is Available at Denver. Acquisition cost $1040. Transfer TR-00051 received 2026-03-31; approval APR-00051. Ledger FA-000051 on file; NBV $573.03. PO PO-2022-0009.</t>
+          <t>Asset MD-00051 — Samsung Galaxy S24 — reconciled to Available in Denver on $1040 acquisition. capital PO PO-2022-0009 supports the cost basis. Source Ledger FA-000051; net book value $573.03. equipment_transfer_log TR-00051 posted Mar 31, 2026; inbound 2026-03-31 approval APR-00051.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -12387,7 +12307,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>MD-00052 (Cisco C9300) is Available at New York. Acquisition cost $6335. Transfer TR-00052 received 2026-05-02; approval APR-00052. FAR row FA-000052; net book value $933.99. PO PO-2022-0009.</t>
+          <t>Working conclusion for MD-00052 (MD-NE-050052): Available at New York; cost $6335. buy path for MD-00052 references PO-2022-0009. equipment_transfer_log TR-00052 posted May 01, 2026; inbound 2026-05-02 approval APR-00052. Source Ledger FA-000052; net book value $933.99.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -12495,7 +12415,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>MD-00053 (MacBook Pro 14) is Available at Seattle. Acquisition cost $2030. Transfer TR-00053 received 2026-06-05; approval APR-00053. Fixed-asset extract includes FA-000053 (NBV $0). PO PO-2022-0009.</t>
+          <t>Working conclusion for MD-00053 (MD-LA-050053): Available at Seattle; cost $2030. hardware_purchase_orders.csv ties MD-00053 to PO-2022-0009. equipment_transfer_log TR-00053 posted Jun 05, 2026; inbound 2026-06-05 approval APR-00053. Source Ledger FA-000053; net book value $0.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -12603,7 +12523,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>MD-00054 (Dell U2723QE) is Available at Atlanta. Acquisition cost $745. Transfer TR-00054 received 2026-01-16; approval APR-00054. Ledger FA-000054 on file; NBV $433.74. PO PO-2022-0009.</t>
+          <t>Asset MD-00054 — Dell U2723QE — reconciled to Available in Atlanta on $745 acquisition. PO PO-2022-0009 documents the buy for MD-00054. Source Ledger FA-000054; net book value $433.74. equipment_transfer_log TR-00054 posted Jan 10, 2026; inbound 2026-01-16 approval APR-00054.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -12711,7 +12631,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>MD-00055 (Samsung Galaxy S24) is Available at Chicago. Acquisition cost $1220. Transfer TR-00055 received 2026-02-12; approval APR-00055. FAR row FA-000055; net book value $812.5. PO PO-2023-0010.</t>
+          <t>Asset MD-00055 — Samsung Galaxy S24 — reconciled to Available in Chicago on $1220 acquisition. acquisition recorded on PO-2023-0010. Source Ledger FA-000055; net book value $812.5. equipment_transfer_log TR-00055 posted Feb 11, 2026; inbound 2026-02-12 approval APR-00055.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -12819,7 +12739,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>MD-00056 (Cisco C9300) is Available at Dallas. Acquisition cost $6200. Transfer TR-00056 received 2026-03-16; approval APR-00056. Fixed-asset extract includes FA-000056 (NBV $1345.24). PO PO-2023-0010.</t>
+          <t>Asset MD-00056 — Cisco C9300 — reconciled to Available in Dallas on $6200 acquisition. capital PO PO-2023-0010 supports the cost basis. Source Ledger FA-000056; net book value $1345.24. equipment_transfer_log TR-00056 posted Mar 16, 2026; inbound 2026-03-16 approval APR-00056.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -12927,7 +12847,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>MD-00057 (Dell Latitude 7440) is Available at Denver. Acquisition cost $1895. Transfer TR-00057 received 2026-04-24; approval APR-00057. Ledger FA-000057 on file; NBV $106.79. PO PO-2023-0010.</t>
+          <t>Working conclusion for MD-00057 (MD-LA-050057): Available at Denver; cost $1895. buy path for MD-00057 references PO-2023-0010. equipment_transfer_log TR-00057 posted Apr 20, 2026; inbound 2026-04-24 approval APR-00057. Source Ledger FA-000057; net book value $106.79.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -13039,7 +12959,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>MD-00058 (Dell U2723QE) is Pending Redeployment at New York. Acquisition cost $610. Transfer TR-00058 received 2026-05-23; approval blank. FAR row FA-000058; net book value $397.56. PO PO-2023-0010.</t>
+          <t>Working conclusion for MD-00058 (MD-MO-050058): Pending Redeployment at New York; cost $610. hardware_purchase_orders.csv ties MD-00058 to PO-2023-0010. equipment_transfer_log TR-00058 posted May 22, 2026; inbound 2026-05-23 blank approval field. Source Ledger FA-000058; net book value $397.56.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -13151,7 +13071,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>MD-00059 (Samsung Galaxy S24) is Pending Redeployment at Seattle. Acquisition cost $1085. Transfer TR-00059 received 2026-06-26; approval blank. Fixed-asset extract includes FA-000059 (NBV $847.35). PO PO-2023-0010.</t>
+          <t>Asset MD-00059 — Samsung Galaxy S24 — reconciled to Pending Redeployment in Seattle on $1085 acquisition. PO PO-2023-0010 documents the buy for MD-00059. Source Ledger FA-000059; net book value $847.35. equipment_transfer_log TR-00059 posted Jun 26, 2026; inbound 2026-06-26 blank approval field.</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -13263,7 +13183,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>MD-00060 (Cisco C9300) is Pending Redeployment at Atlanta. Acquisition cost $6380. Transfer TR-00060 received 2026-02-02; approval APR-00060. Ledger FA-000060 on file; NBV $549.35. PO PO-2023-0010.</t>
+          <t>Working conclusion for MD-00060 (MD-NE-050060): Pending Redeployment at Atlanta; cost $6380. Source Ledger FA-000060; net book value $549.35. order PO-2023-0010 appears in the purchasing extract. equipment_transfer_log TR-00060 posted Jan 30, 2026; inbound 2026-02-02 approval APR-00060.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -13375,7 +13295,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>MD-00061 (Lenovo ThinkPad T14) is Pending Redeployment at Chicago. Acquisition cost $2075. Transfer TR-00061 received 2026-02-03; approval APR-00061. FAR row FA-000061; net book value $0. PO PO-2024-0011.</t>
+          <t>Working conclusion for MD-00061 (MD-LA-050061): Pending Redeployment at Chicago; cost $2075. Source Ledger FA-000061; net book value $0. purchasing file shows PO-2024-0011 for this unit. equipment_transfer_log TR-00061 posted Feb 02, 2026; inbound 2026-02-03 approval APR-00061.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -13487,7 +13407,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 (Dell U2723QE) is Pending Redeployment at Dallas. Acquisition cost $790. Transfer TR-00062 received 2026-03-07; approval APR-00062. Fixed-asset extract includes FA-000062 (NBV $410.63). PO PO-2024-0011.</t>
+          <t>Working conclusion for MD-00062 (MD-MO-050062): Pending Redeployment at Dallas; cost $790. Source Ledger FA-000062; net book value $410.63. order PO-2024-0011 appears in the purchasing extract. equipment_transfer_log TR-00062 posted Mar 07, 2026; inbound 2026-03-07 approval APR-00062.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -13599,7 +13519,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>MD-00063 (Samsung Galaxy S24) is Pending Redeployment at Denver. Acquisition cost $950. Transfer TR-00063 received 2026-04-16; approval APR-00063. Ledger FA-000063 on file; NBV $533.85. PO PO-2024-0011.</t>
+          <t>Cross-checked MD-00063 (MD-MO-050063, Samsung Galaxy S24) against HR, transfers, and ledger extracts. equipment_transfer_log TR-00063 posted Apr 12, 2026; inbound 2026-04-16 approval APR-00063. PO-2024-0011 is the cited purchase order. Source Ledger FA-000063; net book value $533.85.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -13711,7 +13631,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>MD-00064 (Cisco C9300) is Pending Redeployment at New York. Acquisition cost $6245. Transfer TR-00064 received 2026-05-14; approval blank. FAR row FA-000064; net book value $961.76. PO PO-2024-0011.</t>
+          <t>Asset MD-00064 — Cisco C9300 — reconciled to Pending Redeployment in New York on $6245 acquisition. equipment_transfer_log TR-00064 posted May 13, 2026; inbound 2026-05-14 blank approval field. acquisition recorded on PO-2024-0011. Source Ledger FA-000064; net book value $961.76.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -13823,7 +13743,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 (MacBook Pro 14) is Pending Redeployment at Seattle. Acquisition cost $1940. Transfer TR-00065 received 2026-06-23; approval blank. Fixed-asset extract includes FA-000065 (NBV $0). PO PO-2024-0011.</t>
+          <t>Asset MD-00065 — MacBook Pro 14 — reconciled to Pending Redeployment in Seattle on $1940 acquisition. equipment_transfer_log TR-00065 posted Jun 17, 2026; inbound 2026-06-23 blank approval field. purchasing file shows PO-2024-0011 for this unit. Source Ledger FA-000065; net book value $0.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -13935,7 +13855,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>MD-00066 (Dell U2723QE) is Pending Redeployment at Atlanta. Acquisition cost $655. Transfer TR-00066 received 2026-01-25; approval APR-00066. Ledger FA-000066 on file; NBV $385.65. PO PO-2024-0011.</t>
+          <t>Asset MD-00066 — Dell U2723QE — reconciled to Pending Redeployment in Atlanta on $655 acquisition. equipment_transfer_log TR-00066 posted Jan 22, 2026; inbound 2026-01-25 approval APR-00066. buy path for MD-00066 references PO-2024-0011. Source Ledger FA-000066; net book value $385.65.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -14047,7 +13967,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>MD-00067 (Samsung Galaxy S24) is Pending Redeployment at Chicago. Acquisition cost $1130. Transfer TR-00067 received 2026-02-23; approval APR-00067. FAR row FA-000067; net book value $764.93. PO PO-2025-0012.</t>
+          <t>Asset MD-00067 — Samsung Galaxy S24 — reconciled to Pending Redeployment in Chicago on $1130 acquisition. equipment_transfer_log TR-00067 posted Feb 23, 2026; inbound 2026-02-23 approval APR-00067. capital PO PO-2025-0012 supports the cost basis. Source Ledger FA-000067; net book value $764.93.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -14059,7 +13979,7 @@
         <v>1130</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>764.9299999999999</v>
+        <v>764.93</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
@@ -14095,7 +14015,7 @@
         </is>
       </c>
       <c r="V71" t="n">
-        <v>764.9299999999999</v>
+        <v>764.93</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -14159,7 +14079,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>Offboarding return for MD-00068 lacks complete shipment proof; status remains Return Overdue. People file: E0081 (Elliott Park), status Separated. Transfer TR-00068 received 2026-04-03; approval APR-00068. Service desk ticket OFF-00068 on file. Fixed-asset extract includes FA-000068 (NBV $1436.28). PO PO-2025-0012.</t>
+          <t>Working conclusion for MD-00068 (MD-NE-050068): Return Overdue at Remote - Former Employee; cost $6425. offboarding ticket OFF-00068 referenced. hr_employee_status lists Elliott Park (E0081) as Separated. buy path for MD-00068 references PO-2025-0012. return still label-only per shipment file. equipment_transfer_log TR-00068 posted Mar 28, 2026; inbound 2026-04-03 approval APR-00068. Source Ledger FA-000068; net book value $1436.28.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -14271,7 +14191,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>Return for MD-00069 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0082 (Carmen Diaz) is Separated in hr_employee_status. Transfer TR-00069 received 2026-05-04; approval APR-00069. Service desk ticket OFF-00069 on file. Ledger FA-000069 on file; NBV $142.69. PO PO-2025-0012.</t>
+          <t>Asset MD-00069 — Dell Latitude 7440 — reconciled to Return Overdue in Remote - Former Employee on $2120 acquisition. offboarding ticket OFF-00069 referenced. Source Ledger FA-000069; net book value $142.69. hardware_purchase_orders.csv ties MD-00069 to PO-2025-0012. return still label-only per shipment file. hr_employee_status lists Carmen Diaz (E0082) as Separated. equipment_transfer_log TR-00069 posted May 02, 2026; inbound 2026-05-04 approval APR-00069.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -14383,7 +14303,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0083 / Hugh Talbot as Separated. Transfer TR-00070 received 2026-06-03; approval APR-00070. Service desk ticket OFF-00070 on file. FAR row FA-000070; net book value $342.32. PO PO-2025-0012.</t>
+          <t>Asset MD-00070 — Dell U2723QE — reconciled to Return Overdue in Remote - Former Employee on $520 acquisition. offboarding ticket OFF-00070 referenced. equipment_transfer_log TR-00070 posted Jun 03, 2026; inbound 2026-06-03 approval APR-00070. Source Ledger FA-000070; net book value $342.32. purchasing file shows PO-2025-0012 for this unit. hr_employee_status lists Hugh Talbot (E0083) as Separated. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -14495,7 +14415,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>Offboarding return for MD-00071 lacks complete shipment proof; status remains Return Overdue. People file: E0084 (Mira Adelman), status Separated. Transfer TR-00071 received 2026-07-12; approval APR-00071. Service desk ticket OFF-00071 on file. Fixed-asset extract includes FA-000071 (NBV $787.96). PO PO-2025-0012.</t>
+          <t>Asset MD-00071 — Samsung Galaxy S24 — reconciled to Return Overdue in Remote - Former Employee on $995 acquisition. offboarding ticket OFF-00071 referenced. equipment_transfer_log TR-00071 posted Jul 08, 2026; inbound 2026-07-12 approval APR-00071. Source Ledger FA-000071; net book value $787.96. order PO-2025-0012 appears in the purchasing extract. hr_employee_status lists Mira Adelman (E0084) as Separated. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -14607,7 +14527,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>Return for MD-00072 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0085 (Quincy Rhodes) is Separated in hr_employee_status. Transfer TR-00072 received 2026-01-18; approval APR-00072. Service desk ticket OFF-00072 on file. Ledger FA-000072 on file; NBV $500.27. PO PO-2025-0012.</t>
+          <t>Working conclusion for MD-00072 (MD-NE-050072): Return Overdue at Remote - Former Employee; cost $6290. PO-2025-0012 is the cited purchase order. hr_employee_status lists Quincy Rhodes (E0085) as Separated. return still label-only per shipment file. Source Ledger FA-000072; net book value $500.27. equipment_transfer_log TR-00072 posted Jan 18, 2026; inbound 2026-01-18 approval APR-00072. offboarding ticket OFF-00072 referenced.</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -14719,7 +14639,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>MD-00073 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0086 / Sloane Richter as Separated. Transfer TR-00073 received 2026-01-24; approval APR-00073. Service desk ticket OFF-00073 on file. FAR row FA-000073; net book value $0. PO PO-2022-0013.</t>
+          <t>Cross-checked MD-00073 (MD-LA-050073, Lenovo ThinkPad T14) against HR, transfers, and ledger extracts. hr_employee_status lists Sloane Richter (E0086) as Separated. equipment_transfer_log TR-00073 posted Jan 21, 2026; inbound 2026-01-24 approval APR-00073. offboarding ticket OFF-00073 referenced. acquisition recorded on PO-2022-0013. Source Ledger FA-000073; net book value $0. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -14831,7 +14751,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>Offboarding return for MD-00074 lacks complete shipment proof; status remains Return Overdue. People file: E0087 (Nolan Vega), status Separated. Transfer TR-00074 received 2026-02-24; approval APR-00074. Service desk ticket OFF-00074 on file. Fixed-asset extract includes FA-000074 (NBV $359.25). PO PO-2022-0013.</t>
+          <t>Working conclusion for MD-00074 (MD-MO-050074): Return Overdue at Carrier Network / Unverified; cost $700. shipment serial MISMATCH-0074 vs register MD-MO-050074. hr_employee_status lists Nolan Vega (E0087) as Separated. return still label-only per shipment file. Source Ledger FA-000074; net book value $359.25. equipment_transfer_log TR-00074 posted Feb 23, 2026; inbound 2026-02-24 approval APR-00074. offboarding ticket OFF-00074 referenced. purchasing file shows PO-2022-0013 for this unit.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -14943,7 +14863,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Return for MD-00075 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0088 (Ivy Chenoweth) is Separated in hr_employee_status. Transfer TR-00075 received 2026-04-01; approval APR-00075. Service desk ticket OFF-00075 on file. Ledger FA-000075 on file; NBV $647.42. PO PO-2022-0013.</t>
+          <t>Working conclusion for MD-00075 (MD-MO-050075): Return Overdue at Remote - Former Employee; cost $1175. order PO-2022-0013 appears in the purchasing extract. hr_employee_status lists Ivy Chenoweth (E0088) as Separated. return still label-only per shipment file. Source Ledger FA-000075; net book value $647.42. equipment_transfer_log TR-00075 posted Mar 31, 2026; inbound 2026-04-01 approval APR-00075. offboarding ticket OFF-00075 referenced.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -15055,7 +14975,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0089 / Percy Lambert as Separated. Transfer TR-00076 received 2026-05-03; approval APR-00076. Service desk ticket OFF-00076 on file. FAR row FA-000076; net book value $953.89. PO PO-2022-0013.</t>
+          <t>Asset MD-00076 — Cisco C9300 — reconciled to Return Overdue in Carrier Network / Unverified on $6470 acquisition. offboarding ticket OFF-00076 referenced. equipment_transfer_log TR-00076 posted May 01, 2026; inbound 2026-05-03 approval APR-00076. Source Ledger FA-000076; net book value $953.89. hardware_purchase_orders.csv ties MD-00076 to PO-2022-0013. shipment serial MISMATCH-0076 vs register MD-NE-050076. return still label-only per shipment file. hr_employee_status lists Percy Lambert (E0089) as Separated.</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -15167,7 +15087,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Offboarding return for MD-00077 lacks complete shipment proof; status remains Return Overdue. People file: E0090 (Dana Ghosh), status Separated. Transfer TR-00077 received 2026-06-06; approval APR-00077. Service desk ticket OFF-00077 on file. Fixed-asset extract includes FA-000077 (NBV $0). PO PO-2022-0013.</t>
+          <t>Asset MD-00077 — MacBook Pro 14 — reconciled to Return Overdue in Remote - Former Employee on $1850 acquisition. offboarding ticket OFF-00077 referenced. equipment_transfer_log TR-00077 posted Jun 05, 2026; inbound 2026-06-06 approval APR-00077. Source Ledger FA-000077; net book value $0. PO PO-2022-0013 documents the buy for MD-00077. hr_employee_status lists Dana Ghosh (E0090) as Separated. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -15279,7 +15199,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Return for MD-00078 is overdue. Label exists; carrier acceptance and receiving proof do not. Custodian E0091 (Harlan Smith) is Separated in hr_employee_status. Transfer TR-00078 received 2026-01-10; approval APR-00078. Service desk ticket OFF-00078 on file. Ledger FA-000078 on file; NBV $328.95. PO PO-2022-0013.</t>
+          <t>Asset MD-00078 — Dell U2723QE — reconciled to Return Overdue in Remote - Former Employee on $565 acquisition. offboarding ticket OFF-00078 referenced. equipment_transfer_log TR-00078 posted Jan 10, 2026; inbound 2026-01-10 approval APR-00078. Source Ledger FA-000078; net book value $328.95. capital PO PO-2022-0013 supports the cost basis. hr_employee_status lists Harlan Smith (E0091) as Separated. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -15391,7 +15311,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>MD-00079 marked Return Overdue pending carrier + dock evidence. hr_employee_status lists E0092 / June Okoye as Separated. Transfer TR-00079 received 2026-02-13; approval APR-00079. Service desk ticket OFF-00079 on file. FAR row FA-000079; net book value $692.62. PO PO-2023-0014.</t>
+          <t>Asset MD-00079 — Samsung Galaxy S24 — reconciled to Return Overdue in Remote - Former Employee on $1040 acquisition. offboarding ticket OFF-00079 referenced. equipment_transfer_log TR-00079 posted Feb 11, 2026; inbound 2026-02-13 approval APR-00079. Source Ledger FA-000079; net book value $692.62. PO PO-2023-0014 documents the buy for MD-00079. hr_employee_status lists June Okoye (E0092) as Separated. return still label-only per shipment file.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -15503,7 +15423,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>MD-00080 (Cisco C9300) is Available at Atlanta Warehouse. Acquisition cost $6335. Transfer TR-00080 received 2026-03-17; approval APR-00080. Fixed-asset extract includes FA-000080 (NBV $1374.53). PO PO-2023-0014.</t>
+          <t>Asset MD-00080 — Cisco C9300 — reconciled to Available in Atlanta Warehouse on $6335 acquisition. order PO-2023-0014 appears in the purchasing extract. Source Ledger FA-000080; net book value $1374.53. equipment_transfer_log TR-00080 posted Mar 16, 2026; inbound 2026-03-17 approval APR-00080.</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -15615,7 +15535,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>MD-00081 (Dell Latitude 7440) is Available at Atlanta Warehouse. Acquisition cost $2030. Transfer TR-00081 received 2026-04-20; approval APR-00081. Ledger FA-000081 on file; NBV $114.4. PO PO-2023-0014.</t>
+          <t>Asset MD-00081 — Dell Latitude 7440 — reconciled to Available in Atlanta Warehouse on $2030 acquisition. PO-2023-0014 is the cited purchase order. Source Ledger FA-000081; net book value $114.4. equipment_transfer_log TR-00081 posted Apr 20, 2026; inbound 2026-04-20 approval APR-00081.</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -15727,7 +15647,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>MD-00082 is In Transit - Exception at Carrier Network / Unverified; shipment documentation is incomplete. hr_employee_status lists E0095 / Emmett Boyle as Separated. Transfer TR-00082 received 2026-05-24; approval APR-00082. Service desk ticket OFF-00082 on file. FAR row FA-000082; net book value $485.55. PO PO-2023-0014. Tracking 1ZMD00000082 receiving scan shows MISMATCH-0082 vs MD-MO-050082.</t>
+          <t>Asset MD-00082 — Dell U2723QE — reconciled to In Transit - Exception in Carrier Network / Unverified on $745 acquisition. Source Ledger FA-000082; net book value $485.55. receiving_exception_scan_1ZMD00000082.png is an investigative lead only. shipment serial MISMATCH-0082 vs register MD-MO-050082. equipment_transfer_log TR-00082 posted May 22, 2026; inbound 2026-05-24 approval APR-00082. hr_employee_status lists Emmett Boyle (E0095) as Separated. acquisition recorded on PO-2023-0014. carrier label 1ZMD00000082 is not proof of receipt. offboarding ticket OFF-00082 referenced.</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -15839,7 +15759,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 (Samsung Galaxy S24) is Available at Atlanta Warehouse. Acquisition cost $1220. Transfer TR-00083 received 2026-06-27; approval APR-00083. Fixed-asset extract includes FA-000083 (NBV $952.79). PO PO-2023-0014.</t>
+          <t>Files reviewed for MD-00083: Samsung Galaxy S24, basis $1220, operating site Atlanta Warehouse, status Available. Source Ledger FA-000083; net book value $952.79. equipment_transfer_log TR-00083 posted Jun 26, 2026; inbound 2026-06-27 approval APR-00083. purchasing file shows PO-2023-0014 for this unit.</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -15951,7 +15871,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>MD-00084 is In Transit - Exception at Carrier Network / Unverified; shipment documentation is incomplete. Custodian E0072 (Anita Bose) is Separated in hr_employee_status. Transfer TR-00084 received 2026-02-05; approval APR-00084. Service desk ticket OFF-00084 on file. Ledger FA-000084 on file; NBV $533.85. PO PO-2023-0014.</t>
+          <t>Asset MD-00084 — Cisco C9300 — reconciled to In Transit - Exception in Carrier Network / Unverified on $6200 acquisition. Source Ledger FA-000084; net book value $533.85. shipment serial MISMATCH-0084 vs register MD-NE-050084. offboarding ticket OFF-00084 referenced. equipment_transfer_log TR-00084 posted Jan 30, 2026; inbound 2026-02-05 approval APR-00084. hr_employee_status lists Anita Bose (E0072) as Separated. order PO-2023-0014 appears in the purchasing extract.</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -16063,7 +15983,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 (Lenovo ThinkPad T14) is Available at Atlanta Warehouse. Acquisition cost $1895. Transfer TR-00085 received 2026-02-03; approval APR-00085. FAR row FA-000085; net book value $0. PO PO-2024-0015.</t>
+          <t>Working conclusion for MD-00085 (MD-LA-050085): Available at Atlanta Warehouse; cost $1895. Source Ledger FA-000085; net book value $0. equipment_transfer_log TR-00085 posted Feb 02, 2026; inbound 2026-02-03 approval APR-00085. purchasing file shows PO-2024-0015 for this unit.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -16175,7 +16095,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>MD-00086 (Dell U2723QE) is Available at Atlanta Warehouse. Acquisition cost $610. Transfer TR-00086 received 2026-03-08; approval APR-00086. Fixed-asset extract includes FA-000086 (NBV $317.07). PO PO-2024-0015.</t>
+          <t>Working conclusion for MD-00086 (MD-MO-050086): Available at Atlanta Warehouse; cost $610. Source Ledger FA-000086; net book value $317.07. equipment_transfer_log TR-00086 posted Mar 07, 2026; inbound 2026-03-08 approval APR-00086. buy path for MD-00086 references PO-2024-0015.</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -16287,7 +16207,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>MD-00087 (Samsung Galaxy S24) is Available at Atlanta Warehouse. Acquisition cost $1085. Transfer TR-00087 received 2026-04-12; approval APR-00087. Ledger FA-000087 on file; NBV $609.71. PO PO-2024-0015.</t>
+          <t>Working conclusion for MD-00087 (MD-MO-050087): Available at Atlanta Warehouse; cost $1085. Source Ledger FA-000087; net book value $609.71. equipment_transfer_log TR-00087 posted Apr 12, 2026; inbound 2026-04-12 approval APR-00087. hardware_purchase_orders.csv ties MD-00087 to PO-2024-0015.</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -16399,7 +16319,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>MD-00088 (Cisco C9300) is Available at Atlanta Warehouse. Acquisition cost $6380. Transfer TR-00088 received 2026-05-14; approval APR-00088. FAR row FA-000088; net book value $982.55. PO PO-2024-0015. Duplicate serial MD-NE-050088 shared with the paired asset.</t>
+          <t>Files reviewed for MD-00088: Cisco C9300, basis $6380, operating site Atlanta Warehouse, status Available. Source Ledger FA-000088; net book value $982.55. duplicate serial MD-NE-050088 flagged on the register. PO PO-2024-0015 documents the buy for MD-00088. equipment_transfer_log TR-00088 posted May 13, 2026; inbound 2026-05-14 approval APR-00088.</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -16511,7 +16431,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Cannot confirm custody of MD-00089 at this time; register last pointed to Unknown. People file: E0077 (Jonah Freedman), status Separated. Transfer TR-00089 received 2026-06-17; approval APR-00089. Service desk ticket OFF-00089 on file. Fixed-asset extract includes FA-000089 (NBV $0). PO PO-2024-0015.</t>
+          <t>Asset MD-00089 — MacBook Pro 14 — reconciled to Missing in Unknown on $2075 acquisition. Source Ledger FA-000089; net book value $0. last operational site on register was Denver - Closed. offboarding ticket OFF-00089 referenced. equipment_transfer_log TR-00089 posted Jun 17, 2026; inbound 2026-06-17 approval APR-00089. hr_employee_status lists Jonah Freedman (E0077) as Separated. capital PO PO-2024-0015 supports the cost basis.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -16623,7 +16543,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>No confirmed location for MD-00090 (Dell U2723QE); last recorded site was Unknown. Custodian E0078 (Regina Lowe) is Separated in hr_employee_status. Transfer TR-00090 received 2026-01-28; approval APR-00090. Service desk ticket OFF-00090 on file. Ledger FA-000090 on file; NBV $465.13. PO PO-2024-0015.</t>
+          <t>Asset MD-00090 — Dell U2723QE — reconciled to Missing in Unknown on $790 acquisition. offboarding ticket OFF-00090 referenced. Source Ledger FA-000090; net book value $465.13. last operational site on register was Chicago - Closed. PO-2024-0015 is the cited purchase order. hr_employee_status lists Regina Lowe (E0078) as Separated. equipment_transfer_log TR-00090 posted Jan 22, 2026; inbound 2026-01-28 approval APR-00090.</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -16735,7 +16655,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>MD-00091 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0079 / Wes Carvalho as Separated. Transfer TR-00091 received 2026-02-24; approval APR-00091. Service desk ticket OFF-00091 on file. FAR row FA-000091; net book value $643.09. PO PO-2025-0016.</t>
+          <t>Asset MD-00091 — Samsung Galaxy S24 — reconciled to Missing in Unknown on $950 acquisition. offboarding ticket OFF-00091 referenced. Source Ledger FA-000091; net book value $643.09. last operational site on register was Denver - Closed. order PO-2025-0016 appears in the purchasing extract. hr_employee_status lists Wes Carvalho (E0079) as Separated. equipment_transfer_log TR-00091 posted Feb 23, 2026; inbound 2026-02-24 approval APR-00091.</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -16847,7 +16767,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Cannot confirm custody of MD-00092 at this time; register last pointed to Unknown. People file: E0080 (Tara Singh), status Separated. Transfer TR-00092 received 2026-03-28; approval APR-00092. Service desk ticket OFF-00092 on file. Fixed-asset extract includes FA-000092 (NBV $1396.04). PO PO-2025-0016. Duplicate serial MD-NE-050088 shared with the paired asset.</t>
+          <t>Asset MD-00092 — Cisco C9300 — reconciled to Missing in Unknown on $6245 acquisition. offboarding ticket OFF-00092 referenced. Source Ledger FA-000092; net book value $1396.04. last operational site on register was Chicago - Closed. duplicate serial MD-NE-050088 flagged on the register. hr_employee_status lists Tara Singh (E0080) as Separated. equipment_transfer_log TR-00092 posted Mar 28, 2026; inbound 2026-03-28 approval APR-00092. PO-2025-0016 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -16959,7 +16879,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>No confirmed location for MD-00093 (Dell Latitude 7440); last recorded site was Unknown. Custodian E0081 (Elliott Park) is Separated in hr_employee_status. Transfer TR-00093 received 2026-05-06; approval APR-00093. Service desk ticket OFF-00093 on file. Ledger FA-000093 on file; NBV $130.57. PO PO-2025-0016.</t>
+          <t>Files reviewed for MD-00093: Dell Latitude 7440, basis $1940, operating site Unknown, status Missing. equipment_transfer_log TR-00093 posted May 02, 2026; inbound 2026-05-06 approval APR-00093. acquisition recorded on PO-2025-0016. last operational site on register was Denver - Closed. Source Ledger FA-000093; net book value $130.57. offboarding ticket OFF-00093 referenced. hr_employee_status lists Elliott Park (E0081) as Separated.</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -17071,7 +16991,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>MD-00094 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0082 / Carmen Diaz as Separated. Transfer TR-00094 received 2026-06-04; approval APR-00094. Service desk ticket OFF-00094 on file. FAR row FA-000094; net book value $431.2. PO PO-2025-0016.</t>
+          <t>Asset MD-00094 — Dell U2723QE — reconciled to Missing in Unknown on $655 acquisition. offboarding ticket OFF-00094 referenced. Source Ledger FA-000094; net book value $431.2. last operational site on register was Chicago - Closed. purchasing file shows PO-2025-0016 for this unit. hr_employee_status lists Carmen Diaz (E0082) as Separated. equipment_transfer_log TR-00094 posted Jun 03, 2026; inbound 2026-06-04 approval APR-00094.</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -17183,7 +17103,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Cannot confirm custody of MD-00095 at this time; register last pointed to Unknown. People file: E0083 (Hugh Talbot), status Separated. Transfer TR-00095 received 2026-07-08; approval APR-00095. Service desk ticket OFF-00095 on file. Fixed-asset extract includes FA-000095 (NBV $894.87). PO PO-2025-0016.</t>
+          <t>Asset MD-00095 — Samsung Galaxy S24 — reconciled to Missing in Unknown on $1130 acquisition. offboarding ticket OFF-00095 referenced. Source Ledger FA-000095; net book value $894.87. last operational site on register was Denver - Closed. order PO-2025-0016 appears in the purchasing extract. hr_employee_status lists Hugh Talbot (E0083) as Separated. equipment_transfer_log TR-00095 posted Jul 08, 2026; inbound 2026-07-08 approval APR-00095.</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -17295,7 +17215,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>No confirmed location for MD-00096 (Cisco C9300); last recorded site was Unknown. Custodian E0084 (Mira Adelman) is Separated in hr_employee_status. Transfer TR-00096 received 2026-01-19; approval APR-00096. Service desk ticket OFF-00096 on file. Ledger FA-000096 on file; NBV $511.01. PO PO-2025-0016.</t>
+          <t>Asset MD-00096 — Cisco C9300 — reconciled to Missing in Unknown on $6425 acquisition. offboarding ticket OFF-00096 referenced. Source Ledger FA-000096; net book value $511.01. last operational site on register was Chicago - Closed. PO-2025-0016 is the cited purchase order. hr_employee_status lists Mira Adelman (E0084) as Separated. equipment_transfer_log TR-00096 posted Jan 18, 2026; inbound 2026-01-19 approval APR-00096.</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -17407,7 +17327,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>MD-00097 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0085 / Quincy Rhodes as Separated. Transfer TR-00097 received 2026-01-27; approval APR-00097. Service desk ticket OFF-00097 on file. FAR row FA-000097; net book value $0. PO PO-2022-0017.</t>
+          <t>Working conclusion for MD-00097 (MD-LA-050097): Missing at Unknown; cost $2120. offboarding ticket OFF-00097 referenced. purchasing file shows PO-2022-0017 for this unit. last operational site on register was Denver - Closed. Source Ledger FA-000097; net book value $0. equipment_transfer_log TR-00097 posted Jan 21, 2026; inbound 2026-01-27 approval APR-00097. hr_employee_status lists Quincy Rhodes (E0085) as Separated.</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -17519,7 +17439,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>Cannot confirm custody of MD-00098 at this time; register last pointed to Unknown. People file: E0086 (Sloane Richter), status Separated. Transfer TR-00098 received 2026-02-24; approval APR-00098. Service desk ticket OFF-00098 on file. Fixed-asset extract includes FA-000098 (NBV $266.87). PO PO-2022-0017.</t>
+          <t>Asset MD-00098 — Dell U2723QE — reconciled to Missing in Unknown on $520 acquisition. offboarding ticket OFF-00098 referenced. PO-2022-0017 is the cited purchase order. Source Ledger FA-000098; net book value $266.87. equipment_transfer_log TR-00098 posted Feb 23, 2026; inbound 2026-02-24 approval APR-00098. hr_employee_status lists Sloane Richter (E0086) as Separated. last operational site on register was Chicago - Closed.</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -17631,7 +17551,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>No confirmed location for MD-00099 (Samsung Galaxy S24); last recorded site was Unknown. Custodian E0087 (Nolan Vega) is Separated in hr_employee_status. Transfer TR-00099 received 2026-04-02; approval APR-00099. Service desk ticket OFF-00099 on file. Ledger FA-000099 on file; NBV $548.24. PO PO-2022-0017.</t>
+          <t>Working conclusion for MD-00099 (MD-MO-050099): Missing at Unknown; cost $995. offboarding ticket OFF-00099 referenced. purchasing file shows PO-2022-0017 for this unit. last operational site on register was Denver - Closed. Source Ledger FA-000099; net book value $548.24. equipment_transfer_log TR-00099 posted Mar 31, 2026; inbound 2026-04-02 approval APR-00099. hr_employee_status lists Nolan Vega (E0087) as Separated.</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -17743,7 +17663,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>MD-00100 stays Missing. Prior site on file: Unknown. hr_employee_status lists E0088 / Ivy Chenoweth as Separated. Transfer TR-00100 received 2026-05-05; approval APR-00100. Service desk ticket OFF-00100 on file. FAR row FA-000100; net book value $927.36. PO PO-2022-0017.</t>
+          <t>Working conclusion for MD-00100 (MD-NE-050100): Missing at Unknown; cost $6290. offboarding ticket OFF-00100 referenced. hr_employee_status lists Ivy Chenoweth (E0088) as Separated. purchasing file shows PO-2022-0017 for this unit. last operational site on register was Chicago - Closed. equipment_transfer_log TR-00100 posted May 01, 2026; inbound 2026-05-05 approval APR-00100. Source Ledger FA-000100; net book value $927.36.</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -17855,7 +17775,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00101 received 2026-06-07; approval APR-00101. Service desk ticket RET-00101 on file. Fixed-asset extract includes FA-000101 (NBV $0). PO PO-2022-0017.</t>
+          <t>Asset MD-00101 — MacBook Pro 14 — reconciled to Retired/Pending Disposal in Seattle on $1985 acquisition. PO-2022-0017 is the cited purchase order. Source Ledger FA-000101; net book value $0. equipment_transfer_log TR-00101 posted Jun 05, 2026; inbound 2026-06-07 approval APR-00101. offboarding ticket RET-00101 referenced.</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -17967,7 +17887,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00102 received 2026-01-11; approval APR-00102. Service desk ticket RET-00102 on file. Ledger FA-000102 on file; NBV $407.54. PO PO-2022-0017.</t>
+          <t>Files reviewed for MD-00102: Dell U2723QE, basis $700, operating site Atlanta, status Retired/Pending Disposal. Source Ledger FA-000102; net book value $407.54. equipment_transfer_log TR-00102 posted Jan 10, 2026; inbound 2026-01-11 approval APR-00102. offboarding ticket RET-00102 referenced. purchasing file shows PO-2022-0017 for this unit.</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -18079,7 +17999,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>MD-00103 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00103 received 2026-02-14; approval APR-00103. Service desk ticket RET-00103 on file. FAR row FA-000103; net book value $782.53. PO PO-2023-0018.</t>
+          <t>Files reviewed for MD-00103: Samsung Galaxy S24, basis $1175, operating site Chicago, status Retired/Pending Disposal. Source Ledger FA-000103; net book value $782.53. equipment_transfer_log TR-00103 posted Feb 11, 2026; inbound 2026-02-14 approval APR-00103. offboarding ticket RET-00103 referenced. purchasing file shows PO-2023-0018 for this unit.</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -18191,7 +18111,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>MD-00104 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00104 received 2026-03-18; approval APR-00104. Service desk ticket RET-00104 on file. Fixed-asset extract includes FA-000104 (NBV $1403.83). PO PO-2023-0018.</t>
+          <t>Files reviewed for MD-00104: Cisco C9300, basis $6470, operating site Dallas, status Retired/Pending Disposal. Source Ledger FA-000104; net book value $1403.83. equipment_transfer_log TR-00104 posted Mar 16, 2026; inbound 2026-03-18 approval APR-00104. offboarding ticket RET-00104 referenced. PO-2023-0018 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -18303,7 +18223,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00105 received 2026-04-21; approval APR-00105. Service desk ticket RET-00105 on file. Ledger FA-000105 on file; NBV $104.26. PO PO-2023-0018.</t>
+          <t>Asset MD-00105 — Dell Latitude 7440 — reconciled to Retired/Pending Disposal in Denver on $1850 acquisition. purchasing file shows PO-2023-0018 for this unit. Source Ledger FA-000105; net book value $104.26. equipment_transfer_log TR-00105 posted Apr 20, 2026; inbound 2026-04-21 approval APR-00105. offboarding ticket RET-00105 referenced.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -18415,7 +18335,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>MD-00106 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00106 received 2026-05-25; approval APR-00106. Service desk ticket RET-00106 on file. FAR row FA-000106; net book value $368.24. PO PO-2023-0018.</t>
+          <t>Asset MD-00106 — Dell U2723QE — reconciled to Retired/Pending Disposal in New York on $565 acquisition. hardware_purchase_orders.csv ties MD-00106 to PO-2023-0018. Source Ledger FA-000106; net book value $368.24. equipment_transfer_log TR-00106 posted May 22, 2026; inbound 2026-05-25 approval APR-00106. offboarding ticket RET-00106 referenced.</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -18527,7 +18447,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>MD-00107 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00107 received 2026-06-27; approval APR-00107. Service desk ticket RET-00107 on file. Fixed-asset extract includes FA-000107 (NBV $812.21). PO PO-2023-0018.</t>
+          <t>Files reviewed for MD-00107: Samsung Galaxy S24, basis $1040, operating site Seattle, status Retired/Pending Disposal. Source Ledger FA-000107; net book value $812.21. equipment_transfer_log TR-00107 posted Jun 26, 2026; inbound 2026-06-27 approval APR-00107. offboarding ticket RET-00107 referenced. capital PO PO-2023-0018 supports the cost basis.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -18639,7 +18559,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00108 received 2026-01-30; approval APR-00108. Service desk ticket RET-00108 on file. Ledger FA-000108 on file; NBV $545.48. PO PO-2023-0018.</t>
+          <t>Files reviewed for MD-00108: Cisco C9300, basis $6335, operating site Atlanta, status Retired/Pending Disposal. Source Ledger FA-000108; net book value $545.48. equipment_transfer_log TR-00108 posted Jan 30, 2026; inbound 2026-01-30 approval APR-00108. offboarding ticket RET-00108 referenced. hardware_purchase_orders.csv ties MD-00108 to PO-2023-0018.</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -18751,7 +18671,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00109 received 2026-02-04; approval APR-00109. Service desk ticket RET-00109 on file. FAR row FA-000109; net book value $0. PO PO-2024-0019.</t>
+          <t>Files reviewed for MD-00109: Lenovo ThinkPad T14, basis $2030, operating site Chicago, status Retired/Pending Disposal. Source Ledger FA-000109; net book value $0. equipment_transfer_log TR-00109 posted Feb 02, 2026; inbound 2026-02-04 approval APR-00109. offboarding ticket RET-00109 referenced. hardware_purchase_orders.csv ties MD-00109 to PO-2024-0019.</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -18863,7 +18783,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>MD-00110 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00110 received 2026-03-08; approval APR-00110. Service desk ticket RET-00110 on file. Fixed-asset extract includes FA-000110 (NBV $387.24). PO PO-2024-0019.</t>
+          <t>Asset MD-00110 — Dell U2723QE — reconciled to Retired/Pending Disposal in Dallas on $745 acquisition. equipment_transfer_log TR-00110 posted Mar 07, 2026; inbound 2026-03-08 approval APR-00110. Source Ledger FA-000110; net book value $387.24. PO-2024-0019 is the cited purchase order. offboarding ticket RET-00110 referenced.</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -18975,7 +18895,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>MD-00111 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00111 received 2026-04-13; approval APR-00111. Ledger FA-000111 on file; NBV $0. PO PO-2024-0019.</t>
+          <t>Working conclusion for MD-00111 (MD-MO-050111): Disposed at Disposed; cost $1220. Source Ledger FA-000111; net book value $0. purchasing file shows PO-2024-0019 for this unit. equipment_transfer_log TR-00111 posted Apr 12, 2026; inbound 2026-04-13 approval APR-00111.</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -19083,7 +19003,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>MD-00112 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00112 received 2026-05-15; approval APR-00112. FAR row FA-000112; net book value $0. PO PO-2024-0019.</t>
+          <t>Asset MD-00112 — Cisco C9300 — reconciled to Disposed in Disposed on $6200 acquisition. equipment_transfer_log TR-00112 posted May 13, 2026; inbound 2026-05-15 approval APR-00112. Source Ledger FA-000112; net book value $0. PO-2024-0019 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19191,7 +19111,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>MD-00113 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00113 received 2026-06-18; approval APR-00113. Fixed-asset extract includes FA-000113 (NBV $0). PO PO-2024-0019.</t>
+          <t>Files reviewed for MD-00113: MacBook Pro 14, basis $1895, operating site Disposed, status Disposed. Source Ledger FA-000113; net book value $0. purchasing file shows PO-2024-0019 for this unit. equipment_transfer_log TR-00113 posted Jun 17, 2026; inbound 2026-06-18 approval APR-00113.</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19299,7 +19219,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>MD-00114 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00114 received 2026-01-22; approval APR-00114. Service desk ticket RET-00114 on file. Ledger FA-000114 on file; NBV $0. PO PO-2024-0019.</t>
+          <t>Files reviewed for MD-00114: Dell U2723QE, basis $610, operating site Disposed (certificate missing), status Retired/Pending Disposal. Source Ledger FA-000114; net book value $0. PO-2024-0019 is the cited purchase order. offboarding ticket RET-00114 referenced. equipment_transfer_log TR-00114 posted Jan 22, 2026; inbound 2026-01-22 approval APR-00114. no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19411,7 +19331,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>MD-00115 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00115 received 2026-02-25; approval APR-00115. FAR row FA-000115; net book value $0. PO PO-2025-0020.</t>
+          <t>Files reviewed for MD-00115: Samsung Galaxy S24, basis $1085, operating site Disposed, status Disposed. Source Ledger FA-000115; net book value $0. PO PO-2025-0020 documents the buy for MD-00115. equipment_transfer_log TR-00115 posted Feb 23, 2026; inbound 2026-02-25 approval APR-00115.</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19519,7 +19439,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>MD-00116 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00116 received 2026-03-29; approval APR-00116. Fixed-asset extract includes FA-000116 (NBV $0). PO PO-2025-0020.</t>
+          <t>Asset MD-00116 — Cisco C9300 — reconciled to Disposed in Disposed on $6380 acquisition. equipment_transfer_log TR-00116 posted Mar 28, 2026; inbound 2026-03-29 approval APR-00116. PO-2025-0020 is the cited purchase order. Source Ledger FA-000116; net book value $0.</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19627,7 +19547,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>MD-00117 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00117 received 2026-05-02; approval APR-00117. Ledger FA-000117 on file; NBV $0. PO PO-2025-0020.</t>
+          <t>Files reviewed for MD-00117: Dell Latitude 7440, basis $2075, operating site Disposed, status Disposed. Source Ledger FA-000117; net book value $0. purchasing file shows PO-2025-0020 for this unit. equipment_transfer_log TR-00117 posted May 02, 2026; inbound 2026-05-02 approval APR-00117.</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19735,7 +19655,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 is Retired/Pending Disposal. Disposal certificate has not been verified. Transfer TR-00118 received 2026-06-04; approval APR-00118. Service desk ticket RET-00118 on file. FAR row FA-000118; net book value $0. PO PO-2025-0020.</t>
+          <t>Files reviewed for MD-00118: Dell U2723QE, basis $790, operating site Disposed (certificate missing), status Retired/Pending Disposal. Source Ledger FA-000118; net book value $0. PO-2025-0020 is the cited purchase order. offboarding ticket RET-00118 referenced. equipment_transfer_log TR-00118 posted Jun 03, 2026; inbound 2026-06-04 approval APR-00118. no verified disposal certificate located.</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19847,7 +19767,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>MD-00119 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00119 received 2026-07-09; approval APR-00119. Fixed-asset extract includes FA-000119 (NBV $0). PO PO-2025-0020.</t>
+          <t>Files reviewed for MD-00119: Samsung Galaxy S24, basis $950, operating site Disposed, status Disposed. Source Ledger FA-000119; net book value $0. purchasing file shows PO-2025-0020 for this unit. equipment_transfer_log TR-00119 posted Jul 08, 2026; inbound 2026-07-09 approval APR-00119.</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -19959,7 +19879,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>MD-00120 closed as Disposed with certificate support; site recorded as Disposed. Transfer TR-00120 received 2026-01-20; approval APR-00120. Ledger FA-000120 on file; NBV $0. PO PO-2025-0020.</t>
+          <t>Files reviewed for MD-00120: Cisco C9300, basis $6245, operating site Disposed, status Disposed. PO PO-2025-0020 documents the buy for MD-00120. equipment_transfer_log TR-00120 posted Jan 18, 2026; inbound 2026-01-20 approval APR-00120. Source Ledger FA-000120; net book value $0.</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -20063,7 +19983,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>MD-00121 (Lenovo ThinkPad T14) is Available at Chicago. Acquisition cost $1940. Transfer TR-00121 received 2026-01-21; approval APR-00121. FAR row FA-000121; net book value $0. PO PO-2022-0021.</t>
+          <t>Asset MD-00121 — Lenovo ThinkPad T14 — reconciled to Available in Chicago on $1940 acquisition. equipment_transfer_log TR-00121 posted Jan 21, 2026; inbound 2026-01-21 approval APR-00121. Source Ledger FA-000121; net book value $0. buy path for MD-00121 references PO-2022-0021.</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -20171,7 +20091,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>MD-00122 (Dell U2723QE) is Available at Dallas. Acquisition cost $655. Transfer TR-00122 received 2026-02-25; approval APR-00122. Fixed-asset extract includes FA-000122 (NBV $336.15). PO PO-2022-0021.</t>
+          <t>Files reviewed for MD-00122: Dell U2723QE, basis $655, operating site Dallas, status Available. PO PO-2022-0021 documents the buy for MD-00122. equipment_transfer_log TR-00122 posted Feb 23, 2026; inbound 2026-02-25 approval APR-00122. Source Ledger FA-000122; net book value $336.15.</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20279,7 +20199,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>MD-00123 (Samsung Galaxy S24) is Available at Denver. Acquisition cost $1130. Transfer TR-00123 received 2026-04-03; approval APR-00123. Ledger FA-000123 on file; NBV $622.62. PO PO-2022-0021.</t>
+          <t>Files reviewed for MD-00123: Samsung Galaxy S24, basis $1130, operating site Denver, status Available. buy path for MD-00123 references PO-2022-0021. equipment_transfer_log TR-00123 posted Mar 31, 2026; inbound 2026-04-03 approval APR-00123. Source Ledger FA-000123; net book value $622.62.</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20387,7 +20307,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>MD-00124 (Cisco C9300) is Available at New York. Acquisition cost $6425. Transfer TR-00124 received 2026-05-01; approval APR-00124. FAR row FA-000124; net book value $947.26. PO PO-2022-0021.</t>
+          <t>Files reviewed for MD-00124: Cisco C9300, basis $6425, operating site New York, status Available. PO PO-2022-0021 documents the buy for MD-00124. equipment_transfer_log TR-00124 posted May 01, 2026; inbound 2026-05-01 approval APR-00124. Source Ledger FA-000124; net book value $947.26.</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20495,7 +20415,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>MD-00125 (MacBook Pro 14) is Available at Seattle. Acquisition cost $2120. Transfer TR-00125 received 2026-06-08; approval APR-00125. Fixed-asset extract includes FA-000125 (NBV $0). PO PO-2022-0021.</t>
+          <t>Reconciliation packet cites MD-00125 with acquisition $2120 and custody Available at Seattle. equipment_transfer_log TR-00125 posted Jun 05, 2026; inbound 2026-06-08 approval APR-00125. Source Ledger FA-000125; net book value $0. buy path for MD-00125 references PO-2022-0021.</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20603,7 +20523,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>MD-00126 (Dell U2723QE) is Available at Atlanta. Acquisition cost $520. Transfer TR-00126 received 2026-01-12; approval APR-00126. Ledger FA-000126 on file; NBV $302.75. PO PO-2022-0021.</t>
+          <t>Reconciliation packet cites MD-00126 with acquisition $520 and custody Available at Atlanta. equipment_transfer_log TR-00126 posted Jan 10, 2026; inbound 2026-01-12 approval APR-00126. Source Ledger FA-000126; net book value $302.75. purchasing file shows PO-2022-0021 for this unit.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20715,7 +20635,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00127: In Use. Site Denver. Model Samsung Galaxy S24; cost $995. hr_employee_status lists E0061 / Liam Keane as Transferred. Transfer TR-00127 received 2026-02-17; approval blank. FAR row FA-000127; net book value $662.65. PO PO-2023-0022.</t>
+          <t>Reconciliation packet cites MD-00127 with acquisition $995 and custody In Use at Denver. hr_employee_status lists Liam Keane (E0061) as Transferred. equipment_transfer_log TR-00127 posted Feb 11, 2026; inbound 2026-02-17 blank approval field. Source Ledger FA-000127; net book value $662.65. purchasing file shows PO-2023-0022 for this unit.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20827,7 +20747,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>New York holds MD-00128 (Cisco C9300) as In Use. Acquisition $6290. People file: E0062 (Bianca Silva), status Transferred. Transfer TR-00128 received 2026-03-19; approval APR-00128. Fixed-asset extract includes FA-000128 (NBV $1364.77). PO PO-2023-0022.</t>
+          <t>Reconciliation packet cites MD-00128 with acquisition $6290 and custody In Use at New York. hr_employee_status lists Bianca Silva (E0062) as Transferred. equipment_transfer_log TR-00128 posted Mar 16, 2026; inbound 2026-03-19 approval APR-00128. Source Ledger FA-000128; net book value $1364.77. PO-2023-0022 is the cited purchase order.</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20935,7 +20855,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>MD-00129 (Dell Latitude 7440) is In Use at Seattle. Acquisition cost $1985. Custodian E0063 (Greg Hollis) is Transferred in hr_employee_status. Transfer TR-00129 received 2026-04-21; approval APR-00129. Ledger FA-000129 on file; NBV $111.86. PO PO-2023-0022.</t>
+          <t>Reconciliation packet cites MD-00129 with acquisition $1985 and custody In Use at Seattle. hr_employee_status lists Greg Hollis (E0063) as Transferred. equipment_transfer_log TR-00129 posted Apr 20, 2026; inbound 2026-04-21 approval APR-00129. Source Ledger FA-000129; net book value $111.86. purchasing file shows PO-2023-0022 for this unit.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -21043,7 +20963,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>Status for MD-00130: In Use. Site Atlanta. Model Dell U2723QE; cost $700. hr_employee_status lists E0064 / Naomi Berger as Transferred. Transfer TR-00130 received 2026-05-28; approval APR-00130. PO PO-2023-0023 (capitalization_approved=No); $700 below $2,500 so FAR absence is expected under ITAM-001 section 7.</t>
+          <t>Files reviewed for MD-00130: Dell U2723QE, basis $700, operating site Atlanta, status In Use. equipment_transfer_log TR-00130 posted May 22, 2026; inbound 2026-05-28 approval APR-00130. hr_employee_status lists Naomi Berger (E0064) as Transferred. PO-2023-0023 covers under-threshold MD-00130; no FAR row expected under ITAM-001 §7.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -21131,7 +21051,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>Chicago holds MD-00131 (Samsung Galaxy S24) as In Use. Acquisition $1175. People file: E0065 (Felix Moreno), status Transferred. Transfer TR-00131 received 2026-06-28; approval APR-00131. PO PO-2023-0023 (capitalization_approved=No); $1175 below $2,500 so FAR absence is expected under ITAM-001 section 7.</t>
+          <t>Files reviewed for MD-00131: Samsung Galaxy S24, basis $1175, operating site Chicago, status In Use. equipment_transfer_log TR-00131 posted Jun 26, 2026; inbound 2026-06-28 approval APR-00131. hr_employee_status lists Felix Moreno (E0065) as Transferred. PO-2023-0023 covers under-threshold MD-00131; no FAR row expected under ITAM-001 §7.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -21219,7 +21139,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>MD-00132 (Cisco C9300) is In Use at Dallas. Acquisition cost $6470. Custodian E0066 (Sharon Quinlan) is Transferred in hr_employee_status. Transfer TR-00132 received 2026-01-31; approval APR-00132. PO PO-2023-0022; $6470 exceeds $2,500 with no FA row. RN-0132 under-threshold claim rejected.</t>
+          <t>Files reviewed for MD-00132: Cisco C9300, basis $6470, operating site Dallas, status In Use. equipment_transfer_log TR-00132 posted Jan 30, 2026; inbound 2026-01-31 approval APR-00132. hr_employee_status lists Sharon Quinlan (E0066) as Transferred. RN-0132 under-threshold claim rejected; $6,470 exceeds gate with no FA row.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -21301,7 +21221,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -21405,7 +21324,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Finance Controller owns cost-basis cleanup on MD-00017; clear FA-000017 over-depreciation before relying on NBV.</t>
+          <t>Finance Controller: clear FA-000017 over-depreciation and cost basis on MD-00017 before relying on NBV.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -21425,7 +21344,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Pulled PO-2024-0003 and FA-000017; numbers diverge for MD-00017. FA-000017 accumulated depreciation $2160 exceeds acquisition cost $2070 by $90.</t>
+          <t>Pulled PO-2024-0003 and FA-000017 for MD-00017: register $1985.0 vs ledger $2070.0. FA-000017 accumulated depreciation $2160 exceeds acquisition $2070 by $90.</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -21470,7 +21389,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Two assets share MD-LA-050021 (MD-00021,MD-00025). Bench-validate and issue a new serial.</t>
+          <t>Bench-validate and retag duplicate serial MD-LA-050021 involving MD-00021 (EX-0002).</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -21490,7 +21409,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Serial MD-LA-050021 appears on more than one tag (MD-00021,MD-00025).</t>
+          <t>Serial MD-LA-050021 appears on MD-00021 and MD-00021,MD-00025; bench validation required (EX-0002).</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -21535,7 +21454,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>MD-00025 location field lagged after consolidation; update from Denver - Closed to Chicago (EX-0003).</t>
+          <t>Retire the closed-office code on MD-00025 and post Chicago as the working site; cite TR-00025 in the update (EX-0003)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -21555,7 +21474,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Closed floor Denver - Closed remains on MD-00025 despite transfer evidence (EX-0003, TR-00025).</t>
+          <t>Site code Denver - Closed on MD-00025 was retired during consolidation but remains on the asset row. equipment_transfer_log TR-00025 points to Chicago. operating footprint for MD-00025 is Chicago, not Denver - Closed. finding EX-0003.</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -21600,7 +21519,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Retag required - MD-LA-050021 collision involving MD-00025.</t>
+          <t>Bench-validate and retag duplicate serial MD-LA-050021 involving MD-00025 (EX-0004).</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -21620,7 +21539,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Serial MD-LA-050021 appears on more than one tag (MD-00021,MD-00025) [EX-0004].</t>
+          <t>Serial MD-LA-050021 appears on MD-00025 and MD-00021,MD-00025; bench validation required (EX-0004).</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -21665,7 +21584,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>MD-00026 location field lagged after consolidation; update from Chicago - Closed to Dallas (EX-0005).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00026 with Dallas on the register; cite TR-00026 in the update (EX-0005)</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -21685,7 +21604,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Walked register vs HR/transfer: MD-00026 still says Chicago - Closed (EX-0005).</t>
+          <t>equipment_transfer_log TR-00026 points to Dallas. operating footprint for MD-00026 is Dallas, not Chicago - Closed. finding EX-0005. Site code Chicago - Closed on MD-00026 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -21730,7 +21649,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is no longer occupied. Park MD-00027 at Denver on the register (EX-0006).</t>
+          <t>Correct the stale location on MD-00027 (Denver - Closed → Denver); cite TR-00027 in the update (EX-0006)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -21750,7 +21669,7 @@
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Register still codes MD-00027 to Denver - Closed; TR-00027 points to Denver (EX-0006).</t>
+          <t>The register extract for MD-00027 carries location Denver - Closed after that floor was vacated. operating footprint for MD-00027 is Denver, not Denver - Closed. equipment_transfer_log TR-00027 points to Denver. finding EX-0006.</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -21795,7 +21714,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>MD-00028 cannot remain on shuttered floor Chicago - Closed. Set location to New York (EX-0007).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00028 with New York on the register; cite TR-00028 in the update (EX-0007)</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -21815,7 +21734,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00028 is consolidation debt (Chicago - Closed, EX-0007).</t>
+          <t>equipment_transfer_log TR-00028 points to New York. finding EX-0007. operating footprint for MD-00028 is New York, not Chicago - Closed. Inventory row MD-00028 (serial MD-NE-050028) still lists site Chicago - Closed.</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -21860,7 +21779,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Closed floor Denver - Closed stays on MD-00029; rewrite required (EX-0008).</t>
+          <t>Correct the stale location on MD-00029 (Denver - Closed → Seattle); cite TR-00029 in the update (EX-0008)</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -21880,7 +21799,7 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Consolidation left MD-00029 @ Denver - Closed; ops now use Seattle (EX-0008).</t>
+          <t>finding EX-0008. Site code Denver - Closed on MD-00029 was retired during consolidation but remains on the asset row. equipment_transfer_log TR-00029 points to Seattle. operating footprint for MD-00029 is Seattle, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -21925,7 +21844,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Register still lists MD-00030 at Chicago - Closed. Replace with Atlanta (EX-0009).</t>
+          <t>Retire the closed-office code on MD-00030 and post Atlanta as the working site; cite TR-00030 in the update (EX-0009)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -21945,7 +21864,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>TR-00030 destination is not the shuttered office listed for MD-00030 (EX-0009).</t>
+          <t>equipment_transfer_log TR-00030 points to Atlanta. operating footprint for MD-00030 is Atlanta, not Chicago - Closed. finding EX-0009. Site code Chicago - Closed on MD-00030 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -21990,7 +21909,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Fix MD-00031: register site Denver - Closed conflicts with current ops at Chicago (EX-0010).</t>
+          <t>Replace shuttered site Denver - Closed on MD-00031 with Chicago on the register; cite TR-00031 in the update (EX-0010)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -22010,7 +21929,7 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Did not treat closed building Denver - Closed as live location for MD-00031 (EX-0010).</t>
+          <t>Site code Denver - Closed on MD-00031 was retired during consolidation but remains on the asset row. operating footprint for MD-00031 is Chicago, not Denver - Closed. finding EX-0010. equipment_transfer_log TR-00031 points to Chicago.</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -22055,7 +21974,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is no longer occupied. Park MD-00032 at Dallas on the register (EX-0011).</t>
+          <t>Correct the stale location on MD-00032 (Chicago - Closed → Dallas); cite TR-00032 in the update (EX-0011)</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -22075,7 +21994,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Finding EX-0011: MD-00032 location stale at Chicago - Closed; prefer Dallas.</t>
+          <t>The register extract for MD-00032 carries location Chicago - Closed after that floor was vacated. equipment_transfer_log TR-00032 points to Dallas. operating footprint for MD-00032 is Dallas, not Chicago - Closed. finding EX-0011.</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -22120,7 +22039,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Closed floor Denver - Closed stays on MD-00033; rewrite required (EX-0012).</t>
+          <t>Replace shuttered site Denver - Closed on MD-00033 with Denver on the register; cite TR-00033 in the update (EX-0012)</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -22140,7 +22059,7 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Register still codes MD-00033 to Denver - Closed; TR-00033 points to Denver (EX-0012).</t>
+          <t>operating footprint for MD-00033 is Denver, not Denver - Closed. equipment_transfer_log TR-00033 points to Denver. Inventory row MD-00033 (serial MD-LA-050033) still lists site Denver - Closed. finding EX-0012.</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -22185,7 +22104,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Do not leave MD-00034 assigned to unused floor Chicago - Closed (EX-0013).</t>
+          <t>Correct the stale location on MD-00034 (Chicago - Closed → New York); cite TR-00034 in the update (EX-0013)</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -22205,7 +22124,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Register still codes MD-00034 to Chicago - Closed; TR-00034 points to New York (EX-0013).</t>
+          <t>Site code Chicago - Closed on MD-00034 was retired during consolidation but remains on the asset row. operating footprint for MD-00034 is New York, not Chicago - Closed. equipment_transfer_log TR-00034 points to New York. finding EX-0013.</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -22242,7 +22161,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Ledger:FA-000034; PO:PO-2023-0006; RegisterCost:790.0; LedgerCost:930.0; NBVOverstatement:35.0; CorrectNBV:479.88</t>
+          <t>Ledger:FA-000034; PO:PO-2023-0006; RegisterCost:790.0; LedgerCost:930.0</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
@@ -22250,7 +22169,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Align cost on MD-00034: register 790.0 vs ledger 930.0 (FA-000034).</t>
+          <t>Finance Controller: reconcile register $790.0 vs ledger $930.0 on FA-000034 for MD-00034 and confirm NBV $479.88 on FA-000034.</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -22270,7 +22189,7 @@
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Pulled PO-2023-0006 and FA-000034; numbers diverge for MD-00034. Separately, FA-000034 NBV print $514.88 overstates correct NBV $479.88 (acq $930 − accum dep $450.12) by $35.00.</t>
+          <t>Compared PO-2023-0006 and FA-000034 for MD-00034: register acquisition $790.0 vs ledger $930.0. NBV on FA-000034 should be $479.88 (acquisition $930 less accumulated depreciation $450.12).</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -22315,7 +22234,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>HR-aligned site for MD-00035 is Seattle; register still says Denver - Closed (EX-0015).</t>
+          <t>Retire the closed-office code on MD-00035 and post Seattle as the working site; cite TR-00035 in the update (EX-0015)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -22335,7 +22254,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00035 is consolidation debt (Denver - Closed, EX-0015).</t>
+          <t>equipment_transfer_log TR-00035 points to Seattle. finding EX-0015. Site code Denver - Closed on MD-00035 was retired during consolidation but remains on the asset row. operating footprint for MD-00035 is Seattle, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -22380,7 +22299,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Update register location for MD-00036 before the next cert packet (EX-0016).</t>
+          <t>IT Asset Specialist: change MD-00036 location from Chicago - Closed to Atlanta; cite TR-00036 in the update (EX-0016)</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -22400,7 +22319,7 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>HR/transfer support Atlanta; register kept Chicago - Closed for MD-00036 (EX-0016).</t>
+          <t>finding EX-0016. The register extract for MD-00036 carries location Chicago - Closed after that floor was vacated. equipment_transfer_log TR-00036 points to Atlanta. operating footprint for MD-00036 is Atlanta, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -22445,7 +22364,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00037 off Denver - Closed; Chicago is the live office per TR-00037 (EX-0017).</t>
+          <t>Retire the closed-office code on MD-00037 and post Chicago as the working site; cite TR-00037 in the update (EX-0017)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -22465,7 +22384,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Site code on MD-00037 did not survive consolidation (Denver - Closed, EX-0017).</t>
+          <t>equipment_transfer_log TR-00037 points to Chicago. finding EX-0017. operating footprint for MD-00037 is Chicago, not Denver - Closed. Inventory row MD-00037 (serial MD-LA-050037) still lists site Denver - Closed.</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -22510,7 +22429,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>HR-aligned site for MD-00038 is Dallas; register still says Chicago - Closed (EX-0018).</t>
+          <t>IT Asset Specialist: change MD-00038 location from Chicago - Closed to Dallas; cite TR-00038 in the update (EX-0018)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -22530,7 +22449,7 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>Finding EX-0018: MD-00038 location stale at Chicago - Closed; prefer Dallas.</t>
+          <t>equipment_transfer_log TR-00038 points to Dallas. finding EX-0018. Site code Chicago - Closed on MD-00038 was retired during consolidation but remains on the asset row. operating footprint for MD-00038 is Dallas, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -22575,7 +22494,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Remove closed-site coding on MD-00039 (Denver - Closed → Denver, EX-0019).</t>
+          <t>Retire the closed-office code on MD-00039 and post Denver as the working site; cite TR-00039 in the update (EX-0019)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -22595,7 +22514,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Denver is the operating site; MD-00039 still lists Denver - Closed (EX-0019).</t>
+          <t>finding EX-0019. The register extract for MD-00039 carries location Denver - Closed after that floor was vacated. equipment_transfer_log TR-00039 points to Denver. operating footprint for MD-00039 is Denver, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -22640,7 +22559,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist to retire Chicago - Closed on MD-00040 and apply New York (EX-0020).</t>
+          <t>Retire the closed-office code on MD-00040 and post New York as the working site; cite TR-00040 in the update (EX-0020)</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -22660,7 +22579,7 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>Location evidence for MD-00040: closed floor Chicago - Closed vs live New York (EX-0020).</t>
+          <t>equipment_transfer_log TR-00040 points to New York. Site code Chicago - Closed on MD-00040 was retired during consolidation but remains on the asset row. finding EX-0020. operating footprint for MD-00040 is New York, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -22705,7 +22624,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Update register location for MD-00041 before the next cert packet (EX-0021).</t>
+          <t>IT Asset Specialist: change MD-00041 location from Denver - Closed to Seattle; cite TR-00041 in the update (EX-0021)</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -22725,7 +22644,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed conflicts with current footprint for MD-00041 (EX-0021).</t>
+          <t>The register extract for MD-00041 carries location Denver - Closed after that floor was vacated. operating footprint for MD-00041 is Seattle, not Denver - Closed. finding EX-0021. equipment_transfer_log TR-00041 points to Seattle.</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -22770,7 +22689,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Remove closed-site coding on MD-00042 (Chicago - Closed → Atlanta, EX-0022).</t>
+          <t>Retire the closed-office code on MD-00042 and post Atlanta as the working site; cite TR-00042 in the update (EX-0022)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -22790,7 +22709,7 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>Closed floor Chicago - Closed remains on MD-00042 despite transfer evidence (EX-0022, TR-00042).</t>
+          <t>operating footprint for MD-00042 is Atlanta, not Chicago - Closed. finding EX-0022. Inventory row MD-00042 (serial MD-MO-050042) still lists site Chicago - Closed. equipment_transfer_log TR-00042 points to Atlanta.</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -22835,7 +22754,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist owns the location rewrite for MD-00043 at Denver - Closed (EX-0023).</t>
+          <t>IT Asset Specialist: change MD-00043 location from Denver - Closed to Chicago; cite TR-00043 in the update (EX-0023)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -22855,7 +22774,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00043 is consolidation debt (Denver - Closed, EX-0023).</t>
+          <t>operating footprint for MD-00043 is Chicago, not Denver - Closed. finding EX-0023. equipment_transfer_log TR-00043 points to Chicago. Site code Denver - Closed on MD-00043 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -22900,7 +22819,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>MD-00044 / Chicago - Closed is a consolidation leftover - move to Dallas (EX-0024).</t>
+          <t>Retire the closed-office code on MD-00044 and post Dallas as the working site; cite TR-00044 in the update (EX-0024)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -22920,7 +22839,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>Walked register vs HR/transfer: MD-00044 still says Chicago - Closed (EX-0024).</t>
+          <t>operating footprint for MD-00044 is Dallas, not Chicago - Closed. finding EX-0024. equipment_transfer_log TR-00044 points to Dallas. The register extract for MD-00044 carries location Chicago - Closed after that floor was vacated.</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -22965,7 +22884,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00045 off Denver - Closed; Denver is the live office per TR-00045 (EX-0025).</t>
+          <t>IT Asset Specialist: change MD-00045 location from Denver - Closed to Denver; cite TR-00045 in the update (EX-0025)</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -22985,7 +22904,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed conflicts with current footprint for MD-00045 (EX-0025).</t>
+          <t>equipment_transfer_log TR-00045 points to Denver. finding EX-0025. Inventory row MD-00045 (serial MD-LA-050045) still lists site Denver - Closed. operating footprint for MD-00045 is Denver, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -23030,7 +22949,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Fix MD-00046: register site Chicago - Closed conflicts with current ops at New York (EX-0026).</t>
+          <t>Retire the closed-office code on MD-00046 and post New York as the working site; cite TR-00046 in the update (EX-0026)</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -23050,7 +22969,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00046 there on paper - New York is live (EX-0026).</t>
+          <t>equipment_transfer_log TR-00046 points to New York. operating footprint for MD-00046 is New York, not Chicago - Closed. finding EX-0026. Site code Chicago - Closed on MD-00046 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -23095,7 +23014,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00047 off Denver - Closed; Seattle is the live office per TR-00047 (EX-0027).</t>
+          <t>IT Asset Specialist: change MD-00047 location from Denver - Closed to Seattle; cite TR-00047 in the update (EX-0027)</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -23115,7 +23034,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>Physical sites changed; MD-00047 register did not (Denver - Closed, EX-0027).</t>
+          <t>equipment_transfer_log TR-00047 points to Seattle. finding EX-0027. operating footprint for MD-00047 is Seattle, not Denver - Closed. The register extract for MD-00047 carries location Denver - Closed after that floor was vacated.</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -23160,7 +23079,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Closed floor Chicago - Closed stays on MD-00048; rewrite required (EX-0028).</t>
+          <t>Retire the closed-office code on MD-00048 and post Atlanta as the working site; cite TR-00048 in the update (EX-0028)</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -23180,7 +23099,7 @@
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>Unused-office coding on MD-00048 is unsupported by movement files (EX-0028).</t>
+          <t>equipment_transfer_log TR-00048 points to Atlanta. finding EX-0028. operating footprint for MD-00048 is Atlanta, not Chicago - Closed. Inventory row MD-00048 (serial MD-NE-050048) still lists site Chicago - Closed.</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -23225,7 +23144,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>MD-00049 cannot remain on shuttered floor Denver - Closed. Set location to Chicago (EX-0029).</t>
+          <t>IT Asset Specialist: change MD-00049 location from Denver - Closed to Chicago; cite TR-00049 in the update (EX-0029)</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -23245,7 +23164,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>Physical sites changed; MD-00049 register did not (Denver - Closed, EX-0029).</t>
+          <t>equipment_transfer_log TR-00049 points to Chicago. finding EX-0029. Site code Denver - Closed on MD-00049 was retired during consolidation but remains on the asset row. operating footprint for MD-00049 is Chicago, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -23290,7 +23209,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Fix MD-00050: register site Chicago - Closed conflicts with current ops at Dallas (EX-0030).</t>
+          <t>IT Asset Specialist: change MD-00050 location from Chicago - Closed to Dallas; cite TR-00050 in the update (EX-0030)</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -23310,7 +23229,7 @@
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>Site code on MD-00050 did not survive consolidation (Chicago - Closed, EX-0030).</t>
+          <t>operating footprint for MD-00050 is Dallas, not Chicago - Closed. equipment_transfer_log TR-00050 points to Dallas. Inventory row MD-00050 (serial MD-MO-050050) still lists site Chicago - Closed. finding EX-0030.</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -23355,7 +23274,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Operating site for MD-00051 is Denver; TR-00051 confirms, not Denver - Closed (EX-0031).</t>
+          <t>Retire the closed-office code on MD-00051 and post Denver as the working site; cite TR-00051 in the update (EX-0031)</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -23375,7 +23294,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>Closed-site leftover on extract for MD-00051 (Denver - Closed). TR-00051. EX-0031.</t>
+          <t>operating footprint for MD-00051 is Denver, not Denver - Closed. finding EX-0031. Site code Denver - Closed on MD-00051 was retired during consolidation but remains on the asset row. equipment_transfer_log TR-00051 points to Denver.</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -23420,7 +23339,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Reconcile PO-2022-0009 / FA-000051 / register cost for MD-00051.</t>
+          <t>Align cost on MD-00051: register 1040.0 vs ledger 1250.0 (FA-000051) (EX-0032).</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -23440,7 +23359,7 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>Cost spread on MD-00051: ITAM $1040.0, FAR 1250.0 (FA-000051).</t>
+          <t>Register cost $1040.0 on MD-00051 does not match ledger $1250.0 on FA-000051 (EX-0032).</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -23485,7 +23404,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00052 off Chicago - Closed; New York is the live office per TR-00052 (EX-0033).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00052 with New York on the register; cite TR-00052 in the update (EX-0033)</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -23505,7 +23424,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00052 there on paper - New York is live (EX-0033).</t>
+          <t>Site code Chicago - Closed on MD-00052 was retired during consolidation but remains on the asset row. operating footprint for MD-00052 is New York, not Chicago - Closed. equipment_transfer_log TR-00052 points to New York. finding EX-0033.</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -23550,7 +23469,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>HR-aligned site for MD-00053 is Seattle; register still says Denver - Closed (EX-0034).</t>
+          <t>Correct the stale location on MD-00053 (Denver - Closed → Seattle); cite TR-00053 in the update (EX-0034)</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -23570,7 +23489,7 @@
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00053 is consolidation debt (Denver - Closed, EX-0034).</t>
+          <t>The register extract for MD-00053 carries location Denver - Closed after that floor was vacated. finding EX-0034. operating footprint for MD-00053 is Seattle, not Denver - Closed. equipment_transfer_log TR-00053 points to Seattle.</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -23615,7 +23534,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist to retire Chicago - Closed on MD-00054 and apply Atlanta (EX-0035).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00054 with Atlanta on the register; cite TR-00054 in the update (EX-0035)</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -23635,7 +23554,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>TR-00054 destination is not the shuttered office listed for MD-00054 (EX-0035).</t>
+          <t>equipment_transfer_log TR-00054 points to Atlanta. Inventory row MD-00054 (serial MD-MO-050054) still lists site Chicago - Closed. finding EX-0035. operating footprint for MD-00054 is Atlanta, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -23680,7 +23599,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Register still lists MD-00055 at Denver - Closed. Replace with Chicago (EX-0036).</t>
+          <t>Correct the stale location on MD-00055 (Denver - Closed → Chicago); cite TR-00055 in the update (EX-0036)</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -23700,7 +23619,7 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00055 is consolidation debt (Denver - Closed, EX-0036).</t>
+          <t>equipment_transfer_log TR-00055 points to Chicago. finding EX-0036. operating footprint for MD-00055 is Chicago, not Denver - Closed. Site code Denver - Closed on MD-00055 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -23745,7 +23664,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00056 off Chicago - Closed; Dallas is the live office per TR-00056 (EX-0037).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00056 with Dallas on the register; cite TR-00056 in the update (EX-0037)</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -23765,7 +23684,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>TR-00056 destination is not the shuttered office listed for MD-00056 (EX-0037).</t>
+          <t>finding EX-0037. The register extract for MD-00056 carries location Chicago - Closed after that floor was vacated. equipment_transfer_log TR-00056 points to Dallas. operating footprint for MD-00056 is Dallas, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -23810,7 +23729,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Fix MD-00057: register site Denver - Closed conflicts with current ops at Denver (EX-0038).</t>
+          <t>Correct the stale location on MD-00057 (Denver - Closed → Denver); cite TR-00057 in the update (EX-0038)</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -23830,7 +23749,7 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00057 is consolidation debt (Denver - Closed, EX-0038).</t>
+          <t>finding EX-0038. Inventory row MD-00057 (serial MD-LA-050057) still lists site Denver - Closed. equipment_transfer_log TR-00057 points to Denver. operating footprint for MD-00057 is Denver, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -23875,7 +23794,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Separated ID E0071 must leave MD-00058 before status changes.</t>
+          <t>Remove E0071 as custodian on MD-00058; park under Regional IT or IT Stock (EX-0039).</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -23895,7 +23814,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>People extract vs register: MD-00058 retained leaver E0071. OFF-00058.</t>
+          <t>hr_employee_status shows E0071 as separated. Register still assigns MD-00058 to E0071. EX-0039. offboarding ticket OFF-00058 closed without a custodian change on MD-00058.</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -23940,7 +23859,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Do not leave MD-00058 assigned to unused floor Chicago - Closed (EX-0040).</t>
+          <t>Correct the stale location on MD-00058 (Chicago - Closed → New York); cite TR-00058 in the update (EX-0040)</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -23960,7 +23879,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>Unused-office coding on MD-00058 is unsupported by movement files (EX-0040).</t>
+          <t>The register extract for MD-00058 carries location Chicago - Closed after that floor was vacated. finding EX-0040. operating footprint for MD-00058 is New York, not Chicago - Closed. equipment_transfer_log TR-00058 points to New York.</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -24005,7 +23924,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>§4 gap on TR-00058 for MD-00058; get APR or reverse.</t>
+          <t>Obtain APR on TR-00058 or reverse move for MD-00058 (EX-0041).</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -24025,7 +23944,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>Transfer log TR-00058: move recorded, APR missing.</t>
+          <t>Transfer TR-00058 for MD-00058 has a blank approval_id per ITAM-001 §4 (EX-0041).</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -24070,7 +23989,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Close people assignment on MD-00059; ticket OFF-00059.</t>
+          <t>Remove E0072 as custodian on MD-00059; park under Regional IT or IT Stock (EX-0042).</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -24090,7 +24009,7 @@
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>People extract vs register: MD-00059 retained leaver E0072. OFF-00059.</t>
+          <t>hr_employee_status shows E0072 as separated. Register still assigns MD-00059 to E0072. EX-0042. offboarding ticket OFF-00059 closed without a custodian change on MD-00059.</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -24135,7 +24054,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Walkthrough finding EX-0043: MD-00059 still shows Denver - Closed. Correct to Seattle.</t>
+          <t>Correct the stale location on MD-00059 (Denver - Closed → Seattle); cite TR-00059 in the update (EX-0043)</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -24155,7 +24074,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>Seattle is the operating site; MD-00059 still lists Denver - Closed (EX-0043).</t>
+          <t>operating footprint for MD-00059 is Seattle, not Denver - Closed. finding EX-0043. Site code Denver - Closed on MD-00059 was retired during consolidation but remains on the asset row. equipment_transfer_log TR-00059 points to Seattle.</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -24200,7 +24119,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Approval missing on TR-00059. Retro sign-off or return MD-00059.</t>
+          <t>Obtain APR on TR-00059 or reverse move for MD-00059 (EX-0044).</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -24220,7 +24139,7 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>§4 evidence gap - TR-00059 lacks approval for MD-00059.</t>
+          <t>Transfer TR-00059 for MD-00059 has a blank approval_id per ITAM-001 §4 (EX-0044).</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -24265,7 +24184,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Assignment on MD-00060 survived HR term for E0073. Correct it.</t>
+          <t>Remove E0073 as custodian on MD-00060; park under Regional IT or IT Stock (EX-0045).</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -24285,7 +24204,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>Register owner on MD-00060 is stale relative to HR for E0073 (EX-0045).</t>
+          <t>hr_employee_status shows E0073 as separated. EX-0045. Register still assigns MD-00060 to E0073. offboarding ticket OFF-00060 closed without a custodian change on MD-00060.</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -24330,7 +24249,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Do not leave MD-00060 assigned to unused floor Chicago - Closed (EX-0046).</t>
+          <t>IT Asset Specialist: change MD-00060 location from Chicago - Closed to Atlanta; cite TR-00060 in the update (EX-0046)</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -24350,7 +24269,7 @@
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>Location evidence for MD-00060: closed floor Chicago - Closed vs live Atlanta (EX-0046).</t>
+          <t>equipment_transfer_log TR-00060 points to Atlanta. operating footprint for MD-00060 is Atlanta, not Chicago - Closed. finding EX-0046. The register extract for MD-00060 carries location Chicago - Closed after that floor was vacated.</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -24395,7 +24314,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>HR Operations Lead: remove E0074 from MD-00061 and park the kit.</t>
+          <t>Remove E0074 as custodian on MD-00061; park under Regional IT or IT Stock (EX-0047).</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -24415,7 +24334,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>Custodian mismatch MD-00061↔E0074 documented under EX-0047.</t>
+          <t>Register still assigns MD-00061 to E0074. offboarding ticket OFF-00061 closed without a custodian change on MD-00061. hr_employee_status shows E0074 as separated. EX-0047.</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -24460,7 +24379,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Fix MD-00061: register site Denver - Closed conflicts with current ops at Chicago (EX-0048).</t>
+          <t>Correct the stale location on MD-00061 (Denver - Closed → Chicago); cite TR-00061 in the update (EX-0048)</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -24480,7 +24399,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>Finding EX-0048: MD-00061 location stale at Denver - Closed; prefer Chicago.</t>
+          <t>operating footprint for MD-00061 is Chicago, not Denver - Closed. equipment_transfer_log TR-00061 points to Chicago. The register extract for MD-00061 carries location Denver - Closed after that floor was vacated. finding EX-0048.</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -24525,7 +24444,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Recover or write-off later; first take E0075 off MD-00062.</t>
+          <t>Remove E0075 as custodian on MD-00062; park under Regional IT or IT Stock (EX-0049).</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -24545,7 +24464,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 should have moved off E0075 when HR flipped status (EX-0049).</t>
+          <t>hr_employee_status shows E0075 as separated. EX-0049. offboarding ticket OFF-00062 closed without a custodian change on MD-00062. Register still assigns MD-00062 to E0075.</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -24590,7 +24509,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 / Chicago - Closed is a consolidation leftover - move to Dallas (EX-0050).</t>
+          <t>Correct the stale location on MD-00062 (Chicago - Closed → Dallas); cite TR-00062 in the update (EX-0050)</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -24610,7 +24529,7 @@
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>Walked register vs HR/transfer: MD-00062 still says Chicago - Closed (EX-0050).</t>
+          <t>operating footprint for MD-00062 is Dallas, not Chicago - Closed. equipment_transfer_log TR-00062 points to Dallas. Site code Chicago - Closed on MD-00062 was retired during consolidation but remains on the asset row. finding EX-0050.</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -24655,7 +24574,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Assignment on MD-00063 survived HR term for E0076. Correct it.</t>
+          <t>Remove E0076 as custodian on MD-00063; park under Regional IT or IT Stock (EX-0051).</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -24675,7 +24594,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>MD-00063 should have moved off E0076 when HR flipped status (EX-0051).</t>
+          <t>offboarding ticket OFF-00063 closed without a custodian change on MD-00063. EX-0051. Register still assigns MD-00063 to E0076. hr_employee_status shows E0076 as separated.</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -24720,7 +24639,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00063 must reflect Denver after the site close (EX-0052).</t>
+          <t>Retire the closed-office code on MD-00063 and post Denver as the working site; cite TR-00063 in the update (EX-0052)</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -24740,7 +24659,7 @@
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>Inventory row for MD-00063 lagged after site close (Denver - Closed, EX-0052).</t>
+          <t>equipment_transfer_log TR-00063 points to Denver. Site code Denver - Closed on MD-00063 was retired during consolidation but remains on the asset row. finding EX-0052. operating footprint for MD-00063 is Denver, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -24785,7 +24704,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>HR shows E0077 gone - remove as custodian on MD-00064 (OFF-00064).</t>
+          <t>Remove E0077 as custodian on MD-00064; park under Regional IT or IT Stock (EX-0053).</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -24805,7 +24724,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>Offboarding closed for E0077; asset row did not follow for MD-00064 (EX-0053).</t>
+          <t>EX-0053. Register still assigns MD-00064 to E0077. hr_employee_status shows E0077 as separated. offboarding ticket OFF-00064 closed without a custodian change on MD-00064.</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -24850,7 +24769,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is no longer occupied. Park MD-00064 at New York on the register (EX-0054).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00064 with New York on the register; cite TR-00064 in the update (EX-0054)</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -24870,7 +24789,7 @@
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>Register still codes MD-00064 to Chicago - Closed; TR-00064 points to New York (EX-0054).</t>
+          <t>equipment_transfer_log TR-00064 points to New York. Site code Chicago - Closed on MD-00064 was retired during consolidation but remains on the asset row. finding EX-0054. operating footprint for MD-00064 is New York, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -24915,7 +24834,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Either approve TR-00064 after the fact or put MD-00064 back.</t>
+          <t>Obtain APR on TR-00064 or reverse move for MD-00064 (EX-0055).</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -24935,7 +24854,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>TR-00064 shows blank approval_id for MD-00064.</t>
+          <t>Transfer TR-00064 for MD-00064 has a blank approval_id per ITAM-001 §4 (EX-0055).</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -24980,7 +24899,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>People side closed via OFF-00065; asset row still lists E0078. Fix custodian.</t>
+          <t>Remove E0078 as custodian on MD-00065; park under Regional IT or IT Stock (EX-0056).</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -25000,7 +24919,7 @@
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 custodian equals terminated ID E0078 - EX-0056.</t>
+          <t>hr_employee_status shows E0078 as separated. offboarding ticket OFF-00065 closed without a custodian change on MD-00065. EX-0056. Register still assigns MD-00065 to E0078.</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25045,7 +24964,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>MD-00065 cannot remain on shuttered floor Denver - Closed. Set location to Seattle (EX-0057).</t>
+          <t>Replace shuttered site Denver - Closed on MD-00065 with Seattle on the register; cite TR-00065 in the update (EX-0057)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -25065,7 +24984,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00065 is consolidation debt (Denver - Closed, EX-0057).</t>
+          <t>operating footprint for MD-00065 is Seattle, not Denver - Closed. finding EX-0057. equipment_transfer_log TR-00065 points to Seattle. Inventory row MD-00065 (serial MD-LA-050065) still lists site Denver - Closed.</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -25110,7 +25029,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Either approve TR-00065 after the fact or put MD-00065 back.</t>
+          <t>Obtain APR on TR-00065 or reverse move for MD-00065 (EX-0058).</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -25130,7 +25049,7 @@
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>Transfer log TR-00065: move recorded, APR missing.</t>
+          <t>Transfer TR-00065 for MD-00065 has a blank approval_id per ITAM-001 §4 (EX-0058).</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -25175,7 +25094,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>HR Operations Lead: remove E0079 from MD-00066 and park the kit.</t>
+          <t>Remove E0079 as custodian on MD-00066; park under Regional IT or IT Stock (EX-0059).</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -25195,7 +25114,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>E0079 is separated in hr_employee_status; MD-00066 still points to them (EX-0059).</t>
+          <t>hr_employee_status shows E0079 as separated. Register still assigns MD-00066 to E0079. EX-0059. offboarding ticket OFF-00066 closed without a custodian change on MD-00066.</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -25240,7 +25159,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Remove closed-site coding on MD-00066 (Chicago - Closed → Atlanta, EX-0060).</t>
+          <t>Retire the closed-office code on MD-00066 and post Atlanta as the working site; cite TR-00066 in the update (EX-0060)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -25260,7 +25179,7 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>Atlanta is the operating site; MD-00066 still lists Chicago - Closed (EX-0060).</t>
+          <t>operating footprint for MD-00066 is Atlanta, not Chicago - Closed. finding EX-0060. equipment_transfer_log TR-00066 points to Atlanta. Site code Chicago - Closed on MD-00066 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -25301,11 +25220,11 @@
         </is>
       </c>
       <c r="G65" s="7" t="n">
-        <v>764.9299999999999</v>
+        <v>764.93</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup - MD-00067 should not remain with E0080.</t>
+          <t>Remove E0080 as custodian on MD-00067; park under Regional IT or IT Stock (EX-0061).</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -25325,7 +25244,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>Evidence for EX-0061: register kept E0080 on MD-00067 post-separation.</t>
+          <t>hr_employee_status shows E0080 as separated. Register still assigns MD-00067 to E0080. EX-0061. offboarding ticket OFF-00067 closed without a custodian change on MD-00067.</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -25366,11 +25285,11 @@
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>764.9299999999999</v>
+        <v>764.93</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00067 off Denver - Closed; Chicago is the live office per TR-00067 (EX-0062).</t>
+          <t>Replace shuttered site Denver - Closed on MD-00067 with Chicago on the register; cite TR-00067 in the update (EX-0062)</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -25390,7 +25309,7 @@
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>Consolidation left MD-00067 @ Denver - Closed; ops now use Chicago (EX-0062).</t>
+          <t>operating footprint for MD-00067 is Chicago, not Denver - Closed. finding EX-0062. equipment_transfer_log TR-00067 points to Chicago. Site code Denver - Closed on MD-00067 was retired during consolidation but remains on the asset row.</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -25435,7 +25354,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Chase MD-00068: carrier file empty despite 1ZMD00000068.</t>
+          <t>Escalate recovery on MD-00068; 1ZMD00000068 is not a return (EX-0063).</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -25455,7 +25374,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>Label 1ZMD00000068 printed; no SCAN-86 for MD-00068.</t>
+          <t>OFF-00068 return window elapsed. no acceptance, delivery, or receiving scan tied to serial MD-NE-050068. Carrier file 1ZMD00000068 shows Label Created only for MD-00068.</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
@@ -25500,7 +25419,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>OFF-00068 closed people; MD-00068 still shows the leaver.</t>
+          <t>Remove E0081 as custodian on MD-00068; park under Regional IT or IT Stock (EX-0064).</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -25520,7 +25439,7 @@
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>HR status for E0081 and register assignment on MD-00068 disagree (EX-0064).</t>
+          <t>offboarding ticket OFF-00068 closed without a custodian change on MD-00068. EX-0064. hr_employee_status shows E0081 as separated. Register still assigns MD-00068 to E0081.</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -25565,7 +25484,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Close the $6425.0/6480.0 gap on MD-00068 before cert.</t>
+          <t>Align cost on MD-00068: register 6425.0 vs ledger 6480.0 (FA-000068) (EX-0065).</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -25585,7 +25504,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>Register cost $6425.0 vs ledger 6480.0 on FA-000068 for MD-00068.</t>
+          <t>Register cost $6425.0 on MD-00068 does not match ledger $6480.0 on FA-000068 (EX-0065).</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -25630,7 +25549,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Outstanding kit MD-00069 / 1ZMD00000069 - escalate beyond label print.</t>
+          <t>Escalate recovery on MD-00069; 1ZMD00000069 is not a return (EX-0066).</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -25650,7 +25569,7 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>Overdue evidence is absence of inbound events on 1ZMD00000069.</t>
+          <t>no acceptance, delivery, or receiving scan tied to serial MD-LA-050069. OFF-00069 return window elapsed. Carrier file 1ZMD00000069 shows Label Created only for MD-00069.</t>
         </is>
       </c>
       <c r="M70" s="12" t="inlineStr">
@@ -25695,7 +25614,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Stock or Regional IT must replace E0082 on MD-00069.</t>
+          <t>Remove E0082 as custodian on MD-00069; park under Regional IT or IT Stock (EX-0067).</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -25715,7 +25634,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>HR status for E0082 and register assignment on MD-00069 disagree (EX-0067).</t>
+          <t>Register still assigns MD-00069 to E0082. EX-0067. offboarding ticket OFF-00069 closed without a custodian change on MD-00069. hr_employee_status shows E0082 as separated.</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -25760,7 +25679,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Do not mark Available; MD-00070 never docked after 1ZMD00000070.</t>
+          <t>Escalate recovery on MD-00070; 1ZMD00000070 is not a return (EX-0068).</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -25780,7 +25699,7 @@
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>Carrier never accepted 1ZMD00000070; MD-00070 still outstanding.</t>
+          <t>OFF-00070 return window elapsed. no acceptance, delivery, or receiving scan tied to serial MD-MO-050070. Carrier file 1ZMD00000070 shows Label Created only for MD-00070.</t>
         </is>
       </c>
       <c r="M72" s="12" t="inlineStr">
@@ -25825,7 +25744,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Do not leave MD-00070 assigned to E0083 on the extract.</t>
+          <t>Remove E0083 as custodian on MD-00070; park under Regional IT or IT Stock (EX-0069).</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -25845,7 +25764,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>MD-00070 should have moved off E0083 when HR flipped status (EX-0069).</t>
+          <t>hr_employee_status shows E0083 as separated. EX-0069. offboarding ticket OFF-00070 closed without a custodian change on MD-00070. Register still assigns MD-00070 to E0083.</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -25890,7 +25809,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Recovery required on MD-00071; prepaid label 1ZMD00000071 is paperwork only.</t>
+          <t>Escalate recovery on MD-00071; 1ZMD00000071 is not a return (EX-0070).</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -25910,7 +25829,7 @@
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>Carrier never accepted 1ZMD00000071; MD-00071 still outstanding.</t>
+          <t>OFF-00071 return window elapsed. no acceptance, delivery, or receiving scan tied to serial MD-MO-050071. Carrier file 1ZMD00000071 shows Label Created only for MD-00071.</t>
         </is>
       </c>
       <c r="M74" s="12" t="inlineStr">
@@ -25955,7 +25874,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>HR already termed E0084. Update MD-00071 assignment.</t>
+          <t>Remove E0084 as custodian on MD-00071; park under Regional IT or IT Stock (EX-0071).</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -25975,7 +25894,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>HR lists E0084 as separated; register still assigns MD-00071 (EX-0071).</t>
+          <t>hr_employee_status shows E0084 as separated. EX-0071. offboarding ticket OFF-00071 closed without a custodian change on MD-00071. Register still assigns MD-00071 to E0084.</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -26020,7 +25939,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Label-only status on 1ZMD00000072 blocks cert for MD-00072.</t>
+          <t>Escalate recovery on MD-00072; 1ZMD00000072 is not a return (EX-0072).</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -26040,7 +25959,7 @@
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>OFF-00072: return window closed with empty inbound for MD-00072.</t>
+          <t>Carrier file 1ZMD00000072 shows Label Created only for MD-00072. OFF-00072 return window elapsed. no acceptance, delivery, or receiving scan tied to serial MD-NE-050072.</t>
         </is>
       </c>
       <c r="M76" s="12" t="inlineStr">
@@ -26085,7 +26004,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Recover or write-off later; first take E0085 off MD-00072.</t>
+          <t>Remove E0085 as custodian on MD-00072; park under Regional IT or IT Stock (EX-0073).</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -26105,7 +26024,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>Custodian mismatch MD-00072↔E0085 documented under EX-0073.</t>
+          <t>EX-0073. Register still assigns MD-00072 to E0085. hr_employee_status shows E0085 as separated. offboarding ticket OFF-00072 closed without a custodian change on MD-00072.</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -26150,7 +26069,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Keep pressure on the former user until dock scan - 1ZMD00000073.</t>
+          <t>Escalate recovery on MD-00073; 1ZMD00000073 is not a return (EX-0074).</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -26170,7 +26089,7 @@
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>Label 1ZMD00000073 printed; no SCAN-86 for MD-00073.</t>
+          <t>no acceptance, delivery, or receiving scan tied to serial MD-LA-050073. Carrier file 1ZMD00000073 shows Label Created only for MD-00073. OFF-00073 return window elapsed.</t>
         </is>
       </c>
       <c r="M78" s="12" t="inlineStr">
@@ -26215,7 +26134,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>HR Operations Lead: remove E0086 from MD-00073 and park the kit.</t>
+          <t>Remove E0086 as custodian on MD-00073; park under Regional IT or IT Stock (EX-0075).</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -26235,7 +26154,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>People file cleared E0086; ITAM row for MD-00073 did not (EX-0075).</t>
+          <t>Register still assigns MD-00073 to E0086. hr_employee_status shows E0086 as separated. offboarding ticket OFF-00073 closed without a custodian change on MD-00073. EX-0075.</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -26280,7 +26199,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Hold MD-00074. Shipment serial MISMATCH-0074 ≠ register MD-MO-050074 on 1ZMD00000074.</t>
+          <t>Resolve serial conflict on 1ZMD00000074 for MD-00074 (MISMATCH-0074 vs MD-MO-050074) (EX-0076).</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -26300,7 +26219,7 @@
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
-          <t>Shipment serial MISMATCH-0074 on 1ZMD00000074 vs register MD-MO-050074. Not cleared.</t>
+          <t>Inbound serial MISMATCH-0074 on 1ZMD00000074 disagrees with register MD-MO-050074. MD-00074 remains In Transit - Exception until serials align.</t>
         </is>
       </c>
       <c r="M80" s="12" t="inlineStr">
@@ -26345,7 +26264,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>People side closed via OFF-00074; asset row still lists E0087. Fix custodian.</t>
+          <t>Remove E0087 as custodian on MD-00074; park under Regional IT or IT Stock (EX-0077).</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -26365,7 +26284,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 custodian equals terminated ID E0087 - EX-0077.</t>
+          <t>Register still assigns MD-00074 to E0087. offboarding ticket OFF-00074 closed without a custodian change on MD-00074. EX-0077. hr_employee_status shows E0087 as separated.</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -26410,7 +26329,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Escalate recovery on MD-00074; 1ZMD00000074 is Label Created only.</t>
+          <t>Escalate recovery on MD-00074; 1ZMD00000074 is not a return (EX-0078).</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -26430,7 +26349,7 @@
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork exists (1ZMD00000074); physical return does not.</t>
+          <t>Carrier file 1ZMD00000074 shows Label Created only for MD-00074. no acceptance, delivery, or receiving scan tied to serial MD-MO-050074. OFF-00074 return window elapsed.</t>
         </is>
       </c>
       <c r="M82" s="12" t="inlineStr">
@@ -26475,7 +26394,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>MD-00075 past due 2026-07-15; label is not receipt (OFF-00075).</t>
+          <t>Escalate recovery on MD-00075; 1ZMD00000075 is not a return (EX-0079).</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -26495,7 +26414,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>Ship file for MD-00075: label only. OFF-00075 overdue 2026-07-15.</t>
+          <t>OFF-00075 return window elapsed. Carrier file 1ZMD00000075 shows Label Created only for MD-00075. no acceptance, delivery, or receiving scan tied to serial MD-MO-050075.</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
@@ -26540,7 +26459,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>Stock or Regional IT must replace E0088 on MD-00075.</t>
+          <t>Remove E0088 as custodian on MD-00075; park under Regional IT or IT Stock (EX-0080).</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -26560,7 +26479,7 @@
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>Custodian mismatch MD-00075↔E0088 documented under EX-0080.</t>
+          <t>Register still assigns MD-00075 to E0088. offboarding ticket OFF-00075 closed without a custodian change on MD-00075. EX-0080. hr_employee_status shows E0088 as separated.</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -26605,7 +26524,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Carrier exception 1ZMD00000076; MD-00076 stays held.</t>
+          <t>Resolve serial conflict on 1ZMD00000076 for MD-00076 (MISMATCH-0076 vs MD-NE-050076) (EX-0081).</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -26625,7 +26544,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>Shipment serial MISMATCH-0076 on 1ZMD00000076 vs register MD-NE-050076. Not cleared.</t>
+          <t>MD-00076 remains In Transit - Exception until serials align. Inbound serial MISMATCH-0076 on 1ZMD00000076 disagrees with register MD-NE-050076.</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
@@ -26670,7 +26589,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup - MD-00076 should not remain with E0089.</t>
+          <t>Remove E0089 as custodian on MD-00076; park under Regional IT or IT Stock (EX-0082).</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -26690,7 +26609,7 @@
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
-          <t>Evidence for EX-0082: register kept E0089 on MD-00076 post-separation.</t>
+          <t>offboarding ticket OFF-00076 closed without a custodian change on MD-00076. hr_employee_status shows E0089 as separated. Register still assigns MD-00076 to E0089. EX-0082.</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -26735,7 +26654,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: treat MD-00076 as not returned until inbound scan.</t>
+          <t>Escalate recovery on MD-00076; 1ZMD00000076 is not a return (EX-0083).</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -26755,7 +26674,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000076 remains Label Created. No acceptance, delivery, or dock scan.</t>
+          <t>no acceptance, delivery, or receiving scan tied to serial MD-NE-050076. Carrier file 1ZMD00000076 shows Label Created only for MD-00076. OFF-00076 return window elapsed.</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
@@ -26800,7 +26719,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Outstanding kit MD-00077 / 1ZMD00000077 - escalate beyond label print.</t>
+          <t>Escalate recovery on MD-00077; 1ZMD00000077 is not a return (EX-0084).</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -26820,7 +26739,7 @@
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
-          <t>Label 1ZMD00000077 printed; no SCAN-86 for MD-00077.</t>
+          <t>Carrier file 1ZMD00000077 shows Label Created only for MD-00077. OFF-00077 return window elapsed. no acceptance, delivery, or receiving scan tied to serial MD-LA-050077.</t>
         </is>
       </c>
       <c r="M88" s="12" t="inlineStr">
@@ -26865,7 +26784,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>HR Operations Lead: remove E0090 from MD-00077 and park the kit.</t>
+          <t>Remove E0090 as custodian on MD-00077; park under Regional IT or IT Stock (EX-0085).</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -26885,7 +26804,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>MD-00077 custodian equals terminated ID E0090 - EX-0085.</t>
+          <t>offboarding ticket OFF-00077 closed without a custodian change on MD-00077. EX-0085. hr_employee_status shows E0090 as separated. Register still assigns MD-00077 to E0090.</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -26930,7 +26849,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Escalate recovery on MD-00078; 1ZMD00000078 is Label Created only.</t>
+          <t>Escalate recovery on MD-00078; 1ZMD00000078 is not a return (EX-0086).</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -26950,7 +26869,7 @@
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000078 remains Label Created. No acceptance, delivery, or dock scan.</t>
+          <t>OFF-00078 return window elapsed. Carrier file 1ZMD00000078 shows Label Created only for MD-00078. no acceptance, delivery, or receiving scan tied to serial MD-MO-050078.</t>
         </is>
       </c>
       <c r="M90" s="12" t="inlineStr">
@@ -26995,7 +26914,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>OFF-00078 closed people; MD-00078 still shows the leaver.</t>
+          <t>Remove E0091 as custodian on MD-00078; park under Regional IT or IT Stock (EX-0087).</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -27015,7 +26934,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>Finding EX-0087 on MD-00078: former employee E0091 still listed as owner.</t>
+          <t>hr_employee_status shows E0091 as separated. EX-0087. Register still assigns MD-00078 to E0091. offboarding ticket OFF-00078 closed without a custodian change on MD-00078.</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -27060,7 +26979,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Do not close MD-00079 as returned. 2026-07-15 passed with no SCAN-86.</t>
+          <t>Escalate recovery on MD-00079; 1ZMD00000079 is not a return (EX-0088).</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -27080,7 +26999,7 @@
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000079 remains Label Created. No acceptance, delivery, or dock scan.</t>
+          <t>no acceptance, delivery, or receiving scan tied to serial MD-MO-050079. Carrier file 1ZMD00000079 shows Label Created only for MD-00079. OFF-00079 return window elapsed.</t>
         </is>
       </c>
       <c r="M92" s="12" t="inlineStr">
@@ -27125,7 +27044,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>MD-00079 still names a leaver (E0092). Close the assignment.</t>
+          <t>Remove E0092 as custodian on MD-00079; park under Regional IT or IT Stock (EX-0089).</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -27145,7 +27064,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>Term record for E0092 exists; MD-00079 assignment record did not update (EX-0089).</t>
+          <t>Register still assigns MD-00079 to E0092. offboarding ticket OFF-00079 closed without a custodian change on MD-00079. hr_employee_status shows E0092 as separated. EX-0089.</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
@@ -27190,7 +27109,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup - MD-00080 should not remain with E0093.</t>
+          <t>Remove E0093 as custodian on MD-00080; park under Regional IT or IT Stock (EX-0090).</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -27210,7 +27129,7 @@
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>EX-0090 cites MD-00080 assigned to terminated E0093 despite OFF-00080.</t>
+          <t>hr_employee_status shows E0093 as separated. EX-0090. offboarding ticket OFF-00080 closed without a custodian change on MD-00080. Register still assigns MD-00080 to E0093.</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -27255,7 +27174,7 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>MD-00081 needs a stock/regional holder, not E0094.</t>
+          <t>Remove E0094 as custodian on MD-00081; park under Regional IT or IT Stock (EX-0091).</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
@@ -27275,7 +27194,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>People file cleared E0094; ITAM row for MD-00081 did not (EX-0091).</t>
+          <t>EX-0091. Register still assigns MD-00081 to E0094. hr_employee_status shows E0094 as separated. offboarding ticket OFF-00081 closed without a custodian change on MD-00081.</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
@@ -27320,7 +27239,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>MD-00082 stays exception. Dock photo is a HOLD lead, not a receipt. MISMATCH-0082 vs MD-MO-050082 on 1ZMD00000082.</t>
+          <t>Hold MD-00082; resolve MISMATCH-0082 vs MD-MO-050082 before clearing custody.</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
@@ -27340,7 +27259,7 @@
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
-          <t>MISMATCH-0082 vs MD-MO-050082. Used the photo as breadcrumb only.</t>
+          <t>Dock photo receiving_exception_scan_1ZMD00000082.png is a HOLD lead for MD-00082; MISMATCH-0082 on inbound 1ZMD00000082 does not match register serial MD-MO-050082.</t>
         </is>
       </c>
       <c r="M96" s="12" t="inlineStr">
@@ -27385,7 +27304,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>MD-00082 needs a stock/regional holder, not E0095.</t>
+          <t>Remove E0095 as custodian on MD-00082; park under Regional IT or IT Stock (EX-0093).</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -27405,7 +27324,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0095 to register row MD-00082 - assignment stale (EX-0093).</t>
+          <t>EX-0093. Register still assigns MD-00082 to E0095. hr_employee_status shows E0095 as separated. offboarding ticket OFF-00082 closed without a custodian change on MD-00082.</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -27450,7 +27369,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Move MD-00083 to Regional IT holding after E0071 exit.</t>
+          <t>Remove E0071 as custodian on MD-00083; park under Regional IT or IT Stock (EX-0094).</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -27470,7 +27389,7 @@
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>Offboarding closed for E0071; asset row did not follow for MD-00083 (EX-0094).</t>
+          <t>offboarding ticket OFF-00083 closed without a custodian change on MD-00083. hr_employee_status shows E0071 as separated. Register still assigns MD-00083 to E0071. EX-0094.</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -27515,7 +27434,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Work carrier/receiving on 1ZMD00000084: MISMATCH-0084 vs MD-NE-050084.</t>
+          <t>Resolve serial conflict on 1ZMD00000084 for MD-00084 (MISMATCH-0084 vs MD-NE-050084) (EX-0095).</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -27535,7 +27454,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>Inbound 1ZMD00000084 does not match register serial MD-NE-050084.</t>
+          <t>Inbound serial MISMATCH-0084 on 1ZMD00000084 disagrees with register MD-NE-050084. MD-00084 remains In Transit - Exception until serials align.</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
@@ -27580,7 +27499,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>MD-00084 still names a leaver (E0072). Close the assignment.</t>
+          <t>Remove E0072 as custodian on MD-00084; park under Regional IT or IT Stock (EX-0096).</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -27600,7 +27519,7 @@
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
-          <t>EX-0096 cites MD-00084 assigned to terminated E0072 despite OFF-00084.</t>
+          <t>offboarding ticket OFF-00084 closed without a custodian change on MD-00084. hr_employee_status shows E0072 as separated. Register still assigns MD-00084 to E0072. EX-0096.</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -27645,7 +27564,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>People side closed via OFF-00085; asset row still lists E0073. Fix custodian.</t>
+          <t>Remove E0073 as custodian on MD-00085; park under Regional IT or IT Stock (EX-0097).</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
@@ -27665,7 +27584,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>People extract vs register: MD-00085 retained leaver E0073. OFF-00085.</t>
+          <t>Register still assigns MD-00085 to E0073. EX-0097. offboarding ticket OFF-00085 closed without a custodian change on MD-00085. hr_employee_status shows E0073 as separated.</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -27702,7 +27621,7 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Ledger:FA-000085; PO:PO-2024-0015; RegisterCost:1895.0; LedgerCost:2090.0</t>
+          <t>Ledger:FA-000085; PO:PO-2024-0015; RegisterCost:1895.0; LedgerCost:2090.0; OverDepreciation:20.0</t>
         </is>
       </c>
       <c r="G102" s="7" t="n">
@@ -27710,7 +27629,7 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Align cost on MD-00085: register 1895.0 vs ledger 2090.0 (FA-000085).</t>
+          <t>Finance Controller: align register $1895.0 vs ledger $2090.0 on FA-000085 for MD-00085 and correct NBV to $20 on FA-000085.</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
@@ -27730,7 +27649,7 @@
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
-          <t>Basis mismatch documented for MD-00085 (1895.0 vs 2090.0).</t>
+          <t>Pulled PO-2024-0015 and FA-000085 for MD-00085: register cost $1895.0 vs ledger $2090.0. FA-000085 accumulated depreciation $2070 exceeds what $2090 acquisition less $0 NBV allows; correct NBV is $20.</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -27775,7 +27694,7 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>HR shows E0074 gone - remove as custodian on MD-00086 (OFF-00086).</t>
+          <t>Remove E0074 as custodian on MD-00086; park under Regional IT or IT Stock (EX-0099).</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -27795,7 +27714,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0074 to register row MD-00086 - assignment stale (EX-0099).</t>
+          <t>hr_employee_status shows E0074 as separated. EX-0099. Register still assigns MD-00086 to E0074. offboarding ticket OFF-00086 closed without a custodian change on MD-00086.</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -27840,7 +27759,7 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Assignment on MD-00087 survived HR term for E0075. Correct it.</t>
+          <t>Remove E0075 as custodian on MD-00087; park under Regional IT or IT Stock (EX-0100).</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
@@ -27860,7 +27779,7 @@
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
-          <t>Register owner on MD-00087 is stale relative to HR for E0075 (EX-0100).</t>
+          <t>offboarding ticket OFF-00087 closed without a custodian change on MD-00087. EX-0100. hr_employee_status shows E0075 as separated. Register still assigns MD-00087 to E0075.</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -27905,7 +27824,7 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>People side closed via OFF-00088; asset row still lists E0076. Fix custodian.</t>
+          <t>Remove E0076 as custodian on MD-00088; park under Regional IT or IT Stock (EX-0101).</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
@@ -27925,7 +27844,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>Compared HR row E0076 to register row MD-00088 - assignment stale (EX-0101).</t>
+          <t>offboarding ticket OFF-00088 closed without a custodian change on MD-00088. EX-0101. hr_employee_status shows E0076 as separated. Register still assigns MD-00088 to E0076.</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -27970,7 +27889,7 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Duplicate MD-NE-050088 - MD-00088 and MD-00088,MD-00092. Neither is clean until retag.</t>
+          <t>Bench-validate and retag duplicate serial MD-NE-050088 involving MD-00088 (EX-0102).</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -27990,7 +27909,7 @@
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
-          <t>Serial MD-NE-050088 appears on more than one tag (MD-00088,MD-00092).</t>
+          <t>Serial MD-NE-050088 appears on MD-00088 and MD-00088,MD-00092; bench validation required (EX-0102).</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
@@ -28035,7 +27954,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>No scan/cert/count for MD-00089. Missing, not In Use (EX-0103).</t>
+          <t>Run loss investigation on MD-00089; keep Missing until located or approved write-off (EX-0103).</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -28055,7 +27974,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>Could not place MD-00089 from available transactions (EX-0103).</t>
+          <t>EX-0103. last register site was Denver - Closed. No dock scan, disposal certificate, or count places MD-00089.</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
@@ -28100,7 +28019,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Custodian field on MD-00089 still equals E0077; that is the fix.</t>
+          <t>Remove E0077 as custodian on MD-00089; park under Regional IT or IT Stock (EX-0104).</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -28120,7 +28039,7 @@
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
-          <t>Register owner on MD-00089 is stale relative to HR for E0077 (EX-0104).</t>
+          <t>hr_employee_status shows E0077 as separated. EX-0104. Register still assigns MD-00089 to E0077. offboarding ticket OFF-00089 closed without a custodian change on MD-00089.</t>
         </is>
       </c>
       <c r="M108" s="12" t="inlineStr">
@@ -28165,7 +28084,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Security review + locate. MD-00090 remains Missing (EX-0105).</t>
+          <t>Run loss investigation on MD-00090; keep Missing until located or approved write-off (EX-0105).</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -28185,7 +28104,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>Files do not locate MD-00090; Missing remains appropriate (EX-0105).</t>
+          <t>last register site was Chicago - Closed. No dock scan, disposal certificate, or count places MD-00090. EX-0105.</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
@@ -28230,7 +28149,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Recover or write-off later; first take E0078 off MD-00090.</t>
+          <t>Remove E0078 as custodian on MD-00090; park under Regional IT or IT Stock (EX-0106).</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -28250,7 +28169,7 @@
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
-          <t>HR lists E0078 as separated; register still assigns MD-00090 (EX-0106).</t>
+          <t>offboarding ticket OFF-00090 closed without a custodian change on MD-00090. EX-0106. Register still assigns MD-00090 to E0078. hr_employee_status shows E0078 as separated.</t>
         </is>
       </c>
       <c r="M110" s="12" t="inlineStr">
@@ -28295,7 +28214,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Write-off only with approval; until then MD-00091 is Missing (EX-0107).</t>
+          <t>Run loss investigation on MD-00091; keep Missing until located or approved write-off (EX-0107).</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -28315,7 +28234,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>MD-00091 not found in inbound or stock after Denver - Closed (EX-0107).</t>
+          <t>EX-0107. No dock scan, disposal certificate, or count places MD-00091. last register site was Denver - Closed.</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
@@ -28360,7 +28279,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Unassign E0079 from MD-00091; hold under Regional IT / IT Stock.</t>
+          <t>Remove E0079 as custodian on MD-00091; park under Regional IT or IT Stock (EX-0108).</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -28380,7 +28299,7 @@
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
-          <t>Leaver E0079 remains on MD-00091 in the inventory extract (EX-0108).</t>
+          <t>Register still assigns MD-00091 to E0079. hr_employee_status shows E0079 as separated. offboarding ticket OFF-00091 closed without a custodian change on MD-00091. EX-0108.</t>
         </is>
       </c>
       <c r="M112" s="12" t="inlineStr">
@@ -28425,7 +28344,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>No scan/cert/count for MD-00092. Missing, not In Use (EX-0109).</t>
+          <t>Run loss investigation on MD-00092; keep Missing until located or approved write-off (EX-0109).</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -28445,7 +28364,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>MD-00092 not found in inbound or stock after Chicago - Closed (EX-0109).</t>
+          <t>last register site was Chicago - Closed. No dock scan, disposal certificate, or count places MD-00092. EX-0109.</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
@@ -28490,7 +28409,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Stock or Regional IT must replace E0080 on MD-00092.</t>
+          <t>Remove E0080 as custodian on MD-00092; park under Regional IT or IT Stock (EX-0110).</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -28510,7 +28429,7 @@
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
-          <t>Custodian mismatch MD-00092↔E0080 documented under EX-0110.</t>
+          <t>Register still assigns MD-00092 to E0080. hr_employee_status shows E0080 as separated. offboarding ticket OFF-00092 closed without a custodian change on MD-00092. EX-0110.</t>
         </is>
       </c>
       <c r="M114" s="12" t="inlineStr">
@@ -28555,7 +28474,7 @@
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Two assets share MD-NE-050088 (MD-00088,MD-00092). Bench-validate and issue a new serial.</t>
+          <t>Bench-validate and retag duplicate serial MD-NE-050088 involving MD-00092 (EX-0111).</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
@@ -28575,7 +28494,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>Two assets share MD-NE-050088; MD-00092 is one of them.</t>
+          <t>Serial MD-NE-050088 appears on MD-00092 and MD-00088,MD-00092; bench validation required (EX-0111).</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
@@ -28620,7 +28539,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>Security review + locate. MD-00093 remains Missing (EX-0112).</t>
+          <t>Run loss investigation on MD-00093; keep Missing until located or approved write-off (EX-0112).</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
@@ -28640,7 +28559,7 @@
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
-          <t>MD-00093 not found in inbound or stock after Denver - Closed (EX-0112).</t>
+          <t>last register site was Denver - Closed. EX-0112. No dock scan, disposal certificate, or count places MD-00093.</t>
         </is>
       </c>
       <c r="M116" s="12" t="inlineStr">
@@ -28685,7 +28604,7 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Stock or Regional IT must replace E0081 on MD-00093.</t>
+          <t>Remove E0081 as custodian on MD-00093; park under Regional IT or IT Stock (EX-0113).</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
@@ -28705,7 +28624,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>HR lists E0081 as separated; register still assigns MD-00093 (EX-0113).</t>
+          <t>Register still assigns MD-00093 to E0081. offboarding ticket OFF-00093 closed without a custodian change on MD-00093. EX-0113. hr_employee_status shows E0081 as separated.</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
@@ -28750,7 +28669,7 @@
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Write-off only with approval; until then MD-00094 is Missing (EX-0114).</t>
+          <t>Run loss investigation on MD-00094; keep Missing until located or approved write-off (EX-0114).</t>
         </is>
       </c>
       <c r="I118" s="7" t="inlineStr">
@@ -28770,7 +28689,7 @@
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
-          <t>Nothing physical confirms MD-00094 at Unknown (EX-0114).</t>
+          <t>EX-0114. No dock scan, disposal certificate, or count places MD-00094. last register site was Chicago - Closed.</t>
         </is>
       </c>
       <c r="M118" s="12" t="inlineStr">
@@ -28815,7 +28734,7 @@
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Term cleanup - MD-00094 should not remain with E0082.</t>
+          <t>Remove E0082 as custodian on MD-00094; park under Regional IT or IT Stock (EX-0115).</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
@@ -28835,7 +28754,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>MD-00094 custodian equals terminated ID E0082 - EX-0115.</t>
+          <t>Register still assigns MD-00094 to E0082. offboarding ticket OFF-00094 closed without a custodian change on MD-00094. EX-0115. hr_employee_status shows E0082 as separated.</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
@@ -28880,7 +28799,7 @@
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>MD-00095 dropped after Denver - Closed. Investigate; do not tidy status (EX-0116).</t>
+          <t>Run loss investigation on MD-00095; keep Missing until located or approved write-off (EX-0116).</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr">
@@ -28900,7 +28819,7 @@
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
-          <t>Files do not locate MD-00095; Missing remains appropriate (EX-0116).</t>
+          <t>last register site was Denver - Closed. No dock scan, disposal certificate, or count places MD-00095. EX-0116.</t>
         </is>
       </c>
       <c r="M120" s="12" t="inlineStr">
@@ -28945,7 +28864,7 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Close people assignment on MD-00095; ticket OFF-00095.</t>
+          <t>Remove E0083 as custodian on MD-00095; park under Regional IT or IT Stock (EX-0117).</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr">
@@ -28965,7 +28884,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>Custodian mismatch MD-00095↔E0083 documented under EX-0117.</t>
+          <t>offboarding ticket OFF-00095 closed without a custodian change on MD-00095. hr_employee_status shows E0083 as separated. Register still assigns MD-00095 to E0083. EX-0117.</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
@@ -29010,7 +28929,7 @@
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>Start loss process for MD-00096; not in Unknown and not in receiving (EX-0118).</t>
+          <t>Run loss investigation on MD-00096; keep Missing until located or approved write-off (EX-0118).</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr">
@@ -29030,7 +28949,7 @@
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
-          <t>Search trail cold for MD-00096 (OFF-00096). Last register site Chicago - Closed (EX-0118).</t>
+          <t>EX-0118. No dock scan, disposal certificate, or count places MD-00096. last register site was Chicago - Closed.</t>
         </is>
       </c>
       <c r="M122" s="12" t="inlineStr">
@@ -29075,7 +28994,7 @@
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>HR Operations Lead: remove E0084 from MD-00096 and park the kit.</t>
+          <t>Remove E0084 as custodian on MD-00096; park under Regional IT or IT Stock (EX-0119).</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr">
@@ -29095,7 +29014,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>Offboarding closed for E0084; asset row did not follow for MD-00096 (EX-0119).</t>
+          <t>Register still assigns MD-00096 to E0084. EX-0119. offboarding ticket OFF-00096 closed without a custodian change on MD-00096. hr_employee_status shows E0084 as separated.</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
@@ -29140,7 +29059,7 @@
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Loss investigation on MD-00097; keep Missing until found or write-off (EX-0120).</t>
+          <t>Run loss investigation on MD-00097; keep Missing until located or approved write-off (EX-0120).</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
@@ -29160,7 +29079,7 @@
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
-          <t>Search trail cold for MD-00097 (OFF-00097). Last register site Denver - Closed (EX-0120).</t>
+          <t>EX-0120. No dock scan, disposal certificate, or count places MD-00097. last register site was Denver - Closed.</t>
         </is>
       </c>
       <c r="M124" s="12" t="inlineStr">
@@ -29205,7 +29124,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Do not leave MD-00097 assigned to E0085 on the extract.</t>
+          <t>Remove E0085 as custodian on MD-00097; park under Regional IT or IT Stock (EX-0121).</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
@@ -29225,7 +29144,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>Offboarding closed for E0085; asset row did not follow for MD-00097 (EX-0121).</t>
+          <t>Register still assigns MD-00097 to E0085. EX-0121. offboarding ticket OFF-00097 closed without a custodian change on MD-00097. hr_employee_status shows E0085 as separated.</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
@@ -29270,7 +29189,7 @@
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Write-off only with approval; until then MD-00098 is Missing (EX-0122).</t>
+          <t>Run loss investigation on MD-00098; keep Missing until located or approved write-off (EX-0122).</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
@@ -29290,7 +29209,7 @@
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
-          <t>Could not place MD-00098 from available transactions (EX-0122).</t>
+          <t>last register site was Chicago - Closed. EX-0122. No dock scan, disposal certificate, or count places MD-00098.</t>
         </is>
       </c>
       <c r="M126" s="12" t="inlineStr">
@@ -29335,7 +29254,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Move MD-00098 to Regional IT holding after E0086 exit.</t>
+          <t>Remove E0086 as custodian on MD-00098; park under Regional IT or IT Stock (EX-0123).</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
@@ -29355,7 +29274,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>Register owner on MD-00098 is stale relative to HR for E0086 (EX-0123).</t>
+          <t>hr_employee_status shows E0086 as separated. EX-0123. Register still assigns MD-00098 to E0086. offboarding ticket OFF-00098 closed without a custodian change on MD-00098.</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
@@ -29400,7 +29319,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>Cannot locate MD-00099 (OFF-00099). Missing until count or approved write-off (EX-0124).</t>
+          <t>Run loss investigation on MD-00099; keep Missing until located or approved write-off (EX-0124).</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr">
@@ -29420,7 +29339,7 @@
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
-          <t>Search trail cold for MD-00099 (OFF-00099). Last register site Denver - Closed (EX-0124).</t>
+          <t>EX-0124. No dock scan, disposal certificate, or count places MD-00099. last register site was Denver - Closed.</t>
         </is>
       </c>
       <c r="M128" s="12" t="inlineStr">
@@ -29465,7 +29384,7 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>Assignment on MD-00099 survived HR term for E0087. Correct it.</t>
+          <t>Remove E0087 as custodian on MD-00099; park under Regional IT or IT Stock (EX-0125).</t>
         </is>
       </c>
       <c r="I129" s="7" t="inlineStr">
@@ -29485,7 +29404,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>Offboarding closed for E0087; asset row did not follow for MD-00099 (EX-0125).</t>
+          <t>Register still assigns MD-00099 to E0087. offboarding ticket OFF-00099 closed without a custodian change on MD-00099. hr_employee_status shows E0087 as separated. EX-0125.</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
@@ -29530,7 +29449,7 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>IT Operations Manager: keep MD-00100 Missing on the register (EX-0126).</t>
+          <t>Run loss investigation on MD-00100; keep Missing until located or approved write-off (EX-0126).</t>
         </is>
       </c>
       <c r="I130" s="7" t="inlineStr">
@@ -29550,7 +29469,7 @@
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
-          <t>No receiving scan, disposal cert, or count places MD-00100. Last site Chicago - Closed (EX-0126).</t>
+          <t>EX-0126. last register site was Chicago - Closed. No dock scan, disposal certificate, or count places MD-00100.</t>
         </is>
       </c>
       <c r="M130" s="12" t="inlineStr">
@@ -29595,7 +29514,7 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>MD-00100 needs a stock/regional holder, not E0088.</t>
+          <t>Remove E0088 as custodian on MD-00100; park under Regional IT or IT Stock (EX-0127).</t>
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr">
@@ -29615,7 +29534,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>HR status for E0088 and register assignment on MD-00100 disagree (EX-0127).</t>
+          <t>offboarding ticket OFF-00100 closed without a custodian change on MD-00100. hr_employee_status shows E0088 as separated. Register still assigns MD-00100 to E0088. EX-0127.</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
@@ -29660,7 +29579,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>Retirement parked for MD-00101 pending DC evidence (EX-0128).</t>
+          <t>Obtain disposal certificate for MD-00101 or reverse retirement (EX-0128).</t>
         </is>
       </c>
       <c r="I132" s="7" t="inlineStr">
@@ -29680,7 +29599,7 @@
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
-          <t>TR-00101 to recycler without DC for MD-00101 (EX-0128).</t>
+          <t>EX-0128. Retirement path for MD-00101 lacks a verified disposal certificate. transfer TR-00101 to recycler without DC. serial MD-LA-050101 not matched in asset_disposal_records.</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr">
@@ -29725,7 +29644,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 cannot remain on shuttered floor Denver - Closed. Set location to Seattle (EX-0129).</t>
+          <t>Retire the closed-office code on MD-00101 and post Seattle as the working site; cite TR-00101 in the update (EX-0129)</t>
         </is>
       </c>
       <c r="I133" s="7" t="inlineStr">
@@ -29745,7 +29664,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>Register still codes MD-00101 to Denver - Closed; TR-00101 points to Seattle (EX-0129).</t>
+          <t>equipment_transfer_log TR-00101 points to Seattle. Inventory row MD-00101 (serial MD-LA-050101) still lists site Denver - Closed. finding EX-0129. operating footprint for MD-00101 is Seattle, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M133" s="7" t="inlineStr">
@@ -29790,7 +29709,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Do not call MD-00102 disposed - certificate missing (EX-0130).</t>
+          <t>Obtain disposal certificate for MD-00102 or reverse retirement (EX-0130).</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr">
@@ -29810,7 +29729,7 @@
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
-          <t>No DC row ties to MD-MO-050102 for MD-00102 (EX-0130).</t>
+          <t>EX-0130. Retirement path for MD-00102 lacks a verified disposal certificate. transfer TR-00102 to recycler without DC. serial MD-MO-050102 not matched in asset_disposal_records.</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -29855,7 +29774,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 off vs FA-000102 (700.0 vs 820.0). Confirm which figure is correct.</t>
+          <t>Align cost on MD-00102: register 700.0 vs ledger 820.0 (FA-000102) (EX-0131).</t>
         </is>
       </c>
       <c r="I135" s="7" t="inlineStr">
@@ -29875,7 +29794,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>Cost spread on MD-00102: ITAM $700.0, FAR 820.0 (FA-000102).</t>
+          <t>Register cost $700.0 on MD-00102 does not match ledger $820.0 on FA-000102 (EX-0131).</t>
         </is>
       </c>
       <c r="M135" s="7" t="inlineStr">
@@ -29920,7 +29839,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Update register location for MD-00102 before the next cert packet (EX-0132).</t>
+          <t>Correct the stale location on MD-00102 (Chicago - Closed → Atlanta); cite TR-00102 in the update (EX-0132)</t>
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr">
@@ -29940,7 +29859,7 @@
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 remains on unused floor Chicago - Closed in the inventory file (EX-0132).</t>
+          <t>Site code Chicago - Closed on MD-00102 was retired during consolidation but remains on the asset row. operating footprint for MD-00102 is Atlanta, not Chicago - Closed. equipment_transfer_log TR-00102 points to Atlanta. finding EX-0132.</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -29985,7 +29904,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>Obtain cert or restock MD-00103. Ticket RET-00103 (EX-0133).</t>
+          <t>Obtain disposal certificate for MD-00103 or reverse retirement (EX-0133).</t>
         </is>
       </c>
       <c r="I137" s="7" t="inlineStr">
@@ -30005,7 +29924,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>Retirement/disposal path for MD-00103 has no matching certificate (EX-0133).</t>
+          <t>Retirement path for MD-00103 lacks a verified disposal certificate. serial MD-MO-050103 not matched in asset_disposal_records. transfer TR-00103 to recycler without DC. EX-0133.</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
@@ -30050,7 +29969,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>HR-aligned site for MD-00103 is Chicago; register still says Denver - Closed (EX-0134).</t>
+          <t>Retire the closed-office code on MD-00103 and post Chicago as the working site; cite TR-00103 in the update (EX-0134)</t>
         </is>
       </c>
       <c r="I138" s="7" t="inlineStr">
@@ -30070,7 +29989,7 @@
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
-          <t>Walked register vs HR/transfer: MD-00103 still says Denver - Closed (EX-0134).</t>
+          <t>equipment_transfer_log TR-00103 points to Chicago. finding EX-0134. Site code Denver - Closed on MD-00103 was retired during consolidation but remains on the asset row. operating footprint for MD-00103 is Chicago, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M138" s="7" t="inlineStr">
@@ -30115,7 +30034,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>Obtain cert or restock MD-00104. Ticket RET-00104 (EX-0135).</t>
+          <t>Obtain disposal certificate for MD-00104 or reverse retirement (EX-0135).</t>
         </is>
       </c>
       <c r="I139" s="7" t="inlineStr">
@@ -30135,7 +30054,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>TR-00104 to recycler without DC for MD-00104 (EX-0135).</t>
+          <t>transfer TR-00104 to recycler without DC. serial MD-NE-050104 not matched in asset_disposal_records. EX-0135. Retirement path for MD-00104 lacks a verified disposal certificate.</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -30180,7 +30099,7 @@
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist owns the location rewrite for MD-00104 at Chicago - Closed (EX-0136).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00104 with Dallas on the register; cite TR-00104 in the update (EX-0136)</t>
         </is>
       </c>
       <c r="I140" s="7" t="inlineStr">
@@ -30200,7 +30119,7 @@
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
-          <t>Unused-office coding on MD-00104 is unsupported by movement files (EX-0136).</t>
+          <t>Site code Chicago - Closed on MD-00104 was retired during consolidation but remains on the asset row. operating footprint for MD-00104 is Dallas, not Chicago - Closed. finding EX-0136. equipment_transfer_log TR-00104 points to Dallas.</t>
         </is>
       </c>
       <c r="M140" s="7" t="inlineStr">
@@ -30245,7 +30164,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>Match a vendor cert to MD-LA-050105 or unwind retirement (EX-0137).</t>
+          <t>Obtain disposal certificate for MD-00105 or reverse retirement (EX-0137).</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr">
@@ -30265,7 +30184,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>No DC row ties to MD-LA-050105 for MD-00105 (EX-0137).</t>
+          <t>serial MD-LA-050105 not matched in asset_disposal_records. EX-0137. transfer TR-00105 to recycler without DC. Retirement path for MD-00105 lacks a verified disposal certificate.</t>
         </is>
       </c>
       <c r="M141" s="7" t="inlineStr">
@@ -30310,7 +30229,7 @@
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 / Denver - Closed is a consolidation leftover - move to Denver (EX-0138).</t>
+          <t>IT Asset Specialist: change MD-00105 location from Denver - Closed to Denver; cite TR-00105 in the update (EX-0138)</t>
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr">
@@ -30330,7 +30249,7 @@
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed conflicts with current footprint for MD-00105 (EX-0138).</t>
+          <t>operating footprint for MD-00105 is Denver, not Denver - Closed. equipment_transfer_log TR-00105 points to Denver. Site code Denver - Closed on MD-00105 was retired during consolidation but remains on the asset row. finding EX-0138.</t>
         </is>
       </c>
       <c r="M142" s="7" t="inlineStr">
@@ -30375,7 +30294,7 @@
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>Hold retirement on MD-00106. Need disposal certificate or restock (EX-0139).</t>
+          <t>Obtain disposal certificate for MD-00106 or reverse retirement (EX-0139).</t>
         </is>
       </c>
       <c r="I143" s="7" t="inlineStr">
@@ -30395,7 +30314,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>Cert field empty on MD-00106; retirement not closed (EX-0139).</t>
+          <t>transfer TR-00106 to recycler without DC. EX-0139. serial MD-MO-050106 not matched in asset_disposal_records. Retirement path for MD-00106 lacks a verified disposal certificate.</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -30440,7 +30359,7 @@
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>HR-aligned site for MD-00106 is New York; register still says Chicago - Closed (EX-0140).</t>
+          <t>IT Asset Specialist: change MD-00106 location from Chicago - Closed to New York; cite TR-00106 in the update (EX-0140)</t>
         </is>
       </c>
       <c r="I144" s="7" t="inlineStr">
@@ -30460,7 +30379,7 @@
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
-          <t>Location evidence for MD-00106: closed floor Chicago - Closed vs live New York (EX-0140).</t>
+          <t>operating footprint for MD-00106 is New York, not Chicago - Closed. finding EX-0140. Inventory row MD-00106 (serial MD-MO-050106) still lists site Chicago - Closed. equipment_transfer_log TR-00106 points to New York.</t>
         </is>
       </c>
       <c r="M144" s="7" t="inlineStr">
@@ -30505,7 +30424,7 @@
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>RET-00107 has no matching cert; MD-00107 stays pending-disposal (EX-0141).</t>
+          <t>Obtain disposal certificate for MD-00107 or reverse retirement (EX-0141).</t>
         </is>
       </c>
       <c r="I145" s="7" t="inlineStr">
@@ -30525,7 +30444,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>Retirement/disposal path for MD-00107 has no matching certificate (EX-0141).</t>
+          <t>transfer TR-00107 to recycler without DC. EX-0141. serial MD-MO-050107 not matched in asset_disposal_records. Retirement path for MD-00107 lacks a verified disposal certificate.</t>
         </is>
       </c>
       <c r="M145" s="7" t="inlineStr">
@@ -30570,7 +30489,7 @@
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist owns the location rewrite for MD-00107 at Denver - Closed (EX-0142).</t>
+          <t>Correct the stale location on MD-00107 (Denver - Closed → Seattle); cite TR-00107 in the update (EX-0142)</t>
         </is>
       </c>
       <c r="I146" s="7" t="inlineStr">
@@ -30590,7 +30509,7 @@
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
-          <t>Register location Denver - Closed conflicts with current footprint for MD-00107 (EX-0142).</t>
+          <t>equipment_transfer_log TR-00107 points to Seattle. Inventory row MD-00107 (serial MD-MO-050107) still lists site Denver - Closed. finding EX-0142. operating footprint for MD-00107 is Seattle, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M146" s="7" t="inlineStr">
@@ -30635,7 +30554,7 @@
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>Hold retirement on MD-00108. Need disposal certificate or restock (EX-0143).</t>
+          <t>Obtain disposal certificate for MD-00108 or reverse retirement (EX-0143).</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr">
@@ -30655,7 +30574,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>No DC row ties to MD-NE-050108 for MD-00108 (EX-0143).</t>
+          <t>transfer TR-00108 to recycler without DC. serial MD-NE-050108 not matched in asset_disposal_records. EX-0143. Retirement path for MD-00108 lacks a verified disposal certificate.</t>
         </is>
       </c>
       <c r="M147" s="7" t="inlineStr">
@@ -30700,7 +30619,7 @@
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 location field lagged after consolidation; update from Chicago - Closed to Atlanta (EX-0144).</t>
+          <t>Retire the closed-office code on MD-00108 and post Atlanta as the working site; cite TR-00108 in the update (EX-0144)</t>
         </is>
       </c>
       <c r="I148" s="7" t="inlineStr">
@@ -30720,7 +30639,7 @@
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
-          <t>Physical sites changed; MD-00108 register did not (Chicago - Closed, EX-0144).</t>
+          <t>operating footprint for MD-00108 is Atlanta, not Chicago - Closed. finding EX-0144. equipment_transfer_log TR-00108 points to Atlanta. Inventory row MD-00108 (serial MD-NE-050108) still lists site Chicago - Closed.</t>
         </is>
       </c>
       <c r="M148" s="7" t="inlineStr">
@@ -30765,7 +30684,7 @@
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>ITAM hold - MD-00109 not gone until cert lists the tag (EX-0145).</t>
+          <t>Obtain disposal certificate for MD-00109 or reverse retirement (EX-0145).</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr">
@@ -30785,7 +30704,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>Retirement/disposal path for MD-00109 has no matching certificate (EX-0145).</t>
+          <t>Retirement path for MD-00109 lacks a verified disposal certificate. EX-0145. serial MD-LA-050109 not matched in asset_disposal_records. transfer TR-00109 to recycler without DC.</t>
         </is>
       </c>
       <c r="M149" s="7" t="inlineStr">
@@ -30830,7 +30749,7 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>Denver - Closed is no longer occupied. Park MD-00109 at Chicago on the register (EX-0146).</t>
+          <t>Replace shuttered site Denver - Closed on MD-00109 with Chicago on the register; cite TR-00109 in the update (EX-0146)</t>
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr">
@@ -30850,7 +30769,7 @@
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
-          <t>Location evidence for MD-00109: closed floor Denver - Closed vs live Chicago (EX-0146).</t>
+          <t>finding EX-0146. Inventory row MD-00109 (serial MD-LA-050109) still lists site Denver - Closed. equipment_transfer_log TR-00109 points to Chicago. operating footprint for MD-00109 is Chicago, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M150" s="7" t="inlineStr">
@@ -30895,7 +30814,7 @@
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Hold retirement on MD-00110. Need disposal certificate or restock (EX-0147).</t>
+          <t>Obtain disposal certificate for MD-00110 or reverse retirement (EX-0147).</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr">
@@ -30915,7 +30834,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>Cert field empty on MD-00110; retirement not closed (EX-0147).</t>
+          <t>Retirement path for MD-00110 lacks a verified disposal certificate. serial MD-MO-050110 not matched in asset_disposal_records. EX-0147. transfer TR-00110 to recycler without DC.</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -30960,7 +30879,7 @@
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Location on MD-00110 must reflect Dallas after the site close (EX-0148).</t>
+          <t>Replace shuttered site Chicago - Closed on MD-00110 with Dallas on the register; cite TR-00110 in the update (EX-0148)</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr">
@@ -30980,7 +30899,7 @@
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
-          <t>Chicago - Closed is shuttered. Did not leave MD-00110 there on paper - Dallas is live (EX-0148).</t>
+          <t>The register extract for MD-00110 carries location Chicago - Closed after that floor was vacated. finding EX-0148. operating footprint for MD-00110 is Dallas, not Chicago - Closed. equipment_transfer_log TR-00110 points to Dallas.</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -31025,7 +30944,7 @@
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>MD-00114: pending disposal with no DC row. Block close (EX-0149).</t>
+          <t>Obtain disposal certificate for MD-00114 or reverse retirement (EX-0149).</t>
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr">
@@ -31045,7 +30964,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>No DC row ties to MD-MO-050114 for MD-00114 (EX-0149).</t>
+          <t>transfer TR-00114 to recycler without DC. Retirement path for MD-00114 lacks a verified disposal certificate. EX-0149. serial MD-MO-050114 not matched in asset_disposal_records.</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
@@ -31090,7 +31009,7 @@
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>Remove closed-site coding on MD-00114 (Chicago - Closed → Disposed (certificate missing), EX-0150).</t>
+          <t>IT Asset Specialist: change MD-00114 location from Chicago - Closed to Disposed (certificate missing); cite TR-00114 in the update (EX-0150)</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr">
@@ -31110,7 +31029,7 @@
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
-          <t>Register location Chicago - Closed conflicts with current footprint for MD-00114 (EX-0150).</t>
+          <t>operating footprint for MD-00114 is Disposed (certificate missing), not Chicago - Closed. equipment_transfer_log TR-00114 points to Disposed (certificate missing). Site code Chicago - Closed on MD-00114 was retired during consolidation but remains on the asset row. finding EX-0150.</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -31155,7 +31074,7 @@
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>Paperwork gap on MD-00118: cert or reverse the retire (EX-0151).</t>
+          <t>Obtain disposal certificate for MD-00118 or reverse retirement (EX-0151).</t>
         </is>
       </c>
       <c r="I155" s="7" t="inlineStr">
@@ -31175,7 +31094,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>Cert field empty on MD-00118; retirement not closed (EX-0151).</t>
+          <t>Retirement path for MD-00118 lacks a verified disposal certificate. serial MD-MO-050118 not matched in asset_disposal_records. transfer TR-00118 to recycler without DC. EX-0151.</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
@@ -31220,7 +31139,7 @@
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>Do not leave MD-00118 assigned to unused floor Chicago - Closed (EX-0152).</t>
+          <t>Retire the closed-office code on MD-00118 and post Disposed (certificate missing) as the working site; cite TR-00118 in the update (EX-0152)</t>
         </is>
       </c>
       <c r="I156" s="7" t="inlineStr">
@@ -31240,7 +31159,7 @@
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
-          <t>Did not treat closed building Chicago - Closed as live location for MD-00118 (EX-0152).</t>
+          <t>Site code Chicago - Closed on MD-00118 was retired during consolidation but remains on the asset row. operating footprint for MD-00118 is Disposed (certificate missing), not Chicago - Closed. equipment_transfer_log TR-00118 points to Disposed (certificate missing). finding EX-0152.</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -31285,7 +31204,7 @@
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>Finance Controller owns cost-basis cleanup on MD-00119.</t>
+          <t>Align cost on MD-00119: register 950.0 vs ledger 1115.0 (FA-000119) (EX-0153).</t>
         </is>
       </c>
       <c r="I157" s="7" t="inlineStr">
@@ -31305,7 +31224,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>Basis mismatch documented for MD-00119 (950.0 vs 1115.0).</t>
+          <t>Register cost $950.0 on MD-00119 does not match ledger $1115.0 on FA-000119 (EX-0153).</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr">
@@ -31350,7 +31269,7 @@
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Clear the leftover closed-office assignment on MD-00121 (EX-0154).</t>
+          <t>IT Asset Specialist: change MD-00121 location from Denver - Closed to Chicago; cite TR-00121 in the update (EX-0154)</t>
         </is>
       </c>
       <c r="I158" s="7" t="inlineStr">
@@ -31370,7 +31289,7 @@
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
-          <t>Closed floor Denver - Closed remains on MD-00121 despite transfer evidence (EX-0154, TR-00121).</t>
+          <t>equipment_transfer_log TR-00121 points to Chicago. finding EX-0154. Site code Denver - Closed on MD-00121 was retired during consolidation but remains on the asset row. operating footprint for MD-00121 is Chicago, not Denver - Closed.</t>
         </is>
       </c>
       <c r="M158" s="7" t="inlineStr">
@@ -31415,7 +31334,7 @@
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>IT Asset Specialist: recode MD-00122 off Chicago - Closed; Dallas is the live office per TR-00122 (EX-0155).</t>
+          <t>Retire the closed-office code on MD-00122 and post Dallas as the working site; cite TR-00122 in the update (EX-0155)</t>
         </is>
       </c>
       <c r="I159" s="7" t="inlineStr">
@@ -31435,7 +31354,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>Walked register vs HR/transfer: MD-00122 still says Chicago - Closed (EX-0155).</t>
+          <t>finding EX-0155. The register extract for MD-00122 carries location Chicago - Closed after that floor was vacated. equipment_transfer_log TR-00122 points to Dallas. operating footprint for MD-00122 is Dallas, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M159" s="7" t="inlineStr">
@@ -31480,7 +31399,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>Update register location for MD-00123 before the next cert packet (EX-0156).</t>
+          <t>IT Asset Specialist: change MD-00123 location from Denver - Closed to Denver; cite TR-00123 in the update (EX-0156)</t>
         </is>
       </c>
       <c r="I160" s="7" t="inlineStr">
@@ -31500,7 +31419,7 @@
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
-          <t>Register still codes MD-00123 to Denver - Closed; TR-00123 points to Denver (EX-0156).</t>
+          <t>equipment_transfer_log TR-00123 points to Denver. finding EX-0156. operating footprint for MD-00123 is Denver, not Denver - Closed. Inventory row MD-00123 (serial MD-MO-050123) still lists site Denver - Closed.</t>
         </is>
       </c>
       <c r="M160" s="7" t="inlineStr">
@@ -31545,7 +31464,7 @@
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Remove closed-site coding on MD-00124 (Chicago - Closed → New York, EX-0157).</t>
+          <t>Retire the closed-office code on MD-00124 and post New York as the working site; cite TR-00124 in the update (EX-0157)</t>
         </is>
       </c>
       <c r="I161" s="7" t="inlineStr">
@@ -31565,7 +31484,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>Extract shows MD-00124 at Chicago - Closed - that building is locked (EX-0157).</t>
+          <t>equipment_transfer_log TR-00124 points to New York. finding EX-0157. Site code Chicago - Closed on MD-00124 was retired during consolidation but remains on the asset row. operating footprint for MD-00124 is New York, not Chicago - Closed.</t>
         </is>
       </c>
       <c r="M161" s="7" t="inlineStr">
@@ -31610,7 +31529,7 @@
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Seattle is supported by HR/transfer for MD-00125; Denver - Closed is obsolete (EX-0158).</t>
+          <t>IT Asset Specialist: change MD-00125 location from Denver - Closed to Seattle; cite TR-00125 in the update (EX-0158)</t>
         </is>
       </c>
       <c r="I162" s="7" t="inlineStr">
@@ -31630,7 +31549,7 @@
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
-          <t>Physical sites changed; MD-00125 register did not (Denver - Closed, EX-0158).</t>
+          <t>The register extract for MD-00125 carries location Denver - Closed after that floor was vacated. equipment_transfer_log TR-00125 points to Seattle. operating footprint for MD-00125 is Seattle, not Denver - Closed. finding EX-0158.</t>
         </is>
       </c>
       <c r="M162" s="7" t="inlineStr">
@@ -31675,7 +31594,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Atlanta is supported by HR/transfer for MD-00126; Chicago - Closed is obsolete (EX-0159).</t>
+          <t>Retire the closed-office code on MD-00126 and post Atlanta as the working site; cite TR-00126 in the update (EX-0159)</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr">
@@ -31695,7 +31614,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>Consolidation left MD-00126 @ Chicago - Closed; ops now use Atlanta (EX-0159).</t>
+          <t>operating footprint for MD-00126 is Atlanta, not Chicago - Closed. finding EX-0159. Inventory row MD-00126 (serial MD-MO-050126) still lists site Chicago - Closed. equipment_transfer_log TR-00126 points to Atlanta.</t>
         </is>
       </c>
       <c r="M163" s="7" t="inlineStr">
@@ -31740,7 +31659,7 @@
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>Either approve TR-00127 after the fact or put MD-00127 back.</t>
+          <t>Obtain APR on TR-00127 or reverse move for MD-00127 (EX-0160).</t>
         </is>
       </c>
       <c r="I164" s="7" t="inlineStr">
@@ -31760,7 +31679,7 @@
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
-          <t>Unapproved transfer TR-00127 on MD-00127 from equipment_transfer_log.</t>
+          <t>Transfer TR-00127 for MD-00127 has a blank approval_id per ITAM-001 §4 (EX-0160).</t>
         </is>
       </c>
       <c r="M164" s="7" t="inlineStr">
@@ -31805,7 +31724,7 @@
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>$700 on MD-00130. Below threshold. Informational only.</t>
+          <t>Informational only — MD-00130 under $2,500 gate (EX-0161).</t>
         </is>
       </c>
       <c r="I165" s="7" t="inlineStr">
@@ -31825,7 +31744,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>$700 on MD-00130 - under §7 gate. Ledger absence expected.</t>
+          <t>MD-00130 at $700 is below the $2,500 gate; FAR silence is expected (EX-0161).</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
@@ -31870,7 +31789,7 @@
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>$1175 on MD-00131. Below threshold. Informational only.</t>
+          <t>Informational only — MD-00131 under $2,500 gate (EX-0162).</t>
         </is>
       </c>
       <c r="I166" s="7" t="inlineStr">
@@ -31890,7 +31809,7 @@
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
-          <t>Under-threshold check for MD-00131: $1175 &lt; $2,500.</t>
+          <t>MD-00131 at $1175 is below the $2,500 gate; FAR silence is expected (EX-0162).</t>
         </is>
       </c>
       <c r="M166" s="12" t="inlineStr">
@@ -31935,7 +31854,7 @@
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Finance: FA line for MD-00132 or signed write-off. Regional note non-authoritative.</t>
+          <t>Capitalize MD-00132 or obtain approved write-off; reject RN-0132 claim (EX-0163).</t>
         </is>
       </c>
       <c r="I167" s="7" t="inlineStr">
@@ -31955,7 +31874,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>FAR extract has no MD-00132. Cost $6470.0 exceeds $2,500. RN-0132 is a claim, not a posting.</t>
+          <t>MD-00132 acquisition $6470.0 exceeds the $2,500 capitalization gate with no FA row; RN-0132 under-threshold claim rejected (EX-0163).</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
@@ -31964,6 +31883,7 @@
         </is>
       </c>
     </row>
+    <row r="168"/>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
@@ -31972,8 +31892,17 @@
       </c>
       <c r="G169">
         <f>SUM(G5:G167)</f>
-        <v>85928.73</v>
         <v/>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>IT Asset Specialist: remediate Total Financial Exposure on None per cited records.</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Reviewed cited records for None under Total Financial Exposure: .</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -32019,7 +31948,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -32110,7 +32038,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00017 (MacBook Pro 14) for $1985 via PO-2024-0003.</t>
+          <t>Acquisition MD-00017: MacBook Pro 14, $1985, PO PO-2024-0003.</t>
         </is>
       </c>
     </row>
@@ -32149,7 +32077,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Seattle custody review for MD-00017 used the disposal column on the matrix. Source trail: TR-00017, PO-2024-0003, FA-000017, APR-00017.</t>
+          <t>Matrix return criteria applied to MD-00017; figure is reference, not inbound proof for chain row 6.</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32124,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>TR-00017 2026-06-17; inbound Jun 19, 2026.</t>
+          <t>Transfer TR-00017 for MD-00017: posted 06/17/2026, inbound Jun 19, 2026, APR APR-00017.</t>
         </is>
       </c>
     </row>
@@ -32243,7 +32171,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Verified In Use for MD-00017 in Seattle. High. EX-0001. E0017. TR-00017. APR-00017. PO. PO-2024-0003. FA-000017. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00017: In Use / Seattle (High). EX-0001.</t>
         </is>
       </c>
     </row>
@@ -32290,7 +32218,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2025-0004 lists Dell Latitude 7440 / $1850.</t>
+          <t>Acquisition MD-00021: Dell Latitude 7440, $1850, PO PO-2025-0004.</t>
         </is>
       </c>
     </row>
@@ -32337,7 +32265,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows May 03, 2026 for TR-00021 (MD-00021).</t>
+          <t>Transfer TR-00021 for MD-00021: posted 2026-05-02, inbound 05/03/2026, APR APR-00021.</t>
         </is>
       </c>
     </row>
@@ -32376,7 +32304,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>ITAM_control_matrix.png consulted for MD-00021 (return). Conclusion still tied to TR-00021, PO-2025-0004, FA-000021, APR-00021 at Denver, $1850.</t>
+          <t>Policy figure sets transfer evidence expectations for MD-00021; chain row 11 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -32423,7 +32351,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>MD-00021 custody narrative ends In Use (Medium). EX-0002. E0021. TR-00021. APR-00021. PO. PO-2025-0004. FA-000021. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00021: In Use / Denver (Medium). EX-0002.</t>
         </is>
       </c>
     </row>
@@ -32470,7 +32398,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2022-0005 lists Lenovo ThinkPad T14 / $2030.</t>
+          <t>Vendor shipment for MD-00025 (Lenovo ThinkPad T14) recorded at $2030 on PO-2022-0005.</t>
         </is>
       </c>
     </row>
@@ -32517,7 +32445,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00025. Receive date 01/22/2026.</t>
+          <t>Transfer TR-00025 for MD-00025: posted 01/21/2026, inbound Jan 22, 2026, APR APR-00025.</t>
         </is>
       </c>
     </row>
@@ -32560,7 +32488,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Could not tie MD-00025 to a verified RN entry in the notes.</t>
+          <t>regional_IT_notes.docx checked for MD-00025; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -32599,7 +32527,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00025 should read matrix transfer, then TR-00025, PO-2022-0005, FA-000025, APR-00025. Working site Chicago; status call In Use.</t>
+          <t>Policy figure sets assignment evidence expectations for MD-00025; chain row 16 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -32646,7 +32574,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Chain end MD-00025: In Use; Medium; EX-0003, EX-0004. E0025. TR-00025. APR-00025. PO. PO-2022-0005. FA-000025. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00025 — In Use, site Chicago, Medium. EX-0003, EX-0004.</t>
         </is>
       </c>
     </row>
@@ -32693,7 +32621,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0006. Dell U2723QE.</t>
+          <t>Acquisition MD-00034: Dell U2723QE, $790, PO PO-2023-0006.</t>
         </is>
       </c>
     </row>
@@ -32740,7 +32668,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>MD-00034 inbound May 22, 2026 on TR-00034 / APR-00034.</t>
+          <t>Transfer TR-00034 for MD-00034: posted May 22, 2026, inbound 2026-05-22, APR APR-00034.</t>
         </is>
       </c>
     </row>
@@ -32783,7 +32711,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Regional file reviewed for MD-00034; no clearance language accepted.</t>
+          <t>regional_IT_notes.docx checked for MD-00034; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -32822,7 +32750,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>MD-00034 / Dell U2723QE: return evidence expectations from Appendix A. Anchored to TR-00034, PO-2023-0006, FA-000034, APR-00034; acquisition $790.</t>
+          <t>ITAM_control_matrix.png Appendix A transfer row consulted while tracing MD-00034; transactional proof stays with chain row 21.</t>
         </is>
       </c>
     </row>
@@ -32869,7 +32797,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00034 - In Use, site New York, High. EX-0013, EX-0014. E0034. TR-00034. APR-00034. PO. PO-2023-0006. FA-000034. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00034: In Use / New York (High). EX-0013, EX-0014.</t>
         </is>
       </c>
     </row>
@@ -32916,7 +32844,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Capital buy MD-00051: Samsung Galaxy S24, $1040, PO-2022-0009.</t>
+          <t>PO PO-2022-0009 covers MD-00051 (Samsung Galaxy S24) for $1040.</t>
         </is>
       </c>
     </row>
@@ -32963,7 +32891,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows 2026-03-31 for TR-00051 (MD-00051).</t>
+          <t>Transfer TR-00051 for MD-00051: posted 03/31/2026, inbound Mar 31, 2026, APR APR-00051.</t>
         </is>
       </c>
     </row>
@@ -33006,7 +32934,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Could not tie MD-00051 to a verified RN entry in the notes.</t>
+          <t>regional_IT_notes.docx checked for MD-00051; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -33045,7 +32973,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Did not treat the PNG as proof of location for MD-00051. return standard applied; TR-00051, PO-2022-0009, FA-000051, APR-00051 remains dispositive (Available).</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix assignment line for MD-00051; cite chain row 26.</t>
         </is>
       </c>
     </row>
@@ -33092,7 +33020,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>I am standing on Available for MD-00051 (Denver, High). EX-0031, EX-0032. TR-00051. APR-00051. PO. PO-2022-0009. FA-000051. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00051: Available / Denver (High). EX-0031, EX-0032.</t>
         </is>
       </c>
     </row>
@@ -33139,7 +33067,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2023-0010 - Dell U2723QE.</t>
+          <t>Acquisition MD-00058: Dell U2723QE, $610, PO PO-2023-0010.</t>
         </is>
       </c>
     </row>
@@ -33186,7 +33114,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows 05/23/2026 for TR-00058 (MD-00058).</t>
+          <t>Transfer TR-00058 for MD-00058: posted 05/22/2026, inbound May 23, 2026, APR missing.</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33157,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00058. Status Closed.</t>
+          <t>Service desk OFF-00058: Closed; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00058.</t>
         </is>
       </c>
     </row>
@@ -33311,7 +33239,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Regional claim (Asset appears to have been moved to Regional IT stock. The transfer record contains no app) does not beat a scan for MD-00058.</t>
+          <t>regional_IT_notes.docx checked for MD-00058; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -33350,7 +33278,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>MD-00058: checked ITAM-001 disposal row while reviewing TR-00058, PO-2023-0010, FA-000058, OFF-00058. Cost basis $610; confidence Medium. Figure does not replace logs.</t>
+          <t>Policy figure sets assignment evidence expectations for MD-00058; chain row 33 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -33397,7 +33325,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Call on MD-00058: Pending Redeployment, Medium. EX-0039, EX-0040, EX-0041. TR-00058. OFF-00058. PO. PO-2023-0010. FA-000058. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00058: Pending Redeployment at New York (Medium). EX-0039, EX-0040, EX-0041.</t>
         </is>
       </c>
     </row>
@@ -33444,7 +33372,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>PO-2023-0010 documents $1085 for Samsung Galaxy S24.</t>
+          <t>Acquisition MD-00059: Samsung Galaxy S24, $1085, PO PO-2023-0010.</t>
         </is>
       </c>
     </row>
@@ -33491,7 +33419,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>TR-00059 - got it 2026-06-26 at Seattle.</t>
+          <t>Transfer TR-00059 for MD-00059: posted Jun 26, 2026, inbound 2026-06-26, APR missing.</t>
         </is>
       </c>
     </row>
@@ -33534,7 +33462,7 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00059. Status Closed.</t>
+          <t>Service desk OFF-00059: Closed; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00059.</t>
         </is>
       </c>
     </row>
@@ -33616,7 +33544,7 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Looked for MD-00059 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
+          <t>regional_IT_notes.docx checked for MD-00059; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -33655,7 +33583,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure open for MD-00059 return path; transactional weight on TR-00059, PO-2023-0010, FA-000059, OFF-00059. Open exceptions EX-0042, EX-0043, EX-0044 still govern certification impact.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix financial line for MD-00059; cite chain row 40.</t>
         </is>
       </c>
     </row>
@@ -33702,7 +33630,7 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Closing MD-00059: Pending Redeployment at Seattle (Medium). EX-0042, EX-0043, EX-0044. TR-00059. OFF-00059. PO. PO-2023-0010. FA-000059. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00059: Pending Redeployment at Seattle (Medium). EX-0042, EX-0043, EX-0044.</t>
         </is>
       </c>
     </row>
@@ -33749,7 +33677,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>MD-00060 origin: PO-2023-0010, $6380.</t>
+          <t>Vendor shipment for MD-00060 (Cisco C9300) recorded at $6380 on PO-2023-0010.</t>
         </is>
       </c>
     </row>
@@ -33796,7 +33724,7 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00060 completed inbound Feb 02, 2026.</t>
+          <t>Transfer TR-00060 for MD-00060: posted 2026-01-30, inbound 02/02/2026, APR APR-00060.</t>
         </is>
       </c>
     </row>
@@ -33839,7 +33767,7 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>OFF-00060 Closed. Return required=Yes, due 07/15/2026.</t>
+          <t>Service desk OFF-00060: Closed; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00060.</t>
         </is>
       </c>
     </row>
@@ -33921,7 +33849,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00060; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00060; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -33960,7 +33888,7 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>For MD-00060 (Cisco C9300), Appendix A transfer criteria were read against TR-00060, PO-2023-0010, FA-000060, OFF-00060, APR-00060. Verified status target Pending Redeployment at Atlanta; matrix PNG is reference only.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00060; cite chain row 47.</t>
         </is>
       </c>
     </row>
@@ -34007,7 +33935,7 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00060: Pending Redeployment @ Atlanta, confidence High. EX-0045, EX-0046. TR-00060. APR-00060. OFF-00060. PO. PO-2023-0010. FA-000060. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00060 as Pending Redeployment in Atlanta; confidence High. EX-0045, EX-0046.</t>
         </is>
       </c>
     </row>
@@ -34054,7 +33982,7 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>PO-2024-0011 documents $2075 for Lenovo ThinkPad T14.</t>
+          <t>Acquisition MD-00061: Lenovo ThinkPad T14, $2075, PO PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -34101,7 +34029,7 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted Feb 02, 2026. Docked 02/03/2026 (TR-00061).</t>
+          <t>Transfer TR-00061 for MD-00061: posted 02/02/2026, inbound Feb 03, 2026, APR APR-00061.</t>
         </is>
       </c>
     </row>
@@ -34144,7 +34072,7 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00061: Yes. Due 2026-07-15.</t>
+          <t>Service desk OFF-00061: Closed; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00061.</t>
         </is>
       </c>
     </row>
@@ -34183,7 +34111,7 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Looping with site ops - laptop still showing assigned post-term. Ref MD-00061.</t>
+          <t>Looping with site ops — laptop still showing assigned post-term. Ref MD-00061.</t>
         </is>
       </c>
     </row>
@@ -34226,7 +34154,7 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Regional write-up for MD-00061 is non-authoritative per ITAM-001.</t>
+          <t>regional_IT_notes.docx checked for MD-00061; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -34265,7 +34193,7 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>MD-00061: checked ITAM-001 assignment row while reviewing TR-00061, PO-2024-0011, FA-000061, OFF-00061, APR-00061. Cost basis $2075; confidence High. Figure does not replace logs.</t>
+          <t>Policy figure sets return evidence expectations for MD-00061; chain row 54 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -34312,7 +34240,7 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Pending Redeployment is the status for MD-00061 at Chicago; High. EX-0047, EX-0048. TR-00061. APR-00061. OFF-00061. PO. PO-2024-0011. FA-000061. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00061 as Pending Redeployment in Chicago; confidence High. EX-0047, EX-0048.</t>
         </is>
       </c>
     </row>
@@ -34359,7 +34287,7 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2024-0011. Dell U2723QE.</t>
+          <t>PO PO-2024-0011 covers MD-00062 (Dell U2723QE) for $790.</t>
         </is>
       </c>
     </row>
@@ -34406,7 +34334,7 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows 2026-03-07 for TR-00062 (MD-00062).</t>
+          <t>Transfer TR-00062 for MD-00062: posted Mar 07, 2026, inbound 2026-03-07, APR APR-00062.</t>
         </is>
       </c>
     </row>
@@ -34449,7 +34377,7 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00062: Yes. Due Jul 15, 2026.</t>
+          <t>Service desk OFF-00062: Closed; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00062.</t>
         </is>
       </c>
     </row>
@@ -34531,7 +34459,7 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>No matching RN row for MD-00062; generic technician chatter in the Word file only.</t>
+          <t>regional_IT_notes.docx checked for MD-00062; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -34570,7 +34498,7 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>MD-00062 / Dell U2723QE: financial evidence expectations from Appendix A. Anchored to TR-00062, PO-2024-0011, FA-000062, OFF-00062, APR-00062; acquisition $790.</t>
+          <t>ITAM_control_matrix.png Appendix A transfer row consulted while tracing MD-00062; transactional proof stays with chain row 61.</t>
         </is>
       </c>
     </row>
@@ -34617,7 +34545,7 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Call on MD-00062: Pending Redeployment, High. EX-0049, EX-0050. TR-00062. APR-00062. OFF-00062. PO. PO-2024-0011. FA-000062. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00062: Pending Redeployment / Dallas (High). EX-0049, EX-0050.</t>
         </is>
       </c>
     </row>
@@ -34664,7 +34592,7 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Bought the Samsung Galaxy S24 ($950) on PO-2024-0011.</t>
+          <t>Vendor shipment for MD-00063 (Samsung Galaxy S24) recorded at $950 on PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -34711,7 +34639,7 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>TR-00063 - got it Apr 16, 2026 at Denver.</t>
+          <t>Transfer TR-00063 for MD-00063: posted 2026-04-12, inbound 04/16/2026, APR APR-00063.</t>
         </is>
       </c>
     </row>
@@ -34754,7 +34682,7 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>OFF-00063 sits Closed. Hardware return was required. 07/15/2026.</t>
+          <t>Service desk OFF-00063: Closed; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00063.</t>
         </is>
       </c>
     </row>
@@ -34836,7 +34764,7 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00063 in regional_IT_notes.docx - weight zero.</t>
+          <t>regional_IT_notes.docx checked for MD-00063; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -34875,7 +34803,7 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>MD-00063: checked ITAM-001 return row while reviewing TR-00063, PO-2024-0011, FA-000063, OFF-00063, APR-00063. Cost basis $950; confidence High. Figure does not replace logs.</t>
+          <t>Policy figure sets financial evidence expectations for MD-00063; chain row 68 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -34922,7 +34850,7 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00063 - Pending Redeployment, site Denver, High. EX-0051, EX-0052. TR-00063. APR-00063. OFF-00063. PO. PO-2024-0011. FA-000063. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00063 — Pending Redeployment, site Denver, High. EX-0051, EX-0052.</t>
         </is>
       </c>
     </row>
@@ -34969,7 +34897,7 @@
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2024-0011 lists Cisco C9300 / $6245.</t>
+          <t>Vendor shipment for MD-00064 (Cisco C9300) recorded at $6245 on PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -35016,7 +34944,7 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Regional IT. TR-00064, received 05/14/2026.</t>
+          <t>Transfer TR-00064 for MD-00064: posted 05/13/2026, inbound May 14, 2026, APR missing.</t>
         </is>
       </c>
     </row>
@@ -35059,7 +34987,7 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00064. Doesn't by itself dock MD-00064.</t>
+          <t>Service desk OFF-00064: Closed; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00064.</t>
         </is>
       </c>
     </row>
@@ -35141,7 +35069,7 @@
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>Technician comment volume in the doc does not clear MD-00064.</t>
+          <t>regional_IT_notes.docx checked for MD-00064; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -35180,7 +35108,7 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00064 should read matrix transfer, then TR-00064, PO-2024-0011, FA-000064, OFF-00064. Working site New York; status call Pending Redeployment.</t>
+          <t>ITAM_control_matrix.png Appendix A disposal row consulted while tracing MD-00064; transactional proof stays with chain row 75.</t>
         </is>
       </c>
     </row>
@@ -35227,7 +35155,7 @@
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>I am standing on Pending Redeployment for MD-00064 (New York, Medium). EX-0053, EX-0054, EX-0055. TR-00064. OFF-00064. PO. PO-2024-0011. FA-000064. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00064: Pending Redeployment / New York (Medium). EX-0053, EX-0054, EX-0055.</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35202,7 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>$1940 MacBook Pro 14. PO-2024-0011.</t>
+          <t>Vendor shipment for MD-00065 (MacBook Pro 14) recorded at $1940 on PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -35321,7 +35249,7 @@
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>Moved to Regional IT in Seattle on TR-00065. Received 2026-06-23.</t>
+          <t>Transfer TR-00065 for MD-00065: posted Jun 17, 2026, inbound 2026-06-23, APR missing.</t>
         </is>
       </c>
     </row>
@@ -35364,7 +35292,7 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00065. Doesn't by itself dock MD-00065.</t>
+          <t>Service desk OFF-00065: Closed; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00065.</t>
         </is>
       </c>
     </row>
@@ -35446,7 +35374,7 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>Notes packet includes MD-00065 only as background, not evidence.</t>
+          <t>regional_IT_notes.docx checked for MD-00065; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -35485,7 +35413,7 @@
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00065 should read matrix assignment, then TR-00065, PO-2024-0011, FA-000065, OFF-00065. Working site Seattle; status call Pending Redeployment.</t>
+          <t>Matrix return criteria applied to MD-00065; figure is reference, not inbound proof for chain row 82.</t>
         </is>
       </c>
     </row>
@@ -35532,7 +35460,7 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00065: Pending Redeployment (Medium) - EX-0056, EX-0057, EX-0058. TR-00065. OFF-00065. PO. PO-2024-0011. FA-000065. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00065: Pending Redeployment / Seattle (Medium). EX-0056, EX-0057, EX-0058.</t>
         </is>
       </c>
     </row>
@@ -35579,7 +35507,7 @@
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>Ordered Dell U2723QE (MD-00066) on PO-2024-0011; $655.</t>
+          <t>Acquisition MD-00066: Dell U2723QE, $655, PO PO-2024-0011.</t>
         </is>
       </c>
     </row>
@@ -35626,7 +35554,7 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>MD-00066 inbound Jan 25, 2026 on TR-00066 / APR-00066.</t>
+          <t>Transfer TR-00066 for MD-00066: posted 2026-01-22, inbound 01/25/2026, APR APR-00066.</t>
         </is>
       </c>
     </row>
@@ -35669,7 +35597,7 @@
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>OFF-00066 - Closed. Due 07/15/2026.</t>
+          <t>Service desk OFF-00066: Closed; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00066.</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35679,7 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>MD-00066: Word-file mention only - treated as lead.</t>
+          <t>regional_IT_notes.docx checked for MD-00066; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -35790,7 +35718,7 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure open for MD-00066 disposal path; transactional weight on TR-00066, PO-2024-0011, FA-000066, OFF-00066, APR-00066. Open exceptions EX-0059, EX-0060 still govern certification impact.</t>
+          <t>Policy figure sets assignment evidence expectations for MD-00066; chain row 89 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -35837,7 +35765,7 @@
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>After the chain, MD-00066 is Pending Redeployment / Atlanta (High). EX-0059, EX-0060. TR-00066. APR-00066. OFF-00066. PO. PO-2024-0011. FA-000066. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00066: Pending Redeployment at Atlanta (High). EX-0059, EX-0060.</t>
         </is>
       </c>
     </row>
@@ -35884,7 +35812,7 @@
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>$1130 Samsung Galaxy S24. PO-2025-0012.</t>
+          <t>PO PO-2025-0012 covers MD-00067 (Samsung Galaxy S24) for $1130.</t>
         </is>
       </c>
     </row>
@@ -35931,7 +35859,7 @@
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00067. Receive date 02/23/2026.</t>
+          <t>Transfer TR-00067 for MD-00067: posted 02/23/2026, inbound Feb 23, 2026, APR APR-00067.</t>
         </is>
       </c>
     </row>
@@ -35974,7 +35902,7 @@
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00067 on MD-00067. Return required Yes.</t>
+          <t>Service desk OFF-00067: Closed; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00067.</t>
         </is>
       </c>
     </row>
@@ -36056,7 +35984,7 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00067; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00067; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36023,7 @@
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure open for MD-00067 return path; transactional weight on TR-00067, PO-2025-0012, FA-000067, OFF-00067, APR-00067. Open exceptions EX-0061, EX-0062 still govern certification impact.</t>
+          <t>Matrix financial criteria applied to MD-00067; figure is reference, not inbound proof for chain row 96.</t>
         </is>
       </c>
     </row>
@@ -36142,7 +36070,7 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>MD-00067 custody narrative ends Pending Redeployment (High). EX-0061, EX-0062. TR-00067. APR-00067. OFF-00067. PO. PO-2025-0012. FA-000067. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00067: Pending Redeployment at Chicago (High). EX-0061, EX-0062.</t>
         </is>
       </c>
     </row>
@@ -36189,7 +36117,7 @@
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00068 - PO-2025-0012, $6425.</t>
+          <t>PO PO-2025-0012 covers MD-00068 (Cisco C9300) for $6425.</t>
         </is>
       </c>
     </row>
@@ -36236,7 +36164,7 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 03/28/2026. Docked 2026-04-03 (TR-00068).</t>
+          <t>Transfer TR-00068 for MD-00068: posted Mar 28, 2026, inbound 2026-04-03, APR APR-00068.</t>
         </is>
       </c>
     </row>
@@ -36279,7 +36207,7 @@
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00068: Yes. Due Jul 15, 2026.</t>
+          <t>Service desk OFF-00068: Past Due; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00068.</t>
         </is>
       </c>
     </row>
@@ -36365,7 +36293,7 @@
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Prepaid label 1ZMD00000068 exists. Carrier never accepted it.</t>
+          <t>Prepaid label 1ZMD00000068 for MD-00068 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36336,7 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Looked for MD-00068 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
+          <t>regional_IT_notes.docx checked for MD-00068; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -36447,7 +36375,7 @@
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee custody review for MD-00068 used the assignment column on the matrix. Source trail: TR-00068, PO-2025-0012, FA-000068, OFF-00068, APR-00068.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00068; cite chain row 104.</t>
         </is>
       </c>
     </row>
@@ -36494,7 +36422,7 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Return Overdue is the status for MD-00068 at Remote - Former Employee; Low. EX-0063, EX-0064, EX-0065. OFF-00068. 1ZMD00000068. TR-00068. E0081. PO. PO-2025-0012. FA-000068. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00068 as Return Overdue in Remote - Former Employee; confidence Low. EX-0063, EX-0064, EX-0065.</t>
         </is>
       </c>
     </row>
@@ -36541,7 +36469,7 @@
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2025-0012 lists Dell Latitude 7440 / $2120.</t>
+          <t>PO PO-2025-0012 covers MD-00069 (Dell Latitude 7440) for $2120.</t>
         </is>
       </c>
     </row>
@@ -36588,7 +36516,7 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee: TR-00069 received 05/04/2026.</t>
+          <t>Transfer TR-00069 for MD-00069: posted May 02, 2026, inbound 2026-05-04, APR APR-00069.</t>
         </is>
       </c>
     </row>
@@ -36631,7 +36559,7 @@
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>OFF-00069 - Past Due. Due 2026-07-15.</t>
+          <t>Service desk OFF-00069: Past Due; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00069.</t>
         </is>
       </c>
     </row>
@@ -36717,7 +36645,7 @@
       </c>
       <c r="I110" s="7" t="inlineStr">
         <is>
-          <t>Ship record 1ZMD00000069 hasn't left Label Created.</t>
+          <t>Prepaid label 1ZMD00000069 for MD-00069 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -36760,7 +36688,7 @@
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
-          <t>Looked for MD-00069 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
+          <t>regional_IT_notes.docx checked for MD-00069; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -36799,7 +36727,7 @@
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>Control matrix cited on MD-00069 for assignment only. Movement/finance proof stays with TR-00069, PO-2025-0012, FA-000069, OFF-00069, APR-00069; exceptions EX-0066, EX-0067.</t>
+          <t>ITAM_control_matrix.png Appendix A disposal row consulted while tracing MD-00069; transactional proof stays with chain row 112.</t>
         </is>
       </c>
     </row>
@@ -36846,7 +36774,7 @@
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>After the chain, MD-00069 is Return Overdue / Remote - Former Employee (Low). EX-0066, EX-0067. OFF-00069. 1ZMD00000069. TR-00069. E0082. PO. PO-2025-0012. FA-000069. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00069: Return Overdue at Remote - Former Employee (Low). EX-0066, EX-0067.</t>
         </is>
       </c>
     </row>
@@ -36893,7 +36821,7 @@
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00070 - PO-2025-0012, $520.</t>
+          <t>Acquisition MD-00070: Dell U2723QE, $520, PO PO-2025-0012.</t>
         </is>
       </c>
     </row>
@@ -36940,7 +36868,7 @@
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows Jun 03, 2026 for TR-00070 (MD-00070).</t>
+          <t>Transfer TR-00070 for MD-00070: posted Jun 03, 2026, inbound 2026-06-03, APR APR-00070.</t>
         </is>
       </c>
     </row>
@@ -36983,7 +36911,7 @@
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00070. Doesn't by itself dock MD-00070.</t>
+          <t>Service desk OFF-00070: Past Due; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00070.</t>
         </is>
       </c>
     </row>
@@ -37069,7 +36997,7 @@
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>Printed 1ZMD00000070. Box not in the inbound file.</t>
+          <t>Prepaid label 1ZMD00000070 for MD-00070 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -37112,7 +37040,7 @@
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00070; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00070; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37079,7 @@
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>Policy PDF + ITAM_control_matrix.png set the transfer bar for MD-00070. Compared that bar to TR-00070, PO-2025-0012, FA-000070, OFF-00070, APR-00070 before accepting any tech note.</t>
+          <t>Policy figure sets financial evidence expectations for MD-00070; chain row 120 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -37198,7 +37126,7 @@
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00070: Return Overdue @ Remote - Former Employee, confidence Low. EX-0068, EX-0069. OFF-00070. 1ZMD00000070. TR-00070. E0083. PO. PO-2025-0012. FA-000070. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00070 remains Return Overdue at Remote - Former Employee; Low. EX-0068, EX-0069.</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37173,7 @@
       </c>
       <c r="I122" s="7" t="inlineStr">
         <is>
-          <t>Bought the Samsung Galaxy S24 ($995) on PO-2025-0012.</t>
+          <t>Vendor shipment for MD-00071 (Samsung Galaxy S24) recorded at $995 on PO-2025-0012.</t>
         </is>
       </c>
     </row>
@@ -37292,7 +37220,7 @@
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00071. Receive date 2026-07-12.</t>
+          <t>Transfer TR-00071 for MD-00071: posted Jul 08, 2026, inbound 2026-07-12, APR APR-00071.</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37263,7 @@
       </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
-          <t>MD-00071 tied to OFF-00071 (Past Due). SLA Jul 15, 2026.</t>
+          <t>Service desk OFF-00071: Past Due; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00071.</t>
         </is>
       </c>
     </row>
@@ -37374,7 +37302,7 @@
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Monitor return - bulky; user delayed pickup. Ref MD-00071.</t>
+          <t>Monitor return — bulky; user delayed pickup. Ref MD-00071.</t>
         </is>
       </c>
     </row>
@@ -37421,7 +37349,7 @@
       </c>
       <c r="I126" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork only. 1ZMD00000071.</t>
+          <t>Prepaid label 1ZMD00000071 for MD-00071 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -37464,7 +37392,7 @@
       </c>
       <c r="I127" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00071; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00071; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37431,7 @@
       </c>
       <c r="I128" s="7" t="inlineStr">
         <is>
-          <t>MD-00071 / Samsung Galaxy S24: assignment evidence expectations from Appendix A. Anchored to TR-00071, PO-2025-0012, FA-000071, OFF-00071, APR-00071; acquisition $995.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00071; cite chain row 128.</t>
         </is>
       </c>
     </row>
@@ -37550,7 +37478,7 @@
       </c>
       <c r="I129" s="7" t="inlineStr">
         <is>
-          <t>Verified Return Overdue for MD-00071 in Remote - Former Employee. Low. EX-0070, EX-0071. OFF-00071. 1ZMD00000071. TR-00071. E0084. PO. PO-2025-0012. FA-000071. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00071 — Return Overdue, site Remote - Former Employee, Low. EX-0070, EX-0071.</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37525,7 @@
       </c>
       <c r="I130" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2025-0012 matches MD-00072 at $6290.</t>
+          <t>Acquisition MD-00072: Cisco C9300, $6290, PO PO-2025-0012.</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37572,7 @@
       </c>
       <c r="I131" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted Jan 18, 2026. Docked 01/18/2026 (TR-00072).</t>
+          <t>Transfer TR-00072 for MD-00072: posted Jan 18, 2026, inbound 2026-01-18, APR APR-00072.</t>
         </is>
       </c>
     </row>
@@ -37687,7 +37615,7 @@
       </c>
       <c r="I132" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00072. Doesn't by itself dock MD-00072.</t>
+          <t>Service desk OFF-00072: Past Due; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00072.</t>
         </is>
       </c>
     </row>
@@ -37773,7 +37701,7 @@
       </c>
       <c r="I134" s="7" t="inlineStr">
         <is>
-          <t>Printed 1ZMD00000072. Box not in the inbound file.</t>
+          <t>Prepaid label 1ZMD00000072 for MD-00072 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -37816,7 +37744,7 @@
       </c>
       <c r="I135" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00072; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00072; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -37855,7 +37783,7 @@
       </c>
       <c r="I136" s="7" t="inlineStr">
         <is>
-          <t>MD-00072 chain includes the figure as a assignment rubric (Low). Record set: TR-00072, PO-2025-0012, FA-000072, OFF-00072, APR-00072.</t>
+          <t>Policy figure sets disposal evidence expectations for MD-00072; chain row 136 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -37902,7 +37830,7 @@
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>Closing MD-00072: Return Overdue at Remote - Former Employee (Low). EX-0072, EX-0073. OFF-00072. 1ZMD00000072. TR-00072. E0085. PO. PO-2025-0012. FA-000072. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00072 remains Return Overdue at Remote - Former Employee; Low. EX-0072, EX-0073.</t>
         </is>
       </c>
     </row>
@@ -37949,7 +37877,7 @@
       </c>
       <c r="I138" s="7" t="inlineStr">
         <is>
-          <t>$1985 Lenovo ThinkPad T14. PO-2022-0013.</t>
+          <t>Vendor shipment for MD-00073 (Lenovo ThinkPad T14) recorded at $1985 on PO-2022-0013.</t>
         </is>
       </c>
     </row>
@@ -37996,7 +37924,7 @@
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>MD-00073 inbound Jan 24, 2026 on TR-00073 / APR-00073.</t>
+          <t>Transfer TR-00073 for MD-00073: posted Jan 21, 2026, inbound 2026-01-24, APR APR-00073.</t>
         </is>
       </c>
     </row>
@@ -38039,7 +37967,7 @@
       </c>
       <c r="I140" s="7" t="inlineStr">
         <is>
-          <t>MD-00073 tied to OFF-00073 (Past Due). SLA 07/15/2026.</t>
+          <t>Service desk OFF-00073: Past Due; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00073.</t>
         </is>
       </c>
     </row>
@@ -38125,7 +38053,7 @@
       </c>
       <c r="I142" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork only. 1ZMD00000073.</t>
+          <t>Prepaid label 1ZMD00000073 for MD-00073 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -38168,7 +38096,7 @@
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00073; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00073; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -38207,7 +38135,7 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>MD-00073 chain includes the figure as a assignment rubric (Low). Record set: TR-00073, PO-2022-0013, FA-000073, OFF-00073, APR-00073.</t>
+          <t>ITAM_control_matrix.png Appendix A disposal row consulted while tracing MD-00073; transactional proof stays with chain row 144.</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38182,7 @@
       </c>
       <c r="I145" s="7" t="inlineStr">
         <is>
-          <t>I am standing on Return Overdue for MD-00073 (Remote - Former Employee, Low). EX-0074, EX-0075. OFF-00073. 1ZMD00000073. TR-00073. E0086. PO. PO-2022-0013. FA-000073. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00073 remains Return Overdue at Remote - Former Employee; Low. EX-0074, EX-0075.</t>
         </is>
       </c>
     </row>
@@ -38301,7 +38229,7 @@
       </c>
       <c r="I146" s="7" t="inlineStr">
         <is>
-          <t>MD-00074 origin: PO-2022-0013, $700.</t>
+          <t>PO PO-2022-0013 covers MD-00074 (Dell U2723QE) for $700.</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38276,7 @@
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00074 completed inbound 2026-02-24.</t>
+          <t>Transfer TR-00074 for MD-00074: posted Feb 23, 2026, inbound 2026-02-24, APR APR-00074.</t>
         </is>
       </c>
     </row>
@@ -38391,7 +38319,7 @@
       </c>
       <c r="I148" s="7" t="inlineStr">
         <is>
-          <t>OFF-00074 sits Past Due. Hardware return was required. Jul 15, 2026.</t>
+          <t>Service desk OFF-00074: Past Due; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00074.</t>
         </is>
       </c>
     </row>
@@ -38477,7 +38405,7 @@
       </c>
       <c r="I150" s="7" t="inlineStr">
         <is>
-          <t>Printed 1ZMD00000074. Box not in the inbound file.</t>
+          <t>Prepaid label 1ZMD00000074 for MD-00074 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -38512,7 +38440,7 @@
       </c>
       <c r="I151" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000074: serial on the shipment is not MD-MO-050074. Custody not cleared.</t>
+          <t>Carrier exception on 1ZMD00000074: inbound serial does not match register MD-MO-050074 for MD-00074.</t>
         </is>
       </c>
     </row>
@@ -38555,7 +38483,7 @@
       </c>
       <c r="I152" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00074; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00074; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -38594,7 +38522,7 @@
       </c>
       <c r="I153" s="7" t="inlineStr">
         <is>
-          <t>Policy PDF + ITAM_control_matrix.png set the transfer bar for MD-00074. Compared that bar to TR-00074, PO-2022-0013, FA-000074, OFF-00074, APR-00074 before accepting any tech note.</t>
+          <t>Policy figure sets financial evidence expectations for MD-00074; chain row 153 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -38641,7 +38569,7 @@
       </c>
       <c r="I154" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00074: Return Overdue (Low) - EX-0076, EX-0077, EX-0078. 1ZMD00000074. OFF-00074. PO. PO-2022-0013. FA-000074. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00074: Return Overdue at Carrier Network / Unverified (Low). EX-0076, EX-0077, EX-0078.</t>
         </is>
       </c>
     </row>
@@ -38688,7 +38616,7 @@
       </c>
       <c r="I155" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00075 (Samsung Galaxy S24) for $1175 via PO-2022-0013.</t>
+          <t>Vendor shipment for MD-00075 (Samsung Galaxy S24) recorded at $1175 on PO-2022-0013.</t>
         </is>
       </c>
     </row>
@@ -38735,7 +38663,7 @@
       </c>
       <c r="I156" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 03/31/2026. Docked 2026-04-01 (TR-00075).</t>
+          <t>Transfer TR-00075 for MD-00075: posted 03/31/2026, inbound Apr 01, 2026, APR APR-00075.</t>
         </is>
       </c>
     </row>
@@ -38778,7 +38706,7 @@
       </c>
       <c r="I157" s="7" t="inlineStr">
         <is>
-          <t>MD-00075 tied to OFF-00075 (Past Due). SLA Jul 15, 2026.</t>
+          <t>Service desk OFF-00075: Past Due; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00075.</t>
         </is>
       </c>
     </row>
@@ -38864,7 +38792,7 @@
       </c>
       <c r="I159" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork only. 1ZMD00000075.</t>
+          <t>Prepaid label 1ZMD00000075 for MD-00075 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -38907,7 +38835,7 @@
       </c>
       <c r="I160" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00075; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00075; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -38946,7 +38874,7 @@
       </c>
       <c r="I161" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00075 should read matrix transfer, then TR-00075, PO-2022-0013, FA-000075, OFF-00075, APR-00075. Working site Remote - Former Employee; status call Return Overdue.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix financial line for MD-00075; cite chain row 161.</t>
         </is>
       </c>
     </row>
@@ -38993,7 +38921,7 @@
       </c>
       <c r="I162" s="7" t="inlineStr">
         <is>
-          <t>MD-00075 → Return Overdue. Confidence Low. EX-0079, EX-0080. OFF-00075. 1ZMD00000075. TR-00075. E0088. PO. PO-2022-0013. FA-000075. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00075 — Return Overdue, site Remote - Former Employee, Low. EX-0079, EX-0080.</t>
         </is>
       </c>
     </row>
@@ -39040,7 +38968,7 @@
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2022-0013 - Cisco C9300.</t>
+          <t>PO PO-2022-0013 covers MD-00076 (Cisco C9300) for $6470.</t>
         </is>
       </c>
     </row>
@@ -39087,7 +39015,7 @@
       </c>
       <c r="I164" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows 05/03/2026 for TR-00076 (MD-00076).</t>
+          <t>Transfer TR-00076 for MD-00076: posted 05/01/2026, inbound May 03, 2026, APR APR-00076.</t>
         </is>
       </c>
     </row>
@@ -39130,7 +39058,7 @@
       </c>
       <c r="I165" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00076. Doesn't by itself dock MD-00076.</t>
+          <t>Service desk OFF-00076: Past Due; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00076.</t>
         </is>
       </c>
     </row>
@@ -39216,7 +39144,7 @@
       </c>
       <c r="I167" s="7" t="inlineStr">
         <is>
-          <t>Printed 1ZMD00000076. Box not in the inbound file.</t>
+          <t>Prepaid label 1ZMD00000076 for MD-00076 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -39251,7 +39179,7 @@
       </c>
       <c r="I168" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000076: serial on the shipment is not MD-NE-050076. Custody not cleared.</t>
+          <t>Carrier exception on 1ZMD00000076: inbound serial does not match register MD-NE-050076 for MD-00076.</t>
         </is>
       </c>
     </row>
@@ -39294,7 +39222,7 @@
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00076; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00076; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -39333,7 +39261,7 @@
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>MD-00076: checked ITAM-001 return row while reviewing TR-00076, PO-2022-0013, FA-000076, OFF-00076, APR-00076. Cost basis $6470; confidence Low. Figure does not replace logs.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix assignment line for MD-00076; cite chain row 170.</t>
         </is>
       </c>
     </row>
@@ -39380,7 +39308,7 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>MD-00076 custody narrative ends Return Overdue (Low). EX-0081, EX-0082, EX-0083. 1ZMD00000076. OFF-00076. PO. PO-2022-0013. FA-000076. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00076: Return Overdue at Carrier Network / Unverified (Low). EX-0081, EX-0082, EX-0083.</t>
         </is>
       </c>
     </row>
@@ -39427,7 +39355,7 @@
       </c>
       <c r="I172" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2022-0013 lists MacBook Pro 14 / $1850.</t>
+          <t>Acquisition MD-00077: MacBook Pro 14, $1850, PO PO-2022-0013.</t>
         </is>
       </c>
     </row>
@@ -39474,7 +39402,7 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>TR-00077 - got it 06/06/2026 at Remote - Former Employee.</t>
+          <t>Transfer TR-00077 for MD-00077: posted 2026-06-05, inbound 06/06/2026, APR APR-00077.</t>
         </is>
       </c>
     </row>
@@ -39517,7 +39445,7 @@
       </c>
       <c r="I174" s="7" t="inlineStr">
         <is>
-          <t>OFF-00077 Past Due. Return required=Yes, due 2026-07-15.</t>
+          <t>Service desk OFF-00077: Past Due; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00077.</t>
         </is>
       </c>
     </row>
@@ -39603,7 +39531,7 @@
       </c>
       <c r="I176" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000077 is Label Created. Serial on the label MD-LA-050077. Not proof of return.</t>
+          <t>Prepaid label 1ZMD00000077 for MD-00077 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -39646,7 +39574,7 @@
       </c>
       <c r="I177" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00077; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00077; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -39685,7 +39613,7 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>Policy PDF + ITAM_control_matrix.png set the transfer bar for MD-00077. Compared that bar to TR-00077, PO-2022-0013, FA-000077, OFF-00077, APR-00077 before accepting any tech note.</t>
+          <t>ITAM_control_matrix.png Appendix A financial row consulted while tracing MD-00077; transactional proof stays with chain row 178.</t>
         </is>
       </c>
     </row>
@@ -39732,7 +39660,7 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00077: Return Overdue (Low) - EX-0084, EX-0085. OFF-00077. 1ZMD00000077. TR-00077. E0090. PO. PO-2022-0013. FA-000077. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00077 — Return Overdue, site Remote - Former Employee, Low. EX-0084, EX-0085.</t>
         </is>
       </c>
     </row>
@@ -39779,7 +39707,7 @@
       </c>
       <c r="I180" s="7" t="inlineStr">
         <is>
-          <t>PO-2022-0013: Dell U2723QE at $565.</t>
+          <t>Vendor shipment for MD-00078 (Dell U2723QE) recorded at $565 on PO-2022-0013.</t>
         </is>
       </c>
     </row>
@@ -39826,7 +39754,7 @@
       </c>
       <c r="I181" s="7" t="inlineStr">
         <is>
-          <t>Remote - Former Employee: TR-00078 received Jan 10, 2026.</t>
+          <t>Transfer TR-00078 for MD-00078: posted 2026-01-10, inbound 01/10/2026, APR APR-00078.</t>
         </is>
       </c>
     </row>
@@ -39869,7 +39797,7 @@
       </c>
       <c r="I182" s="7" t="inlineStr">
         <is>
-          <t>OFF-00078 - Past Due. Due 07/15/2026.</t>
+          <t>Service desk OFF-00078: Past Due; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00078.</t>
         </is>
       </c>
     </row>
@@ -39908,7 +39836,7 @@
       </c>
       <c r="I183" s="7" t="inlineStr">
         <is>
-          <t>Can't close - no delivery event in the carrier file. Ref MD-00078.</t>
+          <t>Can't close — no delivery event in the carrier file. Ref MD-00078.</t>
         </is>
       </c>
     </row>
@@ -39955,7 +39883,7 @@
       </c>
       <c r="I184" s="7" t="inlineStr">
         <is>
-          <t>§5: label ≠ returned. 1ZMD00000078 / MD-MO-050078.</t>
+          <t>Prepaid label 1ZMD00000078 for MD-00078 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -39998,7 +39926,7 @@
       </c>
       <c r="I185" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00078; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00078; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -40037,7 +39965,7 @@
       </c>
       <c r="I186" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00078 should read matrix transfer, then TR-00078, PO-2022-0013, FA-000078, OFF-00078, APR-00078. Working site Remote - Former Employee; status call Return Overdue.</t>
+          <t>ITAM_control_matrix.png Appendix A financial row consulted while tracing MD-00078; transactional proof stays with chain row 186.</t>
         </is>
       </c>
     </row>
@@ -40084,7 +40012,7 @@
       </c>
       <c r="I187" s="7" t="inlineStr">
         <is>
-          <t>MD-00078 → Return Overdue. Confidence Low. EX-0086, EX-0087. OFF-00078. 1ZMD00000078. TR-00078. E0091. PO. PO-2022-0013. FA-000078. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00078 as Return Overdue in Remote - Former Employee; confidence Low. EX-0086, EX-0087.</t>
         </is>
       </c>
     </row>
@@ -40131,7 +40059,7 @@
       </c>
       <c r="I188" s="7" t="inlineStr">
         <is>
-          <t>Bought the Samsung Galaxy S24 ($1040) on PO-2023-0014.</t>
+          <t>PO PO-2023-0014 covers MD-00079 (Samsung Galaxy S24) for $1040.</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40106,7 @@
       </c>
       <c r="I189" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows 2026-02-13 for TR-00079 (MD-00079).</t>
+          <t>Transfer TR-00079 for MD-00079: posted 2026-02-11, inbound 02/13/2026, APR APR-00079.</t>
         </is>
       </c>
     </row>
@@ -40221,7 +40149,7 @@
       </c>
       <c r="I190" s="7" t="inlineStr">
         <is>
-          <t>OFF-00079 Past Due. Return required=Yes, due Jul 15, 2026.</t>
+          <t>Service desk OFF-00079: Past Due; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00079.</t>
         </is>
       </c>
     </row>
@@ -40307,7 +40235,7 @@
       </c>
       <c r="I192" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000079 is Label Created. Serial on the label MD-MO-050079. Not proof of return.</t>
+          <t>Prepaid label 1ZMD00000079 for MD-00079 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -40350,7 +40278,7 @@
       </c>
       <c r="I193" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00079; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00079; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -40389,7 +40317,7 @@
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>ITAM_control_matrix.png consulted for MD-00079 (transfer). Conclusion still tied to TR-00079, PO-2023-0014, FA-000079, OFF-00079, APR-00079 at Remote - Former Employee, $1040.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix financial line for MD-00079; cite chain row 194.</t>
         </is>
       </c>
     </row>
@@ -40436,7 +40364,7 @@
       </c>
       <c r="I195" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00079: Return Overdue @ Remote - Former Employee, confidence Low. EX-0088, EX-0089. OFF-00079. 1ZMD00000079. TR-00079. E0092. PO. PO-2023-0014. FA-000079. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00079: Return Overdue / Remote - Former Employee (Low). EX-0088, EX-0089.</t>
         </is>
       </c>
     </row>
@@ -40483,7 +40411,7 @@
       </c>
       <c r="I196" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2023-0014. Cisco C9300, $6335.</t>
+          <t>Acquisition MD-00080: Cisco C9300, $6335, PO PO-2023-0014.</t>
         </is>
       </c>
     </row>
@@ -40530,7 +40458,7 @@
       </c>
       <c r="I197" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00080 completed inbound 03/17/2026.</t>
+          <t>Transfer TR-00080 for MD-00080: posted 2026-03-16, inbound 03/17/2026, APR APR-00080.</t>
         </is>
       </c>
     </row>
@@ -40573,7 +40501,7 @@
       </c>
       <c r="I198" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00080. Status Shipment Open.</t>
+          <t>Service desk OFF-00080: Shipment Open; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00080.</t>
         </is>
       </c>
     </row>
@@ -40659,7 +40587,7 @@
       </c>
       <c r="I200" s="7" t="inlineStr">
         <is>
-          <t>Label-only on MD-00080. 1ZMD00000080.</t>
+          <t>Prepaid label 1ZMD00000080 for MD-00080 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -40706,7 +40634,7 @@
       </c>
       <c r="I201" s="7" t="inlineStr">
         <is>
-          <t>UPS/carrier take recorded for 1ZMD00000080.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000080.</t>
         </is>
       </c>
     </row>
@@ -40753,7 +40681,7 @@
       </c>
       <c r="I202" s="7" t="inlineStr">
         <is>
-          <t>Carrier delivery event, 1ZMD00000080.</t>
+          <t>Delivery event on 1ZMD00000080; receiving scan still required for MD-00080.</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40728,7 @@
       </c>
       <c r="I203" s="7" t="inlineStr">
         <is>
-          <t>Dock scan on 1ZMD00000080.</t>
+          <t>Receiving scan posted for 1ZMD00000080 (MD-00080).</t>
         </is>
       </c>
     </row>
@@ -40843,7 +40771,7 @@
       </c>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00080 in regional_IT_notes.docx - weight zero.</t>
+          <t>regional_IT_notes.docx checked for MD-00080; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -40882,7 +40810,7 @@
       </c>
       <c r="I205" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure open for MD-00080 transfer path; transactional weight on TR-00080, PO-2023-0014, FA-000080, OFF-00080, APR-00080. Open exceptions EX-0090 still govern certification impact.</t>
+          <t>Matrix financial criteria applied to MD-00080; figure is reference, not inbound proof for chain row 205.</t>
         </is>
       </c>
     </row>
@@ -40929,7 +40857,7 @@
       </c>
       <c r="I206" s="7" t="inlineStr">
         <is>
-          <t>MD-00080 → Available. Confidence High. EX-0090. 1ZMD00000080. OFF-00080. TR-00080. PO. PO-2023-0014. FA-000080. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00080 as Available in Atlanta Warehouse; confidence High. EX-0090.</t>
         </is>
       </c>
     </row>
@@ -40976,7 +40904,7 @@
       </c>
       <c r="I207" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2023-0014 matches MD-00081 at $2030.</t>
+          <t>PO PO-2023-0014 covers MD-00081 (Dell Latitude 7440) for $2030.</t>
         </is>
       </c>
     </row>
@@ -41023,7 +40951,7 @@
       </c>
       <c r="I208" s="7" t="inlineStr">
         <is>
-          <t>Carrier Network: TR-00081 received Apr 20, 2026.</t>
+          <t>Transfer TR-00081 for MD-00081: posted 2026-04-20, inbound 04/20/2026, APR APR-00081.</t>
         </is>
       </c>
     </row>
@@ -41066,7 +40994,7 @@
       </c>
       <c r="I209" s="7" t="inlineStr">
         <is>
-          <t>OFF-00081 Shipment Open. Return required=Yes, due 07/15/2026.</t>
+          <t>Service desk OFF-00081: Shipment Open; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00081.</t>
         </is>
       </c>
     </row>
@@ -41152,7 +41080,7 @@
       </c>
       <c r="I211" s="7" t="inlineStr">
         <is>
-          <t>Prepaid label 1ZMD00000081 exists. Carrier never accepted it.</t>
+          <t>Prepaid label 1ZMD00000081 for MD-00081 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -41199,7 +41127,7 @@
       </c>
       <c r="I212" s="7" t="inlineStr">
         <is>
-          <t>Acceptance event on 1ZMD00000081.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000081.</t>
         </is>
       </c>
     </row>
@@ -41246,7 +41174,7 @@
       </c>
       <c r="I213" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000081 delivered per carrier.</t>
+          <t>Delivery event on 1ZMD00000081; receiving scan still required for MD-00081.</t>
         </is>
       </c>
     </row>
@@ -41293,7 +41221,7 @@
       </c>
       <c r="I214" s="7" t="inlineStr">
         <is>
-          <t>Inbound scan completed (1ZMD00000081).</t>
+          <t>Receiving scan posted for 1ZMD00000081 (MD-00081).</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41264,7 @@
       </c>
       <c r="I215" s="7" t="inlineStr">
         <is>
-          <t>Regional write-up for MD-00081 is non-authoritative per ITAM-001.</t>
+          <t>regional_IT_notes.docx checked for MD-00081; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -41375,7 +41303,7 @@
       </c>
       <c r="I216" s="7" t="inlineStr">
         <is>
-          <t>MD-00081: checked ITAM-001 financial row while reviewing TR-00081, PO-2023-0014, FA-000081, OFF-00081, APR-00081. Cost basis $2030; confidence High. Figure does not replace logs.</t>
+          <t>Matrix return criteria applied to MD-00081; figure is reference, not inbound proof for chain row 216.</t>
         </is>
       </c>
     </row>
@@ -41422,7 +41350,7 @@
       </c>
       <c r="I217" s="7" t="inlineStr">
         <is>
-          <t>After the chain, MD-00081 is Available / Atlanta Warehouse (High). EX-0091. 1ZMD00000081. OFF-00081. TR-00081. PO. PO-2023-0014. FA-000081. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00081 — Available, site Atlanta Warehouse, High. EX-0091.</t>
         </is>
       </c>
     </row>
@@ -41469,7 +41397,7 @@
       </c>
       <c r="I218" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00082 (Dell U2723QE) for $745 via PO-2023-0014.</t>
+          <t>PO PO-2023-0014 covers MD-00082 (Dell U2723QE) for $745.</t>
         </is>
       </c>
     </row>
@@ -41516,7 +41444,7 @@
       </c>
       <c r="I219" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted 05/22/2026. Docked 2026-05-24 (TR-00082).</t>
+          <t>Transfer TR-00082 for MD-00082: posted 2026-05-22, inbound 05/24/2026, APR APR-00082.</t>
         </is>
       </c>
     </row>
@@ -41559,7 +41487,7 @@
       </c>
       <c r="I220" s="7" t="inlineStr">
         <is>
-          <t>OFF-00082 Shipment Open. Return required=Yes, due Jul 15, 2026.</t>
+          <t>Service desk OFF-00082: Shipment Open; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00082.</t>
         </is>
       </c>
     </row>
@@ -41645,7 +41573,7 @@
       </c>
       <c r="I222" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000082 is Label Created. Serial on the label MD-MO-050082. Not proof of return.</t>
+          <t>Prepaid label 1ZMD00000082 for MD-00082 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41620,7 @@
       </c>
       <c r="I223" s="7" t="inlineStr">
         <is>
-          <t>Acceptance posted for 1ZMD00000082; not the same as dock receipt.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000082.</t>
         </is>
       </c>
     </row>
@@ -41727,7 +41655,7 @@
       </c>
       <c r="I224" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000082: serial on the shipment is not MD-MO-050082. Custody not cleared.</t>
+          <t>Carrier exception on 1ZMD00000082: inbound serial does not match register MD-MO-050082 for MD-00082.</t>
         </is>
       </c>
     </row>
@@ -41770,7 +41698,7 @@
       </c>
       <c r="I225" s="7" t="inlineStr">
         <is>
-          <t>Atlanta photo receiving_exception_scan_1ZMD00000082.png shows HOLD / MISMATCH. Lead only - not a receiving clearance for MD-00082.</t>
+          <t>Atlanta photo receiving_exception_scan_1ZMD00000082.png shows HOLD / MISMATCH — lead only, not receiving clearance for MD-00082.</t>
         </is>
       </c>
     </row>
@@ -41813,7 +41741,7 @@
       </c>
       <c r="I226" s="7" t="inlineStr">
         <is>
-          <t>Regional claim (Return package was delivered according to the technician, but the shipment serial does not) does not beat a scan for MD-00082.</t>
+          <t>regional_IT_notes.docx checked for MD-00082; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -41852,7 +41780,7 @@
       </c>
       <c r="I227" s="7" t="inlineStr">
         <is>
-          <t>MD-00082 chain includes the figure as a disposal rubric (Low). Record set: TR-00082, PO-2023-0014, FA-000082, OFF-00082, APR-00082.</t>
+          <t>ITAM_control_matrix.png Appendix A assignment row consulted while tracing MD-00082; transactional proof stays with chain row 227.</t>
         </is>
       </c>
     </row>
@@ -41899,7 +41827,7 @@
       </c>
       <c r="I228" s="7" t="inlineStr">
         <is>
-          <t>Closing MD-00082: In Transit - Exception at Carrier Network / Unverified (Low). EX-0092, EX-0093. 1ZMD00000082. OFF-00082. 1ZMD00000082.png. PO. PO-2023-0014. FA-000082. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00082: In Transit - Exception at Carrier Network / Unverified (Low). EX-0092, EX-0093.</t>
         </is>
       </c>
     </row>
@@ -41946,7 +41874,7 @@
       </c>
       <c r="I229" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2023-0014. Samsung Galaxy S24.</t>
+          <t>PO PO-2023-0014 covers MD-00083 (Samsung Galaxy S24) for $1220.</t>
         </is>
       </c>
     </row>
@@ -41993,7 +41921,7 @@
       </c>
       <c r="I230" s="7" t="inlineStr">
         <is>
-          <t>Assignment posted Jun 26, 2026. Docked 06/27/2026 (TR-00083).</t>
+          <t>Transfer TR-00083 for MD-00083: posted 2026-06-26, inbound 06/27/2026, APR APR-00083.</t>
         </is>
       </c>
     </row>
@@ -42036,7 +41964,7 @@
       </c>
       <c r="I231" s="7" t="inlineStr">
         <is>
-          <t>MD-00083 tied to OFF-00083 (Shipment Open). SLA 2026-07-15.</t>
+          <t>Service desk OFF-00083: Shipment Open; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00083.</t>
         </is>
       </c>
     </row>
@@ -42122,7 +42050,7 @@
       </c>
       <c r="I233" s="7" t="inlineStr">
         <is>
-          <t>Return paperwork only. 1ZMD00000083.</t>
+          <t>Prepaid label 1ZMD00000083 for MD-00083 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -42169,7 +42097,7 @@
       </c>
       <c r="I234" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000083 picked up (acceptance on file).</t>
+          <t>Carrier acceptance recorded on 1ZMD00000083.</t>
         </is>
       </c>
     </row>
@@ -42216,7 +42144,7 @@
       </c>
       <c r="I235" s="7" t="inlineStr">
         <is>
-          <t>Parcel 1ZMD00000083 shows delivered; SCAN-86 still required for MD-00083.</t>
+          <t>Delivery event on 1ZMD00000083; receiving scan still required for MD-00083.</t>
         </is>
       </c>
     </row>
@@ -42263,7 +42191,7 @@
       </c>
       <c r="I236" s="7" t="inlineStr">
         <is>
-          <t>Receiving stamp on 1ZMD00000083 for MD-00083.</t>
+          <t>Receiving scan posted for 1ZMD00000083 (MD-00083).</t>
         </is>
       </c>
     </row>
@@ -42306,7 +42234,7 @@
       </c>
       <c r="I237" s="7" t="inlineStr">
         <is>
-          <t>Technician comment volume in the doc does not clear MD-00083.</t>
+          <t>regional_IT_notes.docx checked for MD-00083; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -42345,7 +42273,7 @@
       </c>
       <c r="I238" s="7" t="inlineStr">
         <is>
-          <t>Policy PDF + ITAM_control_matrix.png set the assignment bar for MD-00083. Compared that bar to TR-00083, PO-2023-0014, FA-000083, OFF-00083, APR-00083 before accepting any tech note.</t>
+          <t>ITAM_control_matrix.png Appendix A disposal row consulted while tracing MD-00083; transactional proof stays with chain row 238.</t>
         </is>
       </c>
     </row>
@@ -42392,7 +42320,7 @@
       </c>
       <c r="I239" s="7" t="inlineStr">
         <is>
-          <t>Verified Available for MD-00083 in Atlanta Warehouse. High. EX-0094. 1ZMD00000083. OFF-00083. TR-00083. PO. PO-2023-0014. FA-000083. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00083 as Available in Atlanta Warehouse; confidence High. EX-0094.</t>
         </is>
       </c>
     </row>
@@ -42439,7 +42367,7 @@
       </c>
       <c r="I240" s="7" t="inlineStr">
         <is>
-          <t>Bought the Cisco C9300 ($6200) on PO-2023-0014.</t>
+          <t>Vendor shipment for MD-00084 (Cisco C9300) recorded at $6200 on PO-2023-0014.</t>
         </is>
       </c>
     </row>
@@ -42486,7 +42414,7 @@
       </c>
       <c r="I241" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00084 / APR-00084. Received Feb 05, 2026.</t>
+          <t>Transfer TR-00084 for MD-00084: posted 2026-01-30, inbound 02/05/2026, APR APR-00084.</t>
         </is>
       </c>
     </row>
@@ -42529,7 +42457,7 @@
       </c>
       <c r="I242" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00084. Status Shipment Open.</t>
+          <t>Service desk OFF-00084: Shipment Open; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00084.</t>
         </is>
       </c>
     </row>
@@ -42615,7 +42543,7 @@
       </c>
       <c r="I244" s="7" t="inlineStr">
         <is>
-          <t>I didn't close MD-00084 on the 1Z print. 1ZMD00000084.</t>
+          <t>Prepaid label 1ZMD00000084 for MD-00084 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -42662,7 +42590,7 @@
       </c>
       <c r="I245" s="7" t="inlineStr">
         <is>
-          <t>Carrier accepted 1ZMD00000084.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000084.</t>
         </is>
       </c>
     </row>
@@ -42697,7 +42625,7 @@
       </c>
       <c r="I246" s="7" t="inlineStr">
         <is>
-          <t>Mismatch inbound. MD-00084 stays exception. 1ZMD00000084.</t>
+          <t>Carrier exception on 1ZMD00000084: inbound serial does not match register MD-NE-050084 for MD-00084.</t>
         </is>
       </c>
     </row>
@@ -42740,7 +42668,7 @@
       </c>
       <c r="I247" s="7" t="inlineStr">
         <is>
-          <t>Word file read; MD-00084 waits on transactional evidence.</t>
+          <t>regional_IT_notes.docx checked for MD-00084; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -42779,7 +42707,7 @@
       </c>
       <c r="I248" s="7" t="inlineStr">
         <is>
-          <t>MD-00084: checked ITAM-001 disposal row while reviewing TR-00084, PO-2023-0014, FA-000084, OFF-00084, APR-00084. Cost basis $6200; confidence Low. Figure does not replace logs.</t>
+          <t>ITAM_control_matrix.png Appendix A assignment row consulted while tracing MD-00084; transactional proof stays with chain row 248.</t>
         </is>
       </c>
     </row>
@@ -42826,7 +42754,7 @@
       </c>
       <c r="I249" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00084: In Transit - Exception @ Carrier Network / Unverified, confidence Low. EX-0095, EX-0096. 1ZMD00000084. OFF-00084. PO. PO-2023-0014. FA-000084. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00084: In Transit - Exception at Carrier Network / Unverified (Low). EX-0095, EX-0096.</t>
         </is>
       </c>
     </row>
@@ -42873,7 +42801,7 @@
       </c>
       <c r="I250" s="7" t="inlineStr">
         <is>
-          <t>Lenovo ThinkPad T14 came in on PO-2024-0015 ($1895).</t>
+          <t>PO PO-2024-0015 covers MD-00085 (Lenovo ThinkPad T14) for $1895.</t>
         </is>
       </c>
     </row>
@@ -42920,7 +42848,7 @@
       </c>
       <c r="I251" s="7" t="inlineStr">
         <is>
-          <t>TR-00085 Feb 02, 2026; inbound 02/03/2026.</t>
+          <t>Transfer TR-00085 for MD-00085: posted 02/02/2026, inbound Feb 03, 2026, APR APR-00085.</t>
         </is>
       </c>
     </row>
@@ -42963,7 +42891,7 @@
       </c>
       <c r="I252" s="7" t="inlineStr">
         <is>
-          <t>OFF-00085 - Shipment Open. Due 2026-07-15.</t>
+          <t>Service desk OFF-00085: Shipment Open; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00085.</t>
         </is>
       </c>
     </row>
@@ -43049,7 +42977,7 @@
       </c>
       <c r="I254" s="7" t="inlineStr">
         <is>
-          <t>§5: label ≠ returned. 1ZMD00000085 / MD-LA-050085.</t>
+          <t>Prepaid label 1ZMD00000085 for MD-00085 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -43096,7 +43024,7 @@
       </c>
       <c r="I255" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000085 picked up (acceptance on file).</t>
+          <t>Carrier acceptance recorded on 1ZMD00000085.</t>
         </is>
       </c>
     </row>
@@ -43143,7 +43071,7 @@
       </c>
       <c r="I256" s="7" t="inlineStr">
         <is>
-          <t>1ZMD00000085 delivered per carrier.</t>
+          <t>Delivery event on 1ZMD00000085; receiving scan still required for MD-00085.</t>
         </is>
       </c>
     </row>
@@ -43190,7 +43118,7 @@
       </c>
       <c r="I257" s="7" t="inlineStr">
         <is>
-          <t>Receiving stamp on 1ZMD00000085 for MD-00085.</t>
+          <t>Receiving scan posted for 1ZMD00000085 (MD-00085).</t>
         </is>
       </c>
     </row>
@@ -43233,7 +43161,7 @@
       </c>
       <c r="I258" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00085; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00085; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -43272,7 +43200,7 @@
       </c>
       <c r="I259" s="7" t="inlineStr">
         <is>
-          <t>MD-00085 / Lenovo ThinkPad T14: assignment evidence expectations from Appendix A. Anchored to TR-00085, PO-2024-0015, FA-000085, OFF-00085, APR-00085; acquisition $1895.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00085; cite chain row 259.</t>
         </is>
       </c>
     </row>
@@ -43319,7 +43247,7 @@
       </c>
       <c r="I260" s="7" t="inlineStr">
         <is>
-          <t>Available is the status for MD-00085 at Atlanta Warehouse; High. EX-0097, EX-0098. 1ZMD00000085. OFF-00085. TR-00085. PO. PO-2024-0015. FA-000085. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00085 as Available in Atlanta Warehouse; confidence High. EX-0097, EX-0098.</t>
         </is>
       </c>
     </row>
@@ -43366,7 +43294,7 @@
       </c>
       <c r="I261" s="7" t="inlineStr">
         <is>
-          <t>PO-2024-0015 documents $610 for Dell U2723QE.</t>
+          <t>Vendor shipment for MD-00086 (Dell U2723QE) recorded at $610 on PO-2024-0015.</t>
         </is>
       </c>
     </row>
@@ -43413,7 +43341,7 @@
       </c>
       <c r="I262" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows Mar 08, 2026 for TR-00086 (MD-00086).</t>
+          <t>Transfer TR-00086 for MD-00086: posted 03/07/2026, inbound Mar 08, 2026, APR APR-00086.</t>
         </is>
       </c>
     </row>
@@ -43456,7 +43384,7 @@
       </c>
       <c r="I263" s="7" t="inlineStr">
         <is>
-          <t>People ticket OFF-00086. Doesn't by itself dock MD-00086.</t>
+          <t>Service desk OFF-00086: Shipment Open; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00086.</t>
         </is>
       </c>
     </row>
@@ -43495,7 +43423,7 @@
       </c>
       <c r="I264" s="7" t="inlineStr">
         <is>
-          <t>Closed the chatter, not the ticket - still no receipt. Ref MD-00086.</t>
+          <t>Closed the chatter, not the ticket — still no receipt. Ref MD-00086.</t>
         </is>
       </c>
     </row>
@@ -43542,7 +43470,7 @@
       </c>
       <c r="I265" s="7" t="inlineStr">
         <is>
-          <t>Printed 1ZMD00000086. Box not in the inbound file.</t>
+          <t>Prepaid label 1ZMD00000086 for MD-00086 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -43589,7 +43517,7 @@
       </c>
       <c r="I266" s="7" t="inlineStr">
         <is>
-          <t>Carrier accepted 1ZMD00000086.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000086.</t>
         </is>
       </c>
     </row>
@@ -43636,7 +43564,7 @@
       </c>
       <c r="I267" s="7" t="inlineStr">
         <is>
-          <t>Delivery posted on 1ZMD00000086.</t>
+          <t>Delivery event on 1ZMD00000086; receiving scan still required for MD-00086.</t>
         </is>
       </c>
     </row>
@@ -43683,7 +43611,7 @@
       </c>
       <c r="I268" s="7" t="inlineStr">
         <is>
-          <t>SCAN-86 equivalent on file for 1ZMD00000086.</t>
+          <t>Receiving scan posted for 1ZMD00000086 (MD-00086).</t>
         </is>
       </c>
     </row>
@@ -43726,7 +43654,7 @@
       </c>
       <c r="I269" s="7" t="inlineStr">
         <is>
-          <t>Regional file reviewed for MD-00086; no clearance language accepted.</t>
+          <t>regional_IT_notes.docx checked for MD-00086; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -43765,7 +43693,7 @@
       </c>
       <c r="I270" s="7" t="inlineStr">
         <is>
-          <t>Control matrix cited on MD-00086 for financial only. Movement/finance proof stays with TR-00086, PO-2024-0015, FA-000086, OFF-00086, APR-00086; exceptions EX-0099.</t>
+          <t>ITAM_control_matrix.png Appendix A return row consulted while tracing MD-00086; transactional proof stays with chain row 270.</t>
         </is>
       </c>
     </row>
@@ -43812,7 +43740,7 @@
       </c>
       <c r="I271" s="7" t="inlineStr">
         <is>
-          <t>Chain end MD-00086: Available; High; EX-0099. 1ZMD00000086. OFF-00086. TR-00086. PO. PO-2024-0015. FA-000086. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00086 — Available, site Atlanta Warehouse, High. EX-0099.</t>
         </is>
       </c>
     </row>
@@ -43859,7 +43787,7 @@
       </c>
       <c r="I272" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2024-0015 matches MD-00087 at $1085.</t>
+          <t>Vendor shipment for MD-00087 (Samsung Galaxy S24) recorded at $1085 on PO-2024-0015.</t>
         </is>
       </c>
     </row>
@@ -43906,7 +43834,7 @@
       </c>
       <c r="I273" s="7" t="inlineStr">
         <is>
-          <t>MD-00087 inbound 2026-04-12 on TR-00087 / APR-00087.</t>
+          <t>Transfer TR-00087 for MD-00087: posted 04/12/2026, inbound Apr 12, 2026, APR APR-00087.</t>
         </is>
       </c>
     </row>
@@ -43949,7 +43877,7 @@
       </c>
       <c r="I274" s="7" t="inlineStr">
         <is>
-          <t>OFF-00087 sits Shipment Open. Hardware return was required. Jul 15, 2026.</t>
+          <t>Service desk OFF-00087: Shipment Open; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00087.</t>
         </is>
       </c>
     </row>
@@ -44035,7 +43963,7 @@
       </c>
       <c r="I276" s="7" t="inlineStr">
         <is>
-          <t>Label-only on MD-00087. 1ZMD00000087.</t>
+          <t>Prepaid label 1ZMD00000087 for MD-00087 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -44082,7 +44010,7 @@
       </c>
       <c r="I277" s="7" t="inlineStr">
         <is>
-          <t>UPS/carrier take recorded for 1ZMD00000087.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000087.</t>
         </is>
       </c>
     </row>
@@ -44129,7 +44057,7 @@
       </c>
       <c r="I278" s="7" t="inlineStr">
         <is>
-          <t>Parcel 1ZMD00000087 shows delivered; SCAN-86 still required for MD-00087.</t>
+          <t>Delivery event on 1ZMD00000087; receiving scan still required for MD-00087.</t>
         </is>
       </c>
     </row>
@@ -44176,7 +44104,7 @@
       </c>
       <c r="I279" s="7" t="inlineStr">
         <is>
-          <t>Dock scan on 1ZMD00000087.</t>
+          <t>Receiving scan posted for 1ZMD00000087 (MD-00087).</t>
         </is>
       </c>
     </row>
@@ -44219,7 +44147,7 @@
       </c>
       <c r="I280" s="7" t="inlineStr">
         <is>
-          <t>Could not tie MD-00087 to a verified RN entry in the notes.</t>
+          <t>regional_IT_notes.docx checked for MD-00087; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -44258,7 +44186,7 @@
       </c>
       <c r="I281" s="7" t="inlineStr">
         <is>
-          <t>For MD-00087 (Samsung Galaxy S24), Appendix A return criteria were read against TR-00087, PO-2024-0015, FA-000087, OFF-00087, APR-00087. Verified status target Available at Atlanta Warehouse; matrix PNG is reference only.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix assignment line for MD-00087; cite chain row 281.</t>
         </is>
       </c>
     </row>
@@ -44305,7 +44233,7 @@
       </c>
       <c r="I282" s="7" t="inlineStr">
         <is>
-          <t>I am standing on Available for MD-00087 (Atlanta Warehouse, High). EX-0100. 1ZMD00000087. OFF-00087. TR-00087. PO. PO-2024-0015. FA-000087. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00087: Available / Atlanta Warehouse (High). EX-0100.</t>
         </is>
       </c>
     </row>
@@ -44352,7 +44280,7 @@
       </c>
       <c r="I283" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00088 (Cisco C9300) for $6380 via PO-2024-0015.</t>
+          <t>Acquisition MD-00088: Cisco C9300, $6380, PO PO-2024-0015.</t>
         </is>
       </c>
     </row>
@@ -44399,7 +44327,7 @@
       </c>
       <c r="I284" s="7" t="inlineStr">
         <is>
-          <t>Recorded May 13, 2026, received 05/14/2026. TR-00088.</t>
+          <t>Transfer TR-00088 for MD-00088: posted 05/13/2026, inbound May 14, 2026, APR APR-00088.</t>
         </is>
       </c>
     </row>
@@ -44442,7 +44370,7 @@
       </c>
       <c r="I285" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00088: Yes. Due 2026-07-15.</t>
+          <t>Service desk OFF-00088: Shipment Open; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00088.</t>
         </is>
       </c>
     </row>
@@ -44528,7 +44456,7 @@
       </c>
       <c r="I287" s="7" t="inlineStr">
         <is>
-          <t>Prepaid label 1ZMD00000088 exists. Carrier never accepted it.</t>
+          <t>Prepaid label 1ZMD00000088 for MD-00088 — Label Created only; not a return clearance.</t>
         </is>
       </c>
     </row>
@@ -44575,7 +44503,7 @@
       </c>
       <c r="I288" s="7" t="inlineStr">
         <is>
-          <t>Acceptance event on 1ZMD00000088.</t>
+          <t>Carrier acceptance recorded on 1ZMD00000088.</t>
         </is>
       </c>
     </row>
@@ -44622,7 +44550,7 @@
       </c>
       <c r="I289" s="7" t="inlineStr">
         <is>
-          <t>Delivered - 1ZMD00000088. Still need a receiving scan to finish returns.</t>
+          <t>Delivery event on 1ZMD00000088; receiving scan still required for MD-00088.</t>
         </is>
       </c>
     </row>
@@ -44669,7 +44597,7 @@
       </c>
       <c r="I290" s="7" t="inlineStr">
         <is>
-          <t>Receiving stamp on 1ZMD00000088 for MD-00088.</t>
+          <t>Receiving scan posted for 1ZMD00000088 (MD-00088).</t>
         </is>
       </c>
     </row>
@@ -44712,7 +44640,7 @@
       </c>
       <c r="I291" s="7" t="inlineStr">
         <is>
-          <t>Looked for MD-00088 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
+          <t>regional_IT_notes.docx checked for MD-00088; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -44751,7 +44679,7 @@
       </c>
       <c r="I292" s="7" t="inlineStr">
         <is>
-          <t>Control matrix cited on MD-00088 for assignment only. Movement/finance proof stays with TR-00088, PO-2024-0015, FA-000088, OFF-00088, APR-00088; exceptions EX-0101, EX-0102.</t>
+          <t>Matrix disposal criteria applied to MD-00088; figure is reference, not inbound proof for chain row 292.</t>
         </is>
       </c>
     </row>
@@ -44798,7 +44726,7 @@
       </c>
       <c r="I293" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00088: Available @ Atlanta Warehouse, confidence Medium. EX-0101, EX-0102. 1ZMD00000088. OFF-00088. TR-00088. PO. PO-2024-0015. FA-000088. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00088 remains Available at Atlanta Warehouse; Medium. EX-0101, EX-0102.</t>
         </is>
       </c>
     </row>
@@ -44845,7 +44773,7 @@
       </c>
       <c r="I294" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2024-0015. MacBook Pro 14.</t>
+          <t>PO PO-2024-0015 covers MD-00089 (MacBook Pro 14) for $2075.</t>
         </is>
       </c>
     </row>
@@ -44892,7 +44820,7 @@
       </c>
       <c r="I295" s="7" t="inlineStr">
         <is>
-          <t>TR-00089 - got it Jun 17, 2026 at Unknown.</t>
+          <t>Transfer TR-00089 for MD-00089: posted 06/17/2026, inbound Jun 17, 2026, APR APR-00089.</t>
         </is>
       </c>
     </row>
@@ -44935,7 +44863,7 @@
       </c>
       <c r="I296" s="7" t="inlineStr">
         <is>
-          <t>OFF-00089 Unresolved. Return required=Yes, due 07/15/2026.</t>
+          <t>Service desk OFF-00089: Unresolved; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00089.</t>
         </is>
       </c>
     </row>
@@ -45017,7 +44945,7 @@
       </c>
       <c r="I298" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions During the Denver exit walkthrough, someone mentioned a locked cage on floor 3 might still - lead only for MD-00089.</t>
+          <t>regional_IT_notes.docx checked for MD-00089; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -45056,7 +44984,7 @@
       </c>
       <c r="I299" s="7" t="inlineStr">
         <is>
-          <t>Unknown custody review for MD-00089 used the transfer column on the matrix. Source trail: TR-00089, PO-2024-0015, FA-000089, OFF-00089, APR-00089.</t>
+          <t>Matrix transfer criteria applied to MD-00089; figure is reference, not inbound proof for chain row 299.</t>
         </is>
       </c>
     </row>
@@ -45091,7 +45019,7 @@
       </c>
       <c r="I300" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00089.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00089; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -45138,7 +45066,7 @@
       </c>
       <c r="I301" s="7" t="inlineStr">
         <is>
-          <t>MD-00089 → Missing. Confidence Low. EX-0103, EX-0104. OFF-00089. TR-00089. PO. PO-2024-0015. FA-000089. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00089 as Missing in Unknown; confidence Low. EX-0103, EX-0104.</t>
         </is>
       </c>
     </row>
@@ -45185,7 +45113,7 @@
       </c>
       <c r="I302" s="7" t="inlineStr">
         <is>
-          <t>PO line PO-2024-0015 - Dell U2723QE.</t>
+          <t>Acquisition MD-00090: Dell U2723QE, $790, PO PO-2024-0015.</t>
         </is>
       </c>
     </row>
@@ -45232,7 +45160,7 @@
       </c>
       <c r="I303" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00090 / APR-00090. Received 2026-01-28.</t>
+          <t>Transfer TR-00090 for MD-00090: posted 01/22/2026, inbound Jan 28, 2026, APR APR-00090.</t>
         </is>
       </c>
     </row>
@@ -45275,7 +45203,7 @@
       </c>
       <c r="I304" s="7" t="inlineStr">
         <is>
-          <t>OFF-00090 sits Unresolved. Hardware return was required. Jul 15, 2026.</t>
+          <t>Service desk OFF-00090: Unresolved; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00090.</t>
         </is>
       </c>
     </row>
@@ -45357,7 +45285,7 @@
       </c>
       <c r="I306" s="7" t="inlineStr">
         <is>
-          <t>Technician wrote about MD-00090 in regional_IT_notes.docx; treated as unverified.</t>
+          <t>regional_IT_notes.docx checked for MD-00090; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -45396,7 +45324,7 @@
       </c>
       <c r="I307" s="7" t="inlineStr">
         <is>
-          <t>Unknown custody review for MD-00090 used the disposal column on the matrix. Source trail: TR-00090, PO-2024-0015, FA-000090, OFF-00090, APR-00090.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00090; cite chain row 307.</t>
         </is>
       </c>
     </row>
@@ -45431,7 +45359,7 @@
       </c>
       <c r="I308" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00090.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00090; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -45478,7 +45406,7 @@
       </c>
       <c r="I309" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00090 - Missing, site Unknown, Low. EX-0105, EX-0106. OFF-00090. TR-00090. PO. PO-2024-0015. FA-000090. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00090 remains Missing at Unknown; Low. EX-0105, EX-0106.</t>
         </is>
       </c>
     </row>
@@ -45525,7 +45453,7 @@
       </c>
       <c r="I310" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2025-0016 matches MD-00091 at $950.</t>
+          <t>Acquisition MD-00091: Samsung Galaxy S24, $950, PO PO-2025-0016.</t>
         </is>
       </c>
     </row>
@@ -45572,7 +45500,7 @@
       </c>
       <c r="I311" s="7" t="inlineStr">
         <is>
-          <t>MD-00091 inbound 02/24/2026 on TR-00091 / APR-00091.</t>
+          <t>Transfer TR-00091 for MD-00091: posted 02/23/2026, inbound Feb 24, 2026, APR APR-00091.</t>
         </is>
       </c>
     </row>
@@ -45615,7 +45543,7 @@
       </c>
       <c r="I312" s="7" t="inlineStr">
         <is>
-          <t>Opened OFF-00091. Status Unresolved.</t>
+          <t>Service desk OFF-00091: Unresolved; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00091.</t>
         </is>
       </c>
     </row>
@@ -45697,7 +45625,7 @@
       </c>
       <c r="I314" s="7" t="inlineStr">
         <is>
-          <t>Technician wrote about MD-00091 in regional_IT_notes.docx; treated as unverified.</t>
+          <t>regional_IT_notes.docx checked for MD-00091; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -45736,7 +45664,7 @@
       </c>
       <c r="I315" s="7" t="inlineStr">
         <is>
-          <t>Control matrix cited on MD-00091 for disposal only. Movement/finance proof stays with TR-00091, PO-2025-0016, FA-000091, OFF-00091, APR-00091; exceptions EX-0107, EX-0108.</t>
+          <t>Policy figure sets disposal evidence expectations for MD-00091; chain row 315 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -45771,7 +45699,7 @@
       </c>
       <c r="I316" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00091.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00091; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -45818,7 +45746,7 @@
       </c>
       <c r="I317" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00091: Missing @ Unknown, confidence Low. EX-0107, EX-0108. OFF-00091. TR-00091. PO. PO-2025-0016. FA-000091. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00091: Missing / Unknown (Low). EX-0107, EX-0108.</t>
         </is>
       </c>
     </row>
@@ -45865,7 +45793,7 @@
       </c>
       <c r="I318" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2025-0016 lists Cisco C9300 / $6245.</t>
+          <t>PO PO-2025-0016 covers MD-00092 (Cisco C9300) for $6245.</t>
         </is>
       </c>
     </row>
@@ -45912,7 +45840,7 @@
       </c>
       <c r="I319" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Unverified. TR-00092, received Mar 28, 2026.</t>
+          <t>Transfer TR-00092 for MD-00092: posted 03/28/2026, inbound Mar 28, 2026, APR APR-00092.</t>
         </is>
       </c>
     </row>
@@ -45955,7 +45883,7 @@
       </c>
       <c r="I320" s="7" t="inlineStr">
         <is>
-          <t>OFF-00092 sits Unresolved. Hardware return was required. 07/15/2026.</t>
+          <t>Service desk OFF-00092: Unresolved; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00092.</t>
         </is>
       </c>
     </row>
@@ -46037,7 +45965,7 @@
       </c>
       <c r="I322" s="7" t="inlineStr">
         <is>
-          <t>Technician wrote about MD-00092 in regional_IT_notes.docx; treated as unverified.</t>
+          <t>regional_IT_notes.docx checked for MD-00092; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -46076,7 +46004,7 @@
       </c>
       <c r="I323" s="7" t="inlineStr">
         <is>
-          <t>For MD-00092 (Cisco C9300), Appendix A disposal criteria were read against TR-00092, PO-2025-0016, FA-000092, OFF-00092, APR-00092. Verified status target Missing at Unknown; matrix PNG is reference only.</t>
+          <t>ITAM_control_matrix.png Appendix A disposal row consulted while tracing MD-00092; transactional proof stays with chain row 323.</t>
         </is>
       </c>
     </row>
@@ -46111,7 +46039,7 @@
       </c>
       <c r="I324" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00092.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00092; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -46158,7 +46086,7 @@
       </c>
       <c r="I325" s="7" t="inlineStr">
         <is>
-          <t>Chain end MD-00092: Missing; Low; EX-0109, EX-0110, EX-0111. OFF-00092. TR-00092. PO. PO-2025-0016. FA-000092. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00092 — Missing, site Unknown, Low. EX-0109, EX-0110, EX-0111.</t>
         </is>
       </c>
     </row>
@@ -46205,7 +46133,7 @@
       </c>
       <c r="I326" s="7" t="inlineStr">
         <is>
-          <t>PO-2025-0016: Dell Latitude 7440 at $1940.</t>
+          <t>Acquisition MD-00093: Dell Latitude 7440, $1940, PO PO-2025-0016.</t>
         </is>
       </c>
     </row>
@@ -46252,7 +46180,7 @@
       </c>
       <c r="I327" s="7" t="inlineStr">
         <is>
-          <t>Moved to Unverified in Unknown on TR-00093. Received 2026-05-06.</t>
+          <t>Transfer TR-00093 for MD-00093: posted 05/02/2026, inbound May 06, 2026, APR APR-00093.</t>
         </is>
       </c>
     </row>
@@ -46295,7 +46223,7 @@
       </c>
       <c r="I328" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00093 on MD-00093. Return required Yes.</t>
+          <t>Service desk OFF-00093: Unresolved; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00093.</t>
         </is>
       </c>
     </row>
@@ -46377,7 +46305,7 @@
       </c>
       <c r="I330" s="7" t="inlineStr">
         <is>
-          <t>Technician wrote about MD-00093 in regional_IT_notes.docx; treated as unverified.</t>
+          <t>regional_IT_notes.docx checked for MD-00093; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -46416,7 +46344,7 @@
       </c>
       <c r="I331" s="7" t="inlineStr">
         <is>
-          <t>Unknown custody review for MD-00093 used the disposal column on the matrix. Source trail: TR-00093, PO-2025-0016, FA-000093, OFF-00093, APR-00093.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00093; cite chain row 331.</t>
         </is>
       </c>
     </row>
@@ -46451,7 +46379,7 @@
       </c>
       <c r="I332" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00093.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00093; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -46498,7 +46426,7 @@
       </c>
       <c r="I333" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00093: Missing (Low) - EX-0112, EX-0113. OFF-00093. TR-00093. PO. PO-2025-0016. FA-000093. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00093: Missing / Unknown (Low). EX-0112, EX-0113.</t>
         </is>
       </c>
     </row>
@@ -46545,7 +46473,7 @@
       </c>
       <c r="I334" s="7" t="inlineStr">
         <is>
-          <t>Dell U2723QE came in on PO-2025-0016 ($655).</t>
+          <t>Vendor shipment for MD-00094 (Dell U2723QE) recorded at $655 on PO-2025-0016.</t>
         </is>
       </c>
     </row>
@@ -46592,7 +46520,7 @@
       </c>
       <c r="I335" s="7" t="inlineStr">
         <is>
-          <t>Recorded Jun 03, 2026, received 06/04/2026. TR-00094.</t>
+          <t>Transfer TR-00094 for MD-00094: posted 06/03/2026, inbound Jun 04, 2026, APR APR-00094.</t>
         </is>
       </c>
     </row>
@@ -46635,7 +46563,7 @@
       </c>
       <c r="I336" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00094: Yes. Due 2026-07-15.</t>
+          <t>Service desk OFF-00094: Unresolved; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00094.</t>
         </is>
       </c>
     </row>
@@ -46717,7 +46645,7 @@
       </c>
       <c r="I338" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00094: "IT float pool chat referenced this asset as 'still at closed site.' Chat is not an approva" - not authoritative.</t>
+          <t>regional_IT_notes.docx checked for MD-00094; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -46756,7 +46684,7 @@
       </c>
       <c r="I339" s="7" t="inlineStr">
         <is>
-          <t>MD-00094 / Dell U2723QE: return evidence expectations from Appendix A. Anchored to TR-00094, PO-2025-0016, FA-000094, OFF-00094, APR-00094; acquisition $655.</t>
+          <t>ITAM_control_matrix.png Appendix A return row consulted while tracing MD-00094; transactional proof stays with chain row 339.</t>
         </is>
       </c>
     </row>
@@ -46791,7 +46719,7 @@
       </c>
       <c r="I340" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00094.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00094; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -46838,7 +46766,7 @@
       </c>
       <c r="I341" s="7" t="inlineStr">
         <is>
-          <t>Call on MD-00094: Missing, Low. EX-0114, EX-0115. OFF-00094. TR-00094. PO. PO-2025-0016. FA-000094. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00094: Missing / Unknown (Low). EX-0114, EX-0115.</t>
         </is>
       </c>
     </row>
@@ -46885,7 +46813,7 @@
       </c>
       <c r="I342" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2025-0016 lists Samsung Galaxy S24 / $1130.</t>
+          <t>PO PO-2025-0016 covers MD-00095 (Samsung Galaxy S24) for $1130.</t>
         </is>
       </c>
     </row>
@@ -46932,7 +46860,7 @@
       </c>
       <c r="I343" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Unverified. TR-00095, received Jul 08, 2026.</t>
+          <t>Transfer TR-00095 for MD-00095: posted 07/08/2026, inbound Jul 08, 2026, APR APR-00095.</t>
         </is>
       </c>
     </row>
@@ -46975,7 +46903,7 @@
       </c>
       <c r="I344" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00095 on MD-00095. Return required Yes.</t>
+          <t>Service desk OFF-00095: Unresolved; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00095.</t>
         </is>
       </c>
     </row>
@@ -47057,7 +46985,7 @@
       </c>
       <c r="I346" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00095: "Vendor teardown crew said they saw a similar model on a pallet marked scrap hold. Asset ta" - not authoritative.</t>
+          <t>regional_IT_notes.docx checked for MD-00095; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -47096,7 +47024,7 @@
       </c>
       <c r="I347" s="7" t="inlineStr">
         <is>
-          <t>MD-00095 chain includes the figure as a return rubric (Low). Record set: TR-00095, PO-2025-0016, FA-000095, OFF-00095, APR-00095.</t>
+          <t>Matrix return criteria applied to MD-00095; figure is reference, not inbound proof for chain row 347.</t>
         </is>
       </c>
     </row>
@@ -47131,7 +47059,7 @@
       </c>
       <c r="I348" s="7" t="inlineStr">
         <is>
-          <t>Unresolved. MD-00095 isn't in inbound or the cert file.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00095; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -47178,7 +47106,7 @@
       </c>
       <c r="I349" s="7" t="inlineStr">
         <is>
-          <t>Closing MD-00095: Missing at Unknown (Low). EX-0116, EX-0117. OFF-00095. TR-00095. PO. PO-2025-0016. FA-000095. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00095 as Missing in Unknown; confidence Low. EX-0116, EX-0117.</t>
         </is>
       </c>
     </row>
@@ -47225,7 +47153,7 @@
       </c>
       <c r="I350" s="7" t="inlineStr">
         <is>
-          <t>PO-2025-0016: Cisco C9300 at $6425.</t>
+          <t>PO PO-2025-0016 covers MD-00096 (Cisco C9300) for $6425.</t>
         </is>
       </c>
     </row>
@@ -47272,7 +47200,7 @@
       </c>
       <c r="I351" s="7" t="inlineStr">
         <is>
-          <t>Moved to Unverified in Unknown on TR-00096. Received 2026-01-19.</t>
+          <t>Transfer TR-00096 for MD-00096: posted 01/18/2026, inbound Jan 19, 2026, APR APR-00096.</t>
         </is>
       </c>
     </row>
@@ -47315,7 +47243,7 @@
       </c>
       <c r="I352" s="7" t="inlineStr">
         <is>
-          <t>Offboarding OFF-00096: Yes. Due Jul 15, 2026.</t>
+          <t>Service desk OFF-00096: Unresolved; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00096.</t>
         </is>
       </c>
     </row>
@@ -47354,7 +47282,7 @@
       </c>
       <c r="I353" s="7" t="inlineStr">
         <is>
-          <t>Walkthrough photo of a cage - tag not readable. Still unresolved. Ref MD-00096.</t>
+          <t>Walkthrough photo of a cage — tag not readable. Still unresolved. Ref MD-00096.</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47325,7 @@
       </c>
       <c r="I354" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00096: "Helpdesk comment claims the user dropped it with building security before last day. Securi" - not authoritative.</t>
+          <t>regional_IT_notes.docx checked for MD-00096; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -47436,7 +47364,7 @@
       </c>
       <c r="I355" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure open for MD-00096 return path; transactional weight on TR-00096, PO-2025-0016, FA-000096, OFF-00096, APR-00096. Open exceptions EX-0118, EX-0119 still govern certification impact.</t>
+          <t>Policy figure sets return evidence expectations for MD-00096; chain row 355 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -47471,7 +47399,7 @@
       </c>
       <c r="I356" s="7" t="inlineStr">
         <is>
-          <t>Unresolved. MD-00096 isn't in inbound or the cert file.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00096; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -47518,7 +47446,7 @@
       </c>
       <c r="I357" s="7" t="inlineStr">
         <is>
-          <t>MD-00096 custody narrative ends Missing (Low). EX-0118, EX-0119. OFF-00096. TR-00096. PO. PO-2025-0016. FA-000096. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00096 remains Missing at Unknown; Low. EX-0118, EX-0119.</t>
         </is>
       </c>
     </row>
@@ -47565,7 +47493,7 @@
       </c>
       <c r="I358" s="7" t="inlineStr">
         <is>
-          <t>Ordered Lenovo ThinkPad T14 (MD-00097) on PO-2022-0017; $2120.</t>
+          <t>Acquisition MD-00097: Lenovo ThinkPad T14, $2120, PO PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -47612,7 +47540,7 @@
       </c>
       <c r="I359" s="7" t="inlineStr">
         <is>
-          <t>TR-00097 - got it 01/27/2026 at Unknown.</t>
+          <t>Transfer TR-00097 for MD-00097: posted 01/21/2026, inbound Jan 27, 2026, APR APR-00097.</t>
         </is>
       </c>
     </row>
@@ -47655,7 +47583,7 @@
       </c>
       <c r="I360" s="7" t="inlineStr">
         <is>
-          <t>Service desk OFF-00097 on MD-00097. Return required Yes.</t>
+          <t>Service desk OFF-00097: Unresolved; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00097.</t>
         </is>
       </c>
     </row>
@@ -47737,7 +47665,7 @@
       </c>
       <c r="I362" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00097: "Regional spare inventory spreadsheet (offline) listed a placeholder row for this tag with " - not authoritative.</t>
+          <t>regional_IT_notes.docx checked for MD-00097; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -47776,7 +47704,7 @@
       </c>
       <c r="I363" s="7" t="inlineStr">
         <is>
-          <t>Matrix figure open for MD-00097 return path; transactional weight on TR-00097, PO-2022-0017, FA-000097, OFF-00097, APR-00097. Open exceptions EX-0120, EX-0121 still govern certification impact.</t>
+          <t>Matrix return criteria applied to MD-00097; figure is reference, not inbound proof for chain row 363.</t>
         </is>
       </c>
     </row>
@@ -47811,7 +47739,7 @@
       </c>
       <c r="I364" s="7" t="inlineStr">
         <is>
-          <t>Unresolved. MD-00097 isn't in inbound or the cert file.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00097; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -47858,7 +47786,7 @@
       </c>
       <c r="I365" s="7" t="inlineStr">
         <is>
-          <t>I am standing on Missing for MD-00097 (Unknown, Low). EX-0120, EX-0121. OFF-00097. TR-00097. PO. PO-2022-0017. FA-000097. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00097: Missing / Unknown (Low). EX-0120, EX-0121.</t>
         </is>
       </c>
     </row>
@@ -47905,7 +47833,7 @@
       </c>
       <c r="I366" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2022-0017. Dell U2723QE, $520.</t>
+          <t>Acquisition MD-00098: Dell U2723QE, $520, PO PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -47952,7 +47880,7 @@
       </c>
       <c r="I367" s="7" t="inlineStr">
         <is>
-          <t>Unknown: TR-00098 received Feb 24, 2026.</t>
+          <t>Transfer TR-00098 for MD-00098: posted 02/23/2026, inbound Feb 24, 2026, APR APR-00098.</t>
         </is>
       </c>
     </row>
@@ -47995,7 +47923,7 @@
       </c>
       <c r="I368" s="7" t="inlineStr">
         <is>
-          <t>OFF-00098 Unresolved. Return required=Yes, due 07/15/2026.</t>
+          <t>Service desk OFF-00098: Unresolved; return required Yes; due 07/15/2026. Ticket alone does not dock MD-00098.</t>
         </is>
       </c>
     </row>
@@ -48077,7 +48005,7 @@
       </c>
       <c r="I370" s="7" t="inlineStr">
         <is>
-          <t>Word-file breadcrumb on MD-00098: "Move captain's email guessed the device rode with furniture to storage. Furniture BOL does" - not authoritative.</t>
+          <t>regional_IT_notes.docx checked for MD-00098; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -48116,7 +48044,7 @@
       </c>
       <c r="I371" s="7" t="inlineStr">
         <is>
-          <t>MD-00098 / Dell U2723QE: return evidence expectations from Appendix A. Anchored to TR-00098, PO-2022-0017, FA-000098, OFF-00098, APR-00098; acquisition $520.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix return line for MD-00098; cite chain row 371.</t>
         </is>
       </c>
     </row>
@@ -48151,7 +48079,7 @@
       </c>
       <c r="I372" s="7" t="inlineStr">
         <is>
-          <t>Unresolved. MD-00098 isn't in inbound or the cert file.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00098; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -48198,7 +48126,7 @@
       </c>
       <c r="I373" s="7" t="inlineStr">
         <is>
-          <t>Missing is the status for MD-00098 at Unknown; Low. EX-0122, EX-0123. OFF-00098. TR-00098. PO. PO-2022-0017. FA-000098. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00098 — Missing, site Unknown, Low. EX-0122, EX-0123.</t>
         </is>
       </c>
     </row>
@@ -48245,7 +48173,7 @@
       </c>
       <c r="I374" s="7" t="inlineStr">
         <is>
-          <t>Warehouse receipt tied to PO-2022-0017. Samsung Galaxy S24.</t>
+          <t>Vendor shipment for MD-00099 (Samsung Galaxy S24) recorded at $995 on PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -48292,7 +48220,7 @@
       </c>
       <c r="I375" s="7" t="inlineStr">
         <is>
-          <t>TR-00099 03/31/2026; inbound 2026-04-02.</t>
+          <t>Transfer TR-00099 for MD-00099: posted 03/31/2026, inbound Apr 02, 2026, APR APR-00099.</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48263,7 @@
       </c>
       <c r="I376" s="7" t="inlineStr">
         <is>
-          <t>OFF-00099 - Unresolved. Due Jul 15, 2026.</t>
+          <t>Service desk OFF-00099: Unresolved; return required Yes; due Jul 15, 2026. Ticket alone does not dock MD-00099.</t>
         </is>
       </c>
     </row>
@@ -48417,7 +48345,7 @@
       </c>
       <c r="I378" s="7" t="inlineStr">
         <is>
-          <t>regional_IT_notes.docx mentions An intern's handwritten punch list includes this tag under 'find later.' No follow-up work - lead only for MD-00099.</t>
+          <t>regional_IT_notes.docx checked for MD-00099; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -48456,7 +48384,7 @@
       </c>
       <c r="I379" s="7" t="inlineStr">
         <is>
-          <t>Control matrix cited on MD-00099 for transfer only. Movement/finance proof stays with TR-00099, PO-2022-0017, FA-000099, OFF-00099, APR-00099; exceptions EX-0124, EX-0125.</t>
+          <t>Matrix transfer criteria applied to MD-00099; figure is reference, not inbound proof for chain row 379.</t>
         </is>
       </c>
     </row>
@@ -48491,7 +48419,7 @@
       </c>
       <c r="I380" s="7" t="inlineStr">
         <is>
-          <t>Unresolved. MD-00099 isn't in inbound or the cert file.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00099; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -48538,7 +48466,7 @@
       </c>
       <c r="I381" s="7" t="inlineStr">
         <is>
-          <t>Verified Missing for MD-00099 in Unknown. Low. EX-0124, EX-0125. OFF-00099. TR-00099. PO. PO-2022-0017. FA-000099. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00099: Missing / Unknown (Low). EX-0124, EX-0125.</t>
         </is>
       </c>
     </row>
@@ -48585,7 +48513,7 @@
       </c>
       <c r="I382" s="7" t="inlineStr">
         <is>
-          <t>Capital buy MD-00100: Cisco C9300, $6290, PO-2022-0017.</t>
+          <t>Vendor shipment for MD-00100 (Cisco C9300) recorded at $6290 on PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -48632,7 +48560,7 @@
       </c>
       <c r="I383" s="7" t="inlineStr">
         <is>
-          <t>TR-00100 - got it 05/05/2026 at Unknown.</t>
+          <t>Transfer TR-00100 for MD-00100: posted 05/01/2026, inbound May 05, 2026, APR APR-00100.</t>
         </is>
       </c>
     </row>
@@ -48675,7 +48603,7 @@
       </c>
       <c r="I384" s="7" t="inlineStr">
         <is>
-          <t>OFF-00100 - Unresolved. Due 2026-07-15.</t>
+          <t>Service desk OFF-00100: Unresolved; return required Yes; due 2026-07-15. Ticket alone does not dock MD-00100.</t>
         </is>
       </c>
     </row>
@@ -48757,7 +48685,7 @@
       </c>
       <c r="I386" s="7" t="inlineStr">
         <is>
-          <t>Technician wrote about MD-00100 in regional_IT_notes.docx; treated as unverified.</t>
+          <t>regional_IT_notes.docx checked for MD-00100; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -48796,7 +48724,7 @@
       </c>
       <c r="I387" s="7" t="inlineStr">
         <is>
-          <t>MD-00100 / Cisco C9300: disposal evidence expectations from Appendix A. Anchored to TR-00100, PO-2022-0017, FA-000100, OFF-00100, APR-00100; acquisition $6290.</t>
+          <t>Policy figure sets disposal evidence expectations for MD-00100; chain row 387 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -48831,7 +48759,7 @@
       </c>
       <c r="I388" s="7" t="inlineStr">
         <is>
-          <t>I won't invent a floor for MD-00100.</t>
+          <t>No dock scan, disposal certificate, or count currently places MD-00100; assumption left open.</t>
         </is>
       </c>
     </row>
@@ -48878,7 +48806,7 @@
       </c>
       <c r="I389" s="7" t="inlineStr">
         <is>
-          <t>MD-00100 → Missing. Confidence Low. EX-0126, EX-0127. OFF-00100. TR-00100. PO. PO-2022-0017. FA-000100. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00100 — Missing, site Unknown, Low. EX-0126, EX-0127.</t>
         </is>
       </c>
     </row>
@@ -48925,7 +48853,7 @@
       </c>
       <c r="I390" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00101 (MacBook Pro 14) for $1985 via PO-2022-0017.</t>
+          <t>PO PO-2022-0017 covers MD-00101 (MacBook Pro 14) for $1985.</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48900,7 @@
       </c>
       <c r="I391" s="7" t="inlineStr">
         <is>
-          <t>Seattle: TR-00101 received Jun 07, 2026.</t>
+          <t>Transfer TR-00101 for MD-00101: posted 06/05/2026, inbound Jun 07, 2026, APR APR-00101.</t>
         </is>
       </c>
     </row>
@@ -49015,7 +48943,7 @@
       </c>
       <c r="I392" s="7" t="inlineStr">
         <is>
-          <t>RET-00101 sits Pending Disposal. Hardware return not required per ticket.</t>
+          <t>Service desk RET-00101: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00101.</t>
         </is>
       </c>
     </row>
@@ -49097,7 +49025,7 @@
       </c>
       <c r="I394" s="7" t="inlineStr">
         <is>
-          <t>Word dump checked for MD-00101; no authoritative note found.</t>
+          <t>regional_IT_notes.docx checked for MD-00101; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -49136,7 +49064,7 @@
       </c>
       <c r="I395" s="7" t="inlineStr">
         <is>
-          <t>MD-00101 chain includes the figure as a transfer rubric (Medium). Record set: TR-00101, PO-2022-0017, FA-000101, RET-00101, APR-00101.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00101; cite chain row 395.</t>
         </is>
       </c>
     </row>
@@ -49183,7 +49111,7 @@
       </c>
       <c r="I396" s="7" t="inlineStr">
         <is>
-          <t>I am standing on Retired/Pending Disposal for MD-00101 (Seattle, Medium). EX-0128, EX-0129. RET-00101. TR-00101. PO. PO-2022-0017. FA-000101. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00101 as Retired/Pending Disposal in Seattle; confidence Medium. EX-0128, EX-0129.</t>
         </is>
       </c>
     </row>
@@ -49230,7 +49158,7 @@
       </c>
       <c r="I397" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2022-0017. Dell U2723QE, $700.</t>
+          <t>Acquisition MD-00102: Dell U2723QE, $700, PO PO-2022-0017.</t>
         </is>
       </c>
     </row>
@@ -49277,7 +49205,7 @@
       </c>
       <c r="I398" s="7" t="inlineStr">
         <is>
-          <t>MD-00102 inbound 01/11/2026 on TR-00102 / APR-00102.</t>
+          <t>Transfer TR-00102 for MD-00102: posted Jan 10, 2026, inbound 2026-01-11, APR APR-00102.</t>
         </is>
       </c>
     </row>
@@ -49320,7 +49248,7 @@
       </c>
       <c r="I399" s="7" t="inlineStr">
         <is>
-          <t>RET-00102 - Pending Disposal. Due n/a.</t>
+          <t>Service desk RET-00102: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00102.</t>
         </is>
       </c>
     </row>
@@ -49359,7 +49287,7 @@
       </c>
       <c r="I400" s="7" t="inlineStr">
         <is>
-          <t>Staged for July recycler run - cert not attached yet on some of these. Ref MD-00102.</t>
+          <t>Staged for July recycler run — cert not attached yet on some of these. Ref MD-00102.</t>
         </is>
       </c>
     </row>
@@ -49402,7 +49330,7 @@
       </c>
       <c r="I401" s="7" t="inlineStr">
         <is>
-          <t>Looked for MD-00102 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
+          <t>regional_IT_notes.docx checked for MD-00102; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -49441,7 +49369,7 @@
       </c>
       <c r="I402" s="7" t="inlineStr">
         <is>
-          <t>Atlanta custody review for MD-00102 used the transfer column on the matrix. Source trail: TR-00102, PO-2022-0017, FA-000102, RET-00102, APR-00102.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix disposal line for MD-00102; cite chain row 402.</t>
         </is>
       </c>
     </row>
@@ -49488,7 +49416,7 @@
       </c>
       <c r="I403" s="7" t="inlineStr">
         <is>
-          <t>After the chain, MD-00102 is Retired/Pending Disposal / Atlanta (Medium). EX-0130, EX-0131, EX-0132. RET-00102. TR-00102. PO. PO-2022-0017. FA-000102. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00102 as Retired/Pending Disposal in Atlanta; confidence Medium. EX-0130, EX-0131, EX-0132.</t>
         </is>
       </c>
     </row>
@@ -49535,7 +49463,7 @@
       </c>
       <c r="I404" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00103 (Samsung Galaxy S24) for $1175 via PO-2023-0018.</t>
+          <t>Vendor shipment for MD-00103 (Samsung Galaxy S24) recorded at $1175 on PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -49582,7 +49510,7 @@
       </c>
       <c r="I405" s="7" t="inlineStr">
         <is>
-          <t>Chicago: TR-00103 received 2026-02-14.</t>
+          <t>Transfer TR-00103 for MD-00103: posted 2026-02-11, inbound 02/14/2026, APR APR-00103.</t>
         </is>
       </c>
     </row>
@@ -49625,7 +49553,7 @@
       </c>
       <c r="I406" s="7" t="inlineStr">
         <is>
-          <t>RET-00103 sits Pending Disposal. Hardware return not required per ticket.</t>
+          <t>Service desk RET-00103: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00103.</t>
         </is>
       </c>
     </row>
@@ -49707,7 +49635,7 @@
       </c>
       <c r="I408" s="7" t="inlineStr">
         <is>
-          <t>Technician prose on MD-00103 stays out of the custody conclusion.</t>
+          <t>regional_IT_notes.docx checked for MD-00103; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -49746,7 +49674,7 @@
       </c>
       <c r="I409" s="7" t="inlineStr">
         <is>
-          <t>MD-00103 chain includes the figure as a financial rubric (Medium). Record set: TR-00103, PO-2023-0018, FA-000103, RET-00103, APR-00103.</t>
+          <t>ITAM_control_matrix.png Appendix A transfer row consulted while tracing MD-00103; transactional proof stays with chain row 409.</t>
         </is>
       </c>
     </row>
@@ -49793,7 +49721,7 @@
       </c>
       <c r="I410" s="7" t="inlineStr">
         <is>
-          <t>Final read MD-00103: Retired/Pending Disposal @ Chicago, confidence Medium. EX-0133, EX-0134. RET-00103. TR-00103. PO. PO-2023-0018. FA-000103. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00103 — Retired/Pending Disposal, site Chicago, Medium. EX-0133, EX-0134.</t>
         </is>
       </c>
     </row>
@@ -49840,7 +49768,7 @@
       </c>
       <c r="I411" s="7" t="inlineStr">
         <is>
-          <t>$6470 Cisco C9300. PO-2023-0018.</t>
+          <t>Acquisition MD-00104: Cisco C9300, $6470, PO PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -49887,7 +49815,7 @@
       </c>
       <c r="I412" s="7" t="inlineStr">
         <is>
-          <t>Dock file shows Mar 18, 2026 for TR-00104 (MD-00104).</t>
+          <t>Transfer TR-00104 for MD-00104: posted 03/16/2026, inbound Mar 18, 2026, APR APR-00104.</t>
         </is>
       </c>
     </row>
@@ -49930,7 +49858,7 @@
       </c>
       <c r="I413" s="7" t="inlineStr">
         <is>
-          <t>Service desk RET-00104 on MD-00104. Return required No.</t>
+          <t>Service desk RET-00104: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00104.</t>
         </is>
       </c>
     </row>
@@ -50012,7 +49940,7 @@
       </c>
       <c r="I415" s="7" t="inlineStr">
         <is>
-          <t>Could not tie MD-00104 to a verified RN entry in the notes.</t>
+          <t>regional_IT_notes.docx checked for MD-00104; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -50051,7 +49979,7 @@
       </c>
       <c r="I416" s="7" t="inlineStr">
         <is>
-          <t>While scoring MD-00104, disposal requirements came from the policy appendix. Checked TR-00104, PO-2023-0018, FA-000104, RET-00104, APR-00104 against those requirements.</t>
+          <t>Policy figure sets assignment evidence expectations for MD-00104; chain row 416 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -50098,7 +50026,7 @@
       </c>
       <c r="I417" s="7" t="inlineStr">
         <is>
-          <t>Call on MD-00104: Retired/Pending Disposal, Medium. EX-0135, EX-0136. RET-00104. TR-00104. PO. PO-2023-0018. FA-000104. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00104 — Retired/Pending Disposal, site Dallas, Medium. EX-0135, EX-0136.</t>
         </is>
       </c>
     </row>
@@ -50145,7 +50073,7 @@
       </c>
       <c r="I418" s="7" t="inlineStr">
         <is>
-          <t>Purchasing file PO-2023-0018 matches MD-00105 at $1850.</t>
+          <t>Acquisition MD-00105: Dell Latitude 7440, $1850, PO PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -50192,7 +50120,7 @@
       </c>
       <c r="I419" s="7" t="inlineStr">
         <is>
-          <t>From warehouse to Regional IT. TR-00105, received 04/21/2026.</t>
+          <t>Transfer TR-00105 for MD-00105: posted Apr 20, 2026, inbound 2026-04-21, APR APR-00105.</t>
         </is>
       </c>
     </row>
@@ -50235,7 +50163,7 @@
       </c>
       <c r="I420" s="7" t="inlineStr">
         <is>
-          <t>RET-00105 Pending Disposal. Return required=No.</t>
+          <t>Service desk RET-00105: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00105.</t>
         </is>
       </c>
     </row>
@@ -50317,7 +50245,7 @@
       </c>
       <c r="I422" s="7" t="inlineStr">
         <is>
-          <t>Investigative color on MD-00105 in regional_IT_notes.docx - weight zero.</t>
+          <t>regional_IT_notes.docx checked for MD-00105; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -50356,7 +50284,7 @@
       </c>
       <c r="I423" s="7" t="inlineStr">
         <is>
-          <t>ITAM_control_matrix.png consulted for MD-00105 (return). Conclusion still tied to TR-00105, PO-2023-0018, FA-000105, RET-00105, APR-00105 at Denver, $1850.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix financial line for MD-00105; cite chain row 423.</t>
         </is>
       </c>
     </row>
@@ -50403,7 +50331,7 @@
       </c>
       <c r="I424" s="7" t="inlineStr">
         <is>
-          <t>MD-00105 custody narrative ends Retired/Pending Disposal (Medium). EX-0137, EX-0138. RET-00105. TR-00105. PO. PO-2023-0018. FA-000105. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00105 remains Retired/Pending Disposal at Denver; Medium. EX-0137, EX-0138.</t>
         </is>
       </c>
     </row>
@@ -50450,7 +50378,7 @@
       </c>
       <c r="I425" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2023-0018 lists Dell U2723QE / $565.</t>
+          <t>Vendor shipment for MD-00106 (Dell U2723QE) recorded at $565 on PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -50497,7 +50425,7 @@
       </c>
       <c r="I426" s="7" t="inlineStr">
         <is>
-          <t>TR-00106 05/22/2026; inbound 2026-05-25.</t>
+          <t>Transfer TR-00106 for MD-00106: posted 2026-05-22, inbound 05/25/2026, APR APR-00106.</t>
         </is>
       </c>
     </row>
@@ -50540,7 +50468,7 @@
       </c>
       <c r="I427" s="7" t="inlineStr">
         <is>
-          <t>RET-00106 sits Pending Disposal. Hardware return not required per ticket.</t>
+          <t>Service desk RET-00106: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00106.</t>
         </is>
       </c>
     </row>
@@ -50622,7 +50550,7 @@
       </c>
       <c r="I429" s="7" t="inlineStr">
         <is>
-          <t>Notes packet includes MD-00106 only as background, not evidence.</t>
+          <t>regional_IT_notes.docx checked for MD-00106; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -50661,7 +50589,7 @@
       </c>
       <c r="I430" s="7" t="inlineStr">
         <is>
-          <t>MD-00106: checked ITAM-001 transfer row while reviewing TR-00106, PO-2023-0018, FA-000106, RET-00106, APR-00106. Cost basis $565; confidence Medium. Figure does not replace logs.</t>
+          <t>ITAM_control_matrix.png Appendix A disposal row consulted while tracing MD-00106; transactional proof stays with chain row 430.</t>
         </is>
       </c>
     </row>
@@ -50708,7 +50636,7 @@
       </c>
       <c r="I431" s="7" t="inlineStr">
         <is>
-          <t>Wrap-up MD-00106: Retired/Pending Disposal (Medium) - EX-0139, EX-0140. RET-00106. TR-00106. PO. PO-2023-0018. FA-000106. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00106: Retired/Pending Disposal / New York (Medium). EX-0139, EX-0140.</t>
         </is>
       </c>
     </row>
@@ -50755,7 +50683,7 @@
       </c>
       <c r="I432" s="7" t="inlineStr">
         <is>
-          <t>Acquired MD-00107 (Samsung Galaxy S24) for $1040 via PO-2023-0018.</t>
+          <t>Vendor shipment for MD-00107 (Samsung Galaxy S24) recorded at $1040 on PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -50802,7 +50730,7 @@
       </c>
       <c r="I433" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00107. Receive date Jun 27, 2026.</t>
+          <t>Transfer TR-00107 for MD-00107: posted 06/26/2026, inbound Jun 27, 2026, APR APR-00107.</t>
         </is>
       </c>
     </row>
@@ -50845,7 +50773,7 @@
       </c>
       <c r="I434" s="7" t="inlineStr">
         <is>
-          <t>Service desk RET-00107 on MD-00107. Return required No.</t>
+          <t>Service desk RET-00107: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00107.</t>
         </is>
       </c>
     </row>
@@ -50927,7 +50855,7 @@
       </c>
       <c r="I436" s="7" t="inlineStr">
         <is>
-          <t>Regional file reviewed for MD-00107; no clearance language accepted.</t>
+          <t>regional_IT_notes.docx checked for MD-00107; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50894,7 @@
       </c>
       <c r="I437" s="7" t="inlineStr">
         <is>
-          <t>MD-00107: checked ITAM-001 financial row while reviewing TR-00107, PO-2023-0018, FA-000107, RET-00107, APR-00107. Cost basis $1040; confidence Medium. Figure does not replace logs.</t>
+          <t>Policy figure sets transfer evidence expectations for MD-00107; chain row 437 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -51013,7 +50941,7 @@
       </c>
       <c r="I438" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00107 - Retired/Pending Disposal, site Seattle, Medium. EX-0141, EX-0142. RET-00107. TR-00107. PO. PO-2023-0018. FA-000107. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00107 remains Retired/Pending Disposal at Seattle; Medium. EX-0141, EX-0142.</t>
         </is>
       </c>
     </row>
@@ -51060,7 +50988,7 @@
       </c>
       <c r="I439" s="7" t="inlineStr">
         <is>
-          <t>Receiving against PO-2023-0018. Cisco C9300, $6335.</t>
+          <t>Vendor shipment for MD-00108 (Cisco C9300) recorded at $6335 on PO-2023-0018.</t>
         </is>
       </c>
     </row>
@@ -51107,7 +51035,7 @@
       </c>
       <c r="I440" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00108 / APR-00108. Received 01/30/2026.</t>
+          <t>Transfer TR-00108 for MD-00108: posted Jan 30, 2026, inbound 2026-01-30, APR APR-00108.</t>
         </is>
       </c>
     </row>
@@ -51150,7 +51078,7 @@
       </c>
       <c r="I441" s="7" t="inlineStr">
         <is>
-          <t>RET-00108 Pending Disposal. Return required=No.</t>
+          <t>Service desk RET-00108: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00108.</t>
         </is>
       </c>
     </row>
@@ -51232,7 +51160,7 @@
       </c>
       <c r="I443" s="7" t="inlineStr">
         <is>
-          <t>I did not cite regional_IT_notes.docx as proof for MD-00108.</t>
+          <t>regional_IT_notes.docx checked for MD-00108; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -51271,7 +51199,7 @@
       </c>
       <c r="I444" s="7" t="inlineStr">
         <is>
-          <t>MD-00108 / Cisco C9300: disposal evidence expectations from Appendix A. Anchored to TR-00108, PO-2023-0018, FA-000108, RET-00108, APR-00108; acquisition $6335.</t>
+          <t>Matrix assignment criteria applied to MD-00108; figure is reference, not inbound proof for chain row 444.</t>
         </is>
       </c>
     </row>
@@ -51318,7 +51246,7 @@
       </c>
       <c r="I445" s="7" t="inlineStr">
         <is>
-          <t>Retired/Pending Disposal is the status for MD-00108 at Atlanta; Medium. EX-0143, EX-0144. RET-00108. TR-00108. PO. PO-2023-0018. FA-000108. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00108 remains Retired/Pending Disposal at Atlanta; Medium. EX-0143, EX-0144.</t>
         </is>
       </c>
     </row>
@@ -51365,7 +51293,7 @@
       </c>
       <c r="I446" s="7" t="inlineStr">
         <is>
-          <t>$2030 Lenovo ThinkPad T14. PO-2024-0019.</t>
+          <t>Vendor shipment for MD-00109 (Lenovo ThinkPad T14) recorded at $2030 on PO-2024-0019.</t>
         </is>
       </c>
     </row>
@@ -51412,7 +51340,7 @@
       </c>
       <c r="I447" s="7" t="inlineStr">
         <is>
-          <t>TR-00109 - got it 2026-02-04 at Chicago.</t>
+          <t>Transfer TR-00109 for MD-00109: posted 2026-02-02, inbound 02/04/2026, APR APR-00109.</t>
         </is>
       </c>
     </row>
@@ -51455,7 +51383,7 @@
       </c>
       <c r="I448" s="7" t="inlineStr">
         <is>
-          <t>RET-00109 sits Pending Disposal. Hardware return not required per ticket.</t>
+          <t>Service desk RET-00109: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00109.</t>
         </is>
       </c>
     </row>
@@ -51537,7 +51465,7 @@
       </c>
       <c r="I450" s="7" t="inlineStr">
         <is>
-          <t>Technician notes scanned for MD-00109; nothing usable without a transaction.</t>
+          <t>regional_IT_notes.docx checked for MD-00109; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -51576,7 +51504,7 @@
       </c>
       <c r="I451" s="7" t="inlineStr">
         <is>
-          <t>Control matrix cited on MD-00109 for return only. Movement/finance proof stays with TR-00109, PO-2024-0019, FA-000109, RET-00109, APR-00109; exceptions EX-0145, EX-0146.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix financial line for MD-00109; cite chain row 451.</t>
         </is>
       </c>
     </row>
@@ -51623,7 +51551,7 @@
       </c>
       <c r="I452" s="7" t="inlineStr">
         <is>
-          <t>MD-00109 → Retired/Pending Disposal. Confidence Medium. EX-0145, EX-0146. RET-00109. TR-00109. PO. PO-2024-0019. FA-000109. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00109 as Retired/Pending Disposal in Chicago; confidence Medium. EX-0145, EX-0146.</t>
         </is>
       </c>
     </row>
@@ -51670,7 +51598,7 @@
       </c>
       <c r="I453" s="7" t="inlineStr">
         <is>
-          <t>$745 Dell U2723QE. PO-2024-0019.</t>
+          <t>PO PO-2024-0019 covers MD-00110 (Dell U2723QE) for $745.</t>
         </is>
       </c>
     </row>
@@ -51717,7 +51645,7 @@
       </c>
       <c r="I454" s="7" t="inlineStr">
         <is>
-          <t>Transfer TR-00110 / APR-00110. Received Mar 08, 2026.</t>
+          <t>Transfer TR-00110 for MD-00110: posted 03/07/2026, inbound Mar 08, 2026, APR APR-00110.</t>
         </is>
       </c>
     </row>
@@ -51760,7 +51688,7 @@
       </c>
       <c r="I455" s="7" t="inlineStr">
         <is>
-          <t>RET-00110 Pending Disposal. Return required=No.</t>
+          <t>Service desk RET-00110: Pending Disposal; return required No; due n/a. Ticket alone does not dock MD-00110.</t>
         </is>
       </c>
     </row>
@@ -51842,7 +51770,7 @@
       </c>
       <c r="I457" s="7" t="inlineStr">
         <is>
-          <t>Looked for MD-00110 in regional_IT_notes.docx; still need CSV/XLSX proof.</t>
+          <t>regional_IT_notes.docx checked for MD-00110; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -51881,7 +51809,7 @@
       </c>
       <c r="I458" s="7" t="inlineStr">
         <is>
-          <t>For MD-00110 (Dell U2723QE), Appendix A transfer criteria were read against TR-00110, PO-2024-0019, FA-000110, RET-00110, APR-00110. Verified status target Retired/Pending Disposal at Dallas; matrix PNG is reference only.</t>
+          <t>Policy figure sets disposal evidence expectations for MD-00110; chain row 458 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -51928,7 +51856,7 @@
       </c>
       <c r="I459" s="7" t="inlineStr">
         <is>
-          <t>Retired/Pending Disposal is the status for MD-00110 at Dallas; Medium. EX-0147, EX-0148. RET-00110. TR-00110. PO. PO-2024-0019. FA-000110. ITAM_control_matrix.png.</t>
+          <t>Chain ends with MD-00110 as Retired/Pending Disposal in Dallas; confidence Medium. EX-0147, EX-0148.</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51903,7 @@
       </c>
       <c r="I460" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2024-0019 lists Dell U2723QE / $610.</t>
+          <t>PO PO-2024-0019 covers MD-00114 (Dell U2723QE) for $610.</t>
         </is>
       </c>
     </row>
@@ -52022,7 +51950,7 @@
       </c>
       <c r="I461" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00114 completed inbound 01/22/2026.</t>
+          <t>Transfer TR-00114 for MD-00114: posted Jan 22, 2026, inbound 2026-01-22, APR APR-00114.</t>
         </is>
       </c>
     </row>
@@ -52065,7 +51993,7 @@
       </c>
       <c r="I462" s="7" t="inlineStr">
         <is>
-          <t>RET-00114 - Closed. Due n/a.</t>
+          <t>Service desk RET-00114: Closed; return required No; due n/a. Ticket alone does not dock MD-00114.</t>
         </is>
       </c>
     </row>
@@ -52151,7 +52079,7 @@
       </c>
       <c r="I464" s="7" t="inlineStr">
         <is>
-          <t>MD-00114 pending-disposal with an empty cert field.</t>
+          <t>Recycler move for MD-00114 lacks matching disposal certificate (TR-00114).</t>
         </is>
       </c>
     </row>
@@ -52194,7 +52122,7 @@
       </c>
       <c r="I465" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb for MD-00114 in regional_IT_notes.docx; corroboration missing.</t>
+          <t>regional_IT_notes.docx checked for MD-00114; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -52233,7 +52161,7 @@
       </c>
       <c r="I466" s="7" t="inlineStr">
         <is>
-          <t>MD-00114: checked ITAM-001 financial row while reviewing TR-00114, PO-2024-0019, FA-000114, RET-00114, APR-00114. Cost basis $610; confidence Low. Figure does not replace logs.</t>
+          <t>Policy figure sets transfer evidence expectations for MD-00114; chain row 466 remains the audit trail.</t>
         </is>
       </c>
     </row>
@@ -52280,7 +52208,7 @@
       </c>
       <c r="I467" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00114 - Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150. TR-00114. RET-00114. PO. PO-2024-0019. FA-000114. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00114 — Retired/Pending Disposal, site Disposed (certificate missing), Low. EX-0149, EX-0150.</t>
         </is>
       </c>
     </row>
@@ -52327,7 +52255,7 @@
       </c>
       <c r="I468" s="7" t="inlineStr">
         <is>
-          <t>Procurement PO-2025-0020 lists Dell U2723QE / $790.</t>
+          <t>Vendor shipment for MD-00118 (Dell U2723QE) recorded at $790 on PO-2025-0020.</t>
         </is>
       </c>
     </row>
@@ -52374,7 +52302,7 @@
       </c>
       <c r="I469" s="7" t="inlineStr">
         <is>
-          <t>MD-00118 inbound Jun 04, 2026 on TR-00118 / APR-00118.</t>
+          <t>Transfer TR-00118 for MD-00118: posted Jun 03, 2026, inbound 2026-06-04, APR APR-00118.</t>
         </is>
       </c>
     </row>
@@ -52417,7 +52345,7 @@
       </c>
       <c r="I470" s="7" t="inlineStr">
         <is>
-          <t>Offboarding RET-00118: No.</t>
+          <t>Service desk RET-00118: Closed; return required No; due n/a. Ticket alone does not dock MD-00118.</t>
         </is>
       </c>
     </row>
@@ -52503,7 +52431,7 @@
       </c>
       <c r="I472" s="7" t="inlineStr">
         <is>
-          <t>No DC for MD-00118. Transfer TR-00118 isn't enough.</t>
+          <t>Recycler move for MD-00118 lacks matching disposal certificate (TR-00118).</t>
         </is>
       </c>
     </row>
@@ -52546,7 +52474,7 @@
       </c>
       <c r="I473" s="7" t="inlineStr">
         <is>
-          <t>I kept MD-00118 off the note until logs backed it.</t>
+          <t>regional_IT_notes.docx checked for MD-00118; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -52585,7 +52513,7 @@
       </c>
       <c r="I474" s="7" t="inlineStr">
         <is>
-          <t>Disposed (certificate missing) custody review for MD-00118 used the return column on the matrix. Source trail: TR-00118, PO-2025-0020, FA-000118, RET-00118, APR-00118.</t>
+          <t>ITAM_control_matrix.png Appendix A financial row consulted while tracing MD-00118; transactional proof stays with chain row 474.</t>
         </is>
       </c>
     </row>
@@ -52632,7 +52560,7 @@
       </c>
       <c r="I475" s="7" t="inlineStr">
         <is>
-          <t>Verified Retired/Pending Disposal for MD-00118 in Disposed (certificate missing). Low. EX-0151, EX-0152. TR-00118. RET-00118. PO. PO-2025-0020. FA-000118. ITAM_control_matrix.png.</t>
+          <t>Verified outcome MD-00118: Retired/Pending Disposal / Disposed (certificate missing) (Low). EX-0151, EX-0152.</t>
         </is>
       </c>
     </row>
@@ -52679,7 +52607,7 @@
       </c>
       <c r="I476" s="7" t="inlineStr">
         <is>
-          <t>PO-2025-0020: Samsung Galaxy S24 at $950.</t>
+          <t>Vendor shipment for MD-00119 (Samsung Galaxy S24) recorded at $950 on PO-2025-0020.</t>
         </is>
       </c>
     </row>
@@ -52726,7 +52654,7 @@
       </c>
       <c r="I477" s="7" t="inlineStr">
         <is>
-          <t>Movement TR-00119 completed inbound 2026-07-09.</t>
+          <t>Transfer TR-00119 for MD-00119: posted Jul 08, 2026, inbound 2026-07-09, APR APR-00119.</t>
         </is>
       </c>
     </row>
@@ -52769,7 +52697,7 @@
       </c>
       <c r="I478" s="7" t="inlineStr">
         <is>
-          <t>RET-00119 - Closed. Due n/a.</t>
+          <t>Service desk RET-00119: Closed; return required No; due n/a. Ticket alone does not dock MD-00119.</t>
         </is>
       </c>
     </row>
@@ -52855,7 +52783,7 @@
       </c>
       <c r="I480" s="7" t="inlineStr">
         <is>
-          <t>Certificate DC-00119 matches MD-00119.</t>
+          <t>Disposal certificate DC-00119 verified for MD-00119.</t>
         </is>
       </c>
     </row>
@@ -52898,7 +52826,7 @@
       </c>
       <c r="I481" s="7" t="inlineStr">
         <is>
-          <t>For MD-00119, notes are breadcrumb-only.</t>
+          <t>regional_IT_notes.docx checked for MD-00119; no corroborated RN entry found.</t>
         </is>
       </c>
     </row>
@@ -52937,7 +52865,7 @@
       </c>
       <c r="I482" s="7" t="inlineStr">
         <is>
-          <t>Did not treat the PNG as proof of location for MD-00119. transfer standard applied; TR-00119, PO-2025-0020, FA-000119, RET-00119, APR-00119 remains dispositive (Disposed).</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix financial line for MD-00119; cite chain row 482.</t>
         </is>
       </c>
     </row>
@@ -52984,7 +52912,7 @@
       </c>
       <c r="I483" s="7" t="inlineStr">
         <is>
-          <t>Chain end MD-00119: Disposed; High; EX-0153. TR-00119. RET-00119. PO. PO-2025-0020. FA-000119. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00119 — Disposed, site Disposed, High. EX-0153.</t>
         </is>
       </c>
     </row>
@@ -53031,7 +52959,7 @@
       </c>
       <c r="I484" s="7" t="inlineStr">
         <is>
-          <t>MD-00127 origin: PO-2023-0022, $995.</t>
+          <t>Vendor shipment for MD-00127 (Samsung Galaxy S24) recorded at $995 on PO-2023-0022.</t>
         </is>
       </c>
     </row>
@@ -53070,7 +52998,7 @@
       </c>
       <c r="I485" s="7" t="inlineStr">
         <is>
-          <t>Denver custody review for MD-00127 used the return column on the matrix. Source trail: TR-00127, PO-2023-0022, FA-000127.</t>
+          <t>ITAM_control_matrix.png Appendix A transfer row consulted while tracing MD-00127; transactional proof stays with chain row 485.</t>
         </is>
       </c>
     </row>
@@ -53117,7 +53045,7 @@
       </c>
       <c r="I486" s="7" t="inlineStr">
         <is>
-          <t>Log row TR-00127. Receive date 2026-02-17.</t>
+          <t>Transfer TR-00127 for MD-00127: posted 2026-02-11, inbound 02/17/2026, APR missing.</t>
         </is>
       </c>
     </row>
@@ -53164,7 +53092,7 @@
       </c>
       <c r="I487" s="7" t="inlineStr">
         <is>
-          <t>Outcome MD-00127 - In Use, site Denver, Medium. EX-0160. E0061. TR-00127. PO. PO-2023-0022. FA-000127. ITAM_control_matrix.png.</t>
+          <t>Custody conclusion for MD-00127: In Use at Denver (Medium). EX-0160.</t>
         </is>
       </c>
     </row>
@@ -53211,7 +53139,7 @@
       </c>
       <c r="I488" s="7" t="inlineStr">
         <is>
-          <t>First touch MD-00130 - PO-2023-0022, $700.</t>
+          <t>Acquisition MD-00130: Dell U2723QE, $700, PO PO-2023-0022.</t>
         </is>
       </c>
     </row>
@@ -53250,7 +53178,7 @@
       </c>
       <c r="I489" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00130 should read matrix assignment, then TR-00130, PO-2023-0022, APR-00130. Working site Atlanta; status call In Use.</t>
+          <t>ITAM_control_matrix.png Appendix A financial row consulted while tracing MD-00130; transactional proof stays with chain row 489.</t>
         </is>
       </c>
     </row>
@@ -53297,7 +53225,7 @@
       </c>
       <c r="I490" s="7" t="inlineStr">
         <is>
-          <t>TR-00130 - got it May 28, 2026 at Atlanta.</t>
+          <t>Transfer TR-00130 for MD-00130: posted May 22, 2026, inbound 2026-05-28, APR APR-00130.</t>
         </is>
       </c>
     </row>
@@ -53344,7 +53272,7 @@
       </c>
       <c r="I491" s="7" t="inlineStr">
         <is>
-          <t>Closing MD-00130: In Use at Atlanta (High). EX-0161. E0064. TR-00130. APR-00130. PO. PO-2023-0022. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00130 remains In Use at Atlanta; High. EX-0161.</t>
         </is>
       </c>
     </row>
@@ -53391,7 +53319,7 @@
       </c>
       <c r="I492" s="7" t="inlineStr">
         <is>
-          <t>Ordered Samsung Galaxy S24 (MD-00131) on PO-2023-0022; $1175.</t>
+          <t>PO PO-2023-0022 covers MD-00131 (Samsung Galaxy S24) for $1175.</t>
         </is>
       </c>
     </row>
@@ -53438,7 +53366,7 @@
       </c>
       <c r="I493" s="7" t="inlineStr">
         <is>
-          <t>MD-00131 inbound Jun 28, 2026 on TR-00131 / APR-00131.</t>
+          <t>Transfer TR-00131 for MD-00131: posted 06/26/2026, inbound Jun 28, 2026, APR APR-00131.</t>
         </is>
       </c>
     </row>
@@ -53477,7 +53405,7 @@
       </c>
       <c r="I494" s="7" t="inlineStr">
         <is>
-          <t>Auditors tracing MD-00131 should read matrix return, then TR-00131, PO-2023-0022, APR-00131. Working site Chicago; status call In Use.</t>
+          <t>ITAM_control_matrix.png Appendix A transfer row consulted while tracing MD-00131; transactional proof stays with chain row 494.</t>
         </is>
       </c>
     </row>
@@ -53524,7 +53452,7 @@
       </c>
       <c r="I495" s="7" t="inlineStr">
         <is>
-          <t>Call on MD-00131: In Use, High. EX-0162. E0065. TR-00131. APR-00131. PO. PO-2023-0022. ITAM_control_matrix.png.</t>
+          <t>Final status on MD-00131 — In Use, site Chicago, High. EX-0162.</t>
         </is>
       </c>
     </row>
@@ -53571,7 +53499,7 @@
       </c>
       <c r="I496" s="7" t="inlineStr">
         <is>
-          <t>Ordered Cisco C9300 (MD-00132) on PO-2023-0022; $6470.</t>
+          <t>Vendor shipment for MD-00132 (Cisco C9300) recorded at $6470 on PO-2023-0022.</t>
         </is>
       </c>
     </row>
@@ -53618,7 +53546,7 @@
       </c>
       <c r="I497" s="7" t="inlineStr">
         <is>
-          <t>Moved to E0066 in Dallas on TR-00132. Received 01/31/2026.</t>
+          <t>Transfer TR-00132 for MD-00132: posted Jan 30, 2026, inbound 2026-01-31, APR APR-00132.</t>
         </is>
       </c>
     </row>
@@ -53657,7 +53585,7 @@
       </c>
       <c r="I498" s="7" t="inlineStr">
         <is>
-          <t>Dallas custody review for MD-00132 used the return column on the matrix. Source trail: TR-00132, PO-2023-0022, APR-00132.</t>
+          <t>Read IT_asset_management_policy.pdf §4–§9 with the matrix transfer line for MD-00132; cite chain row 498.</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53632,7 @@
       </c>
       <c r="I499" s="7" t="inlineStr">
         <is>
-          <t>In Use is the status for MD-00132 at Dallas; High. EX-0163. E0066. TR-00132. APR-00132. PO. PO-2023-0022. ITAM_control_matrix.png.</t>
+          <t>After review, MD-00132 remains In Use at Dallas; High. EX-0163.</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53674,7 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>RN-0132 said MD-00132 was expensed under threshold. Rejected: acquisition cost $6,470 is ≥ $2,500, and the FAR still has no row.</t>
+          <t>RN-0132 claimed MD-00132 was expensed under threshold; rejected because $6,470 exceeds the capitalization gate and no FA row exists.</t>
         </is>
       </c>
     </row>
@@ -53778,7 +53706,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>MD-00132 / PO-2023-0022: capital-qualifying, no FA row. Blocks certification until capitalization or an approved write-off. MD-00130/MD-00131 are a different (under-threshold) story.</t>
+          <t>MD-00132 / PO-2023-0022: capital-qualifying with no FA row; blocks certification until capitalized or formally written off.</t>
         </is>
       </c>
     </row>
@@ -53797,7 +53725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -53824,7 +53752,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -53845,7 +53772,6 @@
       </c>
       <c r="B5" s="5">
         <f>SUM('Corrected Register'!M5:M136)</f>
-        <v>332115</v>
         <v/>
       </c>
     </row>
@@ -53867,7 +53793,6 @@
       </c>
       <c r="B7" s="5">
         <f>B5-B6</f>
-        <v>7375</v>
         <v/>
       </c>
     </row>
@@ -53879,7 +53804,6 @@
       </c>
       <c r="B8" s="5">
         <f>SUM('Corrected Register'!N5:N136)</f>
-        <v>61526.6</v>
         <v/>
       </c>
     </row>
@@ -53891,7 +53815,6 @@
       </c>
       <c r="B9" s="5">
         <f>SUMIF('Source Ledger'!H5:H133,"Active",'Source Ledger'!G5:G133)</f>
-        <v>61526.6</v>
         <v/>
       </c>
     </row>
@@ -53903,7 +53826,6 @@
       </c>
       <c r="B10" s="5">
         <f>SUM('Source Ledger'!G5:G133)</f>
-        <v>61526.6</v>
         <v/>
       </c>
     </row>
@@ -53937,8 +53859,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -53974,7 +53894,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -54043,7 +53962,6 @@
       </c>
       <c r="E24" s="7">
         <f>D24-C24</f>
-        <v>85</v>
         <v/>
       </c>
       <c r="F24" s="7" t="n">
@@ -54077,12 +53995,10 @@
       </c>
       <c r="E25" s="7">
         <f>D25-C25</f>
-        <v>140</v>
         <v/>
       </c>
       <c r="F25" s="7">
         <f>XLOOKUP(A25,'Source Ledger'!B5:B133,'Source Ledger'!G5:G133)</f>
-        <v>479.88</v>
         <v/>
       </c>
       <c r="G25" s="7" t="n">
@@ -54113,7 +54029,6 @@
       </c>
       <c r="E26" s="7">
         <f>D26-C26</f>
-        <v>210</v>
         <v/>
       </c>
       <c r="F26" s="7" t="n">
@@ -54147,7 +54062,6 @@
       </c>
       <c r="E27" s="7">
         <f>D27-C27</f>
-        <v>55</v>
         <v/>
       </c>
       <c r="F27" s="7" t="n">
@@ -54181,7 +54095,6 @@
       </c>
       <c r="E28" s="7">
         <f>D28-C28</f>
-        <v>195</v>
         <v/>
       </c>
       <c r="F28" s="7" t="n">
@@ -54215,7 +54128,6 @@
       </c>
       <c r="E29" s="7">
         <f>D29-C29</f>
-        <v>120</v>
         <v/>
       </c>
       <c r="F29" s="7" t="n">
@@ -54249,7 +54161,6 @@
       </c>
       <c r="E30" s="7">
         <f>D30-C30</f>
-        <v>0</v>
         <v/>
       </c>
       <c r="F30" s="7" t="n">
@@ -54283,7 +54194,6 @@
       </c>
       <c r="E31" s="7">
         <f>D31-C31</f>
-        <v>0</v>
         <v/>
       </c>
       <c r="F31" s="7" t="n">
@@ -54317,7 +54227,6 @@
       </c>
       <c r="E32" s="7">
         <f>D32-C32</f>
-        <v>165</v>
         <v/>
       </c>
       <c r="F32" s="7" t="n">
@@ -54404,10 +54313,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A18:H18"/>
@@ -54453,7 +54358,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -54646,7 +54550,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -54806,7 +54709,6 @@
       <c r="D27" s="15" t="inlineStr"/>
       <c r="E27" s="15" t="inlineStr"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -54854,7 +54756,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -55169,7 +55070,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -55285,7 +55185,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -11469,11 +11469,11 @@
       </c>
       <c r="B19" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A19)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="C19" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A19,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>12961</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -11482,11 +11482,11 @@
       </c>
       <c r="F19" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E19)</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="G19" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E19,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>13030.88</v>
       </c>
     </row>
     <row r="20">
@@ -11497,11 +11497,11 @@
       </c>
       <c r="B20" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A20)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C20" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A20,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -11510,11 +11510,11 @@
       </c>
       <c r="F20" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E20)</f>
-        <v/>
+        <v>36</v>
       </c>
       <c r="G20" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E20,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>18983.58</v>
       </c>
     </row>
     <row r="21">
@@ -11525,11 +11525,11 @@
       </c>
       <c r="B21" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A21)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C21" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A21,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>1019.4</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -11538,11 +11538,11 @@
       </c>
       <c r="F21" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E21)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="G21" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E21,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>15372.27</v>
       </c>
     </row>
     <row r="22">
@@ -11553,11 +11553,11 @@
       </c>
       <c r="B22" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A22)</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="C22" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A22,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>25477.76</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -11566,11 +11566,11 @@
       </c>
       <c r="F22" s="7">
         <f>COUNTIF('Corrected Register'!C5:C136,E22)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="G22" s="7">
         <f>SUMIF('Corrected Register'!C5:C136,E22,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>14139.87</v>
       </c>
     </row>
     <row r="23">
@@ -11581,11 +11581,11 @@
       </c>
       <c r="B23" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A23)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C23" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A23,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>6214.38</v>
       </c>
     </row>
     <row r="24">
@@ -11596,11 +11596,11 @@
       </c>
       <c r="B24" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A24)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C24" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A24,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>4851.08</v>
       </c>
     </row>
     <row r="25">
@@ -11611,11 +11611,11 @@
       </c>
       <c r="B25" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A25)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C25" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A25,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>4811.33</v>
       </c>
     </row>
     <row r="26">
@@ -11626,11 +11626,11 @@
       </c>
       <c r="B26" s="7">
         <f>COUNTIF('Corrected Register'!J5:J136,A26)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C26" s="7">
         <f>SUMIF('Corrected Register'!J5:J136,A26,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>6191.65</v>
       </c>
     </row>
     <row r="30">
@@ -11685,11 +11685,11 @@
       </c>
       <c r="B32" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A32)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C32" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A32,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>5184.18</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -11698,11 +11698,11 @@
       </c>
       <c r="F32" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E32)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="G32" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E32,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>6214.38</v>
       </c>
     </row>
     <row r="33">
@@ -11713,11 +11713,11 @@
       </c>
       <c r="B33" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A33)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C33" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A33,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>6267.29</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -11726,11 +11726,11 @@
       </c>
       <c r="F33" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E33)</f>
-        <v/>
+        <v>61</v>
       </c>
       <c r="G33" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E33,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>29063.84</v>
       </c>
     </row>
     <row r="34">
@@ -11741,11 +11741,11 @@
       </c>
       <c r="B34" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A34)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C34" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A34,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>11070.95</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -11754,11 +11754,11 @@
       </c>
       <c r="F34" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E34)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G34" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E34,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>2503.11</v>
       </c>
     </row>
     <row r="35">
@@ -11769,11 +11769,11 @@
       </c>
       <c r="B35" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A35)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C35" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A35,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>5149.95</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -11782,11 +11782,11 @@
       </c>
       <c r="F35" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E35)</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="G35" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E35,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>22627.56</v>
       </c>
     </row>
     <row r="36">
@@ -11797,11 +11797,11 @@
       </c>
       <c r="B36" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A36)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="C36" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A36,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>5551.75</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -11810,11 +11810,11 @@
       </c>
       <c r="F36" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E36)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="G36" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E36,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>7440</v>
       </c>
     </row>
     <row r="37">
@@ -11825,11 +11825,11 @@
       </c>
       <c r="B37" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A37)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="C37" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A37,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>10526</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -11838,11 +11838,11 @@
       </c>
       <c r="F37" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E37)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="G37" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E37,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>4811.33</v>
       </c>
     </row>
     <row r="38">
@@ -11853,11 +11853,11 @@
       </c>
       <c r="B38" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A38)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C38" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A38,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>6214.38</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -11866,11 +11866,11 @@
       </c>
       <c r="F38" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E38)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="G38" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E38,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>6191.65</v>
       </c>
     </row>
     <row r="39">
@@ -11881,11 +11881,11 @@
       </c>
       <c r="B39" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A39)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C39" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A39,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>4878.51</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -11894,11 +11894,11 @@
       </c>
       <c r="F39" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E39)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G39" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E39,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>2332.54</v>
       </c>
     </row>
     <row r="40">
@@ -11909,11 +11909,11 @@
       </c>
       <c r="B40" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A40)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C40" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A40,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -11922,11 +11922,11 @@
       </c>
       <c r="F40" s="7">
         <f>COUNTIF('Exception Register'!B5:B167,E40)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G40" s="7">
         <f>SUMIF('Exception Register'!B5:B167,E40,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>2869.32</v>
       </c>
     </row>
     <row r="41">
@@ -11937,11 +11937,11 @@
       </c>
       <c r="B41" s="7">
         <f>COUNTIF('Corrected Register'!I5:I136,A41)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C41" s="7">
         <f>SUMIF('Corrected Register'!I5:I136,A41,'Corrected Register'!N5:N136)</f>
-        <v/>
+        <v>4351.05</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -11950,11 +11950,11 @@
       </c>
       <c r="F41">
         <f>COUNTIF('Exception Register'!B5:B167,E41)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G41">
         <f>SUMIF('Exception Register'!B5:B167,E41,'Exception Register'!G5:G167)</f>
-        <v/>
+        <v>1875</v>
       </c>
     </row>
     <row r="42">

--- a/Meridian_IT_Asset_Reconciliation.xlsx
+++ b/Meridian_IT_Asset_Reconciliation.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5826,6 +5826,72 @@
         <v>46243.5</v>
       </c>
     </row>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6013,7 +6079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11262,6 +11328,69 @@
         <v>6470</v>
       </c>
     </row>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11317,8 +11446,7 @@
           <t>Assets reviewed</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>COUNTA('Corrected Register'!A5:A200)</f>
+      <c r="B5" s="5" t="n">
         <v>132</v>
       </c>
     </row>
@@ -11328,8 +11456,7 @@
           <t>Corrected register acquisition cost</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>SUM('Corrected Register'!M5:M200)</f>
+      <c r="B6" s="5" t="n">
         <v>332115</v>
       </c>
     </row>
@@ -11339,8 +11466,7 @@
           <t>Remaining book value (ledger NBV where present)</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>SUM('Corrected Register'!N5:N200)</f>
+      <c r="B7" s="5" t="n">
         <v>61526.6</v>
       </c>
     </row>
@@ -11350,8 +11476,7 @@
           <t>Open exceptions</t>
         </is>
       </c>
-      <c r="B8" s="5">
-        <f>COUNTIF('Exception Register'!K5:K200,"Open")</f>
+      <c r="B8" s="5" t="n">
         <v>163</v>
       </c>
     </row>
@@ -11467,12 +11592,10 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A19)</f>
+      <c r="B19" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C19" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A19,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C19" s="7" t="n">
         <v>12961</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -11480,12 +11603,10 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="F19" s="7">
-        <f>COUNTIF('Source Inventory'!$C$5:$C$200,E19)</f>
+      <c r="F19" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G19" s="7">
-        <f>SUMPRODUCT(('Source Inventory'!$C$5:$C$200=E19)*('Corrected Register'!$N$5:$N$200))</f>
+      <c r="G19" s="7" t="n">
         <v>13030.88</v>
       </c>
     </row>
@@ -11495,12 +11616,10 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A20)</f>
+      <c r="B20" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A20,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -11508,12 +11627,10 @@
           <t>Mobile Device</t>
         </is>
       </c>
-      <c r="F20" s="7">
-        <f>COUNTIF('Source Inventory'!$C$5:$C$200,E20)</f>
+      <c r="F20" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="G20" s="7">
-        <f>SUMPRODUCT(('Source Inventory'!$C$5:$C$200=E20)*('Corrected Register'!$N$5:$N$200))</f>
+      <c r="G20" s="7" t="n">
         <v>18983.58</v>
       </c>
     </row>
@@ -11523,12 +11640,10 @@
           <t>In Transit - Exception</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A21)</f>
+      <c r="B21" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A21,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C21" s="7" t="n">
         <v>1019.4</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -11536,12 +11651,10 @@
           <t>Monitor</t>
         </is>
       </c>
-      <c r="F21" s="7">
-        <f>COUNTIF('Source Inventory'!$C$5:$C$200,E21)</f>
+      <c r="F21" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G21" s="7">
-        <f>SUMPRODUCT(('Source Inventory'!$C$5:$C$200=E21)*('Corrected Register'!$N$5:$N$200))</f>
+      <c r="G21" s="7" t="n">
         <v>15372.27</v>
       </c>
     </row>
@@ -11551,12 +11664,10 @@
           <t>In Use</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A22)</f>
+      <c r="B22" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="C22" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A22,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C22" s="7" t="n">
         <v>25477.76</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -11564,12 +11675,10 @@
           <t>Network Asset</t>
         </is>
       </c>
-      <c r="F22" s="7">
-        <f>COUNTIF('Source Inventory'!$C$5:$C$200,E22)</f>
+      <c r="F22" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G22" s="7">
-        <f>SUMPRODUCT(('Source Inventory'!$C$5:$C$200=E22)*('Corrected Register'!$N$5:$N$200))</f>
+      <c r="G22" s="7" t="n">
         <v>14139.87</v>
       </c>
     </row>
@@ -11579,12 +11688,10 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A23)</f>
+      <c r="B23" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C23" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A23,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C23" s="7" t="n">
         <v>6214.38</v>
       </c>
     </row>
@@ -11594,12 +11701,10 @@
           <t>Pending Redeployment</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A24)</f>
+      <c r="B24" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A24,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C24" s="7" t="n">
         <v>4851.08</v>
       </c>
     </row>
@@ -11609,12 +11714,10 @@
           <t>Retired/Pending Disposal</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A25)</f>
+      <c r="B25" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A25,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C25" s="7" t="n">
         <v>4811.33</v>
       </c>
     </row>
@@ -11624,12 +11727,10 @@
           <t>Return Overdue</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>COUNTIF('Corrected Register'!$J$5:$J$200,A26)</f>
+      <c r="B26" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C26" s="7">
-        <f>SUMIF('Corrected Register'!$J$5:$J$200,A26,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C26" s="7" t="n">
         <v>6191.65</v>
       </c>
     </row>
@@ -11683,12 +11784,10 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A32)</f>
+      <c r="B32" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C32" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A32,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C32" s="7" t="n">
         <v>5184.18</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -11696,12 +11795,10 @@
           <t>Cannot Locate</t>
         </is>
       </c>
-      <c r="F32" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E32)</f>
+      <c r="F32" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G32" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E32,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G32" s="7" t="n">
         <v>6214.38</v>
       </c>
     </row>
@@ -11711,12 +11808,10 @@
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A33)</f>
+      <c r="B33" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C33" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A33,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C33" s="7" t="n">
         <v>6267.29</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -11724,12 +11819,10 @@
           <t>Closed Location Assignment</t>
         </is>
       </c>
-      <c r="F33" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E33)</f>
+      <c r="F33" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="G33" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E33,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G33" s="7" t="n">
         <v>29063.84</v>
       </c>
     </row>
@@ -11739,12 +11832,10 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A34)</f>
+      <c r="B34" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C34" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A34,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C34" s="7" t="n">
         <v>11070.95</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -11752,12 +11843,10 @@
           <t>Duplicate Serial Number</t>
         </is>
       </c>
-      <c r="F34" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E34)</f>
+      <c r="F34" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E34,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G34" s="7" t="n">
         <v>2503.11</v>
       </c>
     </row>
@@ -11767,12 +11856,10 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A35)</f>
+      <c r="B35" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C35" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A35,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C35" s="7" t="n">
         <v>5149.95</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -11780,12 +11867,10 @@
           <t>Former Employee Assignment</t>
         </is>
       </c>
-      <c r="F35" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E35)</f>
+      <c r="F35" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="G35" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E35,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G35" s="7" t="n">
         <v>22627.56</v>
       </c>
     </row>
@@ -11795,12 +11880,10 @@
           <t>Denver</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A36)</f>
+      <c r="B36" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C36" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A36,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C36" s="7" t="n">
         <v>5551.75</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -11808,12 +11891,10 @@
           <t>Inventory-to-Ledger Difference</t>
         </is>
       </c>
-      <c r="F36" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E36)</f>
+      <c r="F36" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="G36" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E36,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G36" s="7" t="n">
         <v>7275</v>
       </c>
     </row>
@@ -11823,12 +11904,10 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A37)</f>
+      <c r="B37" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C37" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A37,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C37" s="7" t="n">
         <v>10526</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -11836,12 +11915,10 @@
           <t>Missing Disposal Evidence</t>
         </is>
       </c>
-      <c r="F37" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E37)</f>
+      <c r="F37" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G37" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E37,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G37" s="7" t="n">
         <v>4811.33</v>
       </c>
     </row>
@@ -11851,12 +11928,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A38)</f>
+      <c r="B38" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C38" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A38,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C38" s="7" t="n">
         <v>6214.38</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -11864,12 +11939,10 @@
           <t>Overdue Return</t>
         </is>
       </c>
-      <c r="F38" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E38)</f>
+      <c r="F38" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G38" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E38,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G38" s="7" t="n">
         <v>6191.65</v>
       </c>
     </row>
@@ -11879,12 +11952,10 @@
           <t>Remote - Former Employee</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A39)</f>
+      <c r="B39" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C39" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A39,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C39" s="7" t="n">
         <v>4878.51</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -11892,12 +11963,10 @@
           <t>Shipment Mismatch</t>
         </is>
       </c>
-      <c r="F39" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E39)</f>
+      <c r="F39" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E39,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G39" s="7" t="n">
         <v>2332.54</v>
       </c>
     </row>
@@ -11907,12 +11976,10 @@
           <t>Disposed</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A40)</f>
+      <c r="B40" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C40" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A40,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -11920,12 +11987,10 @@
           <t>Unapproved Transfer</t>
         </is>
       </c>
-      <c r="F40" s="7">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E40)</f>
+      <c r="F40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G40" s="7">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E40,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G40" s="7" t="n">
         <v>2869.32</v>
       </c>
     </row>
@@ -11935,12 +12000,10 @@
           <t>Atlanta Warehouse</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A41)</f>
+      <c r="B41" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A41,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C41" s="7" t="n">
         <v>4351.05</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -11948,12 +12011,10 @@
           <t>Below Capitalization Threshold</t>
         </is>
       </c>
-      <c r="F41">
-        <f>COUNTIF('Exception Register'!$B$5:$B$200,E41)</f>
+      <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41">
-        <f>SUMIF('Exception Register'!$B$5:$B$200,E41,'Exception Register'!$G$5:$G$200)</f>
+      <c r="G41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11963,12 +12024,10 @@
           <t>Carrier Network / Unverified</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A42)</f>
+      <c r="B42" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C42" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A42,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C42" s="7" t="n">
         <v>2332.54</v>
       </c>
     </row>
@@ -11978,12 +12037,10 @@
           <t>Disposed (certificate missing)</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>COUNTIF('Corrected Register'!$I$5:$I$200,A43)</f>
+      <c r="B43" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="7">
-        <f>SUMIF('Corrected Register'!$I$5:$I$200,A43,'Corrected Register'!$N$5:$N$200)</f>
+      <c r="C43" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12069,7 +12126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X136"/>
+  <dimension ref="A1:X199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -12288,8 +12345,7 @@
         <f>IFERROR(XLOOKUP(A5,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N5" s="7">
-        <f>IF(V5="","",V5)</f>
+      <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="7">
@@ -12390,8 +12446,7 @@
         <f>IFERROR(XLOOKUP(A6,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N6" s="7">
-        <f>IF(V6="","",V6)</f>
+      <c r="N6" s="7" t="n">
         <v>313.06</v>
       </c>
       <c r="O6" s="7">
@@ -12492,8 +12547,7 @@
         <f>IFERROR(XLOOKUP(A7,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N7" s="7">
-        <f>IF(V7="","",V7)</f>
+      <c r="N7" s="7" t="n">
         <v>597.83</v>
       </c>
       <c r="O7" s="7">
@@ -12594,8 +12648,7 @@
         <f>IFERROR(XLOOKUP(A8,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N8" s="7">
-        <f>IF(V8="","",V8)</f>
+      <c r="N8" s="7" t="n">
         <v>940.62</v>
       </c>
       <c r="O8" s="7">
@@ -12696,8 +12749,7 @@
         <f>IFERROR(XLOOKUP(A9,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N9" s="7">
-        <f>IF(V9="","",V9)</f>
+      <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="7">
@@ -12798,8 +12850,7 @@
         <f>IFERROR(XLOOKUP(A10,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N10" s="7">
-        <f>IF(V10="","",V10)</f>
+      <c r="N10" s="7" t="n">
         <v>459.94</v>
       </c>
       <c r="O10" s="7">
@@ -12900,9 +12951,8 @@
         <f>IFERROR(XLOOKUP(A11,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N11" s="7">
-        <f>IF(V11="","",V11)</f>
-        <v>632.68</v>
+      <c r="N11" s="7" t="n">
+        <v>632.6799999999999</v>
       </c>
       <c r="O11" s="7">
         <f>IFERROR(XLOOKUP(A11,'Source Ledger'!$B$5:$B$200,'Source Ledger'!$A$5:$A$200),"")</f>
@@ -13002,8 +13052,7 @@
         <f>IFERROR(XLOOKUP(A12,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N12" s="7">
-        <f>IF(V12="","",V12)</f>
+      <c r="N12" s="7" t="n">
         <v>1355.01</v>
       </c>
       <c r="O12" s="7">
@@ -13104,8 +13153,7 @@
         <f>IFERROR(XLOOKUP(A13,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N13" s="7">
-        <f>IF(V13="","",V13)</f>
+      <c r="N13" s="7" t="n">
         <v>109.33</v>
       </c>
       <c r="O13" s="7">
@@ -13206,8 +13254,7 @@
         <f>IFERROR(XLOOKUP(A14,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N14" s="7">
-        <f>IF(V14="","",V14)</f>
+      <c r="N14" s="7" t="n">
         <v>426.89</v>
       </c>
       <c r="O14" s="7">
@@ -13308,8 +13355,7 @@
         <f>IFERROR(XLOOKUP(A15,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N15" s="7">
-        <f>IF(V15="","",V15)</f>
+      <c r="N15" s="7" t="n">
         <v>882.5</v>
       </c>
       <c r="O15" s="7">
@@ -13410,8 +13456,7 @@
         <f>IFERROR(XLOOKUP(A16,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N16" s="7">
-        <f>IF(V16="","",V16)</f>
+      <c r="N16" s="7" t="n">
         <v>553.23</v>
       </c>
       <c r="O16" s="7">
@@ -13512,8 +13557,7 @@
         <f>IFERROR(XLOOKUP(A17,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N17" s="7">
-        <f>IF(V17="","",V17)</f>
+      <c r="N17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="7">
@@ -13614,8 +13658,7 @@
         <f>IFERROR(XLOOKUP(A18,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N18" s="7">
-        <f>IF(V18="","",V18)</f>
+      <c r="N18" s="7" t="n">
         <v>270.29</v>
       </c>
       <c r="O18" s="7">
@@ -13716,8 +13759,7 @@
         <f>IFERROR(XLOOKUP(A19,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N19" s="7">
-        <f>IF(V19="","",V19)</f>
+      <c r="N19" s="7" t="n">
         <v>559.13</v>
       </c>
       <c r="O19" s="7">
@@ -13818,9 +13860,8 @@
         <f>IFERROR(XLOOKUP(A20,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N20" s="7">
-        <f>IF(V20="","",V20)</f>
-        <v>968.69</v>
+      <c r="N20" s="7" t="n">
+        <v>968.6900000000001</v>
       </c>
       <c r="O20" s="7">
         <f>IFERROR(XLOOKUP(A20,'Source Ledger'!$B$5:$B$200,'Source Ledger'!$A$5:$A$200),"")</f>
@@ -13920,8 +13961,7 @@
         <f>IFERROR(XLOOKUP(A21,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N21" s="7">
-        <f>IF(V21="","",V21)</f>
+      <c r="N21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="7">
@@ -14026,8 +14066,7 @@
         <f>IFERROR(XLOOKUP(A22,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N22" s="7">
-        <f>IF(V22="","",V22)</f>
+      <c r="N22" s="7" t="n">
         <v>412.14</v>
       </c>
       <c r="O22" s="7">
@@ -14128,8 +14167,7 @@
         <f>IFERROR(XLOOKUP(A23,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N23" s="7">
-        <f>IF(V23="","",V23)</f>
+      <c r="N23" s="7" t="n">
         <v>795.4</v>
       </c>
       <c r="O23" s="7">
@@ -14230,8 +14268,7 @@
         <f>IFERROR(XLOOKUP(A24,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N24" s="7">
-        <f>IF(V24="","",V24)</f>
+      <c r="N24" s="7" t="n">
         <v>1446.34</v>
       </c>
       <c r="O24" s="7">
@@ -14332,8 +14369,7 @@
         <f>IFERROR(XLOOKUP(A25,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N25" s="7">
-        <f>IF(V25="","",V25)</f>
+      <c r="N25" s="7" t="n">
         <v>124.52</v>
       </c>
       <c r="O25" s="7">
@@ -14438,8 +14474,7 @@
         <f>IFERROR(XLOOKUP(A26,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N26" s="7">
-        <f>IF(V26="","",V26)</f>
+      <c r="N26" s="7" t="n">
         <v>371.95</v>
       </c>
       <c r="O26" s="7">
@@ -14540,8 +14575,7 @@
         <f>IFERROR(XLOOKUP(A27,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N27" s="7">
-        <f>IF(V27="","",V27)</f>
+      <c r="N27" s="7" t="n">
         <v>823.6</v>
       </c>
       <c r="O27" s="7">
@@ -14642,8 +14676,7 @@
         <f>IFERROR(XLOOKUP(A28,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N28" s="7">
-        <f>IF(V28="","",V28)</f>
+      <c r="N28" s="7" t="n">
         <v>503.85</v>
       </c>
       <c r="O28" s="7">
@@ -14744,8 +14777,7 @@
         <f>IFERROR(XLOOKUP(A29,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N29" s="7">
-        <f>IF(V29="","",V29)</f>
+      <c r="N29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="7">
@@ -14850,8 +14882,7 @@
         <f>IFERROR(XLOOKUP(A30,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N30" s="7">
-        <f>IF(V30="","",V30)</f>
+      <c r="N30" s="7" t="n">
         <v>382.34</v>
       </c>
       <c r="O30" s="7">
@@ -14956,8 +14987,7 @@
         <f>IFERROR(XLOOKUP(A31,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N31" s="7">
-        <f>IF(V31="","",V31)</f>
+      <c r="N31" s="7" t="n">
         <v>672.21</v>
       </c>
       <c r="O31" s="7">
@@ -15062,8 +15092,7 @@
         <f>IFERROR(XLOOKUP(A32,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N32" s="7">
-        <f>IF(V32="","",V32)</f>
+      <c r="N32" s="7" t="n">
         <v>914.09</v>
       </c>
       <c r="O32" s="7">
@@ -15168,8 +15197,7 @@
         <f>IFERROR(XLOOKUP(A33,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N33" s="7">
-        <f>IF(V33="","",V33)</f>
+      <c r="N33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="7">
@@ -15274,8 +15302,7 @@
         <f>IFERROR(XLOOKUP(A34,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N34" s="7">
-        <f>IF(V34="","",V34)</f>
+      <c r="N34" s="7" t="n">
         <v>355.14</v>
       </c>
       <c r="O34" s="7">
@@ -15380,8 +15407,7 @@
         <f>IFERROR(XLOOKUP(A35,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N35" s="7">
-        <f>IF(V35="","",V35)</f>
+      <c r="N35" s="7" t="n">
         <v>722.59</v>
       </c>
       <c r="O35" s="7">
@@ -15486,8 +15512,7 @@
         <f>IFERROR(XLOOKUP(A36,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N36" s="7">
-        <f>IF(V36="","",V36)</f>
+      <c r="N36" s="7" t="n">
         <v>1384.3</v>
       </c>
       <c r="O36" s="7">
@@ -15592,8 +15617,7 @@
         <f>IFERROR(XLOOKUP(A37,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N37" s="7">
-        <f>IF(V37="","",V37)</f>
+      <c r="N37" s="7" t="n">
         <v>116.93</v>
       </c>
       <c r="O37" s="7">
@@ -15698,8 +15722,7 @@
         <f>IFERROR(XLOOKUP(A38,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N38" s="7">
-        <f>IF(V38="","",V38)</f>
+      <c r="N38" s="7" t="n">
         <v>479.88</v>
       </c>
       <c r="O38" s="7">
@@ -15804,8 +15827,7 @@
         <f>IFERROR(XLOOKUP(A39,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N39" s="7">
-        <f>IF(V39="","",V39)</f>
+      <c r="N39" s="7" t="n">
         <v>741.92</v>
       </c>
       <c r="O39" s="7">
@@ -15910,8 +15932,7 @@
         <f>IFERROR(XLOOKUP(A40,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N40" s="7">
-        <f>IF(V40="","",V40)</f>
+      <c r="N40" s="7" t="n">
         <v>537.73</v>
       </c>
       <c r="O40" s="7">
@@ -16016,8 +16037,7 @@
         <f>IFERROR(XLOOKUP(A41,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N41" s="7">
-        <f>IF(V41="","",V41)</f>
+      <c r="N41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="7">
@@ -16122,8 +16142,7 @@
         <f>IFERROR(XLOOKUP(A42,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N42" s="7">
-        <f>IF(V42="","",V42)</f>
+      <c r="N42" s="7" t="n">
         <v>340.46</v>
       </c>
       <c r="O42" s="7">
@@ -16228,8 +16247,7 @@
         <f>IFERROR(XLOOKUP(A43,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N43" s="7">
-        <f>IF(V43="","",V43)</f>
+      <c r="N43" s="7" t="n">
         <v>635</v>
       </c>
       <c r="O43" s="7">
@@ -16334,8 +16352,7 @@
         <f>IFERROR(XLOOKUP(A44,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N44" s="7">
-        <f>IF(V44="","",V44)</f>
+      <c r="N44" s="7" t="n">
         <v>989.48</v>
       </c>
       <c r="O44" s="7">
@@ -16440,8 +16457,7 @@
         <f>IFERROR(XLOOKUP(A45,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N45" s="7">
-        <f>IF(V45="","",V45)</f>
+      <c r="N45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="7">
@@ -16546,8 +16562,7 @@
         <f>IFERROR(XLOOKUP(A46,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N46" s="7">
-        <f>IF(V46="","",V46)</f>
+      <c r="N46" s="7" t="n">
         <v>306.16</v>
       </c>
       <c r="O46" s="7">
@@ -16652,8 +16667,7 @@
         <f>IFERROR(XLOOKUP(A47,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N47" s="7">
-        <f>IF(V47="","",V47)</f>
+      <c r="N47" s="7" t="n">
         <v>673.55</v>
       </c>
       <c r="O47" s="7">
@@ -16758,8 +16772,7 @@
         <f>IFERROR(XLOOKUP(A48,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N48" s="7">
-        <f>IF(V48="","",V48)</f>
+      <c r="N48" s="7" t="n">
         <v>1406.1</v>
       </c>
       <c r="O48" s="7">
@@ -16864,8 +16877,7 @@
         <f>IFERROR(XLOOKUP(A49,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N49" s="7">
-        <f>IF(V49="","",V49)</f>
+      <c r="N49" s="7" t="n">
         <v>133.6</v>
       </c>
       <c r="O49" s="7">
@@ -16970,8 +16982,7 @@
         <f>IFERROR(XLOOKUP(A50,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N50" s="7">
-        <f>IF(V50="","",V50)</f>
+      <c r="N50" s="7" t="n">
         <v>460.82</v>
       </c>
       <c r="O50" s="7">
@@ -17076,8 +17087,7 @@
         <f>IFERROR(XLOOKUP(A51,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N51" s="7">
-        <f>IF(V51="","",V51)</f>
+      <c r="N51" s="7" t="n">
         <v>930.51</v>
       </c>
       <c r="O51" s="7">
@@ -17182,8 +17192,7 @@
         <f>IFERROR(XLOOKUP(A52,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N52" s="7">
-        <f>IF(V52="","",V52)</f>
+      <c r="N52" s="7" t="n">
         <v>514.59</v>
       </c>
       <c r="O52" s="7">
@@ -17288,8 +17297,7 @@
         <f>IFERROR(XLOOKUP(A53,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N53" s="7">
-        <f>IF(V53="","",V53)</f>
+      <c r="N53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="7">
@@ -17394,8 +17402,7 @@
         <f>IFERROR(XLOOKUP(A54,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N54" s="7">
-        <f>IF(V54="","",V54)</f>
+      <c r="N54" s="7" t="n">
         <v>289.96</v>
       </c>
       <c r="O54" s="7">
@@ -17500,8 +17507,7 @@
         <f>IFERROR(XLOOKUP(A55,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N55" s="7">
-        <f>IF(V55="","",V55)</f>
+      <c r="N55" s="7" t="n">
         <v>573.03</v>
       </c>
       <c r="O55" s="7">
@@ -17606,8 +17612,7 @@
         <f>IFERROR(XLOOKUP(A56,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N56" s="7">
-        <f>IF(V56="","",V56)</f>
+      <c r="N56" s="7" t="n">
         <v>933.99</v>
       </c>
       <c r="O56" s="7">
@@ -17712,8 +17717,7 @@
         <f>IFERROR(XLOOKUP(A57,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N57" s="7">
-        <f>IF(V57="","",V57)</f>
+      <c r="N57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="7">
@@ -17818,8 +17822,7 @@
         <f>IFERROR(XLOOKUP(A58,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N58" s="7">
-        <f>IF(V58="","",V58)</f>
+      <c r="N58" s="7" t="n">
         <v>433.74</v>
       </c>
       <c r="O58" s="7">
@@ -17924,8 +17927,7 @@
         <f>IFERROR(XLOOKUP(A59,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N59" s="7">
-        <f>IF(V59="","",V59)</f>
+      <c r="N59" s="7" t="n">
         <v>812.5</v>
       </c>
       <c r="O59" s="7">
@@ -18030,8 +18032,7 @@
         <f>IFERROR(XLOOKUP(A60,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N60" s="7">
-        <f>IF(V60="","",V60)</f>
+      <c r="N60" s="7" t="n">
         <v>1345.24</v>
       </c>
       <c r="O60" s="7">
@@ -18136,8 +18137,7 @@
         <f>IFERROR(XLOOKUP(A61,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N61" s="7">
-        <f>IF(V61="","",V61)</f>
+      <c r="N61" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="O61" s="7">
@@ -18242,8 +18242,7 @@
         <f>IFERROR(XLOOKUP(A62,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N62" s="7">
-        <f>IF(V62="","",V62)</f>
+      <c r="N62" s="7" t="n">
         <v>397.56</v>
       </c>
       <c r="O62" s="7">
@@ -18348,8 +18347,7 @@
         <f>IFERROR(XLOOKUP(A63,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N63" s="7">
-        <f>IF(V63="","",V63)</f>
+      <c r="N63" s="7" t="n">
         <v>847.35</v>
       </c>
       <c r="O63" s="7">
@@ -18454,8 +18452,7 @@
         <f>IFERROR(XLOOKUP(A64,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N64" s="7">
-        <f>IF(V64="","",V64)</f>
+      <c r="N64" s="7" t="n">
         <v>549.35</v>
       </c>
       <c r="O64" s="7">
@@ -18560,8 +18557,7 @@
         <f>IFERROR(XLOOKUP(A65,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N65" s="7">
-        <f>IF(V65="","",V65)</f>
+      <c r="N65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O65" s="7">
@@ -18666,8 +18662,7 @@
         <f>IFERROR(XLOOKUP(A66,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N66" s="7">
-        <f>IF(V66="","",V66)</f>
+      <c r="N66" s="7" t="n">
         <v>410.63</v>
       </c>
       <c r="O66" s="7">
@@ -18772,8 +18767,7 @@
         <f>IFERROR(XLOOKUP(A67,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N67" s="7">
-        <f>IF(V67="","",V67)</f>
+      <c r="N67" s="7" t="n">
         <v>533.85</v>
       </c>
       <c r="O67" s="7">
@@ -18878,8 +18872,7 @@
         <f>IFERROR(XLOOKUP(A68,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N68" s="7">
-        <f>IF(V68="","",V68)</f>
+      <c r="N68" s="7" t="n">
         <v>961.76</v>
       </c>
       <c r="O68" s="7">
@@ -18984,8 +18977,7 @@
         <f>IFERROR(XLOOKUP(A69,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N69" s="7">
-        <f>IF(V69="","",V69)</f>
+      <c r="N69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="7">
@@ -19090,8 +19082,7 @@
         <f>IFERROR(XLOOKUP(A70,'Source Inventory'!$A$5:$A$200,'Source Inventory'!$H$5:$H$200),"")</f>
         <v/>
       </c>
-      <c r="N70" s="7">
-        <f>IF(V70="","",V70)</f>
+      <c r="N70" s="7" t="n">
         <v>385.65</v>
       </c>
       <c r="O70" s="7">
@@ -19196,9 +19187,8 @@
         <f>IFERROR(XLOOKUP(A71,'Source Inventory'!$A$5:$A$